--- a/data_printer.xlsx
+++ b/data_printer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erick\Desktop\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D0DEE9-8DF1-4B3D-AAE3-3B6FE667979A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7675D2F-7780-4ACC-90ED-52C8BEDF4187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A8AA41B5-7AA1-4FF7-A9B8-54B8A4E1AF28}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4369" uniqueCount="1316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4370" uniqueCount="1318">
   <si>
     <t>INDICE</t>
   </si>
@@ -3986,13 +3986,19 @@
   </si>
   <si>
     <t>XAABR75657</t>
+  </si>
+  <si>
+    <t>LUCIANA</t>
+  </si>
+  <si>
+    <t>Retirada do andre Gomes depois de ter danificado a impressora assim danificando os sensores de papel.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4165,7 +4171,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4310,13 +4316,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -5013,7 +5012,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}" name="Controle_Inventario_Impressoras" displayName="Controle_Inventario_Impressoras" ref="A1:J499" tableType="queryTable" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57">
-  <autoFilter ref="A1:J499" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}"/>
+  <autoFilter ref="A1:J499" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="SEDUC"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J27">
     <sortCondition ref="A13"/>
   </sortState>
@@ -5365,7 +5370,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD39631B-97B8-405A-AA43-14CDFBC77F92}">
   <dimension ref="A1:J499"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33.109375" style="2" bestFit="1" customWidth="1"/>
@@ -5380,7 +5385,7 @@
     <col min="11" max="16384" width="9.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5412,7 +5417,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" hidden="1">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -5444,7 +5449,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" hidden="1">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -5476,7 +5481,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" hidden="1">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -5508,7 +5513,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" hidden="1">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -5540,7 +5545,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" hidden="1">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -5572,7 +5577,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" hidden="1">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -5604,7 +5609,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" hidden="1">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -5636,7 +5641,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" hidden="1">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -5666,7 +5671,7 @@
       </c>
       <c r="J9" s="7"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" hidden="1">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -5696,7 +5701,7 @@
       </c>
       <c r="J10" s="7"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -5728,7 +5733,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" hidden="1">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -5760,7 +5765,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" hidden="1">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -5792,7 +5797,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" hidden="1">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -5824,7 +5829,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" hidden="1">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -5856,7 +5861,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" hidden="1">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -5885,7 +5890,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" hidden="1">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -5917,7 +5922,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" hidden="1">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -5949,7 +5954,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" hidden="1">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -5981,7 +5986,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -6013,7 +6018,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" hidden="1">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -6045,7 +6050,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" ht="15.75" hidden="1" customHeight="1">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -6077,7 +6082,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" hidden="1">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -6109,7 +6114,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" hidden="1">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -6141,7 +6146,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" hidden="1">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -6173,7 +6178,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" hidden="1">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -6202,7 +6207,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" hidden="1">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -6231,7 +6236,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" hidden="1">
       <c r="A28" s="4">
         <v>27</v>
       </c>
@@ -6263,7 +6268,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" hidden="1">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -6295,7 +6300,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" hidden="1">
       <c r="A30" s="4">
         <v>29</v>
       </c>
@@ -6327,7 +6332,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" hidden="1">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -6359,7 +6364,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" hidden="1">
       <c r="A32" s="4">
         <v>31</v>
       </c>
@@ -6391,7 +6396,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" hidden="1">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -6423,7 +6428,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" hidden="1">
       <c r="A34" s="4">
         <v>33</v>
       </c>
@@ -6455,7 +6460,7 @@
         <v>1297</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" hidden="1">
       <c r="A35" s="4">
         <v>34</v>
       </c>
@@ -6487,7 +6492,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" hidden="1">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -6519,7 +6524,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" hidden="1">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -6548,7 +6553,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" hidden="1">
       <c r="A38" s="4">
         <v>37</v>
       </c>
@@ -6580,7 +6585,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" hidden="1">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -6612,7 +6617,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" hidden="1">
       <c r="A40" s="4">
         <v>39</v>
       </c>
@@ -6644,7 +6649,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" hidden="1">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -6676,7 +6681,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" hidden="1">
       <c r="A42" s="4">
         <v>41</v>
       </c>
@@ -6708,7 +6713,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" hidden="1">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -6740,7 +6745,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" hidden="1">
       <c r="A44" s="4">
         <v>43</v>
       </c>
@@ -6772,7 +6777,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" hidden="1">
       <c r="A45" s="4">
         <v>44</v>
       </c>
@@ -6801,7 +6806,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" hidden="1">
       <c r="A46" s="4">
         <v>45</v>
       </c>
@@ -6833,7 +6838,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" hidden="1">
       <c r="A47" s="4">
         <v>46</v>
       </c>
@@ -6865,7 +6870,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" hidden="1">
       <c r="A48" s="4">
         <v>47</v>
       </c>
@@ -6897,7 +6902,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" hidden="1">
       <c r="A49" s="4">
         <v>48</v>
       </c>
@@ -6926,7 +6931,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" hidden="1">
       <c r="A50" s="4">
         <v>49</v>
       </c>
@@ -6955,7 +6960,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" hidden="1">
       <c r="A51" s="4">
         <v>50</v>
       </c>
@@ -6987,7 +6992,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" hidden="1">
       <c r="A52" s="4">
         <v>51</v>
       </c>
@@ -7019,7 +7024,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" hidden="1">
       <c r="A53" s="4">
         <v>52</v>
       </c>
@@ -7051,7 +7056,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" hidden="1">
       <c r="A54" s="4">
         <v>53</v>
       </c>
@@ -7083,7 +7088,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" hidden="1">
       <c r="A55" s="4">
         <v>54</v>
       </c>
@@ -7112,7 +7117,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" hidden="1">
       <c r="A56" s="4">
         <v>55</v>
       </c>
@@ -7141,7 +7146,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" hidden="1">
       <c r="A57" s="4">
         <v>56</v>
       </c>
@@ -7170,7 +7175,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" hidden="1">
       <c r="A58" s="4">
         <v>57</v>
       </c>
@@ -7199,7 +7204,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" hidden="1">
       <c r="A59" s="4">
         <v>58</v>
       </c>
@@ -7228,7 +7233,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" hidden="1">
       <c r="A60" s="4">
         <v>59</v>
       </c>
@@ -7257,7 +7262,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" hidden="1">
       <c r="A61" s="4">
         <v>60</v>
       </c>
@@ -7289,7 +7294,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" hidden="1">
       <c r="A62" s="4">
         <v>61</v>
       </c>
@@ -7321,7 +7326,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" hidden="1">
       <c r="A63" s="4">
         <v>62</v>
       </c>
@@ -7350,7 +7355,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" hidden="1">
       <c r="A64" s="4">
         <v>63</v>
       </c>
@@ -7382,7 +7387,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" hidden="1">
       <c r="A65" s="4">
         <v>64</v>
       </c>
@@ -7411,7 +7416,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" hidden="1">
       <c r="A66" s="4">
         <v>65</v>
       </c>
@@ -7440,7 +7445,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" hidden="1">
       <c r="A67" s="4">
         <v>66</v>
       </c>
@@ -7469,7 +7474,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" hidden="1">
       <c r="A68" s="4">
         <v>67</v>
       </c>
@@ -7498,7 +7503,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" hidden="1">
       <c r="A69" s="4">
         <v>68</v>
       </c>
@@ -7530,7 +7535,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" hidden="1">
       <c r="A70" s="4">
         <v>69</v>
       </c>
@@ -7562,7 +7567,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" hidden="1">
       <c r="A71" s="4">
         <v>70</v>
       </c>
@@ -7591,7 +7596,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10">
       <c r="A72" s="4">
         <v>71</v>
       </c>
@@ -7623,7 +7628,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" hidden="1">
       <c r="A73" s="4">
         <v>72</v>
       </c>
@@ -7655,7 +7660,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" hidden="1">
       <c r="A74" s="4">
         <v>73</v>
       </c>
@@ -7687,7 +7692,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" hidden="1">
       <c r="A75" s="4">
         <v>74</v>
       </c>
@@ -7716,7 +7721,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" hidden="1">
       <c r="A76" s="4">
         <v>75</v>
       </c>
@@ -7748,7 +7753,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" hidden="1">
       <c r="A77" s="4">
         <v>76</v>
       </c>
@@ -7780,7 +7785,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" hidden="1">
       <c r="A78" s="4">
         <v>77</v>
       </c>
@@ -7812,7 +7817,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" hidden="1">
       <c r="A79" s="4">
         <v>78</v>
       </c>
@@ -7844,7 +7849,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" hidden="1">
       <c r="A80" s="4">
         <v>79</v>
       </c>
@@ -7876,7 +7881,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" hidden="1">
       <c r="A81" s="4">
         <v>80</v>
       </c>
@@ -7908,7 +7913,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" hidden="1">
       <c r="A82" s="4">
         <v>81</v>
       </c>
@@ -7934,7 +7939,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" hidden="1">
       <c r="A83" s="4">
         <v>82</v>
       </c>
@@ -7960,7 +7965,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" hidden="1">
       <c r="A84" s="4">
         <v>83</v>
       </c>
@@ -7986,7 +7991,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" hidden="1">
       <c r="A85" s="4">
         <v>84</v>
       </c>
@@ -8018,7 +8023,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10" hidden="1">
       <c r="A86" s="4">
         <v>85</v>
       </c>
@@ -8050,7 +8055,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" hidden="1">
       <c r="A87" s="4">
         <v>86</v>
       </c>
@@ -8082,7 +8087,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10" hidden="1">
       <c r="A88" s="4">
         <v>87</v>
       </c>
@@ -8114,7 +8119,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" hidden="1">
       <c r="A89" s="4">
         <v>88</v>
       </c>
@@ -8143,7 +8148,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" hidden="1">
       <c r="A90" s="4">
         <v>89</v>
       </c>
@@ -8175,7 +8180,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10" hidden="1">
       <c r="A91" s="4">
         <v>90</v>
       </c>
@@ -8207,7 +8212,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" hidden="1">
       <c r="A92" s="4">
         <v>91</v>
       </c>
@@ -8233,7 +8238,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" hidden="1">
       <c r="A93" s="4">
         <v>92</v>
       </c>
@@ -8259,7 +8264,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" hidden="1">
       <c r="A94" s="4">
         <v>93</v>
       </c>
@@ -8291,7 +8296,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" hidden="1">
       <c r="A95" s="4">
         <v>94</v>
       </c>
@@ -8320,7 +8325,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10" hidden="1">
       <c r="A96" s="4">
         <v>95</v>
       </c>
@@ -8349,7 +8354,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10" hidden="1">
       <c r="A97" s="4">
         <v>96</v>
       </c>
@@ -8378,7 +8383,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10" hidden="1">
       <c r="A98" s="4">
         <v>97</v>
       </c>
@@ -8407,7 +8412,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:10" hidden="1">
       <c r="A99" s="4">
         <v>98</v>
       </c>
@@ -8439,7 +8444,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:10" hidden="1">
       <c r="A100" s="4">
         <v>99</v>
       </c>
@@ -8471,7 +8476,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:10" hidden="1">
       <c r="A101" s="4">
         <v>100</v>
       </c>
@@ -8503,7 +8508,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:10" hidden="1">
       <c r="A102" s="4">
         <v>101</v>
       </c>
@@ -8535,7 +8540,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:10" hidden="1">
       <c r="A103" s="4">
         <v>102</v>
       </c>
@@ -8567,7 +8572,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:10" hidden="1">
       <c r="A104" s="4">
         <v>103</v>
       </c>
@@ -8599,7 +8604,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:10" hidden="1">
       <c r="A105" s="4">
         <v>104</v>
       </c>
@@ -8631,7 +8636,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:10" hidden="1">
       <c r="A106" s="4">
         <v>105</v>
       </c>
@@ -8663,7 +8668,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:10" hidden="1">
       <c r="A107" s="4">
         <v>106</v>
       </c>
@@ -8695,7 +8700,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:10" hidden="1">
       <c r="A108" s="4">
         <v>107</v>
       </c>
@@ -8723,7 +8728,7 @@
       </c>
       <c r="J108" s="24"/>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:10" hidden="1">
       <c r="A109" s="4">
         <v>108</v>
       </c>
@@ -8755,7 +8760,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:10" hidden="1">
       <c r="A110" s="4">
         <v>109</v>
       </c>
@@ -8787,7 +8792,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:10" hidden="1">
       <c r="A111" s="4">
         <v>110</v>
       </c>
@@ -8819,7 +8824,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:10" hidden="1">
       <c r="A112" s="4">
         <v>111</v>
       </c>
@@ -8851,7 +8856,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:10" hidden="1">
       <c r="A113" s="4">
         <v>112</v>
       </c>
@@ -8883,7 +8888,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:10" hidden="1">
       <c r="A114" s="4">
         <v>113</v>
       </c>
@@ -8915,7 +8920,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:10" hidden="1">
       <c r="A115" s="4">
         <v>114</v>
       </c>
@@ -8947,7 +8952,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10" hidden="1">
       <c r="A116" s="4">
         <v>115</v>
       </c>
@@ -8979,7 +8984,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:10" hidden="1">
       <c r="A117" s="4">
         <v>116</v>
       </c>
@@ -9011,7 +9016,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:10" hidden="1">
       <c r="A118" s="4">
         <v>117</v>
       </c>
@@ -9043,7 +9048,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10" hidden="1">
       <c r="A119" s="4">
         <v>118</v>
       </c>
@@ -9075,7 +9080,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:10" hidden="1">
       <c r="A120" s="4">
         <v>119</v>
       </c>
@@ -9107,7 +9112,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10" hidden="1">
       <c r="A121" s="4">
         <v>120</v>
       </c>
@@ -9139,7 +9144,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:10" hidden="1">
       <c r="A122" s="4">
         <v>121</v>
       </c>
@@ -9171,7 +9176,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:10" hidden="1">
       <c r="A123" s="4">
         <v>122</v>
       </c>
@@ -9203,7 +9208,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:10" hidden="1">
       <c r="A124" s="4">
         <v>123</v>
       </c>
@@ -9235,7 +9240,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10" hidden="1">
       <c r="A125" s="4">
         <v>124</v>
       </c>
@@ -9267,7 +9272,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:10">
       <c r="A126" s="4">
         <v>125</v>
       </c>
@@ -9299,7 +9304,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:10" hidden="1">
       <c r="A127" s="4">
         <v>126</v>
       </c>
@@ -9331,7 +9336,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:10" hidden="1">
       <c r="A128" s="4">
         <v>127</v>
       </c>
@@ -9363,7 +9368,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:10" hidden="1">
       <c r="A129" s="4">
         <v>128</v>
       </c>
@@ -9395,7 +9400,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:10" hidden="1">
       <c r="A130" s="4">
         <v>129</v>
       </c>
@@ -9427,7 +9432,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:10" hidden="1">
       <c r="A131" s="4">
         <v>130</v>
       </c>
@@ -9459,7 +9464,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:10">
       <c r="A132" s="4">
         <v>131</v>
       </c>
@@ -9491,7 +9496,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:10">
       <c r="A133" s="4">
         <v>132</v>
       </c>
@@ -9523,7 +9528,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:10">
       <c r="A134" s="4">
         <v>133</v>
       </c>
@@ -9555,7 +9560,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:10" hidden="1">
       <c r="A135" s="4">
         <v>134</v>
       </c>
@@ -9587,7 +9592,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:10">
       <c r="A136" s="4">
         <v>135</v>
       </c>
@@ -9619,7 +9624,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:10" hidden="1">
       <c r="A137" s="4">
         <v>136</v>
       </c>
@@ -9651,7 +9656,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:10" hidden="1">
       <c r="A138" s="4">
         <v>137</v>
       </c>
@@ -9683,7 +9688,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:10" hidden="1">
       <c r="A139" s="4">
         <v>138</v>
       </c>
@@ -9715,7 +9720,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:10" hidden="1">
       <c r="A140" s="4">
         <v>139</v>
       </c>
@@ -9747,7 +9752,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:10" hidden="1">
       <c r="A141" s="4">
         <v>140</v>
       </c>
@@ -9779,7 +9784,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:10" hidden="1">
       <c r="A142" s="4">
         <v>141</v>
       </c>
@@ -9811,7 +9816,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:10" hidden="1">
       <c r="A143" s="4">
         <v>142</v>
       </c>
@@ -9841,7 +9846,7 @@
       </c>
       <c r="J143" s="24"/>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:10" hidden="1">
       <c r="A144" s="4">
         <v>143</v>
       </c>
@@ -9873,7 +9878,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:10" hidden="1">
       <c r="A145" s="4">
         <v>144</v>
       </c>
@@ -9905,7 +9910,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:10" hidden="1">
       <c r="A146" s="4">
         <v>145</v>
       </c>
@@ -9937,7 +9942,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:10">
       <c r="A147" s="4">
         <v>146</v>
       </c>
@@ -9969,7 +9974,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:10" hidden="1">
       <c r="A148" s="4">
         <v>147</v>
       </c>
@@ -10001,7 +10006,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:10" hidden="1">
       <c r="A149" s="4">
         <v>148</v>
       </c>
@@ -10033,7 +10038,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:10">
       <c r="A150" s="4">
         <v>149</v>
       </c>
@@ -10065,7 +10070,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:10">
       <c r="A151" s="4">
         <v>150</v>
       </c>
@@ -10097,7 +10102,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:10">
       <c r="A152" s="4">
         <v>151</v>
       </c>
@@ -10127,7 +10132,7 @@
       </c>
       <c r="J152" s="24"/>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:10">
       <c r="A153" s="4">
         <v>152</v>
       </c>
@@ -10157,7 +10162,7 @@
       </c>
       <c r="J153" s="24"/>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:10">
       <c r="A154" s="4">
         <v>153</v>
       </c>
@@ -10189,7 +10194,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:10" hidden="1">
       <c r="A155" s="4">
         <v>154</v>
       </c>
@@ -10221,7 +10226,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:10" hidden="1">
       <c r="A156" s="4">
         <v>155</v>
       </c>
@@ -10253,8 +10258,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A157" s="54"/>
+    <row r="157" spans="1:10" hidden="1">
       <c r="B157" s="2" t="s">
         <v>244</v>
       </c>
@@ -10267,23 +10271,23 @@
       <c r="E157" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F157" s="54" t="s">
+      <c r="F157" s="1" t="s">
         <v>1313</v>
       </c>
       <c r="G157" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H157" s="55">
+      <c r="H157" s="9">
         <v>46211</v>
       </c>
-      <c r="I157" s="55" t="s">
-        <v>575</v>
-      </c>
-      <c r="J157" s="56" t="s">
+      <c r="I157" s="9" t="s">
+        <v>575</v>
+      </c>
+      <c r="J157" s="3" t="s">
         <v>1314</v>
       </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:10" hidden="1">
       <c r="A158" s="4">
         <v>156</v>
       </c>
@@ -10315,7 +10319,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:10" hidden="1">
       <c r="A159" s="4">
         <v>157</v>
       </c>
@@ -10347,7 +10351,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:10" hidden="1">
       <c r="A160" s="4">
         <v>158</v>
       </c>
@@ -10379,7 +10383,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:10" hidden="1">
       <c r="A161" s="4">
         <v>159</v>
       </c>
@@ -10411,7 +10415,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:10" hidden="1">
       <c r="A162" s="4">
         <v>160</v>
       </c>
@@ -10443,7 +10447,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:10" hidden="1">
       <c r="A163" s="4">
         <v>161</v>
       </c>
@@ -10475,7 +10479,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:10" hidden="1">
       <c r="A164" s="4">
         <v>162</v>
       </c>
@@ -10507,7 +10511,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:10" hidden="1">
       <c r="A165" s="4">
         <v>163</v>
       </c>
@@ -10536,7 +10540,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:10" hidden="1">
       <c r="A166" s="4">
         <v>164</v>
       </c>
@@ -10565,7 +10569,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:10" hidden="1">
       <c r="A167" s="4">
         <v>165</v>
       </c>
@@ -10592,7 +10596,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:10" hidden="1">
       <c r="A168" s="4">
         <v>166</v>
       </c>
@@ -10624,7 +10628,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:10" hidden="1">
       <c r="A169" s="4">
         <v>167</v>
       </c>
@@ -10653,7 +10657,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:10" hidden="1">
       <c r="A170" s="4">
         <v>168</v>
       </c>
@@ -10685,7 +10689,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:10" hidden="1">
       <c r="A171" s="4">
         <v>169</v>
       </c>
@@ -10717,7 +10721,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:10" hidden="1">
       <c r="A172" s="4">
         <v>170</v>
       </c>
@@ -10749,7 +10753,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:10" hidden="1">
       <c r="A173" s="4">
         <v>171</v>
       </c>
@@ -10781,7 +10785,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:10" hidden="1">
       <c r="A174" s="4">
         <v>172</v>
       </c>
@@ -10810,7 +10814,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:10" hidden="1">
       <c r="A175" s="4">
         <v>173</v>
       </c>
@@ -10839,7 +10843,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:10" hidden="1">
       <c r="A176" s="4">
         <v>174</v>
       </c>
@@ -10871,7 +10875,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:10" hidden="1">
       <c r="A177" s="4">
         <v>175</v>
       </c>
@@ -10897,7 +10901,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:10" hidden="1">
       <c r="A178" s="4">
         <v>176</v>
       </c>
@@ -10927,7 +10931,7 @@
       </c>
       <c r="J178" s="24"/>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:10" hidden="1">
       <c r="A179" s="4">
         <v>177</v>
       </c>
@@ -10959,7 +10963,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:10" hidden="1">
       <c r="A180" s="4">
         <v>178</v>
       </c>
@@ -10988,7 +10992,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:10" hidden="1">
       <c r="A181" s="4">
         <v>179</v>
       </c>
@@ -11020,7 +11024,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:10" hidden="1">
       <c r="A182" s="4">
         <v>180</v>
       </c>
@@ -11049,7 +11053,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:10" hidden="1">
       <c r="A183" s="4">
         <v>181</v>
       </c>
@@ -11078,7 +11082,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:10" hidden="1">
       <c r="A184" s="4">
         <v>182</v>
       </c>
@@ -11107,7 +11111,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:10" hidden="1">
       <c r="A185" s="4">
         <v>183</v>
       </c>
@@ -11136,7 +11140,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:10" hidden="1">
       <c r="A186" s="4">
         <v>184</v>
       </c>
@@ -11165,7 +11169,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:10" hidden="1">
       <c r="A187" s="4">
         <v>185</v>
       </c>
@@ -11194,7 +11198,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:10" hidden="1">
       <c r="A188" s="4">
         <v>186</v>
       </c>
@@ -11223,7 +11227,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:10" hidden="1">
       <c r="A189" s="4">
         <v>187</v>
       </c>
@@ -11252,7 +11256,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:10" hidden="1">
       <c r="A190" s="4">
         <v>188</v>
       </c>
@@ -11281,7 +11285,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:10" hidden="1">
       <c r="A191" s="4">
         <v>189</v>
       </c>
@@ -11310,7 +11314,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:10" hidden="1">
       <c r="A192" s="4">
         <v>190</v>
       </c>
@@ -11339,7 +11343,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:10" hidden="1">
       <c r="A193" s="4">
         <v>191</v>
       </c>
@@ -11368,7 +11372,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:10" hidden="1">
       <c r="A194" s="4">
         <v>192</v>
       </c>
@@ -11397,7 +11401,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:10" hidden="1">
       <c r="A195" s="4">
         <v>193</v>
       </c>
@@ -11426,7 +11430,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:10" hidden="1">
       <c r="A196" s="4">
         <v>194</v>
       </c>
@@ -11455,7 +11459,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:10" hidden="1">
       <c r="A197" s="4">
         <v>195</v>
       </c>
@@ -11484,7 +11488,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:10" hidden="1">
       <c r="A198" s="4">
         <v>196</v>
       </c>
@@ -11513,7 +11517,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:10" hidden="1">
       <c r="A199" s="4">
         <v>197</v>
       </c>
@@ -11542,7 +11546,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:10" hidden="1">
       <c r="A200" s="4">
         <v>198</v>
       </c>
@@ -11571,7 +11575,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:10" hidden="1">
       <c r="A201" s="4">
         <v>199</v>
       </c>
@@ -11600,7 +11604,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:10" hidden="1">
       <c r="A202" s="4">
         <v>200</v>
       </c>
@@ -11629,7 +11633,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:10" hidden="1">
       <c r="A203" s="4">
         <v>201</v>
       </c>
@@ -11658,7 +11662,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:10" hidden="1">
       <c r="A204" s="4">
         <v>202</v>
       </c>
@@ -11690,7 +11694,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:10" hidden="1">
       <c r="A205" s="4">
         <v>203</v>
       </c>
@@ -11722,7 +11726,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:10" hidden="1">
       <c r="A206" s="4">
         <v>204</v>
       </c>
@@ -11754,7 +11758,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:10" hidden="1">
       <c r="A207" s="4">
         <v>205</v>
       </c>
@@ -11786,7 +11790,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:10" hidden="1">
       <c r="A208" s="4">
         <v>206</v>
       </c>
@@ -11816,7 +11820,7 @@
       </c>
       <c r="J208" s="24"/>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:10" hidden="1">
       <c r="A209" s="4">
         <v>207</v>
       </c>
@@ -11848,7 +11852,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:10" hidden="1">
       <c r="A210" s="4">
         <v>208</v>
       </c>
@@ -11880,7 +11884,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:10" hidden="1">
       <c r="A211" s="4">
         <v>209</v>
       </c>
@@ -11912,7 +11916,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:10">
       <c r="A212" s="4">
         <v>210</v>
       </c>
@@ -11944,7 +11948,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:10" hidden="1">
       <c r="A213" s="4">
         <v>211</v>
       </c>
@@ -11976,7 +11980,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:10" hidden="1">
       <c r="A214" s="4">
         <v>212</v>
       </c>
@@ -12008,7 +12012,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:10">
       <c r="A215" s="4">
         <v>213</v>
       </c>
@@ -12022,10 +12026,10 @@
         <v>950</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>23</v>
+        <v>1056</v>
       </c>
       <c r="G215" s="1" t="s">
         <v>30</v>
@@ -12040,7 +12044,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:10" hidden="1">
       <c r="A216" s="4">
         <v>214</v>
       </c>
@@ -12072,7 +12076,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:10" hidden="1">
       <c r="A217" s="4">
         <v>215</v>
       </c>
@@ -12104,7 +12108,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:10">
       <c r="A218" s="4">
         <v>216</v>
       </c>
@@ -12136,7 +12140,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:10">
       <c r="A219" s="4">
         <v>217</v>
       </c>
@@ -12168,7 +12172,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:10" hidden="1">
       <c r="A220" s="4">
         <v>218</v>
       </c>
@@ -12200,7 +12204,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:10" hidden="1">
       <c r="A221" s="4">
         <v>219</v>
       </c>
@@ -12232,7 +12236,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:10" hidden="1">
       <c r="A222" s="4">
         <v>220</v>
       </c>
@@ -12264,7 +12268,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:10" hidden="1">
       <c r="A223" s="4">
         <v>221</v>
       </c>
@@ -12296,7 +12300,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:10" hidden="1">
       <c r="A224" s="4">
         <v>222</v>
       </c>
@@ -12328,7 +12332,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:10" hidden="1">
       <c r="A225" s="4">
         <v>223</v>
       </c>
@@ -12360,7 +12364,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:10" hidden="1">
       <c r="A226" s="4">
         <v>224</v>
       </c>
@@ -12392,7 +12396,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:10">
       <c r="A227" s="4">
         <v>225</v>
       </c>
@@ -12424,7 +12428,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:10" hidden="1">
       <c r="A228" s="4">
         <v>226</v>
       </c>
@@ -12456,7 +12460,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:10">
       <c r="A229" s="4">
         <v>227</v>
       </c>
@@ -12488,7 +12492,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:10" hidden="1">
       <c r="A230" s="4">
         <v>228</v>
       </c>
@@ -12520,7 +12524,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:10">
       <c r="A231" s="4">
         <v>229</v>
       </c>
@@ -12552,7 +12556,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:10" hidden="1">
       <c r="A232" s="4">
         <v>230</v>
       </c>
@@ -12584,7 +12588,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:10" hidden="1">
       <c r="A233" s="4">
         <v>231</v>
       </c>
@@ -12616,7 +12620,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:10">
       <c r="A234" s="4">
         <v>232</v>
       </c>
@@ -12648,7 +12652,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:10" hidden="1">
       <c r="A235" s="4">
         <v>233</v>
       </c>
@@ -12680,7 +12684,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:10" hidden="1">
       <c r="A236" s="4">
         <v>234</v>
       </c>
@@ -12712,7 +12716,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:10" hidden="1">
       <c r="A237" s="4">
         <v>235</v>
       </c>
@@ -12744,7 +12748,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:10">
       <c r="A238" s="4">
         <v>236</v>
       </c>
@@ -12776,7 +12780,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:10" hidden="1">
       <c r="A239" s="4">
         <v>237</v>
       </c>
@@ -12808,7 +12812,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:10" hidden="1">
       <c r="A240" s="4">
         <v>238</v>
       </c>
@@ -12840,7 +12844,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:10">
       <c r="A241" s="4">
         <v>239</v>
       </c>
@@ -12872,7 +12876,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="242" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:10" ht="15.6">
       <c r="A242" s="4">
         <v>240</v>
       </c>
@@ -12904,7 +12908,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:10">
       <c r="A243" s="4">
         <v>241</v>
       </c>
@@ -12936,7 +12940,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:10">
       <c r="A244" s="4">
         <v>242</v>
       </c>
@@ -12968,7 +12972,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:10">
       <c r="A245" s="4">
         <v>243</v>
       </c>
@@ -13000,7 +13004,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:10" hidden="1">
       <c r="A246" s="4">
         <v>244</v>
       </c>
@@ -13032,7 +13036,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:10" hidden="1">
       <c r="A247" s="4">
         <v>245</v>
       </c>
@@ -13062,7 +13066,7 @@
       </c>
       <c r="J247" s="20"/>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:10" hidden="1">
       <c r="A248" s="4">
         <v>246</v>
       </c>
@@ -13094,7 +13098,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:10" hidden="1">
       <c r="A249" s="4">
         <v>247</v>
       </c>
@@ -13126,7 +13130,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:10" hidden="1">
       <c r="A250" s="4">
         <v>248</v>
       </c>
@@ -13158,7 +13162,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:10" hidden="1">
       <c r="A251" s="4">
         <v>249</v>
       </c>
@@ -13190,7 +13194,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:10">
       <c r="A252" s="4">
         <v>250</v>
       </c>
@@ -13222,7 +13226,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:10" hidden="1">
       <c r="A253" s="4">
         <v>251</v>
       </c>
@@ -13251,7 +13255,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:10" hidden="1">
       <c r="A254" s="4">
         <v>252</v>
       </c>
@@ -13283,7 +13287,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:10" hidden="1">
       <c r="A255" s="4">
         <v>253</v>
       </c>
@@ -13315,7 +13319,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:10" hidden="1">
       <c r="A256" s="4">
         <v>254</v>
       </c>
@@ -13347,7 +13351,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:10" hidden="1">
       <c r="A257" s="4">
         <v>255</v>
       </c>
@@ -13376,7 +13380,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:10" hidden="1">
       <c r="A258" s="4">
         <v>256</v>
       </c>
@@ -13408,7 +13412,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:10" hidden="1">
       <c r="A259" s="4">
         <v>257</v>
       </c>
@@ -13437,7 +13441,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:10" hidden="1">
       <c r="A260" s="4">
         <v>258</v>
       </c>
@@ -13466,7 +13470,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:10" hidden="1">
       <c r="A261" s="4">
         <v>259</v>
       </c>
@@ -13498,7 +13502,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:10" hidden="1">
       <c r="A262" s="4">
         <v>260</v>
       </c>
@@ -13530,7 +13534,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:10">
       <c r="A263" s="4">
         <v>261</v>
       </c>
@@ -13562,7 +13566,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:10">
       <c r="A264" s="4">
         <v>262</v>
       </c>
@@ -13594,7 +13598,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:10" hidden="1">
       <c r="A265" s="4">
         <v>263</v>
       </c>
@@ -13626,7 +13630,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:10" hidden="1">
       <c r="A266" s="4">
         <v>264</v>
       </c>
@@ -13658,7 +13662,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:10" hidden="1">
       <c r="A267" s="4">
         <v>265</v>
       </c>
@@ -13690,7 +13694,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:10" hidden="1">
       <c r="A268" s="4">
         <v>266</v>
       </c>
@@ -13722,7 +13726,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:10" hidden="1">
       <c r="A269" s="4">
         <v>267</v>
       </c>
@@ -13754,7 +13758,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:10" hidden="1">
       <c r="A270" s="4">
         <v>268</v>
       </c>
@@ -13786,7 +13790,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:10" hidden="1">
       <c r="A271" s="4">
         <v>269</v>
       </c>
@@ -13818,7 +13822,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:10" hidden="1">
       <c r="A272" s="4">
         <v>270</v>
       </c>
@@ -13850,7 +13854,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:10" hidden="1">
       <c r="A273" s="4">
         <v>271</v>
       </c>
@@ -13882,7 +13886,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:10" hidden="1">
       <c r="A274" s="4">
         <v>272</v>
       </c>
@@ -13914,7 +13918,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:10" hidden="1">
       <c r="A275" s="4">
         <v>273</v>
       </c>
@@ -13946,7 +13950,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:10" hidden="1">
       <c r="A276" s="4">
         <v>274</v>
       </c>
@@ -13978,7 +13982,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:10" hidden="1">
       <c r="A277" s="4">
         <v>275</v>
       </c>
@@ -14010,7 +14014,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:10" hidden="1">
       <c r="A278" s="4">
         <v>276</v>
       </c>
@@ -14042,7 +14046,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:10" hidden="1">
       <c r="A279" s="4">
         <v>277</v>
       </c>
@@ -14074,7 +14078,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:10" hidden="1">
       <c r="A280" s="4">
         <v>278</v>
       </c>
@@ -14106,7 +14110,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:10" hidden="1">
       <c r="A281" s="4">
         <v>279</v>
       </c>
@@ -14138,7 +14142,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:10" hidden="1">
       <c r="A282" s="4">
         <v>280</v>
       </c>
@@ -14170,7 +14174,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:10" hidden="1">
       <c r="A283" s="4">
         <v>281</v>
       </c>
@@ -14202,7 +14206,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:10" hidden="1">
       <c r="A284" s="4">
         <v>282</v>
       </c>
@@ -14234,7 +14238,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:10" hidden="1">
       <c r="A285" s="4">
         <v>283</v>
       </c>
@@ -14266,7 +14270,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:10" hidden="1">
       <c r="A286" s="4">
         <v>284</v>
       </c>
@@ -14298,7 +14302,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:10" hidden="1">
       <c r="A287" s="4">
         <v>285</v>
       </c>
@@ -14330,7 +14334,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:10" hidden="1">
       <c r="A288" s="4">
         <v>286</v>
       </c>
@@ -14362,7 +14366,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:10" hidden="1">
       <c r="A289" s="4">
         <v>287</v>
       </c>
@@ -14394,7 +14398,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:10" hidden="1">
       <c r="A290" s="4">
         <v>288</v>
       </c>
@@ -14426,7 +14430,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:10" hidden="1">
       <c r="A291" s="4">
         <v>289</v>
       </c>
@@ -14458,7 +14462,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:10" hidden="1">
       <c r="A292" s="4">
         <v>290</v>
       </c>
@@ -14490,7 +14494,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:10" hidden="1">
       <c r="A293" s="4">
         <v>291</v>
       </c>
@@ -14522,7 +14526,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:10" hidden="1">
       <c r="A294" s="4">
         <v>292</v>
       </c>
@@ -14554,7 +14558,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:10" hidden="1">
       <c r="A295" s="4">
         <v>293</v>
       </c>
@@ -14586,7 +14590,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:10" hidden="1">
       <c r="A296" s="4">
         <v>294</v>
       </c>
@@ -14618,7 +14622,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:10" hidden="1">
       <c r="A297" s="4">
         <v>295</v>
       </c>
@@ -14650,7 +14654,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:10" hidden="1">
       <c r="A298" s="4">
         <v>296</v>
       </c>
@@ -14682,7 +14686,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:10" hidden="1">
       <c r="A299" s="4">
         <v>297</v>
       </c>
@@ -14714,7 +14718,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:10" hidden="1">
       <c r="A300" s="4">
         <v>298</v>
       </c>
@@ -14746,7 +14750,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:10" hidden="1">
       <c r="A301" s="4">
         <v>299</v>
       </c>
@@ -14778,7 +14782,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:10" hidden="1">
       <c r="A302" s="4">
         <v>300</v>
       </c>
@@ -14810,7 +14814,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:10" hidden="1">
       <c r="A303" s="4">
         <v>301</v>
       </c>
@@ -14842,7 +14846,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="304" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:10" hidden="1">
       <c r="A304" s="4">
         <v>302</v>
       </c>
@@ -14874,7 +14878,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:10" hidden="1">
       <c r="A305" s="4">
         <v>303</v>
       </c>
@@ -14906,7 +14910,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:10" hidden="1">
       <c r="A306" s="4">
         <v>304</v>
       </c>
@@ -14938,7 +14942,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:10" hidden="1">
       <c r="A307" s="4">
         <v>305</v>
       </c>
@@ -14970,7 +14974,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:10" hidden="1">
       <c r="A308" s="4">
         <v>306</v>
       </c>
@@ -15002,7 +15006,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:10" hidden="1">
       <c r="A309" s="4">
         <v>307</v>
       </c>
@@ -15034,7 +15038,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:10" hidden="1">
       <c r="A310" s="4">
         <v>308</v>
       </c>
@@ -15066,7 +15070,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:10" hidden="1">
       <c r="A311" s="4">
         <v>309</v>
       </c>
@@ -15098,7 +15102,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:10" hidden="1">
       <c r="A312" s="4">
         <v>310</v>
       </c>
@@ -15130,7 +15134,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:10" hidden="1">
       <c r="A313" s="4">
         <v>311</v>
       </c>
@@ -15162,7 +15166,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:10" hidden="1">
       <c r="A314" s="4">
         <v>312</v>
       </c>
@@ -15194,7 +15198,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:10" hidden="1">
       <c r="A315" s="4">
         <v>313</v>
       </c>
@@ -15226,7 +15230,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:10" hidden="1">
       <c r="A316" s="4">
         <v>314</v>
       </c>
@@ -15258,7 +15262,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:10" hidden="1">
       <c r="A317" s="4">
         <v>315</v>
       </c>
@@ -15290,7 +15294,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:10" hidden="1">
       <c r="A318" s="4">
         <v>316</v>
       </c>
@@ -15322,7 +15326,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:10" hidden="1">
       <c r="A319" s="4">
         <v>317</v>
       </c>
@@ -15354,7 +15358,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:10" hidden="1">
       <c r="A320" s="4">
         <v>318</v>
       </c>
@@ -15386,7 +15390,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:10" hidden="1">
       <c r="A321" s="4">
         <v>319</v>
       </c>
@@ -15418,7 +15422,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:10" hidden="1">
       <c r="A322" s="4">
         <v>320</v>
       </c>
@@ -15450,7 +15454,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:10" hidden="1">
       <c r="A323" s="4">
         <v>321</v>
       </c>
@@ -15482,7 +15486,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:10" hidden="1">
       <c r="A324" s="4">
         <v>322</v>
       </c>
@@ -15514,7 +15518,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:10" hidden="1">
       <c r="A325" s="4">
         <v>323</v>
       </c>
@@ -15546,7 +15550,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:10" hidden="1">
       <c r="A326" s="4">
         <v>324</v>
       </c>
@@ -15578,7 +15582,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:10" hidden="1">
       <c r="A327" s="4">
         <v>325</v>
       </c>
@@ -15610,7 +15614,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:10" hidden="1">
       <c r="A328" s="4">
         <v>326</v>
       </c>
@@ -15642,7 +15646,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:10" hidden="1">
       <c r="A329" s="4">
         <v>327</v>
       </c>
@@ -15674,7 +15678,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:10" hidden="1">
       <c r="A330" s="4">
         <v>328</v>
       </c>
@@ -15706,7 +15710,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:10" hidden="1">
       <c r="A331" s="4">
         <v>329</v>
       </c>
@@ -15738,7 +15742,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:10" hidden="1">
       <c r="A332" s="4">
         <v>330</v>
       </c>
@@ -15770,7 +15774,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:10" hidden="1">
       <c r="A333" s="4">
         <v>331</v>
       </c>
@@ -15802,7 +15806,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:10" hidden="1">
       <c r="A334" s="4">
         <v>332</v>
       </c>
@@ -15834,7 +15838,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:10" hidden="1">
       <c r="A335" s="4">
         <v>333</v>
       </c>
@@ -15866,7 +15870,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="336" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:10" hidden="1">
       <c r="A336" s="4">
         <v>334</v>
       </c>
@@ -15898,7 +15902,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="337" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:10" hidden="1">
       <c r="A337" s="4">
         <v>335</v>
       </c>
@@ -15930,7 +15934,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="338" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:10" hidden="1">
       <c r="A338" s="4">
         <v>336</v>
       </c>
@@ -15962,7 +15966,7 @@
         <v>1312</v>
       </c>
     </row>
-    <row r="339" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:10" hidden="1">
       <c r="A339" s="4">
         <v>337</v>
       </c>
@@ -15994,7 +15998,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="340" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:10" hidden="1">
       <c r="A340" s="4">
         <v>338</v>
       </c>
@@ -16026,7 +16030,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="341" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:10" hidden="1">
       <c r="A341" s="4">
         <v>339</v>
       </c>
@@ -16058,7 +16062,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="342" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:10" hidden="1">
       <c r="A342" s="4">
         <v>340</v>
       </c>
@@ -16090,7 +16094,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="343" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:10" hidden="1">
       <c r="A343" s="4">
         <v>341</v>
       </c>
@@ -16122,7 +16126,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="344" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:10" hidden="1">
       <c r="A344" s="4">
         <v>342</v>
       </c>
@@ -16154,7 +16158,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="345" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:10" hidden="1">
       <c r="A345" s="4">
         <v>343</v>
       </c>
@@ -16186,7 +16190,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="346" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:10" hidden="1">
       <c r="A346" s="4">
         <v>344</v>
       </c>
@@ -16218,7 +16222,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="347" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:10" hidden="1">
       <c r="A347" s="4">
         <v>345</v>
       </c>
@@ -16250,7 +16254,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="348" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:10" hidden="1">
       <c r="A348" s="4">
         <v>346</v>
       </c>
@@ -16282,7 +16286,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="349" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:10" hidden="1">
       <c r="A349" s="4">
         <v>347</v>
       </c>
@@ -16314,7 +16318,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="350" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:10" hidden="1">
       <c r="A350" s="4">
         <v>348</v>
       </c>
@@ -16346,7 +16350,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="351" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:10" hidden="1">
       <c r="A351" s="4">
         <v>349</v>
       </c>
@@ -16378,7 +16382,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="352" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:10" hidden="1">
       <c r="A352" s="4">
         <v>350</v>
       </c>
@@ -16410,7 +16414,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="353" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:10" hidden="1">
       <c r="A353" s="4">
         <v>351</v>
       </c>
@@ -16442,7 +16446,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="354" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:10" hidden="1">
       <c r="A354" s="4">
         <v>352</v>
       </c>
@@ -16474,7 +16478,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="355" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:10" hidden="1">
       <c r="A355" s="4">
         <v>353</v>
       </c>
@@ -16506,7 +16510,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="356" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:10" hidden="1">
       <c r="A356" s="4">
         <v>354</v>
       </c>
@@ -16538,7 +16542,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="357" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:10" hidden="1">
       <c r="A357" s="4">
         <v>355</v>
       </c>
@@ -16570,7 +16574,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="358" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:10" hidden="1">
       <c r="A358" s="4">
         <v>356</v>
       </c>
@@ -16602,7 +16606,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="359" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:10" hidden="1">
       <c r="A359" s="4">
         <v>357</v>
       </c>
@@ -16634,7 +16638,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:10" hidden="1">
       <c r="A360" s="4">
         <v>358</v>
       </c>
@@ -16666,7 +16670,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="361" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:10" hidden="1">
       <c r="A361" s="4">
         <v>359</v>
       </c>
@@ -16698,7 +16702,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="362" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:10" hidden="1">
       <c r="A362" s="4">
         <v>360</v>
       </c>
@@ -16730,7 +16734,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="363" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:10" hidden="1">
       <c r="A363" s="4">
         <v>361</v>
       </c>
@@ -16762,7 +16766,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="364" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:10" hidden="1">
       <c r="A364" s="4">
         <v>362</v>
       </c>
@@ -16794,7 +16798,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="365" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:10" hidden="1">
       <c r="A365" s="4">
         <v>363</v>
       </c>
@@ -16826,7 +16830,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="366" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:10" hidden="1">
       <c r="A366" s="4">
         <v>364</v>
       </c>
@@ -16858,7 +16862,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:10" hidden="1">
       <c r="A367" s="4">
         <v>365</v>
       </c>
@@ -16890,7 +16894,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="368" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:10" hidden="1">
       <c r="A368" s="4">
         <v>366</v>
       </c>
@@ -16922,7 +16926,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="369" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:10" hidden="1">
       <c r="A369" s="4">
         <v>367</v>
       </c>
@@ -16954,7 +16958,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="370" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:10" hidden="1">
       <c r="A370" s="4">
         <v>368</v>
       </c>
@@ -16986,7 +16990,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="371" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:10" hidden="1">
       <c r="A371" s="4">
         <v>369</v>
       </c>
@@ -17018,7 +17022,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="372" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:10" hidden="1">
       <c r="A372" s="4">
         <v>370</v>
       </c>
@@ -17050,7 +17054,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="373" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:10" hidden="1">
       <c r="A373" s="4">
         <v>371</v>
       </c>
@@ -17082,7 +17086,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="374" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:10" hidden="1">
       <c r="A374" s="4">
         <v>372</v>
       </c>
@@ -17114,7 +17118,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="375" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:10" hidden="1">
       <c r="A375" s="4">
         <v>373</v>
       </c>
@@ -17146,7 +17150,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="376" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:10" hidden="1">
       <c r="A376" s="4">
         <v>374</v>
       </c>
@@ -17178,7 +17182,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="377" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:10" hidden="1">
       <c r="A377" s="4">
         <v>375</v>
       </c>
@@ -17210,7 +17214,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="378" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:10" hidden="1">
       <c r="A378" s="4">
         <v>376</v>
       </c>
@@ -17242,7 +17246,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="379" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:10" hidden="1">
       <c r="A379" s="4">
         <v>377</v>
       </c>
@@ -17274,7 +17278,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="380" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:10" hidden="1">
       <c r="A380" s="4">
         <v>378</v>
       </c>
@@ -17306,7 +17310,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="381" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:10" hidden="1">
       <c r="A381" s="4">
         <v>379</v>
       </c>
@@ -17338,7 +17342,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="382" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:10" hidden="1">
       <c r="A382" s="4">
         <v>380</v>
       </c>
@@ -17370,7 +17374,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="383" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:10" hidden="1">
       <c r="A383" s="4">
         <v>381</v>
       </c>
@@ -17402,7 +17406,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="384" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:10" hidden="1">
       <c r="A384" s="4">
         <v>382</v>
       </c>
@@ -17434,7 +17438,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="385" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:10" hidden="1">
       <c r="A385" s="4">
         <v>383</v>
       </c>
@@ -17448,10 +17452,10 @@
         <v>720</v>
       </c>
       <c r="E385" s="1" t="s">
-        <v>21</v>
+        <v>959</v>
       </c>
       <c r="F385" s="1" t="s">
-        <v>23</v>
+        <v>1316</v>
       </c>
       <c r="G385" s="1" t="s">
         <v>14</v>
@@ -17466,7 +17470,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="386" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:10" hidden="1">
       <c r="A386" s="4">
         <v>384</v>
       </c>
@@ -17498,7 +17502,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="387" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:10" hidden="1">
       <c r="A387" s="4">
         <v>385</v>
       </c>
@@ -17530,7 +17534,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="388" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:10" hidden="1">
       <c r="A388" s="4">
         <v>386</v>
       </c>
@@ -17562,7 +17566,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="389" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:10" hidden="1">
       <c r="A389" s="4">
         <v>387</v>
       </c>
@@ -17594,7 +17598,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="390" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:10" hidden="1">
       <c r="A390" s="4">
         <v>388</v>
       </c>
@@ -17626,7 +17630,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="391" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:10" hidden="1">
       <c r="A391" s="4">
         <v>389</v>
       </c>
@@ -17658,7 +17662,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="392" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:10" hidden="1">
       <c r="A392" s="4">
         <v>390</v>
       </c>
@@ -17690,7 +17694,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="393" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:10" hidden="1">
       <c r="A393" s="4">
         <v>391</v>
       </c>
@@ -17722,7 +17726,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="394" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:10" hidden="1">
       <c r="A394" s="4">
         <v>392</v>
       </c>
@@ -17754,7 +17758,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="395" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:10" hidden="1">
       <c r="A395" s="4">
         <v>393</v>
       </c>
@@ -17786,7 +17790,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="396" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:10" hidden="1">
       <c r="A396" s="4">
         <v>394</v>
       </c>
@@ -17818,7 +17822,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="397" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:10" hidden="1">
       <c r="A397" s="4">
         <v>395</v>
       </c>
@@ -17850,7 +17854,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="398" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:10" hidden="1">
       <c r="A398" s="4">
         <v>396</v>
       </c>
@@ -17882,7 +17886,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="399" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:10" hidden="1">
       <c r="A399" s="4">
         <v>397</v>
       </c>
@@ -17914,7 +17918,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="400" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:10" hidden="1">
       <c r="A400" s="4">
         <v>398</v>
       </c>
@@ -17946,7 +17950,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="401" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:10" hidden="1">
       <c r="A401" s="4">
         <v>399</v>
       </c>
@@ -17978,7 +17982,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="402" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:10" hidden="1">
       <c r="A402" s="4">
         <v>400</v>
       </c>
@@ -18010,7 +18014,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="403" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:10" hidden="1">
       <c r="A403" s="4">
         <v>401</v>
       </c>
@@ -18042,7 +18046,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="404" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:10" hidden="1">
       <c r="A404" s="4">
         <v>402</v>
       </c>
@@ -18074,7 +18078,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="405" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:10" hidden="1">
       <c r="A405" s="4">
         <v>403</v>
       </c>
@@ -18106,7 +18110,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="406" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:10" hidden="1">
       <c r="A406" s="4">
         <v>404</v>
       </c>
@@ -18138,7 +18142,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="407" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:10" hidden="1">
       <c r="A407" s="4">
         <v>405</v>
       </c>
@@ -18170,7 +18174,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="408" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:10" hidden="1">
       <c r="A408" s="4">
         <v>406</v>
       </c>
@@ -18202,7 +18206,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="409" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:10" hidden="1">
       <c r="A409" s="4">
         <v>407</v>
       </c>
@@ -18234,7 +18238,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="410" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:10" hidden="1">
       <c r="A410" s="4">
         <v>408</v>
       </c>
@@ -18266,7 +18270,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="411" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:10" hidden="1">
       <c r="A411" s="4">
         <v>409</v>
       </c>
@@ -18298,7 +18302,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="412" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:10" hidden="1">
       <c r="A412" s="4">
         <v>410</v>
       </c>
@@ -18330,7 +18334,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="413" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:10" hidden="1">
       <c r="A413" s="4">
         <v>411</v>
       </c>
@@ -18362,7 +18366,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="414" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:10" hidden="1">
       <c r="A414" s="4">
         <v>412</v>
       </c>
@@ -18394,7 +18398,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="415" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:10" hidden="1">
       <c r="A415" s="4">
         <v>413</v>
       </c>
@@ -18426,7 +18430,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="416" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:10" hidden="1">
       <c r="A416" s="4">
         <v>414</v>
       </c>
@@ -18458,7 +18462,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="417" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:10" hidden="1">
       <c r="A417" s="4">
         <v>415</v>
       </c>
@@ -18490,7 +18494,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="418" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:10" hidden="1">
       <c r="A418" s="4">
         <v>416</v>
       </c>
@@ -18522,7 +18526,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="419" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:10" hidden="1">
       <c r="A419" s="4">
         <v>417</v>
       </c>
@@ -18554,7 +18558,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="420" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:10" hidden="1">
       <c r="A420" s="4">
         <v>418</v>
       </c>
@@ -18586,7 +18590,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="421" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:10" hidden="1">
       <c r="A421" s="4">
         <v>419</v>
       </c>
@@ -18618,7 +18622,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="422" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:10" hidden="1">
       <c r="A422" s="4">
         <v>420</v>
       </c>
@@ -18650,7 +18654,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="423" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:10" hidden="1">
       <c r="A423" s="4">
         <v>421</v>
       </c>
@@ -18682,7 +18686,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="424" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:10" hidden="1">
       <c r="A424" s="4">
         <v>422</v>
       </c>
@@ -18714,7 +18718,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="425" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:10" hidden="1">
       <c r="A425" s="4">
         <v>423</v>
       </c>
@@ -18746,7 +18750,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="426" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:10" hidden="1">
       <c r="A426" s="4">
         <v>424</v>
       </c>
@@ -18778,7 +18782,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="427" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:10" hidden="1">
       <c r="A427" s="4">
         <v>425</v>
       </c>
@@ -18810,7 +18814,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="428" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:10" hidden="1">
       <c r="A428" s="4">
         <v>426</v>
       </c>
@@ -18842,7 +18846,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="429" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:10" hidden="1">
       <c r="A429" s="4">
         <v>427</v>
       </c>
@@ -18874,7 +18878,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="430" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:10" hidden="1">
       <c r="A430" s="4">
         <v>428</v>
       </c>
@@ -18906,7 +18910,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="431" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:10" hidden="1">
       <c r="A431" s="4">
         <v>429</v>
       </c>
@@ -18938,7 +18942,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="432" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:10" hidden="1">
       <c r="A432" s="4">
         <v>430</v>
       </c>
@@ -18970,7 +18974,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="433" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:10" hidden="1">
       <c r="A433" s="4">
         <v>431</v>
       </c>
@@ -19002,7 +19006,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="434" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:10" hidden="1">
       <c r="A434" s="4">
         <v>432</v>
       </c>
@@ -19034,7 +19038,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="435" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:10" hidden="1">
       <c r="A435" s="4">
         <v>433</v>
       </c>
@@ -19064,7 +19068,7 @@
       </c>
       <c r="J435" s="24"/>
     </row>
-    <row r="436" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:10" hidden="1">
       <c r="A436" s="4">
         <v>434</v>
       </c>
@@ -19096,7 +19100,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="437" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:10" hidden="1">
       <c r="A437" s="4">
         <v>435</v>
       </c>
@@ -19128,7 +19132,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="438" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:10" hidden="1">
       <c r="A438" s="4">
         <v>436</v>
       </c>
@@ -19160,7 +19164,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="439" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:10" hidden="1">
       <c r="A439" s="4">
         <v>437</v>
       </c>
@@ -19192,7 +19196,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="440" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:10" hidden="1">
       <c r="A440" s="4">
         <v>438</v>
       </c>
@@ -19224,7 +19228,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="441" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:10" hidden="1">
       <c r="A441" s="4">
         <v>439</v>
       </c>
@@ -19256,7 +19260,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="442" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:10" hidden="1">
       <c r="A442" s="4">
         <v>440</v>
       </c>
@@ -19288,7 +19292,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="443" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:10" hidden="1">
       <c r="A443" s="4">
         <v>441</v>
       </c>
@@ -19320,7 +19324,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="444" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:10" hidden="1">
       <c r="A444" s="4">
         <v>442</v>
       </c>
@@ -19352,7 +19356,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="445" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:10" hidden="1">
       <c r="A445" s="4">
         <v>443</v>
       </c>
@@ -19384,7 +19388,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="446" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:10" hidden="1">
       <c r="A446" s="4">
         <v>444</v>
       </c>
@@ -19416,7 +19420,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="447" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:10" hidden="1">
       <c r="A447" s="4">
         <v>445</v>
       </c>
@@ -19448,7 +19452,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="448" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:10">
       <c r="A448" s="4">
         <v>446</v>
       </c>
@@ -19480,7 +19484,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="449" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:10" hidden="1">
       <c r="A449" s="4">
         <v>447</v>
       </c>
@@ -19510,7 +19514,7 @@
       </c>
       <c r="J449" s="24"/>
     </row>
-    <row r="450" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:10" hidden="1">
       <c r="A450" s="4">
         <v>448</v>
       </c>
@@ -19540,7 +19544,7 @@
       </c>
       <c r="J450" s="24"/>
     </row>
-    <row r="451" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:10" hidden="1">
       <c r="A451" s="4">
         <v>449</v>
       </c>
@@ -19572,7 +19576,7 @@
         <v>1299</v>
       </c>
     </row>
-    <row r="452" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:10" hidden="1">
       <c r="A452" s="4">
         <v>450</v>
       </c>
@@ -19602,7 +19606,7 @@
       </c>
       <c r="J452" s="24"/>
     </row>
-    <row r="453" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:10">
       <c r="A453" s="4">
         <v>451</v>
       </c>
@@ -19632,7 +19636,7 @@
       </c>
       <c r="J453" s="24"/>
     </row>
-    <row r="454" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:10">
       <c r="A454" s="4">
         <v>452</v>
       </c>
@@ -19662,7 +19666,7 @@
       </c>
       <c r="J454" s="24"/>
     </row>
-    <row r="455" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:10">
       <c r="A455" s="4">
         <v>453</v>
       </c>
@@ -19692,7 +19696,7 @@
       </c>
       <c r="J455" s="24"/>
     </row>
-    <row r="456" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:10" hidden="1">
       <c r="A456" s="4">
         <v>454</v>
       </c>
@@ -19722,7 +19726,7 @@
       </c>
       <c r="J456" s="24"/>
     </row>
-    <row r="457" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:10" hidden="1">
       <c r="A457" s="4">
         <v>455</v>
       </c>
@@ -19752,7 +19756,7 @@
       </c>
       <c r="J457" s="24"/>
     </row>
-    <row r="458" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:10">
       <c r="A458" s="4">
         <v>456</v>
       </c>
@@ -19782,7 +19786,7 @@
       </c>
       <c r="J458" s="24"/>
     </row>
-    <row r="459" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:10">
       <c r="A459" s="4">
         <v>457</v>
       </c>
@@ -19812,7 +19816,7 @@
       </c>
       <c r="J459" s="24"/>
     </row>
-    <row r="460" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:10">
       <c r="A460" s="4">
         <v>458</v>
       </c>
@@ -19842,7 +19846,7 @@
       </c>
       <c r="J460" s="24"/>
     </row>
-    <row r="461" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:10">
       <c r="A461" s="4">
         <v>459</v>
       </c>
@@ -19874,7 +19878,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="462" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:10">
       <c r="A462" s="4">
         <v>460</v>
       </c>
@@ -19904,7 +19908,7 @@
       </c>
       <c r="J462" s="24"/>
     </row>
-    <row r="463" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:10">
       <c r="A463" s="4">
         <v>461</v>
       </c>
@@ -19934,7 +19938,7 @@
       </c>
       <c r="J463" s="24"/>
     </row>
-    <row r="464" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:10">
       <c r="A464" s="4">
         <v>462</v>
       </c>
@@ -19964,7 +19968,7 @@
       </c>
       <c r="J464" s="24"/>
     </row>
-    <row r="465" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:10">
       <c r="A465" s="4">
         <v>463</v>
       </c>
@@ -19994,7 +19998,7 @@
       </c>
       <c r="J465" s="24"/>
     </row>
-    <row r="466" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:10">
       <c r="A466" s="4">
         <v>464</v>
       </c>
@@ -20024,7 +20028,7 @@
       </c>
       <c r="J466" s="24"/>
     </row>
-    <row r="467" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:10">
       <c r="A467" s="4">
         <v>465</v>
       </c>
@@ -20054,7 +20058,7 @@
       </c>
       <c r="J467" s="24"/>
     </row>
-    <row r="468" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:10">
       <c r="A468" s="4">
         <v>466</v>
       </c>
@@ -20084,7 +20088,7 @@
       </c>
       <c r="J468" s="24"/>
     </row>
-    <row r="469" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:10">
       <c r="A469" s="4">
         <v>467</v>
       </c>
@@ -20114,7 +20118,7 @@
       </c>
       <c r="J469" s="24"/>
     </row>
-    <row r="470" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:10">
       <c r="A470" s="4">
         <v>468</v>
       </c>
@@ -20144,7 +20148,7 @@
       </c>
       <c r="J470" s="24"/>
     </row>
-    <row r="471" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:10">
       <c r="A471" s="4">
         <v>469</v>
       </c>
@@ -20174,7 +20178,7 @@
       </c>
       <c r="J471" s="24"/>
     </row>
-    <row r="472" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:10">
       <c r="A472" s="4">
         <v>470</v>
       </c>
@@ -20204,7 +20208,7 @@
       </c>
       <c r="J472" s="24"/>
     </row>
-    <row r="473" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:10">
       <c r="A473" s="4">
         <v>471</v>
       </c>
@@ -20234,7 +20238,7 @@
       </c>
       <c r="J473" s="24"/>
     </row>
-    <row r="474" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:10">
       <c r="A474" s="4">
         <v>472</v>
       </c>
@@ -20264,7 +20268,7 @@
       </c>
       <c r="J474" s="24"/>
     </row>
-    <row r="475" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:10">
       <c r="A475" s="4">
         <v>473</v>
       </c>
@@ -20294,7 +20298,7 @@
       </c>
       <c r="J475" s="24"/>
     </row>
-    <row r="476" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:10">
       <c r="A476" s="4">
         <v>474</v>
       </c>
@@ -20324,7 +20328,7 @@
       </c>
       <c r="J476" s="24"/>
     </row>
-    <row r="477" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:10">
       <c r="A477" s="4">
         <v>475</v>
       </c>
@@ -20354,7 +20358,7 @@
       </c>
       <c r="J477" s="24"/>
     </row>
-    <row r="478" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:10">
       <c r="A478" s="4">
         <v>476</v>
       </c>
@@ -20384,7 +20388,7 @@
       </c>
       <c r="J478" s="24"/>
     </row>
-    <row r="479" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:10">
       <c r="A479" s="4">
         <v>477</v>
       </c>
@@ -20414,7 +20418,7 @@
       </c>
       <c r="J479" s="24"/>
     </row>
-    <row r="480" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:10">
       <c r="A480" s="4">
         <v>478</v>
       </c>
@@ -20444,7 +20448,7 @@
       </c>
       <c r="J480" s="24"/>
     </row>
-    <row r="481" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:10">
       <c r="A481" s="4">
         <v>479</v>
       </c>
@@ -20474,7 +20478,7 @@
       </c>
       <c r="J481" s="24"/>
     </row>
-    <row r="482" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:10">
       <c r="A482" s="4">
         <v>480</v>
       </c>
@@ -20504,7 +20508,7 @@
       </c>
       <c r="J482" s="24"/>
     </row>
-    <row r="483" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:10">
       <c r="A483" s="4">
         <v>481</v>
       </c>
@@ -20534,7 +20538,7 @@
       </c>
       <c r="J483" s="24"/>
     </row>
-    <row r="484" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:10">
       <c r="A484" s="4">
         <v>482</v>
       </c>
@@ -20564,7 +20568,7 @@
       </c>
       <c r="J484" s="24"/>
     </row>
-    <row r="485" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:10">
       <c r="A485" s="4">
         <v>483</v>
       </c>
@@ -20594,7 +20598,7 @@
       </c>
       <c r="J485" s="24"/>
     </row>
-    <row r="486" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:10">
       <c r="A486" s="4">
         <v>484</v>
       </c>
@@ -20624,7 +20628,7 @@
       </c>
       <c r="J486" s="24"/>
     </row>
-    <row r="487" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:10">
       <c r="A487" s="4">
         <v>485</v>
       </c>
@@ -20654,7 +20658,7 @@
       </c>
       <c r="J487" s="24"/>
     </row>
-    <row r="488" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:10">
       <c r="A488" s="4">
         <v>486</v>
       </c>
@@ -20668,10 +20672,10 @@
         <v>1256</v>
       </c>
       <c r="E488" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F488" s="1" t="s">
-        <v>1056</v>
+        <v>23</v>
       </c>
       <c r="G488" s="1" t="s">
         <v>30</v>
@@ -20682,9 +20686,11 @@
       <c r="I488" s="4" t="s">
         <v>575</v>
       </c>
-      <c r="J488" s="24"/>
-    </row>
-    <row r="489" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J488" s="3" t="s">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="489" spans="1:10">
       <c r="A489" s="4">
         <v>487</v>
       </c>
@@ -20714,7 +20720,7 @@
       </c>
       <c r="J489" s="24"/>
     </row>
-    <row r="490" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:10">
       <c r="A490" s="4">
         <v>488</v>
       </c>
@@ -20744,7 +20750,7 @@
       </c>
       <c r="J490" s="24"/>
     </row>
-    <row r="491" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:10">
       <c r="A491" s="4">
         <v>489</v>
       </c>
@@ -20774,7 +20780,7 @@
       </c>
       <c r="J491" s="24"/>
     </row>
-    <row r="492" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:10">
       <c r="A492" s="4">
         <v>490</v>
       </c>
@@ -20804,7 +20810,7 @@
       </c>
       <c r="J492" s="24"/>
     </row>
-    <row r="493" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:10">
       <c r="A493" s="4">
         <v>491</v>
       </c>
@@ -20834,7 +20840,7 @@
       </c>
       <c r="J493" s="24"/>
     </row>
-    <row r="494" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:10" hidden="1">
       <c r="A494" s="4">
         <v>492</v>
       </c>
@@ -20864,7 +20870,7 @@
       </c>
       <c r="J494" s="24"/>
     </row>
-    <row r="495" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:10" hidden="1">
       <c r="A495" s="4">
         <v>493</v>
       </c>
@@ -20894,7 +20900,7 @@
       </c>
       <c r="J495" s="24"/>
     </row>
-    <row r="496" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:10" hidden="1">
       <c r="A496" s="4">
         <v>494</v>
       </c>
@@ -20924,7 +20930,7 @@
       </c>
       <c r="J496" s="24"/>
     </row>
-    <row r="497" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:10">
       <c r="A497" s="4">
         <v>495</v>
       </c>
@@ -20954,7 +20960,7 @@
       </c>
       <c r="J497" s="24"/>
     </row>
-    <row r="498" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:10" hidden="1">
       <c r="A498" s="4">
         <v>496</v>
       </c>
@@ -20984,7 +20990,7 @@
       </c>
       <c r="J498" s="24"/>
     </row>
-    <row r="499" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:10" hidden="1">
       <c r="A499" s="4">
         <v>497</v>
       </c>
@@ -21033,7 +21039,7 @@
   <conditionalFormatting sqref="D447 D2:D356">
     <cfRule type="duplicateValues" dxfId="27" priority="84"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G204 E249:E1048576 E1:E247">
+  <conditionalFormatting sqref="E1:E247 G204 E249:E1048576">
     <cfRule type="cellIs" dxfId="26" priority="14" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
@@ -21090,7 +21096,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6771508-02DF-4FAC-B7A7-A6278CE7AE5B}">
   <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
@@ -21099,7 +21105,7 @@
     <col min="6" max="6" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>516</v>
       </c>
@@ -21119,7 +21125,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6">
       <c r="A2" s="42" t="s">
         <v>871</v>
       </c>
@@ -21139,7 +21145,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6">
       <c r="A3" s="42" t="s">
         <v>871</v>
       </c>
@@ -21159,7 +21165,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6">
       <c r="A4" s="42" t="s">
         <v>871</v>
       </c>
@@ -21179,7 +21185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6">
       <c r="A5" s="42" t="s">
         <v>871</v>
       </c>
@@ -21199,7 +21205,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6">
       <c r="A6" s="42" t="s">
         <v>871</v>
       </c>
@@ -21219,7 +21225,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6">
       <c r="A7" s="42" t="s">
         <v>871</v>
       </c>
@@ -21239,7 +21245,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>521</v>
       </c>
@@ -21256,7 +21262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>521</v>
       </c>
@@ -21273,7 +21279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>521</v>
       </c>
@@ -21290,7 +21296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>521</v>
       </c>
@@ -21307,7 +21313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>521</v>
       </c>
@@ -21324,7 +21330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>521</v>
       </c>
@@ -21341,7 +21347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>521</v>
       </c>
@@ -21358,7 +21364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>521</v>
       </c>
@@ -21375,7 +21381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>521</v>
       </c>
@@ -21392,7 +21398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>521</v>
       </c>
@@ -21409,7 +21415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>521</v>
       </c>
@@ -21426,7 +21432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>521</v>
       </c>
@@ -21443,7 +21449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>521</v>
       </c>
@@ -21460,7 +21466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>526</v>
       </c>
@@ -21480,7 +21486,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
         <v>526</v>
       </c>
@@ -21500,7 +21506,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
         <v>526</v>
       </c>
@@ -21520,7 +21526,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
         <v>526</v>
       </c>
@@ -21540,7 +21546,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
         <v>526</v>
       </c>
@@ -21560,7 +21566,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
         <v>526</v>
       </c>
@@ -21580,7 +21586,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
         <v>526</v>
       </c>
@@ -21600,7 +21606,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
         <v>539</v>
       </c>
@@ -21620,7 +21626,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
         <v>543</v>
       </c>
@@ -21640,7 +21646,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
         <v>545</v>
       </c>
@@ -21660,7 +21666,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6">
       <c r="A31" t="s">
         <v>545</v>
       </c>
@@ -21680,7 +21686,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
         <v>539</v>
       </c>
@@ -21712,7 +21718,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD4931DD-77FA-4EF6-BAB3-744C5E5D53EC}">
   <dimension ref="A1:XFC75"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.88671875" bestFit="1" customWidth="1"/>
@@ -21729,7 +21735,7 @@
     <col min="16384" max="16384" width="16.21875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -21761,7 +21767,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -21793,7 +21799,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -21825,7 +21831,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -21857,7 +21863,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -21889,7 +21895,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -21921,7 +21927,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -21953,7 +21959,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -21985,7 +21991,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -22017,7 +22023,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -22049,7 +22055,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -22081,7 +22087,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -22113,7 +22119,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -22145,7 +22151,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -22177,7 +22183,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -22209,7 +22215,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -22241,7 +22247,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -22273,7 +22279,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -22305,7 +22311,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -22337,7 +22343,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -22369,7 +22375,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -22401,7 +22407,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -22433,7 +22439,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -22465,7 +22471,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -22497,7 +22503,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -22527,7 +22533,7 @@
       </c>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -22557,7 +22563,7 @@
       </c>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -22587,7 +22593,7 @@
       </c>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10">
       <c r="A28" s="4">
         <v>27</v>
       </c>
@@ -22617,7 +22623,7 @@
       </c>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -22647,7 +22653,7 @@
       </c>
       <c r="J29" s="3"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10">
       <c r="A30" s="4">
         <v>29</v>
       </c>
@@ -22677,7 +22683,7 @@
       </c>
       <c r="J30" s="3"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -22707,7 +22713,7 @@
       </c>
       <c r="J31" s="3"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10">
       <c r="A32" s="4">
         <v>31</v>
       </c>
@@ -22737,7 +22743,7 @@
       </c>
       <c r="J32" s="3"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -22767,7 +22773,7 @@
       </c>
       <c r="J33" s="3"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10">
       <c r="A34" s="4">
         <v>33</v>
       </c>
@@ -22797,7 +22803,7 @@
       </c>
       <c r="J34" s="3"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10">
       <c r="A35" s="4">
         <v>34</v>
       </c>
@@ -22827,7 +22833,7 @@
       </c>
       <c r="J35" s="3"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -22857,7 +22863,7 @@
       </c>
       <c r="J36" s="3"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -22887,7 +22893,7 @@
       </c>
       <c r="J37" s="3"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10">
       <c r="A38" s="4">
         <v>37</v>
       </c>
@@ -22917,7 +22923,7 @@
       </c>
       <c r="J38" s="3"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -22947,7 +22953,7 @@
       </c>
       <c r="J39" s="3"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10">
       <c r="A40" s="4">
         <v>39</v>
       </c>
@@ -22977,7 +22983,7 @@
       </c>
       <c r="J40" s="3"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -23007,7 +23013,7 @@
       </c>
       <c r="J41" s="3"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10">
       <c r="A42" s="4">
         <v>41</v>
       </c>
@@ -23036,7 +23042,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -23068,7 +23074,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10">
       <c r="A44" s="33">
         <v>43</v>
       </c>
@@ -23100,7 +23106,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10">
       <c r="A45" s="18">
         <v>44</v>
       </c>
@@ -23129,7 +23135,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10">
       <c r="A46" s="18">
         <v>45</v>
       </c>
@@ -23158,7 +23164,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10">
       <c r="A47" s="18">
         <v>46</v>
       </c>
@@ -23187,7 +23193,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10">
       <c r="A48" s="18">
         <v>47</v>
       </c>
@@ -23216,7 +23222,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10">
       <c r="A49" s="18">
         <v>48</v>
       </c>
@@ -23245,7 +23251,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10">
       <c r="A50" s="18">
         <v>49</v>
       </c>
@@ -23277,7 +23283,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10">
       <c r="A51" s="18">
         <v>50</v>
       </c>
@@ -23309,7 +23315,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="52" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" s="3" customFormat="1">
       <c r="A52" s="4">
         <v>51</v>
       </c>
@@ -23341,7 +23347,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="53" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" s="3" customFormat="1">
       <c r="A53" s="4">
         <v>52</v>
       </c>
@@ -23373,102 +23379,102 @@
         <v>690</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10">
       <c r="A54" s="18"/>
       <c r="B54" s="21"/>
       <c r="C54" s="49"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10">
       <c r="A55" s="18"/>
       <c r="B55" s="21"/>
       <c r="C55" s="49"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10">
       <c r="B56" s="21"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10">
       <c r="B57" s="21"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10">
       <c r="A58" s="18"/>
       <c r="B58" s="22"/>
       <c r="C58" s="49"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10">
       <c r="A59" s="18"/>
       <c r="B59" s="22"/>
       <c r="C59" s="49"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10">
       <c r="A60" s="18"/>
       <c r="B60" s="22"/>
       <c r="C60" s="49"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10">
       <c r="A61" s="18"/>
       <c r="B61" s="22"/>
       <c r="C61" s="49"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10">
       <c r="A62" s="18"/>
       <c r="B62" s="22"/>
       <c r="C62" s="49"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10">
       <c r="A63" s="18"/>
       <c r="B63" s="22"/>
       <c r="C63" s="49"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10">
       <c r="A64" s="18"/>
       <c r="B64" s="22"/>
       <c r="C64" s="49"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3">
       <c r="A65" s="18"/>
       <c r="B65" s="22"/>
       <c r="C65" s="49"/>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3">
       <c r="A66" s="18"/>
       <c r="B66" s="22"/>
       <c r="C66" s="49"/>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3">
       <c r="A67" s="18"/>
       <c r="B67" s="22"/>
       <c r="C67" s="49"/>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3">
       <c r="A68" s="18"/>
       <c r="B68" s="22"/>
       <c r="C68" s="49"/>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3">
       <c r="A69" s="18"/>
       <c r="B69" s="22"/>
       <c r="C69" s="49"/>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3">
       <c r="A70" s="18"/>
       <c r="B70" s="22"/>
       <c r="C70" s="49"/>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3">
       <c r="A71" s="18"/>
       <c r="B71" s="22"/>
       <c r="C71" s="49"/>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3">
       <c r="B72" s="21"/>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3">
       <c r="B73" s="21"/>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3">
       <c r="B74" s="21"/>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3">
       <c r="B75" s="21"/>
     </row>
   </sheetData>

--- a/data_printer.xlsx
+++ b/data_printer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erick\Desktop\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CEB9412-4775-4963-84A8-5B8EED42CFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57BB6E86-F82B-43B3-9870-8BA5BA8E324C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A8AA41B5-7AA1-4FF7-A9B8-54B8A4E1AF28}"/>
   </bookViews>
@@ -2632,9 +2632,6 @@
     <t>UNNOMED - SPA</t>
   </si>
   <si>
-    <t>ESTAVA NA PROG 2 - PAÇO; ESTAVA NO DARCY RIBEIRO; RETIRADA MAESTRO KIKO ERRO 673-10  23/10/2025; TROCA DE UNIDADE DE IMAGEM CILINDRO LAMINA DE LIMPEZA PRC ROLO TRANSMISSOR FUSÃO ROLETES 23/10/2025; INSTALADA NO UNNOMED -SPA 24/10/2025</t>
-  </si>
-  <si>
     <t>U66799B5N415317</t>
   </si>
   <si>
@@ -3989,13 +3986,16 @@
   </si>
   <si>
     <t>CHEGOU DISTRIVISA 23/08/2024; FEITO INSTALAÇÃO SALA LICITAÇÃO 16/10/2024; INSTALADA NO MERCADO ANDRADE NO DIA 15/04/2025; RETIRADA PARA O DEPOSITO  14/05/2025; FICOU 8 MESES NA WP E NOA RESOLVERAM;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTAVA NA PROG 2 - PAÇO; ESTAVA NO DARCY RIBEIRO; RETIRADA MAESTRO KIKO ERRO 673-10  23/10/2025; TROCA DE UNIDADE DE IMAGEM CILINDRO LAMINA DE LIMPEZA PRC ROLO TRANSMISSOR FUSÃO ROLETES 23/10/2025; INSTALADA NO UNNOMED -SPA 24/10/2025; </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5361,7 +5361,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD39631B-97B8-405A-AA43-14CDFBC77F92}">
   <dimension ref="A1:J499"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33.109375" style="2" bestFit="1" customWidth="1"/>
@@ -5376,7 +5376,7 @@
     <col min="11" max="16384" width="9.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5408,7 +5408,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -5440,7 +5440,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -5472,7 +5472,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -5501,10 +5501,10 @@
         <v>574</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>1248</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -5536,7 +5536,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -5568,7 +5568,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -5600,7 +5600,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -5632,7 +5632,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -5662,7 +5662,7 @@
       </c>
       <c r="J9" s="7"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -5692,12 +5692,12 @@
       </c>
       <c r="J10" s="7"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>11</v>
@@ -5721,15 +5721,15 @@
         <v>574</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>11</v>
@@ -5753,10 +5753,10 @@
         <v>574</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>1258</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -5785,10 +5785,10 @@
         <v>574</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>1233</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -5805,7 +5805,7 @@
         <v>350</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>14</v>
@@ -5817,10 +5817,10 @@
         <v>574</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -5849,10 +5849,10 @@
         <v>574</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>1244</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -5881,7 +5881,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -5913,7 +5913,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -5945,7 +5945,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -5977,7 +5977,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -5994,7 +5994,7 @@
         <v>19</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>14</v>
@@ -6006,10 +6006,10 @@
         <v>574</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>1045</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -6041,7 +6041,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="15.75" customHeight="1">
+    <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -6070,10 +6070,10 @@
         <v>574</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>1254</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -6090,7 +6090,7 @@
         <v>76</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>14</v>
@@ -6105,7 +6105,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -6137,7 +6137,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -6169,7 +6169,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -6198,7 +6198,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -6227,7 +6227,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>27</v>
       </c>
@@ -6259,7 +6259,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -6288,10 +6288,10 @@
         <v>574</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>29</v>
       </c>
@@ -6323,7 +6323,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -6355,7 +6355,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>31</v>
       </c>
@@ -6387,7 +6387,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -6419,7 +6419,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
         <v>33</v>
       </c>
@@ -6448,10 +6448,10 @@
         <v>574</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>1296</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>34</v>
       </c>
@@ -6483,7 +6483,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -6497,7 +6497,7 @@
         <v>84</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>837</v>
@@ -6515,7 +6515,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -6544,7 +6544,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
         <v>37</v>
       </c>
@@ -6576,7 +6576,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -6608,7 +6608,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
         <v>39</v>
       </c>
@@ -6640,7 +6640,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -6672,7 +6672,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
         <v>41</v>
       </c>
@@ -6704,7 +6704,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -6736,7 +6736,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
         <v>43</v>
       </c>
@@ -6768,7 +6768,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
         <v>44</v>
       </c>
@@ -6797,7 +6797,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="4">
         <v>45</v>
       </c>
@@ -6829,7 +6829,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
         <v>46</v>
       </c>
@@ -6861,7 +6861,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="4">
         <v>47</v>
       </c>
@@ -6893,7 +6893,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="4">
         <v>48</v>
       </c>
@@ -6922,7 +6922,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="4">
         <v>49</v>
       </c>
@@ -6951,7 +6951,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="4">
         <v>50</v>
       </c>
@@ -6983,12 +6983,12 @@
         <v>114</v>
       </c>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="4">
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>11</v>
@@ -7015,12 +7015,12 @@
         <v>624</v>
       </c>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="4">
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>11</v>
@@ -7047,12 +7047,12 @@
         <v>625</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="4">
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>11</v>
@@ -7064,7 +7064,7 @@
         <v>68</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>68</v>
@@ -7079,7 +7079,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="4">
         <v>54</v>
       </c>
@@ -7108,7 +7108,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="4">
         <v>55</v>
       </c>
@@ -7137,7 +7137,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="4">
         <v>56</v>
       </c>
@@ -7166,7 +7166,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="4">
         <v>57</v>
       </c>
@@ -7195,7 +7195,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="4">
         <v>58</v>
       </c>
@@ -7224,7 +7224,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="4">
         <v>59</v>
       </c>
@@ -7253,7 +7253,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="4">
         <v>60</v>
       </c>
@@ -7285,7 +7285,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="4">
         <v>61</v>
       </c>
@@ -7317,7 +7317,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="4">
         <v>62</v>
       </c>
@@ -7346,7 +7346,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="4">
         <v>63</v>
       </c>
@@ -7378,7 +7378,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="4">
         <v>64</v>
       </c>
@@ -7407,7 +7407,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="4">
         <v>65</v>
       </c>
@@ -7436,7 +7436,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="67" spans="1:10">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="4">
         <v>66</v>
       </c>
@@ -7465,7 +7465,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="4">
         <v>67</v>
       </c>
@@ -7494,7 +7494,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="4">
         <v>68</v>
       </c>
@@ -7526,7 +7526,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="4">
         <v>69</v>
       </c>
@@ -7558,7 +7558,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="4">
         <v>70</v>
       </c>
@@ -7587,7 +7587,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="72" spans="1:10">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="4">
         <v>71</v>
       </c>
@@ -7604,7 +7604,7 @@
         <v>19</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="G72" s="4" t="s">
         <v>14</v>
@@ -7616,10 +7616,10 @@
         <v>574</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>1262</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="4">
         <v>72</v>
       </c>
@@ -7651,7 +7651,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="4">
         <v>73</v>
       </c>
@@ -7683,7 +7683,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="75" spans="1:10">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="4">
         <v>74</v>
       </c>
@@ -7712,7 +7712,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="76" spans="1:10">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="4">
         <v>75</v>
       </c>
@@ -7744,7 +7744,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="77" spans="1:10">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" s="4">
         <v>76</v>
       </c>
@@ -7776,7 +7776,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="78" spans="1:10">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="4">
         <v>77</v>
       </c>
@@ -7808,7 +7808,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="4">
         <v>78</v>
       </c>
@@ -7840,7 +7840,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="80" spans="1:10">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="4">
         <v>79</v>
       </c>
@@ -7854,7 +7854,7 @@
         <v>655</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>162</v>
@@ -7872,7 +7872,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="81" spans="1:10">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="4">
         <v>80</v>
       </c>
@@ -7886,7 +7886,7 @@
         <v>164</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>165</v>
@@ -7904,7 +7904,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="82" spans="1:10">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="4">
         <v>81</v>
       </c>
@@ -7918,7 +7918,7 @@
         <v>656</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>167</v>
@@ -7930,7 +7930,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="83" spans="1:10">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="4">
         <v>82</v>
       </c>
@@ -7944,7 +7944,7 @@
         <v>657</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>168</v>
@@ -7956,7 +7956,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="84" spans="1:10">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" s="4">
         <v>83</v>
       </c>
@@ -7970,7 +7970,7 @@
         <v>658</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>169</v>
@@ -7982,7 +7982,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="85" spans="1:10">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="4">
         <v>84</v>
       </c>
@@ -7996,7 +7996,7 @@
         <v>659</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>170</v>
@@ -8014,7 +8014,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="86" spans="1:10">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" s="4">
         <v>85</v>
       </c>
@@ -8028,7 +8028,7 @@
         <v>172</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>173</v>
@@ -8046,7 +8046,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="87" spans="1:10">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="4">
         <v>86</v>
       </c>
@@ -8057,7 +8057,7 @@
         <v>11</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>21</v>
@@ -8075,10 +8075,10 @@
         <v>574</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>1196</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" s="4">
         <v>87</v>
       </c>
@@ -8092,7 +8092,7 @@
         <v>660</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>176</v>
@@ -8110,7 +8110,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="89" spans="1:10">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="4">
         <v>88</v>
       </c>
@@ -8124,7 +8124,7 @@
         <v>661</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>178</v>
@@ -8139,7 +8139,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="90" spans="1:10">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" s="4">
         <v>89</v>
       </c>
@@ -8153,10 +8153,10 @@
         <v>662</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>30</v>
@@ -8168,10 +8168,10 @@
         <v>574</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" s="4">
         <v>90</v>
       </c>
@@ -8185,7 +8185,7 @@
         <v>663</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>180</v>
@@ -8203,7 +8203,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="92" spans="1:10">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" s="4">
         <v>91</v>
       </c>
@@ -8217,7 +8217,7 @@
         <v>664</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>181</v>
@@ -8229,7 +8229,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="93" spans="1:10">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" s="4">
         <v>92</v>
       </c>
@@ -8243,7 +8243,7 @@
         <v>665</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>182</v>
@@ -8255,7 +8255,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="94" spans="1:10">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" s="4">
         <v>93</v>
       </c>
@@ -8269,7 +8269,7 @@
         <v>184</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>185</v>
@@ -8287,7 +8287,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="95" spans="1:10">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="4">
         <v>94</v>
       </c>
@@ -8298,10 +8298,10 @@
         <v>11</v>
       </c>
       <c r="D95" s="2" t="s">
+        <v>965</v>
+      </c>
+      <c r="E95" s="1" t="s">
         <v>966</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>967</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>190</v>
@@ -8316,7 +8316,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="96" spans="1:10">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" s="4">
         <v>95</v>
       </c>
@@ -8345,7 +8345,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="97" spans="1:10">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" s="4">
         <v>96</v>
       </c>
@@ -8374,7 +8374,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="98" spans="1:10">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" s="4">
         <v>97</v>
       </c>
@@ -8403,7 +8403,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="99" spans="1:10">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" s="4">
         <v>98</v>
       </c>
@@ -8435,7 +8435,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="100" spans="1:10">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" s="4">
         <v>99</v>
       </c>
@@ -8467,7 +8467,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="101" spans="1:10">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" s="4">
         <v>100</v>
       </c>
@@ -8499,7 +8499,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="102" spans="1:10">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" s="4">
         <v>101</v>
       </c>
@@ -8516,7 +8516,7 @@
         <v>76</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="G102" s="4" t="s">
         <v>14</v>
@@ -8528,10 +8528,10 @@
         <v>574</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" s="4">
         <v>102</v>
       </c>
@@ -8563,7 +8563,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="104" spans="1:10">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" s="4">
         <v>103</v>
       </c>
@@ -8595,7 +8595,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="105" spans="1:10">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" s="4">
         <v>104</v>
       </c>
@@ -8627,7 +8627,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="106" spans="1:10">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" s="4">
         <v>105</v>
       </c>
@@ -8659,7 +8659,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="107" spans="1:10">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" s="4">
         <v>106</v>
       </c>
@@ -8691,7 +8691,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="108" spans="1:10">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" s="4">
         <v>107</v>
       </c>
@@ -8702,7 +8702,7 @@
         <v>11</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>21</v>
@@ -8719,7 +8719,7 @@
       </c>
       <c r="J108" s="24"/>
     </row>
-    <row r="109" spans="1:10">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" s="4">
         <v>108</v>
       </c>
@@ -8751,7 +8751,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="110" spans="1:10">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" s="4">
         <v>109</v>
       </c>
@@ -8783,7 +8783,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="111" spans="1:10">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" s="4">
         <v>110</v>
       </c>
@@ -8815,7 +8815,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="112" spans="1:10">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" s="4">
         <v>111</v>
       </c>
@@ -8847,7 +8847,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="113" spans="1:10">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" s="4">
         <v>112</v>
       </c>
@@ -8879,7 +8879,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="114" spans="1:10">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" s="4">
         <v>113</v>
       </c>
@@ -8911,7 +8911,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="115" spans="1:10">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" s="4">
         <v>114</v>
       </c>
@@ -8943,7 +8943,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="116" spans="1:10">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" s="4">
         <v>115</v>
       </c>
@@ -8975,7 +8975,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="117" spans="1:10">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" s="4">
         <v>116</v>
       </c>
@@ -9007,7 +9007,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="118" spans="1:10">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" s="4">
         <v>117</v>
       </c>
@@ -9039,7 +9039,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="119" spans="1:10">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" s="4">
         <v>118</v>
       </c>
@@ -9071,7 +9071,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="120" spans="1:10">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" s="4">
         <v>119</v>
       </c>
@@ -9103,7 +9103,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="121" spans="1:10">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" s="4">
         <v>120</v>
       </c>
@@ -9135,7 +9135,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="122" spans="1:10">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" s="4">
         <v>121</v>
       </c>
@@ -9167,7 +9167,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="123" spans="1:10">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" s="4">
         <v>122</v>
       </c>
@@ -9196,10 +9196,10 @@
         <v>574</v>
       </c>
       <c r="J123" s="3" t="s">
-        <v>1207</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" s="4">
         <v>123</v>
       </c>
@@ -9216,7 +9216,7 @@
         <v>68</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="G124" s="1" t="s">
         <v>30</v>
@@ -9231,7 +9231,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="125" spans="1:10">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" s="4">
         <v>124</v>
       </c>
@@ -9248,7 +9248,7 @@
         <v>68</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="G125" s="4" t="s">
         <v>14</v>
@@ -9260,10 +9260,10 @@
         <v>574</v>
       </c>
       <c r="J125" s="3" t="s">
-        <v>1208</v>
-      </c>
-    </row>
-    <row r="126" spans="1:10">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" s="4">
         <v>125</v>
       </c>
@@ -9280,7 +9280,7 @@
         <v>19</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="G126" s="1" t="s">
         <v>30</v>
@@ -9295,7 +9295,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="127" spans="1:10">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" s="4">
         <v>126</v>
       </c>
@@ -9327,7 +9327,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="128" spans="1:10">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" s="4">
         <v>127</v>
       </c>
@@ -9359,7 +9359,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="129" spans="1:10">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" s="4">
         <v>128</v>
       </c>
@@ -9391,7 +9391,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="130" spans="1:10">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" s="4">
         <v>129</v>
       </c>
@@ -9423,7 +9423,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="131" spans="1:10">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" s="4">
         <v>130</v>
       </c>
@@ -9455,7 +9455,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="132" spans="1:10">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" s="4">
         <v>131</v>
       </c>
@@ -9472,7 +9472,7 @@
         <v>19</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="G132" s="4" t="s">
         <v>14</v>
@@ -9487,7 +9487,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="133" spans="1:10">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" s="4">
         <v>132</v>
       </c>
@@ -9504,7 +9504,7 @@
         <v>19</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="G133" s="4" t="s">
         <v>14</v>
@@ -9516,10 +9516,10 @@
         <v>574</v>
       </c>
       <c r="J133" s="3" t="s">
-        <v>1263</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" s="4">
         <v>133</v>
       </c>
@@ -9536,7 +9536,7 @@
         <v>19</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="G134" s="4" t="s">
         <v>14</v>
@@ -9551,7 +9551,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="135" spans="1:10">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" s="4">
         <v>134</v>
       </c>
@@ -9580,10 +9580,10 @@
         <v>574</v>
       </c>
       <c r="J135" s="3" t="s">
-        <v>1084</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" s="4">
         <v>135</v>
       </c>
@@ -9600,7 +9600,7 @@
         <v>19</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="G136" s="4" t="s">
         <v>14</v>
@@ -9615,7 +9615,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="137" spans="1:10">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" s="4">
         <v>136</v>
       </c>
@@ -9647,7 +9647,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="138" spans="1:10">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" s="4">
         <v>137</v>
       </c>
@@ -9676,10 +9676,10 @@
         <v>574</v>
       </c>
       <c r="J138" s="3" t="s">
-        <v>1310</v>
-      </c>
-    </row>
-    <row r="139" spans="1:10">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" s="4">
         <v>138</v>
       </c>
@@ -9708,10 +9708,10 @@
         <v>646</v>
       </c>
       <c r="J139" s="3" t="s">
-        <v>1091</v>
-      </c>
-    </row>
-    <row r="140" spans="1:10">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" s="4">
         <v>139</v>
       </c>
@@ -9743,7 +9743,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="141" spans="1:10">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" s="4">
         <v>140</v>
       </c>
@@ -9757,10 +9757,10 @@
         <v>241</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>76</v>
+        <v>21</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>1072</v>
+        <v>23</v>
       </c>
       <c r="G141" s="4" t="s">
         <v>14</v>
@@ -9772,10 +9772,10 @@
         <v>574</v>
       </c>
       <c r="J141" s="12" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="142" spans="1:10">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" s="4">
         <v>141</v>
       </c>
@@ -9792,7 +9792,7 @@
         <v>13</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="G142" s="4" t="s">
         <v>14</v>
@@ -9804,15 +9804,15 @@
         <v>574</v>
       </c>
       <c r="J142" s="3" t="s">
-        <v>1309</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" s="4">
         <v>142</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>83</v>
@@ -9824,7 +9824,7 @@
         <v>68</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="G143" s="1" t="s">
         <v>68</v>
@@ -9837,7 +9837,7 @@
       </c>
       <c r="J143" s="24"/>
     </row>
-    <row r="144" spans="1:10">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" s="4">
         <v>143</v>
       </c>
@@ -9854,7 +9854,7 @@
         <v>68</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="G144" s="4" t="s">
         <v>14</v>
@@ -9866,10 +9866,10 @@
         <v>574</v>
       </c>
       <c r="J144" s="3" t="s">
-        <v>1035</v>
-      </c>
-    </row>
-    <row r="145" spans="1:10">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" s="4">
         <v>144</v>
       </c>
@@ -9880,13 +9880,13 @@
         <v>83</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="G145" s="4" t="s">
         <v>14</v>
@@ -9898,10 +9898,10 @@
         <v>574</v>
       </c>
       <c r="J145" s="3" t="s">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="146" spans="1:10">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" s="4">
         <v>145</v>
       </c>
@@ -9918,7 +9918,7 @@
         <v>68</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="G146" s="13" t="s">
         <v>14</v>
@@ -9933,7 +9933,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="147" spans="1:10">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" s="4">
         <v>146</v>
       </c>
@@ -9950,7 +9950,7 @@
         <v>19</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="G147" s="13" t="s">
         <v>14</v>
@@ -9962,10 +9962,10 @@
         <v>574</v>
       </c>
       <c r="J147" s="3" t="s">
-        <v>1293</v>
-      </c>
-    </row>
-    <row r="148" spans="1:10">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" s="4">
         <v>147</v>
       </c>
@@ -9982,7 +9982,7 @@
         <v>68</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="G148" s="13" t="s">
         <v>14</v>
@@ -9997,7 +9997,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="149" spans="1:10">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" s="4">
         <v>148</v>
       </c>
@@ -10014,7 +10014,7 @@
         <v>68</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="G149" s="13" t="s">
         <v>14</v>
@@ -10029,7 +10029,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="150" spans="1:10">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A150" s="4">
         <v>149</v>
       </c>
@@ -10040,13 +10040,13 @@
         <v>83</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="G150" s="13" t="s">
         <v>14</v>
@@ -10058,10 +10058,10 @@
         <v>646</v>
       </c>
       <c r="J150" s="3" t="s">
-        <v>1290</v>
-      </c>
-    </row>
-    <row r="151" spans="1:10">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151" s="4">
         <v>150</v>
       </c>
@@ -10072,13 +10072,13 @@
         <v>83</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="G151" s="13" t="s">
         <v>14</v>
@@ -10090,10 +10090,10 @@
         <v>574</v>
       </c>
       <c r="J151" s="3" t="s">
-        <v>1283</v>
-      </c>
-    </row>
-    <row r="152" spans="1:10">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A152" s="4">
         <v>151</v>
       </c>
@@ -10104,13 +10104,13 @@
         <v>83</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="G152" s="13" t="s">
         <v>14</v>
@@ -10123,7 +10123,7 @@
       </c>
       <c r="J152" s="24"/>
     </row>
-    <row r="153" spans="1:10">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153" s="4">
         <v>152</v>
       </c>
@@ -10134,13 +10134,13 @@
         <v>83</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="G153" s="13" t="s">
         <v>14</v>
@@ -10153,7 +10153,7 @@
       </c>
       <c r="J153" s="24"/>
     </row>
-    <row r="154" spans="1:10">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A154" s="4">
         <v>153</v>
       </c>
@@ -10164,13 +10164,13 @@
         <v>83</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="G154" s="13" t="s">
         <v>14</v>
@@ -10182,10 +10182,10 @@
         <v>646</v>
       </c>
       <c r="J154" s="3" t="s">
-        <v>1265</v>
-      </c>
-    </row>
-    <row r="155" spans="1:10">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155" s="4">
         <v>154</v>
       </c>
@@ -10196,13 +10196,13 @@
         <v>83</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="G155" s="13" t="s">
         <v>14</v>
@@ -10214,10 +10214,10 @@
         <v>574</v>
       </c>
       <c r="J155" s="3" t="s">
-        <v>1304</v>
-      </c>
-    </row>
-    <row r="156" spans="1:10">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A156" s="4">
         <v>155</v>
       </c>
@@ -10228,13 +10228,13 @@
         <v>83</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="G156" s="13" t="s">
         <v>14</v>
@@ -10246,10 +10246,10 @@
         <v>574</v>
       </c>
       <c r="J156" s="3" t="s">
-        <v>1307</v>
-      </c>
-    </row>
-    <row r="157" spans="1:10">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B157" s="2" t="s">
         <v>244</v>
       </c>
@@ -10257,13 +10257,13 @@
         <v>83</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="G157" s="13" t="s">
         <v>14</v>
@@ -10275,10 +10275,10 @@
         <v>574</v>
       </c>
       <c r="J157" s="3" t="s">
-        <v>1313</v>
-      </c>
-    </row>
-    <row r="158" spans="1:10">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A158" s="4">
         <v>156</v>
       </c>
@@ -10307,10 +10307,10 @@
         <v>574</v>
       </c>
       <c r="J158" s="3" t="s">
-        <v>1294</v>
-      </c>
-    </row>
-    <row r="159" spans="1:10">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A159" s="4">
         <v>157</v>
       </c>
@@ -10342,7 +10342,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="160" spans="1:10">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A160" s="4">
         <v>158</v>
       </c>
@@ -10374,7 +10374,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="161" spans="1:10">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161" s="4">
         <v>159</v>
       </c>
@@ -10391,7 +10391,7 @@
         <v>68</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="G161" s="4" t="s">
         <v>14</v>
@@ -10403,10 +10403,10 @@
         <v>574</v>
       </c>
       <c r="J161" s="3" t="s">
-        <v>1102</v>
-      </c>
-    </row>
-    <row r="162" spans="1:10">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162" s="4">
         <v>160</v>
       </c>
@@ -10438,7 +10438,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="163" spans="1:10">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163" s="4">
         <v>161</v>
       </c>
@@ -10467,10 +10467,10 @@
         <v>574</v>
       </c>
       <c r="J163" s="7" t="s">
-        <v>907</v>
-      </c>
-    </row>
-    <row r="164" spans="1:10">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" s="4">
         <v>162</v>
       </c>
@@ -10487,7 +10487,7 @@
         <v>350</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="G164" s="4" t="s">
         <v>14</v>
@@ -10499,10 +10499,10 @@
         <v>646</v>
       </c>
       <c r="J164" s="3" t="s">
-        <v>867</v>
-      </c>
-    </row>
-    <row r="165" spans="1:10">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165" s="4">
         <v>163</v>
       </c>
@@ -10531,7 +10531,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="166" spans="1:10">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A166" s="4">
         <v>164</v>
       </c>
@@ -10560,7 +10560,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="167" spans="1:10">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A167" s="4">
         <v>165</v>
       </c>
@@ -10587,7 +10587,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="168" spans="1:10">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A168" s="4">
         <v>166</v>
       </c>
@@ -10604,7 +10604,7 @@
         <v>350</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="G168" s="4" t="s">
         <v>14</v>
@@ -10616,10 +10616,10 @@
         <v>574</v>
       </c>
       <c r="J168" s="3" t="s">
-        <v>1095</v>
-      </c>
-    </row>
-    <row r="169" spans="1:10">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A169" s="4">
         <v>167</v>
       </c>
@@ -10648,7 +10648,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="170" spans="1:10">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A170" s="4">
         <v>168</v>
       </c>
@@ -10680,7 +10680,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="171" spans="1:10">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A171" s="4">
         <v>169</v>
       </c>
@@ -10712,7 +10712,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="172" spans="1:10">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A172" s="4">
         <v>170</v>
       </c>
@@ -10741,10 +10741,10 @@
         <v>574</v>
       </c>
       <c r="J172" s="3" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="173" spans="1:10">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A173" s="4">
         <v>171</v>
       </c>
@@ -10776,7 +10776,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="174" spans="1:10">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A174" s="4">
         <v>172</v>
       </c>
@@ -10805,7 +10805,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="175" spans="1:10">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A175" s="4">
         <v>173</v>
       </c>
@@ -10834,7 +10834,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="176" spans="1:10">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A176" s="4">
         <v>174</v>
       </c>
@@ -10866,7 +10866,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="177" spans="1:10">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A177" s="4">
         <v>175</v>
       </c>
@@ -10880,7 +10880,7 @@
         <v>188</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>189</v>
@@ -10892,7 +10892,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="178" spans="1:10">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A178" s="4">
         <v>176</v>
       </c>
@@ -10903,13 +10903,13 @@
         <v>83</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="G178" s="4" t="s">
         <v>14</v>
@@ -10922,7 +10922,7 @@
       </c>
       <c r="J178" s="24"/>
     </row>
-    <row r="179" spans="1:10">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A179" s="4">
         <v>177</v>
       </c>
@@ -10951,10 +10951,10 @@
         <v>574</v>
       </c>
       <c r="J179" s="3" t="s">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="180" spans="1:10">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A180" s="4">
         <v>178</v>
       </c>
@@ -10968,10 +10968,10 @@
         <v>286</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="G180" s="4" t="s">
         <v>14</v>
@@ -10983,7 +10983,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="181" spans="1:10">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A181" s="4">
         <v>179</v>
       </c>
@@ -10994,7 +10994,7 @@
         <v>83</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>13</v>
@@ -11012,10 +11012,10 @@
         <v>574</v>
       </c>
       <c r="J181" s="3" t="s">
-        <v>1237</v>
-      </c>
-    </row>
-    <row r="182" spans="1:10">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A182" s="4">
         <v>180</v>
       </c>
@@ -11029,10 +11029,10 @@
         <v>287</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="G182" s="4" t="s">
         <v>14</v>
@@ -11044,7 +11044,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="183" spans="1:10">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A183" s="4">
         <v>181</v>
       </c>
@@ -11073,7 +11073,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="184" spans="1:10">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A184" s="4">
         <v>182</v>
       </c>
@@ -11102,7 +11102,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="185" spans="1:10">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A185" s="4">
         <v>183</v>
       </c>
@@ -11131,7 +11131,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="186" spans="1:10">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A186" s="4">
         <v>184</v>
       </c>
@@ -11160,7 +11160,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="187" spans="1:10">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A187" s="4">
         <v>185</v>
       </c>
@@ -11189,7 +11189,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="188" spans="1:10">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A188" s="4">
         <v>186</v>
       </c>
@@ -11218,7 +11218,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="189" spans="1:10">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A189" s="4">
         <v>187</v>
       </c>
@@ -11247,7 +11247,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="190" spans="1:10">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A190" s="4">
         <v>188</v>
       </c>
@@ -11276,7 +11276,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="191" spans="1:10">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A191" s="4">
         <v>189</v>
       </c>
@@ -11305,7 +11305,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="192" spans="1:10">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A192" s="4">
         <v>190</v>
       </c>
@@ -11334,7 +11334,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="193" spans="1:10">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A193" s="4">
         <v>191</v>
       </c>
@@ -11363,7 +11363,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="194" spans="1:10">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A194" s="4">
         <v>192</v>
       </c>
@@ -11392,7 +11392,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="195" spans="1:10">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A195" s="4">
         <v>193</v>
       </c>
@@ -11421,7 +11421,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="196" spans="1:10">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A196" s="4">
         <v>194</v>
       </c>
@@ -11450,7 +11450,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="197" spans="1:10">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A197" s="4">
         <v>195</v>
       </c>
@@ -11479,7 +11479,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="198" spans="1:10">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" s="4">
         <v>196</v>
       </c>
@@ -11508,7 +11508,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="199" spans="1:10">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" s="4">
         <v>197</v>
       </c>
@@ -11537,7 +11537,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="200" spans="1:10">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" s="4">
         <v>198</v>
       </c>
@@ -11566,7 +11566,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="201" spans="1:10">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" s="4">
         <v>199</v>
       </c>
@@ -11595,7 +11595,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="202" spans="1:10">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" s="4">
         <v>200</v>
       </c>
@@ -11624,7 +11624,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="203" spans="1:10">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" s="4">
         <v>201</v>
       </c>
@@ -11653,7 +11653,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="204" spans="1:10">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" s="4">
         <v>202</v>
       </c>
@@ -11685,7 +11685,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="205" spans="1:10">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205" s="4">
         <v>203</v>
       </c>
@@ -11714,10 +11714,10 @@
         <v>574</v>
       </c>
       <c r="J205" s="3" t="s">
-        <v>1257</v>
-      </c>
-    </row>
-    <row r="206" spans="1:10">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" s="4">
         <v>204</v>
       </c>
@@ -11731,10 +11731,10 @@
         <v>314</v>
       </c>
       <c r="E206" s="4" t="s">
+        <v>957</v>
+      </c>
+      <c r="F206" s="4" t="s">
         <v>958</v>
-      </c>
-      <c r="F206" s="4" t="s">
-        <v>959</v>
       </c>
       <c r="G206" s="4" t="s">
         <v>14</v>
@@ -11749,7 +11749,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="207" spans="1:10">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207" s="4">
         <v>205</v>
       </c>
@@ -11781,7 +11781,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="208" spans="1:10">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A208" s="4">
         <v>206</v>
       </c>
@@ -11792,13 +11792,13 @@
         <v>11</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="E208" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="G208" s="4" t="s">
         <v>14</v>
@@ -11811,7 +11811,7 @@
       </c>
       <c r="J208" s="24"/>
     </row>
-    <row r="209" spans="1:10">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A209" s="4">
         <v>207</v>
       </c>
@@ -11822,7 +11822,7 @@
         <v>11</v>
       </c>
       <c r="D209" s="5" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="E209" s="4" t="s">
         <v>21</v>
@@ -11840,10 +11840,10 @@
         <v>574</v>
       </c>
       <c r="J209" s="3" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="210" spans="1:10">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210" s="4">
         <v>208</v>
       </c>
@@ -11857,10 +11857,10 @@
         <v>316</v>
       </c>
       <c r="E210" s="4" t="s">
+        <v>957</v>
+      </c>
+      <c r="F210" s="4" t="s">
         <v>958</v>
-      </c>
-      <c r="F210" s="4" t="s">
-        <v>959</v>
       </c>
       <c r="G210" s="4" t="s">
         <v>14</v>
@@ -11875,7 +11875,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="211" spans="1:10">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A211" s="4">
         <v>209</v>
       </c>
@@ -11907,7 +11907,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="212" spans="1:10">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A212" s="4">
         <v>210</v>
       </c>
@@ -11924,7 +11924,7 @@
         <v>19</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="G212" s="4" t="s">
         <v>14</v>
@@ -11936,10 +11936,10 @@
         <v>574</v>
       </c>
       <c r="J212" s="8" t="s">
-        <v>1040</v>
-      </c>
-    </row>
-    <row r="213" spans="1:10">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A213" s="4">
         <v>211</v>
       </c>
@@ -11971,7 +11971,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="214" spans="1:10">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A214" s="4">
         <v>212</v>
       </c>
@@ -12000,10 +12000,10 @@
         <v>574</v>
       </c>
       <c r="J214" s="3" t="s">
-        <v>1261</v>
-      </c>
-    </row>
-    <row r="215" spans="1:10">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A215" s="4">
         <v>213</v>
       </c>
@@ -12014,13 +12014,13 @@
         <v>11</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="E215" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="G215" s="1" t="s">
         <v>30</v>
@@ -12032,10 +12032,10 @@
         <v>574</v>
       </c>
       <c r="J215" s="3" t="s">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="216" spans="1:10">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A216" s="4">
         <v>214</v>
       </c>
@@ -12064,10 +12064,10 @@
         <v>574</v>
       </c>
       <c r="J216" s="3" t="s">
-        <v>1017</v>
-      </c>
-    </row>
-    <row r="217" spans="1:10">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A217" s="4">
         <v>215</v>
       </c>
@@ -12099,7 +12099,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="218" spans="1:10">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A218" s="4">
         <v>216</v>
       </c>
@@ -12116,7 +12116,7 @@
         <v>19</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="G218" s="4" t="s">
         <v>14</v>
@@ -12128,10 +12128,10 @@
         <v>574</v>
       </c>
       <c r="J218" s="3" t="s">
-        <v>1047</v>
-      </c>
-    </row>
-    <row r="219" spans="1:10">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A219" s="4">
         <v>217</v>
       </c>
@@ -12148,7 +12148,7 @@
         <v>19</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="G219" s="4" t="s">
         <v>14</v>
@@ -12163,7 +12163,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="220" spans="1:10">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A220" s="4">
         <v>218</v>
       </c>
@@ -12180,7 +12180,7 @@
         <v>76</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="G220" s="4" t="s">
         <v>14</v>
@@ -12192,10 +12192,10 @@
         <v>574</v>
       </c>
       <c r="J220" s="3" t="s">
-        <v>1029</v>
-      </c>
-    </row>
-    <row r="221" spans="1:10">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A221" s="4">
         <v>219</v>
       </c>
@@ -12224,10 +12224,10 @@
         <v>574</v>
       </c>
       <c r="J221" s="3" t="s">
-        <v>918</v>
-      </c>
-    </row>
-    <row r="222" spans="1:10">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A222" s="4">
         <v>220</v>
       </c>
@@ -12259,7 +12259,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="223" spans="1:10">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A223" s="4">
         <v>221</v>
       </c>
@@ -12291,7 +12291,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="224" spans="1:10">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A224" s="4">
         <v>222</v>
       </c>
@@ -12323,7 +12323,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="225" spans="1:10">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A225" s="4">
         <v>223</v>
       </c>
@@ -12355,7 +12355,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="226" spans="1:10">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A226" s="4">
         <v>224</v>
       </c>
@@ -12384,10 +12384,10 @@
         <v>574</v>
       </c>
       <c r="J226" s="3" t="s">
-        <v>1049</v>
-      </c>
-    </row>
-    <row r="227" spans="1:10">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227" s="4">
         <v>225</v>
       </c>
@@ -12404,7 +12404,7 @@
         <v>19</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="G227" s="4" t="s">
         <v>14</v>
@@ -12416,10 +12416,10 @@
         <v>574</v>
       </c>
       <c r="J227" s="3" t="s">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="228" spans="1:10">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A228" s="4">
         <v>226</v>
       </c>
@@ -12451,7 +12451,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="229" spans="1:10">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A229" s="4">
         <v>227</v>
       </c>
@@ -12468,7 +12468,7 @@
         <v>19</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="G229" s="4" t="s">
         <v>14</v>
@@ -12483,7 +12483,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="230" spans="1:10">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A230" s="4">
         <v>228</v>
       </c>
@@ -12512,10 +12512,10 @@
         <v>574</v>
       </c>
       <c r="J230" s="3" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="231" spans="1:10">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A231" s="4">
         <v>229</v>
       </c>
@@ -12532,7 +12532,7 @@
         <v>19</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="G231" s="4" t="s">
         <v>14</v>
@@ -12544,10 +12544,10 @@
         <v>574</v>
       </c>
       <c r="J231" s="3" t="s">
-        <v>1080</v>
-      </c>
-    </row>
-    <row r="232" spans="1:10">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A232" s="4">
         <v>230</v>
       </c>
@@ -12579,7 +12579,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="233" spans="1:10">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A233" s="4">
         <v>231</v>
       </c>
@@ -12608,10 +12608,10 @@
         <v>574</v>
       </c>
       <c r="J233" s="3" t="s">
-        <v>1259</v>
-      </c>
-    </row>
-    <row r="234" spans="1:10">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A234" s="4">
         <v>232</v>
       </c>
@@ -12628,7 +12628,7 @@
         <v>19</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="G234" s="4" t="s">
         <v>14</v>
@@ -12640,10 +12640,10 @@
         <v>574</v>
       </c>
       <c r="J234" s="3" t="s">
-        <v>1278</v>
-      </c>
-    </row>
-    <row r="235" spans="1:10">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A235" s="4">
         <v>233</v>
       </c>
@@ -12675,7 +12675,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="236" spans="1:10">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A236" s="4">
         <v>234</v>
       </c>
@@ -12707,7 +12707,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="237" spans="1:10">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A237" s="4">
         <v>235</v>
       </c>
@@ -12739,7 +12739,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="238" spans="1:10">
+    <row r="238" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A238" s="4">
         <v>236</v>
       </c>
@@ -12756,7 +12756,7 @@
         <v>19</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="G238" s="4" t="s">
         <v>14</v>
@@ -12768,10 +12768,10 @@
         <v>574</v>
       </c>
       <c r="J238" s="3" t="s">
-        <v>1041</v>
-      </c>
-    </row>
-    <row r="239" spans="1:10">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="239" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A239" s="4">
         <v>237</v>
       </c>
@@ -12803,7 +12803,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="240" spans="1:10">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A240" s="4">
         <v>238</v>
       </c>
@@ -12820,7 +12820,7 @@
         <v>76</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="G240" s="4" t="s">
         <v>14</v>
@@ -12832,10 +12832,10 @@
         <v>574</v>
       </c>
       <c r="J240" s="7" t="s">
-        <v>1090</v>
-      </c>
-    </row>
-    <row r="241" spans="1:10">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="241" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A241" s="4">
         <v>239</v>
       </c>
@@ -12852,7 +12852,7 @@
         <v>19</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="G241" s="4" t="s">
         <v>14</v>
@@ -12867,7 +12867,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="242" spans="1:10" ht="15.6">
+    <row r="242" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A242" s="4">
         <v>240</v>
       </c>
@@ -12884,7 +12884,7 @@
         <v>19</v>
       </c>
       <c r="F242" s="50" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="G242" s="4" t="s">
         <v>14</v>
@@ -12896,10 +12896,10 @@
         <v>574</v>
       </c>
       <c r="J242" s="7" t="s">
-        <v>1038</v>
-      </c>
-    </row>
-    <row r="243" spans="1:10">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A243" s="4">
         <v>241</v>
       </c>
@@ -12916,7 +12916,7 @@
         <v>19</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="G243" s="4" t="s">
         <v>14</v>
@@ -12928,10 +12928,10 @@
         <v>646</v>
       </c>
       <c r="J243" s="3" t="s">
-        <v>1030</v>
-      </c>
-    </row>
-    <row r="244" spans="1:10">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A244" s="4">
         <v>242</v>
       </c>
@@ -12948,7 +12948,7 @@
         <v>19</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="G244" s="4" t="s">
         <v>14</v>
@@ -12963,7 +12963,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="245" spans="1:10">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A245" s="4">
         <v>243</v>
       </c>
@@ -12980,7 +12980,7 @@
         <v>19</v>
       </c>
       <c r="F245" s="41" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G245" s="4" t="s">
         <v>14</v>
@@ -12992,10 +12992,10 @@
         <v>574</v>
       </c>
       <c r="J245" s="8" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="246" spans="1:10">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="246" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A246" s="4">
         <v>244</v>
       </c>
@@ -13024,10 +13024,10 @@
         <v>574</v>
       </c>
       <c r="J246" s="8" t="s">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="247" spans="1:10">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="247" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A247" s="4">
         <v>245</v>
       </c>
@@ -13041,10 +13041,10 @@
         <v>573</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="G247" s="1" t="s">
         <v>14</v>
@@ -13057,7 +13057,7 @@
       </c>
       <c r="J247" s="20"/>
     </row>
-    <row r="248" spans="1:10">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A248" s="4">
         <v>246</v>
       </c>
@@ -13089,7 +13089,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="249" spans="1:10">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A249" s="4">
         <v>247</v>
       </c>
@@ -13118,10 +13118,10 @@
         <v>574</v>
       </c>
       <c r="J249" s="3" t="s">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="250" spans="1:10">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A250" s="4">
         <v>248</v>
       </c>
@@ -13150,10 +13150,10 @@
         <v>574</v>
       </c>
       <c r="J250" s="3" t="s">
-        <v>1228</v>
-      </c>
-    </row>
-    <row r="251" spans="1:10">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A251" s="4">
         <v>249</v>
       </c>
@@ -13170,7 +13170,7 @@
         <v>68</v>
       </c>
       <c r="F251" s="4" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="G251" s="4" t="s">
         <v>14</v>
@@ -13182,15 +13182,15 @@
         <v>574</v>
       </c>
       <c r="J251" s="3" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="252" spans="1:10">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A252" s="4">
         <v>250</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>11</v>
@@ -13202,7 +13202,7 @@
         <v>19</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="G252" s="1" t="s">
         <v>19</v>
@@ -13217,7 +13217,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="253" spans="1:10">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A253" s="4">
         <v>251</v>
       </c>
@@ -13246,7 +13246,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="254" spans="1:10">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A254" s="4">
         <v>252</v>
       </c>
@@ -13278,7 +13278,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="255" spans="1:10">
+    <row r="255" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A255" s="4">
         <v>253</v>
       </c>
@@ -13307,10 +13307,10 @@
         <v>574</v>
       </c>
       <c r="J255" s="3" t="s">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="256" spans="1:10">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="256" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A256" s="4">
         <v>254</v>
       </c>
@@ -13342,7 +13342,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="257" spans="1:10">
+    <row r="257" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A257" s="4">
         <v>255</v>
       </c>
@@ -13356,7 +13356,7 @@
         <v>377</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="F257" s="1" t="s">
         <v>378</v>
@@ -13371,7 +13371,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="258" spans="1:10">
+    <row r="258" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A258" s="4">
         <v>256</v>
       </c>
@@ -13385,7 +13385,7 @@
         <v>668</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="F258" s="1" t="s">
         <v>380</v>
@@ -13403,7 +13403,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="259" spans="1:10">
+    <row r="259" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A259" s="4">
         <v>257</v>
       </c>
@@ -13417,7 +13417,7 @@
         <v>381</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="F259" s="1" t="s">
         <v>382</v>
@@ -13432,7 +13432,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="260" spans="1:10">
+    <row r="260" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A260" s="4">
         <v>258</v>
       </c>
@@ -13446,7 +13446,7 @@
         <v>383</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="F260" s="1" t="s">
         <v>175</v>
@@ -13461,7 +13461,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="261" spans="1:10">
+    <row r="261" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A261" s="4">
         <v>259</v>
       </c>
@@ -13493,7 +13493,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="262" spans="1:10">
+    <row r="262" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A262" s="4">
         <v>260</v>
       </c>
@@ -13522,10 +13522,10 @@
         <v>574</v>
       </c>
       <c r="J262" s="3" t="s">
-        <v>1085</v>
-      </c>
-    </row>
-    <row r="263" spans="1:10">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="263" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A263" s="4">
         <v>261</v>
       </c>
@@ -13542,7 +13542,7 @@
         <v>19</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="G263" s="4" t="s">
         <v>14</v>
@@ -13554,10 +13554,10 @@
         <v>574</v>
       </c>
       <c r="J263" s="3" t="s">
-        <v>1235</v>
-      </c>
-    </row>
-    <row r="264" spans="1:10">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="264" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A264" s="4">
         <v>262</v>
       </c>
@@ -13574,7 +13574,7 @@
         <v>19</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="G264" s="4" t="s">
         <v>14</v>
@@ -13586,10 +13586,10 @@
         <v>574</v>
       </c>
       <c r="J264" s="3" t="s">
-        <v>1280</v>
-      </c>
-    </row>
-    <row r="265" spans="1:10">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="265" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A265" s="4">
         <v>263</v>
       </c>
@@ -13621,7 +13621,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="266" spans="1:10">
+    <row r="266" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A266" s="4">
         <v>264</v>
       </c>
@@ -13653,7 +13653,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="267" spans="1:10">
+    <row r="267" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A267" s="4">
         <v>265</v>
       </c>
@@ -13682,10 +13682,10 @@
         <v>574</v>
       </c>
       <c r="J267" s="3" t="s">
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="268" spans="1:10">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="268" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A268" s="4">
         <v>266</v>
       </c>
@@ -13717,7 +13717,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="269" spans="1:10">
+    <row r="269" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A269" s="4">
         <v>267</v>
       </c>
@@ -13749,7 +13749,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="270" spans="1:10">
+    <row r="270" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A270" s="4">
         <v>268</v>
       </c>
@@ -13781,7 +13781,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="271" spans="1:10">
+    <row r="271" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A271" s="4">
         <v>269</v>
       </c>
@@ -13813,7 +13813,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="272" spans="1:10">
+    <row r="272" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A272" s="4">
         <v>270</v>
       </c>
@@ -13830,7 +13830,7 @@
         <v>13</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="G272" s="4" t="s">
         <v>14</v>
@@ -13842,10 +13842,10 @@
         <v>646</v>
       </c>
       <c r="J272" s="3" t="s">
-        <v>1239</v>
-      </c>
-    </row>
-    <row r="273" spans="1:10">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="273" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A273" s="4">
         <v>271</v>
       </c>
@@ -13874,10 +13874,10 @@
         <v>574</v>
       </c>
       <c r="J273" s="3" t="s">
-        <v>1316</v>
-      </c>
-    </row>
-    <row r="274" spans="1:10">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="274" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A274" s="4">
         <v>272</v>
       </c>
@@ -13909,7 +13909,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="275" spans="1:10">
+    <row r="275" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A275" s="4">
         <v>273</v>
       </c>
@@ -13926,7 +13926,7 @@
         <v>68</v>
       </c>
       <c r="F275" s="4" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="G275" s="4" t="s">
         <v>14</v>
@@ -13941,7 +13941,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="276" spans="1:10">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A276" s="4">
         <v>274</v>
       </c>
@@ -13973,7 +13973,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="277" spans="1:10">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A277" s="4">
         <v>275</v>
       </c>
@@ -14005,7 +14005,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="278" spans="1:10">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A278" s="4">
         <v>276</v>
       </c>
@@ -14037,7 +14037,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="279" spans="1:10">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A279" s="4">
         <v>277</v>
       </c>
@@ -14069,7 +14069,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="280" spans="1:10">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A280" s="4">
         <v>278</v>
       </c>
@@ -14086,7 +14086,7 @@
         <v>350</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="G280" s="1" t="s">
         <v>14</v>
@@ -14098,10 +14098,10 @@
         <v>574</v>
       </c>
       <c r="J280" s="3" t="s">
-        <v>1064</v>
-      </c>
-    </row>
-    <row r="281" spans="1:10">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="281" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A281" s="4">
         <v>279</v>
       </c>
@@ -14118,7 +14118,7 @@
         <v>68</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="G281" s="1" t="s">
         <v>14</v>
@@ -14133,7 +14133,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="282" spans="1:10">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A282" s="4">
         <v>280</v>
       </c>
@@ -14150,7 +14150,7 @@
         <v>68</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="G282" s="1" t="s">
         <v>14</v>
@@ -14165,7 +14165,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="283" spans="1:10">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A283" s="4">
         <v>281</v>
       </c>
@@ -14182,7 +14182,7 @@
         <v>68</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="G283" s="1" t="s">
         <v>14</v>
@@ -14197,7 +14197,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="284" spans="1:10">
+    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A284" s="4">
         <v>282</v>
       </c>
@@ -14214,7 +14214,7 @@
         <v>68</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="G284" s="1" t="s">
         <v>14</v>
@@ -14229,7 +14229,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="285" spans="1:10">
+    <row r="285" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A285" s="4">
         <v>283</v>
       </c>
@@ -14246,7 +14246,7 @@
         <v>68</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="G285" s="1" t="s">
         <v>14</v>
@@ -14261,7 +14261,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="286" spans="1:10">
+    <row r="286" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A286" s="4">
         <v>284</v>
       </c>
@@ -14278,7 +14278,7 @@
         <v>68</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="G286" s="1" t="s">
         <v>14</v>
@@ -14293,7 +14293,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="287" spans="1:10">
+    <row r="287" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A287" s="4">
         <v>285</v>
       </c>
@@ -14310,7 +14310,7 @@
         <v>68</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="G287" s="1" t="s">
         <v>14</v>
@@ -14325,7 +14325,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="288" spans="1:10">
+    <row r="288" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A288" s="4">
         <v>286</v>
       </c>
@@ -14342,7 +14342,7 @@
         <v>68</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="G288" s="1" t="s">
         <v>14</v>
@@ -14357,7 +14357,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="289" spans="1:10">
+    <row r="289" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A289" s="4">
         <v>287</v>
       </c>
@@ -14374,7 +14374,7 @@
         <v>68</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="G289" s="1" t="s">
         <v>14</v>
@@ -14389,7 +14389,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="290" spans="1:10">
+    <row r="290" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A290" s="4">
         <v>288</v>
       </c>
@@ -14406,7 +14406,7 @@
         <v>68</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="G290" s="1" t="s">
         <v>14</v>
@@ -14421,7 +14421,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="291" spans="1:10">
+    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A291" s="4">
         <v>289</v>
       </c>
@@ -14438,7 +14438,7 @@
         <v>68</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="G291" s="1" t="s">
         <v>14</v>
@@ -14453,7 +14453,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="292" spans="1:10">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A292" s="4">
         <v>290</v>
       </c>
@@ -14470,7 +14470,7 @@
         <v>68</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="G292" s="1" t="s">
         <v>14</v>
@@ -14485,7 +14485,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="293" spans="1:10">
+    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A293" s="4">
         <v>291</v>
       </c>
@@ -14502,7 +14502,7 @@
         <v>68</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="G293" s="1" t="s">
         <v>14</v>
@@ -14517,7 +14517,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="294" spans="1:10">
+    <row r="294" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A294" s="4">
         <v>292</v>
       </c>
@@ -14534,7 +14534,7 @@
         <v>76</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="G294" s="1" t="s">
         <v>14</v>
@@ -14546,10 +14546,10 @@
         <v>646</v>
       </c>
       <c r="J294" s="3" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="295" spans="1:10">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="295" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A295" s="4">
         <v>293</v>
       </c>
@@ -14566,7 +14566,7 @@
         <v>68</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="G295" s="1" t="s">
         <v>14</v>
@@ -14581,7 +14581,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="296" spans="1:10">
+    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A296" s="4">
         <v>294</v>
       </c>
@@ -14598,7 +14598,7 @@
         <v>68</v>
       </c>
       <c r="F296" s="4" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="G296" s="1" t="s">
         <v>14</v>
@@ -14613,7 +14613,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="297" spans="1:10">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A297" s="4">
         <v>295</v>
       </c>
@@ -14630,7 +14630,7 @@
         <v>68</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="G297" s="1" t="s">
         <v>14</v>
@@ -14645,7 +14645,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="298" spans="1:10">
+    <row r="298" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A298" s="4">
         <v>296</v>
       </c>
@@ -14662,7 +14662,7 @@
         <v>68</v>
       </c>
       <c r="F298" s="4" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="G298" s="1" t="s">
         <v>14</v>
@@ -14677,7 +14677,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="299" spans="1:10">
+    <row r="299" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A299" s="4">
         <v>297</v>
       </c>
@@ -14709,7 +14709,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="300" spans="1:10">
+    <row r="300" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A300" s="4">
         <v>298</v>
       </c>
@@ -14741,7 +14741,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="301" spans="1:10">
+    <row r="301" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A301" s="4">
         <v>299</v>
       </c>
@@ -14773,7 +14773,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="302" spans="1:10">
+    <row r="302" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A302" s="4">
         <v>300</v>
       </c>
@@ -14805,7 +14805,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="303" spans="1:10">
+    <row r="303" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A303" s="4">
         <v>301</v>
       </c>
@@ -14837,7 +14837,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="304" spans="1:10">
+    <row r="304" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A304" s="4">
         <v>302</v>
       </c>
@@ -14869,7 +14869,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="305" spans="1:10">
+    <row r="305" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A305" s="4">
         <v>303</v>
       </c>
@@ -14901,7 +14901,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="306" spans="1:10">
+    <row r="306" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A306" s="4">
         <v>304</v>
       </c>
@@ -14933,7 +14933,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="307" spans="1:10">
+    <row r="307" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A307" s="4">
         <v>305</v>
       </c>
@@ -14965,7 +14965,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="308" spans="1:10">
+    <row r="308" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A308" s="4">
         <v>306</v>
       </c>
@@ -14997,7 +14997,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="309" spans="1:10">
+    <row r="309" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A309" s="4">
         <v>307</v>
       </c>
@@ -15029,7 +15029,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="310" spans="1:10">
+    <row r="310" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A310" s="4">
         <v>308</v>
       </c>
@@ -15061,7 +15061,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="311" spans="1:10">
+    <row r="311" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A311" s="4">
         <v>309</v>
       </c>
@@ -15093,7 +15093,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="312" spans="1:10">
+    <row r="312" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A312" s="4">
         <v>310</v>
       </c>
@@ -15125,7 +15125,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="313" spans="1:10">
+    <row r="313" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A313" s="4">
         <v>311</v>
       </c>
@@ -15154,10 +15154,10 @@
         <v>574</v>
       </c>
       <c r="J313" s="3" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="314" spans="1:10">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="314" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A314" s="4">
         <v>312</v>
       </c>
@@ -15189,7 +15189,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="315" spans="1:10">
+    <row r="315" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A315" s="4">
         <v>313</v>
       </c>
@@ -15206,7 +15206,7 @@
         <v>68</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="G315" s="1" t="s">
         <v>14</v>
@@ -15221,7 +15221,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="316" spans="1:10">
+    <row r="316" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A316" s="4">
         <v>314</v>
       </c>
@@ -15250,10 +15250,10 @@
         <v>574</v>
       </c>
       <c r="J316" s="3" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="317" spans="1:10">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="317" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A317" s="4">
         <v>315</v>
       </c>
@@ -15285,7 +15285,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="318" spans="1:10">
+    <row r="318" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A318" s="4">
         <v>316</v>
       </c>
@@ -15317,7 +15317,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="319" spans="1:10">
+    <row r="319" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A319" s="4">
         <v>317</v>
       </c>
@@ -15349,7 +15349,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="320" spans="1:10">
+    <row r="320" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A320" s="4">
         <v>318</v>
       </c>
@@ -15381,7 +15381,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="321" spans="1:10">
+    <row r="321" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A321" s="4">
         <v>319</v>
       </c>
@@ -15413,7 +15413,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="322" spans="1:10">
+    <row r="322" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A322" s="4">
         <v>320</v>
       </c>
@@ -15430,7 +15430,7 @@
         <v>68</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="G322" s="1" t="s">
         <v>14</v>
@@ -15445,7 +15445,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="323" spans="1:10">
+    <row r="323" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A323" s="4">
         <v>321</v>
       </c>
@@ -15477,7 +15477,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="324" spans="1:10">
+    <row r="324" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A324" s="4">
         <v>322</v>
       </c>
@@ -15509,7 +15509,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="325" spans="1:10">
+    <row r="325" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A325" s="4">
         <v>323</v>
       </c>
@@ -15541,7 +15541,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="326" spans="1:10">
+    <row r="326" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A326" s="4">
         <v>324</v>
       </c>
@@ -15558,7 +15558,7 @@
         <v>68</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="G326" s="1" t="s">
         <v>14</v>
@@ -15573,7 +15573,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="327" spans="1:10">
+    <row r="327" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A327" s="4">
         <v>325</v>
       </c>
@@ -15590,7 +15590,7 @@
         <v>68</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="G327" s="1" t="s">
         <v>14</v>
@@ -15605,7 +15605,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="328" spans="1:10">
+    <row r="328" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A328" s="4">
         <v>326</v>
       </c>
@@ -15622,7 +15622,7 @@
         <v>68</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="G328" s="1" t="s">
         <v>14</v>
@@ -15637,7 +15637,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="329" spans="1:10">
+    <row r="329" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A329" s="4">
         <v>327</v>
       </c>
@@ -15654,7 +15654,7 @@
         <v>68</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="G329" s="1" t="s">
         <v>14</v>
@@ -15669,7 +15669,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="330" spans="1:10">
+    <row r="330" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A330" s="4">
         <v>328</v>
       </c>
@@ -15686,7 +15686,7 @@
         <v>68</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="G330" s="1" t="s">
         <v>14</v>
@@ -15701,7 +15701,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="331" spans="1:10">
+    <row r="331" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A331" s="4">
         <v>329</v>
       </c>
@@ -15718,7 +15718,7 @@
         <v>68</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="G331" s="1" t="s">
         <v>14</v>
@@ -15733,7 +15733,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="332" spans="1:10">
+    <row r="332" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A332" s="4">
         <v>330</v>
       </c>
@@ -15750,7 +15750,7 @@
         <v>68</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="G332" s="1" t="s">
         <v>14</v>
@@ -15765,7 +15765,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="333" spans="1:10">
+    <row r="333" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A333" s="4">
         <v>331</v>
       </c>
@@ -15782,7 +15782,7 @@
         <v>68</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="G333" s="1" t="s">
         <v>14</v>
@@ -15797,7 +15797,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="334" spans="1:10">
+    <row r="334" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A334" s="4">
         <v>332</v>
       </c>
@@ -15814,7 +15814,7 @@
         <v>68</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="G334" s="1" t="s">
         <v>14</v>
@@ -15829,7 +15829,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="335" spans="1:10">
+    <row r="335" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A335" s="4">
         <v>333</v>
       </c>
@@ -15846,7 +15846,7 @@
         <v>68</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="G335" s="1" t="s">
         <v>14</v>
@@ -15861,7 +15861,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="336" spans="1:10">
+    <row r="336" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A336" s="4">
         <v>334</v>
       </c>
@@ -15878,7 +15878,7 @@
         <v>68</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="G336" s="1" t="s">
         <v>14</v>
@@ -15893,7 +15893,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="337" spans="1:10">
+    <row r="337" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A337" s="4">
         <v>335</v>
       </c>
@@ -15910,7 +15910,7 @@
         <v>68</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="G337" s="1" t="s">
         <v>14</v>
@@ -15925,7 +15925,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="338" spans="1:10">
+    <row r="338" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A338" s="4">
         <v>336</v>
       </c>
@@ -15942,7 +15942,7 @@
         <v>68</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="G338" s="1" t="s">
         <v>14</v>
@@ -15954,10 +15954,10 @@
         <v>574</v>
       </c>
       <c r="J338" s="3" t="s">
-        <v>1311</v>
-      </c>
-    </row>
-    <row r="339" spans="1:10">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="339" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A339" s="4">
         <v>337</v>
       </c>
@@ -15974,7 +15974,7 @@
         <v>68</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="G339" s="1" t="s">
         <v>14</v>
@@ -15989,7 +15989,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="340" spans="1:10">
+    <row r="340" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A340" s="4">
         <v>338</v>
       </c>
@@ -16006,7 +16006,7 @@
         <v>68</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="G340" s="1" t="s">
         <v>14</v>
@@ -16021,7 +16021,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="341" spans="1:10">
+    <row r="341" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A341" s="4">
         <v>339</v>
       </c>
@@ -16038,7 +16038,7 @@
         <v>68</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="G341" s="1" t="s">
         <v>14</v>
@@ -16053,7 +16053,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="342" spans="1:10">
+    <row r="342" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A342" s="4">
         <v>340</v>
       </c>
@@ -16085,7 +16085,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="343" spans="1:10">
+    <row r="343" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A343" s="4">
         <v>341</v>
       </c>
@@ -16102,7 +16102,7 @@
         <v>68</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="G343" s="1" t="s">
         <v>14</v>
@@ -16117,7 +16117,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="344" spans="1:10">
+    <row r="344" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A344" s="4">
         <v>342</v>
       </c>
@@ -16134,7 +16134,7 @@
         <v>68</v>
       </c>
       <c r="F344" s="4" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="G344" s="1" t="s">
         <v>14</v>
@@ -16149,7 +16149,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="345" spans="1:10">
+    <row r="345" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A345" s="4">
         <v>343</v>
       </c>
@@ -16166,7 +16166,7 @@
         <v>68</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="G345" s="1" t="s">
         <v>14</v>
@@ -16181,7 +16181,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="346" spans="1:10">
+    <row r="346" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A346" s="4">
         <v>344</v>
       </c>
@@ -16198,7 +16198,7 @@
         <v>68</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="G346" s="1" t="s">
         <v>14</v>
@@ -16213,7 +16213,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="347" spans="1:10">
+    <row r="347" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A347" s="4">
         <v>345</v>
       </c>
@@ -16230,7 +16230,7 @@
         <v>68</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="G347" s="1" t="s">
         <v>14</v>
@@ -16245,7 +16245,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="348" spans="1:10">
+    <row r="348" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A348" s="4">
         <v>346</v>
       </c>
@@ -16262,7 +16262,7 @@
         <v>68</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="G348" s="1" t="s">
         <v>14</v>
@@ -16277,7 +16277,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="349" spans="1:10">
+    <row r="349" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A349" s="4">
         <v>347</v>
       </c>
@@ -16309,7 +16309,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="350" spans="1:10">
+    <row r="350" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A350" s="4">
         <v>348</v>
       </c>
@@ -16341,7 +16341,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="351" spans="1:10">
+    <row r="351" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A351" s="4">
         <v>349</v>
       </c>
@@ -16373,7 +16373,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="352" spans="1:10">
+    <row r="352" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A352" s="4">
         <v>350</v>
       </c>
@@ -16405,7 +16405,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="353" spans="1:10">
+    <row r="353" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A353" s="4">
         <v>351</v>
       </c>
@@ -16437,7 +16437,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="354" spans="1:10">
+    <row r="354" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A354" s="4">
         <v>352</v>
       </c>
@@ -16469,7 +16469,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="355" spans="1:10">
+    <row r="355" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A355" s="4">
         <v>353</v>
       </c>
@@ -16501,7 +16501,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="356" spans="1:10">
+    <row r="356" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A356" s="4">
         <v>354</v>
       </c>
@@ -16518,7 +16518,7 @@
         <v>76</v>
       </c>
       <c r="F356" s="1" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="G356" s="13" t="s">
         <v>14</v>
@@ -16530,10 +16530,10 @@
         <v>574</v>
       </c>
       <c r="J356" s="3" t="s">
-        <v>1004</v>
-      </c>
-    </row>
-    <row r="357" spans="1:10">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="357" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A357" s="4">
         <v>355</v>
       </c>
@@ -16565,7 +16565,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="358" spans="1:10">
+    <row r="358" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A358" s="4">
         <v>356</v>
       </c>
@@ -16597,7 +16597,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="359" spans="1:10">
+    <row r="359" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A359" s="4">
         <v>357</v>
       </c>
@@ -16629,7 +16629,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="360" spans="1:10">
+    <row r="360" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A360" s="4">
         <v>358</v>
       </c>
@@ -16661,7 +16661,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="361" spans="1:10">
+    <row r="361" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A361" s="4">
         <v>359</v>
       </c>
@@ -16693,7 +16693,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="362" spans="1:10">
+    <row r="362" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A362" s="4">
         <v>360</v>
       </c>
@@ -16725,7 +16725,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="363" spans="1:10">
+    <row r="363" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A363" s="4">
         <v>361</v>
       </c>
@@ -16754,10 +16754,10 @@
         <v>574</v>
       </c>
       <c r="J363" s="3" t="s">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="364" spans="1:10">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="364" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A364" s="4">
         <v>362</v>
       </c>
@@ -16789,7 +16789,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="365" spans="1:10">
+    <row r="365" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A365" s="4">
         <v>363</v>
       </c>
@@ -16821,7 +16821,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="366" spans="1:10">
+    <row r="366" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A366" s="4">
         <v>364</v>
       </c>
@@ -16835,10 +16835,10 @@
         <v>707</v>
       </c>
       <c r="E366" s="1" t="s">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="F366" s="1" t="s">
-        <v>23</v>
+        <v>1071</v>
       </c>
       <c r="G366" s="1" t="s">
         <v>14</v>
@@ -16850,10 +16850,10 @@
         <v>574</v>
       </c>
       <c r="J366" s="3" t="s">
-        <v>1301</v>
-      </c>
-    </row>
-    <row r="367" spans="1:10">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="367" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A367" s="4">
         <v>365</v>
       </c>
@@ -16885,7 +16885,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="368" spans="1:10">
+    <row r="368" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A368" s="4">
         <v>366</v>
       </c>
@@ -16917,7 +16917,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="369" spans="1:10">
+    <row r="369" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A369" s="4">
         <v>367</v>
       </c>
@@ -16949,7 +16949,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="370" spans="1:10">
+    <row r="370" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A370" s="4">
         <v>368</v>
       </c>
@@ -16966,7 +16966,7 @@
         <v>76</v>
       </c>
       <c r="F370" s="1" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="G370" s="1" t="s">
         <v>14</v>
@@ -16978,10 +16978,10 @@
         <v>574</v>
       </c>
       <c r="J370" s="3" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="371" spans="1:10">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="371" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A371" s="4">
         <v>369</v>
       </c>
@@ -16992,7 +16992,7 @@
         <v>11</v>
       </c>
       <c r="D371" s="38" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="E371" s="1" t="s">
         <v>76</v>
@@ -17010,10 +17010,10 @@
         <v>574</v>
       </c>
       <c r="J371" s="3" t="s">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="372" spans="1:10">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="372" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A372" s="4">
         <v>370</v>
       </c>
@@ -17024,13 +17024,13 @@
         <v>11</v>
       </c>
       <c r="D372" s="38" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E372" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F372" s="1" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="G372" s="1" t="s">
         <v>14</v>
@@ -17042,10 +17042,10 @@
         <v>574</v>
       </c>
       <c r="J372" s="3" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="373" spans="1:10">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="373" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A373" s="4">
         <v>371</v>
       </c>
@@ -17056,13 +17056,13 @@
         <v>11</v>
       </c>
       <c r="D373" s="38" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="E373" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F373" s="1" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="G373" s="1" t="s">
         <v>14</v>
@@ -17074,10 +17074,10 @@
         <v>574</v>
       </c>
       <c r="J373" s="3" t="s">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="374" spans="1:10">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="374" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A374" s="4">
         <v>372</v>
       </c>
@@ -17088,13 +17088,13 @@
         <v>11</v>
       </c>
       <c r="D374" s="38" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="E374" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F374" s="1" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="G374" s="1" t="s">
         <v>14</v>
@@ -17106,10 +17106,10 @@
         <v>574</v>
       </c>
       <c r="J374" s="3" t="s">
-        <v>936</v>
-      </c>
-    </row>
-    <row r="375" spans="1:10">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="375" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A375" s="4">
         <v>373</v>
       </c>
@@ -17120,13 +17120,13 @@
         <v>11</v>
       </c>
       <c r="D375" s="38" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="E375" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F375" s="1" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="G375" s="1" t="s">
         <v>14</v>
@@ -17138,10 +17138,10 @@
         <v>646</v>
       </c>
       <c r="J375" s="3" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="376" spans="1:10">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="376" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A376" s="4">
         <v>374</v>
       </c>
@@ -17152,13 +17152,13 @@
         <v>11</v>
       </c>
       <c r="D376" s="38" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="E376" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F376" s="1" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="G376" s="1" t="s">
         <v>14</v>
@@ -17170,10 +17170,10 @@
         <v>646</v>
       </c>
       <c r="J376" s="3" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="377" spans="1:10">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="377" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A377" s="4">
         <v>375</v>
       </c>
@@ -17184,13 +17184,13 @@
         <v>11</v>
       </c>
       <c r="D377" s="38" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="E377" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F377" s="1" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="G377" s="1" t="s">
         <v>14</v>
@@ -17202,10 +17202,10 @@
         <v>574</v>
       </c>
       <c r="J377" s="3" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="378" spans="1:10">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="378" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A378" s="4">
         <v>376</v>
       </c>
@@ -17216,7 +17216,7 @@
         <v>11</v>
       </c>
       <c r="D378" s="38" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="E378" s="1" t="s">
         <v>76</v>
@@ -17234,10 +17234,10 @@
         <v>646</v>
       </c>
       <c r="J378" s="3" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="379" spans="1:10">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="379" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A379" s="4">
         <v>377</v>
       </c>
@@ -17248,13 +17248,13 @@
         <v>11</v>
       </c>
       <c r="D379" s="38" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E379" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F379" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="G379" s="1" t="s">
         <v>14</v>
@@ -17266,10 +17266,10 @@
         <v>646</v>
       </c>
       <c r="J379" s="3" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="380" spans="1:10">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="380" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A380" s="4">
         <v>378</v>
       </c>
@@ -17280,7 +17280,7 @@
         <v>11</v>
       </c>
       <c r="D380" s="38" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="E380" s="1" t="s">
         <v>76</v>
@@ -17298,10 +17298,10 @@
         <v>646</v>
       </c>
       <c r="J380" s="3" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="381" spans="1:10">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="381" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A381" s="4">
         <v>379</v>
       </c>
@@ -17318,7 +17318,7 @@
         <v>68</v>
       </c>
       <c r="F381" s="1" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="G381" s="1" t="s">
         <v>14</v>
@@ -17330,10 +17330,10 @@
         <v>574</v>
       </c>
       <c r="J381" s="3" t="s">
-        <v>995</v>
-      </c>
-    </row>
-    <row r="382" spans="1:10">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="382" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A382" s="4">
         <v>380</v>
       </c>
@@ -17362,10 +17362,10 @@
         <v>574</v>
       </c>
       <c r="J382" s="3" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="383" spans="1:10">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="383" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A383" s="4">
         <v>381</v>
       </c>
@@ -17382,7 +17382,7 @@
         <v>76</v>
       </c>
       <c r="F383" s="1" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="G383" s="1" t="s">
         <v>14</v>
@@ -17394,10 +17394,10 @@
         <v>574</v>
       </c>
       <c r="J383" s="3" t="s">
-        <v>1172</v>
-      </c>
-    </row>
-    <row r="384" spans="1:10">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="384" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A384" s="4">
         <v>382</v>
       </c>
@@ -17426,10 +17426,10 @@
         <v>574</v>
       </c>
       <c r="J384" s="3" t="s">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="385" spans="1:10">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="385" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A385" s="4">
         <v>383</v>
       </c>
@@ -17458,10 +17458,10 @@
         <v>646</v>
       </c>
       <c r="J385" s="3" t="s">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="386" spans="1:10">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="386" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A386" s="4">
         <v>384</v>
       </c>
@@ -17493,7 +17493,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="387" spans="1:10">
+    <row r="387" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A387" s="4">
         <v>385</v>
       </c>
@@ -17510,7 +17510,7 @@
         <v>76</v>
       </c>
       <c r="F387" s="1" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="G387" s="1" t="s">
         <v>14</v>
@@ -17522,10 +17522,10 @@
         <v>574</v>
       </c>
       <c r="J387" s="3" t="s">
-        <v>1174</v>
-      </c>
-    </row>
-    <row r="388" spans="1:10">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="388" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A388" s="4">
         <v>386</v>
       </c>
@@ -17542,7 +17542,7 @@
         <v>76</v>
       </c>
       <c r="F388" s="1" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="G388" s="1" t="s">
         <v>14</v>
@@ -17554,10 +17554,10 @@
         <v>574</v>
       </c>
       <c r="J388" s="3" t="s">
-        <v>1176</v>
-      </c>
-    </row>
-    <row r="389" spans="1:10">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="389" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A389" s="4">
         <v>387</v>
       </c>
@@ -17589,7 +17589,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="390" spans="1:10">
+    <row r="390" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A390" s="4">
         <v>388</v>
       </c>
@@ -17621,7 +17621,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="391" spans="1:10">
+    <row r="391" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A391" s="4">
         <v>389</v>
       </c>
@@ -17638,7 +17638,7 @@
         <v>76</v>
       </c>
       <c r="F391" s="1" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G391" s="1" t="s">
         <v>14</v>
@@ -17650,10 +17650,10 @@
         <v>574</v>
       </c>
       <c r="J391" s="3" t="s">
-        <v>1178</v>
-      </c>
-    </row>
-    <row r="392" spans="1:10">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="392" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A392" s="4">
         <v>390</v>
       </c>
@@ -17670,7 +17670,7 @@
         <v>76</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="G392" s="1" t="s">
         <v>14</v>
@@ -17682,10 +17682,10 @@
         <v>574</v>
       </c>
       <c r="J392" s="3" t="s">
-        <v>1180</v>
-      </c>
-    </row>
-    <row r="393" spans="1:10">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="393" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A393" s="4">
         <v>391</v>
       </c>
@@ -17702,7 +17702,7 @@
         <v>68</v>
       </c>
       <c r="F393" s="1" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="G393" s="1" t="s">
         <v>14</v>
@@ -17714,10 +17714,10 @@
         <v>574</v>
       </c>
       <c r="J393" s="3" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="394" spans="1:10">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="394" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A394" s="4">
         <v>392</v>
       </c>
@@ -17749,7 +17749,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="395" spans="1:10">
+    <row r="395" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A395" s="4">
         <v>393</v>
       </c>
@@ -17781,7 +17781,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="396" spans="1:10">
+    <row r="396" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A396" s="4">
         <v>394</v>
       </c>
@@ -17798,7 +17798,7 @@
         <v>76</v>
       </c>
       <c r="F396" s="1" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="G396" s="1" t="s">
         <v>14</v>
@@ -17810,10 +17810,10 @@
         <v>574</v>
       </c>
       <c r="J396" s="3" t="s">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="397" spans="1:10">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="397" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A397" s="4">
         <v>395</v>
       </c>
@@ -17824,13 +17824,13 @@
         <v>11</v>
       </c>
       <c r="D397" s="2" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="E397" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F397" s="1" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="G397" s="1" t="s">
         <v>14</v>
@@ -17842,10 +17842,10 @@
         <v>574</v>
       </c>
       <c r="J397" s="3" t="s">
-        <v>913</v>
-      </c>
-    </row>
-    <row r="398" spans="1:10">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="398" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A398" s="4">
         <v>396</v>
       </c>
@@ -17856,13 +17856,13 @@
         <v>11</v>
       </c>
       <c r="D398" s="2" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="E398" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F398" s="1" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="G398" s="1" t="s">
         <v>14</v>
@@ -17874,10 +17874,10 @@
         <v>646</v>
       </c>
       <c r="J398" s="3" t="s">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="399" spans="1:10">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="399" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A399" s="4">
         <v>397</v>
       </c>
@@ -17888,13 +17888,13 @@
         <v>11</v>
       </c>
       <c r="D399" s="2" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="E399" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F399" s="1" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="G399" s="1" t="s">
         <v>14</v>
@@ -17906,10 +17906,10 @@
         <v>574</v>
       </c>
       <c r="J399" s="3" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="400" spans="1:10">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="400" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A400" s="4">
         <v>398</v>
       </c>
@@ -17920,13 +17920,13 @@
         <v>11</v>
       </c>
       <c r="D400" s="2" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="E400" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F400" s="1" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="G400" s="1" t="s">
         <v>14</v>
@@ -17938,10 +17938,10 @@
         <v>574</v>
       </c>
       <c r="J400" s="3" t="s">
-        <v>1240</v>
-      </c>
-    </row>
-    <row r="401" spans="1:10">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="401" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A401" s="4">
         <v>399</v>
       </c>
@@ -17952,13 +17952,13 @@
         <v>11</v>
       </c>
       <c r="D401" s="2" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="E401" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F401" s="1" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="G401" s="1" t="s">
         <v>14</v>
@@ -17970,10 +17970,10 @@
         <v>574</v>
       </c>
       <c r="J401" s="3" t="s">
-        <v>1014</v>
-      </c>
-    </row>
-    <row r="402" spans="1:10">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="402" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A402" s="4">
         <v>400</v>
       </c>
@@ -17984,13 +17984,13 @@
         <v>11</v>
       </c>
       <c r="D402" s="2" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="E402" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F402" s="1" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="G402" s="1" t="s">
         <v>14</v>
@@ -18002,10 +18002,10 @@
         <v>574</v>
       </c>
       <c r="J402" s="3" t="s">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="403" spans="1:10">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="403" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A403" s="4">
         <v>401</v>
       </c>
@@ -18016,13 +18016,13 @@
         <v>11</v>
       </c>
       <c r="D403" s="2" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="E403" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F403" s="1" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="G403" s="1" t="s">
         <v>14</v>
@@ -18034,10 +18034,10 @@
         <v>574</v>
       </c>
       <c r="J403" s="3" t="s">
-        <v>1021</v>
-      </c>
-    </row>
-    <row r="404" spans="1:10">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="404" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A404" s="4">
         <v>402</v>
       </c>
@@ -18069,7 +18069,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="405" spans="1:10">
+    <row r="405" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A405" s="4">
         <v>403</v>
       </c>
@@ -18101,7 +18101,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="406" spans="1:10">
+    <row r="406" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A406" s="4">
         <v>404</v>
       </c>
@@ -18133,7 +18133,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="407" spans="1:10">
+    <row r="407" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A407" s="4">
         <v>405</v>
       </c>
@@ -18165,7 +18165,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="408" spans="1:10">
+    <row r="408" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A408" s="4">
         <v>406</v>
       </c>
@@ -18197,7 +18197,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="409" spans="1:10">
+    <row r="409" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A409" s="4">
         <v>407</v>
       </c>
@@ -18229,7 +18229,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="410" spans="1:10">
+    <row r="410" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A410" s="4">
         <v>408</v>
       </c>
@@ -18261,7 +18261,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="411" spans="1:10">
+    <row r="411" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A411" s="4">
         <v>409</v>
       </c>
@@ -18293,7 +18293,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="412" spans="1:10">
+    <row r="412" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A412" s="4">
         <v>410</v>
       </c>
@@ -18325,7 +18325,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="413" spans="1:10">
+    <row r="413" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A413" s="4">
         <v>411</v>
       </c>
@@ -18336,13 +18336,13 @@
         <v>11</v>
       </c>
       <c r="D413" s="5" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="E413" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F413" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="G413" s="1" t="s">
         <v>14</v>
@@ -18354,10 +18354,10 @@
         <v>574</v>
       </c>
       <c r="J413" s="3" t="s">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="414" spans="1:10">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="414" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A414" s="4">
         <v>412</v>
       </c>
@@ -18368,13 +18368,13 @@
         <v>11</v>
       </c>
       <c r="D414" s="5" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="E414" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F414" s="1" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="G414" s="1" t="s">
         <v>14</v>
@@ -18386,10 +18386,10 @@
         <v>574</v>
       </c>
       <c r="J414" s="3" t="s">
-        <v>932</v>
-      </c>
-    </row>
-    <row r="415" spans="1:10">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="415" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A415" s="4">
         <v>413</v>
       </c>
@@ -18400,13 +18400,13 @@
         <v>11</v>
       </c>
       <c r="D415" s="5" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="E415" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F415" s="1" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="G415" s="1" t="s">
         <v>14</v>
@@ -18418,10 +18418,10 @@
         <v>574</v>
       </c>
       <c r="J415" s="3" t="s">
-        <v>944</v>
-      </c>
-    </row>
-    <row r="416" spans="1:10">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="416" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A416" s="4">
         <v>414</v>
       </c>
@@ -18432,13 +18432,13 @@
         <v>11</v>
       </c>
       <c r="D416" s="5" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="E416" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F416" s="1" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="G416" s="1" t="s">
         <v>14</v>
@@ -18450,10 +18450,10 @@
         <v>574</v>
       </c>
       <c r="J416" s="3" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="417" spans="1:10">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="417" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A417" s="4">
         <v>415</v>
       </c>
@@ -18464,13 +18464,13 @@
         <v>11</v>
       </c>
       <c r="D417" s="5" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E417" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F417" s="1" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="G417" s="1" t="s">
         <v>14</v>
@@ -18482,10 +18482,10 @@
         <v>574</v>
       </c>
       <c r="J417" s="3" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="418" spans="1:10">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="418" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A418" s="4">
         <v>416</v>
       </c>
@@ -18517,7 +18517,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="419" spans="1:10">
+    <row r="419" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A419" s="4">
         <v>417</v>
       </c>
@@ -18549,7 +18549,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="420" spans="1:10">
+    <row r="420" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A420" s="4">
         <v>418</v>
       </c>
@@ -18581,7 +18581,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="421" spans="1:10">
+    <row r="421" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A421" s="4">
         <v>419</v>
       </c>
@@ -18613,7 +18613,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="422" spans="1:10">
+    <row r="422" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A422" s="4">
         <v>420</v>
       </c>
@@ -18645,7 +18645,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="423" spans="1:10">
+    <row r="423" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A423" s="4">
         <v>421</v>
       </c>
@@ -18677,7 +18677,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="424" spans="1:10">
+    <row r="424" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A424" s="4">
         <v>422</v>
       </c>
@@ -18709,7 +18709,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="425" spans="1:10">
+    <row r="425" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A425" s="4">
         <v>423</v>
       </c>
@@ -18741,7 +18741,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="426" spans="1:10">
+    <row r="426" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A426" s="4">
         <v>424</v>
       </c>
@@ -18758,7 +18758,7 @@
         <v>76</v>
       </c>
       <c r="F426" s="1" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="G426" s="1" t="s">
         <v>14</v>
@@ -18770,10 +18770,10 @@
         <v>646</v>
       </c>
       <c r="J426" s="3" t="s">
-        <v>1186</v>
-      </c>
-    </row>
-    <row r="427" spans="1:10">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="427" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A427" s="4">
         <v>425</v>
       </c>
@@ -18784,13 +18784,13 @@
         <v>11</v>
       </c>
       <c r="D427" s="5" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="E427" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F427" s="1" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="G427" s="1" t="s">
         <v>14</v>
@@ -18802,10 +18802,10 @@
         <v>574</v>
       </c>
       <c r="J427" s="3" t="s">
-        <v>934</v>
-      </c>
-    </row>
-    <row r="428" spans="1:10">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="428" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A428" s="4">
         <v>426</v>
       </c>
@@ -18816,13 +18816,13 @@
         <v>11</v>
       </c>
       <c r="D428" s="5" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="E428" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F428" s="1" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="G428" s="1" t="s">
         <v>14</v>
@@ -18834,10 +18834,10 @@
         <v>574</v>
       </c>
       <c r="J428" s="3" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="429" spans="1:10">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="429" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A429" s="4">
         <v>427</v>
       </c>
@@ -18848,13 +18848,13 @@
         <v>11</v>
       </c>
       <c r="D429" s="5" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="E429" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F429" s="1" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="G429" s="1" t="s">
         <v>14</v>
@@ -18866,10 +18866,10 @@
         <v>574</v>
       </c>
       <c r="J429" s="3" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="430" spans="1:10">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="430" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A430" s="4">
         <v>428</v>
       </c>
@@ -18880,13 +18880,13 @@
         <v>11</v>
       </c>
       <c r="D430" s="5" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="E430" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F430" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="G430" s="1" t="s">
         <v>14</v>
@@ -18898,10 +18898,10 @@
         <v>574</v>
       </c>
       <c r="J430" s="3" t="s">
-        <v>953</v>
-      </c>
-    </row>
-    <row r="431" spans="1:10">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="431" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A431" s="4">
         <v>429</v>
       </c>
@@ -18912,13 +18912,13 @@
         <v>11</v>
       </c>
       <c r="D431" s="5" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="E431" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F431" s="1" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="G431" s="1" t="s">
         <v>14</v>
@@ -18930,10 +18930,10 @@
         <v>574</v>
       </c>
       <c r="J431" s="3" t="s">
-        <v>956</v>
-      </c>
-    </row>
-    <row r="432" spans="1:10">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="432" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A432" s="4">
         <v>430</v>
       </c>
@@ -18944,13 +18944,13 @@
         <v>11</v>
       </c>
       <c r="D432" s="5" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="E432" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F432" s="1" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="G432" s="1" t="s">
         <v>14</v>
@@ -18962,10 +18962,10 @@
         <v>574</v>
       </c>
       <c r="J432" s="3" t="s">
-        <v>1219</v>
-      </c>
-    </row>
-    <row r="433" spans="1:10">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="433" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A433" s="4">
         <v>431</v>
       </c>
@@ -18976,13 +18976,13 @@
         <v>11</v>
       </c>
       <c r="D433" s="5" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E433" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F433" s="1" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="G433" s="1" t="s">
         <v>14</v>
@@ -18994,10 +18994,10 @@
         <v>574</v>
       </c>
       <c r="J433" s="3" t="s">
-        <v>988</v>
-      </c>
-    </row>
-    <row r="434" spans="1:10">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="434" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A434" s="4">
         <v>432</v>
       </c>
@@ -19008,13 +19008,13 @@
         <v>11</v>
       </c>
       <c r="D434" s="5" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="E434" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F434" s="1" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="G434" s="1" t="s">
         <v>14</v>
@@ -19026,10 +19026,10 @@
         <v>646</v>
       </c>
       <c r="J434" s="3" t="s">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="435" spans="1:10">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="435" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A435" s="4">
         <v>433</v>
       </c>
@@ -19040,13 +19040,13 @@
         <v>11</v>
       </c>
       <c r="D435" s="5" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="E435" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F435" s="1" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="G435" s="1" t="s">
         <v>14</v>
@@ -19059,7 +19059,7 @@
       </c>
       <c r="J435" s="24"/>
     </row>
-    <row r="436" spans="1:10">
+    <row r="436" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A436" s="4">
         <v>434</v>
       </c>
@@ -19070,7 +19070,7 @@
         <v>11</v>
       </c>
       <c r="D436" s="5" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="E436" s="1" t="s">
         <v>76</v>
@@ -19088,10 +19088,10 @@
         <v>574</v>
       </c>
       <c r="J436" s="3" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="437" spans="1:10">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="437" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A437" s="4">
         <v>435</v>
       </c>
@@ -19120,10 +19120,10 @@
         <v>574</v>
       </c>
       <c r="J437" s="3" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="438" spans="1:10">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="438" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A438" s="4">
         <v>436</v>
       </c>
@@ -19140,7 +19140,7 @@
         <v>350</v>
       </c>
       <c r="F438" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G438" s="1" t="s">
         <v>14</v>
@@ -19152,10 +19152,10 @@
         <v>574</v>
       </c>
       <c r="J438" s="3" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="439" spans="1:10">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="439" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A439" s="4">
         <v>437</v>
       </c>
@@ -19172,7 +19172,7 @@
         <v>76</v>
       </c>
       <c r="F439" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="G439" s="1" t="s">
         <v>14</v>
@@ -19184,10 +19184,10 @@
         <v>574</v>
       </c>
       <c r="J439" s="3" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="440" spans="1:10">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="440" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A440" s="4">
         <v>438</v>
       </c>
@@ -19198,13 +19198,13 @@
         <v>11</v>
       </c>
       <c r="D440" s="5" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="E440" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F440" s="1" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="G440" s="1" t="s">
         <v>14</v>
@@ -19216,10 +19216,10 @@
         <v>574</v>
       </c>
       <c r="J440" s="3" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="441" spans="1:10">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="441" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A441" s="4">
         <v>439</v>
       </c>
@@ -19248,10 +19248,10 @@
         <v>574</v>
       </c>
       <c r="J441" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="442" spans="1:10">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="442" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A442" s="4">
         <v>440</v>
       </c>
@@ -19262,7 +19262,7 @@
         <v>11</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="E442" s="1" t="s">
         <v>350</v>
@@ -19280,10 +19280,10 @@
         <v>574</v>
       </c>
       <c r="J442" s="3" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="443" spans="1:10">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="443" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A443" s="4">
         <v>441</v>
       </c>
@@ -19294,7 +19294,7 @@
         <v>11</v>
       </c>
       <c r="D443" s="2" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E443" s="1" t="s">
         <v>350</v>
@@ -19312,10 +19312,10 @@
         <v>574</v>
       </c>
       <c r="J443" s="3" t="s">
-        <v>1006</v>
-      </c>
-    </row>
-    <row r="444" spans="1:10">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="444" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A444" s="4">
         <v>442</v>
       </c>
@@ -19326,13 +19326,13 @@
         <v>11</v>
       </c>
       <c r="D444" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="E444" s="1" t="s">
         <v>350</v>
       </c>
       <c r="F444" s="1" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="G444" s="1" t="s">
         <v>30</v>
@@ -19344,10 +19344,10 @@
         <v>574</v>
       </c>
       <c r="J444" s="3" t="s">
-        <v>1026</v>
-      </c>
-    </row>
-    <row r="445" spans="1:10">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="445" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A445" s="4">
         <v>443</v>
       </c>
@@ -19358,13 +19358,13 @@
         <v>11</v>
       </c>
       <c r="D445" s="2" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="E445" s="1" t="s">
         <v>350</v>
       </c>
       <c r="F445" s="1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="G445" s="1" t="s">
         <v>30</v>
@@ -19376,10 +19376,10 @@
         <v>574</v>
       </c>
       <c r="J445" s="3" t="s">
-        <v>1025</v>
-      </c>
-    </row>
-    <row r="446" spans="1:10">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="446" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A446" s="4">
         <v>444</v>
       </c>
@@ -19390,13 +19390,13 @@
         <v>11</v>
       </c>
       <c r="D446" s="2" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="E446" s="1" t="s">
         <v>350</v>
       </c>
       <c r="F446" s="1" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="G446" s="1" t="s">
         <v>30</v>
@@ -19408,10 +19408,10 @@
         <v>574</v>
       </c>
       <c r="J446" s="3" t="s">
-        <v>1033</v>
-      </c>
-    </row>
-    <row r="447" spans="1:10">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="447" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A447" s="4">
         <v>445</v>
       </c>
@@ -19443,18 +19443,18 @@
         <v>647</v>
       </c>
     </row>
-    <row r="448" spans="1:10">
+    <row r="448" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A448" s="4">
         <v>446</v>
       </c>
       <c r="B448" s="53" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="C448" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="E448" s="1" t="s">
         <v>19</v>
@@ -19472,27 +19472,27 @@
         <v>574</v>
       </c>
       <c r="J448" s="3" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="449" spans="1:10">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="449" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A449" s="4">
         <v>447</v>
       </c>
       <c r="B449" s="53" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="C449" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="E449" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F449" s="1" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="G449" s="1" t="s">
         <v>30</v>
@@ -19505,18 +19505,18 @@
       </c>
       <c r="J449" s="24"/>
     </row>
-    <row r="450" spans="1:10">
+    <row r="450" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A450" s="4">
         <v>448</v>
       </c>
       <c r="B450" s="53" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="C450" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="E450" s="1" t="s">
         <v>350</v>
@@ -19535,24 +19535,24 @@
       </c>
       <c r="J450" s="24"/>
     </row>
-    <row r="451" spans="1:10">
+    <row r="451" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A451" s="4">
         <v>449</v>
       </c>
       <c r="B451" s="53" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="C451" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D451" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="E451" s="1" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="F451" s="1" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="G451" s="1" t="s">
         <v>30</v>
@@ -19564,27 +19564,27 @@
         <v>574</v>
       </c>
       <c r="J451" s="3" t="s">
-        <v>1298</v>
-      </c>
-    </row>
-    <row r="452" spans="1:10">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="452" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A452" s="4">
         <v>450</v>
       </c>
       <c r="B452" s="53" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="C452" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="E452" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F452" s="1" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="G452" s="1" t="s">
         <v>30</v>
@@ -19597,24 +19597,24 @@
       </c>
       <c r="J452" s="24"/>
     </row>
-    <row r="453" spans="1:10">
+    <row r="453" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A453" s="4">
         <v>451</v>
       </c>
       <c r="B453" s="53" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="C453" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D453" s="2" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="E453" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F453" s="1" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="G453" s="1" t="s">
         <v>30</v>
@@ -19627,24 +19627,24 @@
       </c>
       <c r="J453" s="24"/>
     </row>
-    <row r="454" spans="1:10">
+    <row r="454" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A454" s="4">
         <v>452</v>
       </c>
       <c r="B454" s="53" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="C454" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D454" s="2" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="E454" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F454" s="1" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="G454" s="1" t="s">
         <v>30</v>
@@ -19657,24 +19657,24 @@
       </c>
       <c r="J454" s="24"/>
     </row>
-    <row r="455" spans="1:10">
+    <row r="455" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A455" s="4">
         <v>453</v>
       </c>
       <c r="B455" s="53" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="C455" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D455" s="2" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="E455" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F455" s="1" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="G455" s="1" t="s">
         <v>30</v>
@@ -19687,24 +19687,24 @@
       </c>
       <c r="J455" s="24"/>
     </row>
-    <row r="456" spans="1:10">
+    <row r="456" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A456" s="4">
         <v>454</v>
       </c>
       <c r="B456" s="53" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="C456" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D456" s="2" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="E456" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F456" s="1" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="G456" s="1" t="s">
         <v>30</v>
@@ -19717,24 +19717,24 @@
       </c>
       <c r="J456" s="24"/>
     </row>
-    <row r="457" spans="1:10">
+    <row r="457" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A457" s="4">
         <v>455</v>
       </c>
       <c r="B457" s="53" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="C457" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D457" s="2" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="E457" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F457" s="1" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="G457" s="1" t="s">
         <v>30</v>
@@ -19747,24 +19747,24 @@
       </c>
       <c r="J457" s="24"/>
     </row>
-    <row r="458" spans="1:10">
+    <row r="458" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A458" s="4">
         <v>456</v>
       </c>
       <c r="B458" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C458" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D458" s="2" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="E458" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F458" s="1" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="G458" s="1" t="s">
         <v>30</v>
@@ -19777,24 +19777,24 @@
       </c>
       <c r="J458" s="24"/>
     </row>
-    <row r="459" spans="1:10">
+    <row r="459" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A459" s="4">
         <v>457</v>
       </c>
       <c r="B459" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C459" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D459" s="2" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="E459" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F459" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="G459" s="1" t="s">
         <v>30</v>
@@ -19807,24 +19807,24 @@
       </c>
       <c r="J459" s="24"/>
     </row>
-    <row r="460" spans="1:10">
+    <row r="460" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A460" s="4">
         <v>458</v>
       </c>
       <c r="B460" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C460" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D460" s="2" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="E460" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F460" s="1" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="G460" s="1" t="s">
         <v>30</v>
@@ -19837,24 +19837,24 @@
       </c>
       <c r="J460" s="24"/>
     </row>
-    <row r="461" spans="1:10">
+    <row r="461" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A461" s="4">
         <v>459</v>
       </c>
       <c r="B461" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C461" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D461" s="2" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="E461" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F461" s="1" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="G461" s="1" t="s">
         <v>30</v>
@@ -19866,27 +19866,27 @@
         <v>574</v>
       </c>
       <c r="J461" s="3" t="s">
-        <v>1286</v>
-      </c>
-    </row>
-    <row r="462" spans="1:10">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="462" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A462" s="4">
         <v>460</v>
       </c>
       <c r="B462" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C462" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D462" s="2" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="E462" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F462" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="G462" s="1" t="s">
         <v>30</v>
@@ -19899,24 +19899,24 @@
       </c>
       <c r="J462" s="24"/>
     </row>
-    <row r="463" spans="1:10">
+    <row r="463" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A463" s="4">
         <v>461</v>
       </c>
       <c r="B463" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C463" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D463" s="2" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="E463" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F463" s="1" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="G463" s="1" t="s">
         <v>30</v>
@@ -19929,24 +19929,24 @@
       </c>
       <c r="J463" s="24"/>
     </row>
-    <row r="464" spans="1:10">
+    <row r="464" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A464" s="4">
         <v>462</v>
       </c>
       <c r="B464" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C464" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D464" s="2" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="E464" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F464" s="1" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="G464" s="1" t="s">
         <v>30</v>
@@ -19959,24 +19959,24 @@
       </c>
       <c r="J464" s="24"/>
     </row>
-    <row r="465" spans="1:10">
+    <row r="465" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A465" s="4">
         <v>463</v>
       </c>
       <c r="B465" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C465" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D465" s="2" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="E465" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F465" s="1" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G465" s="1" t="s">
         <v>30</v>
@@ -19989,24 +19989,24 @@
       </c>
       <c r="J465" s="24"/>
     </row>
-    <row r="466" spans="1:10">
+    <row r="466" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A466" s="4">
         <v>464</v>
       </c>
       <c r="B466" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C466" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D466" s="2" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="E466" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F466" s="1" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="G466" s="1" t="s">
         <v>30</v>
@@ -20019,24 +20019,24 @@
       </c>
       <c r="J466" s="24"/>
     </row>
-    <row r="467" spans="1:10">
+    <row r="467" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A467" s="4">
         <v>465</v>
       </c>
       <c r="B467" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C467" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D467" s="2" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="E467" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F467" s="1" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="G467" s="1" t="s">
         <v>30</v>
@@ -20049,24 +20049,24 @@
       </c>
       <c r="J467" s="24"/>
     </row>
-    <row r="468" spans="1:10">
+    <row r="468" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A468" s="4">
         <v>466</v>
       </c>
       <c r="B468" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C468" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D468" s="2" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="E468" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F468" s="1" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="G468" s="1" t="s">
         <v>30</v>
@@ -20079,24 +20079,24 @@
       </c>
       <c r="J468" s="24"/>
     </row>
-    <row r="469" spans="1:10">
+    <row r="469" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A469" s="4">
         <v>467</v>
       </c>
       <c r="B469" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C469" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D469" s="2" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="E469" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F469" s="1" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="G469" s="1" t="s">
         <v>30</v>
@@ -20109,24 +20109,24 @@
       </c>
       <c r="J469" s="24"/>
     </row>
-    <row r="470" spans="1:10">
+    <row r="470" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A470" s="4">
         <v>468</v>
       </c>
       <c r="B470" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C470" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D470" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="E470" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F470" s="1" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="G470" s="1" t="s">
         <v>30</v>
@@ -20139,24 +20139,24 @@
       </c>
       <c r="J470" s="24"/>
     </row>
-    <row r="471" spans="1:10">
+    <row r="471" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A471" s="4">
         <v>469</v>
       </c>
       <c r="B471" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C471" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D471" s="2" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="E471" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F471" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="G471" s="1" t="s">
         <v>30</v>
@@ -20169,24 +20169,24 @@
       </c>
       <c r="J471" s="24"/>
     </row>
-    <row r="472" spans="1:10">
+    <row r="472" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A472" s="4">
         <v>470</v>
       </c>
       <c r="B472" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C472" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D472" s="2" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="E472" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F472" s="1" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="G472" s="1" t="s">
         <v>30</v>
@@ -20199,24 +20199,24 @@
       </c>
       <c r="J472" s="24"/>
     </row>
-    <row r="473" spans="1:10">
+    <row r="473" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A473" s="4">
         <v>471</v>
       </c>
       <c r="B473" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C473" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D473" s="2" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="E473" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F473" s="1" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="G473" s="1" t="s">
         <v>30</v>
@@ -20229,24 +20229,24 @@
       </c>
       <c r="J473" s="24"/>
     </row>
-    <row r="474" spans="1:10">
+    <row r="474" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A474" s="4">
         <v>472</v>
       </c>
       <c r="B474" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C474" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D474" s="2" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="E474" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F474" s="1" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="G474" s="1" t="s">
         <v>30</v>
@@ -20259,24 +20259,24 @@
       </c>
       <c r="J474" s="24"/>
     </row>
-    <row r="475" spans="1:10">
+    <row r="475" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A475" s="4">
         <v>473</v>
       </c>
       <c r="B475" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C475" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D475" s="2" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="E475" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F475" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="G475" s="1" t="s">
         <v>30</v>
@@ -20289,24 +20289,24 @@
       </c>
       <c r="J475" s="24"/>
     </row>
-    <row r="476" spans="1:10">
+    <row r="476" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A476" s="4">
         <v>474</v>
       </c>
       <c r="B476" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C476" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D476" s="2" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="E476" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F476" s="1" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="G476" s="1" t="s">
         <v>30</v>
@@ -20319,24 +20319,24 @@
       </c>
       <c r="J476" s="24"/>
     </row>
-    <row r="477" spans="1:10">
+    <row r="477" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A477" s="4">
         <v>475</v>
       </c>
       <c r="B477" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C477" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D477" s="2" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="E477" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F477" s="1" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="G477" s="1" t="s">
         <v>30</v>
@@ -20349,24 +20349,24 @@
       </c>
       <c r="J477" s="24"/>
     </row>
-    <row r="478" spans="1:10">
+    <row r="478" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A478" s="4">
         <v>476</v>
       </c>
       <c r="B478" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C478" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D478" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="E478" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F478" s="1" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="G478" s="1" t="s">
         <v>30</v>
@@ -20379,24 +20379,24 @@
       </c>
       <c r="J478" s="24"/>
     </row>
-    <row r="479" spans="1:10">
+    <row r="479" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A479" s="4">
         <v>477</v>
       </c>
       <c r="B479" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C479" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D479" s="2" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E479" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F479" s="1" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="G479" s="1" t="s">
         <v>30</v>
@@ -20409,24 +20409,24 @@
       </c>
       <c r="J479" s="24"/>
     </row>
-    <row r="480" spans="1:10">
+    <row r="480" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A480" s="4">
         <v>478</v>
       </c>
       <c r="B480" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C480" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D480" s="2" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="E480" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F480" s="1" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G480" s="1" t="s">
         <v>30</v>
@@ -20439,24 +20439,24 @@
       </c>
       <c r="J480" s="24"/>
     </row>
-    <row r="481" spans="1:10">
+    <row r="481" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A481" s="4">
         <v>479</v>
       </c>
       <c r="B481" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C481" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D481" s="2" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="E481" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F481" s="1" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="G481" s="1" t="s">
         <v>30</v>
@@ -20469,24 +20469,24 @@
       </c>
       <c r="J481" s="24"/>
     </row>
-    <row r="482" spans="1:10">
+    <row r="482" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A482" s="4">
         <v>480</v>
       </c>
       <c r="B482" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C482" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D482" s="2" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="E482" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F482" s="1" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="G482" s="1" t="s">
         <v>30</v>
@@ -20499,18 +20499,18 @@
       </c>
       <c r="J482" s="24"/>
     </row>
-    <row r="483" spans="1:10">
+    <row r="483" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A483" s="4">
         <v>481</v>
       </c>
       <c r="B483" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C483" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D483" s="2" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="E483" s="1" t="s">
         <v>19</v>
@@ -20529,24 +20529,24 @@
       </c>
       <c r="J483" s="24"/>
     </row>
-    <row r="484" spans="1:10">
+    <row r="484" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A484" s="4">
         <v>482</v>
       </c>
       <c r="B484" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C484" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D484" s="2" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="E484" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F484" s="1" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="G484" s="1" t="s">
         <v>30</v>
@@ -20559,24 +20559,24 @@
       </c>
       <c r="J484" s="24"/>
     </row>
-    <row r="485" spans="1:10">
+    <row r="485" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A485" s="4">
         <v>483</v>
       </c>
       <c r="B485" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C485" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D485" s="2" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="E485" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F485" s="1" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="G485" s="1" t="s">
         <v>30</v>
@@ -20589,24 +20589,24 @@
       </c>
       <c r="J485" s="24"/>
     </row>
-    <row r="486" spans="1:10">
+    <row r="486" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A486" s="4">
         <v>484</v>
       </c>
       <c r="B486" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C486" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D486" s="2" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="E486" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F486" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="G486" s="1" t="s">
         <v>30</v>
@@ -20619,24 +20619,24 @@
       </c>
       <c r="J486" s="24"/>
     </row>
-    <row r="487" spans="1:10">
+    <row r="487" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A487" s="4">
         <v>485</v>
       </c>
       <c r="B487" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C487" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D487" s="2" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="E487" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F487" s="1" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="G487" s="1" t="s">
         <v>30</v>
@@ -20649,18 +20649,18 @@
       </c>
       <c r="J487" s="24"/>
     </row>
-    <row r="488" spans="1:10">
+    <row r="488" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A488" s="4">
         <v>486</v>
       </c>
       <c r="B488" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C488" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D488" s="2" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="E488" s="1" t="s">
         <v>21</v>
@@ -20678,27 +20678,27 @@
         <v>574</v>
       </c>
       <c r="J488" s="3" t="s">
-        <v>1315</v>
-      </c>
-    </row>
-    <row r="489" spans="1:10">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="489" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A489" s="4">
         <v>487</v>
       </c>
       <c r="B489" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C489" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D489" s="2" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="E489" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F489" s="1" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="G489" s="1" t="s">
         <v>30</v>
@@ -20711,24 +20711,24 @@
       </c>
       <c r="J489" s="24"/>
     </row>
-    <row r="490" spans="1:10">
+    <row r="490" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A490" s="4">
         <v>488</v>
       </c>
       <c r="B490" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C490" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D490" s="2" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="E490" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F490" s="1" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="G490" s="1" t="s">
         <v>30</v>
@@ -20741,24 +20741,24 @@
       </c>
       <c r="J490" s="24"/>
     </row>
-    <row r="491" spans="1:10">
+    <row r="491" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A491" s="4">
         <v>489</v>
       </c>
       <c r="B491" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C491" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D491" s="2" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="E491" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F491" s="1" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="G491" s="1" t="s">
         <v>30</v>
@@ -20771,24 +20771,24 @@
       </c>
       <c r="J491" s="24"/>
     </row>
-    <row r="492" spans="1:10">
+    <row r="492" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A492" s="4">
         <v>490</v>
       </c>
       <c r="B492" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C492" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D492" s="2" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="E492" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F492" s="1" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="G492" s="1" t="s">
         <v>30</v>
@@ -20801,24 +20801,24 @@
       </c>
       <c r="J492" s="24"/>
     </row>
-    <row r="493" spans="1:10">
+    <row r="493" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A493" s="4">
         <v>491</v>
       </c>
       <c r="B493" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C493" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D493" s="2" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="E493" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F493" s="1" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="G493" s="1" t="s">
         <v>30</v>
@@ -20831,12 +20831,12 @@
       </c>
       <c r="J493" s="24"/>
     </row>
-    <row r="494" spans="1:10">
+    <row r="494" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A494" s="4">
         <v>492</v>
       </c>
       <c r="B494" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C494" s="1" t="s">
         <v>11</v>
@@ -20861,12 +20861,12 @@
       </c>
       <c r="J494" s="24"/>
     </row>
-    <row r="495" spans="1:10">
+    <row r="495" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A495" s="4">
         <v>493</v>
       </c>
       <c r="B495" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C495" s="1" t="s">
         <v>11</v>
@@ -20891,12 +20891,12 @@
       </c>
       <c r="J495" s="24"/>
     </row>
-    <row r="496" spans="1:10">
+    <row r="496" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A496" s="4">
         <v>494</v>
       </c>
       <c r="B496" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C496" s="1" t="s">
         <v>11</v>
@@ -20921,18 +20921,18 @@
       </c>
       <c r="J496" s="24"/>
     </row>
-    <row r="497" spans="1:10">
+    <row r="497" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A497" s="4">
         <v>495</v>
       </c>
       <c r="B497" s="52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C497" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D497" s="2" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="E497" s="1" t="s">
         <v>19</v>
@@ -20951,18 +20951,18 @@
       </c>
       <c r="J497" s="24"/>
     </row>
-    <row r="498" spans="1:10">
+    <row r="498" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A498" s="4">
         <v>496</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="C498" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D498" s="2" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="E498" s="1" t="s">
         <v>21</v>
@@ -20981,24 +20981,24 @@
       </c>
       <c r="J498" s="24"/>
     </row>
-    <row r="499" spans="1:10">
+    <row r="499" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A499" s="4">
         <v>497</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="C499" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D499" s="2" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E499" s="1" t="s">
+        <v>966</v>
+      </c>
+      <c r="F499" s="1" t="s">
         <v>1274</v>
-      </c>
-      <c r="E499" s="1" t="s">
-        <v>967</v>
-      </c>
-      <c r="F499" s="1" t="s">
-        <v>1275</v>
       </c>
       <c r="G499" s="1" t="s">
         <v>30</v>
@@ -21087,7 +21087,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6771508-02DF-4FAC-B7A7-A6278CE7AE5B}">
   <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
@@ -21096,7 +21096,7 @@
     <col min="6" max="6" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>516</v>
       </c>
@@ -21116,127 +21116,127 @@
         <v>520</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="42" t="s">
+        <v>869</v>
+      </c>
+      <c r="B2" s="42" t="s">
         <v>870</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="C2" s="42" t="s">
         <v>871</v>
       </c>
-      <c r="C2" s="42" t="s">
+      <c r="D2" s="43" t="s">
+        <v>897</v>
+      </c>
+      <c r="E2" s="44" t="s">
         <v>872</v>
-      </c>
-      <c r="D2" s="43" t="s">
-        <v>898</v>
-      </c>
-      <c r="E2" s="44" t="s">
-        <v>873</v>
       </c>
       <c r="F2" s="46">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="42" t="s">
+        <v>869</v>
+      </c>
+      <c r="B3" s="42" t="s">
         <v>870</v>
       </c>
-      <c r="B3" s="42" t="s">
+      <c r="C3" s="42" t="s">
         <v>871</v>
       </c>
-      <c r="C3" s="42" t="s">
+      <c r="D3" s="43" t="s">
+        <v>898</v>
+      </c>
+      <c r="E3" s="44" t="s">
         <v>872</v>
-      </c>
-      <c r="D3" s="43" t="s">
-        <v>899</v>
-      </c>
-      <c r="E3" s="44" t="s">
-        <v>873</v>
       </c>
       <c r="F3" s="46">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="42" t="s">
+        <v>869</v>
+      </c>
+      <c r="B4" s="42" t="s">
         <v>870</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="C4" s="42" t="s">
         <v>871</v>
       </c>
-      <c r="C4" s="42" t="s">
+      <c r="D4" s="43" t="s">
+        <v>899</v>
+      </c>
+      <c r="E4" s="44" t="s">
         <v>872</v>
-      </c>
-      <c r="D4" s="43" t="s">
-        <v>900</v>
-      </c>
-      <c r="E4" s="44" t="s">
-        <v>873</v>
       </c>
       <c r="F4" s="46">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="42" t="s">
+        <v>869</v>
+      </c>
+      <c r="B5" s="42" t="s">
         <v>870</v>
       </c>
-      <c r="B5" s="42" t="s">
+      <c r="C5" s="42" t="s">
         <v>871</v>
       </c>
-      <c r="C5" s="42" t="s">
+      <c r="D5" s="43" t="s">
+        <v>900</v>
+      </c>
+      <c r="E5" s="44" t="s">
         <v>872</v>
-      </c>
-      <c r="D5" s="43" t="s">
-        <v>901</v>
-      </c>
-      <c r="E5" s="44" t="s">
-        <v>873</v>
       </c>
       <c r="F5" s="46">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="42" t="s">
+        <v>869</v>
+      </c>
+      <c r="B6" s="42" t="s">
         <v>870</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="C6" s="42" t="s">
         <v>871</v>
       </c>
-      <c r="C6" s="42" t="s">
+      <c r="D6" s="43" t="s">
+        <v>901</v>
+      </c>
+      <c r="E6" s="44" t="s">
         <v>872</v>
-      </c>
-      <c r="D6" s="43" t="s">
-        <v>902</v>
-      </c>
-      <c r="E6" s="44" t="s">
-        <v>873</v>
       </c>
       <c r="F6" s="46">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="42" t="s">
+        <v>869</v>
+      </c>
+      <c r="B7" s="42" t="s">
         <v>870</v>
       </c>
-      <c r="B7" s="42" t="s">
+      <c r="C7" s="42" t="s">
         <v>871</v>
       </c>
-      <c r="C7" s="42" t="s">
+      <c r="D7" s="44" t="s">
+        <v>902</v>
+      </c>
+      <c r="E7" s="44" t="s">
         <v>872</v>
-      </c>
-      <c r="D7" s="44" t="s">
-        <v>903</v>
-      </c>
-      <c r="E7" s="44" t="s">
-        <v>873</v>
       </c>
       <c r="F7" s="46">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>521</v>
       </c>
@@ -21253,7 +21253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>521</v>
       </c>
@@ -21270,7 +21270,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>521</v>
       </c>
@@ -21287,7 +21287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>521</v>
       </c>
@@ -21304,7 +21304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>521</v>
       </c>
@@ -21321,7 +21321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>521</v>
       </c>
@@ -21338,7 +21338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>521</v>
       </c>
@@ -21355,7 +21355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>521</v>
       </c>
@@ -21372,7 +21372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>521</v>
       </c>
@@ -21389,7 +21389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>521</v>
       </c>
@@ -21406,7 +21406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>521</v>
       </c>
@@ -21423,7 +21423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>521</v>
       </c>
@@ -21440,7 +21440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>521</v>
       </c>
@@ -21457,7 +21457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>526</v>
       </c>
@@ -21477,7 +21477,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>526</v>
       </c>
@@ -21497,7 +21497,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>526</v>
       </c>
@@ -21517,7 +21517,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>526</v>
       </c>
@@ -21537,7 +21537,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>526</v>
       </c>
@@ -21557,7 +21557,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>526</v>
       </c>
@@ -21577,7 +21577,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>526</v>
       </c>
@@ -21597,7 +21597,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>539</v>
       </c>
@@ -21617,7 +21617,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>543</v>
       </c>
@@ -21637,7 +21637,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>545</v>
       </c>
@@ -21657,7 +21657,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>545</v>
       </c>
@@ -21677,7 +21677,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>539</v>
       </c>
@@ -21709,7 +21709,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD4931DD-77FA-4EF6-BAB3-744C5E5D53EC}">
   <dimension ref="A1:XFC75"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.88671875" bestFit="1" customWidth="1"/>
@@ -21726,7 +21726,7 @@
     <col min="16384" max="16384" width="16.21875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -21758,7 +21758,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -21790,7 +21790,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -21822,7 +21822,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -21854,7 +21854,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -21886,7 +21886,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -21918,7 +21918,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -21950,7 +21950,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -21982,7 +21982,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -22014,7 +22014,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -22046,7 +22046,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -22078,7 +22078,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -22110,7 +22110,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -22142,7 +22142,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -22174,7 +22174,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -22206,7 +22206,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -22238,7 +22238,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -22270,7 +22270,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -22302,7 +22302,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -22334,7 +22334,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -22366,7 +22366,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -22398,7 +22398,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -22430,7 +22430,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -22462,7 +22462,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -22494,7 +22494,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -22524,7 +22524,7 @@
       </c>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -22554,7 +22554,7 @@
       </c>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -22584,7 +22584,7 @@
       </c>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>27</v>
       </c>
@@ -22614,7 +22614,7 @@
       </c>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -22644,7 +22644,7 @@
       </c>
       <c r="J29" s="3"/>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>29</v>
       </c>
@@ -22674,7 +22674,7 @@
       </c>
       <c r="J30" s="3"/>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -22704,7 +22704,7 @@
       </c>
       <c r="J31" s="3"/>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>31</v>
       </c>
@@ -22734,7 +22734,7 @@
       </c>
       <c r="J32" s="3"/>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -22764,7 +22764,7 @@
       </c>
       <c r="J33" s="3"/>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
         <v>33</v>
       </c>
@@ -22794,7 +22794,7 @@
       </c>
       <c r="J34" s="3"/>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>34</v>
       </c>
@@ -22824,7 +22824,7 @@
       </c>
       <c r="J35" s="3"/>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="J36" s="3"/>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -22884,7 +22884,7 @@
       </c>
       <c r="J37" s="3"/>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
         <v>37</v>
       </c>
@@ -22914,7 +22914,7 @@
       </c>
       <c r="J38" s="3"/>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -22944,7 +22944,7 @@
       </c>
       <c r="J39" s="3"/>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
         <v>39</v>
       </c>
@@ -22974,7 +22974,7 @@
       </c>
       <c r="J40" s="3"/>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -23004,7 +23004,7 @@
       </c>
       <c r="J41" s="3"/>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
         <v>41</v>
       </c>
@@ -23033,7 +23033,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -23065,15 +23065,15 @@
         <v>804</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="33">
         <v>43</v>
       </c>
       <c r="B44" t="s">
+        <v>873</v>
+      </c>
+      <c r="C44" s="33" t="s">
         <v>874</v>
-      </c>
-      <c r="C44" s="33" t="s">
-        <v>875</v>
       </c>
       <c r="D44" s="33">
         <v>101</v>
@@ -23094,18 +23094,18 @@
         <v>15</v>
       </c>
       <c r="J44" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="18">
         <v>44</v>
       </c>
       <c r="B45" t="s">
+        <v>873</v>
+      </c>
+      <c r="C45" s="48" t="s">
         <v>874</v>
-      </c>
-      <c r="C45" s="48" t="s">
-        <v>875</v>
       </c>
       <c r="D45" s="33">
         <v>102</v>
@@ -23126,15 +23126,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="18">
         <v>45</v>
       </c>
       <c r="B46" s="45" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="C46" s="48" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="D46">
         <v>201</v>
@@ -23155,15 +23155,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="18">
         <v>46</v>
       </c>
       <c r="B47" s="45" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="C47" s="48" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="D47">
         <v>202</v>
@@ -23184,15 +23184,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="18">
         <v>47</v>
       </c>
       <c r="B48" s="45" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="C48" s="48" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="D48">
         <v>203</v>
@@ -23213,15 +23213,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="18">
         <v>48</v>
       </c>
       <c r="B49" s="45" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="C49" s="48" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="D49">
         <v>204</v>
@@ -23242,15 +23242,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="18">
         <v>49</v>
       </c>
       <c r="B50" s="45" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="C50" s="48" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="D50">
         <v>205</v>
@@ -23271,18 +23271,18 @@
         <v>15</v>
       </c>
       <c r="J50" t="s">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="18">
         <v>50</v>
       </c>
       <c r="B51" s="45" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="C51" s="48" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="D51">
         <v>206</v>
@@ -23291,7 +23291,7 @@
         <v>13</v>
       </c>
       <c r="F51" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="G51" t="s">
         <v>30</v>
@@ -23303,10 +23303,10 @@
         <v>15</v>
       </c>
       <c r="J51" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" s="3" customFormat="1">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4">
         <v>51</v>
       </c>
@@ -23335,10 +23335,10 @@
         <v>574</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" s="3" customFormat="1">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4">
         <v>52</v>
       </c>
@@ -23355,7 +23355,7 @@
         <v>68</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>14</v>
@@ -23370,102 +23370,102 @@
         <v>689</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="18"/>
       <c r="B54" s="21"/>
       <c r="C54" s="49"/>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="18"/>
       <c r="B55" s="21"/>
       <c r="C55" s="49"/>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B56" s="21"/>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B57" s="21"/>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="18"/>
       <c r="B58" s="22"/>
       <c r="C58" s="49"/>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="18"/>
       <c r="B59" s="22"/>
       <c r="C59" s="49"/>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="18"/>
       <c r="B60" s="22"/>
       <c r="C60" s="49"/>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="18"/>
       <c r="B61" s="22"/>
       <c r="C61" s="49"/>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="18"/>
       <c r="B62" s="22"/>
       <c r="C62" s="49"/>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="18"/>
       <c r="B63" s="22"/>
       <c r="C63" s="49"/>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="18"/>
       <c r="B64" s="22"/>
       <c r="C64" s="49"/>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="18"/>
       <c r="B65" s="22"/>
       <c r="C65" s="49"/>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="18"/>
       <c r="B66" s="22"/>
       <c r="C66" s="49"/>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="18"/>
       <c r="B67" s="22"/>
       <c r="C67" s="49"/>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="18"/>
       <c r="B68" s="22"/>
       <c r="C68" s="49"/>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="18"/>
       <c r="B69" s="22"/>
       <c r="C69" s="49"/>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="18"/>
       <c r="B70" s="22"/>
       <c r="C70" s="49"/>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="18"/>
       <c r="B71" s="22"/>
       <c r="C71" s="49"/>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B72" s="21"/>
     </row>
-    <row r="73" spans="1:3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B73" s="21"/>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B74" s="21"/>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B75" s="21"/>
     </row>
   </sheetData>

--- a/data_printer.xlsx
+++ b/data_printer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erick\Desktop\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57BB6E86-F82B-43B3-9870-8BA5BA8E324C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A60AC6D-FD10-4A92-A3CD-DA3CF6F02F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A8AA41B5-7AA1-4FF7-A9B8-54B8A4E1AF28}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4370" uniqueCount="1317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4370" uniqueCount="1318">
   <si>
     <t>INDICE</t>
   </si>
@@ -3925,9 +3925,6 @@
     <t>E.M. DR. FABIO SIQUEIRA</t>
   </si>
   <si>
-    <t>PROBLEMA NA UNIDADE DE FUSÃO; RETIRADA PAIVA MACHARETE 10/06/2026;</t>
-  </si>
-  <si>
     <t>FERNANDO</t>
   </si>
   <si>
@@ -3989,13 +3986,19 @@
   </si>
   <si>
     <t xml:space="preserve">ESTAVA NA PROG 2 - PAÇO; ESTAVA NO DARCY RIBEIRO; RETIRADA MAESTRO KIKO ERRO 673-10  23/10/2025; TROCA DE UNIDADE DE IMAGEM CILINDRO LAMINA DE LIMPEZA PRC ROLO TRANSMISSOR FUSÃO ROLETES 23/10/2025; INSTALADA NO UNNOMED -SPA 24/10/2025; </t>
+  </si>
+  <si>
+    <t>BATALHAO 42º</t>
+  </si>
+  <si>
+    <t>PROBLEMA NA UNIDADE DE FUSÃO; RETIRADA PAIVA MACHARETE 10/06/2026; INSTALADA NA 42º BATALHAO ARARUAMA 05/08/2026;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5361,7 +5364,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD39631B-97B8-405A-AA43-14CDFBC77F92}">
   <dimension ref="A1:J499"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33.109375" style="2" bestFit="1" customWidth="1"/>
@@ -5376,7 +5379,7 @@
     <col min="11" max="16384" width="9.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5408,7 +5411,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -5440,7 +5443,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -5472,7 +5475,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -5504,7 +5507,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -5536,7 +5539,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -5568,7 +5571,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -5600,7 +5603,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -5632,7 +5635,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -5662,7 +5665,7 @@
       </c>
       <c r="J9" s="7"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -5692,7 +5695,7 @@
       </c>
       <c r="J10" s="7"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -5724,7 +5727,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -5756,7 +5759,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -5788,7 +5791,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -5820,7 +5823,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -5852,7 +5855,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -5881,7 +5884,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -5913,7 +5916,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -5945,7 +5948,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -5977,7 +5980,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -6009,7 +6012,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -6041,7 +6044,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" ht="15.75" customHeight="1">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -6073,7 +6076,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -6105,7 +6108,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -6137,7 +6140,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -6169,7 +6172,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -6198,7 +6201,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -6227,7 +6230,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10">
       <c r="A28" s="4">
         <v>27</v>
       </c>
@@ -6259,7 +6262,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -6291,7 +6294,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10">
       <c r="A30" s="4">
         <v>29</v>
       </c>
@@ -6323,7 +6326,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -6355,7 +6358,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10">
       <c r="A32" s="4">
         <v>31</v>
       </c>
@@ -6387,7 +6390,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -6419,7 +6422,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10">
       <c r="A34" s="4">
         <v>33</v>
       </c>
@@ -6433,10 +6436,10 @@
         <v>78</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>23</v>
+        <v>1316</v>
       </c>
       <c r="G34" s="4" t="s">
         <v>14</v>
@@ -6448,10 +6451,10 @@
         <v>574</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>1295</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" s="4">
         <v>34</v>
       </c>
@@ -6483,7 +6486,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -6515,7 +6518,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -6544,7 +6547,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10">
       <c r="A38" s="4">
         <v>37</v>
       </c>
@@ -6576,7 +6579,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -6608,7 +6611,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10">
       <c r="A40" s="4">
         <v>39</v>
       </c>
@@ -6640,7 +6643,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -6672,7 +6675,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10">
       <c r="A42" s="4">
         <v>41</v>
       </c>
@@ -6704,7 +6707,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -6736,7 +6739,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10">
       <c r="A44" s="4">
         <v>43</v>
       </c>
@@ -6768,7 +6771,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10">
       <c r="A45" s="4">
         <v>44</v>
       </c>
@@ -6797,7 +6800,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10">
       <c r="A46" s="4">
         <v>45</v>
       </c>
@@ -6829,7 +6832,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10">
       <c r="A47" s="4">
         <v>46</v>
       </c>
@@ -6861,7 +6864,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10">
       <c r="A48" s="4">
         <v>47</v>
       </c>
@@ -6893,7 +6896,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10">
       <c r="A49" s="4">
         <v>48</v>
       </c>
@@ -6922,7 +6925,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10">
       <c r="A50" s="4">
         <v>49</v>
       </c>
@@ -6951,7 +6954,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10">
       <c r="A51" s="4">
         <v>50</v>
       </c>
@@ -6983,7 +6986,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10">
       <c r="A52" s="4">
         <v>51</v>
       </c>
@@ -7015,7 +7018,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10">
       <c r="A53" s="4">
         <v>52</v>
       </c>
@@ -7047,7 +7050,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10">
       <c r="A54" s="4">
         <v>53</v>
       </c>
@@ -7079,7 +7082,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10">
       <c r="A55" s="4">
         <v>54</v>
       </c>
@@ -7108,7 +7111,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10">
       <c r="A56" s="4">
         <v>55</v>
       </c>
@@ -7137,7 +7140,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10">
       <c r="A57" s="4">
         <v>56</v>
       </c>
@@ -7166,7 +7169,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10">
       <c r="A58" s="4">
         <v>57</v>
       </c>
@@ -7195,7 +7198,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10">
       <c r="A59" s="4">
         <v>58</v>
       </c>
@@ -7224,7 +7227,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10">
       <c r="A60" s="4">
         <v>59</v>
       </c>
@@ -7253,7 +7256,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10">
       <c r="A61" s="4">
         <v>60</v>
       </c>
@@ -7285,7 +7288,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10">
       <c r="A62" s="4">
         <v>61</v>
       </c>
@@ -7317,7 +7320,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10">
       <c r="A63" s="4">
         <v>62</v>
       </c>
@@ -7346,7 +7349,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10">
       <c r="A64" s="4">
         <v>63</v>
       </c>
@@ -7378,7 +7381,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10">
       <c r="A65" s="4">
         <v>64</v>
       </c>
@@ -7407,7 +7410,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10">
       <c r="A66" s="4">
         <v>65</v>
       </c>
@@ -7436,7 +7439,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10">
       <c r="A67" s="4">
         <v>66</v>
       </c>
@@ -7465,7 +7468,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10">
       <c r="A68" s="4">
         <v>67</v>
       </c>
@@ -7494,7 +7497,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10">
       <c r="A69" s="4">
         <v>68</v>
       </c>
@@ -7526,7 +7529,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10">
       <c r="A70" s="4">
         <v>69</v>
       </c>
@@ -7558,7 +7561,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10">
       <c r="A71" s="4">
         <v>70</v>
       </c>
@@ -7587,7 +7590,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10">
       <c r="A72" s="4">
         <v>71</v>
       </c>
@@ -7619,7 +7622,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10">
       <c r="A73" s="4">
         <v>72</v>
       </c>
@@ -7651,7 +7654,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10">
       <c r="A74" s="4">
         <v>73</v>
       </c>
@@ -7683,7 +7686,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10">
       <c r="A75" s="4">
         <v>74</v>
       </c>
@@ -7712,7 +7715,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10">
       <c r="A76" s="4">
         <v>75</v>
       </c>
@@ -7744,7 +7747,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10">
       <c r="A77" s="4">
         <v>76</v>
       </c>
@@ -7776,7 +7779,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10">
       <c r="A78" s="4">
         <v>77</v>
       </c>
@@ -7808,7 +7811,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10">
       <c r="A79" s="4">
         <v>78</v>
       </c>
@@ -7840,7 +7843,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10">
       <c r="A80" s="4">
         <v>79</v>
       </c>
@@ -7872,7 +7875,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10">
       <c r="A81" s="4">
         <v>80</v>
       </c>
@@ -7904,7 +7907,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10">
       <c r="A82" s="4">
         <v>81</v>
       </c>
@@ -7930,7 +7933,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10">
       <c r="A83" s="4">
         <v>82</v>
       </c>
@@ -7956,7 +7959,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10">
       <c r="A84" s="4">
         <v>83</v>
       </c>
@@ -7982,7 +7985,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10">
       <c r="A85" s="4">
         <v>84</v>
       </c>
@@ -8014,7 +8017,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10">
       <c r="A86" s="4">
         <v>85</v>
       </c>
@@ -8046,7 +8049,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10">
       <c r="A87" s="4">
         <v>86</v>
       </c>
@@ -8078,7 +8081,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10">
       <c r="A88" s="4">
         <v>87</v>
       </c>
@@ -8110,7 +8113,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10">
       <c r="A89" s="4">
         <v>88</v>
       </c>
@@ -8139,7 +8142,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10">
       <c r="A90" s="4">
         <v>89</v>
       </c>
@@ -8171,7 +8174,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10">
       <c r="A91" s="4">
         <v>90</v>
       </c>
@@ -8203,7 +8206,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10">
       <c r="A92" s="4">
         <v>91</v>
       </c>
@@ -8229,7 +8232,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10">
       <c r="A93" s="4">
         <v>92</v>
       </c>
@@ -8255,7 +8258,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10">
       <c r="A94" s="4">
         <v>93</v>
       </c>
@@ -8287,7 +8290,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10">
       <c r="A95" s="4">
         <v>94</v>
       </c>
@@ -8316,7 +8319,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10">
       <c r="A96" s="4">
         <v>95</v>
       </c>
@@ -8345,7 +8348,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10">
       <c r="A97" s="4">
         <v>96</v>
       </c>
@@ -8374,7 +8377,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10">
       <c r="A98" s="4">
         <v>97</v>
       </c>
@@ -8403,7 +8406,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:10">
       <c r="A99" s="4">
         <v>98</v>
       </c>
@@ -8435,7 +8438,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:10">
       <c r="A100" s="4">
         <v>99</v>
       </c>
@@ -8467,7 +8470,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:10">
       <c r="A101" s="4">
         <v>100</v>
       </c>
@@ -8499,7 +8502,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:10">
       <c r="A102" s="4">
         <v>101</v>
       </c>
@@ -8531,7 +8534,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:10">
       <c r="A103" s="4">
         <v>102</v>
       </c>
@@ -8563,7 +8566,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:10">
       <c r="A104" s="4">
         <v>103</v>
       </c>
@@ -8595,7 +8598,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:10">
       <c r="A105" s="4">
         <v>104</v>
       </c>
@@ -8627,7 +8630,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:10">
       <c r="A106" s="4">
         <v>105</v>
       </c>
@@ -8659,7 +8662,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:10">
       <c r="A107" s="4">
         <v>106</v>
       </c>
@@ -8691,7 +8694,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:10">
       <c r="A108" s="4">
         <v>107</v>
       </c>
@@ -8719,7 +8722,7 @@
       </c>
       <c r="J108" s="24"/>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:10">
       <c r="A109" s="4">
         <v>108</v>
       </c>
@@ -8751,7 +8754,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:10">
       <c r="A110" s="4">
         <v>109</v>
       </c>
@@ -8783,7 +8786,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:10">
       <c r="A111" s="4">
         <v>110</v>
       </c>
@@ -8815,7 +8818,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:10">
       <c r="A112" s="4">
         <v>111</v>
       </c>
@@ -8847,7 +8850,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:10">
       <c r="A113" s="4">
         <v>112</v>
       </c>
@@ -8879,7 +8882,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:10">
       <c r="A114" s="4">
         <v>113</v>
       </c>
@@ -8911,7 +8914,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:10">
       <c r="A115" s="4">
         <v>114</v>
       </c>
@@ -8943,7 +8946,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10">
       <c r="A116" s="4">
         <v>115</v>
       </c>
@@ -8975,7 +8978,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:10">
       <c r="A117" s="4">
         <v>116</v>
       </c>
@@ -9007,7 +9010,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:10">
       <c r="A118" s="4">
         <v>117</v>
       </c>
@@ -9039,7 +9042,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10">
       <c r="A119" s="4">
         <v>118</v>
       </c>
@@ -9071,7 +9074,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:10">
       <c r="A120" s="4">
         <v>119</v>
       </c>
@@ -9103,7 +9106,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10">
       <c r="A121" s="4">
         <v>120</v>
       </c>
@@ -9135,7 +9138,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:10">
       <c r="A122" s="4">
         <v>121</v>
       </c>
@@ -9167,7 +9170,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:10">
       <c r="A123" s="4">
         <v>122</v>
       </c>
@@ -9199,7 +9202,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:10">
       <c r="A124" s="4">
         <v>123</v>
       </c>
@@ -9231,7 +9234,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10">
       <c r="A125" s="4">
         <v>124</v>
       </c>
@@ -9263,7 +9266,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:10">
       <c r="A126" s="4">
         <v>125</v>
       </c>
@@ -9295,7 +9298,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:10">
       <c r="A127" s="4">
         <v>126</v>
       </c>
@@ -9327,7 +9330,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:10">
       <c r="A128" s="4">
         <v>127</v>
       </c>
@@ -9359,7 +9362,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:10">
       <c r="A129" s="4">
         <v>128</v>
       </c>
@@ -9391,7 +9394,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:10">
       <c r="A130" s="4">
         <v>129</v>
       </c>
@@ -9423,7 +9426,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:10">
       <c r="A131" s="4">
         <v>130</v>
       </c>
@@ -9455,7 +9458,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:10">
       <c r="A132" s="4">
         <v>131</v>
       </c>
@@ -9487,7 +9490,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:10">
       <c r="A133" s="4">
         <v>132</v>
       </c>
@@ -9519,7 +9522,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:10">
       <c r="A134" s="4">
         <v>133</v>
       </c>
@@ -9551,7 +9554,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:10">
       <c r="A135" s="4">
         <v>134</v>
       </c>
@@ -9583,7 +9586,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:10">
       <c r="A136" s="4">
         <v>135</v>
       </c>
@@ -9615,7 +9618,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:10">
       <c r="A137" s="4">
         <v>136</v>
       </c>
@@ -9647,7 +9650,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:10">
       <c r="A138" s="4">
         <v>137</v>
       </c>
@@ -9676,10 +9679,10 @@
         <v>574</v>
       </c>
       <c r="J138" s="3" t="s">
-        <v>1309</v>
-      </c>
-    </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10">
       <c r="A139" s="4">
         <v>138</v>
       </c>
@@ -9711,7 +9714,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:10">
       <c r="A140" s="4">
         <v>139</v>
       </c>
@@ -9743,7 +9746,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:10">
       <c r="A141" s="4">
         <v>140</v>
       </c>
@@ -9772,10 +9775,10 @@
         <v>574</v>
       </c>
       <c r="J141" s="12" t="s">
-        <v>1316</v>
-      </c>
-    </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10">
       <c r="A142" s="4">
         <v>141</v>
       </c>
@@ -9804,10 +9807,10 @@
         <v>574</v>
       </c>
       <c r="J142" s="3" t="s">
-        <v>1308</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10">
       <c r="A143" s="4">
         <v>142</v>
       </c>
@@ -9837,7 +9840,7 @@
       </c>
       <c r="J143" s="24"/>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:10">
       <c r="A144" s="4">
         <v>143</v>
       </c>
@@ -9869,7 +9872,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:10">
       <c r="A145" s="4">
         <v>144</v>
       </c>
@@ -9901,7 +9904,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:10">
       <c r="A146" s="4">
         <v>145</v>
       </c>
@@ -9933,7 +9936,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:10">
       <c r="A147" s="4">
         <v>146</v>
       </c>
@@ -9965,7 +9968,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:10">
       <c r="A148" s="4">
         <v>147</v>
       </c>
@@ -9997,7 +10000,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:10">
       <c r="A149" s="4">
         <v>148</v>
       </c>
@@ -10029,7 +10032,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:10">
       <c r="A150" s="4">
         <v>149</v>
       </c>
@@ -10061,7 +10064,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:10">
       <c r="A151" s="4">
         <v>150</v>
       </c>
@@ -10093,7 +10096,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:10">
       <c r="A152" s="4">
         <v>151</v>
       </c>
@@ -10123,7 +10126,7 @@
       </c>
       <c r="J152" s="24"/>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:10">
       <c r="A153" s="4">
         <v>152</v>
       </c>
@@ -10153,7 +10156,7 @@
       </c>
       <c r="J153" s="24"/>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:10">
       <c r="A154" s="4">
         <v>153</v>
       </c>
@@ -10185,7 +10188,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:10">
       <c r="A155" s="4">
         <v>154</v>
       </c>
@@ -10196,13 +10199,13 @@
         <v>83</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="G155" s="13" t="s">
         <v>14</v>
@@ -10214,10 +10217,10 @@
         <v>574</v>
       </c>
       <c r="J155" s="3" t="s">
-        <v>1303</v>
-      </c>
-    </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10">
       <c r="A156" s="4">
         <v>155</v>
       </c>
@@ -10228,13 +10231,13 @@
         <v>83</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="G156" s="13" t="s">
         <v>14</v>
@@ -10246,10 +10249,10 @@
         <v>574</v>
       </c>
       <c r="J156" s="3" t="s">
-        <v>1306</v>
-      </c>
-    </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10">
       <c r="B157" s="2" t="s">
         <v>244</v>
       </c>
@@ -10257,13 +10260,13 @@
         <v>83</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="G157" s="13" t="s">
         <v>14</v>
@@ -10275,10 +10278,10 @@
         <v>574</v>
       </c>
       <c r="J157" s="3" t="s">
-        <v>1312</v>
-      </c>
-    </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10">
       <c r="A158" s="4">
         <v>156</v>
       </c>
@@ -10310,7 +10313,7 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:10">
       <c r="A159" s="4">
         <v>157</v>
       </c>
@@ -10342,7 +10345,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:10">
       <c r="A160" s="4">
         <v>158</v>
       </c>
@@ -10374,7 +10377,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:10">
       <c r="A161" s="4">
         <v>159</v>
       </c>
@@ -10406,7 +10409,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:10">
       <c r="A162" s="4">
         <v>160</v>
       </c>
@@ -10438,7 +10441,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:10">
       <c r="A163" s="4">
         <v>161</v>
       </c>
@@ -10470,7 +10473,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:10">
       <c r="A164" s="4">
         <v>162</v>
       </c>
@@ -10502,7 +10505,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:10">
       <c r="A165" s="4">
         <v>163</v>
       </c>
@@ -10531,7 +10534,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:10">
       <c r="A166" s="4">
         <v>164</v>
       </c>
@@ -10560,7 +10563,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:10">
       <c r="A167" s="4">
         <v>165</v>
       </c>
@@ -10587,7 +10590,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:10">
       <c r="A168" s="4">
         <v>166</v>
       </c>
@@ -10619,7 +10622,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:10">
       <c r="A169" s="4">
         <v>167</v>
       </c>
@@ -10648,7 +10651,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:10">
       <c r="A170" s="4">
         <v>168</v>
       </c>
@@ -10680,7 +10683,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:10">
       <c r="A171" s="4">
         <v>169</v>
       </c>
@@ -10712,7 +10715,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:10">
       <c r="A172" s="4">
         <v>170</v>
       </c>
@@ -10744,7 +10747,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:10">
       <c r="A173" s="4">
         <v>171</v>
       </c>
@@ -10776,7 +10779,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:10">
       <c r="A174" s="4">
         <v>172</v>
       </c>
@@ -10805,7 +10808,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:10">
       <c r="A175" s="4">
         <v>173</v>
       </c>
@@ -10834,7 +10837,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:10">
       <c r="A176" s="4">
         <v>174</v>
       </c>
@@ -10866,7 +10869,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:10">
       <c r="A177" s="4">
         <v>175</v>
       </c>
@@ -10892,7 +10895,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:10">
       <c r="A178" s="4">
         <v>176</v>
       </c>
@@ -10922,7 +10925,7 @@
       </c>
       <c r="J178" s="24"/>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:10">
       <c r="A179" s="4">
         <v>177</v>
       </c>
@@ -10954,7 +10957,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:10">
       <c r="A180" s="4">
         <v>178</v>
       </c>
@@ -10983,7 +10986,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:10">
       <c r="A181" s="4">
         <v>179</v>
       </c>
@@ -11015,7 +11018,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:10">
       <c r="A182" s="4">
         <v>180</v>
       </c>
@@ -11044,7 +11047,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:10">
       <c r="A183" s="4">
         <v>181</v>
       </c>
@@ -11073,7 +11076,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:10">
       <c r="A184" s="4">
         <v>182</v>
       </c>
@@ -11102,7 +11105,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:10">
       <c r="A185" s="4">
         <v>183</v>
       </c>
@@ -11131,7 +11134,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:10">
       <c r="A186" s="4">
         <v>184</v>
       </c>
@@ -11160,7 +11163,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:10">
       <c r="A187" s="4">
         <v>185</v>
       </c>
@@ -11189,7 +11192,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:10">
       <c r="A188" s="4">
         <v>186</v>
       </c>
@@ -11218,7 +11221,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:10">
       <c r="A189" s="4">
         <v>187</v>
       </c>
@@ -11247,7 +11250,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:10">
       <c r="A190" s="4">
         <v>188</v>
       </c>
@@ -11276,7 +11279,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:10">
       <c r="A191" s="4">
         <v>189</v>
       </c>
@@ -11305,7 +11308,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:10">
       <c r="A192" s="4">
         <v>190</v>
       </c>
@@ -11334,7 +11337,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:10">
       <c r="A193" s="4">
         <v>191</v>
       </c>
@@ -11363,7 +11366,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:10">
       <c r="A194" s="4">
         <v>192</v>
       </c>
@@ -11392,7 +11395,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:10">
       <c r="A195" s="4">
         <v>193</v>
       </c>
@@ -11421,7 +11424,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:10">
       <c r="A196" s="4">
         <v>194</v>
       </c>
@@ -11450,7 +11453,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:10">
       <c r="A197" s="4">
         <v>195</v>
       </c>
@@ -11479,7 +11482,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:10">
       <c r="A198" s="4">
         <v>196</v>
       </c>
@@ -11508,7 +11511,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:10">
       <c r="A199" s="4">
         <v>197</v>
       </c>
@@ -11537,7 +11540,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:10">
       <c r="A200" s="4">
         <v>198</v>
       </c>
@@ -11566,7 +11569,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:10">
       <c r="A201" s="4">
         <v>199</v>
       </c>
@@ -11595,7 +11598,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:10">
       <c r="A202" s="4">
         <v>200</v>
       </c>
@@ -11624,7 +11627,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:10">
       <c r="A203" s="4">
         <v>201</v>
       </c>
@@ -11653,7 +11656,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:10">
       <c r="A204" s="4">
         <v>202</v>
       </c>
@@ -11685,7 +11688,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:10">
       <c r="A205" s="4">
         <v>203</v>
       </c>
@@ -11717,7 +11720,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:10">
       <c r="A206" s="4">
         <v>204</v>
       </c>
@@ -11749,7 +11752,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:10">
       <c r="A207" s="4">
         <v>205</v>
       </c>
@@ -11781,7 +11784,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:10">
       <c r="A208" s="4">
         <v>206</v>
       </c>
@@ -11811,7 +11814,7 @@
       </c>
       <c r="J208" s="24"/>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:10">
       <c r="A209" s="4">
         <v>207</v>
       </c>
@@ -11843,7 +11846,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:10">
       <c r="A210" s="4">
         <v>208</v>
       </c>
@@ -11875,7 +11878,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:10">
       <c r="A211" s="4">
         <v>209</v>
       </c>
@@ -11907,7 +11910,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:10">
       <c r="A212" s="4">
         <v>210</v>
       </c>
@@ -11939,7 +11942,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:10">
       <c r="A213" s="4">
         <v>211</v>
       </c>
@@ -11971,7 +11974,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:10">
       <c r="A214" s="4">
         <v>212</v>
       </c>
@@ -12003,7 +12006,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:10">
       <c r="A215" s="4">
         <v>213</v>
       </c>
@@ -12035,7 +12038,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:10">
       <c r="A216" s="4">
         <v>214</v>
       </c>
@@ -12067,7 +12070,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:10">
       <c r="A217" s="4">
         <v>215</v>
       </c>
@@ -12099,7 +12102,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:10">
       <c r="A218" s="4">
         <v>216</v>
       </c>
@@ -12131,7 +12134,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:10">
       <c r="A219" s="4">
         <v>217</v>
       </c>
@@ -12163,7 +12166,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:10">
       <c r="A220" s="4">
         <v>218</v>
       </c>
@@ -12195,7 +12198,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:10">
       <c r="A221" s="4">
         <v>219</v>
       </c>
@@ -12227,7 +12230,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:10">
       <c r="A222" s="4">
         <v>220</v>
       </c>
@@ -12259,7 +12262,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:10">
       <c r="A223" s="4">
         <v>221</v>
       </c>
@@ -12291,7 +12294,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:10">
       <c r="A224" s="4">
         <v>222</v>
       </c>
@@ -12323,7 +12326,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:10">
       <c r="A225" s="4">
         <v>223</v>
       </c>
@@ -12355,7 +12358,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:10">
       <c r="A226" s="4">
         <v>224</v>
       </c>
@@ -12387,7 +12390,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:10">
       <c r="A227" s="4">
         <v>225</v>
       </c>
@@ -12419,7 +12422,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:10">
       <c r="A228" s="4">
         <v>226</v>
       </c>
@@ -12451,7 +12454,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:10">
       <c r="A229" s="4">
         <v>227</v>
       </c>
@@ -12483,7 +12486,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:10">
       <c r="A230" s="4">
         <v>228</v>
       </c>
@@ -12515,7 +12518,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:10">
       <c r="A231" s="4">
         <v>229</v>
       </c>
@@ -12547,7 +12550,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:10">
       <c r="A232" s="4">
         <v>230</v>
       </c>
@@ -12579,7 +12582,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:10">
       <c r="A233" s="4">
         <v>231</v>
       </c>
@@ -12611,7 +12614,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:10">
       <c r="A234" s="4">
         <v>232</v>
       </c>
@@ -12643,7 +12646,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:10">
       <c r="A235" s="4">
         <v>233</v>
       </c>
@@ -12675,7 +12678,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:10">
       <c r="A236" s="4">
         <v>234</v>
       </c>
@@ -12707,7 +12710,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:10">
       <c r="A237" s="4">
         <v>235</v>
       </c>
@@ -12739,7 +12742,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:10">
       <c r="A238" s="4">
         <v>236</v>
       </c>
@@ -12771,7 +12774,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:10">
       <c r="A239" s="4">
         <v>237</v>
       </c>
@@ -12803,7 +12806,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:10">
       <c r="A240" s="4">
         <v>238</v>
       </c>
@@ -12835,7 +12838,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:10">
       <c r="A241" s="4">
         <v>239</v>
       </c>
@@ -12867,7 +12870,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="242" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:10" ht="15.6">
       <c r="A242" s="4">
         <v>240</v>
       </c>
@@ -12899,7 +12902,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:10">
       <c r="A243" s="4">
         <v>241</v>
       </c>
@@ -12931,7 +12934,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:10">
       <c r="A244" s="4">
         <v>242</v>
       </c>
@@ -12963,7 +12966,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:10">
       <c r="A245" s="4">
         <v>243</v>
       </c>
@@ -12995,7 +12998,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:10">
       <c r="A246" s="4">
         <v>244</v>
       </c>
@@ -13027,7 +13030,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:10">
       <c r="A247" s="4">
         <v>245</v>
       </c>
@@ -13057,7 +13060,7 @@
       </c>
       <c r="J247" s="20"/>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:10">
       <c r="A248" s="4">
         <v>246</v>
       </c>
@@ -13089,7 +13092,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:10">
       <c r="A249" s="4">
         <v>247</v>
       </c>
@@ -13121,7 +13124,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:10">
       <c r="A250" s="4">
         <v>248</v>
       </c>
@@ -13153,7 +13156,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:10">
       <c r="A251" s="4">
         <v>249</v>
       </c>
@@ -13185,7 +13188,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:10">
       <c r="A252" s="4">
         <v>250</v>
       </c>
@@ -13217,7 +13220,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:10">
       <c r="A253" s="4">
         <v>251</v>
       </c>
@@ -13246,7 +13249,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:10">
       <c r="A254" s="4">
         <v>252</v>
       </c>
@@ -13278,7 +13281,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:10">
       <c r="A255" s="4">
         <v>253</v>
       </c>
@@ -13310,7 +13313,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:10">
       <c r="A256" s="4">
         <v>254</v>
       </c>
@@ -13342,7 +13345,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:10">
       <c r="A257" s="4">
         <v>255</v>
       </c>
@@ -13371,7 +13374,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:10">
       <c r="A258" s="4">
         <v>256</v>
       </c>
@@ -13403,7 +13406,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:10">
       <c r="A259" s="4">
         <v>257</v>
       </c>
@@ -13432,7 +13435,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:10">
       <c r="A260" s="4">
         <v>258</v>
       </c>
@@ -13461,7 +13464,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:10">
       <c r="A261" s="4">
         <v>259</v>
       </c>
@@ -13493,7 +13496,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:10">
       <c r="A262" s="4">
         <v>260</v>
       </c>
@@ -13525,7 +13528,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:10">
       <c r="A263" s="4">
         <v>261</v>
       </c>
@@ -13557,7 +13560,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:10">
       <c r="A264" s="4">
         <v>262</v>
       </c>
@@ -13589,7 +13592,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:10">
       <c r="A265" s="4">
         <v>263</v>
       </c>
@@ -13621,7 +13624,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:10">
       <c r="A266" s="4">
         <v>264</v>
       </c>
@@ -13653,7 +13656,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:10">
       <c r="A267" s="4">
         <v>265</v>
       </c>
@@ -13685,7 +13688,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:10">
       <c r="A268" s="4">
         <v>266</v>
       </c>
@@ -13717,7 +13720,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:10">
       <c r="A269" s="4">
         <v>267</v>
       </c>
@@ -13749,7 +13752,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:10">
       <c r="A270" s="4">
         <v>268</v>
       </c>
@@ -13781,7 +13784,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:10">
       <c r="A271" s="4">
         <v>269</v>
       </c>
@@ -13813,7 +13816,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:10">
       <c r="A272" s="4">
         <v>270</v>
       </c>
@@ -13845,7 +13848,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:10">
       <c r="A273" s="4">
         <v>271</v>
       </c>
@@ -13874,10 +13877,10 @@
         <v>574</v>
       </c>
       <c r="J273" s="3" t="s">
-        <v>1315</v>
-      </c>
-    </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="274" spans="1:10">
       <c r="A274" s="4">
         <v>272</v>
       </c>
@@ -13909,7 +13912,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:10">
       <c r="A275" s="4">
         <v>273</v>
       </c>
@@ -13926,7 +13929,7 @@
         <v>68</v>
       </c>
       <c r="F275" s="4" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="G275" s="4" t="s">
         <v>14</v>
@@ -13941,7 +13944,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:10">
       <c r="A276" s="4">
         <v>274</v>
       </c>
@@ -13973,7 +13976,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:10">
       <c r="A277" s="4">
         <v>275</v>
       </c>
@@ -14005,7 +14008,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:10">
       <c r="A278" s="4">
         <v>276</v>
       </c>
@@ -14037,7 +14040,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:10">
       <c r="A279" s="4">
         <v>277</v>
       </c>
@@ -14069,7 +14072,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:10">
       <c r="A280" s="4">
         <v>278</v>
       </c>
@@ -14101,7 +14104,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:10">
       <c r="A281" s="4">
         <v>279</v>
       </c>
@@ -14133,7 +14136,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:10">
       <c r="A282" s="4">
         <v>280</v>
       </c>
@@ -14165,7 +14168,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:10">
       <c r="A283" s="4">
         <v>281</v>
       </c>
@@ -14197,7 +14200,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:10">
       <c r="A284" s="4">
         <v>282</v>
       </c>
@@ -14229,7 +14232,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:10">
       <c r="A285" s="4">
         <v>283</v>
       </c>
@@ -14261,7 +14264,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:10">
       <c r="A286" s="4">
         <v>284</v>
       </c>
@@ -14293,7 +14296,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:10">
       <c r="A287" s="4">
         <v>285</v>
       </c>
@@ -14325,7 +14328,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:10">
       <c r="A288" s="4">
         <v>286</v>
       </c>
@@ -14357,7 +14360,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:10">
       <c r="A289" s="4">
         <v>287</v>
       </c>
@@ -14389,7 +14392,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:10">
       <c r="A290" s="4">
         <v>288</v>
       </c>
@@ -14421,7 +14424,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:10">
       <c r="A291" s="4">
         <v>289</v>
       </c>
@@ -14453,7 +14456,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:10">
       <c r="A292" s="4">
         <v>290</v>
       </c>
@@ -14485,7 +14488,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:10">
       <c r="A293" s="4">
         <v>291</v>
       </c>
@@ -14517,7 +14520,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:10">
       <c r="A294" s="4">
         <v>292</v>
       </c>
@@ -14549,7 +14552,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:10">
       <c r="A295" s="4">
         <v>293</v>
       </c>
@@ -14581,7 +14584,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:10">
       <c r="A296" s="4">
         <v>294</v>
       </c>
@@ -14613,7 +14616,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:10">
       <c r="A297" s="4">
         <v>295</v>
       </c>
@@ -14645,7 +14648,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:10">
       <c r="A298" s="4">
         <v>296</v>
       </c>
@@ -14677,7 +14680,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:10">
       <c r="A299" s="4">
         <v>297</v>
       </c>
@@ -14709,7 +14712,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:10">
       <c r="A300" s="4">
         <v>298</v>
       </c>
@@ -14741,7 +14744,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:10">
       <c r="A301" s="4">
         <v>299</v>
       </c>
@@ -14773,7 +14776,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:10">
       <c r="A302" s="4">
         <v>300</v>
       </c>
@@ -14805,7 +14808,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:10">
       <c r="A303" s="4">
         <v>301</v>
       </c>
@@ -14837,7 +14840,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="304" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:10">
       <c r="A304" s="4">
         <v>302</v>
       </c>
@@ -14869,7 +14872,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:10">
       <c r="A305" s="4">
         <v>303</v>
       </c>
@@ -14901,7 +14904,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:10">
       <c r="A306" s="4">
         <v>304</v>
       </c>
@@ -14933,7 +14936,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:10">
       <c r="A307" s="4">
         <v>305</v>
       </c>
@@ -14965,7 +14968,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:10">
       <c r="A308" s="4">
         <v>306</v>
       </c>
@@ -14997,7 +15000,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:10">
       <c r="A309" s="4">
         <v>307</v>
       </c>
@@ -15029,7 +15032,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:10">
       <c r="A310" s="4">
         <v>308</v>
       </c>
@@ -15061,7 +15064,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:10">
       <c r="A311" s="4">
         <v>309</v>
       </c>
@@ -15093,7 +15096,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:10">
       <c r="A312" s="4">
         <v>310</v>
       </c>
@@ -15125,7 +15128,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:10">
       <c r="A313" s="4">
         <v>311</v>
       </c>
@@ -15157,7 +15160,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:10">
       <c r="A314" s="4">
         <v>312</v>
       </c>
@@ -15189,7 +15192,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:10">
       <c r="A315" s="4">
         <v>313</v>
       </c>
@@ -15221,7 +15224,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:10">
       <c r="A316" s="4">
         <v>314</v>
       </c>
@@ -15253,7 +15256,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:10">
       <c r="A317" s="4">
         <v>315</v>
       </c>
@@ -15285,7 +15288,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:10">
       <c r="A318" s="4">
         <v>316</v>
       </c>
@@ -15317,7 +15320,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:10">
       <c r="A319" s="4">
         <v>317</v>
       </c>
@@ -15349,7 +15352,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:10">
       <c r="A320" s="4">
         <v>318</v>
       </c>
@@ -15381,7 +15384,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:10">
       <c r="A321" s="4">
         <v>319</v>
       </c>
@@ -15413,7 +15416,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:10">
       <c r="A322" s="4">
         <v>320</v>
       </c>
@@ -15445,7 +15448,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:10">
       <c r="A323" s="4">
         <v>321</v>
       </c>
@@ -15477,7 +15480,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:10">
       <c r="A324" s="4">
         <v>322</v>
       </c>
@@ -15509,7 +15512,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:10">
       <c r="A325" s="4">
         <v>323</v>
       </c>
@@ -15541,7 +15544,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:10">
       <c r="A326" s="4">
         <v>324</v>
       </c>
@@ -15573,7 +15576,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:10">
       <c r="A327" s="4">
         <v>325</v>
       </c>
@@ -15605,7 +15608,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:10">
       <c r="A328" s="4">
         <v>326</v>
       </c>
@@ -15637,7 +15640,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:10">
       <c r="A329" s="4">
         <v>327</v>
       </c>
@@ -15669,7 +15672,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:10">
       <c r="A330" s="4">
         <v>328</v>
       </c>
@@ -15701,7 +15704,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:10">
       <c r="A331" s="4">
         <v>329</v>
       </c>
@@ -15733,7 +15736,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:10">
       <c r="A332" s="4">
         <v>330</v>
       </c>
@@ -15765,7 +15768,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:10">
       <c r="A333" s="4">
         <v>331</v>
       </c>
@@ -15797,7 +15800,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:10">
       <c r="A334" s="4">
         <v>332</v>
       </c>
@@ -15829,7 +15832,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:10">
       <c r="A335" s="4">
         <v>333</v>
       </c>
@@ -15861,7 +15864,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="336" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:10">
       <c r="A336" s="4">
         <v>334</v>
       </c>
@@ -15893,7 +15896,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="337" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:10">
       <c r="A337" s="4">
         <v>335</v>
       </c>
@@ -15925,7 +15928,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="338" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:10">
       <c r="A338" s="4">
         <v>336</v>
       </c>
@@ -15954,10 +15957,10 @@
         <v>574</v>
       </c>
       <c r="J338" s="3" t="s">
-        <v>1310</v>
-      </c>
-    </row>
-    <row r="339" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="339" spans="1:10">
       <c r="A339" s="4">
         <v>337</v>
       </c>
@@ -15989,7 +15992,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="340" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:10">
       <c r="A340" s="4">
         <v>338</v>
       </c>
@@ -16021,7 +16024,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="341" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:10">
       <c r="A341" s="4">
         <v>339</v>
       </c>
@@ -16053,7 +16056,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="342" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:10">
       <c r="A342" s="4">
         <v>340</v>
       </c>
@@ -16085,7 +16088,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="343" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:10">
       <c r="A343" s="4">
         <v>341</v>
       </c>
@@ -16117,7 +16120,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="344" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:10">
       <c r="A344" s="4">
         <v>342</v>
       </c>
@@ -16149,7 +16152,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="345" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:10">
       <c r="A345" s="4">
         <v>343</v>
       </c>
@@ -16181,7 +16184,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="346" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:10">
       <c r="A346" s="4">
         <v>344</v>
       </c>
@@ -16213,7 +16216,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="347" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:10">
       <c r="A347" s="4">
         <v>345</v>
       </c>
@@ -16245,7 +16248,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="348" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:10">
       <c r="A348" s="4">
         <v>346</v>
       </c>
@@ -16277,7 +16280,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="349" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:10">
       <c r="A349" s="4">
         <v>347</v>
       </c>
@@ -16309,7 +16312,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="350" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:10">
       <c r="A350" s="4">
         <v>348</v>
       </c>
@@ -16341,7 +16344,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="351" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:10">
       <c r="A351" s="4">
         <v>349</v>
       </c>
@@ -16373,7 +16376,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="352" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:10">
       <c r="A352" s="4">
         <v>350</v>
       </c>
@@ -16405,7 +16408,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="353" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:10">
       <c r="A353" s="4">
         <v>351</v>
       </c>
@@ -16437,7 +16440,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="354" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:10">
       <c r="A354" s="4">
         <v>352</v>
       </c>
@@ -16469,7 +16472,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="355" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:10">
       <c r="A355" s="4">
         <v>353</v>
       </c>
@@ -16501,7 +16504,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="356" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:10">
       <c r="A356" s="4">
         <v>354</v>
       </c>
@@ -16533,7 +16536,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="357" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:10">
       <c r="A357" s="4">
         <v>355</v>
       </c>
@@ -16565,7 +16568,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="358" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:10">
       <c r="A358" s="4">
         <v>356</v>
       </c>
@@ -16597,7 +16600,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="359" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:10">
       <c r="A359" s="4">
         <v>357</v>
       </c>
@@ -16629,7 +16632,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:10">
       <c r="A360" s="4">
         <v>358</v>
       </c>
@@ -16661,7 +16664,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="361" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:10">
       <c r="A361" s="4">
         <v>359</v>
       </c>
@@ -16693,7 +16696,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="362" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:10">
       <c r="A362" s="4">
         <v>360</v>
       </c>
@@ -16725,7 +16728,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="363" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:10">
       <c r="A363" s="4">
         <v>361</v>
       </c>
@@ -16757,7 +16760,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="364" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:10">
       <c r="A364" s="4">
         <v>362</v>
       </c>
@@ -16789,7 +16792,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="365" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:10">
       <c r="A365" s="4">
         <v>363</v>
       </c>
@@ -16821,7 +16824,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="366" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:10">
       <c r="A366" s="4">
         <v>364</v>
       </c>
@@ -16850,10 +16853,10 @@
         <v>574</v>
       </c>
       <c r="J366" s="3" t="s">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="367" spans="1:10">
       <c r="A367" s="4">
         <v>365</v>
       </c>
@@ -16885,7 +16888,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="368" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:10">
       <c r="A368" s="4">
         <v>366</v>
       </c>
@@ -16917,7 +16920,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="369" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:10">
       <c r="A369" s="4">
         <v>367</v>
       </c>
@@ -16949,7 +16952,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="370" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:10">
       <c r="A370" s="4">
         <v>368</v>
       </c>
@@ -16981,7 +16984,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="371" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:10">
       <c r="A371" s="4">
         <v>369</v>
       </c>
@@ -17013,7 +17016,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="372" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:10">
       <c r="A372" s="4">
         <v>370</v>
       </c>
@@ -17045,7 +17048,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="373" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:10">
       <c r="A373" s="4">
         <v>371</v>
       </c>
@@ -17077,7 +17080,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="374" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:10">
       <c r="A374" s="4">
         <v>372</v>
       </c>
@@ -17109,7 +17112,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="375" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:10">
       <c r="A375" s="4">
         <v>373</v>
       </c>
@@ -17141,7 +17144,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="376" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:10">
       <c r="A376" s="4">
         <v>374</v>
       </c>
@@ -17173,7 +17176,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="377" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:10">
       <c r="A377" s="4">
         <v>375</v>
       </c>
@@ -17205,7 +17208,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="378" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:10">
       <c r="A378" s="4">
         <v>376</v>
       </c>
@@ -17237,7 +17240,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="379" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:10">
       <c r="A379" s="4">
         <v>377</v>
       </c>
@@ -17269,7 +17272,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="380" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:10">
       <c r="A380" s="4">
         <v>378</v>
       </c>
@@ -17301,7 +17304,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="381" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:10">
       <c r="A381" s="4">
         <v>379</v>
       </c>
@@ -17333,7 +17336,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="382" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:10">
       <c r="A382" s="4">
         <v>380</v>
       </c>
@@ -17365,7 +17368,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="383" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:10">
       <c r="A383" s="4">
         <v>381</v>
       </c>
@@ -17397,7 +17400,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="384" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:10">
       <c r="A384" s="4">
         <v>382</v>
       </c>
@@ -17429,7 +17432,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="385" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:10">
       <c r="A385" s="4">
         <v>383</v>
       </c>
@@ -17461,7 +17464,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="386" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:10">
       <c r="A386" s="4">
         <v>384</v>
       </c>
@@ -17493,7 +17496,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="387" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:10">
       <c r="A387" s="4">
         <v>385</v>
       </c>
@@ -17525,7 +17528,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="388" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:10">
       <c r="A388" s="4">
         <v>386</v>
       </c>
@@ -17557,7 +17560,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="389" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:10">
       <c r="A389" s="4">
         <v>387</v>
       </c>
@@ -17589,7 +17592,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="390" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:10">
       <c r="A390" s="4">
         <v>388</v>
       </c>
@@ -17621,7 +17624,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="391" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:10">
       <c r="A391" s="4">
         <v>389</v>
       </c>
@@ -17653,7 +17656,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="392" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:10">
       <c r="A392" s="4">
         <v>390</v>
       </c>
@@ -17685,7 +17688,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="393" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:10">
       <c r="A393" s="4">
         <v>391</v>
       </c>
@@ -17717,7 +17720,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="394" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:10">
       <c r="A394" s="4">
         <v>392</v>
       </c>
@@ -17749,7 +17752,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="395" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:10">
       <c r="A395" s="4">
         <v>393</v>
       </c>
@@ -17781,7 +17784,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="396" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:10">
       <c r="A396" s="4">
         <v>394</v>
       </c>
@@ -17798,7 +17801,7 @@
         <v>76</v>
       </c>
       <c r="F396" s="1" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="G396" s="1" t="s">
         <v>14</v>
@@ -17810,10 +17813,10 @@
         <v>574</v>
       </c>
       <c r="J396" s="3" t="s">
-        <v>1299</v>
-      </c>
-    </row>
-    <row r="397" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="397" spans="1:10">
       <c r="A397" s="4">
         <v>395</v>
       </c>
@@ -17845,7 +17848,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="398" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:10">
       <c r="A398" s="4">
         <v>396</v>
       </c>
@@ -17877,7 +17880,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="399" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:10">
       <c r="A399" s="4">
         <v>397</v>
       </c>
@@ -17909,7 +17912,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="400" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:10">
       <c r="A400" s="4">
         <v>398</v>
       </c>
@@ -17941,7 +17944,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="401" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:10">
       <c r="A401" s="4">
         <v>399</v>
       </c>
@@ -17973,7 +17976,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="402" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:10">
       <c r="A402" s="4">
         <v>400</v>
       </c>
@@ -18005,7 +18008,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="403" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:10">
       <c r="A403" s="4">
         <v>401</v>
       </c>
@@ -18037,7 +18040,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="404" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:10">
       <c r="A404" s="4">
         <v>402</v>
       </c>
@@ -18069,7 +18072,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="405" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:10">
       <c r="A405" s="4">
         <v>403</v>
       </c>
@@ -18101,7 +18104,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="406" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:10">
       <c r="A406" s="4">
         <v>404</v>
       </c>
@@ -18133,7 +18136,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="407" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:10">
       <c r="A407" s="4">
         <v>405</v>
       </c>
@@ -18165,7 +18168,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="408" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:10">
       <c r="A408" s="4">
         <v>406</v>
       </c>
@@ -18197,7 +18200,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="409" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:10">
       <c r="A409" s="4">
         <v>407</v>
       </c>
@@ -18229,7 +18232,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="410" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:10">
       <c r="A410" s="4">
         <v>408</v>
       </c>
@@ -18261,7 +18264,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="411" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:10">
       <c r="A411" s="4">
         <v>409</v>
       </c>
@@ -18293,7 +18296,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="412" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:10">
       <c r="A412" s="4">
         <v>410</v>
       </c>
@@ -18325,7 +18328,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="413" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:10">
       <c r="A413" s="4">
         <v>411</v>
       </c>
@@ -18357,7 +18360,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="414" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:10">
       <c r="A414" s="4">
         <v>412</v>
       </c>
@@ -18389,7 +18392,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="415" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:10">
       <c r="A415" s="4">
         <v>413</v>
       </c>
@@ -18421,7 +18424,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="416" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:10">
       <c r="A416" s="4">
         <v>414</v>
       </c>
@@ -18453,7 +18456,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="417" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:10">
       <c r="A417" s="4">
         <v>415</v>
       </c>
@@ -18485,7 +18488,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="418" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:10">
       <c r="A418" s="4">
         <v>416</v>
       </c>
@@ -18517,7 +18520,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="419" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:10">
       <c r="A419" s="4">
         <v>417</v>
       </c>
@@ -18549,7 +18552,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="420" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:10">
       <c r="A420" s="4">
         <v>418</v>
       </c>
@@ -18581,7 +18584,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="421" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:10">
       <c r="A421" s="4">
         <v>419</v>
       </c>
@@ -18613,7 +18616,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="422" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:10">
       <c r="A422" s="4">
         <v>420</v>
       </c>
@@ -18645,7 +18648,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="423" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:10">
       <c r="A423" s="4">
         <v>421</v>
       </c>
@@ -18677,7 +18680,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="424" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:10">
       <c r="A424" s="4">
         <v>422</v>
       </c>
@@ -18709,7 +18712,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="425" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:10">
       <c r="A425" s="4">
         <v>423</v>
       </c>
@@ -18741,7 +18744,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="426" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:10">
       <c r="A426" s="4">
         <v>424</v>
       </c>
@@ -18773,7 +18776,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="427" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:10">
       <c r="A427" s="4">
         <v>425</v>
       </c>
@@ -18805,7 +18808,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="428" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:10">
       <c r="A428" s="4">
         <v>426</v>
       </c>
@@ -18837,7 +18840,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="429" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:10">
       <c r="A429" s="4">
         <v>427</v>
       </c>
@@ -18869,7 +18872,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="430" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:10">
       <c r="A430" s="4">
         <v>428</v>
       </c>
@@ -18901,7 +18904,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="431" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:10">
       <c r="A431" s="4">
         <v>429</v>
       </c>
@@ -18933,7 +18936,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="432" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:10">
       <c r="A432" s="4">
         <v>430</v>
       </c>
@@ -18965,7 +18968,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="433" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:10">
       <c r="A433" s="4">
         <v>431</v>
       </c>
@@ -18997,7 +19000,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="434" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:10">
       <c r="A434" s="4">
         <v>432</v>
       </c>
@@ -19029,7 +19032,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="435" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:10">
       <c r="A435" s="4">
         <v>433</v>
       </c>
@@ -19059,7 +19062,7 @@
       </c>
       <c r="J435" s="24"/>
     </row>
-    <row r="436" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:10">
       <c r="A436" s="4">
         <v>434</v>
       </c>
@@ -19091,7 +19094,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="437" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:10">
       <c r="A437" s="4">
         <v>435</v>
       </c>
@@ -19123,7 +19126,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="438" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:10">
       <c r="A438" s="4">
         <v>436</v>
       </c>
@@ -19155,7 +19158,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="439" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:10">
       <c r="A439" s="4">
         <v>437</v>
       </c>
@@ -19187,7 +19190,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="440" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:10">
       <c r="A440" s="4">
         <v>438</v>
       </c>
@@ -19219,7 +19222,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="441" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:10">
       <c r="A441" s="4">
         <v>439</v>
       </c>
@@ -19251,7 +19254,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="442" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:10">
       <c r="A442" s="4">
         <v>440</v>
       </c>
@@ -19283,7 +19286,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="443" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:10">
       <c r="A443" s="4">
         <v>441</v>
       </c>
@@ -19315,7 +19318,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="444" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:10">
       <c r="A444" s="4">
         <v>442</v>
       </c>
@@ -19347,7 +19350,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="445" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:10">
       <c r="A445" s="4">
         <v>443</v>
       </c>
@@ -19379,7 +19382,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="446" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:10">
       <c r="A446" s="4">
         <v>444</v>
       </c>
@@ -19411,7 +19414,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="447" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:10">
       <c r="A447" s="4">
         <v>445</v>
       </c>
@@ -19443,7 +19446,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="448" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:10">
       <c r="A448" s="4">
         <v>446</v>
       </c>
@@ -19475,7 +19478,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="449" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:10">
       <c r="A449" s="4">
         <v>447</v>
       </c>
@@ -19505,7 +19508,7 @@
       </c>
       <c r="J449" s="24"/>
     </row>
-    <row r="450" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:10">
       <c r="A450" s="4">
         <v>448</v>
       </c>
@@ -19535,7 +19538,7 @@
       </c>
       <c r="J450" s="24"/>
     </row>
-    <row r="451" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:10">
       <c r="A451" s="4">
         <v>449</v>
       </c>
@@ -19552,7 +19555,7 @@
         <v>957</v>
       </c>
       <c r="F451" s="1" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="G451" s="1" t="s">
         <v>30</v>
@@ -19564,10 +19567,10 @@
         <v>574</v>
       </c>
       <c r="J451" s="3" t="s">
-        <v>1297</v>
-      </c>
-    </row>
-    <row r="452" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="452" spans="1:10">
       <c r="A452" s="4">
         <v>450</v>
       </c>
@@ -19597,7 +19600,7 @@
       </c>
       <c r="J452" s="24"/>
     </row>
-    <row r="453" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:10">
       <c r="A453" s="4">
         <v>451</v>
       </c>
@@ -19627,7 +19630,7 @@
       </c>
       <c r="J453" s="24"/>
     </row>
-    <row r="454" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:10">
       <c r="A454" s="4">
         <v>452</v>
       </c>
@@ -19657,7 +19660,7 @@
       </c>
       <c r="J454" s="24"/>
     </row>
-    <row r="455" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:10">
       <c r="A455" s="4">
         <v>453</v>
       </c>
@@ -19687,7 +19690,7 @@
       </c>
       <c r="J455" s="24"/>
     </row>
-    <row r="456" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:10">
       <c r="A456" s="4">
         <v>454</v>
       </c>
@@ -19717,7 +19720,7 @@
       </c>
       <c r="J456" s="24"/>
     </row>
-    <row r="457" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:10">
       <c r="A457" s="4">
         <v>455</v>
       </c>
@@ -19747,7 +19750,7 @@
       </c>
       <c r="J457" s="24"/>
     </row>
-    <row r="458" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:10">
       <c r="A458" s="4">
         <v>456</v>
       </c>
@@ -19777,7 +19780,7 @@
       </c>
       <c r="J458" s="24"/>
     </row>
-    <row r="459" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:10">
       <c r="A459" s="4">
         <v>457</v>
       </c>
@@ -19807,7 +19810,7 @@
       </c>
       <c r="J459" s="24"/>
     </row>
-    <row r="460" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:10">
       <c r="A460" s="4">
         <v>458</v>
       </c>
@@ -19837,7 +19840,7 @@
       </c>
       <c r="J460" s="24"/>
     </row>
-    <row r="461" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:10">
       <c r="A461" s="4">
         <v>459</v>
       </c>
@@ -19869,7 +19872,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="462" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:10">
       <c r="A462" s="4">
         <v>460</v>
       </c>
@@ -19899,7 +19902,7 @@
       </c>
       <c r="J462" s="24"/>
     </row>
-    <row r="463" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:10">
       <c r="A463" s="4">
         <v>461</v>
       </c>
@@ -19929,7 +19932,7 @@
       </c>
       <c r="J463" s="24"/>
     </row>
-    <row r="464" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:10">
       <c r="A464" s="4">
         <v>462</v>
       </c>
@@ -19959,7 +19962,7 @@
       </c>
       <c r="J464" s="24"/>
     </row>
-    <row r="465" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:10">
       <c r="A465" s="4">
         <v>463</v>
       </c>
@@ -19989,7 +19992,7 @@
       </c>
       <c r="J465" s="24"/>
     </row>
-    <row r="466" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:10">
       <c r="A466" s="4">
         <v>464</v>
       </c>
@@ -20019,7 +20022,7 @@
       </c>
       <c r="J466" s="24"/>
     </row>
-    <row r="467" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:10">
       <c r="A467" s="4">
         <v>465</v>
       </c>
@@ -20049,7 +20052,7 @@
       </c>
       <c r="J467" s="24"/>
     </row>
-    <row r="468" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:10">
       <c r="A468" s="4">
         <v>466</v>
       </c>
@@ -20079,7 +20082,7 @@
       </c>
       <c r="J468" s="24"/>
     </row>
-    <row r="469" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:10">
       <c r="A469" s="4">
         <v>467</v>
       </c>
@@ -20109,7 +20112,7 @@
       </c>
       <c r="J469" s="24"/>
     </row>
-    <row r="470" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:10">
       <c r="A470" s="4">
         <v>468</v>
       </c>
@@ -20139,7 +20142,7 @@
       </c>
       <c r="J470" s="24"/>
     </row>
-    <row r="471" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:10">
       <c r="A471" s="4">
         <v>469</v>
       </c>
@@ -20169,7 +20172,7 @@
       </c>
       <c r="J471" s="24"/>
     </row>
-    <row r="472" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:10">
       <c r="A472" s="4">
         <v>470</v>
       </c>
@@ -20199,7 +20202,7 @@
       </c>
       <c r="J472" s="24"/>
     </row>
-    <row r="473" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:10">
       <c r="A473" s="4">
         <v>471</v>
       </c>
@@ -20229,7 +20232,7 @@
       </c>
       <c r="J473" s="24"/>
     </row>
-    <row r="474" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:10">
       <c r="A474" s="4">
         <v>472</v>
       </c>
@@ -20259,7 +20262,7 @@
       </c>
       <c r="J474" s="24"/>
     </row>
-    <row r="475" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:10">
       <c r="A475" s="4">
         <v>473</v>
       </c>
@@ -20289,7 +20292,7 @@
       </c>
       <c r="J475" s="24"/>
     </row>
-    <row r="476" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:10">
       <c r="A476" s="4">
         <v>474</v>
       </c>
@@ -20319,7 +20322,7 @@
       </c>
       <c r="J476" s="24"/>
     </row>
-    <row r="477" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:10">
       <c r="A477" s="4">
         <v>475</v>
       </c>
@@ -20349,7 +20352,7 @@
       </c>
       <c r="J477" s="24"/>
     </row>
-    <row r="478" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:10">
       <c r="A478" s="4">
         <v>476</v>
       </c>
@@ -20379,7 +20382,7 @@
       </c>
       <c r="J478" s="24"/>
     </row>
-    <row r="479" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:10">
       <c r="A479" s="4">
         <v>477</v>
       </c>
@@ -20409,7 +20412,7 @@
       </c>
       <c r="J479" s="24"/>
     </row>
-    <row r="480" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:10">
       <c r="A480" s="4">
         <v>478</v>
       </c>
@@ -20439,7 +20442,7 @@
       </c>
       <c r="J480" s="24"/>
     </row>
-    <row r="481" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:10">
       <c r="A481" s="4">
         <v>479</v>
       </c>
@@ -20469,7 +20472,7 @@
       </c>
       <c r="J481" s="24"/>
     </row>
-    <row r="482" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:10">
       <c r="A482" s="4">
         <v>480</v>
       </c>
@@ -20499,7 +20502,7 @@
       </c>
       <c r="J482" s="24"/>
     </row>
-    <row r="483" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:10">
       <c r="A483" s="4">
         <v>481</v>
       </c>
@@ -20529,7 +20532,7 @@
       </c>
       <c r="J483" s="24"/>
     </row>
-    <row r="484" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:10">
       <c r="A484" s="4">
         <v>482</v>
       </c>
@@ -20559,7 +20562,7 @@
       </c>
       <c r="J484" s="24"/>
     </row>
-    <row r="485" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:10">
       <c r="A485" s="4">
         <v>483</v>
       </c>
@@ -20589,7 +20592,7 @@
       </c>
       <c r="J485" s="24"/>
     </row>
-    <row r="486" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:10">
       <c r="A486" s="4">
         <v>484</v>
       </c>
@@ -20619,7 +20622,7 @@
       </c>
       <c r="J486" s="24"/>
     </row>
-    <row r="487" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:10">
       <c r="A487" s="4">
         <v>485</v>
       </c>
@@ -20649,7 +20652,7 @@
       </c>
       <c r="J487" s="24"/>
     </row>
-    <row r="488" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:10">
       <c r="A488" s="4">
         <v>486</v>
       </c>
@@ -20678,10 +20681,10 @@
         <v>574</v>
       </c>
       <c r="J488" s="3" t="s">
-        <v>1314</v>
-      </c>
-    </row>
-    <row r="489" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="489" spans="1:10">
       <c r="A489" s="4">
         <v>487</v>
       </c>
@@ -20711,7 +20714,7 @@
       </c>
       <c r="J489" s="24"/>
     </row>
-    <row r="490" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:10">
       <c r="A490" s="4">
         <v>488</v>
       </c>
@@ -20741,7 +20744,7 @@
       </c>
       <c r="J490" s="24"/>
     </row>
-    <row r="491" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:10">
       <c r="A491" s="4">
         <v>489</v>
       </c>
@@ -20771,7 +20774,7 @@
       </c>
       <c r="J491" s="24"/>
     </row>
-    <row r="492" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:10">
       <c r="A492" s="4">
         <v>490</v>
       </c>
@@ -20801,7 +20804,7 @@
       </c>
       <c r="J492" s="24"/>
     </row>
-    <row r="493" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:10">
       <c r="A493" s="4">
         <v>491</v>
       </c>
@@ -20831,7 +20834,7 @@
       </c>
       <c r="J493" s="24"/>
     </row>
-    <row r="494" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:10">
       <c r="A494" s="4">
         <v>492</v>
       </c>
@@ -20861,7 +20864,7 @@
       </c>
       <c r="J494" s="24"/>
     </row>
-    <row r="495" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:10">
       <c r="A495" s="4">
         <v>493</v>
       </c>
@@ -20891,7 +20894,7 @@
       </c>
       <c r="J495" s="24"/>
     </row>
-    <row r="496" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:10">
       <c r="A496" s="4">
         <v>494</v>
       </c>
@@ -20921,7 +20924,7 @@
       </c>
       <c r="J496" s="24"/>
     </row>
-    <row r="497" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:10">
       <c r="A497" s="4">
         <v>495</v>
       </c>
@@ -20951,7 +20954,7 @@
       </c>
       <c r="J497" s="24"/>
     </row>
-    <row r="498" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:10">
       <c r="A498" s="4">
         <v>496</v>
       </c>
@@ -20981,7 +20984,7 @@
       </c>
       <c r="J498" s="24"/>
     </row>
-    <row r="499" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:10">
       <c r="A499" s="4">
         <v>497</v>
       </c>
@@ -21087,7 +21090,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6771508-02DF-4FAC-B7A7-A6278CE7AE5B}">
   <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
@@ -21096,7 +21099,7 @@
     <col min="6" max="6" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>516</v>
       </c>
@@ -21116,7 +21119,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6">
       <c r="A2" s="42" t="s">
         <v>869</v>
       </c>
@@ -21136,7 +21139,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6">
       <c r="A3" s="42" t="s">
         <v>869</v>
       </c>
@@ -21156,7 +21159,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6">
       <c r="A4" s="42" t="s">
         <v>869</v>
       </c>
@@ -21176,7 +21179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6">
       <c r="A5" s="42" t="s">
         <v>869</v>
       </c>
@@ -21196,7 +21199,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6">
       <c r="A6" s="42" t="s">
         <v>869</v>
       </c>
@@ -21216,7 +21219,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6">
       <c r="A7" s="42" t="s">
         <v>869</v>
       </c>
@@ -21236,7 +21239,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>521</v>
       </c>
@@ -21253,7 +21256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>521</v>
       </c>
@@ -21270,7 +21273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>521</v>
       </c>
@@ -21287,7 +21290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>521</v>
       </c>
@@ -21304,7 +21307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>521</v>
       </c>
@@ -21321,7 +21324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>521</v>
       </c>
@@ -21338,7 +21341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>521</v>
       </c>
@@ -21355,7 +21358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>521</v>
       </c>
@@ -21372,7 +21375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>521</v>
       </c>
@@ -21389,7 +21392,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>521</v>
       </c>
@@ -21406,7 +21409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>521</v>
       </c>
@@ -21423,7 +21426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>521</v>
       </c>
@@ -21440,7 +21443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>521</v>
       </c>
@@ -21457,7 +21460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>526</v>
       </c>
@@ -21477,7 +21480,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
         <v>526</v>
       </c>
@@ -21497,7 +21500,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
         <v>526</v>
       </c>
@@ -21517,7 +21520,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
         <v>526</v>
       </c>
@@ -21537,7 +21540,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
         <v>526</v>
       </c>
@@ -21557,7 +21560,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
         <v>526</v>
       </c>
@@ -21577,7 +21580,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
         <v>526</v>
       </c>
@@ -21597,7 +21600,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
         <v>539</v>
       </c>
@@ -21617,7 +21620,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
         <v>543</v>
       </c>
@@ -21637,7 +21640,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
         <v>545</v>
       </c>
@@ -21657,7 +21660,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6">
       <c r="A31" t="s">
         <v>545</v>
       </c>
@@ -21677,7 +21680,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
         <v>539</v>
       </c>
@@ -21709,7 +21712,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD4931DD-77FA-4EF6-BAB3-744C5E5D53EC}">
   <dimension ref="A1:XFC75"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.88671875" bestFit="1" customWidth="1"/>
@@ -21726,7 +21729,7 @@
     <col min="16384" max="16384" width="16.21875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -21758,7 +21761,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -21790,7 +21793,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -21822,7 +21825,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -21854,7 +21857,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -21886,7 +21889,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -21918,7 +21921,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -21950,7 +21953,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -21982,7 +21985,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -22014,7 +22017,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -22046,7 +22049,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -22078,7 +22081,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -22110,7 +22113,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -22142,7 +22145,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -22174,7 +22177,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -22206,7 +22209,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -22238,7 +22241,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -22270,7 +22273,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -22302,7 +22305,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -22334,7 +22337,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -22366,7 +22369,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -22398,7 +22401,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -22430,7 +22433,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -22462,7 +22465,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -22494,7 +22497,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -22524,7 +22527,7 @@
       </c>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -22554,7 +22557,7 @@
       </c>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -22584,7 +22587,7 @@
       </c>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10">
       <c r="A28" s="4">
         <v>27</v>
       </c>
@@ -22614,7 +22617,7 @@
       </c>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -22644,7 +22647,7 @@
       </c>
       <c r="J29" s="3"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10">
       <c r="A30" s="4">
         <v>29</v>
       </c>
@@ -22674,7 +22677,7 @@
       </c>
       <c r="J30" s="3"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -22704,7 +22707,7 @@
       </c>
       <c r="J31" s="3"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10">
       <c r="A32" s="4">
         <v>31</v>
       </c>
@@ -22734,7 +22737,7 @@
       </c>
       <c r="J32" s="3"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -22764,7 +22767,7 @@
       </c>
       <c r="J33" s="3"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10">
       <c r="A34" s="4">
         <v>33</v>
       </c>
@@ -22794,7 +22797,7 @@
       </c>
       <c r="J34" s="3"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10">
       <c r="A35" s="4">
         <v>34</v>
       </c>
@@ -22824,7 +22827,7 @@
       </c>
       <c r="J35" s="3"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -22854,7 +22857,7 @@
       </c>
       <c r="J36" s="3"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -22884,7 +22887,7 @@
       </c>
       <c r="J37" s="3"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10">
       <c r="A38" s="4">
         <v>37</v>
       </c>
@@ -22914,7 +22917,7 @@
       </c>
       <c r="J38" s="3"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -22944,7 +22947,7 @@
       </c>
       <c r="J39" s="3"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10">
       <c r="A40" s="4">
         <v>39</v>
       </c>
@@ -22974,7 +22977,7 @@
       </c>
       <c r="J40" s="3"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -23004,7 +23007,7 @@
       </c>
       <c r="J41" s="3"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10">
       <c r="A42" s="4">
         <v>41</v>
       </c>
@@ -23033,7 +23036,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -23065,7 +23068,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10">
       <c r="A44" s="33">
         <v>43</v>
       </c>
@@ -23097,7 +23100,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10">
       <c r="A45" s="18">
         <v>44</v>
       </c>
@@ -23126,7 +23129,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10">
       <c r="A46" s="18">
         <v>45</v>
       </c>
@@ -23155,7 +23158,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10">
       <c r="A47" s="18">
         <v>46</v>
       </c>
@@ -23184,7 +23187,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10">
       <c r="A48" s="18">
         <v>47</v>
       </c>
@@ -23213,7 +23216,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10">
       <c r="A49" s="18">
         <v>48</v>
       </c>
@@ -23242,7 +23245,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10">
       <c r="A50" s="18">
         <v>49</v>
       </c>
@@ -23274,7 +23277,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10">
       <c r="A51" s="18">
         <v>50</v>
       </c>
@@ -23306,7 +23309,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="52" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" s="3" customFormat="1">
       <c r="A52" s="4">
         <v>51</v>
       </c>
@@ -23338,7 +23341,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="53" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" s="3" customFormat="1">
       <c r="A53" s="4">
         <v>52</v>
       </c>
@@ -23370,102 +23373,102 @@
         <v>689</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10">
       <c r="A54" s="18"/>
       <c r="B54" s="21"/>
       <c r="C54" s="49"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10">
       <c r="A55" s="18"/>
       <c r="B55" s="21"/>
       <c r="C55" s="49"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10">
       <c r="B56" s="21"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10">
       <c r="B57" s="21"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10">
       <c r="A58" s="18"/>
       <c r="B58" s="22"/>
       <c r="C58" s="49"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10">
       <c r="A59" s="18"/>
       <c r="B59" s="22"/>
       <c r="C59" s="49"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10">
       <c r="A60" s="18"/>
       <c r="B60" s="22"/>
       <c r="C60" s="49"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10">
       <c r="A61" s="18"/>
       <c r="B61" s="22"/>
       <c r="C61" s="49"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10">
       <c r="A62" s="18"/>
       <c r="B62" s="22"/>
       <c r="C62" s="49"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10">
       <c r="A63" s="18"/>
       <c r="B63" s="22"/>
       <c r="C63" s="49"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10">
       <c r="A64" s="18"/>
       <c r="B64" s="22"/>
       <c r="C64" s="49"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3">
       <c r="A65" s="18"/>
       <c r="B65" s="22"/>
       <c r="C65" s="49"/>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3">
       <c r="A66" s="18"/>
       <c r="B66" s="22"/>
       <c r="C66" s="49"/>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3">
       <c r="A67" s="18"/>
       <c r="B67" s="22"/>
       <c r="C67" s="49"/>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3">
       <c r="A68" s="18"/>
       <c r="B68" s="22"/>
       <c r="C68" s="49"/>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3">
       <c r="A69" s="18"/>
       <c r="B69" s="22"/>
       <c r="C69" s="49"/>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3">
       <c r="A70" s="18"/>
       <c r="B70" s="22"/>
       <c r="C70" s="49"/>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3">
       <c r="A71" s="18"/>
       <c r="B71" s="22"/>
       <c r="C71" s="49"/>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3">
       <c r="B72" s="21"/>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3">
       <c r="B73" s="21"/>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3">
       <c r="B74" s="21"/>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3">
       <c r="B75" s="21"/>
     </row>
   </sheetData>

--- a/data_printer.xlsx
+++ b/data_printer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erick\Desktop\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DB5A489-6681-4088-A890-43763C6D5A9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBB567A0-35B9-4349-B86C-53FDB7C19E2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A8AA41B5-7AA1-4FF7-A9B8-54B8A4E1AF28}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4377" uniqueCount="1322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4377" uniqueCount="1321">
   <si>
     <t>INDICE</t>
   </si>
@@ -2785,9 +2785,6 @@
     <t>ESTAVA NO COMITE NO CENTRO DE ARARUAMA - PROBLEMA NÃO PUXA PAPEL; RETIRADA PAÇO DIVIDA ATIVA 18/11/2025;</t>
   </si>
   <si>
-    <t>ESTAVA NA SEPOL; COLOCADA SEDUC RH NO DIA 11/07/2025  FOI TROCADO CILINDRO; RETIRADA DA SEDUC RH POR PROBLEMAS DE REDE DA IMPRESSORA 01/08/2025; INSTALADA BELLA CASA CABO FRIO 17/09/2025; INSTALADA DIVIDA ATIVA PAÇO 18/11/2025;</t>
-  </si>
-  <si>
     <t>IMPRESSORA RETIRADA DA ESCOLA AFRANIO VALLADARES EM 02/10/2024 - PROBLEMA DE ATOLAMENTO E FUSÃO COM PROBLEMA; INSTALADA ESCOLA DARCY RIBEIRO 19/11/2025;</t>
   </si>
   <si>
@@ -3658,9 +3655,6 @@
     <t>ESTAVA PAÇO DEHU RETIRADA PARA MANUTENÇÃO 20/05/2025; INSTALADA PAÇO PROTOCOLO 08/04/2026;</t>
   </si>
   <si>
-    <t xml:space="preserve">PAÇO - DIVIDA ATIVA - ADM </t>
-  </si>
-  <si>
     <t>XC75051324</t>
   </si>
   <si>
@@ -3733,9 +3727,6 @@
     <t>INSTALADA EM 24/10/2024; RETIRADA SEDUC XEROX 17/04/2026;</t>
   </si>
   <si>
-    <t>ESTAVA NA SEPOL FUNDO MUNICIPAL; INSTALADA SEDUC NUTRIÇÃO 06/08/2025; RETIRADA NUTRIÇÃO SEDUC 17/04/2026;</t>
-  </si>
-  <si>
     <t>ESTAVA NO COMITE EM FRENTE AO SICOOB; ESTAVA NA SEDUC - ALMOXARIFADO; RETIRADA SEDUC TESOURARIA 17/04/2026;</t>
   </si>
   <si>
@@ -3853,9 +3844,6 @@
     <t>CNC1M6B0CH</t>
   </si>
   <si>
-    <t>FAZENDA</t>
-  </si>
-  <si>
     <t>XC75051327</t>
   </si>
   <si>
@@ -4004,6 +3992,15 @@
   </si>
   <si>
     <t>PRAÇA ESCOLA PRAIA SECA</t>
+  </si>
+  <si>
+    <t>DIVIDA ATIVA - ADM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTAVA NA SEPOL FUNDO MUNICIPAL; INSTALADA SEDUC NUTRIÇÃO 06/08/2025; RETIRADA NUTRIÇÃO SEDUC 17/04/2026; </t>
+  </si>
+  <si>
+    <t>ESTAVA NA SEPOL; COLOCADA SEDUC RH NO DIA 11/07/2025  FOI TROCADO CILINDRO; RETIRADA DA SEDUC RH POR PROBLEMAS DE REDE DA IMPRESSORA 01/08/2025; INSTALADA BELLA CASA CABO FRIO 17/09/2025; INSTALADA DIVIDA ATIVA PAÇO 18/11/2025; Retirada do paço com problema de rede 20/08/2026;</t>
   </si>
 </sst>
 </file>
@@ -4189,7 +4186,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4334,16 +4331,10 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -5532,7 +5523,7 @@
         <v>574</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -5728,7 +5719,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>11</v>
@@ -5752,7 +5743,7 @@
         <v>574</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -5760,7 +5751,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>11</v>
@@ -5772,7 +5763,7 @@
         <v>858</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>1321</v>
+        <v>1317</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>19</v>
@@ -5784,7 +5775,7 @@
         <v>574</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -5816,7 +5807,7 @@
         <v>574</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -5880,7 +5871,7 @@
         <v>574</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -6025,7 +6016,7 @@
         <v>19</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>14</v>
@@ -6037,7 +6028,7 @@
         <v>574</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -6101,7 +6092,7 @@
         <v>574</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -6121,7 +6112,7 @@
         <v>76</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>14</v>
@@ -6467,7 +6458,7 @@
         <v>19</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
       <c r="G34" s="4" t="s">
         <v>14</v>
@@ -6479,7 +6470,7 @@
         <v>574</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>1314</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -6528,7 +6519,7 @@
         <v>84</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>836</v>
@@ -7019,7 +7010,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>11</v>
@@ -7051,7 +7042,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>11</v>
@@ -7083,7 +7074,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>11</v>
@@ -7095,7 +7086,7 @@
         <v>68</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>68</v>
@@ -7635,7 +7626,7 @@
         <v>19</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="G72" s="4" t="s">
         <v>14</v>
@@ -7647,7 +7638,7 @@
         <v>574</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -7885,7 +7876,7 @@
         <v>654</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>162</v>
@@ -7917,7 +7908,7 @@
         <v>164</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>165</v>
@@ -7949,7 +7940,7 @@
         <v>655</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>167</v>
@@ -7975,7 +7966,7 @@
         <v>656</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>168</v>
@@ -8001,7 +7992,7 @@
         <v>657</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>965</v>
+        <v>28</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>169</v>
@@ -8027,7 +8018,7 @@
         <v>658</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>170</v>
@@ -8059,7 +8050,7 @@
         <v>172</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>173</v>
@@ -8088,7 +8079,7 @@
         <v>11</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>21</v>
@@ -8106,7 +8097,7 @@
         <v>574</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="88" spans="1:10">
@@ -8123,7 +8114,7 @@
         <v>659</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>176</v>
@@ -8155,7 +8146,7 @@
         <v>660</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>178</v>
@@ -8184,10 +8175,10 @@
         <v>661</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>30</v>
@@ -8216,7 +8207,7 @@
         <v>662</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>180</v>
@@ -8248,7 +8239,7 @@
         <v>663</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>181</v>
@@ -8274,7 +8265,7 @@
         <v>664</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>182</v>
@@ -8300,7 +8291,7 @@
         <v>184</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>185</v>
@@ -8329,10 +8320,10 @@
         <v>11</v>
       </c>
       <c r="D95" s="2" t="s">
+        <v>963</v>
+      </c>
+      <c r="E95" s="1" t="s">
         <v>964</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>965</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>190</v>
@@ -8547,7 +8538,7 @@
         <v>76</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="G102" s="4" t="s">
         <v>14</v>
@@ -8559,7 +8550,7 @@
         <v>574</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="103" spans="1:10">
@@ -8733,7 +8724,7 @@
         <v>11</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>21</v>
@@ -9227,7 +9218,7 @@
         <v>574</v>
       </c>
       <c r="J123" s="3" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="124" spans="1:10">
@@ -9247,7 +9238,7 @@
         <v>68</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="G124" s="1" t="s">
         <v>30</v>
@@ -9279,7 +9270,7 @@
         <v>68</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="G125" s="4" t="s">
         <v>14</v>
@@ -9291,7 +9282,7 @@
         <v>574</v>
       </c>
       <c r="J125" s="3" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="126" spans="1:10">
@@ -9311,7 +9302,7 @@
         <v>19</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="G126" s="1" t="s">
         <v>30</v>
@@ -9503,7 +9494,7 @@
         <v>19</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>1291</v>
+        <v>1287</v>
       </c>
       <c r="G132" s="4" t="s">
         <v>14</v>
@@ -9535,7 +9526,7 @@
         <v>19</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="G133" s="4" t="s">
         <v>14</v>
@@ -9547,7 +9538,7 @@
         <v>574</v>
       </c>
       <c r="J133" s="3" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="134" spans="1:10">
@@ -9567,7 +9558,7 @@
         <v>19</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G134" s="4" t="s">
         <v>14</v>
@@ -9611,7 +9602,7 @@
         <v>574</v>
       </c>
       <c r="J135" s="3" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="136" spans="1:10">
@@ -9631,7 +9622,7 @@
         <v>19</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="G136" s="4" t="s">
         <v>14</v>
@@ -9707,7 +9698,7 @@
         <v>574</v>
       </c>
       <c r="J138" s="3" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="139" spans="1:10">
@@ -9739,7 +9730,7 @@
         <v>646</v>
       </c>
       <c r="J139" s="3" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="140" spans="1:10">
@@ -9803,7 +9794,7 @@
         <v>574</v>
       </c>
       <c r="J141" s="12" t="s">
-        <v>1312</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="142" spans="1:10">
@@ -9823,7 +9814,7 @@
         <v>13</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="G142" s="4" t="s">
         <v>14</v>
@@ -9835,7 +9826,7 @@
         <v>574</v>
       </c>
       <c r="J142" s="3" t="s">
-        <v>1304</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="143" spans="1:10">
@@ -9843,7 +9834,7 @@
         <v>142</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>83</v>
@@ -9855,7 +9846,7 @@
         <v>68</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="G143" s="1" t="s">
         <v>68</v>
@@ -9885,7 +9876,7 @@
         <v>68</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="G144" s="4" t="s">
         <v>14</v>
@@ -9897,7 +9888,7 @@
         <v>574</v>
       </c>
       <c r="J144" s="3" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="145" spans="1:10">
@@ -9911,13 +9902,13 @@
         <v>83</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="G145" s="4" t="s">
         <v>14</v>
@@ -9929,7 +9920,7 @@
         <v>574</v>
       </c>
       <c r="J145" s="3" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="146" spans="1:10">
@@ -9949,7 +9940,7 @@
         <v>68</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="G146" s="13" t="s">
         <v>14</v>
@@ -9981,7 +9972,7 @@
         <v>19</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>1287</v>
+        <v>1283</v>
       </c>
       <c r="G147" s="13" t="s">
         <v>14</v>
@@ -9993,7 +9984,7 @@
         <v>574</v>
       </c>
       <c r="J147" s="3" t="s">
-        <v>1289</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="148" spans="1:10">
@@ -10013,7 +10004,7 @@
         <v>68</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="G148" s="13" t="s">
         <v>14</v>
@@ -10045,7 +10036,7 @@
         <v>68</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="G149" s="13" t="s">
         <v>14</v>
@@ -10071,13 +10062,13 @@
         <v>83</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>1285</v>
+        <v>1281</v>
       </c>
       <c r="G150" s="13" t="s">
         <v>14</v>
@@ -10089,7 +10080,7 @@
         <v>646</v>
       </c>
       <c r="J150" s="3" t="s">
-        <v>1286</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="151" spans="1:10">
@@ -10103,13 +10094,13 @@
         <v>83</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="G151" s="13" t="s">
         <v>14</v>
@@ -10121,7 +10112,7 @@
         <v>574</v>
       </c>
       <c r="J151" s="3" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="152" spans="1:10">
@@ -10135,13 +10126,13 @@
         <v>83</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>1288</v>
+        <v>1284</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
       <c r="G152" s="13" t="s">
         <v>14</v>
@@ -10165,13 +10156,13 @@
         <v>83</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="G153" s="13" t="s">
         <v>14</v>
@@ -10195,13 +10186,13 @@
         <v>83</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="G154" s="13" t="s">
         <v>14</v>
@@ -10213,7 +10204,7 @@
         <v>646</v>
       </c>
       <c r="J154" s="3" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="155" spans="1:10">
@@ -10227,13 +10218,13 @@
         <v>83</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>1297</v>
+        <v>1293</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>1298</v>
+        <v>1294</v>
       </c>
       <c r="G155" s="13" t="s">
         <v>14</v>
@@ -10245,7 +10236,7 @@
         <v>574</v>
       </c>
       <c r="J155" s="3" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="156" spans="1:10">
@@ -10259,13 +10250,13 @@
         <v>83</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>1300</v>
+        <v>1296</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>1301</v>
+        <v>1297</v>
       </c>
       <c r="G156" s="13" t="s">
         <v>14</v>
@@ -10277,7 +10268,7 @@
         <v>574</v>
       </c>
       <c r="J156" s="3" t="s">
-        <v>1302</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="157" spans="1:10">
@@ -10291,13 +10282,13 @@
         <v>83</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>1309</v>
+        <v>1305</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>1307</v>
+        <v>1303</v>
       </c>
       <c r="G157" s="13" t="s">
         <v>14</v>
@@ -10309,7 +10300,7 @@
         <v>574</v>
       </c>
       <c r="J157" s="3" t="s">
-        <v>1308</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="158" spans="1:10">
@@ -10323,21 +10314,21 @@
         <v>83</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>1319</v>
-      </c>
-      <c r="E158" s="56" t="s">
+        <v>1315</v>
+      </c>
+      <c r="E158" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F158" s="56" t="s">
-        <v>1320</v>
-      </c>
-      <c r="G158" s="56" t="s">
+      <c r="F158" s="1" t="s">
+        <v>1316</v>
+      </c>
+      <c r="G158" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H158" s="54">
         <v>46248</v>
       </c>
-      <c r="I158" s="57" t="s">
+      <c r="I158" s="9" t="s">
         <v>574</v>
       </c>
       <c r="J158" s="55"/>
@@ -10371,7 +10362,7 @@
         <v>574</v>
       </c>
       <c r="J159" s="3" t="s">
-        <v>1290</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="160" spans="1:10">
@@ -10455,7 +10446,7 @@
         <v>68</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="G162" s="4" t="s">
         <v>14</v>
@@ -10467,7 +10458,7 @@
         <v>574</v>
       </c>
       <c r="J162" s="3" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="163" spans="1:10">
@@ -10668,7 +10659,7 @@
         <v>350</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="G169" s="4" t="s">
         <v>14</v>
@@ -10680,7 +10671,7 @@
         <v>574</v>
       </c>
       <c r="J169" s="3" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="170" spans="1:10">
@@ -10805,7 +10796,7 @@
         <v>574</v>
       </c>
       <c r="J173" s="3" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="174" spans="1:10">
@@ -10944,7 +10935,7 @@
         <v>188</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>189</v>
@@ -10967,13 +10958,13 @@
         <v>83</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="G179" s="4" t="s">
         <v>14</v>
@@ -11015,7 +11006,7 @@
         <v>574</v>
       </c>
       <c r="J180" s="3" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="181" spans="1:10">
@@ -11032,10 +11023,10 @@
         <v>286</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="G181" s="4" t="s">
         <v>14</v>
@@ -11058,7 +11049,7 @@
         <v>83</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>1233</v>
+        <v>1230</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>13</v>
@@ -11076,7 +11067,7 @@
         <v>574</v>
       </c>
       <c r="J182" s="3" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="183" spans="1:10">
@@ -11093,10 +11084,10 @@
         <v>287</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="G183" s="4" t="s">
         <v>14</v>
@@ -11778,7 +11769,7 @@
         <v>574</v>
       </c>
       <c r="J206" s="3" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="207" spans="1:10">
@@ -11795,10 +11786,10 @@
         <v>314</v>
       </c>
       <c r="E207" s="4" t="s">
+        <v>955</v>
+      </c>
+      <c r="F207" s="4" t="s">
         <v>956</v>
-      </c>
-      <c r="F207" s="4" t="s">
-        <v>957</v>
       </c>
       <c r="G207" s="4" t="s">
         <v>14</v>
@@ -11856,13 +11847,13 @@
         <v>11</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="E209" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="G209" s="4" t="s">
         <v>14</v>
@@ -11904,7 +11895,7 @@
         <v>574</v>
       </c>
       <c r="J210" s="3" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="211" spans="1:10">
@@ -11921,10 +11912,10 @@
         <v>316</v>
       </c>
       <c r="E211" s="4" t="s">
+        <v>955</v>
+      </c>
+      <c r="F211" s="4" t="s">
         <v>956</v>
-      </c>
-      <c r="F211" s="4" t="s">
-        <v>957</v>
       </c>
       <c r="G211" s="4" t="s">
         <v>14</v>
@@ -11988,7 +11979,7 @@
         <v>19</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="G213" s="4" t="s">
         <v>14</v>
@@ -12000,7 +11991,7 @@
         <v>574</v>
       </c>
       <c r="J213" s="8" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="214" spans="1:10">
@@ -12052,7 +12043,7 @@
         <v>68</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>1315</v>
+        <v>1311</v>
       </c>
       <c r="G215" s="4" t="s">
         <v>14</v>
@@ -12064,7 +12055,7 @@
         <v>574</v>
       </c>
       <c r="J215" s="3" t="s">
-        <v>1316</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="216" spans="1:10">
@@ -12078,13 +12069,13 @@
         <v>11</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="E216" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="G216" s="1" t="s">
         <v>30</v>
@@ -12096,7 +12087,7 @@
         <v>574</v>
       </c>
       <c r="J216" s="3" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="217" spans="1:10">
@@ -12128,7 +12119,7 @@
         <v>574</v>
       </c>
       <c r="J217" s="3" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="218" spans="1:10">
@@ -12180,7 +12171,7 @@
         <v>19</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="G219" s="4" t="s">
         <v>14</v>
@@ -12192,7 +12183,7 @@
         <v>574</v>
       </c>
       <c r="J219" s="3" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="220" spans="1:10">
@@ -12212,7 +12203,7 @@
         <v>19</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="G220" s="4" t="s">
         <v>14</v>
@@ -12244,7 +12235,7 @@
         <v>76</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="G221" s="4" t="s">
         <v>14</v>
@@ -12256,7 +12247,7 @@
         <v>574</v>
       </c>
       <c r="J221" s="3" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="222" spans="1:10">
@@ -12288,7 +12279,7 @@
         <v>574</v>
       </c>
       <c r="J222" s="3" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="223" spans="1:10">
@@ -12448,7 +12439,7 @@
         <v>574</v>
       </c>
       <c r="J227" s="3" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="228" spans="1:10">
@@ -12468,7 +12459,7 @@
         <v>19</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="G228" s="4" t="s">
         <v>14</v>
@@ -12480,7 +12471,7 @@
         <v>574</v>
       </c>
       <c r="J228" s="3" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="229" spans="1:10">
@@ -12532,7 +12523,7 @@
         <v>19</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="G230" s="4" t="s">
         <v>14</v>
@@ -12576,7 +12567,7 @@
         <v>574</v>
       </c>
       <c r="J231" s="3" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="232" spans="1:10">
@@ -12596,7 +12587,7 @@
         <v>19</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="G232" s="4" t="s">
         <v>14</v>
@@ -12608,7 +12599,7 @@
         <v>574</v>
       </c>
       <c r="J232" s="3" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="233" spans="1:10">
@@ -12672,7 +12663,7 @@
         <v>574</v>
       </c>
       <c r="J234" s="3" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="235" spans="1:10">
@@ -12692,7 +12683,7 @@
         <v>19</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="G235" s="4" t="s">
         <v>14</v>
@@ -12704,7 +12695,7 @@
         <v>574</v>
       </c>
       <c r="J235" s="3" t="s">
-        <v>1274</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="236" spans="1:10">
@@ -12820,7 +12811,7 @@
         <v>19</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="G239" s="4" t="s">
         <v>14</v>
@@ -12832,7 +12823,7 @@
         <v>574</v>
       </c>
       <c r="J239" s="3" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="240" spans="1:10">
@@ -12884,7 +12875,7 @@
         <v>76</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="G241" s="4" t="s">
         <v>14</v>
@@ -12896,7 +12887,7 @@
         <v>574</v>
       </c>
       <c r="J241" s="7" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="242" spans="1:10">
@@ -12916,7 +12907,7 @@
         <v>19</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="G242" s="4" t="s">
         <v>14</v>
@@ -12948,7 +12939,7 @@
         <v>19</v>
       </c>
       <c r="F243" s="50" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="G243" s="4" t="s">
         <v>14</v>
@@ -12960,7 +12951,7 @@
         <v>574</v>
       </c>
       <c r="J243" s="7" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="244" spans="1:10">
@@ -12980,7 +12971,7 @@
         <v>19</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="G244" s="4" t="s">
         <v>14</v>
@@ -12992,7 +12983,7 @@
         <v>646</v>
       </c>
       <c r="J244" s="3" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="245" spans="1:10">
@@ -13012,7 +13003,7 @@
         <v>19</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="G245" s="4" t="s">
         <v>14</v>
@@ -13044,7 +13035,7 @@
         <v>19</v>
       </c>
       <c r="F246" s="41" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="G246" s="4" t="s">
         <v>14</v>
@@ -13056,7 +13047,7 @@
         <v>574</v>
       </c>
       <c r="J246" s="8" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="247" spans="1:10">
@@ -13088,7 +13079,7 @@
         <v>574</v>
       </c>
       <c r="J247" s="8" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="248" spans="1:10">
@@ -13105,10 +13096,10 @@
         <v>573</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="G248" s="1" t="s">
         <v>14</v>
@@ -13167,10 +13158,10 @@
         <v>365</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>605</v>
+        <v>1318</v>
       </c>
       <c r="G250" s="4" t="s">
         <v>14</v>
@@ -13182,7 +13173,7 @@
         <v>574</v>
       </c>
       <c r="J250" s="3" t="s">
-        <v>1231</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="251" spans="1:10">
@@ -13214,7 +13205,7 @@
         <v>574</v>
       </c>
       <c r="J251" s="3" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="252" spans="1:10">
@@ -13231,10 +13222,10 @@
         <v>367</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="F252" s="4" t="s">
-        <v>1206</v>
+        <v>23</v>
       </c>
       <c r="G252" s="4" t="s">
         <v>14</v>
@@ -13246,7 +13237,7 @@
         <v>574</v>
       </c>
       <c r="J252" s="3" t="s">
-        <v>915</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="253" spans="1:10">
@@ -13254,7 +13245,7 @@
         <v>252</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>11</v>
@@ -13263,10 +13254,10 @@
         <v>39</v>
       </c>
       <c r="E253" s="4" t="s">
-        <v>19</v>
+        <v>858</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="G253" s="1" t="s">
         <v>19</v>
@@ -13371,7 +13362,7 @@
         <v>574</v>
       </c>
       <c r="J256" s="3" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="257" spans="1:10">
@@ -13420,7 +13411,7 @@
         <v>377</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="F258" s="1" t="s">
         <v>378</v>
@@ -13449,7 +13440,7 @@
         <v>667</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="F259" s="1" t="s">
         <v>380</v>
@@ -13481,7 +13472,7 @@
         <v>381</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="F260" s="1" t="s">
         <v>382</v>
@@ -13510,7 +13501,7 @@
         <v>383</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="F261" s="1" t="s">
         <v>175</v>
@@ -13586,7 +13577,7 @@
         <v>574</v>
       </c>
       <c r="J263" s="3" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="264" spans="1:10">
@@ -13606,7 +13597,7 @@
         <v>19</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>1283</v>
+        <v>1279</v>
       </c>
       <c r="G264" s="4" t="s">
         <v>14</v>
@@ -13618,7 +13609,7 @@
         <v>574</v>
       </c>
       <c r="J264" s="3" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="265" spans="1:10">
@@ -13638,7 +13629,7 @@
         <v>19</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>1275</v>
+        <v>1271</v>
       </c>
       <c r="G265" s="4" t="s">
         <v>14</v>
@@ -13650,7 +13641,7 @@
         <v>574</v>
       </c>
       <c r="J265" s="3" t="s">
-        <v>1276</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="266" spans="1:10">
@@ -13746,7 +13737,7 @@
         <v>574</v>
       </c>
       <c r="J268" s="3" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="269" spans="1:10">
@@ -13894,7 +13885,7 @@
         <v>13</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="G273" s="4" t="s">
         <v>14</v>
@@ -13906,7 +13897,7 @@
         <v>646</v>
       </c>
       <c r="J273" s="3" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="274" spans="1:10">
@@ -13938,7 +13929,7 @@
         <v>574</v>
       </c>
       <c r="J274" s="3" t="s">
-        <v>1311</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="275" spans="1:10">
@@ -13990,7 +13981,7 @@
         <v>68</v>
       </c>
       <c r="F276" s="4" t="s">
-        <v>1303</v>
+        <v>1299</v>
       </c>
       <c r="G276" s="4" t="s">
         <v>14</v>
@@ -14150,7 +14141,7 @@
         <v>350</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="G281" s="1" t="s">
         <v>14</v>
@@ -14162,7 +14153,7 @@
         <v>574</v>
       </c>
       <c r="J281" s="3" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="282" spans="1:10">
@@ -14182,7 +14173,7 @@
         <v>68</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="G282" s="1" t="s">
         <v>14</v>
@@ -14214,7 +14205,7 @@
         <v>68</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="G283" s="1" t="s">
         <v>14</v>
@@ -14246,7 +14237,7 @@
         <v>68</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="G284" s="1" t="s">
         <v>14</v>
@@ -14278,7 +14269,7 @@
         <v>68</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="G285" s="1" t="s">
         <v>14</v>
@@ -14310,7 +14301,7 @@
         <v>68</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="G286" s="1" t="s">
         <v>14</v>
@@ -14342,7 +14333,7 @@
         <v>68</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="G287" s="1" t="s">
         <v>14</v>
@@ -14374,7 +14365,7 @@
         <v>68</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="G288" s="1" t="s">
         <v>14</v>
@@ -14406,7 +14397,7 @@
         <v>68</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="G289" s="1" t="s">
         <v>14</v>
@@ -14438,7 +14429,7 @@
         <v>68</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="G290" s="1" t="s">
         <v>14</v>
@@ -14470,7 +14461,7 @@
         <v>68</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="G291" s="1" t="s">
         <v>14</v>
@@ -14502,7 +14493,7 @@
         <v>68</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="G292" s="1" t="s">
         <v>14</v>
@@ -14534,7 +14525,7 @@
         <v>68</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="G293" s="1" t="s">
         <v>14</v>
@@ -14566,7 +14557,7 @@
         <v>68</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="G294" s="1" t="s">
         <v>14</v>
@@ -14598,7 +14589,7 @@
         <v>76</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="G295" s="1" t="s">
         <v>14</v>
@@ -14610,7 +14601,7 @@
         <v>646</v>
       </c>
       <c r="J295" s="3" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="296" spans="1:10">
@@ -14630,7 +14621,7 @@
         <v>68</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="G296" s="1" t="s">
         <v>14</v>
@@ -14662,7 +14653,7 @@
         <v>68</v>
       </c>
       <c r="F297" s="4" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="G297" s="1" t="s">
         <v>14</v>
@@ -14694,7 +14685,7 @@
         <v>68</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="G298" s="1" t="s">
         <v>14</v>
@@ -14726,7 +14717,7 @@
         <v>68</v>
       </c>
       <c r="F299" s="4" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="G299" s="1" t="s">
         <v>14</v>
@@ -15218,7 +15209,7 @@
         <v>574</v>
       </c>
       <c r="J314" s="3" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="315" spans="1:10">
@@ -15270,7 +15261,7 @@
         <v>68</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="G316" s="1" t="s">
         <v>14</v>
@@ -15314,7 +15305,7 @@
         <v>574</v>
       </c>
       <c r="J317" s="3" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="318" spans="1:10">
@@ -15494,7 +15485,7 @@
         <v>68</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="G323" s="1" t="s">
         <v>14</v>
@@ -15622,7 +15613,7 @@
         <v>68</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="G327" s="1" t="s">
         <v>14</v>
@@ -15654,7 +15645,7 @@
         <v>68</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="G328" s="1" t="s">
         <v>14</v>
@@ -15686,7 +15677,7 @@
         <v>68</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="G329" s="1" t="s">
         <v>14</v>
@@ -15718,7 +15709,7 @@
         <v>68</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="G330" s="1" t="s">
         <v>14</v>
@@ -15750,7 +15741,7 @@
         <v>68</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="G331" s="1" t="s">
         <v>14</v>
@@ -15782,7 +15773,7 @@
         <v>68</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="G332" s="1" t="s">
         <v>14</v>
@@ -15814,7 +15805,7 @@
         <v>68</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="G333" s="1" t="s">
         <v>14</v>
@@ -15846,7 +15837,7 @@
         <v>68</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="G334" s="1" t="s">
         <v>14</v>
@@ -15878,7 +15869,7 @@
         <v>68</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="G335" s="1" t="s">
         <v>14</v>
@@ -15910,7 +15901,7 @@
         <v>68</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="G336" s="1" t="s">
         <v>14</v>
@@ -15942,7 +15933,7 @@
         <v>68</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="G337" s="1" t="s">
         <v>14</v>
@@ -15974,7 +15965,7 @@
         <v>68</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="G338" s="1" t="s">
         <v>14</v>
@@ -16006,7 +15997,7 @@
         <v>68</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="G339" s="1" t="s">
         <v>14</v>
@@ -16018,7 +16009,7 @@
         <v>574</v>
       </c>
       <c r="J339" s="3" t="s">
-        <v>1306</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="340" spans="1:10">
@@ -16038,7 +16029,7 @@
         <v>68</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="G340" s="1" t="s">
         <v>14</v>
@@ -16070,7 +16061,7 @@
         <v>68</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="G341" s="1" t="s">
         <v>14</v>
@@ -16102,7 +16093,7 @@
         <v>68</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="G342" s="1" t="s">
         <v>14</v>
@@ -16166,7 +16157,7 @@
         <v>68</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="G344" s="1" t="s">
         <v>14</v>
@@ -16198,7 +16189,7 @@
         <v>68</v>
       </c>
       <c r="F345" s="4" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="G345" s="1" t="s">
         <v>14</v>
@@ -16230,7 +16221,7 @@
         <v>68</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="G346" s="1" t="s">
         <v>14</v>
@@ -16262,7 +16253,7 @@
         <v>68</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="G347" s="1" t="s">
         <v>14</v>
@@ -16294,7 +16285,7 @@
         <v>68</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="G348" s="1" t="s">
         <v>14</v>
@@ -16326,7 +16317,7 @@
         <v>68</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="G349" s="1" t="s">
         <v>14</v>
@@ -16582,7 +16573,7 @@
         <v>76</v>
       </c>
       <c r="F357" s="1" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="G357" s="13" t="s">
         <v>14</v>
@@ -16594,7 +16585,7 @@
         <v>574</v>
       </c>
       <c r="J357" s="3" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="358" spans="1:10">
@@ -16902,7 +16893,7 @@
         <v>76</v>
       </c>
       <c r="F367" s="1" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G367" s="1" t="s">
         <v>14</v>
@@ -16914,7 +16905,7 @@
         <v>574</v>
       </c>
       <c r="J367" s="3" t="s">
-        <v>1296</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="368" spans="1:10">
@@ -17030,7 +17021,7 @@
         <v>76</v>
       </c>
       <c r="F371" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="G371" s="1" t="s">
         <v>14</v>
@@ -17074,7 +17065,7 @@
         <v>574</v>
       </c>
       <c r="J372" s="3" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="373" spans="1:10">
@@ -17094,7 +17085,7 @@
         <v>76</v>
       </c>
       <c r="F373" s="1" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="G373" s="1" t="s">
         <v>14</v>
@@ -17106,7 +17097,7 @@
         <v>574</v>
       </c>
       <c r="J373" s="3" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="374" spans="1:10">
@@ -17126,7 +17117,7 @@
         <v>76</v>
       </c>
       <c r="F374" s="1" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="G374" s="1" t="s">
         <v>14</v>
@@ -17138,7 +17129,7 @@
         <v>574</v>
       </c>
       <c r="J374" s="3" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="375" spans="1:10">
@@ -17158,7 +17149,7 @@
         <v>76</v>
       </c>
       <c r="F375" s="1" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="G375" s="1" t="s">
         <v>14</v>
@@ -17170,7 +17161,7 @@
         <v>574</v>
       </c>
       <c r="J375" s="3" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="376" spans="1:10">
@@ -17190,7 +17181,7 @@
         <v>76</v>
       </c>
       <c r="F376" s="1" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="G376" s="1" t="s">
         <v>14</v>
@@ -17254,7 +17245,7 @@
         <v>68</v>
       </c>
       <c r="F378" s="1" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="G378" s="1" t="s">
         <v>14</v>
@@ -17318,7 +17309,7 @@
         <v>68</v>
       </c>
       <c r="F380" s="1" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="G380" s="1" t="s">
         <v>14</v>
@@ -17382,7 +17373,7 @@
         <v>68</v>
       </c>
       <c r="F382" s="1" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="G382" s="1" t="s">
         <v>14</v>
@@ -17394,7 +17385,7 @@
         <v>574</v>
       </c>
       <c r="J382" s="3" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="383" spans="1:10">
@@ -17446,7 +17437,7 @@
         <v>76</v>
       </c>
       <c r="F384" s="1" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="G384" s="1" t="s">
         <v>14</v>
@@ -17458,7 +17449,7 @@
         <v>574</v>
       </c>
       <c r="J384" s="3" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="385" spans="1:10">
@@ -17490,7 +17481,7 @@
         <v>574</v>
       </c>
       <c r="J385" s="3" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="386" spans="1:10">
@@ -17522,7 +17513,7 @@
         <v>646</v>
       </c>
       <c r="J386" s="3" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="387" spans="1:10">
@@ -17574,7 +17565,7 @@
         <v>76</v>
       </c>
       <c r="F388" s="1" t="s">
-        <v>1317</v>
+        <v>1313</v>
       </c>
       <c r="G388" s="1" t="s">
         <v>14</v>
@@ -17586,7 +17577,7 @@
         <v>574</v>
       </c>
       <c r="J388" s="3" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="389" spans="1:10">
@@ -17606,7 +17597,7 @@
         <v>76</v>
       </c>
       <c r="F389" s="1" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="G389" s="1" t="s">
         <v>14</v>
@@ -17618,7 +17609,7 @@
         <v>574</v>
       </c>
       <c r="J389" s="3" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="390" spans="1:10">
@@ -17702,7 +17693,7 @@
         <v>76</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="G392" s="1" t="s">
         <v>14</v>
@@ -17714,7 +17705,7 @@
         <v>574</v>
       </c>
       <c r="J392" s="3" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="393" spans="1:10">
@@ -17734,7 +17725,7 @@
         <v>76</v>
       </c>
       <c r="F393" s="1" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="G393" s="1" t="s">
         <v>14</v>
@@ -17746,7 +17737,7 @@
         <v>574</v>
       </c>
       <c r="J393" s="3" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="394" spans="1:10">
@@ -17766,7 +17757,7 @@
         <v>68</v>
       </c>
       <c r="F394" s="1" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="G394" s="1" t="s">
         <v>14</v>
@@ -17778,7 +17769,7 @@
         <v>574</v>
       </c>
       <c r="J394" s="3" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="395" spans="1:10">
@@ -17862,7 +17853,7 @@
         <v>76</v>
       </c>
       <c r="F397" s="1" t="s">
-        <v>1294</v>
+        <v>1290</v>
       </c>
       <c r="G397" s="1" t="s">
         <v>14</v>
@@ -17874,7 +17865,7 @@
         <v>574</v>
       </c>
       <c r="J397" s="3" t="s">
-        <v>1295</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="398" spans="1:10">
@@ -17894,7 +17885,7 @@
         <v>68</v>
       </c>
       <c r="F398" s="1" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="G398" s="1" t="s">
         <v>14</v>
@@ -17926,7 +17917,7 @@
         <v>68</v>
       </c>
       <c r="F399" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="G399" s="1" t="s">
         <v>14</v>
@@ -17938,7 +17929,7 @@
         <v>646</v>
       </c>
       <c r="J399" s="3" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="400" spans="1:10">
@@ -17952,13 +17943,13 @@
         <v>11</v>
       </c>
       <c r="D400" s="2" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="E400" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F400" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="G400" s="1" t="s">
         <v>14</v>
@@ -17970,7 +17961,7 @@
         <v>574</v>
       </c>
       <c r="J400" s="3" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="401" spans="1:10">
@@ -17984,13 +17975,13 @@
         <v>11</v>
       </c>
       <c r="D401" s="2" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="E401" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F401" s="1" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="G401" s="1" t="s">
         <v>14</v>
@@ -18002,7 +17993,7 @@
         <v>574</v>
       </c>
       <c r="J401" s="3" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="402" spans="1:10">
@@ -18016,13 +18007,13 @@
         <v>11</v>
       </c>
       <c r="D402" s="2" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="E402" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F402" s="1" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="G402" s="1" t="s">
         <v>14</v>
@@ -18034,7 +18025,7 @@
         <v>574</v>
       </c>
       <c r="J402" s="3" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="403" spans="1:10">
@@ -18048,13 +18039,13 @@
         <v>11</v>
       </c>
       <c r="D403" s="2" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="E403" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F403" s="1" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="G403" s="1" t="s">
         <v>14</v>
@@ -18066,7 +18057,7 @@
         <v>574</v>
       </c>
       <c r="J403" s="3" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="404" spans="1:10">
@@ -18080,13 +18071,13 @@
         <v>11</v>
       </c>
       <c r="D404" s="2" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="E404" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F404" s="1" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="G404" s="1" t="s">
         <v>14</v>
@@ -18098,7 +18089,7 @@
         <v>574</v>
       </c>
       <c r="J404" s="3" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="405" spans="1:10">
@@ -18400,13 +18391,13 @@
         <v>11</v>
       </c>
       <c r="D414" s="5" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="E414" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F414" s="1" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="G414" s="1" t="s">
         <v>14</v>
@@ -18418,7 +18409,7 @@
         <v>574</v>
       </c>
       <c r="J414" s="3" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="415" spans="1:10">
@@ -18432,13 +18423,13 @@
         <v>11</v>
       </c>
       <c r="D415" s="5" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="E415" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F415" s="1" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="G415" s="1" t="s">
         <v>14</v>
@@ -18450,7 +18441,7 @@
         <v>574</v>
       </c>
       <c r="J415" s="3" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="416" spans="1:10">
@@ -18464,13 +18455,13 @@
         <v>11</v>
       </c>
       <c r="D416" s="5" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E416" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F416" s="1" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="G416" s="1" t="s">
         <v>14</v>
@@ -18482,7 +18473,7 @@
         <v>574</v>
       </c>
       <c r="J416" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="417" spans="1:10">
@@ -18496,13 +18487,13 @@
         <v>11</v>
       </c>
       <c r="D417" s="5" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="E417" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F417" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="G417" s="1" t="s">
         <v>14</v>
@@ -18514,7 +18505,7 @@
         <v>574</v>
       </c>
       <c r="J417" s="3" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="418" spans="1:10">
@@ -18528,13 +18519,13 @@
         <v>11</v>
       </c>
       <c r="D418" s="5" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="E418" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F418" s="1" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="G418" s="1" t="s">
         <v>14</v>
@@ -18546,7 +18537,7 @@
         <v>574</v>
       </c>
       <c r="J418" s="3" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="419" spans="1:10">
@@ -18822,7 +18813,7 @@
         <v>76</v>
       </c>
       <c r="F427" s="1" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="G427" s="1" t="s">
         <v>14</v>
@@ -18834,7 +18825,7 @@
         <v>646</v>
       </c>
       <c r="J427" s="3" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="428" spans="1:10">
@@ -18848,7 +18839,7 @@
         <v>11</v>
       </c>
       <c r="D428" s="5" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="E428" s="1" t="s">
         <v>76</v>
@@ -18866,7 +18857,7 @@
         <v>574</v>
       </c>
       <c r="J428" s="3" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="429" spans="1:10">
@@ -18880,7 +18871,7 @@
         <v>11</v>
       </c>
       <c r="D429" s="5" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="E429" s="1" t="s">
         <v>76</v>
@@ -18898,7 +18889,7 @@
         <v>574</v>
       </c>
       <c r="J429" s="3" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="430" spans="1:10">
@@ -18912,13 +18903,13 @@
         <v>11</v>
       </c>
       <c r="D430" s="5" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="E430" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F430" s="1" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="G430" s="1" t="s">
         <v>14</v>
@@ -18930,7 +18921,7 @@
         <v>574</v>
       </c>
       <c r="J430" s="3" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="431" spans="1:10">
@@ -18944,13 +18935,13 @@
         <v>11</v>
       </c>
       <c r="D431" s="5" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="E431" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F431" s="1" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="G431" s="1" t="s">
         <v>14</v>
@@ -18962,7 +18953,7 @@
         <v>574</v>
       </c>
       <c r="J431" s="3" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="432" spans="1:10">
@@ -18976,13 +18967,13 @@
         <v>11</v>
       </c>
       <c r="D432" s="5" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E432" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F432" s="1" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="G432" s="1" t="s">
         <v>14</v>
@@ -18994,7 +18985,7 @@
         <v>574</v>
       </c>
       <c r="J432" s="3" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="433" spans="1:10">
@@ -19008,13 +18999,13 @@
         <v>11</v>
       </c>
       <c r="D433" s="5" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E433" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F433" s="1" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="G433" s="1" t="s">
         <v>14</v>
@@ -19026,7 +19017,7 @@
         <v>574</v>
       </c>
       <c r="J433" s="3" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="434" spans="1:10">
@@ -19040,7 +19031,7 @@
         <v>11</v>
       </c>
       <c r="D434" s="5" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="E434" s="1" t="s">
         <v>76</v>
@@ -19058,7 +19049,7 @@
         <v>574</v>
       </c>
       <c r="J434" s="3" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="435" spans="1:10">
@@ -19072,13 +19063,13 @@
         <v>11</v>
       </c>
       <c r="D435" s="5" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="E435" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F435" s="1" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="G435" s="1" t="s">
         <v>14</v>
@@ -19090,7 +19081,7 @@
         <v>646</v>
       </c>
       <c r="J435" s="3" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="436" spans="1:10">
@@ -19104,13 +19095,13 @@
         <v>11</v>
       </c>
       <c r="D436" s="5" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="E436" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F436" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="G436" s="1" t="s">
         <v>14</v>
@@ -19134,7 +19125,7 @@
         <v>11</v>
       </c>
       <c r="D437" s="5" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="E437" s="1" t="s">
         <v>76</v>
@@ -19152,7 +19143,7 @@
         <v>574</v>
       </c>
       <c r="J437" s="3" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="438" spans="1:10">
@@ -19184,7 +19175,7 @@
         <v>574</v>
       </c>
       <c r="J438" s="3" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="439" spans="1:10">
@@ -19216,7 +19207,7 @@
         <v>574</v>
       </c>
       <c r="J439" s="3" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="440" spans="1:10">
@@ -19236,7 +19227,7 @@
         <v>76</v>
       </c>
       <c r="F440" s="1" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="G440" s="1" t="s">
         <v>14</v>
@@ -19248,7 +19239,7 @@
         <v>574</v>
       </c>
       <c r="J440" s="3" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="441" spans="1:10">
@@ -19262,13 +19253,13 @@
         <v>11</v>
       </c>
       <c r="D441" s="5" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="E441" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F441" s="1" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="G441" s="1" t="s">
         <v>14</v>
@@ -19280,7 +19271,7 @@
         <v>574</v>
       </c>
       <c r="J441" s="3" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="442" spans="1:10">
@@ -19312,7 +19303,7 @@
         <v>574</v>
       </c>
       <c r="J442" s="3" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="443" spans="1:10">
@@ -19326,7 +19317,7 @@
         <v>11</v>
       </c>
       <c r="D443" s="2" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E443" s="1" t="s">
         <v>350</v>
@@ -19344,7 +19335,7 @@
         <v>574</v>
       </c>
       <c r="J443" s="3" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="444" spans="1:10">
@@ -19358,7 +19349,7 @@
         <v>11</v>
       </c>
       <c r="D444" s="2" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E444" s="1" t="s">
         <v>350</v>
@@ -19376,7 +19367,7 @@
         <v>574</v>
       </c>
       <c r="J444" s="3" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="445" spans="1:10">
@@ -19390,13 +19381,13 @@
         <v>11</v>
       </c>
       <c r="D445" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="E445" s="1" t="s">
         <v>350</v>
       </c>
       <c r="F445" s="1" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="G445" s="1" t="s">
         <v>30</v>
@@ -19408,7 +19399,7 @@
         <v>574</v>
       </c>
       <c r="J445" s="3" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="446" spans="1:10">
@@ -19422,13 +19413,13 @@
         <v>11</v>
       </c>
       <c r="D446" s="2" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="E446" s="1" t="s">
         <v>350</v>
       </c>
       <c r="F446" s="1" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="G446" s="1" t="s">
         <v>30</v>
@@ -19440,7 +19431,7 @@
         <v>574</v>
       </c>
       <c r="J446" s="3" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="447" spans="1:10">
@@ -19454,13 +19445,13 @@
         <v>11</v>
       </c>
       <c r="D447" s="2" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="E447" s="1" t="s">
         <v>350</v>
       </c>
       <c r="F447" s="1" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="G447" s="1" t="s">
         <v>30</v>
@@ -19472,7 +19463,7 @@
         <v>574</v>
       </c>
       <c r="J447" s="3" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="448" spans="1:10">
@@ -19512,13 +19503,13 @@
         <v>448</v>
       </c>
       <c r="B449" s="53" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="C449" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="E449" s="1" t="s">
         <v>19</v>
@@ -19536,7 +19527,7 @@
         <v>574</v>
       </c>
       <c r="J449" s="3" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="450" spans="1:10">
@@ -19544,19 +19535,19 @@
         <v>449</v>
       </c>
       <c r="B450" s="53" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="C450" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="E450" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F450" s="1" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="G450" s="1" t="s">
         <v>30</v>
@@ -19574,13 +19565,13 @@
         <v>450</v>
       </c>
       <c r="B451" s="53" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="C451" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D451" s="2" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="E451" s="1" t="s">
         <v>350</v>
@@ -19604,19 +19595,19 @@
         <v>451</v>
       </c>
       <c r="B452" s="53" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="C452" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="E452" s="1" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="F452" s="1" t="s">
-        <v>1292</v>
+        <v>1288</v>
       </c>
       <c r="G452" s="1" t="s">
         <v>30</v>
@@ -19628,7 +19619,7 @@
         <v>574</v>
       </c>
       <c r="J452" s="3" t="s">
-        <v>1293</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="453" spans="1:10">
@@ -19636,19 +19627,19 @@
         <v>452</v>
       </c>
       <c r="B453" s="53" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="C453" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D453" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="E453" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F453" s="1" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="G453" s="1" t="s">
         <v>30</v>
@@ -19666,19 +19657,19 @@
         <v>453</v>
       </c>
       <c r="B454" s="53" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="C454" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D454" s="2" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="E454" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F454" s="1" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="G454" s="1" t="s">
         <v>30</v>
@@ -19696,19 +19687,19 @@
         <v>454</v>
       </c>
       <c r="B455" s="53" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="C455" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D455" s="2" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="E455" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F455" s="1" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="G455" s="1" t="s">
         <v>30</v>
@@ -19726,19 +19717,19 @@
         <v>455</v>
       </c>
       <c r="B456" s="53" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="C456" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D456" s="2" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="E456" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F456" s="1" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="G456" s="1" t="s">
         <v>30</v>
@@ -19756,19 +19747,19 @@
         <v>456</v>
       </c>
       <c r="B457" s="53" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="C457" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D457" s="2" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="E457" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F457" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="G457" s="1" t="s">
         <v>30</v>
@@ -19786,19 +19777,19 @@
         <v>457</v>
       </c>
       <c r="B458" s="53" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="C458" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D458" s="2" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="E458" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F458" s="1" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="G458" s="1" t="s">
         <v>30</v>
@@ -19816,19 +19807,19 @@
         <v>458</v>
       </c>
       <c r="B459" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C459" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D459" s="2" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="E459" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F459" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="G459" s="1" t="s">
         <v>30</v>
@@ -19846,19 +19837,19 @@
         <v>459</v>
       </c>
       <c r="B460" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C460" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D460" s="2" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="E460" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F460" s="1" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="G460" s="1" t="s">
         <v>30</v>
@@ -19876,19 +19867,19 @@
         <v>460</v>
       </c>
       <c r="B461" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C461" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D461" s="2" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="E461" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F461" s="1" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="G461" s="1" t="s">
         <v>30</v>
@@ -19906,19 +19897,19 @@
         <v>461</v>
       </c>
       <c r="B462" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C462" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D462" s="2" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="E462" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F462" s="1" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="G462" s="1" t="s">
         <v>30</v>
@@ -19930,7 +19921,7 @@
         <v>574</v>
       </c>
       <c r="J462" s="3" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="463" spans="1:10">
@@ -19938,19 +19929,19 @@
         <v>462</v>
       </c>
       <c r="B463" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C463" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D463" s="2" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="E463" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F463" s="1" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="G463" s="1" t="s">
         <v>30</v>
@@ -19968,19 +19959,19 @@
         <v>463</v>
       </c>
       <c r="B464" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C464" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D464" s="2" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="E464" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F464" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="G464" s="1" t="s">
         <v>30</v>
@@ -19998,19 +19989,19 @@
         <v>464</v>
       </c>
       <c r="B465" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C465" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D465" s="2" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="E465" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F465" s="1" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="G465" s="1" t="s">
         <v>30</v>
@@ -20028,19 +20019,19 @@
         <v>465</v>
       </c>
       <c r="B466" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C466" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D466" s="2" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="E466" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F466" s="1" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="G466" s="1" t="s">
         <v>30</v>
@@ -20058,19 +20049,19 @@
         <v>466</v>
       </c>
       <c r="B467" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C467" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D467" s="2" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="E467" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F467" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="G467" s="1" t="s">
         <v>30</v>
@@ -20088,19 +20079,19 @@
         <v>467</v>
       </c>
       <c r="B468" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C468" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D468" s="2" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="E468" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F468" s="1" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="G468" s="1" t="s">
         <v>30</v>
@@ -20118,19 +20109,19 @@
         <v>468</v>
       </c>
       <c r="B469" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C469" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D469" s="2" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="E469" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F469" s="1" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="G469" s="1" t="s">
         <v>30</v>
@@ -20148,19 +20139,19 @@
         <v>469</v>
       </c>
       <c r="B470" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C470" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D470" s="2" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="E470" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F470" s="1" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="G470" s="1" t="s">
         <v>30</v>
@@ -20178,19 +20169,19 @@
         <v>470</v>
       </c>
       <c r="B471" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C471" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D471" s="2" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="E471" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F471" s="1" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="G471" s="1" t="s">
         <v>30</v>
@@ -20208,19 +20199,19 @@
         <v>471</v>
       </c>
       <c r="B472" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C472" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D472" s="2" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="E472" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F472" s="1" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="G472" s="1" t="s">
         <v>30</v>
@@ -20238,19 +20229,19 @@
         <v>472</v>
       </c>
       <c r="B473" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C473" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D473" s="2" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="E473" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F473" s="1" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="G473" s="1" t="s">
         <v>30</v>
@@ -20268,19 +20259,19 @@
         <v>473</v>
       </c>
       <c r="B474" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C474" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D474" s="2" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="E474" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F474" s="1" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="G474" s="1" t="s">
         <v>30</v>
@@ -20298,19 +20289,19 @@
         <v>474</v>
       </c>
       <c r="B475" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C475" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D475" s="2" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="E475" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F475" s="1" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="G475" s="1" t="s">
         <v>30</v>
@@ -20328,19 +20319,19 @@
         <v>475</v>
       </c>
       <c r="B476" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C476" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D476" s="2" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="E476" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F476" s="1" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="G476" s="1" t="s">
         <v>30</v>
@@ -20358,19 +20349,19 @@
         <v>476</v>
       </c>
       <c r="B477" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C477" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D477" s="2" t="s">
-        <v>1281</v>
+        <v>1277</v>
       </c>
       <c r="E477" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F477" s="1" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="G477" s="1" t="s">
         <v>30</v>
@@ -20388,19 +20379,19 @@
         <v>477</v>
       </c>
       <c r="B478" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C478" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D478" s="2" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="E478" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F478" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="G478" s="1" t="s">
         <v>30</v>
@@ -20418,19 +20409,19 @@
         <v>478</v>
       </c>
       <c r="B479" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C479" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D479" s="2" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="E479" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F479" s="1" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="G479" s="1" t="s">
         <v>30</v>
@@ -20448,19 +20439,19 @@
         <v>479</v>
       </c>
       <c r="B480" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C480" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D480" s="2" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="E480" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F480" s="1" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="G480" s="1" t="s">
         <v>30</v>
@@ -20478,19 +20469,19 @@
         <v>480</v>
       </c>
       <c r="B481" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C481" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D481" s="2" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="E481" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F481" s="1" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="G481" s="1" t="s">
         <v>30</v>
@@ -20508,19 +20499,19 @@
         <v>481</v>
       </c>
       <c r="B482" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C482" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D482" s="2" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="E482" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F482" s="1" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="G482" s="1" t="s">
         <v>30</v>
@@ -20538,19 +20529,19 @@
         <v>482</v>
       </c>
       <c r="B483" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C483" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D483" s="2" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="E483" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F483" s="1" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="G483" s="1" t="s">
         <v>30</v>
@@ -20568,13 +20559,13 @@
         <v>483</v>
       </c>
       <c r="B484" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C484" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D484" s="2" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="E484" s="1" t="s">
         <v>19</v>
@@ -20598,19 +20589,19 @@
         <v>484</v>
       </c>
       <c r="B485" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C485" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D485" s="2" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="E485" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F485" s="1" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="G485" s="1" t="s">
         <v>30</v>
@@ -20628,19 +20619,19 @@
         <v>485</v>
       </c>
       <c r="B486" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C486" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D486" s="2" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
       <c r="E486" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F486" s="1" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="G486" s="1" t="s">
         <v>30</v>
@@ -20658,19 +20649,19 @@
         <v>486</v>
       </c>
       <c r="B487" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C487" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D487" s="2" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="E487" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F487" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="G487" s="1" t="s">
         <v>30</v>
@@ -20688,19 +20679,19 @@
         <v>487</v>
       </c>
       <c r="B488" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C488" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D488" s="2" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="E488" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F488" s="1" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="G488" s="1" t="s">
         <v>30</v>
@@ -20718,13 +20709,13 @@
         <v>488</v>
       </c>
       <c r="B489" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C489" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D489" s="2" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
       <c r="E489" s="1" t="s">
         <v>21</v>
@@ -20742,7 +20733,7 @@
         <v>574</v>
       </c>
       <c r="J489" s="3" t="s">
-        <v>1310</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="490" spans="1:10">
@@ -20750,19 +20741,19 @@
         <v>489</v>
       </c>
       <c r="B490" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C490" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D490" s="2" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="E490" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F490" s="1" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="G490" s="1" t="s">
         <v>30</v>
@@ -20780,19 +20771,19 @@
         <v>490</v>
       </c>
       <c r="B491" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C491" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D491" s="2" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="E491" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F491" s="1" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="G491" s="1" t="s">
         <v>30</v>
@@ -20810,19 +20801,19 @@
         <v>491</v>
       </c>
       <c r="B492" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C492" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D492" s="2" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="E492" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F492" s="1" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="G492" s="1" t="s">
         <v>30</v>
@@ -20840,19 +20831,19 @@
         <v>492</v>
       </c>
       <c r="B493" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C493" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D493" s="2" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="E493" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F493" s="1" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="G493" s="1" t="s">
         <v>30</v>
@@ -20870,19 +20861,19 @@
         <v>493</v>
       </c>
       <c r="B494" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C494" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D494" s="2" t="s">
-        <v>1280</v>
+        <v>1276</v>
       </c>
       <c r="E494" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F494" s="1" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="G494" s="1" t="s">
         <v>30</v>
@@ -20900,7 +20891,7 @@
         <v>494</v>
       </c>
       <c r="B495" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C495" s="1" t="s">
         <v>11</v>
@@ -20909,7 +20900,7 @@
         <v>816</v>
       </c>
       <c r="E495" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F495" s="1" t="s">
         <v>736</v>
@@ -20930,7 +20921,7 @@
         <v>495</v>
       </c>
       <c r="B496" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C496" s="1" t="s">
         <v>11</v>
@@ -20960,13 +20951,13 @@
         <v>496</v>
       </c>
       <c r="B497" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C497" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D497" s="2" t="s">
-        <v>1318</v>
+        <v>1314</v>
       </c>
       <c r="E497" s="1" t="s">
         <v>19</v>
@@ -20990,13 +20981,13 @@
         <v>497</v>
       </c>
       <c r="B498" s="52" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C498" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D498" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="E498" s="1" t="s">
         <v>19</v>
@@ -21020,19 +21011,19 @@
         <v>498</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="C499" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D499" s="2" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="E499" s="1" t="s">
-        <v>21</v>
+        <v>964</v>
       </c>
       <c r="F499" s="1" t="s">
-        <v>23</v>
+        <v>373</v>
       </c>
       <c r="G499" s="1" t="s">
         <v>30</v>
@@ -21050,19 +21041,19 @@
         <v>499</v>
       </c>
       <c r="B500" s="2" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
       <c r="C500" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D500" s="2" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="E500" s="1" t="s">
-        <v>965</v>
+        <v>30</v>
       </c>
       <c r="F500" s="1" t="s">
-        <v>1271</v>
+        <v>23</v>
       </c>
       <c r="G500" s="1" t="s">
         <v>30</v>
@@ -21094,7 +21085,7 @@
   <conditionalFormatting sqref="D448 D2:D357">
     <cfRule type="duplicateValues" dxfId="27" priority="84"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G205 E250:E1048576 E1:E248">
+  <conditionalFormatting sqref="E1:E248 G205 E250:E1048576">
     <cfRule type="cellIs" dxfId="26" priority="14" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
@@ -23399,7 +23390,7 @@
         <v>574</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="53" spans="1:10" s="3" customFormat="1">
@@ -23419,7 +23410,7 @@
         <v>68</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>14</v>

--- a/data_printer.xlsx
+++ b/data_printer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erick\Desktop\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBB567A0-35B9-4349-B86C-53FDB7C19E2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA920499-E609-4E06-8C53-561CFCE2A39D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A8AA41B5-7AA1-4FF7-A9B8-54B8A4E1AF28}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4377" uniqueCount="1321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4378" uniqueCount="1323">
   <si>
     <t>INDICE</t>
   </si>
@@ -1864,9 +1864,6 @@
     <t>INSTALADA NO MERCADO ANDRADE (1212/2022/1); FOI RETIRADA NO DIA 15/04/2025 PARA MANUTENÇÃO; FEITA MANUTENÇÃO POR FLAVIO ANDRADE LIMPEZA INTERNA EXTENA FUSAO BELT UNIDADE DE IMAGENS AS 4 LIXEIRA E RESTALADA NO MERCADO ANDRADE 14/05/2025;</t>
   </si>
   <si>
-    <t>_MERCADO ANDRADE - CPD</t>
-  </si>
-  <si>
     <t>XAABJ99407</t>
   </si>
   <si>
@@ -2404,9 +2401,6 @@
     <t>CENTRO POP - ADM</t>
   </si>
   <si>
-    <t xml:space="preserve">_MERCADO ANDRADE </t>
-  </si>
-  <si>
     <t>RETIRADA DA SEPOL GABINETE 10/10/2025; INSTALADA MERCADO ANDRADE 12/10/2025;</t>
   </si>
   <si>
@@ -3874,9 +3868,6 @@
     <t>XC75051307</t>
   </si>
   <si>
-    <t>instalação em 18/03/2026 na caixa, impressora quebrada não para de erro papel preso05/05/2026;</t>
-  </si>
-  <si>
     <t>CRECHE - C.M. ALEXANDRE M. MARTINS</t>
   </si>
   <si>
@@ -4001,6 +3992,21 @@
   </si>
   <si>
     <t>ESTAVA NA SEPOL; COLOCADA SEDUC RH NO DIA 11/07/2025  FOI TROCADO CILINDRO; RETIRADA DA SEDUC RH POR PROBLEMAS DE REDE DA IMPRESSORA 01/08/2025; INSTALADA BELLA CASA CABO FRIO 17/09/2025; INSTALADA DIVIDA ATIVA PAÇO 18/11/2025; Retirada do paço com problema de rede 20/08/2026;</t>
+  </si>
+  <si>
+    <t>XC75036979</t>
+  </si>
+  <si>
+    <t>instalada na escola menino robson em 15/05/2026;</t>
+  </si>
+  <si>
+    <t>instalação em 18/03/2026 na caixa, impressora quebrada não para de erro papel preso05/05/2026; instalada na escola fernando de carvalho 16/08/2026;</t>
+  </si>
+  <si>
+    <t>_MERCADO ANDRADE MM</t>
+  </si>
+  <si>
+    <t>_MERCADO ANDRADE MM - CPD</t>
   </si>
 </sst>
 </file>
@@ -5447,7 +5453,7 @@
         <v>13</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>14</v>
@@ -5459,7 +5465,7 @@
         <v>574</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5479,7 +5485,7 @@
         <v>13</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>14</v>
@@ -5523,7 +5529,7 @@
         <v>574</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -5543,7 +5549,7 @@
         <v>13</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>14</v>
@@ -5555,7 +5561,7 @@
         <v>574</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -5619,7 +5625,7 @@
         <v>574</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -5719,7 +5725,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>11</v>
@@ -5728,7 +5734,7 @@
         <v>39</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>40</v>
@@ -5743,7 +5749,7 @@
         <v>574</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -5751,7 +5757,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>11</v>
@@ -5760,10 +5766,10 @@
         <v>39</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>1317</v>
+        <v>1314</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>19</v>
@@ -5775,7 +5781,7 @@
         <v>574</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -5789,7 +5795,7 @@
         <v>11</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>28</v>
@@ -5807,7 +5813,7 @@
         <v>574</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -5827,7 +5833,7 @@
         <v>350</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>14</v>
@@ -5839,7 +5845,7 @@
         <v>574</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -5853,7 +5859,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>28</v>
@@ -5871,7 +5877,7 @@
         <v>574</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -6016,7 +6022,7 @@
         <v>19</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>14</v>
@@ -6028,7 +6034,7 @@
         <v>574</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -6092,7 +6098,7 @@
         <v>574</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -6112,7 +6118,7 @@
         <v>76</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>14</v>
@@ -6310,7 +6316,7 @@
         <v>574</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -6426,7 +6432,7 @@
         <v>13</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="G33" s="4" t="s">
         <v>14</v>
@@ -6438,7 +6444,7 @@
         <v>574</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -6458,7 +6464,7 @@
         <v>19</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>1309</v>
+        <v>1306</v>
       </c>
       <c r="G34" s="4" t="s">
         <v>14</v>
@@ -6470,7 +6476,7 @@
         <v>574</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>1310</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -6519,10 +6525,10 @@
         <v>84</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>14</v>
@@ -6534,7 +6540,7 @@
         <v>574</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -6691,7 +6697,7 @@
         <v>574</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
     </row>
     <row r="42" spans="1:10">
@@ -7010,7 +7016,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>11</v>
@@ -7034,7 +7040,7 @@
         <v>574</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -7042,7 +7048,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>11</v>
@@ -7066,7 +7072,7 @@
         <v>574</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -7074,7 +7080,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>11</v>
@@ -7086,7 +7092,7 @@
         <v>68</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>68</v>
@@ -7098,7 +7104,7 @@
         <v>574</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -7112,7 +7118,7 @@
         <v>11</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>21</v>
@@ -7591,7 +7597,7 @@
         <v>11</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>21</v>
@@ -7626,7 +7632,7 @@
         <v>19</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="G72" s="4" t="s">
         <v>14</v>
@@ -7638,7 +7644,7 @@
         <v>574</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -7873,10 +7879,10 @@
         <v>11</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>162</v>
@@ -7908,7 +7914,7 @@
         <v>164</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>165</v>
@@ -7937,10 +7943,10 @@
         <v>11</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>167</v>
@@ -7963,10 +7969,10 @@
         <v>11</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>168</v>
@@ -7989,7 +7995,7 @@
         <v>11</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>28</v>
@@ -8015,10 +8021,10 @@
         <v>11</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>170</v>
@@ -8050,7 +8056,7 @@
         <v>172</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>173</v>
@@ -8079,7 +8085,7 @@
         <v>11</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>21</v>
@@ -8097,7 +8103,7 @@
         <v>574</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="88" spans="1:10">
@@ -8111,10 +8117,10 @@
         <v>11</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>176</v>
@@ -8143,10 +8149,10 @@
         <v>11</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>178</v>
@@ -8172,13 +8178,13 @@
         <v>11</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>30</v>
@@ -8190,7 +8196,7 @@
         <v>574</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
     </row>
     <row r="91" spans="1:10">
@@ -8204,10 +8210,10 @@
         <v>11</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>180</v>
@@ -8236,10 +8242,10 @@
         <v>11</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>181</v>
@@ -8262,10 +8268,10 @@
         <v>11</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>182</v>
@@ -8291,7 +8297,7 @@
         <v>184</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>185</v>
@@ -8306,7 +8312,7 @@
         <v>574</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="95" spans="1:10">
@@ -8320,10 +8326,10 @@
         <v>11</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>190</v>
@@ -8538,7 +8544,7 @@
         <v>76</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="G102" s="4" t="s">
         <v>14</v>
@@ -8550,7 +8556,7 @@
         <v>574</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="103" spans="1:10">
@@ -8724,7 +8730,7 @@
         <v>11</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>21</v>
@@ -9218,7 +9224,7 @@
         <v>574</v>
       </c>
       <c r="J123" s="3" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="124" spans="1:10">
@@ -9232,13 +9238,13 @@
         <v>11</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="G124" s="1" t="s">
         <v>30</v>
@@ -9250,7 +9256,7 @@
         <v>574</v>
       </c>
       <c r="J124" s="3" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="125" spans="1:10">
@@ -9270,7 +9276,7 @@
         <v>68</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="G125" s="4" t="s">
         <v>14</v>
@@ -9282,7 +9288,7 @@
         <v>574</v>
       </c>
       <c r="J125" s="3" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="126" spans="1:10">
@@ -9296,13 +9302,13 @@
         <v>11</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="E126" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="G126" s="1" t="s">
         <v>30</v>
@@ -9328,7 +9334,7 @@
         <v>11</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="E127" s="4" t="s">
         <v>21</v>
@@ -9410,7 +9416,7 @@
         <v>574</v>
       </c>
       <c r="J129" s="3" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="130" spans="1:10">
@@ -9474,7 +9480,7 @@
         <v>574</v>
       </c>
       <c r="J131" s="3" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="132" spans="1:10">
@@ -9494,7 +9500,7 @@
         <v>19</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>1287</v>
+        <v>1284</v>
       </c>
       <c r="G132" s="4" t="s">
         <v>14</v>
@@ -9506,7 +9512,7 @@
         <v>574</v>
       </c>
       <c r="J132" s="3" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="133" spans="1:10">
@@ -9526,7 +9532,7 @@
         <v>19</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="G133" s="4" t="s">
         <v>14</v>
@@ -9538,7 +9544,7 @@
         <v>574</v>
       </c>
       <c r="J133" s="3" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="134" spans="1:10">
@@ -9558,7 +9564,7 @@
         <v>19</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="G134" s="4" t="s">
         <v>14</v>
@@ -9567,10 +9573,10 @@
         <v>45936</v>
       </c>
       <c r="I134" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J134" s="3" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="135" spans="1:10">
@@ -9602,7 +9608,7 @@
         <v>574</v>
       </c>
       <c r="J135" s="3" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="136" spans="1:10">
@@ -9622,7 +9628,7 @@
         <v>19</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="G136" s="4" t="s">
         <v>14</v>
@@ -9634,7 +9640,7 @@
         <v>574</v>
       </c>
       <c r="J136" s="3" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="137" spans="1:10">
@@ -9686,7 +9692,7 @@
         <v>13</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="G138" s="4" t="s">
         <v>14</v>
@@ -9698,7 +9704,7 @@
         <v>574</v>
       </c>
       <c r="J138" s="3" t="s">
-        <v>1301</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="139" spans="1:10">
@@ -9718,7 +9724,7 @@
         <v>13</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="G139" s="4" t="s">
         <v>14</v>
@@ -9727,10 +9733,10 @@
         <v>45952</v>
       </c>
       <c r="I139" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J139" s="3" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="140" spans="1:10">
@@ -9794,7 +9800,7 @@
         <v>574</v>
       </c>
       <c r="J141" s="12" t="s">
-        <v>1308</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="142" spans="1:10">
@@ -9814,7 +9820,7 @@
         <v>13</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="G142" s="4" t="s">
         <v>14</v>
@@ -9826,7 +9832,7 @@
         <v>574</v>
       </c>
       <c r="J142" s="3" t="s">
-        <v>1300</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="143" spans="1:10">
@@ -9834,7 +9840,7 @@
         <v>142</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>83</v>
@@ -9846,7 +9852,7 @@
         <v>68</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="G143" s="1" t="s">
         <v>68</v>
@@ -9876,7 +9882,7 @@
         <v>68</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="G144" s="4" t="s">
         <v>14</v>
@@ -9888,7 +9894,7 @@
         <v>574</v>
       </c>
       <c r="J144" s="3" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="145" spans="1:10">
@@ -9902,13 +9908,13 @@
         <v>83</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="G145" s="4" t="s">
         <v>14</v>
@@ -9920,7 +9926,7 @@
         <v>574</v>
       </c>
       <c r="J145" s="3" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
     </row>
     <row r="146" spans="1:10">
@@ -9940,7 +9946,7 @@
         <v>68</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="G146" s="13" t="s">
         <v>14</v>
@@ -9972,7 +9978,7 @@
         <v>19</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>1283</v>
+        <v>1280</v>
       </c>
       <c r="G147" s="13" t="s">
         <v>14</v>
@@ -9984,7 +9990,7 @@
         <v>574</v>
       </c>
       <c r="J147" s="3" t="s">
-        <v>1285</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="148" spans="1:10">
@@ -9998,13 +10004,13 @@
         <v>83</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="G148" s="13" t="s">
         <v>14</v>
@@ -10016,7 +10022,7 @@
         <v>574</v>
       </c>
       <c r="J148" s="3" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="149" spans="1:10">
@@ -10030,13 +10036,13 @@
         <v>83</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="G149" s="13" t="s">
         <v>14</v>
@@ -10048,7 +10054,7 @@
         <v>574</v>
       </c>
       <c r="J149" s="3" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="150" spans="1:10">
@@ -10062,13 +10068,13 @@
         <v>83</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>1280</v>
+        <v>1277</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
       <c r="G150" s="13" t="s">
         <v>14</v>
@@ -10077,10 +10083,10 @@
         <v>46162</v>
       </c>
       <c r="I150" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J150" s="3" t="s">
-        <v>1282</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="151" spans="1:10">
@@ -10094,13 +10100,13 @@
         <v>83</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="G151" s="13" t="s">
         <v>14</v>
@@ -10112,7 +10118,7 @@
         <v>574</v>
       </c>
       <c r="J151" s="3" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="152" spans="1:10">
@@ -10126,13 +10132,13 @@
         <v>83</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="G152" s="13" t="s">
         <v>14</v>
@@ -10141,7 +10147,7 @@
         <v>46154</v>
       </c>
       <c r="I152" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J152" s="24"/>
     </row>
@@ -10156,13 +10162,13 @@
         <v>83</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="G153" s="13" t="s">
         <v>14</v>
@@ -10171,7 +10177,7 @@
         <v>46154</v>
       </c>
       <c r="I153" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J153" s="24"/>
     </row>
@@ -10186,13 +10192,13 @@
         <v>83</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="G154" s="13" t="s">
         <v>14</v>
@@ -10201,10 +10207,10 @@
         <v>46150</v>
       </c>
       <c r="I154" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J154" s="3" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="155" spans="1:10">
@@ -10218,13 +10224,13 @@
         <v>83</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>1293</v>
+        <v>1290</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
       <c r="G155" s="13" t="s">
         <v>14</v>
@@ -10236,7 +10242,7 @@
         <v>574</v>
       </c>
       <c r="J155" s="3" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="156" spans="1:10">
@@ -10250,13 +10256,13 @@
         <v>83</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>1296</v>
+        <v>1293</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>1297</v>
+        <v>1294</v>
       </c>
       <c r="G156" s="13" t="s">
         <v>14</v>
@@ -10268,7 +10274,7 @@
         <v>574</v>
       </c>
       <c r="J156" s="3" t="s">
-        <v>1298</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="157" spans="1:10">
@@ -10282,13 +10288,13 @@
         <v>83</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>1305</v>
+        <v>1302</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>1303</v>
+        <v>1300</v>
       </c>
       <c r="G157" s="13" t="s">
         <v>14</v>
@@ -10300,7 +10306,7 @@
         <v>574</v>
       </c>
       <c r="J157" s="3" t="s">
-        <v>1304</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="158" spans="1:10">
@@ -10314,13 +10320,13 @@
         <v>83</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
       <c r="G158" s="1" t="s">
         <v>14</v>
@@ -10338,13 +10344,13 @@
         <v>158</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>21</v>
@@ -10362,7 +10368,7 @@
         <v>574</v>
       </c>
       <c r="J159" s="3" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="160" spans="1:10">
@@ -10446,7 +10452,7 @@
         <v>68</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="G162" s="4" t="s">
         <v>14</v>
@@ -10458,7 +10464,7 @@
         <v>574</v>
       </c>
       <c r="J162" s="3" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="163" spans="1:10">
@@ -10522,7 +10528,7 @@
         <v>574</v>
       </c>
       <c r="J164" s="7" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
     </row>
     <row r="165" spans="1:10">
@@ -10542,7 +10548,7 @@
         <v>350</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="G165" s="4" t="s">
         <v>14</v>
@@ -10551,10 +10557,10 @@
         <v>45959</v>
       </c>
       <c r="I165" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J165" s="3" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
     </row>
     <row r="166" spans="1:10">
@@ -10659,7 +10665,7 @@
         <v>350</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="G169" s="4" t="s">
         <v>14</v>
@@ -10671,7 +10677,7 @@
         <v>574</v>
       </c>
       <c r="J169" s="3" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="170" spans="1:10">
@@ -10796,7 +10802,7 @@
         <v>574</v>
       </c>
       <c r="J173" s="3" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="174" spans="1:10">
@@ -10935,7 +10941,7 @@
         <v>188</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>189</v>
@@ -10944,7 +10950,7 @@
         <v>14</v>
       </c>
       <c r="I178" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="179" spans="1:10">
@@ -10958,13 +10964,13 @@
         <v>83</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="E179" s="1" t="s">
+        <v>953</v>
+      </c>
+      <c r="F179" s="1" t="s">
         <v>955</v>
-      </c>
-      <c r="F179" s="1" t="s">
-        <v>957</v>
       </c>
       <c r="G179" s="4" t="s">
         <v>14</v>
@@ -11006,7 +11012,7 @@
         <v>574</v>
       </c>
       <c r="J180" s="3" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="181" spans="1:10">
@@ -11023,10 +11029,10 @@
         <v>286</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="G181" s="4" t="s">
         <v>14</v>
@@ -11049,13 +11055,13 @@
         <v>83</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="G182" s="4" t="s">
         <v>14</v>
@@ -11067,7 +11073,7 @@
         <v>574</v>
       </c>
       <c r="J182" s="3" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="183" spans="1:10">
@@ -11084,10 +11090,10 @@
         <v>287</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="G183" s="4" t="s">
         <v>14</v>
@@ -11769,7 +11775,7 @@
         <v>574</v>
       </c>
       <c r="J206" s="3" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="207" spans="1:10">
@@ -11786,10 +11792,10 @@
         <v>314</v>
       </c>
       <c r="E207" s="4" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="F207" s="4" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="G207" s="4" t="s">
         <v>14</v>
@@ -11847,13 +11853,13 @@
         <v>11</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="E209" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="G209" s="4" t="s">
         <v>14</v>
@@ -11877,7 +11883,7 @@
         <v>11</v>
       </c>
       <c r="D210" s="5" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="E210" s="4" t="s">
         <v>21</v>
@@ -11895,7 +11901,7 @@
         <v>574</v>
       </c>
       <c r="J210" s="3" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
     </row>
     <row r="211" spans="1:10">
@@ -11912,10 +11918,10 @@
         <v>316</v>
       </c>
       <c r="E211" s="4" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="F211" s="4" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="G211" s="4" t="s">
         <v>14</v>
@@ -11979,7 +11985,7 @@
         <v>19</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="G213" s="4" t="s">
         <v>14</v>
@@ -11991,7 +11997,7 @@
         <v>574</v>
       </c>
       <c r="J213" s="8" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="214" spans="1:10">
@@ -12043,7 +12049,7 @@
         <v>68</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
       <c r="G215" s="4" t="s">
         <v>14</v>
@@ -12055,7 +12061,7 @@
         <v>574</v>
       </c>
       <c r="J215" s="3" t="s">
-        <v>1312</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="216" spans="1:10">
@@ -12069,13 +12075,13 @@
         <v>11</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="E216" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="G216" s="1" t="s">
         <v>30</v>
@@ -12087,7 +12093,7 @@
         <v>574</v>
       </c>
       <c r="J216" s="3" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
     </row>
     <row r="217" spans="1:10">
@@ -12119,7 +12125,7 @@
         <v>574</v>
       </c>
       <c r="J217" s="3" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="218" spans="1:10">
@@ -12171,7 +12177,7 @@
         <v>19</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="G219" s="4" t="s">
         <v>14</v>
@@ -12183,7 +12189,7 @@
         <v>574</v>
       </c>
       <c r="J219" s="3" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="220" spans="1:10">
@@ -12203,7 +12209,7 @@
         <v>19</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="G220" s="4" t="s">
         <v>14</v>
@@ -12215,7 +12221,7 @@
         <v>574</v>
       </c>
       <c r="J220" s="3" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="221" spans="1:10">
@@ -12235,7 +12241,7 @@
         <v>76</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="G221" s="4" t="s">
         <v>14</v>
@@ -12247,7 +12253,7 @@
         <v>574</v>
       </c>
       <c r="J221" s="3" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="222" spans="1:10">
@@ -12279,7 +12285,7 @@
         <v>574</v>
       </c>
       <c r="J222" s="3" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
     </row>
     <row r="223" spans="1:10">
@@ -12439,7 +12445,7 @@
         <v>574</v>
       </c>
       <c r="J227" s="3" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="228" spans="1:10">
@@ -12459,7 +12465,7 @@
         <v>19</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="G228" s="4" t="s">
         <v>14</v>
@@ -12471,7 +12477,7 @@
         <v>574</v>
       </c>
       <c r="J228" s="3" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="229" spans="1:10">
@@ -12523,7 +12529,7 @@
         <v>19</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="G230" s="4" t="s">
         <v>14</v>
@@ -12532,10 +12538,10 @@
         <v>45933</v>
       </c>
       <c r="I230" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J230" s="3" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="231" spans="1:10">
@@ -12567,7 +12573,7 @@
         <v>574</v>
       </c>
       <c r="J231" s="3" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
     </row>
     <row r="232" spans="1:10">
@@ -12587,7 +12593,7 @@
         <v>19</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="G232" s="4" t="s">
         <v>14</v>
@@ -12599,7 +12605,7 @@
         <v>574</v>
       </c>
       <c r="J232" s="3" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="233" spans="1:10">
@@ -12663,7 +12669,7 @@
         <v>574</v>
       </c>
       <c r="J234" s="3" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="235" spans="1:10">
@@ -12683,7 +12689,7 @@
         <v>19</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="G235" s="4" t="s">
         <v>14</v>
@@ -12695,7 +12701,7 @@
         <v>574</v>
       </c>
       <c r="J235" s="3" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="236" spans="1:10">
@@ -12741,13 +12747,13 @@
         <v>11</v>
       </c>
       <c r="D237" s="5" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="E237" s="1" t="s">
         <v>350</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="G237" s="4" t="s">
         <v>14</v>
@@ -12759,7 +12765,7 @@
         <v>574</v>
       </c>
       <c r="J237" s="3" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="238" spans="1:10">
@@ -12811,7 +12817,7 @@
         <v>19</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="G239" s="4" t="s">
         <v>14</v>
@@ -12823,7 +12829,7 @@
         <v>574</v>
       </c>
       <c r="J239" s="3" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="240" spans="1:10">
@@ -12875,7 +12881,7 @@
         <v>76</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="G241" s="4" t="s">
         <v>14</v>
@@ -12887,7 +12893,7 @@
         <v>574</v>
       </c>
       <c r="J241" s="7" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="242" spans="1:10">
@@ -12907,7 +12913,7 @@
         <v>19</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="G242" s="4" t="s">
         <v>14</v>
@@ -12939,7 +12945,7 @@
         <v>19</v>
       </c>
       <c r="F243" s="50" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="G243" s="4" t="s">
         <v>14</v>
@@ -12951,7 +12957,7 @@
         <v>574</v>
       </c>
       <c r="J243" s="7" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="244" spans="1:10">
@@ -12971,7 +12977,7 @@
         <v>19</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="G244" s="4" t="s">
         <v>14</v>
@@ -12980,10 +12986,10 @@
         <v>44127</v>
       </c>
       <c r="I244" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J244" s="3" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="245" spans="1:10">
@@ -13003,7 +13009,7 @@
         <v>19</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="G245" s="4" t="s">
         <v>14</v>
@@ -13015,7 +13021,7 @@
         <v>574</v>
       </c>
       <c r="J245" s="3" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="246" spans="1:10">
@@ -13035,7 +13041,7 @@
         <v>19</v>
       </c>
       <c r="F246" s="41" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="G246" s="4" t="s">
         <v>14</v>
@@ -13047,7 +13053,7 @@
         <v>574</v>
       </c>
       <c r="J246" s="8" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="247" spans="1:10">
@@ -13067,7 +13073,7 @@
         <v>350</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="G247" s="13" t="s">
         <v>14</v>
@@ -13079,7 +13085,7 @@
         <v>574</v>
       </c>
       <c r="J247" s="8" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="248" spans="1:10">
@@ -13096,10 +13102,10 @@
         <v>573</v>
       </c>
       <c r="E248" s="1" t="s">
+        <v>953</v>
+      </c>
+      <c r="F248" s="1" t="s">
         <v>955</v>
-      </c>
-      <c r="F248" s="1" t="s">
-        <v>957</v>
       </c>
       <c r="G248" s="1" t="s">
         <v>14</v>
@@ -13126,10 +13132,10 @@
         <v>559</v>
       </c>
       <c r="E249" s="33" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>608</v>
+        <v>1322</v>
       </c>
       <c r="G249" s="13" t="s">
         <v>14</v>
@@ -13141,7 +13147,7 @@
         <v>574</v>
       </c>
       <c r="J249" s="8" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
     </row>
     <row r="250" spans="1:10">
@@ -13161,7 +13167,7 @@
         <v>68</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
       <c r="G250" s="4" t="s">
         <v>14</v>
@@ -13173,7 +13179,7 @@
         <v>574</v>
       </c>
       <c r="J250" s="3" t="s">
-        <v>1319</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="251" spans="1:10">
@@ -13205,7 +13211,7 @@
         <v>574</v>
       </c>
       <c r="J251" s="3" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="252" spans="1:10">
@@ -13237,7 +13243,7 @@
         <v>574</v>
       </c>
       <c r="J252" s="3" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="253" spans="1:10">
@@ -13245,7 +13251,7 @@
         <v>252</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>11</v>
@@ -13254,10 +13260,10 @@
         <v>39</v>
       </c>
       <c r="E253" s="4" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="G253" s="1" t="s">
         <v>19</v>
@@ -13315,10 +13321,10 @@
         <v>372</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>788</v>
+        <v>1321</v>
       </c>
       <c r="G255" s="4" t="s">
         <v>14</v>
@@ -13330,7 +13336,7 @@
         <v>574</v>
       </c>
       <c r="J255" s="3" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="256" spans="1:10">
@@ -13344,7 +13350,7 @@
         <v>83</v>
       </c>
       <c r="D256" s="10" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="E256" s="1" t="s">
         <v>30</v>
@@ -13362,7 +13368,7 @@
         <v>574</v>
       </c>
       <c r="J256" s="3" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
     </row>
     <row r="257" spans="1:10">
@@ -13411,7 +13417,7 @@
         <v>377</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="F258" s="1" t="s">
         <v>378</v>
@@ -13437,10 +13443,10 @@
         <v>11</v>
       </c>
       <c r="D259" s="10" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="F259" s="1" t="s">
         <v>380</v>
@@ -13472,7 +13478,7 @@
         <v>381</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="F260" s="1" t="s">
         <v>382</v>
@@ -13501,7 +13507,7 @@
         <v>383</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="F261" s="1" t="s">
         <v>175</v>
@@ -13527,7 +13533,7 @@
         <v>83</v>
       </c>
       <c r="D262" s="35" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="E262" s="1" t="s">
         <v>30</v>
@@ -13545,7 +13551,7 @@
         <v>574</v>
       </c>
       <c r="J262" s="3" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
     </row>
     <row r="263" spans="1:10">
@@ -13577,7 +13583,7 @@
         <v>574</v>
       </c>
       <c r="J263" s="3" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="264" spans="1:10">
@@ -13597,7 +13603,7 @@
         <v>19</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="G264" s="4" t="s">
         <v>14</v>
@@ -13609,7 +13615,7 @@
         <v>574</v>
       </c>
       <c r="J264" s="3" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="265" spans="1:10">
@@ -13629,7 +13635,7 @@
         <v>19</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="G265" s="4" t="s">
         <v>14</v>
@@ -13641,7 +13647,7 @@
         <v>574</v>
       </c>
       <c r="J265" s="3" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="266" spans="1:10">
@@ -13737,7 +13743,7 @@
         <v>574</v>
       </c>
       <c r="J268" s="3" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="269" spans="1:10">
@@ -13865,7 +13871,7 @@
         <v>574</v>
       </c>
       <c r="J272" s="3" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="273" spans="1:10">
@@ -13885,7 +13891,7 @@
         <v>13</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="G273" s="4" t="s">
         <v>14</v>
@@ -13894,10 +13900,10 @@
         <v>45649</v>
       </c>
       <c r="I273" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J273" s="3" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="274" spans="1:10">
@@ -13929,7 +13935,7 @@
         <v>574</v>
       </c>
       <c r="J274" s="3" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="275" spans="1:10">
@@ -13981,7 +13987,7 @@
         <v>68</v>
       </c>
       <c r="F276" s="4" t="s">
-        <v>1299</v>
+        <v>1296</v>
       </c>
       <c r="G276" s="4" t="s">
         <v>14</v>
@@ -14141,7 +14147,7 @@
         <v>350</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="G281" s="1" t="s">
         <v>14</v>
@@ -14153,7 +14159,7 @@
         <v>574</v>
       </c>
       <c r="J281" s="3" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="282" spans="1:10">
@@ -14173,7 +14179,7 @@
         <v>68</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="G282" s="1" t="s">
         <v>14</v>
@@ -14205,7 +14211,7 @@
         <v>68</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="G283" s="1" t="s">
         <v>14</v>
@@ -14237,7 +14243,7 @@
         <v>68</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="G284" s="1" t="s">
         <v>14</v>
@@ -14269,7 +14275,7 @@
         <v>68</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="G285" s="1" t="s">
         <v>14</v>
@@ -14301,7 +14307,7 @@
         <v>68</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="G286" s="1" t="s">
         <v>14</v>
@@ -14333,7 +14339,7 @@
         <v>68</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="G287" s="1" t="s">
         <v>14</v>
@@ -14365,7 +14371,7 @@
         <v>68</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="G288" s="1" t="s">
         <v>14</v>
@@ -14397,7 +14403,7 @@
         <v>68</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="G289" s="1" t="s">
         <v>14</v>
@@ -14429,7 +14435,7 @@
         <v>68</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="G290" s="1" t="s">
         <v>14</v>
@@ -14461,7 +14467,7 @@
         <v>68</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="G291" s="1" t="s">
         <v>14</v>
@@ -14493,7 +14499,7 @@
         <v>68</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="G292" s="1" t="s">
         <v>14</v>
@@ -14525,7 +14531,7 @@
         <v>68</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="G293" s="1" t="s">
         <v>14</v>
@@ -14557,7 +14563,7 @@
         <v>68</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="G294" s="1" t="s">
         <v>14</v>
@@ -14589,7 +14595,7 @@
         <v>76</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="G295" s="1" t="s">
         <v>14</v>
@@ -14598,10 +14604,10 @@
         <v>45597</v>
       </c>
       <c r="I295" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J295" s="3" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
     </row>
     <row r="296" spans="1:10">
@@ -14621,7 +14627,7 @@
         <v>68</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="G296" s="1" t="s">
         <v>14</v>
@@ -14653,7 +14659,7 @@
         <v>68</v>
       </c>
       <c r="F297" s="4" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="G297" s="1" t="s">
         <v>14</v>
@@ -14685,7 +14691,7 @@
         <v>68</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="G298" s="1" t="s">
         <v>14</v>
@@ -14717,7 +14723,7 @@
         <v>68</v>
       </c>
       <c r="F299" s="4" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="G299" s="1" t="s">
         <v>14</v>
@@ -15165,7 +15171,7 @@
         <v>76</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="G313" s="1" t="s">
         <v>14</v>
@@ -15209,7 +15215,7 @@
         <v>574</v>
       </c>
       <c r="J314" s="3" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
     </row>
     <row r="315" spans="1:10">
@@ -15229,7 +15235,7 @@
         <v>76</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="G315" s="1" t="s">
         <v>14</v>
@@ -15241,7 +15247,7 @@
         <v>574</v>
       </c>
       <c r="J315" s="3" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
     </row>
     <row r="316" spans="1:10">
@@ -15261,7 +15267,7 @@
         <v>68</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="G316" s="1" t="s">
         <v>14</v>
@@ -15293,7 +15299,7 @@
         <v>76</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="G317" s="1" t="s">
         <v>14</v>
@@ -15305,7 +15311,7 @@
         <v>574</v>
       </c>
       <c r="J317" s="3" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
     </row>
     <row r="318" spans="1:10">
@@ -15485,7 +15491,7 @@
         <v>68</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="G323" s="1" t="s">
         <v>14</v>
@@ -15497,7 +15503,7 @@
         <v>574</v>
       </c>
       <c r="J323" s="3" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="324" spans="1:10">
@@ -15613,7 +15619,7 @@
         <v>68</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="G327" s="1" t="s">
         <v>14</v>
@@ -15645,7 +15651,7 @@
         <v>68</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="G328" s="1" t="s">
         <v>14</v>
@@ -15677,7 +15683,7 @@
         <v>68</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="G329" s="1" t="s">
         <v>14</v>
@@ -15709,7 +15715,7 @@
         <v>68</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="G330" s="1" t="s">
         <v>14</v>
@@ -15741,7 +15747,7 @@
         <v>68</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="G331" s="1" t="s">
         <v>14</v>
@@ -15773,7 +15779,7 @@
         <v>68</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="G332" s="1" t="s">
         <v>14</v>
@@ -15805,7 +15811,7 @@
         <v>68</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="G333" s="1" t="s">
         <v>14</v>
@@ -15837,7 +15843,7 @@
         <v>68</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="G334" s="1" t="s">
         <v>14</v>
@@ -15869,7 +15875,7 @@
         <v>68</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="G335" s="1" t="s">
         <v>14</v>
@@ -15901,7 +15907,7 @@
         <v>68</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="G336" s="1" t="s">
         <v>14</v>
@@ -15933,7 +15939,7 @@
         <v>68</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="G337" s="1" t="s">
         <v>14</v>
@@ -15965,7 +15971,7 @@
         <v>68</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="G338" s="1" t="s">
         <v>14</v>
@@ -15997,7 +16003,7 @@
         <v>68</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="G339" s="1" t="s">
         <v>14</v>
@@ -16009,7 +16015,7 @@
         <v>574</v>
       </c>
       <c r="J339" s="3" t="s">
-        <v>1302</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="340" spans="1:10">
@@ -16029,7 +16035,7 @@
         <v>68</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="G340" s="1" t="s">
         <v>14</v>
@@ -16061,7 +16067,7 @@
         <v>68</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="G341" s="1" t="s">
         <v>14</v>
@@ -16093,7 +16099,7 @@
         <v>68</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="G342" s="1" t="s">
         <v>14</v>
@@ -16125,7 +16131,7 @@
         <v>76</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="G343" s="1" t="s">
         <v>14</v>
@@ -16151,13 +16157,13 @@
         <v>11</v>
       </c>
       <c r="D344" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="E344" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="G344" s="1" t="s">
         <v>14</v>
@@ -16169,7 +16175,7 @@
         <v>574</v>
       </c>
       <c r="J344" s="3" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="345" spans="1:10">
@@ -16183,13 +16189,13 @@
         <v>11</v>
       </c>
       <c r="D345" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="E345" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F345" s="4" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="G345" s="1" t="s">
         <v>14</v>
@@ -16201,7 +16207,7 @@
         <v>574</v>
       </c>
       <c r="J345" s="3" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="346" spans="1:10">
@@ -16215,13 +16221,13 @@
         <v>11</v>
       </c>
       <c r="D346" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="E346" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="G346" s="1" t="s">
         <v>14</v>
@@ -16233,7 +16239,7 @@
         <v>574</v>
       </c>
       <c r="J346" s="3" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="347" spans="1:10">
@@ -16247,13 +16253,13 @@
         <v>11</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E347" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="G347" s="1" t="s">
         <v>14</v>
@@ -16265,7 +16271,7 @@
         <v>574</v>
       </c>
       <c r="J347" s="3" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="348" spans="1:10">
@@ -16279,13 +16285,13 @@
         <v>11</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="E348" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="G348" s="1" t="s">
         <v>14</v>
@@ -16297,7 +16303,7 @@
         <v>574</v>
       </c>
       <c r="J348" s="3" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="349" spans="1:10">
@@ -16311,13 +16317,13 @@
         <v>11</v>
       </c>
       <c r="D349" s="2" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="E349" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="G349" s="1" t="s">
         <v>14</v>
@@ -16329,7 +16335,7 @@
         <v>574</v>
       </c>
       <c r="J349" s="3" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="350" spans="1:10">
@@ -16343,13 +16349,13 @@
         <v>11</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="E350" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="G350" s="1" t="s">
         <v>14</v>
@@ -16361,7 +16367,7 @@
         <v>574</v>
       </c>
       <c r="J350" s="3" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="351" spans="1:10">
@@ -16375,13 +16381,13 @@
         <v>11</v>
       </c>
       <c r="D351" s="2" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E351" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="G351" s="1" t="s">
         <v>14</v>
@@ -16393,7 +16399,7 @@
         <v>574</v>
       </c>
       <c r="J351" s="3" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="352" spans="1:10">
@@ -16407,13 +16413,13 @@
         <v>11</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="E352" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F352" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="G352" s="1" t="s">
         <v>14</v>
@@ -16425,7 +16431,7 @@
         <v>574</v>
       </c>
       <c r="J352" s="3" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="353" spans="1:10">
@@ -16439,13 +16445,13 @@
         <v>11</v>
       </c>
       <c r="D353" s="2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="E353" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F353" s="1" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="G353" s="1" t="s">
         <v>14</v>
@@ -16457,7 +16463,7 @@
         <v>574</v>
       </c>
       <c r="J353" s="3" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="354" spans="1:10">
@@ -16471,13 +16477,13 @@
         <v>11</v>
       </c>
       <c r="D354" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="E354" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F354" s="1" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G354" s="1" t="s">
         <v>14</v>
@@ -16489,7 +16495,7 @@
         <v>574</v>
       </c>
       <c r="J354" s="3" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="355" spans="1:10">
@@ -16573,7 +16579,7 @@
         <v>76</v>
       </c>
       <c r="F357" s="1" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="G357" s="13" t="s">
         <v>14</v>
@@ -16585,7 +16591,7 @@
         <v>574</v>
       </c>
       <c r="J357" s="3" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
     </row>
     <row r="358" spans="1:10">
@@ -16599,7 +16605,7 @@
         <v>11</v>
       </c>
       <c r="D358" s="38" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="E358" s="1" t="s">
         <v>76</v>
@@ -16617,7 +16623,7 @@
         <v>574</v>
       </c>
       <c r="J358" s="3" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="359" spans="1:10">
@@ -16631,7 +16637,7 @@
         <v>11</v>
       </c>
       <c r="D359" s="38" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E359" s="1" t="s">
         <v>76</v>
@@ -16649,7 +16655,7 @@
         <v>574</v>
       </c>
       <c r="J359" s="3" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="360" spans="1:10">
@@ -16663,13 +16669,13 @@
         <v>11</v>
       </c>
       <c r="D360" s="38" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="E360" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F360" s="1" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="G360" s="1" t="s">
         <v>14</v>
@@ -16681,7 +16687,7 @@
         <v>574</v>
       </c>
       <c r="J360" s="3" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="361" spans="1:10">
@@ -16695,13 +16701,13 @@
         <v>11</v>
       </c>
       <c r="D361" s="38" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="E361" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F361" s="1" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="G361" s="1" t="s">
         <v>14</v>
@@ -16713,7 +16719,7 @@
         <v>574</v>
       </c>
       <c r="J361" s="3" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="362" spans="1:10">
@@ -16727,13 +16733,13 @@
         <v>11</v>
       </c>
       <c r="D362" s="38" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E362" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F362" s="1" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="G362" s="1" t="s">
         <v>14</v>
@@ -16745,7 +16751,7 @@
         <v>574</v>
       </c>
       <c r="J362" s="3" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="363" spans="1:10">
@@ -16759,13 +16765,13 @@
         <v>11</v>
       </c>
       <c r="D363" s="38" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E363" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F363" s="1" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="G363" s="1" t="s">
         <v>14</v>
@@ -16777,7 +16783,7 @@
         <v>574</v>
       </c>
       <c r="J363" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="364" spans="1:10">
@@ -16791,13 +16797,13 @@
         <v>11</v>
       </c>
       <c r="D364" s="38" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="E364" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F364" s="1" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="G364" s="1" t="s">
         <v>14</v>
@@ -16809,7 +16815,7 @@
         <v>574</v>
       </c>
       <c r="J364" s="3" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
     </row>
     <row r="365" spans="1:10">
@@ -16823,13 +16829,13 @@
         <v>11</v>
       </c>
       <c r="D365" s="38" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E365" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F365" s="1" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="G365" s="1" t="s">
         <v>14</v>
@@ -16841,7 +16847,7 @@
         <v>574</v>
       </c>
       <c r="J365" s="3" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
     </row>
     <row r="366" spans="1:10">
@@ -16855,13 +16861,13 @@
         <v>11</v>
       </c>
       <c r="D366" s="38" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="E366" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F366" s="1" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="G366" s="1" t="s">
         <v>14</v>
@@ -16873,7 +16879,7 @@
         <v>574</v>
       </c>
       <c r="J366" s="3" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
     </row>
     <row r="367" spans="1:10">
@@ -16887,13 +16893,13 @@
         <v>11</v>
       </c>
       <c r="D367" s="38" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E367" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F367" s="1" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="G367" s="1" t="s">
         <v>14</v>
@@ -16905,7 +16911,7 @@
         <v>574</v>
       </c>
       <c r="J367" s="3" t="s">
-        <v>1292</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="368" spans="1:10">
@@ -16919,13 +16925,13 @@
         <v>11</v>
       </c>
       <c r="D368" s="38" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="E368" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F368" s="1" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="G368" s="1" t="s">
         <v>14</v>
@@ -16937,7 +16943,7 @@
         <v>574</v>
       </c>
       <c r="J368" s="3" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="369" spans="1:10">
@@ -16951,13 +16957,13 @@
         <v>11</v>
       </c>
       <c r="D369" s="38" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E369" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F369" s="1" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="G369" s="1" t="s">
         <v>14</v>
@@ -16969,7 +16975,7 @@
         <v>574</v>
       </c>
       <c r="J369" s="3" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
     </row>
     <row r="370" spans="1:10">
@@ -16983,13 +16989,13 @@
         <v>11</v>
       </c>
       <c r="D370" s="38" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="E370" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F370" s="1" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="G370" s="1" t="s">
         <v>14</v>
@@ -17001,7 +17007,7 @@
         <v>574</v>
       </c>
       <c r="J370" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="371" spans="1:10">
@@ -17015,13 +17021,13 @@
         <v>11</v>
       </c>
       <c r="D371" s="38" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="E371" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F371" s="1" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="G371" s="1" t="s">
         <v>14</v>
@@ -17033,7 +17039,7 @@
         <v>574</v>
       </c>
       <c r="J371" s="3" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="372" spans="1:10">
@@ -17047,7 +17053,7 @@
         <v>11</v>
       </c>
       <c r="D372" s="38" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="E372" s="1" t="s">
         <v>76</v>
@@ -17065,7 +17071,7 @@
         <v>574</v>
       </c>
       <c r="J372" s="3" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
     </row>
     <row r="373" spans="1:10">
@@ -17079,13 +17085,13 @@
         <v>11</v>
       </c>
       <c r="D373" s="38" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="E373" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F373" s="1" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="G373" s="1" t="s">
         <v>14</v>
@@ -17097,7 +17103,7 @@
         <v>574</v>
       </c>
       <c r="J373" s="3" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
     </row>
     <row r="374" spans="1:10">
@@ -17111,13 +17117,13 @@
         <v>11</v>
       </c>
       <c r="D374" s="38" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="E374" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F374" s="1" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="G374" s="1" t="s">
         <v>14</v>
@@ -17129,7 +17135,7 @@
         <v>574</v>
       </c>
       <c r="J374" s="3" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
     </row>
     <row r="375" spans="1:10">
@@ -17143,13 +17149,13 @@
         <v>11</v>
       </c>
       <c r="D375" s="38" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="E375" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F375" s="1" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="G375" s="1" t="s">
         <v>14</v>
@@ -17161,7 +17167,7 @@
         <v>574</v>
       </c>
       <c r="J375" s="3" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
     <row r="376" spans="1:10">
@@ -17175,13 +17181,13 @@
         <v>11</v>
       </c>
       <c r="D376" s="38" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="E376" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F376" s="1" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="G376" s="1" t="s">
         <v>14</v>
@@ -17190,10 +17196,10 @@
         <v>45968</v>
       </c>
       <c r="I376" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J376" s="3" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="377" spans="1:10">
@@ -17207,13 +17213,13 @@
         <v>11</v>
       </c>
       <c r="D377" s="38" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="E377" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F377" s="1" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="G377" s="1" t="s">
         <v>14</v>
@@ -17222,10 +17228,10 @@
         <v>45968</v>
       </c>
       <c r="I377" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J377" s="3" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="378" spans="1:10">
@@ -17239,13 +17245,13 @@
         <v>11</v>
       </c>
       <c r="D378" s="38" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="E378" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F378" s="1" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="G378" s="1" t="s">
         <v>14</v>
@@ -17257,7 +17263,7 @@
         <v>574</v>
       </c>
       <c r="J378" s="3" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
     </row>
     <row r="379" spans="1:10">
@@ -17271,13 +17277,13 @@
         <v>11</v>
       </c>
       <c r="D379" s="38" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="E379" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F379" s="1" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="G379" s="1" t="s">
         <v>14</v>
@@ -17286,10 +17292,10 @@
         <v>45968</v>
       </c>
       <c r="I379" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J379" s="3" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
     </row>
     <row r="380" spans="1:10">
@@ -17303,13 +17309,13 @@
         <v>11</v>
       </c>
       <c r="D380" s="38" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="E380" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F380" s="1" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="G380" s="1" t="s">
         <v>14</v>
@@ -17318,10 +17324,10 @@
         <v>45968</v>
       </c>
       <c r="I380" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J380" s="3" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
     </row>
     <row r="381" spans="1:10">
@@ -17335,13 +17341,13 @@
         <v>11</v>
       </c>
       <c r="D381" s="38" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="E381" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F381" s="1" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="G381" s="1" t="s">
         <v>14</v>
@@ -17350,10 +17356,10 @@
         <v>45971</v>
       </c>
       <c r="I381" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J381" s="3" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
     </row>
     <row r="382" spans="1:10">
@@ -17361,19 +17367,19 @@
         <v>381</v>
       </c>
       <c r="B382" s="25" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D382" s="38" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E382" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F382" s="1" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="G382" s="1" t="s">
         <v>14</v>
@@ -17385,7 +17391,7 @@
         <v>574</v>
       </c>
       <c r="J382" s="3" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
     </row>
     <row r="383" spans="1:10">
@@ -17393,13 +17399,13 @@
         <v>382</v>
       </c>
       <c r="B383" s="25" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D383" s="38" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E383" s="1" t="s">
         <v>350</v>
@@ -17417,7 +17423,7 @@
         <v>574</v>
       </c>
       <c r="J383" s="3" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="384" spans="1:10">
@@ -17425,19 +17431,19 @@
         <v>383</v>
       </c>
       <c r="B384" s="25" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D384" s="38" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="E384" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F384" s="1" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="G384" s="1" t="s">
         <v>14</v>
@@ -17449,7 +17455,7 @@
         <v>574</v>
       </c>
       <c r="J384" s="3" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="385" spans="1:10">
@@ -17457,19 +17463,19 @@
         <v>384</v>
       </c>
       <c r="B385" s="25" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D385" s="38" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="E385" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F385" s="1" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="G385" s="1" t="s">
         <v>14</v>
@@ -17481,7 +17487,7 @@
         <v>574</v>
       </c>
       <c r="J385" s="3" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
     </row>
     <row r="386" spans="1:10">
@@ -17489,13 +17495,13 @@
         <v>385</v>
       </c>
       <c r="B386" s="25" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D386" s="38" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="E386" s="1" t="s">
         <v>21</v>
@@ -17510,10 +17516,10 @@
         <v>46129</v>
       </c>
       <c r="I386" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J386" s="3" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
     </row>
     <row r="387" spans="1:10">
@@ -17521,19 +17527,19 @@
         <v>386</v>
       </c>
       <c r="B387" s="25" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D387" s="39" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="E387" s="1" t="s">
         <v>350</v>
       </c>
       <c r="F387" s="1" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="G387" s="1" t="s">
         <v>14</v>
@@ -17545,7 +17551,7 @@
         <v>574</v>
       </c>
       <c r="J387" s="3" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="388" spans="1:10">
@@ -17553,19 +17559,19 @@
         <v>387</v>
       </c>
       <c r="B388" s="25" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D388" s="38" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E388" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F388" s="1" t="s">
-        <v>1313</v>
+        <v>1310</v>
       </c>
       <c r="G388" s="1" t="s">
         <v>14</v>
@@ -17577,7 +17583,7 @@
         <v>574</v>
       </c>
       <c r="J388" s="3" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="389" spans="1:10">
@@ -17585,19 +17591,19 @@
         <v>388</v>
       </c>
       <c r="B389" s="25" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D389" s="38" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="E389" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F389" s="1" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="G389" s="1" t="s">
         <v>14</v>
@@ -17609,7 +17615,7 @@
         <v>574</v>
       </c>
       <c r="J389" s="3" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="390" spans="1:10">
@@ -17617,19 +17623,19 @@
         <v>389</v>
       </c>
       <c r="B390" s="25" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D390" s="39" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="E390" s="1" t="s">
         <v>350</v>
       </c>
       <c r="F390" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="G390" s="1" t="s">
         <v>14</v>
@@ -17641,7 +17647,7 @@
         <v>574</v>
       </c>
       <c r="J390" s="3" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="391" spans="1:10">
@@ -17649,19 +17655,19 @@
         <v>390</v>
       </c>
       <c r="B391" s="25" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D391" s="39" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="E391" s="1" t="s">
         <v>350</v>
       </c>
       <c r="F391" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="G391" s="1" t="s">
         <v>14</v>
@@ -17673,7 +17679,7 @@
         <v>574</v>
       </c>
       <c r="J391" s="3" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="392" spans="1:10">
@@ -17681,19 +17687,19 @@
         <v>391</v>
       </c>
       <c r="B392" s="25" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D392" s="38" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E392" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="G392" s="1" t="s">
         <v>14</v>
@@ -17705,7 +17711,7 @@
         <v>574</v>
       </c>
       <c r="J392" s="3" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="393" spans="1:10">
@@ -17713,19 +17719,19 @@
         <v>392</v>
       </c>
       <c r="B393" s="25" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D393" s="38" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E393" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F393" s="1" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="G393" s="1" t="s">
         <v>14</v>
@@ -17737,7 +17743,7 @@
         <v>574</v>
       </c>
       <c r="J393" s="3" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="394" spans="1:10">
@@ -17745,19 +17751,19 @@
         <v>393</v>
       </c>
       <c r="B394" s="25" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D394" s="38" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E394" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F394" s="1" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="G394" s="1" t="s">
         <v>14</v>
@@ -17769,7 +17775,7 @@
         <v>574</v>
       </c>
       <c r="J394" s="3" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
     </row>
     <row r="395" spans="1:10">
@@ -17777,19 +17783,19 @@
         <v>394</v>
       </c>
       <c r="B395" s="26" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D395" s="39" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="E395" s="1" t="s">
         <v>350</v>
       </c>
       <c r="F395" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="G395" s="1" t="s">
         <v>14</v>
@@ -17801,7 +17807,7 @@
         <v>574</v>
       </c>
       <c r="J395" s="3" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="396" spans="1:10">
@@ -17815,7 +17821,7 @@
         <v>11</v>
       </c>
       <c r="D396" s="2" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="E396" s="1" t="s">
         <v>13</v>
@@ -17833,7 +17839,7 @@
         <v>574</v>
       </c>
       <c r="J396" s="3" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
     </row>
     <row r="397" spans="1:10">
@@ -17847,13 +17853,13 @@
         <v>11</v>
       </c>
       <c r="D397" s="2" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="E397" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F397" s="1" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="G397" s="1" t="s">
         <v>14</v>
@@ -17865,7 +17871,7 @@
         <v>574</v>
       </c>
       <c r="J397" s="3" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="398" spans="1:10">
@@ -17879,13 +17885,13 @@
         <v>11</v>
       </c>
       <c r="D398" s="2" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="E398" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F398" s="1" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="G398" s="1" t="s">
         <v>14</v>
@@ -17897,7 +17903,7 @@
         <v>574</v>
       </c>
       <c r="J398" s="3" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
     </row>
     <row r="399" spans="1:10">
@@ -17911,13 +17917,13 @@
         <v>11</v>
       </c>
       <c r="D399" s="2" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="E399" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F399" s="1" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="G399" s="1" t="s">
         <v>14</v>
@@ -17926,10 +17932,10 @@
         <v>45960</v>
       </c>
       <c r="I399" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J399" s="3" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
     </row>
     <row r="400" spans="1:10">
@@ -17943,13 +17949,13 @@
         <v>11</v>
       </c>
       <c r="D400" s="2" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="E400" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F400" s="1" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="G400" s="1" t="s">
         <v>14</v>
@@ -17961,7 +17967,7 @@
         <v>574</v>
       </c>
       <c r="J400" s="3" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="401" spans="1:10">
@@ -17975,13 +17981,13 @@
         <v>11</v>
       </c>
       <c r="D401" s="2" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="E401" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F401" s="1" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="G401" s="1" t="s">
         <v>14</v>
@@ -17993,7 +17999,7 @@
         <v>574</v>
       </c>
       <c r="J401" s="3" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="402" spans="1:10">
@@ -18007,13 +18013,13 @@
         <v>11</v>
       </c>
       <c r="D402" s="2" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="E402" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F402" s="1" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="G402" s="1" t="s">
         <v>14</v>
@@ -18025,7 +18031,7 @@
         <v>574</v>
       </c>
       <c r="J402" s="3" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="403" spans="1:10">
@@ -18039,13 +18045,13 @@
         <v>11</v>
       </c>
       <c r="D403" s="2" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="E403" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F403" s="1" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="G403" s="1" t="s">
         <v>14</v>
@@ -18057,7 +18063,7 @@
         <v>574</v>
       </c>
       <c r="J403" s="3" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="404" spans="1:10">
@@ -18071,13 +18077,13 @@
         <v>11</v>
       </c>
       <c r="D404" s="2" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="E404" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F404" s="1" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="G404" s="1" t="s">
         <v>14</v>
@@ -18089,7 +18095,7 @@
         <v>574</v>
       </c>
       <c r="J404" s="3" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="405" spans="1:10">
@@ -18097,19 +18103,19 @@
         <v>404</v>
       </c>
       <c r="B405" s="28" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C405" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D405" s="5" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="E405" s="1" t="s">
         <v>350</v>
       </c>
       <c r="F405" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="G405" s="1" t="s">
         <v>14</v>
@@ -18121,7 +18127,7 @@
         <v>574</v>
       </c>
       <c r="J405" s="3" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="406" spans="1:10">
@@ -18129,19 +18135,19 @@
         <v>405</v>
       </c>
       <c r="B406" s="28" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C406" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D406" s="5" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="E406" s="1" t="s">
         <v>350</v>
       </c>
       <c r="F406" s="1" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="G406" s="1" t="s">
         <v>14</v>
@@ -18153,7 +18159,7 @@
         <v>574</v>
       </c>
       <c r="J406" s="24" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="407" spans="1:10">
@@ -18161,19 +18167,19 @@
         <v>406</v>
       </c>
       <c r="B407" s="28" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C407" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D407" s="5" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="E407" s="1" t="s">
         <v>350</v>
       </c>
       <c r="F407" s="1" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="G407" s="1" t="s">
         <v>14</v>
@@ -18185,7 +18191,7 @@
         <v>574</v>
       </c>
       <c r="J407" s="3" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="408" spans="1:10">
@@ -18193,19 +18199,19 @@
         <v>407</v>
       </c>
       <c r="B408" s="28" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C408" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D408" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E408" s="1" t="s">
         <v>350</v>
       </c>
       <c r="F408" s="1" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G408" s="1" t="s">
         <v>14</v>
@@ -18217,7 +18223,7 @@
         <v>574</v>
       </c>
       <c r="J408" s="3" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="409" spans="1:10">
@@ -18225,19 +18231,19 @@
         <v>408</v>
       </c>
       <c r="B409" s="28" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C409" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D409" s="5" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="E409" s="1" t="s">
         <v>350</v>
       </c>
       <c r="F409" s="1" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="G409" s="1" t="s">
         <v>14</v>
@@ -18249,7 +18255,7 @@
         <v>574</v>
       </c>
       <c r="J409" s="24" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="410" spans="1:10">
@@ -18257,19 +18263,19 @@
         <v>409</v>
       </c>
       <c r="B410" s="28" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C410" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D410" s="5" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="E410" s="1" t="s">
         <v>350</v>
       </c>
       <c r="F410" s="1" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="G410" s="1" t="s">
         <v>14</v>
@@ -18281,7 +18287,7 @@
         <v>574</v>
       </c>
       <c r="J410" s="3" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="411" spans="1:10">
@@ -18289,19 +18295,19 @@
         <v>410</v>
       </c>
       <c r="B411" s="28" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C411" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D411" s="5" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E411" s="1" t="s">
         <v>350</v>
       </c>
       <c r="F411" s="1" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="G411" s="1" t="s">
         <v>14</v>
@@ -18313,7 +18319,7 @@
         <v>574</v>
       </c>
       <c r="J411" s="3" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="412" spans="1:10">
@@ -18321,19 +18327,19 @@
         <v>411</v>
       </c>
       <c r="B412" s="28" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C412" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D412" s="5" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="E412" s="1" t="s">
         <v>350</v>
       </c>
       <c r="F412" s="1" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="G412" s="1" t="s">
         <v>14</v>
@@ -18345,7 +18351,7 @@
         <v>574</v>
       </c>
       <c r="J412" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="413" spans="1:10">
@@ -18353,19 +18359,19 @@
         <v>412</v>
       </c>
       <c r="B413" s="28" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C413" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D413" s="5" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="E413" s="1" t="s">
         <v>350</v>
       </c>
       <c r="F413" s="1" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="G413" s="1" t="s">
         <v>14</v>
@@ -18377,7 +18383,7 @@
         <v>574</v>
       </c>
       <c r="J413" s="3" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="414" spans="1:10">
@@ -18385,19 +18391,19 @@
         <v>413</v>
       </c>
       <c r="B414" s="28" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C414" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D414" s="5" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="E414" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F414" s="1" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="G414" s="1" t="s">
         <v>14</v>
@@ -18409,7 +18415,7 @@
         <v>574</v>
       </c>
       <c r="J414" s="3" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="415" spans="1:10">
@@ -18417,19 +18423,19 @@
         <v>414</v>
       </c>
       <c r="B415" s="28" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C415" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D415" s="5" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="E415" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F415" s="1" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="G415" s="1" t="s">
         <v>14</v>
@@ -18441,7 +18447,7 @@
         <v>574</v>
       </c>
       <c r="J415" s="3" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
     </row>
     <row r="416" spans="1:10">
@@ -18449,19 +18455,19 @@
         <v>415</v>
       </c>
       <c r="B416" s="28" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C416" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D416" s="5" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="E416" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F416" s="1" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="G416" s="1" t="s">
         <v>14</v>
@@ -18473,7 +18479,7 @@
         <v>574</v>
       </c>
       <c r="J416" s="3" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
     </row>
     <row r="417" spans="1:10">
@@ -18481,19 +18487,19 @@
         <v>416</v>
       </c>
       <c r="B417" s="28" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C417" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D417" s="5" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="E417" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F417" s="1" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="G417" s="1" t="s">
         <v>14</v>
@@ -18505,7 +18511,7 @@
         <v>574</v>
       </c>
       <c r="J417" s="3" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
     </row>
     <row r="418" spans="1:10">
@@ -18513,19 +18519,19 @@
         <v>417</v>
       </c>
       <c r="B418" s="28" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C418" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D418" s="5" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="E418" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F418" s="1" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="G418" s="1" t="s">
         <v>14</v>
@@ -18537,7 +18543,7 @@
         <v>574</v>
       </c>
       <c r="J418" s="3" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="419" spans="1:10">
@@ -18545,19 +18551,19 @@
         <v>418</v>
       </c>
       <c r="B419" s="29" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C419" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D419" s="5" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="E419" s="1" t="s">
         <v>350</v>
       </c>
       <c r="F419" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="G419" s="1" t="s">
         <v>14</v>
@@ -18569,7 +18575,7 @@
         <v>574</v>
       </c>
       <c r="J419" s="3" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="420" spans="1:10">
@@ -18577,19 +18583,19 @@
         <v>419</v>
       </c>
       <c r="B420" s="29" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C420" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D420" s="5" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E420" s="1" t="s">
         <v>350</v>
       </c>
       <c r="F420" s="1" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="G420" s="1" t="s">
         <v>14</v>
@@ -18601,7 +18607,7 @@
         <v>574</v>
       </c>
       <c r="J420" s="3" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="421" spans="1:10">
@@ -18609,19 +18615,19 @@
         <v>420</v>
       </c>
       <c r="B421" s="29" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C421" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D421" s="5" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="E421" s="1" t="s">
         <v>350</v>
       </c>
       <c r="F421" s="1" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="G421" s="1" t="s">
         <v>14</v>
@@ -18633,7 +18639,7 @@
         <v>574</v>
       </c>
       <c r="J421" s="3" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="422" spans="1:10">
@@ -18641,19 +18647,19 @@
         <v>421</v>
       </c>
       <c r="B422" s="29" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C422" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D422" s="5" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="E422" s="1" t="s">
         <v>350</v>
       </c>
       <c r="F422" s="1" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="G422" s="1" t="s">
         <v>14</v>
@@ -18665,7 +18671,7 @@
         <v>574</v>
       </c>
       <c r="J422" s="3" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
     </row>
     <row r="423" spans="1:10">
@@ -18673,19 +18679,19 @@
         <v>422</v>
       </c>
       <c r="B423" s="29" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C423" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D423" s="5" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="E423" s="1" t="s">
         <v>350</v>
       </c>
       <c r="F423" s="1" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="G423" s="1" t="s">
         <v>14</v>
@@ -18697,7 +18703,7 @@
         <v>574</v>
       </c>
       <c r="J423" s="3" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="424" spans="1:10">
@@ -18705,19 +18711,19 @@
         <v>423</v>
       </c>
       <c r="B424" s="29" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C424" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D424" s="5" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="E424" s="1" t="s">
         <v>350</v>
       </c>
       <c r="F424" s="1" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="G424" s="1" t="s">
         <v>14</v>
@@ -18729,7 +18735,7 @@
         <v>574</v>
       </c>
       <c r="J424" s="3" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
     </row>
     <row r="425" spans="1:10">
@@ -18737,19 +18743,19 @@
         <v>424</v>
       </c>
       <c r="B425" s="29" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C425" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D425" s="5" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="E425" s="1" t="s">
         <v>350</v>
       </c>
       <c r="F425" s="1" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="G425" s="1" t="s">
         <v>14</v>
@@ -18761,7 +18767,7 @@
         <v>574</v>
       </c>
       <c r="J425" s="3" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
     </row>
     <row r="426" spans="1:10">
@@ -18769,19 +18775,19 @@
         <v>425</v>
       </c>
       <c r="B426" s="29" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C426" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D426" s="5" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="E426" s="1" t="s">
         <v>350</v>
       </c>
       <c r="F426" s="1" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="G426" s="1" t="s">
         <v>14</v>
@@ -18793,7 +18799,7 @@
         <v>574</v>
       </c>
       <c r="J426" s="3" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
     </row>
     <row r="427" spans="1:10">
@@ -18801,19 +18807,19 @@
         <v>426</v>
       </c>
       <c r="B427" s="29" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C427" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D427" s="5" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="E427" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F427" s="1" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="G427" s="1" t="s">
         <v>14</v>
@@ -18822,10 +18828,10 @@
         <v>45960</v>
       </c>
       <c r="I427" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J427" s="3" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="428" spans="1:10">
@@ -18833,19 +18839,19 @@
         <v>427</v>
       </c>
       <c r="B428" s="29" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C428" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D428" s="5" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="E428" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F428" s="1" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="G428" s="1" t="s">
         <v>14</v>
@@ -18857,7 +18863,7 @@
         <v>574</v>
       </c>
       <c r="J428" s="3" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="429" spans="1:10">
@@ -18865,19 +18871,19 @@
         <v>428</v>
       </c>
       <c r="B429" s="29" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C429" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D429" s="5" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="E429" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F429" s="1" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="G429" s="1" t="s">
         <v>14</v>
@@ -18889,7 +18895,7 @@
         <v>574</v>
       </c>
       <c r="J429" s="3" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
     </row>
     <row r="430" spans="1:10">
@@ -18897,19 +18903,19 @@
         <v>429</v>
       </c>
       <c r="B430" s="29" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C430" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D430" s="5" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="E430" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F430" s="1" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="G430" s="1" t="s">
         <v>14</v>
@@ -18921,7 +18927,7 @@
         <v>574</v>
       </c>
       <c r="J430" s="3" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
     </row>
     <row r="431" spans="1:10">
@@ -18929,19 +18935,19 @@
         <v>430</v>
       </c>
       <c r="B431" s="29" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C431" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D431" s="5" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="E431" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F431" s="1" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="G431" s="1" t="s">
         <v>14</v>
@@ -18953,7 +18959,7 @@
         <v>574</v>
       </c>
       <c r="J431" s="3" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
     </row>
     <row r="432" spans="1:10">
@@ -18961,19 +18967,19 @@
         <v>431</v>
       </c>
       <c r="B432" s="29" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C432" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D432" s="5" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="E432" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F432" s="1" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="G432" s="1" t="s">
         <v>14</v>
@@ -18985,7 +18991,7 @@
         <v>574</v>
       </c>
       <c r="J432" s="3" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
     </row>
     <row r="433" spans="1:10">
@@ -18993,19 +18999,19 @@
         <v>432</v>
       </c>
       <c r="B433" s="29" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C433" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D433" s="5" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="E433" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F433" s="1" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="G433" s="1" t="s">
         <v>14</v>
@@ -19017,7 +19023,7 @@
         <v>574</v>
       </c>
       <c r="J433" s="3" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="434" spans="1:10">
@@ -19025,19 +19031,19 @@
         <v>433</v>
       </c>
       <c r="B434" s="29" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C434" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D434" s="5" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="E434" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F434" s="1" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="G434" s="1" t="s">
         <v>14</v>
@@ -19049,7 +19055,7 @@
         <v>574</v>
       </c>
       <c r="J434" s="3" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="435" spans="1:10">
@@ -19057,19 +19063,19 @@
         <v>434</v>
       </c>
       <c r="B435" s="29" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C435" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D435" s="5" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="E435" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F435" s="1" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="G435" s="1" t="s">
         <v>14</v>
@@ -19078,10 +19084,10 @@
         <v>46037</v>
       </c>
       <c r="I435" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J435" s="3" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
     </row>
     <row r="436" spans="1:10">
@@ -19089,19 +19095,19 @@
         <v>435</v>
       </c>
       <c r="B436" s="29" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C436" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D436" s="5" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="E436" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F436" s="1" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="G436" s="1" t="s">
         <v>14</v>
@@ -19119,19 +19125,19 @@
         <v>436</v>
       </c>
       <c r="B437" s="29" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C437" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D437" s="5" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="E437" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F437" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="G437" s="1" t="s">
         <v>14</v>
@@ -19143,7 +19149,7 @@
         <v>574</v>
       </c>
       <c r="J437" s="3" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="438" spans="1:10">
@@ -19151,19 +19157,19 @@
         <v>437</v>
       </c>
       <c r="B438" s="40" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="C438" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D438" s="5" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="E438" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F438" s="1" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="G438" s="1" t="s">
         <v>14</v>
@@ -19175,7 +19181,7 @@
         <v>574</v>
       </c>
       <c r="J438" s="3" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
     </row>
     <row r="439" spans="1:10">
@@ -19183,19 +19189,19 @@
         <v>438</v>
       </c>
       <c r="B439" s="40" t="s">
+        <v>851</v>
+      </c>
+      <c r="C439" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D439" s="5" t="s">
         <v>853</v>
-      </c>
-      <c r="C439" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D439" s="5" t="s">
-        <v>855</v>
       </c>
       <c r="E439" s="1" t="s">
         <v>350</v>
       </c>
       <c r="F439" s="1" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="G439" s="1" t="s">
         <v>14</v>
@@ -19207,7 +19213,7 @@
         <v>574</v>
       </c>
       <c r="J439" s="3" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="440" spans="1:10">
@@ -19215,19 +19221,19 @@
         <v>439</v>
       </c>
       <c r="B440" s="40" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="C440" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D440" s="5" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="E440" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F440" s="1" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="G440" s="1" t="s">
         <v>14</v>
@@ -19239,7 +19245,7 @@
         <v>574</v>
       </c>
       <c r="J440" s="3" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
     </row>
     <row r="441" spans="1:10">
@@ -19247,19 +19253,19 @@
         <v>440</v>
       </c>
       <c r="B441" s="40" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="C441" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D441" s="5" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="E441" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F441" s="1" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="G441" s="1" t="s">
         <v>14</v>
@@ -19271,7 +19277,7 @@
         <v>574</v>
       </c>
       <c r="J441" s="3" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="442" spans="1:10">
@@ -19279,19 +19285,19 @@
         <v>441</v>
       </c>
       <c r="B442" s="40" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="C442" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D442" s="5" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="E442" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F442" s="1" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="G442" s="1" t="s">
         <v>14</v>
@@ -19303,7 +19309,7 @@
         <v>574</v>
       </c>
       <c r="J442" s="3" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="443" spans="1:10">
@@ -19311,19 +19317,19 @@
         <v>442</v>
       </c>
       <c r="B443" s="31" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="C443" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D443" s="2" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="E443" s="1" t="s">
         <v>350</v>
       </c>
       <c r="F443" s="1" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="G443" s="1" t="s">
         <v>30</v>
@@ -19335,7 +19341,7 @@
         <v>574</v>
       </c>
       <c r="J443" s="3" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="444" spans="1:10">
@@ -19343,19 +19349,19 @@
         <v>443</v>
       </c>
       <c r="B444" s="31" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="C444" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D444" s="2" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="E444" s="1" t="s">
         <v>350</v>
       </c>
       <c r="F444" s="1" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="G444" s="1" t="s">
         <v>30</v>
@@ -19367,7 +19373,7 @@
         <v>574</v>
       </c>
       <c r="J444" s="3" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="445" spans="1:10">
@@ -19375,19 +19381,19 @@
         <v>444</v>
       </c>
       <c r="B445" s="31" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="C445" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D445" s="2" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="E445" s="1" t="s">
         <v>350</v>
       </c>
       <c r="F445" s="1" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="G445" s="1" t="s">
         <v>30</v>
@@ -19399,7 +19405,7 @@
         <v>574</v>
       </c>
       <c r="J445" s="3" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="446" spans="1:10">
@@ -19407,19 +19413,19 @@
         <v>445</v>
       </c>
       <c r="B446" s="31" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="C446" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D446" s="2" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="E446" s="1" t="s">
         <v>350</v>
       </c>
       <c r="F446" s="1" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="G446" s="1" t="s">
         <v>30</v>
@@ -19431,7 +19437,7 @@
         <v>574</v>
       </c>
       <c r="J446" s="3" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="447" spans="1:10">
@@ -19439,19 +19445,19 @@
         <v>446</v>
       </c>
       <c r="B447" s="31" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="C447" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D447" s="2" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="E447" s="1" t="s">
         <v>350</v>
       </c>
       <c r="F447" s="1" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="G447" s="1" t="s">
         <v>30</v>
@@ -19463,7 +19469,7 @@
         <v>574</v>
       </c>
       <c r="J447" s="3" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="448" spans="1:10">
@@ -19471,16 +19477,16 @@
         <v>447</v>
       </c>
       <c r="B448" s="52" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C448" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="E448" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F448" s="1" t="s">
         <v>373</v>
@@ -19495,7 +19501,7 @@
         <v>574</v>
       </c>
       <c r="J448" s="3" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="449" spans="1:10">
@@ -19503,19 +19509,19 @@
         <v>448</v>
       </c>
       <c r="B449" s="53" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="C449" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="E449" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F449" s="1" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="G449" s="1" t="s">
         <v>30</v>
@@ -19527,7 +19533,7 @@
         <v>574</v>
       </c>
       <c r="J449" s="3" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="450" spans="1:10">
@@ -19535,19 +19541,19 @@
         <v>449</v>
       </c>
       <c r="B450" s="53" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="C450" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="E450" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F450" s="1" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="G450" s="1" t="s">
         <v>30</v>
@@ -19565,13 +19571,13 @@
         <v>450</v>
       </c>
       <c r="B451" s="53" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="C451" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D451" s="2" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="E451" s="1" t="s">
         <v>350</v>
@@ -19586,7 +19592,7 @@
         <v>46174</v>
       </c>
       <c r="I451" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J451" s="24"/>
     </row>
@@ -19595,19 +19601,19 @@
         <v>451</v>
       </c>
       <c r="B452" s="53" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="C452" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="E452" s="1" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="F452" s="1" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
       <c r="G452" s="1" t="s">
         <v>30</v>
@@ -19619,7 +19625,7 @@
         <v>574</v>
       </c>
       <c r="J452" s="3" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="453" spans="1:10">
@@ -19627,19 +19633,19 @@
         <v>452</v>
       </c>
       <c r="B453" s="53" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="C453" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D453" s="2" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="E453" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F453" s="1" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="G453" s="1" t="s">
         <v>30</v>
@@ -19657,19 +19663,19 @@
         <v>453</v>
       </c>
       <c r="B454" s="53" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="C454" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D454" s="2" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="E454" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F454" s="1" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="G454" s="1" t="s">
         <v>30</v>
@@ -19678,7 +19684,7 @@
         <v>46104</v>
       </c>
       <c r="I454" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J454" s="24"/>
     </row>
@@ -19687,19 +19693,19 @@
         <v>454</v>
       </c>
       <c r="B455" s="53" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="C455" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D455" s="2" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="E455" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F455" s="1" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="G455" s="1" t="s">
         <v>30</v>
@@ -19708,7 +19714,7 @@
         <v>46129</v>
       </c>
       <c r="I455" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J455" s="24"/>
     </row>
@@ -19717,19 +19723,19 @@
         <v>455</v>
       </c>
       <c r="B456" s="53" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="C456" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D456" s="2" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="E456" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F456" s="1" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="G456" s="1" t="s">
         <v>30</v>
@@ -19747,19 +19753,19 @@
         <v>456</v>
       </c>
       <c r="B457" s="53" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="C457" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D457" s="2" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="E457" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F457" s="1" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="G457" s="1" t="s">
         <v>30</v>
@@ -19768,7 +19774,7 @@
         <v>46146</v>
       </c>
       <c r="I457" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J457" s="24"/>
     </row>
@@ -19777,19 +19783,19 @@
         <v>457</v>
       </c>
       <c r="B458" s="53" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="C458" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D458" s="2" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="E458" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F458" s="1" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="G458" s="1" t="s">
         <v>30</v>
@@ -19807,19 +19813,19 @@
         <v>458</v>
       </c>
       <c r="B459" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C459" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D459" s="2" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="E459" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F459" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="G459" s="1" t="s">
         <v>30</v>
@@ -19828,7 +19834,7 @@
         <v>46091</v>
       </c>
       <c r="I459" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J459" s="24"/>
     </row>
@@ -19837,19 +19843,19 @@
         <v>459</v>
       </c>
       <c r="B460" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C460" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D460" s="2" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="E460" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F460" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="G460" s="1" t="s">
         <v>30</v>
@@ -19867,19 +19873,19 @@
         <v>460</v>
       </c>
       <c r="B461" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C461" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D461" s="2" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="E461" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F461" s="1" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="G461" s="1" t="s">
         <v>30</v>
@@ -19897,19 +19903,19 @@
         <v>461</v>
       </c>
       <c r="B462" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C462" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D462" s="2" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="E462" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F462" s="1" t="s">
-        <v>1154</v>
+        <v>1054</v>
       </c>
       <c r="G462" s="1" t="s">
         <v>30</v>
@@ -19921,7 +19927,7 @@
         <v>574</v>
       </c>
       <c r="J462" s="3" t="s">
-        <v>1278</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="463" spans="1:10">
@@ -19929,19 +19935,19 @@
         <v>462</v>
       </c>
       <c r="B463" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C463" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D463" s="2" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="E463" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F463" s="1" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="G463" s="1" t="s">
         <v>30</v>
@@ -19950,7 +19956,7 @@
         <v>46099</v>
       </c>
       <c r="I463" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J463" s="24"/>
     </row>
@@ -19959,19 +19965,19 @@
         <v>463</v>
       </c>
       <c r="B464" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C464" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D464" s="2" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="E464" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F464" s="1" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="G464" s="1" t="s">
         <v>30</v>
@@ -19980,7 +19986,7 @@
         <v>46099</v>
       </c>
       <c r="I464" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J464" s="24"/>
     </row>
@@ -19989,19 +19995,19 @@
         <v>464</v>
       </c>
       <c r="B465" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C465" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D465" s="2" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="E465" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F465" s="1" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="G465" s="1" t="s">
         <v>30</v>
@@ -20019,19 +20025,19 @@
         <v>465</v>
       </c>
       <c r="B466" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C466" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D466" s="2" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="E466" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F466" s="1" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="G466" s="1" t="s">
         <v>30</v>
@@ -20040,7 +20046,7 @@
         <v>46105</v>
       </c>
       <c r="I466" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J466" s="24"/>
     </row>
@@ -20049,19 +20055,19 @@
         <v>466</v>
       </c>
       <c r="B467" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C467" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D467" s="2" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="E467" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F467" s="1" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="G467" s="1" t="s">
         <v>30</v>
@@ -20070,7 +20076,7 @@
         <v>46105</v>
       </c>
       <c r="I467" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J467" s="24"/>
     </row>
@@ -20079,19 +20085,19 @@
         <v>467</v>
       </c>
       <c r="B468" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C468" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D468" s="2" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="E468" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F468" s="1" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="G468" s="1" t="s">
         <v>30</v>
@@ -20100,7 +20106,7 @@
         <v>46108</v>
       </c>
       <c r="I468" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J468" s="24"/>
     </row>
@@ -20109,19 +20115,19 @@
         <v>468</v>
       </c>
       <c r="B469" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C469" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D469" s="2" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="E469" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F469" s="1" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="G469" s="1" t="s">
         <v>30</v>
@@ -20130,7 +20136,7 @@
         <v>46108</v>
       </c>
       <c r="I469" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J469" s="24"/>
     </row>
@@ -20139,19 +20145,19 @@
         <v>469</v>
       </c>
       <c r="B470" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C470" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D470" s="2" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="E470" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F470" s="1" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="G470" s="1" t="s">
         <v>30</v>
@@ -20169,19 +20175,19 @@
         <v>470</v>
       </c>
       <c r="B471" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C471" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D471" s="2" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="E471" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F471" s="1" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="G471" s="1" t="s">
         <v>30</v>
@@ -20190,7 +20196,7 @@
         <v>46113</v>
       </c>
       <c r="I471" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J471" s="24"/>
     </row>
@@ -20199,19 +20205,19 @@
         <v>471</v>
       </c>
       <c r="B472" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C472" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D472" s="2" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="E472" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F472" s="1" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="G472" s="1" t="s">
         <v>30</v>
@@ -20229,19 +20235,19 @@
         <v>472</v>
       </c>
       <c r="B473" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C473" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D473" s="2" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="E473" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F473" s="1" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="G473" s="1" t="s">
         <v>30</v>
@@ -20259,19 +20265,19 @@
         <v>473</v>
       </c>
       <c r="B474" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C474" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D474" s="2" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="E474" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F474" s="1" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="G474" s="1" t="s">
         <v>30</v>
@@ -20280,7 +20286,7 @@
         <v>46118</v>
       </c>
       <c r="I474" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J474" s="24"/>
     </row>
@@ -20289,19 +20295,19 @@
         <v>474</v>
       </c>
       <c r="B475" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C475" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D475" s="2" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="E475" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F475" s="1" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="G475" s="1" t="s">
         <v>30</v>
@@ -20310,7 +20316,7 @@
         <v>46119</v>
       </c>
       <c r="I475" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J475" s="24"/>
     </row>
@@ -20319,19 +20325,19 @@
         <v>475</v>
       </c>
       <c r="B476" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C476" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D476" s="2" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="E476" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F476" s="1" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="G476" s="1" t="s">
         <v>30</v>
@@ -20340,7 +20346,7 @@
         <v>46120</v>
       </c>
       <c r="I476" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J476" s="24"/>
     </row>
@@ -20349,19 +20355,19 @@
         <v>476</v>
       </c>
       <c r="B477" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C477" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D477" s="2" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="E477" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F477" s="1" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="G477" s="1" t="s">
         <v>30</v>
@@ -20370,7 +20376,7 @@
         <v>46120</v>
       </c>
       <c r="I477" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J477" s="24"/>
     </row>
@@ -20379,19 +20385,19 @@
         <v>477</v>
       </c>
       <c r="B478" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C478" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D478" s="2" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="E478" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F478" s="1" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="G478" s="1" t="s">
         <v>30</v>
@@ -20400,7 +20406,7 @@
         <v>46120</v>
       </c>
       <c r="I478" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J478" s="24"/>
     </row>
@@ -20409,19 +20415,19 @@
         <v>478</v>
       </c>
       <c r="B479" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C479" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D479" s="2" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="E479" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F479" s="1" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="G479" s="1" t="s">
         <v>30</v>
@@ -20439,19 +20445,19 @@
         <v>479</v>
       </c>
       <c r="B480" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C480" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D480" s="2" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="E480" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F480" s="1" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="G480" s="1" t="s">
         <v>30</v>
@@ -20469,19 +20475,19 @@
         <v>480</v>
       </c>
       <c r="B481" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C481" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D481" s="2" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="E481" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F481" s="1" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="G481" s="1" t="s">
         <v>30</v>
@@ -20499,19 +20505,19 @@
         <v>481</v>
       </c>
       <c r="B482" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C482" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D482" s="2" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="E482" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F482" s="1" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="G482" s="1" t="s">
         <v>30</v>
@@ -20529,19 +20535,19 @@
         <v>482</v>
       </c>
       <c r="B483" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C483" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D483" s="2" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="E483" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F483" s="1" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="G483" s="1" t="s">
         <v>30</v>
@@ -20550,7 +20556,7 @@
         <v>46128</v>
       </c>
       <c r="I483" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J483" s="24"/>
     </row>
@@ -20559,13 +20565,13 @@
         <v>483</v>
       </c>
       <c r="B484" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C484" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D484" s="2" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="E484" s="1" t="s">
         <v>19</v>
@@ -20589,19 +20595,19 @@
         <v>484</v>
       </c>
       <c r="B485" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C485" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D485" s="2" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="E485" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F485" s="1" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="G485" s="1" t="s">
         <v>30</v>
@@ -20619,19 +20625,19 @@
         <v>485</v>
       </c>
       <c r="B486" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C486" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D486" s="2" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="E486" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F486" s="1" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="G486" s="1" t="s">
         <v>30</v>
@@ -20649,19 +20655,19 @@
         <v>486</v>
       </c>
       <c r="B487" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C487" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D487" s="2" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="E487" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F487" s="1" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="G487" s="1" t="s">
         <v>30</v>
@@ -20670,7 +20676,7 @@
         <v>46134</v>
       </c>
       <c r="I487" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J487" s="24"/>
     </row>
@@ -20679,19 +20685,19 @@
         <v>487</v>
       </c>
       <c r="B488" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C488" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D488" s="2" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="E488" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F488" s="1" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="G488" s="1" t="s">
         <v>30</v>
@@ -20709,13 +20715,13 @@
         <v>488</v>
       </c>
       <c r="B489" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C489" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D489" s="2" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="E489" s="1" t="s">
         <v>21</v>
@@ -20733,7 +20739,7 @@
         <v>574</v>
       </c>
       <c r="J489" s="3" t="s">
-        <v>1306</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="490" spans="1:10">
@@ -20741,19 +20747,19 @@
         <v>489</v>
       </c>
       <c r="B490" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C490" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D490" s="2" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="E490" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F490" s="1" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="G490" s="1" t="s">
         <v>30</v>
@@ -20771,19 +20777,19 @@
         <v>490</v>
       </c>
       <c r="B491" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C491" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D491" s="2" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="E491" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F491" s="1" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="G491" s="1" t="s">
         <v>30</v>
@@ -20801,19 +20807,19 @@
         <v>491</v>
       </c>
       <c r="B492" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C492" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D492" s="2" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="E492" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F492" s="1" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="G492" s="1" t="s">
         <v>30</v>
@@ -20822,7 +20828,7 @@
         <v>46161</v>
       </c>
       <c r="I492" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J492" s="24"/>
     </row>
@@ -20831,19 +20837,19 @@
         <v>492</v>
       </c>
       <c r="B493" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C493" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D493" s="2" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="E493" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F493" s="1" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="G493" s="1" t="s">
         <v>30</v>
@@ -20852,7 +20858,7 @@
         <v>46164</v>
       </c>
       <c r="I493" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J493" s="24"/>
     </row>
@@ -20861,19 +20867,19 @@
         <v>493</v>
       </c>
       <c r="B494" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C494" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D494" s="2" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="E494" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F494" s="1" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="G494" s="1" t="s">
         <v>30</v>
@@ -20891,19 +20897,19 @@
         <v>494</v>
       </c>
       <c r="B495" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C495" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D495" s="2" t="s">
-        <v>816</v>
+        <v>1318</v>
       </c>
       <c r="E495" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F495" s="1" t="s">
-        <v>736</v>
+        <v>1152</v>
       </c>
       <c r="G495" s="1" t="s">
         <v>30</v>
@@ -20914,26 +20920,28 @@
       <c r="I495" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="J495" s="24"/>
+      <c r="J495" s="3" t="s">
+        <v>1319</v>
+      </c>
     </row>
     <row r="496" spans="1:10">
       <c r="A496" s="4">
         <v>495</v>
       </c>
       <c r="B496" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C496" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D496" s="2" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="E496" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F496" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="G496" s="1" t="s">
         <v>30</v>
@@ -20951,13 +20959,13 @@
         <v>496</v>
       </c>
       <c r="B497" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C497" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D497" s="2" t="s">
-        <v>1314</v>
+        <v>1311</v>
       </c>
       <c r="E497" s="1" t="s">
         <v>19</v>
@@ -20981,13 +20989,13 @@
         <v>497</v>
       </c>
       <c r="B498" s="52" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C498" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D498" s="2" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="E498" s="1" t="s">
         <v>19</v>
@@ -21011,16 +21019,16 @@
         <v>498</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="C499" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D499" s="2" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="E499" s="1" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="F499" s="1" t="s">
         <v>373</v>
@@ -21041,13 +21049,13 @@
         <v>499</v>
       </c>
       <c r="B500" s="2" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="C500" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D500" s="2" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="E500" s="1" t="s">
         <v>30</v>
@@ -21173,19 +21181,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="42" t="s">
+        <v>866</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>867</v>
+      </c>
+      <c r="C2" s="42" t="s">
         <v>868</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="D2" s="43" t="s">
+        <v>894</v>
+      </c>
+      <c r="E2" s="44" t="s">
         <v>869</v>
-      </c>
-      <c r="C2" s="42" t="s">
-        <v>870</v>
-      </c>
-      <c r="D2" s="43" t="s">
-        <v>896</v>
-      </c>
-      <c r="E2" s="44" t="s">
-        <v>871</v>
       </c>
       <c r="F2" s="46">
         <v>22</v>
@@ -21193,19 +21201,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="42" t="s">
+        <v>866</v>
+      </c>
+      <c r="B3" s="42" t="s">
+        <v>867</v>
+      </c>
+      <c r="C3" s="42" t="s">
         <v>868</v>
       </c>
-      <c r="B3" s="42" t="s">
+      <c r="D3" s="43" t="s">
+        <v>895</v>
+      </c>
+      <c r="E3" s="44" t="s">
         <v>869</v>
-      </c>
-      <c r="C3" s="42" t="s">
-        <v>870</v>
-      </c>
-      <c r="D3" s="43" t="s">
-        <v>897</v>
-      </c>
-      <c r="E3" s="44" t="s">
-        <v>871</v>
       </c>
       <c r="F3" s="46">
         <v>5</v>
@@ -21213,19 +21221,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="42" t="s">
+        <v>866</v>
+      </c>
+      <c r="B4" s="42" t="s">
+        <v>867</v>
+      </c>
+      <c r="C4" s="42" t="s">
         <v>868</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="D4" s="43" t="s">
+        <v>896</v>
+      </c>
+      <c r="E4" s="44" t="s">
         <v>869</v>
-      </c>
-      <c r="C4" s="42" t="s">
-        <v>870</v>
-      </c>
-      <c r="D4" s="43" t="s">
-        <v>898</v>
-      </c>
-      <c r="E4" s="44" t="s">
-        <v>871</v>
       </c>
       <c r="F4" s="46">
         <v>1</v>
@@ -21233,19 +21241,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="42" t="s">
+        <v>866</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>867</v>
+      </c>
+      <c r="C5" s="42" t="s">
         <v>868</v>
       </c>
-      <c r="B5" s="42" t="s">
+      <c r="D5" s="43" t="s">
+        <v>897</v>
+      </c>
+      <c r="E5" s="44" t="s">
         <v>869</v>
-      </c>
-      <c r="C5" s="42" t="s">
-        <v>870</v>
-      </c>
-      <c r="D5" s="43" t="s">
-        <v>899</v>
-      </c>
-      <c r="E5" s="44" t="s">
-        <v>871</v>
       </c>
       <c r="F5" s="46">
         <v>3</v>
@@ -21253,19 +21261,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="42" t="s">
+        <v>866</v>
+      </c>
+      <c r="B6" s="42" t="s">
+        <v>867</v>
+      </c>
+      <c r="C6" s="42" t="s">
         <v>868</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="D6" s="43" t="s">
+        <v>898</v>
+      </c>
+      <c r="E6" s="44" t="s">
         <v>869</v>
-      </c>
-      <c r="C6" s="42" t="s">
-        <v>870</v>
-      </c>
-      <c r="D6" s="43" t="s">
-        <v>900</v>
-      </c>
-      <c r="E6" s="44" t="s">
-        <v>871</v>
       </c>
       <c r="F6" s="46">
         <v>3</v>
@@ -21273,19 +21281,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="42" t="s">
+        <v>866</v>
+      </c>
+      <c r="B7" s="42" t="s">
+        <v>867</v>
+      </c>
+      <c r="C7" s="42" t="s">
         <v>868</v>
       </c>
-      <c r="B7" s="42" t="s">
+      <c r="D7" s="44" t="s">
+        <v>899</v>
+      </c>
+      <c r="E7" s="44" t="s">
         <v>869</v>
-      </c>
-      <c r="C7" s="42" t="s">
-        <v>870</v>
-      </c>
-      <c r="D7" s="44" t="s">
-        <v>901</v>
-      </c>
-      <c r="E7" s="44" t="s">
-        <v>871</v>
       </c>
       <c r="F7" s="46">
         <v>6</v>
@@ -21792,10 +21800,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>688</v>
+      </c>
+      <c r="E1" t="s">
         <v>689</v>
-      </c>
-      <c r="E1" t="s">
-        <v>690</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
@@ -21804,13 +21812,13 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
+        <v>690</v>
+      </c>
+      <c r="I1" t="s">
         <v>691</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>692</v>
-      </c>
-      <c r="J1" t="s">
-        <v>693</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -21818,16 +21826,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>373</v>
@@ -21842,7 +21850,7 @@
         <v>15</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -21850,16 +21858,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>373</v>
@@ -21874,7 +21882,7 @@
         <v>15</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -21882,16 +21890,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>373</v>
@@ -21906,7 +21914,7 @@
         <v>15</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -21914,16 +21922,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>373</v>
@@ -21938,7 +21946,7 @@
         <v>15</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -21946,16 +21954,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>373</v>
@@ -21970,7 +21978,7 @@
         <v>15</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -21978,16 +21986,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>373</v>
@@ -22002,7 +22010,7 @@
         <v>15</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -22010,16 +22018,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>373</v>
@@ -22034,7 +22042,7 @@
         <v>15</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -22042,16 +22050,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D9" s="1">
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>373</v>
@@ -22066,7 +22074,7 @@
         <v>15</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -22074,16 +22082,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D10" s="1">
         <v>9</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>373</v>
@@ -22098,7 +22106,7 @@
         <v>15</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -22106,16 +22114,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D11" s="1">
         <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>373</v>
@@ -22130,7 +22138,7 @@
         <v>15</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -22138,16 +22146,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="D12" s="1">
+        <v>11</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>638</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="D12" s="1">
-        <v>11</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>639</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>373</v>
@@ -22162,7 +22170,7 @@
         <v>15</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -22170,16 +22178,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D13" s="1">
         <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>373</v>
@@ -22194,7 +22202,7 @@
         <v>15</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -22202,16 +22210,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D14" s="1">
         <v>13</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>373</v>
@@ -22226,7 +22234,7 @@
         <v>15</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -22234,16 +22242,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="D15" s="1">
+        <v>14</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>638</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="D15" s="1">
-        <v>14</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>639</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>373</v>
@@ -22258,7 +22266,7 @@
         <v>15</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -22266,16 +22274,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D16" s="1">
         <v>15</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>373</v>
@@ -22290,7 +22298,7 @@
         <v>15</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -22298,16 +22306,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D17" s="1">
         <v>16</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>373</v>
@@ -22322,7 +22330,7 @@
         <v>15</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -22330,16 +22338,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D18" s="1">
         <v>17</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>373</v>
@@ -22354,7 +22362,7 @@
         <v>15</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -22362,16 +22370,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D19" s="1">
         <v>18</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>373</v>
@@ -22386,7 +22394,7 @@
         <v>15</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -22394,16 +22402,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D20" s="1">
         <v>19</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>373</v>
@@ -22418,7 +22426,7 @@
         <v>15</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -22426,16 +22434,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D21" s="1">
         <v>20</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>373</v>
@@ -22450,7 +22458,7 @@
         <v>15</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -22458,16 +22466,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D22" s="1">
         <v>21</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>373</v>
@@ -22482,7 +22490,7 @@
         <v>15</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -22490,16 +22498,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D23" s="1">
         <v>22</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>373</v>
@@ -22514,7 +22522,7 @@
         <v>15</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -22522,16 +22530,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D24" s="1">
         <v>23</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>373</v>
@@ -22546,7 +22554,7 @@
         <v>15</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -22554,10 +22562,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D25" s="1">
         <v>24</v>
@@ -22584,10 +22592,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D26" s="1">
         <v>25</v>
@@ -22614,10 +22622,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D27" s="1">
         <v>26</v>
@@ -22644,10 +22652,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D28" s="1">
         <v>27</v>
@@ -22674,10 +22682,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D29" s="1">
         <v>28</v>
@@ -22704,10 +22712,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D30" s="1">
         <v>29</v>
@@ -22734,10 +22742,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D31" s="1">
         <v>30</v>
@@ -22764,10 +22772,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D32" s="1">
         <v>31</v>
@@ -22794,10 +22802,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D33" s="1">
         <v>32</v>
@@ -22824,10 +22832,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D34" s="1">
         <v>33</v>
@@ -22854,10 +22862,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D35" s="1">
         <v>34</v>
@@ -22884,10 +22892,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D36" s="1">
         <v>35</v>
@@ -22914,10 +22922,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D37" s="1">
         <v>36</v>
@@ -22944,10 +22952,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D38" s="1">
         <v>37</v>
@@ -22974,19 +22982,19 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C39" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>649</v>
-      </c>
       <c r="E39" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>30</v>
@@ -23004,19 +23012,19 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>30</v>
@@ -23034,16 +23042,16 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C41" s="47" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>373</v>
@@ -23064,19 +23072,19 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="C42" s="47" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D42" s="33" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="G42" t="s">
         <v>30</v>
@@ -23093,19 +23101,19 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="C43" s="47" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D43" s="33" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="E43" t="s">
         <v>13</v>
       </c>
       <c r="F43" s="33" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="G43" t="s">
         <v>30</v>
@@ -23117,7 +23125,7 @@
         <v>15</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -23125,16 +23133,16 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="C44" s="33" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="D44" s="33">
         <v>101</v>
       </c>
       <c r="E44" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F44" t="s">
         <v>605</v>
@@ -23149,7 +23157,7 @@
         <v>15</v>
       </c>
       <c r="J44" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -23157,10 +23165,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="C45" s="48" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="D45" s="33">
         <v>102</v>
@@ -23186,10 +23194,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="45" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="C46" s="48" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="D46">
         <v>201</v>
@@ -23215,10 +23223,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="45" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="C47" s="48" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="D47">
         <v>202</v>
@@ -23244,10 +23252,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="45" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="C48" s="48" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="D48">
         <v>203</v>
@@ -23273,10 +23281,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="45" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="C49" s="48" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="D49">
         <v>204</v>
@@ -23302,10 +23310,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="45" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="C50" s="48" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="D50">
         <v>205</v>
@@ -23314,7 +23322,7 @@
         <v>13</v>
       </c>
       <c r="F50" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="G50" t="s">
         <v>30</v>
@@ -23326,7 +23334,7 @@
         <v>15</v>
       </c>
       <c r="J50" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -23334,10 +23342,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="45" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="C51" s="48" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="D51">
         <v>206</v>
@@ -23346,7 +23354,7 @@
         <v>13</v>
       </c>
       <c r="F51" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="G51" t="s">
         <v>30</v>
@@ -23358,7 +23366,7 @@
         <v>15</v>
       </c>
       <c r="J51" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
     </row>
     <row r="52" spans="1:10" s="3" customFormat="1">
@@ -23366,13 +23374,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>844</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>845</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>846</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>847</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>68</v>
@@ -23390,7 +23398,7 @@
         <v>574</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="53" spans="1:10" s="3" customFormat="1">
@@ -23398,10 +23406,10 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="C53" s="1" t="s">
         <v>686</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>687</v>
       </c>
       <c r="D53" s="14">
         <v>22011316</v>
@@ -23410,7 +23418,7 @@
         <v>68</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>14</v>
@@ -23422,7 +23430,7 @@
         <v>574</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="54" spans="1:10">

--- a/data_printer.xlsx
+++ b/data_printer.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erick\Desktop\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA920499-E609-4E06-8C53-561CFCE2A39D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AE0427E-8D04-4790-AE8E-1E993AB425AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A8AA41B5-7AA1-4FF7-A9B8-54B8A4E1AF28}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4378" uniqueCount="1323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4378" uniqueCount="1324">
   <si>
     <t>INDICE</t>
   </si>
@@ -3949,9 +3949,6 @@
     <t>XAABR75657</t>
   </si>
   <si>
-    <t>Retirada do andre Gomes depois de ter danificado a impressora assim danificando os sensores de papel.</t>
-  </si>
-  <si>
     <t>CHEGOU DISTRIVISA 23/08/2024; FEITO INSTALAÇÃO SALA LICITAÇÃO 16/10/2024; INSTALADA NO MERCADO ANDRADE NO DIA 15/04/2025; RETIRADA PARA O DEPOSITO  14/05/2025; FICOU 8 MESES NA WP E NOA RESOLVERAM;</t>
   </si>
   <si>
@@ -4007,6 +4004,12 @@
   </si>
   <si>
     <t>_MERCADO ANDRADE MM - CPD</t>
+  </si>
+  <si>
+    <t>PROBLEMA DE INTUPIMENTO NA COR AZUL FEITO REPARO NA DIGI8FAX; INSTALADA SEDUC SUB SECRETARIA 04/09/2026;</t>
+  </si>
+  <si>
+    <t>Retirada do andre Gomes depois de ter danificado a impressora assim danificando os sensores de papel. INSTALADA NA ESCOLA CELINA MESQUITA 28/08/2026;</t>
   </si>
 </sst>
 </file>
@@ -5037,7 +5040,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}" name="Controle_Inventario_Impressoras" displayName="Controle_Inventario_Impressoras" ref="A1:J500" tableType="queryTable" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57">
-  <autoFilter ref="A1:J500" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}"/>
+  <autoFilter ref="A1:J500" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="SEDUC"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J27">
     <sortCondition ref="A13"/>
   </sortState>
@@ -5436,7 +5445,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" hidden="1">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -5468,7 +5477,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" hidden="1">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -5500,7 +5509,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" hidden="1">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -5532,7 +5541,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" hidden="1">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -5564,7 +5573,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" hidden="1">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -5596,7 +5605,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" hidden="1">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -5628,7 +5637,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" hidden="1">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -5660,7 +5669,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" hidden="1">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -5690,7 +5699,7 @@
       </c>
       <c r="J9" s="7"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" hidden="1">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -5720,7 +5729,7 @@
       </c>
       <c r="J10" s="7"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" hidden="1">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -5752,7 +5761,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" hidden="1">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -5769,7 +5778,7 @@
         <v>856</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>19</v>
@@ -5784,7 +5793,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" hidden="1">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -5816,7 +5825,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" hidden="1">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -5848,7 +5857,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" hidden="1">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -5880,7 +5889,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" hidden="1">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -5909,7 +5918,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" hidden="1">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -5941,7 +5950,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" hidden="1">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -5973,7 +5982,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" hidden="1">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -6037,7 +6046,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" hidden="1">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -6069,7 +6078,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="15.75" customHeight="1">
+    <row r="22" spans="1:10" ht="15.75" hidden="1" customHeight="1">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -6101,7 +6110,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" hidden="1">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -6133,7 +6142,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" hidden="1">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -6165,7 +6174,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" hidden="1">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -6197,7 +6206,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" hidden="1">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -6226,7 +6235,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" hidden="1">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -6255,7 +6264,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" hidden="1">
       <c r="A28" s="4">
         <v>27</v>
       </c>
@@ -6287,7 +6296,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" hidden="1">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -6319,7 +6328,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" hidden="1">
       <c r="A30" s="4">
         <v>29</v>
       </c>
@@ -6351,7 +6360,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" hidden="1">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -6383,7 +6392,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" hidden="1">
       <c r="A32" s="4">
         <v>31</v>
       </c>
@@ -6415,7 +6424,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" hidden="1">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -6464,7 +6473,7 @@
         <v>19</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="G34" s="4" t="s">
         <v>14</v>
@@ -6476,10 +6485,10 @@
         <v>574</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>1307</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" hidden="1">
       <c r="A35" s="4">
         <v>34</v>
       </c>
@@ -6511,7 +6520,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" hidden="1">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -6543,7 +6552,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" hidden="1">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -6572,7 +6581,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" hidden="1">
       <c r="A38" s="4">
         <v>37</v>
       </c>
@@ -6604,7 +6613,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" hidden="1">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -6636,7 +6645,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:10" hidden="1">
       <c r="A40" s="4">
         <v>39</v>
       </c>
@@ -6668,7 +6677,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:10" hidden="1">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -6700,7 +6709,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" hidden="1">
       <c r="A42" s="4">
         <v>41</v>
       </c>
@@ -6732,7 +6741,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:10" hidden="1">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -6764,7 +6773,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" hidden="1">
       <c r="A44" s="4">
         <v>43</v>
       </c>
@@ -6796,7 +6805,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:10" hidden="1">
       <c r="A45" s="4">
         <v>44</v>
       </c>
@@ -6825,7 +6834,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:10" hidden="1">
       <c r="A46" s="4">
         <v>45</v>
       </c>
@@ -6857,7 +6866,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:10" hidden="1">
       <c r="A47" s="4">
         <v>46</v>
       </c>
@@ -6889,7 +6898,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" hidden="1">
       <c r="A48" s="4">
         <v>47</v>
       </c>
@@ -6921,7 +6930,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" hidden="1">
       <c r="A49" s="4">
         <v>48</v>
       </c>
@@ -6950,7 +6959,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:10" hidden="1">
       <c r="A50" s="4">
         <v>49</v>
       </c>
@@ -6979,7 +6988,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" hidden="1">
       <c r="A51" s="4">
         <v>50</v>
       </c>
@@ -7011,7 +7020,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" hidden="1">
       <c r="A52" s="4">
         <v>51</v>
       </c>
@@ -7043,7 +7052,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:10" hidden="1">
       <c r="A53" s="4">
         <v>52</v>
       </c>
@@ -7075,7 +7084,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" hidden="1">
       <c r="A54" s="4">
         <v>53</v>
       </c>
@@ -7107,7 +7116,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" hidden="1">
       <c r="A55" s="4">
         <v>54</v>
       </c>
@@ -7136,7 +7145,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:10" hidden="1">
       <c r="A56" s="4">
         <v>55</v>
       </c>
@@ -7165,7 +7174,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" hidden="1">
       <c r="A57" s="4">
         <v>56</v>
       </c>
@@ -7194,7 +7203,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" hidden="1">
       <c r="A58" s="4">
         <v>57</v>
       </c>
@@ -7223,7 +7232,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" hidden="1">
       <c r="A59" s="4">
         <v>58</v>
       </c>
@@ -7252,7 +7261,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" hidden="1">
       <c r="A60" s="4">
         <v>59</v>
       </c>
@@ -7281,7 +7290,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:10" hidden="1">
       <c r="A61" s="4">
         <v>60</v>
       </c>
@@ -7313,7 +7322,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:10" hidden="1">
       <c r="A62" s="4">
         <v>61</v>
       </c>
@@ -7345,7 +7354,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:10" hidden="1">
       <c r="A63" s="4">
         <v>62</v>
       </c>
@@ -7374,7 +7383,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:10" hidden="1">
       <c r="A64" s="4">
         <v>63</v>
       </c>
@@ -7406,7 +7415,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" spans="1:10" hidden="1">
       <c r="A65" s="4">
         <v>64</v>
       </c>
@@ -7435,7 +7444,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" spans="1:10" hidden="1">
       <c r="A66" s="4">
         <v>65</v>
       </c>
@@ -7464,7 +7473,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="67" spans="1:10">
+    <row r="67" spans="1:10" hidden="1">
       <c r="A67" s="4">
         <v>66</v>
       </c>
@@ -7493,7 +7502,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" spans="1:10" hidden="1">
       <c r="A68" s="4">
         <v>67</v>
       </c>
@@ -7522,7 +7531,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" spans="1:10" hidden="1">
       <c r="A69" s="4">
         <v>68</v>
       </c>
@@ -7554,7 +7563,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" spans="1:10" hidden="1">
       <c r="A70" s="4">
         <v>69</v>
       </c>
@@ -7586,7 +7595,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" spans="1:10" hidden="1">
       <c r="A71" s="4">
         <v>70</v>
       </c>
@@ -7647,7 +7656,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" spans="1:10" hidden="1">
       <c r="A73" s="4">
         <v>72</v>
       </c>
@@ -7679,7 +7688,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" spans="1:10" hidden="1">
       <c r="A74" s="4">
         <v>73</v>
       </c>
@@ -7711,7 +7720,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="75" spans="1:10">
+    <row r="75" spans="1:10" hidden="1">
       <c r="A75" s="4">
         <v>74</v>
       </c>
@@ -7740,7 +7749,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="76" spans="1:10">
+    <row r="76" spans="1:10" hidden="1">
       <c r="A76" s="4">
         <v>75</v>
       </c>
@@ -7772,7 +7781,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="77" spans="1:10">
+    <row r="77" spans="1:10" hidden="1">
       <c r="A77" s="4">
         <v>76</v>
       </c>
@@ -7804,7 +7813,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="78" spans="1:10">
+    <row r="78" spans="1:10" hidden="1">
       <c r="A78" s="4">
         <v>77</v>
       </c>
@@ -7836,7 +7845,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" spans="1:10" hidden="1">
       <c r="A79" s="4">
         <v>78</v>
       </c>
@@ -7868,7 +7877,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="80" spans="1:10">
+    <row r="80" spans="1:10" hidden="1">
       <c r="A80" s="4">
         <v>79</v>
       </c>
@@ -7900,7 +7909,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="81" spans="1:10">
+    <row r="81" spans="1:10" hidden="1">
       <c r="A81" s="4">
         <v>80</v>
       </c>
@@ -7932,7 +7941,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="82" spans="1:10">
+    <row r="82" spans="1:10" hidden="1">
       <c r="A82" s="4">
         <v>81</v>
       </c>
@@ -7958,7 +7967,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="83" spans="1:10">
+    <row r="83" spans="1:10" hidden="1">
       <c r="A83" s="4">
         <v>82</v>
       </c>
@@ -7984,7 +7993,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="84" spans="1:10">
+    <row r="84" spans="1:10" hidden="1">
       <c r="A84" s="4">
         <v>83</v>
       </c>
@@ -8010,7 +8019,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="85" spans="1:10">
+    <row r="85" spans="1:10" hidden="1">
       <c r="A85" s="4">
         <v>84</v>
       </c>
@@ -8042,7 +8051,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="86" spans="1:10">
+    <row r="86" spans="1:10" hidden="1">
       <c r="A86" s="4">
         <v>85</v>
       </c>
@@ -8074,7 +8083,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="87" spans="1:10">
+    <row r="87" spans="1:10" hidden="1">
       <c r="A87" s="4">
         <v>86</v>
       </c>
@@ -8106,7 +8115,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="88" spans="1:10">
+    <row r="88" spans="1:10" hidden="1">
       <c r="A88" s="4">
         <v>87</v>
       </c>
@@ -8138,7 +8147,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="89" spans="1:10">
+    <row r="89" spans="1:10" hidden="1">
       <c r="A89" s="4">
         <v>88</v>
       </c>
@@ -8167,7 +8176,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="90" spans="1:10">
+    <row r="90" spans="1:10" hidden="1">
       <c r="A90" s="4">
         <v>89</v>
       </c>
@@ -8199,7 +8208,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="91" spans="1:10">
+    <row r="91" spans="1:10" hidden="1">
       <c r="A91" s="4">
         <v>90</v>
       </c>
@@ -8231,7 +8240,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="92" spans="1:10">
+    <row r="92" spans="1:10" hidden="1">
       <c r="A92" s="4">
         <v>91</v>
       </c>
@@ -8257,7 +8266,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="93" spans="1:10">
+    <row r="93" spans="1:10" hidden="1">
       <c r="A93" s="4">
         <v>92</v>
       </c>
@@ -8283,7 +8292,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="94" spans="1:10">
+    <row r="94" spans="1:10" hidden="1">
       <c r="A94" s="4">
         <v>93</v>
       </c>
@@ -8315,7 +8324,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="95" spans="1:10">
+    <row r="95" spans="1:10" hidden="1">
       <c r="A95" s="4">
         <v>94</v>
       </c>
@@ -8344,7 +8353,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="96" spans="1:10">
+    <row r="96" spans="1:10" hidden="1">
       <c r="A96" s="4">
         <v>95</v>
       </c>
@@ -8373,7 +8382,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="97" spans="1:10">
+    <row r="97" spans="1:10" hidden="1">
       <c r="A97" s="4">
         <v>96</v>
       </c>
@@ -8402,7 +8411,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="98" spans="1:10">
+    <row r="98" spans="1:10" hidden="1">
       <c r="A98" s="4">
         <v>97</v>
       </c>
@@ -8431,7 +8440,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="99" spans="1:10">
+    <row r="99" spans="1:10" hidden="1">
       <c r="A99" s="4">
         <v>98</v>
       </c>
@@ -8463,7 +8472,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="100" spans="1:10">
+    <row r="100" spans="1:10" hidden="1">
       <c r="A100" s="4">
         <v>99</v>
       </c>
@@ -8495,7 +8504,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="101" spans="1:10">
+    <row r="101" spans="1:10" hidden="1">
       <c r="A101" s="4">
         <v>100</v>
       </c>
@@ -8527,7 +8536,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="102" spans="1:10">
+    <row r="102" spans="1:10" hidden="1">
       <c r="A102" s="4">
         <v>101</v>
       </c>
@@ -8559,7 +8568,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="103" spans="1:10">
+    <row r="103" spans="1:10" hidden="1">
       <c r="A103" s="4">
         <v>102</v>
       </c>
@@ -8591,7 +8600,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="104" spans="1:10">
+    <row r="104" spans="1:10" hidden="1">
       <c r="A104" s="4">
         <v>103</v>
       </c>
@@ -8623,7 +8632,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="105" spans="1:10">
+    <row r="105" spans="1:10" hidden="1">
       <c r="A105" s="4">
         <v>104</v>
       </c>
@@ -8655,7 +8664,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="106" spans="1:10">
+    <row r="106" spans="1:10" hidden="1">
       <c r="A106" s="4">
         <v>105</v>
       </c>
@@ -8687,7 +8696,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="107" spans="1:10">
+    <row r="107" spans="1:10" hidden="1">
       <c r="A107" s="4">
         <v>106</v>
       </c>
@@ -8719,7 +8728,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="108" spans="1:10">
+    <row r="108" spans="1:10" hidden="1">
       <c r="A108" s="4">
         <v>107</v>
       </c>
@@ -8747,7 +8756,7 @@
       </c>
       <c r="J108" s="24"/>
     </row>
-    <row r="109" spans="1:10">
+    <row r="109" spans="1:10" hidden="1">
       <c r="A109" s="4">
         <v>108</v>
       </c>
@@ -8779,7 +8788,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="110" spans="1:10">
+    <row r="110" spans="1:10" hidden="1">
       <c r="A110" s="4">
         <v>109</v>
       </c>
@@ -8811,7 +8820,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="111" spans="1:10">
+    <row r="111" spans="1:10" hidden="1">
       <c r="A111" s="4">
         <v>110</v>
       </c>
@@ -8843,7 +8852,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="112" spans="1:10">
+    <row r="112" spans="1:10" hidden="1">
       <c r="A112" s="4">
         <v>111</v>
       </c>
@@ -8875,7 +8884,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="113" spans="1:10">
+    <row r="113" spans="1:10" hidden="1">
       <c r="A113" s="4">
         <v>112</v>
       </c>
@@ -8907,7 +8916,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="114" spans="1:10">
+    <row r="114" spans="1:10" hidden="1">
       <c r="A114" s="4">
         <v>113</v>
       </c>
@@ -8939,7 +8948,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="115" spans="1:10">
+    <row r="115" spans="1:10" hidden="1">
       <c r="A115" s="4">
         <v>114</v>
       </c>
@@ -8971,7 +8980,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="116" spans="1:10">
+    <row r="116" spans="1:10" hidden="1">
       <c r="A116" s="4">
         <v>115</v>
       </c>
@@ -9003,7 +9012,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="117" spans="1:10">
+    <row r="117" spans="1:10" hidden="1">
       <c r="A117" s="4">
         <v>116</v>
       </c>
@@ -9035,7 +9044,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="118" spans="1:10">
+    <row r="118" spans="1:10" hidden="1">
       <c r="A118" s="4">
         <v>117</v>
       </c>
@@ -9067,7 +9076,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="119" spans="1:10">
+    <row r="119" spans="1:10" hidden="1">
       <c r="A119" s="4">
         <v>118</v>
       </c>
@@ -9099,7 +9108,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="120" spans="1:10">
+    <row r="120" spans="1:10" hidden="1">
       <c r="A120" s="4">
         <v>119</v>
       </c>
@@ -9131,7 +9140,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="121" spans="1:10">
+    <row r="121" spans="1:10" hidden="1">
       <c r="A121" s="4">
         <v>120</v>
       </c>
@@ -9163,7 +9172,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="122" spans="1:10">
+    <row r="122" spans="1:10" hidden="1">
       <c r="A122" s="4">
         <v>121</v>
       </c>
@@ -9195,7 +9204,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="123" spans="1:10">
+    <row r="123" spans="1:10" hidden="1">
       <c r="A123" s="4">
         <v>122</v>
       </c>
@@ -9227,7 +9236,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="124" spans="1:10">
+    <row r="124" spans="1:10" hidden="1">
       <c r="A124" s="4">
         <v>123</v>
       </c>
@@ -9259,7 +9268,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="125" spans="1:10">
+    <row r="125" spans="1:10" hidden="1">
       <c r="A125" s="4">
         <v>124</v>
       </c>
@@ -9323,7 +9332,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="127" spans="1:10">
+    <row r="127" spans="1:10" hidden="1">
       <c r="A127" s="4">
         <v>126</v>
       </c>
@@ -9355,7 +9364,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="128" spans="1:10">
+    <row r="128" spans="1:10" hidden="1">
       <c r="A128" s="4">
         <v>127</v>
       </c>
@@ -9387,7 +9396,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="129" spans="1:10">
+    <row r="129" spans="1:10" hidden="1">
       <c r="A129" s="4">
         <v>128</v>
       </c>
@@ -9419,7 +9428,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="130" spans="1:10">
+    <row r="130" spans="1:10" hidden="1">
       <c r="A130" s="4">
         <v>129</v>
       </c>
@@ -9451,7 +9460,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="131" spans="1:10">
+    <row r="131" spans="1:10" hidden="1">
       <c r="A131" s="4">
         <v>130</v>
       </c>
@@ -9579,7 +9588,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="135" spans="1:10">
+    <row r="135" spans="1:10" hidden="1">
       <c r="A135" s="4">
         <v>134</v>
       </c>
@@ -9643,7 +9652,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="137" spans="1:10">
+    <row r="137" spans="1:10" hidden="1">
       <c r="A137" s="4">
         <v>136</v>
       </c>
@@ -9675,7 +9684,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="138" spans="1:10">
+    <row r="138" spans="1:10" hidden="1">
       <c r="A138" s="4">
         <v>137</v>
       </c>
@@ -9707,7 +9716,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="139" spans="1:10">
+    <row r="139" spans="1:10" hidden="1">
       <c r="A139" s="4">
         <v>138</v>
       </c>
@@ -9739,7 +9748,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="140" spans="1:10">
+    <row r="140" spans="1:10" hidden="1">
       <c r="A140" s="4">
         <v>139</v>
       </c>
@@ -9771,7 +9780,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="141" spans="1:10">
+    <row r="141" spans="1:10" hidden="1">
       <c r="A141" s="4">
         <v>140</v>
       </c>
@@ -9800,10 +9809,10 @@
         <v>574</v>
       </c>
       <c r="J141" s="12" t="s">
-        <v>1305</v>
-      </c>
-    </row>
-    <row r="142" spans="1:10">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" hidden="1">
       <c r="A142" s="4">
         <v>141</v>
       </c>
@@ -9835,7 +9844,7 @@
         <v>1297</v>
       </c>
     </row>
-    <row r="143" spans="1:10">
+    <row r="143" spans="1:10" hidden="1">
       <c r="A143" s="4">
         <v>142</v>
       </c>
@@ -9865,7 +9874,7 @@
       </c>
       <c r="J143" s="24"/>
     </row>
-    <row r="144" spans="1:10">
+    <row r="144" spans="1:10" hidden="1">
       <c r="A144" s="4">
         <v>143</v>
       </c>
@@ -9897,7 +9906,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="145" spans="1:10">
+    <row r="145" spans="1:10" hidden="1">
       <c r="A145" s="4">
         <v>144</v>
       </c>
@@ -9929,7 +9938,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="146" spans="1:10">
+    <row r="146" spans="1:10" hidden="1">
       <c r="A146" s="4">
         <v>145</v>
       </c>
@@ -9993,7 +10002,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="148" spans="1:10">
+    <row r="148" spans="1:10" hidden="1">
       <c r="A148" s="4">
         <v>147</v>
       </c>
@@ -10025,7 +10034,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="149" spans="1:10">
+    <row r="149" spans="1:10" hidden="1">
       <c r="A149" s="4">
         <v>148</v>
       </c>
@@ -10213,7 +10222,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="155" spans="1:10">
+    <row r="155" spans="1:10" hidden="1">
       <c r="A155" s="4">
         <v>154</v>
       </c>
@@ -10245,7 +10254,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="156" spans="1:10">
+    <row r="156" spans="1:10" hidden="1">
       <c r="A156" s="4">
         <v>155</v>
       </c>
@@ -10277,7 +10286,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="157" spans="1:10">
+    <row r="157" spans="1:10" hidden="1">
       <c r="A157" s="4">
         <v>156</v>
       </c>
@@ -10309,7 +10318,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="158" spans="1:10">
+    <row r="158" spans="1:10" hidden="1">
       <c r="A158" s="4">
         <v>157</v>
       </c>
@@ -10320,13 +10329,13 @@
         <v>83</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="G158" s="1" t="s">
         <v>14</v>
@@ -10339,7 +10348,7 @@
       </c>
       <c r="J158" s="55"/>
     </row>
-    <row r="159" spans="1:10">
+    <row r="159" spans="1:10" hidden="1">
       <c r="A159" s="4">
         <v>158</v>
       </c>
@@ -10371,7 +10380,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="160" spans="1:10">
+    <row r="160" spans="1:10" hidden="1">
       <c r="A160" s="4">
         <v>159</v>
       </c>
@@ -10403,7 +10412,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="161" spans="1:10">
+    <row r="161" spans="1:10" hidden="1">
       <c r="A161" s="4">
         <v>160</v>
       </c>
@@ -10435,7 +10444,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="162" spans="1:10">
+    <row r="162" spans="1:10" hidden="1">
       <c r="A162" s="4">
         <v>161</v>
       </c>
@@ -10467,7 +10476,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="163" spans="1:10">
+    <row r="163" spans="1:10" hidden="1">
       <c r="A163" s="4">
         <v>162</v>
       </c>
@@ -10499,7 +10508,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="164" spans="1:10">
+    <row r="164" spans="1:10" hidden="1">
       <c r="A164" s="4">
         <v>163</v>
       </c>
@@ -10531,7 +10540,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="165" spans="1:10">
+    <row r="165" spans="1:10" hidden="1">
       <c r="A165" s="4">
         <v>164</v>
       </c>
@@ -10563,7 +10572,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="166" spans="1:10">
+    <row r="166" spans="1:10" hidden="1">
       <c r="A166" s="4">
         <v>165</v>
       </c>
@@ -10592,7 +10601,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="167" spans="1:10">
+    <row r="167" spans="1:10" hidden="1">
       <c r="A167" s="4">
         <v>166</v>
       </c>
@@ -10621,7 +10630,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="168" spans="1:10">
+    <row r="168" spans="1:10" hidden="1">
       <c r="A168" s="4">
         <v>167</v>
       </c>
@@ -10648,7 +10657,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="169" spans="1:10">
+    <row r="169" spans="1:10" hidden="1">
       <c r="A169" s="4">
         <v>168</v>
       </c>
@@ -10680,7 +10689,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="170" spans="1:10">
+    <row r="170" spans="1:10" hidden="1">
       <c r="A170" s="4">
         <v>169</v>
       </c>
@@ -10709,7 +10718,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="171" spans="1:10">
+    <row r="171" spans="1:10" hidden="1">
       <c r="A171" s="4">
         <v>170</v>
       </c>
@@ -10741,7 +10750,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="172" spans="1:10">
+    <row r="172" spans="1:10" hidden="1">
       <c r="A172" s="4">
         <v>171</v>
       </c>
@@ -10773,7 +10782,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="173" spans="1:10">
+    <row r="173" spans="1:10" hidden="1">
       <c r="A173" s="4">
         <v>172</v>
       </c>
@@ -10805,7 +10814,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="174" spans="1:10">
+    <row r="174" spans="1:10" hidden="1">
       <c r="A174" s="4">
         <v>173</v>
       </c>
@@ -10837,7 +10846,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="175" spans="1:10">
+    <row r="175" spans="1:10" hidden="1">
       <c r="A175" s="4">
         <v>174</v>
       </c>
@@ -10866,7 +10875,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="176" spans="1:10">
+    <row r="176" spans="1:10" hidden="1">
       <c r="A176" s="4">
         <v>175</v>
       </c>
@@ -10895,7 +10904,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="177" spans="1:10">
+    <row r="177" spans="1:10" hidden="1">
       <c r="A177" s="4">
         <v>176</v>
       </c>
@@ -10927,7 +10936,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="178" spans="1:10">
+    <row r="178" spans="1:10" hidden="1">
       <c r="A178" s="4">
         <v>177</v>
       </c>
@@ -10953,7 +10962,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="179" spans="1:10">
+    <row r="179" spans="1:10" hidden="1">
       <c r="A179" s="4">
         <v>178</v>
       </c>
@@ -10983,7 +10992,7 @@
       </c>
       <c r="J179" s="24"/>
     </row>
-    <row r="180" spans="1:10">
+    <row r="180" spans="1:10" hidden="1">
       <c r="A180" s="4">
         <v>179</v>
       </c>
@@ -11015,7 +11024,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="181" spans="1:10">
+    <row r="181" spans="1:10" hidden="1">
       <c r="A181" s="4">
         <v>180</v>
       </c>
@@ -11044,7 +11053,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="182" spans="1:10">
+    <row r="182" spans="1:10" hidden="1">
       <c r="A182" s="4">
         <v>181</v>
       </c>
@@ -11076,7 +11085,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="183" spans="1:10">
+    <row r="183" spans="1:10" hidden="1">
       <c r="A183" s="4">
         <v>182</v>
       </c>
@@ -11105,7 +11114,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="184" spans="1:10">
+    <row r="184" spans="1:10" hidden="1">
       <c r="A184" s="4">
         <v>183</v>
       </c>
@@ -11134,7 +11143,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="185" spans="1:10">
+    <row r="185" spans="1:10" hidden="1">
       <c r="A185" s="4">
         <v>184</v>
       </c>
@@ -11163,7 +11172,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="186" spans="1:10">
+    <row r="186" spans="1:10" hidden="1">
       <c r="A186" s="4">
         <v>185</v>
       </c>
@@ -11192,7 +11201,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="187" spans="1:10">
+    <row r="187" spans="1:10" hidden="1">
       <c r="A187" s="4">
         <v>186</v>
       </c>
@@ -11221,7 +11230,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="188" spans="1:10">
+    <row r="188" spans="1:10" hidden="1">
       <c r="A188" s="4">
         <v>187</v>
       </c>
@@ -11250,7 +11259,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="189" spans="1:10">
+    <row r="189" spans="1:10" hidden="1">
       <c r="A189" s="4">
         <v>188</v>
       </c>
@@ -11279,7 +11288,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="190" spans="1:10">
+    <row r="190" spans="1:10" hidden="1">
       <c r="A190" s="4">
         <v>189</v>
       </c>
@@ -11308,7 +11317,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="191" spans="1:10">
+    <row r="191" spans="1:10" hidden="1">
       <c r="A191" s="4">
         <v>190</v>
       </c>
@@ -11337,7 +11346,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="192" spans="1:10">
+    <row r="192" spans="1:10" hidden="1">
       <c r="A192" s="4">
         <v>191</v>
       </c>
@@ -11366,7 +11375,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="193" spans="1:10">
+    <row r="193" spans="1:10" hidden="1">
       <c r="A193" s="4">
         <v>192</v>
       </c>
@@ -11395,7 +11404,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="194" spans="1:10">
+    <row r="194" spans="1:10" hidden="1">
       <c r="A194" s="4">
         <v>193</v>
       </c>
@@ -11424,7 +11433,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="195" spans="1:10">
+    <row r="195" spans="1:10" hidden="1">
       <c r="A195" s="4">
         <v>194</v>
       </c>
@@ -11453,7 +11462,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="196" spans="1:10">
+    <row r="196" spans="1:10" hidden="1">
       <c r="A196" s="4">
         <v>195</v>
       </c>
@@ -11482,7 +11491,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="197" spans="1:10">
+    <row r="197" spans="1:10" hidden="1">
       <c r="A197" s="4">
         <v>196</v>
       </c>
@@ -11511,7 +11520,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="198" spans="1:10">
+    <row r="198" spans="1:10" hidden="1">
       <c r="A198" s="4">
         <v>197</v>
       </c>
@@ -11540,7 +11549,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="199" spans="1:10">
+    <row r="199" spans="1:10" hidden="1">
       <c r="A199" s="4">
         <v>198</v>
       </c>
@@ -11569,7 +11578,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="200" spans="1:10">
+    <row r="200" spans="1:10" hidden="1">
       <c r="A200" s="4">
         <v>199</v>
       </c>
@@ -11598,7 +11607,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="201" spans="1:10">
+    <row r="201" spans="1:10" hidden="1">
       <c r="A201" s="4">
         <v>200</v>
       </c>
@@ -11627,7 +11636,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="202" spans="1:10">
+    <row r="202" spans="1:10" hidden="1">
       <c r="A202" s="4">
         <v>201</v>
       </c>
@@ -11656,7 +11665,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="203" spans="1:10">
+    <row r="203" spans="1:10" hidden="1">
       <c r="A203" s="4">
         <v>202</v>
       </c>
@@ -11685,7 +11694,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="204" spans="1:10">
+    <row r="204" spans="1:10" hidden="1">
       <c r="A204" s="4">
         <v>203</v>
       </c>
@@ -11714,7 +11723,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="205" spans="1:10">
+    <row r="205" spans="1:10" hidden="1">
       <c r="A205" s="4">
         <v>204</v>
       </c>
@@ -11746,7 +11755,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="206" spans="1:10">
+    <row r="206" spans="1:10" hidden="1">
       <c r="A206" s="4">
         <v>205</v>
       </c>
@@ -11778,7 +11787,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="207" spans="1:10">
+    <row r="207" spans="1:10" hidden="1">
       <c r="A207" s="4">
         <v>206</v>
       </c>
@@ -11810,7 +11819,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="208" spans="1:10">
+    <row r="208" spans="1:10" hidden="1">
       <c r="A208" s="4">
         <v>207</v>
       </c>
@@ -11842,7 +11851,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="209" spans="1:10">
+    <row r="209" spans="1:10" hidden="1">
       <c r="A209" s="4">
         <v>208</v>
       </c>
@@ -11872,7 +11881,7 @@
       </c>
       <c r="J209" s="24"/>
     </row>
-    <row r="210" spans="1:10">
+    <row r="210" spans="1:10" hidden="1">
       <c r="A210" s="4">
         <v>209</v>
       </c>
@@ -11904,7 +11913,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="211" spans="1:10">
+    <row r="211" spans="1:10" hidden="1">
       <c r="A211" s="4">
         <v>210</v>
       </c>
@@ -11936,7 +11945,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="212" spans="1:10">
+    <row r="212" spans="1:10" hidden="1">
       <c r="A212" s="4">
         <v>211</v>
       </c>
@@ -12000,7 +12009,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="214" spans="1:10">
+    <row r="214" spans="1:10" hidden="1">
       <c r="A214" s="4">
         <v>213</v>
       </c>
@@ -12032,7 +12041,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="215" spans="1:10">
+    <row r="215" spans="1:10" hidden="1">
       <c r="A215" s="4">
         <v>214</v>
       </c>
@@ -12049,7 +12058,7 @@
         <v>68</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="G215" s="4" t="s">
         <v>14</v>
@@ -12061,7 +12070,7 @@
         <v>574</v>
       </c>
       <c r="J215" s="3" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="216" spans="1:10">
@@ -12096,7 +12105,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="217" spans="1:10">
+    <row r="217" spans="1:10" hidden="1">
       <c r="A217" s="4">
         <v>216</v>
       </c>
@@ -12128,7 +12137,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="218" spans="1:10">
+    <row r="218" spans="1:10" hidden="1">
       <c r="A218" s="4">
         <v>217</v>
       </c>
@@ -12224,7 +12233,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="221" spans="1:10">
+    <row r="221" spans="1:10" hidden="1">
       <c r="A221" s="4">
         <v>220</v>
       </c>
@@ -12256,7 +12265,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="222" spans="1:10">
+    <row r="222" spans="1:10" hidden="1">
       <c r="A222" s="4">
         <v>221</v>
       </c>
@@ -12288,7 +12297,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="223" spans="1:10">
+    <row r="223" spans="1:10" hidden="1">
       <c r="A223" s="4">
         <v>222</v>
       </c>
@@ -12320,7 +12329,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="224" spans="1:10">
+    <row r="224" spans="1:10" hidden="1">
       <c r="A224" s="4">
         <v>223</v>
       </c>
@@ -12352,7 +12361,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="225" spans="1:10">
+    <row r="225" spans="1:10" hidden="1">
       <c r="A225" s="4">
         <v>224</v>
       </c>
@@ -12384,7 +12393,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="226" spans="1:10">
+    <row r="226" spans="1:10" hidden="1">
       <c r="A226" s="4">
         <v>225</v>
       </c>
@@ -12416,7 +12425,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="227" spans="1:10">
+    <row r="227" spans="1:10" hidden="1">
       <c r="A227" s="4">
         <v>226</v>
       </c>
@@ -12480,7 +12489,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="229" spans="1:10">
+    <row r="229" spans="1:10" hidden="1">
       <c r="A229" s="4">
         <v>228</v>
       </c>
@@ -12544,7 +12553,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="231" spans="1:10">
+    <row r="231" spans="1:10" hidden="1">
       <c r="A231" s="4">
         <v>230</v>
       </c>
@@ -12608,7 +12617,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="233" spans="1:10">
+    <row r="233" spans="1:10" hidden="1">
       <c r="A233" s="4">
         <v>232</v>
       </c>
@@ -12640,7 +12649,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="234" spans="1:10">
+    <row r="234" spans="1:10" hidden="1">
       <c r="A234" s="4">
         <v>233</v>
       </c>
@@ -12704,7 +12713,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="236" spans="1:10">
+    <row r="236" spans="1:10" hidden="1">
       <c r="A236" s="4">
         <v>235</v>
       </c>
@@ -12736,7 +12745,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="237" spans="1:10">
+    <row r="237" spans="1:10" hidden="1">
       <c r="A237" s="4">
         <v>236</v>
       </c>
@@ -12768,7 +12777,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="238" spans="1:10">
+    <row r="238" spans="1:10" hidden="1">
       <c r="A238" s="4">
         <v>237</v>
       </c>
@@ -12814,10 +12823,10 @@
         <v>352</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>1037</v>
+        <v>23</v>
       </c>
       <c r="G239" s="4" t="s">
         <v>14</v>
@@ -12832,7 +12841,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="240" spans="1:10">
+    <row r="240" spans="1:10" hidden="1">
       <c r="A240" s="4">
         <v>239</v>
       </c>
@@ -12864,7 +12873,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="241" spans="1:10">
+    <row r="241" spans="1:10" hidden="1">
       <c r="A241" s="4">
         <v>240</v>
       </c>
@@ -13056,7 +13065,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="247" spans="1:10">
+    <row r="247" spans="1:10" hidden="1">
       <c r="A247" s="4">
         <v>246</v>
       </c>
@@ -13088,7 +13097,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="248" spans="1:10">
+    <row r="248" spans="1:10" hidden="1">
       <c r="A248" s="4">
         <v>247</v>
       </c>
@@ -13118,7 +13127,7 @@
       </c>
       <c r="J248" s="20"/>
     </row>
-    <row r="249" spans="1:10">
+    <row r="249" spans="1:10" hidden="1">
       <c r="A249" s="4">
         <v>248</v>
       </c>
@@ -13135,7 +13144,7 @@
         <v>856</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="G249" s="13" t="s">
         <v>14</v>
@@ -13150,7 +13159,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="250" spans="1:10">
+    <row r="250" spans="1:10" hidden="1">
       <c r="A250" s="4">
         <v>249</v>
       </c>
@@ -13167,7 +13176,7 @@
         <v>68</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="G250" s="4" t="s">
         <v>14</v>
@@ -13179,10 +13188,10 @@
         <v>574</v>
       </c>
       <c r="J250" s="3" t="s">
-        <v>1316</v>
-      </c>
-    </row>
-    <row r="251" spans="1:10">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="251" spans="1:10" hidden="1">
       <c r="A251" s="4">
         <v>250</v>
       </c>
@@ -13214,7 +13223,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="252" spans="1:10">
+    <row r="252" spans="1:10" hidden="1">
       <c r="A252" s="4">
         <v>251</v>
       </c>
@@ -13243,10 +13252,10 @@
         <v>574</v>
       </c>
       <c r="J252" s="3" t="s">
-        <v>1317</v>
-      </c>
-    </row>
-    <row r="253" spans="1:10">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="253" spans="1:10" hidden="1">
       <c r="A253" s="4">
         <v>252</v>
       </c>
@@ -13278,7 +13287,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="254" spans="1:10">
+    <row r="254" spans="1:10" hidden="1">
       <c r="A254" s="4">
         <v>253</v>
       </c>
@@ -13307,7 +13316,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="255" spans="1:10">
+    <row r="255" spans="1:10" hidden="1">
       <c r="A255" s="4">
         <v>254</v>
       </c>
@@ -13324,7 +13333,7 @@
         <v>856</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="G255" s="4" t="s">
         <v>14</v>
@@ -13339,7 +13348,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="256" spans="1:10">
+    <row r="256" spans="1:10" hidden="1">
       <c r="A256" s="4">
         <v>255</v>
       </c>
@@ -13371,7 +13380,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="257" spans="1:10">
+    <row r="257" spans="1:10" hidden="1">
       <c r="A257" s="4">
         <v>256</v>
       </c>
@@ -13403,7 +13412,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="258" spans="1:10">
+    <row r="258" spans="1:10" hidden="1">
       <c r="A258" s="4">
         <v>257</v>
       </c>
@@ -13432,7 +13441,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="259" spans="1:10">
+    <row r="259" spans="1:10" hidden="1">
       <c r="A259" s="4">
         <v>258</v>
       </c>
@@ -13464,7 +13473,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="260" spans="1:10">
+    <row r="260" spans="1:10" hidden="1">
       <c r="A260" s="4">
         <v>259</v>
       </c>
@@ -13493,7 +13502,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="261" spans="1:10">
+    <row r="261" spans="1:10" hidden="1">
       <c r="A261" s="4">
         <v>260</v>
       </c>
@@ -13522,7 +13531,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="262" spans="1:10">
+    <row r="262" spans="1:10" hidden="1">
       <c r="A262" s="4">
         <v>261</v>
       </c>
@@ -13554,7 +13563,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="263" spans="1:10">
+    <row r="263" spans="1:10" hidden="1">
       <c r="A263" s="4">
         <v>262</v>
       </c>
@@ -13650,7 +13659,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="266" spans="1:10">
+    <row r="266" spans="1:10" hidden="1">
       <c r="A266" s="4">
         <v>265</v>
       </c>
@@ -13682,7 +13691,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="267" spans="1:10">
+    <row r="267" spans="1:10" hidden="1">
       <c r="A267" s="4">
         <v>266</v>
       </c>
@@ -13714,7 +13723,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="268" spans="1:10">
+    <row r="268" spans="1:10" hidden="1">
       <c r="A268" s="4">
         <v>267</v>
       </c>
@@ -13746,7 +13755,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="269" spans="1:10">
+    <row r="269" spans="1:10" hidden="1">
       <c r="A269" s="4">
         <v>268</v>
       </c>
@@ -13778,7 +13787,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="270" spans="1:10">
+    <row r="270" spans="1:10" hidden="1">
       <c r="A270" s="4">
         <v>269</v>
       </c>
@@ -13810,7 +13819,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="271" spans="1:10">
+    <row r="271" spans="1:10" hidden="1">
       <c r="A271" s="4">
         <v>270</v>
       </c>
@@ -13842,7 +13851,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="272" spans="1:10">
+    <row r="272" spans="1:10" hidden="1">
       <c r="A272" s="4">
         <v>271</v>
       </c>
@@ -13874,7 +13883,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="273" spans="1:10">
+    <row r="273" spans="1:10" hidden="1">
       <c r="A273" s="4">
         <v>272</v>
       </c>
@@ -13906,7 +13915,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="274" spans="1:10">
+    <row r="274" spans="1:10" hidden="1">
       <c r="A274" s="4">
         <v>273</v>
       </c>
@@ -13935,10 +13944,10 @@
         <v>574</v>
       </c>
       <c r="J274" s="3" t="s">
-        <v>1304</v>
-      </c>
-    </row>
-    <row r="275" spans="1:10">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="275" spans="1:10" hidden="1">
       <c r="A275" s="4">
         <v>274</v>
       </c>
@@ -13970,7 +13979,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="276" spans="1:10">
+    <row r="276" spans="1:10" hidden="1">
       <c r="A276" s="4">
         <v>275</v>
       </c>
@@ -14002,7 +14011,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="277" spans="1:10">
+    <row r="277" spans="1:10" hidden="1">
       <c r="A277" s="4">
         <v>276</v>
       </c>
@@ -14034,7 +14043,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="278" spans="1:10">
+    <row r="278" spans="1:10" hidden="1">
       <c r="A278" s="4">
         <v>277</v>
       </c>
@@ -14066,7 +14075,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="279" spans="1:10">
+    <row r="279" spans="1:10" hidden="1">
       <c r="A279" s="4">
         <v>278</v>
       </c>
@@ -14098,7 +14107,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="280" spans="1:10">
+    <row r="280" spans="1:10" hidden="1">
       <c r="A280" s="4">
         <v>279</v>
       </c>
@@ -14130,7 +14139,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="281" spans="1:10">
+    <row r="281" spans="1:10" hidden="1">
       <c r="A281" s="4">
         <v>280</v>
       </c>
@@ -14162,7 +14171,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="282" spans="1:10">
+    <row r="282" spans="1:10" hidden="1">
       <c r="A282" s="4">
         <v>281</v>
       </c>
@@ -14194,7 +14203,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="283" spans="1:10">
+    <row r="283" spans="1:10" hidden="1">
       <c r="A283" s="4">
         <v>282</v>
       </c>
@@ -14226,7 +14235,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="284" spans="1:10">
+    <row r="284" spans="1:10" hidden="1">
       <c r="A284" s="4">
         <v>283</v>
       </c>
@@ -14258,7 +14267,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="285" spans="1:10">
+    <row r="285" spans="1:10" hidden="1">
       <c r="A285" s="4">
         <v>284</v>
       </c>
@@ -14290,7 +14299,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="286" spans="1:10">
+    <row r="286" spans="1:10" hidden="1">
       <c r="A286" s="4">
         <v>285</v>
       </c>
@@ -14322,7 +14331,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="287" spans="1:10">
+    <row r="287" spans="1:10" hidden="1">
       <c r="A287" s="4">
         <v>286</v>
       </c>
@@ -14354,7 +14363,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="288" spans="1:10">
+    <row r="288" spans="1:10" hidden="1">
       <c r="A288" s="4">
         <v>287</v>
       </c>
@@ -14386,7 +14395,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="289" spans="1:10">
+    <row r="289" spans="1:10" hidden="1">
       <c r="A289" s="4">
         <v>288</v>
       </c>
@@ -14418,7 +14427,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="290" spans="1:10">
+    <row r="290" spans="1:10" hidden="1">
       <c r="A290" s="4">
         <v>289</v>
       </c>
@@ -14450,7 +14459,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="291" spans="1:10">
+    <row r="291" spans="1:10" hidden="1">
       <c r="A291" s="4">
         <v>290</v>
       </c>
@@ -14482,7 +14491,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="292" spans="1:10">
+    <row r="292" spans="1:10" hidden="1">
       <c r="A292" s="4">
         <v>291</v>
       </c>
@@ -14514,7 +14523,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="293" spans="1:10">
+    <row r="293" spans="1:10" hidden="1">
       <c r="A293" s="4">
         <v>292</v>
       </c>
@@ -14546,7 +14555,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="294" spans="1:10">
+    <row r="294" spans="1:10" hidden="1">
       <c r="A294" s="4">
         <v>293</v>
       </c>
@@ -14578,7 +14587,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="295" spans="1:10">
+    <row r="295" spans="1:10" hidden="1">
       <c r="A295" s="4">
         <v>294</v>
       </c>
@@ -14610,7 +14619,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="296" spans="1:10">
+    <row r="296" spans="1:10" hidden="1">
       <c r="A296" s="4">
         <v>295</v>
       </c>
@@ -14642,7 +14651,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="297" spans="1:10">
+    <row r="297" spans="1:10" hidden="1">
       <c r="A297" s="4">
         <v>296</v>
       </c>
@@ -14674,7 +14683,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="298" spans="1:10">
+    <row r="298" spans="1:10" hidden="1">
       <c r="A298" s="4">
         <v>297</v>
       </c>
@@ -14706,7 +14715,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="299" spans="1:10">
+    <row r="299" spans="1:10" hidden="1">
       <c r="A299" s="4">
         <v>298</v>
       </c>
@@ -14738,7 +14747,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="300" spans="1:10">
+    <row r="300" spans="1:10" hidden="1">
       <c r="A300" s="4">
         <v>299</v>
       </c>
@@ -14770,7 +14779,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="301" spans="1:10">
+    <row r="301" spans="1:10" hidden="1">
       <c r="A301" s="4">
         <v>300</v>
       </c>
@@ -14802,7 +14811,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="302" spans="1:10">
+    <row r="302" spans="1:10" hidden="1">
       <c r="A302" s="4">
         <v>301</v>
       </c>
@@ -14834,7 +14843,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="303" spans="1:10">
+    <row r="303" spans="1:10" hidden="1">
       <c r="A303" s="4">
         <v>302</v>
       </c>
@@ -14866,7 +14875,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="304" spans="1:10">
+    <row r="304" spans="1:10" hidden="1">
       <c r="A304" s="4">
         <v>303</v>
       </c>
@@ -14898,7 +14907,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="305" spans="1:10">
+    <row r="305" spans="1:10" hidden="1">
       <c r="A305" s="4">
         <v>304</v>
       </c>
@@ -14930,7 +14939,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="306" spans="1:10">
+    <row r="306" spans="1:10" hidden="1">
       <c r="A306" s="4">
         <v>305</v>
       </c>
@@ -14962,7 +14971,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="307" spans="1:10">
+    <row r="307" spans="1:10" hidden="1">
       <c r="A307" s="4">
         <v>306</v>
       </c>
@@ -14994,7 +15003,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="308" spans="1:10">
+    <row r="308" spans="1:10" hidden="1">
       <c r="A308" s="4">
         <v>307</v>
       </c>
@@ -15026,7 +15035,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="309" spans="1:10">
+    <row r="309" spans="1:10" hidden="1">
       <c r="A309" s="4">
         <v>308</v>
       </c>
@@ -15058,7 +15067,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="310" spans="1:10">
+    <row r="310" spans="1:10" hidden="1">
       <c r="A310" s="4">
         <v>309</v>
       </c>
@@ -15090,7 +15099,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="311" spans="1:10">
+    <row r="311" spans="1:10" hidden="1">
       <c r="A311" s="4">
         <v>310</v>
       </c>
@@ -15122,7 +15131,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="312" spans="1:10">
+    <row r="312" spans="1:10" hidden="1">
       <c r="A312" s="4">
         <v>311</v>
       </c>
@@ -15154,7 +15163,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="313" spans="1:10">
+    <row r="313" spans="1:10" hidden="1">
       <c r="A313" s="4">
         <v>312</v>
       </c>
@@ -15186,7 +15195,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="314" spans="1:10">
+    <row r="314" spans="1:10" hidden="1">
       <c r="A314" s="4">
         <v>313</v>
       </c>
@@ -15218,7 +15227,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="315" spans="1:10">
+    <row r="315" spans="1:10" hidden="1">
       <c r="A315" s="4">
         <v>314</v>
       </c>
@@ -15250,7 +15259,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="316" spans="1:10">
+    <row r="316" spans="1:10" hidden="1">
       <c r="A316" s="4">
         <v>315</v>
       </c>
@@ -15282,7 +15291,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="317" spans="1:10">
+    <row r="317" spans="1:10" hidden="1">
       <c r="A317" s="4">
         <v>316</v>
       </c>
@@ -15314,7 +15323,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="318" spans="1:10">
+    <row r="318" spans="1:10" hidden="1">
       <c r="A318" s="4">
         <v>317</v>
       </c>
@@ -15346,7 +15355,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="319" spans="1:10">
+    <row r="319" spans="1:10" hidden="1">
       <c r="A319" s="4">
         <v>318</v>
       </c>
@@ -15378,7 +15387,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="320" spans="1:10">
+    <row r="320" spans="1:10" hidden="1">
       <c r="A320" s="4">
         <v>319</v>
       </c>
@@ -15410,7 +15419,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="321" spans="1:10">
+    <row r="321" spans="1:10" hidden="1">
       <c r="A321" s="4">
         <v>320</v>
       </c>
@@ -15442,7 +15451,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="322" spans="1:10">
+    <row r="322" spans="1:10" hidden="1">
       <c r="A322" s="4">
         <v>321</v>
       </c>
@@ -15474,7 +15483,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="323" spans="1:10">
+    <row r="323" spans="1:10" hidden="1">
       <c r="A323" s="4">
         <v>322</v>
       </c>
@@ -15506,7 +15515,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="324" spans="1:10">
+    <row r="324" spans="1:10" hidden="1">
       <c r="A324" s="4">
         <v>323</v>
       </c>
@@ -15538,7 +15547,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="325" spans="1:10">
+    <row r="325" spans="1:10" hidden="1">
       <c r="A325" s="4">
         <v>324</v>
       </c>
@@ -15570,7 +15579,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="326" spans="1:10">
+    <row r="326" spans="1:10" hidden="1">
       <c r="A326" s="4">
         <v>325</v>
       </c>
@@ -15602,7 +15611,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="327" spans="1:10">
+    <row r="327" spans="1:10" hidden="1">
       <c r="A327" s="4">
         <v>326</v>
       </c>
@@ -15634,7 +15643,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="328" spans="1:10">
+    <row r="328" spans="1:10" hidden="1">
       <c r="A328" s="4">
         <v>327</v>
       </c>
@@ -15666,7 +15675,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="329" spans="1:10">
+    <row r="329" spans="1:10" hidden="1">
       <c r="A329" s="4">
         <v>328</v>
       </c>
@@ -15698,7 +15707,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="330" spans="1:10">
+    <row r="330" spans="1:10" hidden="1">
       <c r="A330" s="4">
         <v>329</v>
       </c>
@@ -15730,7 +15739,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="331" spans="1:10">
+    <row r="331" spans="1:10" hidden="1">
       <c r="A331" s="4">
         <v>330</v>
       </c>
@@ -15762,7 +15771,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="332" spans="1:10">
+    <row r="332" spans="1:10" hidden="1">
       <c r="A332" s="4">
         <v>331</v>
       </c>
@@ -15794,7 +15803,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="333" spans="1:10">
+    <row r="333" spans="1:10" hidden="1">
       <c r="A333" s="4">
         <v>332</v>
       </c>
@@ -15826,7 +15835,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="334" spans="1:10">
+    <row r="334" spans="1:10" hidden="1">
       <c r="A334" s="4">
         <v>333</v>
       </c>
@@ -15858,7 +15867,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="335" spans="1:10">
+    <row r="335" spans="1:10" hidden="1">
       <c r="A335" s="4">
         <v>334</v>
       </c>
@@ -15890,7 +15899,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="336" spans="1:10">
+    <row r="336" spans="1:10" hidden="1">
       <c r="A336" s="4">
         <v>335</v>
       </c>
@@ -15922,7 +15931,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="337" spans="1:10">
+    <row r="337" spans="1:10" hidden="1">
       <c r="A337" s="4">
         <v>336</v>
       </c>
@@ -15954,7 +15963,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="338" spans="1:10">
+    <row r="338" spans="1:10" hidden="1">
       <c r="A338" s="4">
         <v>337</v>
       </c>
@@ -15986,7 +15995,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="339" spans="1:10">
+    <row r="339" spans="1:10" hidden="1">
       <c r="A339" s="4">
         <v>338</v>
       </c>
@@ -16018,7 +16027,7 @@
         <v>1299</v>
       </c>
     </row>
-    <row r="340" spans="1:10">
+    <row r="340" spans="1:10" hidden="1">
       <c r="A340" s="4">
         <v>339</v>
       </c>
@@ -16050,7 +16059,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="341" spans="1:10">
+    <row r="341" spans="1:10" hidden="1">
       <c r="A341" s="4">
         <v>340</v>
       </c>
@@ -16082,7 +16091,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="342" spans="1:10">
+    <row r="342" spans="1:10" hidden="1">
       <c r="A342" s="4">
         <v>341</v>
       </c>
@@ -16114,7 +16123,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="343" spans="1:10">
+    <row r="343" spans="1:10" hidden="1">
       <c r="A343" s="4">
         <v>342</v>
       </c>
@@ -16146,7 +16155,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="344" spans="1:10">
+    <row r="344" spans="1:10" hidden="1">
       <c r="A344" s="4">
         <v>343</v>
       </c>
@@ -16178,7 +16187,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="345" spans="1:10">
+    <row r="345" spans="1:10" hidden="1">
       <c r="A345" s="4">
         <v>344</v>
       </c>
@@ -16210,7 +16219,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="346" spans="1:10">
+    <row r="346" spans="1:10" hidden="1">
       <c r="A346" s="4">
         <v>345</v>
       </c>
@@ -16242,7 +16251,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="347" spans="1:10">
+    <row r="347" spans="1:10" hidden="1">
       <c r="A347" s="4">
         <v>346</v>
       </c>
@@ -16274,7 +16283,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="348" spans="1:10">
+    <row r="348" spans="1:10" hidden="1">
       <c r="A348" s="4">
         <v>347</v>
       </c>
@@ -16306,7 +16315,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="349" spans="1:10">
+    <row r="349" spans="1:10" hidden="1">
       <c r="A349" s="4">
         <v>348</v>
       </c>
@@ -16338,7 +16347,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="350" spans="1:10">
+    <row r="350" spans="1:10" hidden="1">
       <c r="A350" s="4">
         <v>349</v>
       </c>
@@ -16370,7 +16379,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="351" spans="1:10">
+    <row r="351" spans="1:10" hidden="1">
       <c r="A351" s="4">
         <v>350</v>
       </c>
@@ -16402,7 +16411,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="352" spans="1:10">
+    <row r="352" spans="1:10" hidden="1">
       <c r="A352" s="4">
         <v>351</v>
       </c>
@@ -16434,7 +16443,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="353" spans="1:10">
+    <row r="353" spans="1:10" hidden="1">
       <c r="A353" s="4">
         <v>352</v>
       </c>
@@ -16466,7 +16475,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="354" spans="1:10">
+    <row r="354" spans="1:10" hidden="1">
       <c r="A354" s="4">
         <v>353</v>
       </c>
@@ -16498,7 +16507,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="355" spans="1:10">
+    <row r="355" spans="1:10" hidden="1">
       <c r="A355" s="4">
         <v>354</v>
       </c>
@@ -16530,7 +16539,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="356" spans="1:10">
+    <row r="356" spans="1:10" hidden="1">
       <c r="A356" s="4">
         <v>355</v>
       </c>
@@ -16562,7 +16571,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="357" spans="1:10">
+    <row r="357" spans="1:10" hidden="1">
       <c r="A357" s="4">
         <v>356</v>
       </c>
@@ -16594,7 +16603,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="358" spans="1:10">
+    <row r="358" spans="1:10" hidden="1">
       <c r="A358" s="4">
         <v>357</v>
       </c>
@@ -16626,7 +16635,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="359" spans="1:10">
+    <row r="359" spans="1:10" hidden="1">
       <c r="A359" s="4">
         <v>358</v>
       </c>
@@ -16658,7 +16667,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="360" spans="1:10">
+    <row r="360" spans="1:10" hidden="1">
       <c r="A360" s="4">
         <v>359</v>
       </c>
@@ -16690,7 +16699,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="361" spans="1:10">
+    <row r="361" spans="1:10" hidden="1">
       <c r="A361" s="4">
         <v>360</v>
       </c>
@@ -16722,7 +16731,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="362" spans="1:10">
+    <row r="362" spans="1:10" hidden="1">
       <c r="A362" s="4">
         <v>361</v>
       </c>
@@ -16754,7 +16763,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="363" spans="1:10">
+    <row r="363" spans="1:10" hidden="1">
       <c r="A363" s="4">
         <v>362</v>
       </c>
@@ -16786,7 +16795,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="364" spans="1:10">
+    <row r="364" spans="1:10" hidden="1">
       <c r="A364" s="4">
         <v>363</v>
       </c>
@@ -16818,7 +16827,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="365" spans="1:10">
+    <row r="365" spans="1:10" hidden="1">
       <c r="A365" s="4">
         <v>364</v>
       </c>
@@ -16850,7 +16859,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="366" spans="1:10">
+    <row r="366" spans="1:10" hidden="1">
       <c r="A366" s="4">
         <v>365</v>
       </c>
@@ -16882,7 +16891,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="367" spans="1:10">
+    <row r="367" spans="1:10" hidden="1">
       <c r="A367" s="4">
         <v>366</v>
       </c>
@@ -16914,7 +16923,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="368" spans="1:10">
+    <row r="368" spans="1:10" hidden="1">
       <c r="A368" s="4">
         <v>367</v>
       </c>
@@ -16946,7 +16955,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="369" spans="1:10">
+    <row r="369" spans="1:10" hidden="1">
       <c r="A369" s="4">
         <v>368</v>
       </c>
@@ -16978,7 +16987,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="370" spans="1:10">
+    <row r="370" spans="1:10" hidden="1">
       <c r="A370" s="4">
         <v>369</v>
       </c>
@@ -17010,7 +17019,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="371" spans="1:10">
+    <row r="371" spans="1:10" hidden="1">
       <c r="A371" s="4">
         <v>370</v>
       </c>
@@ -17042,7 +17051,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="372" spans="1:10">
+    <row r="372" spans="1:10" hidden="1">
       <c r="A372" s="4">
         <v>371</v>
       </c>
@@ -17074,7 +17083,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="373" spans="1:10">
+    <row r="373" spans="1:10" hidden="1">
       <c r="A373" s="4">
         <v>372</v>
       </c>
@@ -17106,7 +17115,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="374" spans="1:10">
+    <row r="374" spans="1:10" hidden="1">
       <c r="A374" s="4">
         <v>373</v>
       </c>
@@ -17138,7 +17147,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="375" spans="1:10">
+    <row r="375" spans="1:10" hidden="1">
       <c r="A375" s="4">
         <v>374</v>
       </c>
@@ -17170,7 +17179,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="376" spans="1:10">
+    <row r="376" spans="1:10" hidden="1">
       <c r="A376" s="4">
         <v>375</v>
       </c>
@@ -17202,7 +17211,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="377" spans="1:10">
+    <row r="377" spans="1:10" hidden="1">
       <c r="A377" s="4">
         <v>376</v>
       </c>
@@ -17234,7 +17243,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="378" spans="1:10">
+    <row r="378" spans="1:10" hidden="1">
       <c r="A378" s="4">
         <v>377</v>
       </c>
@@ -17266,7 +17275,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="379" spans="1:10">
+    <row r="379" spans="1:10" hidden="1">
       <c r="A379" s="4">
         <v>378</v>
       </c>
@@ -17298,7 +17307,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="380" spans="1:10">
+    <row r="380" spans="1:10" hidden="1">
       <c r="A380" s="4">
         <v>379</v>
       </c>
@@ -17330,7 +17339,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="381" spans="1:10">
+    <row r="381" spans="1:10" hidden="1">
       <c r="A381" s="4">
         <v>380</v>
       </c>
@@ -17362,7 +17371,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="382" spans="1:10">
+    <row r="382" spans="1:10" hidden="1">
       <c r="A382" s="4">
         <v>381</v>
       </c>
@@ -17394,7 +17403,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="383" spans="1:10">
+    <row r="383" spans="1:10" hidden="1">
       <c r="A383" s="4">
         <v>382</v>
       </c>
@@ -17426,7 +17435,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="384" spans="1:10">
+    <row r="384" spans="1:10" hidden="1">
       <c r="A384" s="4">
         <v>383</v>
       </c>
@@ -17458,7 +17467,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="385" spans="1:10">
+    <row r="385" spans="1:10" hidden="1">
       <c r="A385" s="4">
         <v>384</v>
       </c>
@@ -17504,10 +17513,10 @@
         <v>717</v>
       </c>
       <c r="E386" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F386" s="1" t="s">
-        <v>23</v>
+        <v>1220</v>
       </c>
       <c r="G386" s="1" t="s">
         <v>14</v>
@@ -17519,10 +17528,10 @@
         <v>645</v>
       </c>
       <c r="J386" s="3" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="387" spans="1:10">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="387" spans="1:10" hidden="1">
       <c r="A387" s="4">
         <v>386</v>
       </c>
@@ -17554,7 +17563,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="388" spans="1:10">
+    <row r="388" spans="1:10" hidden="1">
       <c r="A388" s="4">
         <v>387</v>
       </c>
@@ -17571,7 +17580,7 @@
         <v>76</v>
       </c>
       <c r="F388" s="1" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="G388" s="1" t="s">
         <v>14</v>
@@ -17586,7 +17595,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="389" spans="1:10">
+    <row r="389" spans="1:10" hidden="1">
       <c r="A389" s="4">
         <v>388</v>
       </c>
@@ -17618,7 +17627,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="390" spans="1:10">
+    <row r="390" spans="1:10" hidden="1">
       <c r="A390" s="4">
         <v>389</v>
       </c>
@@ -17650,7 +17659,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="391" spans="1:10">
+    <row r="391" spans="1:10" hidden="1">
       <c r="A391" s="4">
         <v>390</v>
       </c>
@@ -17682,7 +17691,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="392" spans="1:10">
+    <row r="392" spans="1:10" hidden="1">
       <c r="A392" s="4">
         <v>391</v>
       </c>
@@ -17714,7 +17723,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="393" spans="1:10">
+    <row r="393" spans="1:10" hidden="1">
       <c r="A393" s="4">
         <v>392</v>
       </c>
@@ -17746,7 +17755,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="394" spans="1:10">
+    <row r="394" spans="1:10" hidden="1">
       <c r="A394" s="4">
         <v>393</v>
       </c>
@@ -17778,7 +17787,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="395" spans="1:10">
+    <row r="395" spans="1:10" hidden="1">
       <c r="A395" s="4">
         <v>394</v>
       </c>
@@ -17810,7 +17819,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="396" spans="1:10">
+    <row r="396" spans="1:10" hidden="1">
       <c r="A396" s="4">
         <v>395</v>
       </c>
@@ -17842,7 +17851,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="397" spans="1:10">
+    <row r="397" spans="1:10" hidden="1">
       <c r="A397" s="4">
         <v>396</v>
       </c>
@@ -17874,7 +17883,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="398" spans="1:10">
+    <row r="398" spans="1:10" hidden="1">
       <c r="A398" s="4">
         <v>397</v>
       </c>
@@ -17906,7 +17915,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="399" spans="1:10">
+    <row r="399" spans="1:10" hidden="1">
       <c r="A399" s="4">
         <v>398</v>
       </c>
@@ -17938,7 +17947,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="400" spans="1:10">
+    <row r="400" spans="1:10" hidden="1">
       <c r="A400" s="4">
         <v>399</v>
       </c>
@@ -17970,7 +17979,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="401" spans="1:10">
+    <row r="401" spans="1:10" hidden="1">
       <c r="A401" s="4">
         <v>400</v>
       </c>
@@ -18002,7 +18011,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="402" spans="1:10">
+    <row r="402" spans="1:10" hidden="1">
       <c r="A402" s="4">
         <v>401</v>
       </c>
@@ -18034,7 +18043,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="403" spans="1:10">
+    <row r="403" spans="1:10" hidden="1">
       <c r="A403" s="4">
         <v>402</v>
       </c>
@@ -18066,7 +18075,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="404" spans="1:10">
+    <row r="404" spans="1:10" hidden="1">
       <c r="A404" s="4">
         <v>403</v>
       </c>
@@ -18098,7 +18107,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="405" spans="1:10">
+    <row r="405" spans="1:10" hidden="1">
       <c r="A405" s="4">
         <v>404</v>
       </c>
@@ -18130,7 +18139,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="406" spans="1:10">
+    <row r="406" spans="1:10" hidden="1">
       <c r="A406" s="4">
         <v>405</v>
       </c>
@@ -18162,7 +18171,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="407" spans="1:10">
+    <row r="407" spans="1:10" hidden="1">
       <c r="A407" s="4">
         <v>406</v>
       </c>
@@ -18194,7 +18203,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="408" spans="1:10">
+    <row r="408" spans="1:10" hidden="1">
       <c r="A408" s="4">
         <v>407</v>
       </c>
@@ -18226,7 +18235,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="409" spans="1:10">
+    <row r="409" spans="1:10" hidden="1">
       <c r="A409" s="4">
         <v>408</v>
       </c>
@@ -18258,7 +18267,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="410" spans="1:10">
+    <row r="410" spans="1:10" hidden="1">
       <c r="A410" s="4">
         <v>409</v>
       </c>
@@ -18290,7 +18299,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="411" spans="1:10">
+    <row r="411" spans="1:10" hidden="1">
       <c r="A411" s="4">
         <v>410</v>
       </c>
@@ -18322,7 +18331,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="412" spans="1:10">
+    <row r="412" spans="1:10" hidden="1">
       <c r="A412" s="4">
         <v>411</v>
       </c>
@@ -18354,7 +18363,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="413" spans="1:10">
+    <row r="413" spans="1:10" hidden="1">
       <c r="A413" s="4">
         <v>412</v>
       </c>
@@ -18386,7 +18395,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="414" spans="1:10">
+    <row r="414" spans="1:10" hidden="1">
       <c r="A414" s="4">
         <v>413</v>
       </c>
@@ -18418,7 +18427,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="415" spans="1:10">
+    <row r="415" spans="1:10" hidden="1">
       <c r="A415" s="4">
         <v>414</v>
       </c>
@@ -18450,7 +18459,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="416" spans="1:10">
+    <row r="416" spans="1:10" hidden="1">
       <c r="A416" s="4">
         <v>415</v>
       </c>
@@ -18482,7 +18491,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="417" spans="1:10">
+    <row r="417" spans="1:10" hidden="1">
       <c r="A417" s="4">
         <v>416</v>
       </c>
@@ -18514,7 +18523,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="418" spans="1:10">
+    <row r="418" spans="1:10" hidden="1">
       <c r="A418" s="4">
         <v>417</v>
       </c>
@@ -18546,7 +18555,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="419" spans="1:10">
+    <row r="419" spans="1:10" hidden="1">
       <c r="A419" s="4">
         <v>418</v>
       </c>
@@ -18578,7 +18587,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="420" spans="1:10">
+    <row r="420" spans="1:10" hidden="1">
       <c r="A420" s="4">
         <v>419</v>
       </c>
@@ -18610,7 +18619,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="421" spans="1:10">
+    <row r="421" spans="1:10" hidden="1">
       <c r="A421" s="4">
         <v>420</v>
       </c>
@@ -18642,7 +18651,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="422" spans="1:10">
+    <row r="422" spans="1:10" hidden="1">
       <c r="A422" s="4">
         <v>421</v>
       </c>
@@ -18674,7 +18683,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="423" spans="1:10">
+    <row r="423" spans="1:10" hidden="1">
       <c r="A423" s="4">
         <v>422</v>
       </c>
@@ -18706,7 +18715,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="424" spans="1:10">
+    <row r="424" spans="1:10" hidden="1">
       <c r="A424" s="4">
         <v>423</v>
       </c>
@@ -18738,7 +18747,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="425" spans="1:10">
+    <row r="425" spans="1:10" hidden="1">
       <c r="A425" s="4">
         <v>424</v>
       </c>
@@ -18770,7 +18779,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="426" spans="1:10">
+    <row r="426" spans="1:10" hidden="1">
       <c r="A426" s="4">
         <v>425</v>
       </c>
@@ -18802,7 +18811,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="427" spans="1:10">
+    <row r="427" spans="1:10" hidden="1">
       <c r="A427" s="4">
         <v>426</v>
       </c>
@@ -18834,7 +18843,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="428" spans="1:10">
+    <row r="428" spans="1:10" hidden="1">
       <c r="A428" s="4">
         <v>427</v>
       </c>
@@ -18866,7 +18875,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="429" spans="1:10">
+    <row r="429" spans="1:10" hidden="1">
       <c r="A429" s="4">
         <v>428</v>
       </c>
@@ -18898,7 +18907,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="430" spans="1:10">
+    <row r="430" spans="1:10" hidden="1">
       <c r="A430" s="4">
         <v>429</v>
       </c>
@@ -18930,7 +18939,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="431" spans="1:10">
+    <row r="431" spans="1:10" hidden="1">
       <c r="A431" s="4">
         <v>430</v>
       </c>
@@ -18962,7 +18971,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="432" spans="1:10">
+    <row r="432" spans="1:10" hidden="1">
       <c r="A432" s="4">
         <v>431</v>
       </c>
@@ -18994,7 +19003,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="433" spans="1:10">
+    <row r="433" spans="1:10" hidden="1">
       <c r="A433" s="4">
         <v>432</v>
       </c>
@@ -19026,7 +19035,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="434" spans="1:10">
+    <row r="434" spans="1:10" hidden="1">
       <c r="A434" s="4">
         <v>433</v>
       </c>
@@ -19058,7 +19067,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="435" spans="1:10">
+    <row r="435" spans="1:10" hidden="1">
       <c r="A435" s="4">
         <v>434</v>
       </c>
@@ -19090,7 +19099,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="436" spans="1:10">
+    <row r="436" spans="1:10" hidden="1">
       <c r="A436" s="4">
         <v>435</v>
       </c>
@@ -19120,7 +19129,7 @@
       </c>
       <c r="J436" s="24"/>
     </row>
-    <row r="437" spans="1:10">
+    <row r="437" spans="1:10" hidden="1">
       <c r="A437" s="4">
         <v>436</v>
       </c>
@@ -19152,7 +19161,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="438" spans="1:10">
+    <row r="438" spans="1:10" hidden="1">
       <c r="A438" s="4">
         <v>437</v>
       </c>
@@ -19184,7 +19193,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="439" spans="1:10">
+    <row r="439" spans="1:10" hidden="1">
       <c r="A439" s="4">
         <v>438</v>
       </c>
@@ -19216,7 +19225,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="440" spans="1:10">
+    <row r="440" spans="1:10" hidden="1">
       <c r="A440" s="4">
         <v>439</v>
       </c>
@@ -19248,7 +19257,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="441" spans="1:10">
+    <row r="441" spans="1:10" hidden="1">
       <c r="A441" s="4">
         <v>440</v>
       </c>
@@ -19280,7 +19289,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="442" spans="1:10">
+    <row r="442" spans="1:10" hidden="1">
       <c r="A442" s="4">
         <v>441</v>
       </c>
@@ -19312,7 +19321,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="443" spans="1:10">
+    <row r="443" spans="1:10" hidden="1">
       <c r="A443" s="4">
         <v>442</v>
       </c>
@@ -19344,7 +19353,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="444" spans="1:10">
+    <row r="444" spans="1:10" hidden="1">
       <c r="A444" s="4">
         <v>443</v>
       </c>
@@ -19376,7 +19385,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="445" spans="1:10">
+    <row r="445" spans="1:10" hidden="1">
       <c r="A445" s="4">
         <v>444</v>
       </c>
@@ -19408,7 +19417,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="446" spans="1:10">
+    <row r="446" spans="1:10" hidden="1">
       <c r="A446" s="4">
         <v>445</v>
       </c>
@@ -19440,7 +19449,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="447" spans="1:10">
+    <row r="447" spans="1:10" hidden="1">
       <c r="A447" s="4">
         <v>446</v>
       </c>
@@ -19472,7 +19481,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="448" spans="1:10">
+    <row r="448" spans="1:10" hidden="1">
       <c r="A448" s="4">
         <v>447</v>
       </c>
@@ -19536,7 +19545,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="450" spans="1:10">
+    <row r="450" spans="1:10" hidden="1">
       <c r="A450" s="4">
         <v>449</v>
       </c>
@@ -19566,7 +19575,7 @@
       </c>
       <c r="J450" s="24"/>
     </row>
-    <row r="451" spans="1:10">
+    <row r="451" spans="1:10" hidden="1">
       <c r="A451" s="4">
         <v>450</v>
       </c>
@@ -19596,7 +19605,7 @@
       </c>
       <c r="J451" s="24"/>
     </row>
-    <row r="452" spans="1:10">
+    <row r="452" spans="1:10" hidden="1">
       <c r="A452" s="4">
         <v>451</v>
       </c>
@@ -19628,7 +19637,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="453" spans="1:10">
+    <row r="453" spans="1:10" hidden="1">
       <c r="A453" s="4">
         <v>452</v>
       </c>
@@ -19748,7 +19757,7 @@
       </c>
       <c r="J456" s="24"/>
     </row>
-    <row r="457" spans="1:10">
+    <row r="457" spans="1:10" hidden="1">
       <c r="A457" s="4">
         <v>456</v>
       </c>
@@ -19778,7 +19787,7 @@
       </c>
       <c r="J457" s="24"/>
     </row>
-    <row r="458" spans="1:10">
+    <row r="458" spans="1:10" hidden="1">
       <c r="A458" s="4">
         <v>457</v>
       </c>
@@ -19927,7 +19936,7 @@
         <v>574</v>
       </c>
       <c r="J462" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="463" spans="1:10">
@@ -20724,10 +20733,10 @@
         <v>1247</v>
       </c>
       <c r="E489" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F489" s="1" t="s">
-        <v>23</v>
+        <v>1037</v>
       </c>
       <c r="G489" s="1" t="s">
         <v>30</v>
@@ -20739,7 +20748,7 @@
         <v>574</v>
       </c>
       <c r="J489" s="3" t="s">
-        <v>1303</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="490" spans="1:10">
@@ -20903,7 +20912,7 @@
         <v>11</v>
       </c>
       <c r="D495" s="2" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="E495" s="1" t="s">
         <v>19</v>
@@ -20921,10 +20930,10 @@
         <v>574</v>
       </c>
       <c r="J495" s="3" t="s">
-        <v>1319</v>
-      </c>
-    </row>
-    <row r="496" spans="1:10">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="496" spans="1:10" hidden="1">
       <c r="A496" s="4">
         <v>495</v>
       </c>
@@ -20965,7 +20974,7 @@
         <v>11</v>
       </c>
       <c r="D497" s="2" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="E497" s="1" t="s">
         <v>19</v>
@@ -21014,7 +21023,7 @@
       </c>
       <c r="J498" s="24"/>
     </row>
-    <row r="499" spans="1:10">
+    <row r="499" spans="1:10" hidden="1">
       <c r="A499" s="4">
         <v>498</v>
       </c>
@@ -21044,7 +21053,7 @@
       </c>
       <c r="J499" s="24"/>
     </row>
-    <row r="500" spans="1:10">
+    <row r="500" spans="1:10" hidden="1">
       <c r="A500" s="4">
         <v>499</v>
       </c>

--- a/data_printer.xlsx
+++ b/data_printer.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erick\Desktop\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BFEBABB-061E-4675-A873-3A74B23706F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC1F28D6-A10F-4E85-BC78-81B0CEDE9CCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A8AA41B5-7AA1-4FF7-A9B8-54B8A4E1AF28}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5317" uniqueCount="1395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5317" uniqueCount="1443">
   <si>
     <t>INDICE</t>
   </si>
@@ -4233,6 +4233,150 @@
   </si>
   <si>
     <t>PROPIA</t>
+  </si>
+  <si>
+    <t>E. AFRANIO</t>
+  </si>
+  <si>
+    <t>E. CAMARON</t>
+  </si>
+  <si>
+    <t>INFORMATICA</t>
+  </si>
+  <si>
+    <t>UPA - CONSULTORIO 02</t>
+  </si>
+  <si>
+    <t>X67Y015684</t>
+  </si>
+  <si>
+    <t>X67Y015687</t>
+  </si>
+  <si>
+    <t>X67Y015694</t>
+  </si>
+  <si>
+    <t>X67Y015695</t>
+  </si>
+  <si>
+    <t>X67Y015696</t>
+  </si>
+  <si>
+    <t>X67Y015697</t>
+  </si>
+  <si>
+    <t>UPA - CONSULTORIO 01</t>
+  </si>
+  <si>
+    <t>UPA - CONSULTORIO 04</t>
+  </si>
+  <si>
+    <t>X67Y015836</t>
+  </si>
+  <si>
+    <t>UPA - CONSULTORIO 05</t>
+  </si>
+  <si>
+    <t>X67Y015845</t>
+  </si>
+  <si>
+    <t>UPA - CONSULTORIO 06</t>
+  </si>
+  <si>
+    <t>UPA - CONSULTORIO 08</t>
+  </si>
+  <si>
+    <t>X67Y015728</t>
+  </si>
+  <si>
+    <t>X67Y015834</t>
+  </si>
+  <si>
+    <t>UPA - SERV. SOCIAL</t>
+  </si>
+  <si>
+    <t>X67Y015822</t>
+  </si>
+  <si>
+    <t>UPA - ODONTOLOGIA</t>
+  </si>
+  <si>
+    <t>PAM - CONSULTORIO 03</t>
+  </si>
+  <si>
+    <t>PAM - CONSULTORIO 04</t>
+  </si>
+  <si>
+    <t>PAM - CONSULTORIO 05</t>
+  </si>
+  <si>
+    <t>PAM - CONSULTORIO 06</t>
+  </si>
+  <si>
+    <t>PAM - CONSULTORIO 07</t>
+  </si>
+  <si>
+    <t>PAM - CONSULTORIO 10</t>
+  </si>
+  <si>
+    <t>PAM - CONSULTORIO 13</t>
+  </si>
+  <si>
+    <t>PAM - CONSULTORIO 14</t>
+  </si>
+  <si>
+    <t>PAM - CONSULTORIO 15</t>
+  </si>
+  <si>
+    <t>PAM - CONSULTORIO 16</t>
+  </si>
+  <si>
+    <t>X67Y015838</t>
+  </si>
+  <si>
+    <t>X67Y015780</t>
+  </si>
+  <si>
+    <t>X67Y015681</t>
+  </si>
+  <si>
+    <t>X67Y015748</t>
+  </si>
+  <si>
+    <t>X67Y015680</t>
+  </si>
+  <si>
+    <t>X67Y015707</t>
+  </si>
+  <si>
+    <t>X67Y015</t>
+  </si>
+  <si>
+    <t>PAM - CONSULTORIO 18</t>
+  </si>
+  <si>
+    <t>PAM_ARA</t>
+  </si>
+  <si>
+    <t>X67Y014632</t>
+  </si>
+  <si>
+    <t>X67Y014655</t>
+  </si>
+  <si>
+    <t>XC75053952</t>
+  </si>
+  <si>
+    <t>XC75053933</t>
+  </si>
+  <si>
+    <t>XC75053941</t>
+  </si>
+  <si>
+    <t>XC750539</t>
+  </si>
+  <si>
+    <t>CANIBALIZADA</t>
   </si>
 </sst>
 </file>
@@ -4444,7 +4588,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4599,20 +4743,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -4620,7 +4751,7 @@
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="71">
+  <dxfs count="68">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -4824,11 +4955,28 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color theme="1"/>
       </font>
       <fill>
         <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4859,53 +5007,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5057,25 +5158,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="none">
           <bgColor auto="1"/>
@@ -5225,6 +5307,25 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -5437,23 +5538,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}" name="Controle_Inventario_Impressoras" displayName="Controle_Inventario_Impressoras" ref="A1:K580" tableType="queryTable" totalsRowShown="0" headerRowDxfId="70" dataDxfId="69">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}" name="Controle_Inventario_Impressoras" displayName="Controle_Inventario_Impressoras" ref="A1:K580" tableType="queryTable" totalsRowShown="0" headerRowDxfId="67" dataDxfId="66">
   <autoFilter ref="A1:K580" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K37">
     <sortCondition ref="A23"/>
   </sortState>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F8E3D681-C494-47F2-8429-052381C12AF1}" uniqueName="1" name="INDICE" queryTableFieldId="1" dataDxfId="68"/>
-    <tableColumn id="2" xr3:uid="{EE2E8FA5-A99D-4573-9868-408DB8FD4417}" uniqueName="2" name="MODELO" queryTableFieldId="2" dataDxfId="67"/>
-    <tableColumn id="11" xr3:uid="{CB5196C0-CCA1-4329-825F-D71E0948A542}" uniqueName="11" name="TIPO" queryTableFieldId="16390" dataDxfId="66"/>
-    <tableColumn id="3" xr3:uid="{27BC8F35-CC2C-44A1-BAF7-B0390B09477F}" uniqueName="3" name="NUMERO DE SERIE" queryTableFieldId="3" dataDxfId="65"/>
-    <tableColumn id="4" xr3:uid="{552F7A6E-6277-4DC1-9CDA-EA7FDCCE8E36}" uniqueName="4" name="LOCALIZAÇÃO" queryTableFieldId="4" dataDxfId="64"/>
-    <tableColumn id="5" xr3:uid="{4C8345F1-6E01-4566-9030-039665486C03}" uniqueName="5" name="SETOR" queryTableFieldId="5" dataDxfId="63"/>
-    <tableColumn id="9" xr3:uid="{10436F87-F6F1-46C4-A81A-8D144AC72FDF}" uniqueName="9" name="EMPRESA" queryTableFieldId="16389" dataDxfId="62"/>
-    <tableColumn id="13" xr3:uid="{40F07CF2-DF5F-4979-A5BB-71FA79C89740}" uniqueName="13" name="GRUPO" queryTableFieldId="16393" dataDxfId="45"/>
-    <tableColumn id="6" xr3:uid="{B7941BA2-3E1C-476B-A3C7-BA155A35A2D0}" uniqueName="6" name="ATUALIZADO" queryTableFieldId="6" dataDxfId="61"/>
-    <tableColumn id="7" xr3:uid="{4338F703-CE4B-4443-8A10-74F64ED8CD42}" uniqueName="7" name="PRINTWAY" queryTableFieldId="16391" dataDxfId="60"/>
-    <tableColumn id="8" xr3:uid="{02B7C1FB-8EA9-4F22-BCCF-3D1809FFEDCC}" uniqueName="8" name="OBSERVAÇÃO" queryTableFieldId="8" dataDxfId="59"/>
+    <tableColumn id="1" xr3:uid="{F8E3D681-C494-47F2-8429-052381C12AF1}" uniqueName="1" name="INDICE" queryTableFieldId="1" dataDxfId="65"/>
+    <tableColumn id="2" xr3:uid="{EE2E8FA5-A99D-4573-9868-408DB8FD4417}" uniqueName="2" name="MODELO" queryTableFieldId="2" dataDxfId="64"/>
+    <tableColumn id="11" xr3:uid="{CB5196C0-CCA1-4329-825F-D71E0948A542}" uniqueName="11" name="TIPO" queryTableFieldId="16390" dataDxfId="63"/>
+    <tableColumn id="3" xr3:uid="{27BC8F35-CC2C-44A1-BAF7-B0390B09477F}" uniqueName="3" name="NUMERO DE SERIE" queryTableFieldId="3" dataDxfId="62"/>
+    <tableColumn id="4" xr3:uid="{552F7A6E-6277-4DC1-9CDA-EA7FDCCE8E36}" uniqueName="4" name="LOCALIZAÇÃO" queryTableFieldId="4" dataDxfId="61"/>
+    <tableColumn id="5" xr3:uid="{4C8345F1-6E01-4566-9030-039665486C03}" uniqueName="5" name="SETOR" queryTableFieldId="5" dataDxfId="60"/>
+    <tableColumn id="9" xr3:uid="{10436F87-F6F1-46C4-A81A-8D144AC72FDF}" uniqueName="9" name="EMPRESA" queryTableFieldId="16389" dataDxfId="59"/>
+    <tableColumn id="13" xr3:uid="{40F07CF2-DF5F-4979-A5BB-71FA79C89740}" uniqueName="13" name="GRUPO" queryTableFieldId="16393" dataDxfId="58"/>
+    <tableColumn id="6" xr3:uid="{B7941BA2-3E1C-476B-A3C7-BA155A35A2D0}" uniqueName="6" name="ATUALIZADO" queryTableFieldId="6" dataDxfId="57"/>
+    <tableColumn id="7" xr3:uid="{4338F703-CE4B-4443-8A10-74F64ED8CD42}" uniqueName="7" name="PRINTWAY" queryTableFieldId="16391" dataDxfId="56"/>
+    <tableColumn id="8" xr3:uid="{02B7C1FB-8EA9-4F22-BCCF-3D1809FFEDCC}" uniqueName="8" name="OBSERVAÇÃO" queryTableFieldId="8" dataDxfId="55"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5468,26 +5569,26 @@
     <tableColumn id="3" xr3:uid="{95A3DCD3-FE19-4A74-9940-661D6BB94B25}" name="MODELO"/>
     <tableColumn id="4" xr3:uid="{521C03E5-7FA9-4789-8198-9E0781F3ABC7}" name="DESCRIÇÃO"/>
     <tableColumn id="5" xr3:uid="{579D81F0-AA4C-4609-BF35-AF838B2B149B}" name="COR"/>
-    <tableColumn id="6" xr3:uid="{19487D13-EF31-43DA-89CA-4AA1E1029C34}" name="QUANTIDADE" dataDxfId="58"/>
+    <tableColumn id="6" xr3:uid="{19487D13-EF31-43DA-89CA-4AA1E1029C34}" name="QUANTIDADE" dataDxfId="54"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FBC7B6D1-65BC-435E-B4FF-CC495249D6BD}" name="Tabela4" displayName="Tabela4" ref="A1:J51" insertRowShift="1" totalsRowShown="0" headerRowDxfId="57" dataDxfId="56">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FBC7B6D1-65BC-435E-B4FF-CC495249D6BD}" name="Tabela4" displayName="Tabela4" ref="A1:J51" insertRowShift="1" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52">
   <autoFilter ref="A1:J51" xr:uid="{FBC7B6D1-65BC-435E-B4FF-CC495249D6BD}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{A3ABFE90-9D3C-42DA-8CF0-D71D91CAB9BB}" name="INDICE" dataDxfId="55"/>
-    <tableColumn id="2" xr3:uid="{A733301C-FC8A-4542-8BA2-BBEA67F3D424}" name="MODELO" dataDxfId="54"/>
-    <tableColumn id="3" xr3:uid="{C6E07CD7-A3F4-4433-BB55-99FA29AE99FA}" name="TIPO" dataDxfId="53"/>
-    <tableColumn id="4" xr3:uid="{007A788B-09E3-480D-A6BC-6718BD4566C1}" name="SERIAL" dataDxfId="52"/>
-    <tableColumn id="5" xr3:uid="{ACA8BAA3-86EA-4046-9E8D-0C6E6216A0B1}" name="LOCALIDADE" dataDxfId="51"/>
-    <tableColumn id="6" xr3:uid="{D2E86C5C-2786-4CA5-9B36-02C6270BDE33}" name="SETOR" dataDxfId="50"/>
-    <tableColumn id="7" xr3:uid="{3F4C4914-DB98-431A-AD17-7760541C7F42}" name="EMPRESA" dataDxfId="49"/>
-    <tableColumn id="8" xr3:uid="{4F681722-ADFE-4A58-BC0F-8623348ECD33}" name="DATA" dataDxfId="48"/>
-    <tableColumn id="9" xr3:uid="{13FFF32F-FC49-429E-BD6E-76ADCE6F7534}" name="MONIT." dataDxfId="47"/>
-    <tableColumn id="10" xr3:uid="{F4255CFF-6FAD-434F-93D8-3A0C54269527}" name="DETALHES" dataDxfId="46"/>
+    <tableColumn id="1" xr3:uid="{A3ABFE90-9D3C-42DA-8CF0-D71D91CAB9BB}" name="INDICE" dataDxfId="51"/>
+    <tableColumn id="2" xr3:uid="{A733301C-FC8A-4542-8BA2-BBEA67F3D424}" name="MODELO" dataDxfId="50"/>
+    <tableColumn id="3" xr3:uid="{C6E07CD7-A3F4-4433-BB55-99FA29AE99FA}" name="TIPO" dataDxfId="49"/>
+    <tableColumn id="4" xr3:uid="{007A788B-09E3-480D-A6BC-6718BD4566C1}" name="SERIAL" dataDxfId="48"/>
+    <tableColumn id="5" xr3:uid="{ACA8BAA3-86EA-4046-9E8D-0C6E6216A0B1}" name="LOCALIDADE" dataDxfId="47"/>
+    <tableColumn id="6" xr3:uid="{D2E86C5C-2786-4CA5-9B36-02C6270BDE33}" name="SETOR" dataDxfId="46"/>
+    <tableColumn id="7" xr3:uid="{3F4C4914-DB98-431A-AD17-7760541C7F42}" name="EMPRESA" dataDxfId="45"/>
+    <tableColumn id="8" xr3:uid="{4F681722-ADFE-4A58-BC0F-8623348ECD33}" name="DATA" dataDxfId="44"/>
+    <tableColumn id="9" xr3:uid="{13FFF32F-FC49-429E-BD6E-76ADCE6F7534}" name="MONIT." dataDxfId="43"/>
+    <tableColumn id="10" xr3:uid="{F4255CFF-6FAD-434F-93D8-3A0C54269527}" name="DETALHES" dataDxfId="42"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6008,7 +6109,7 @@
       </c>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="58">
+      <c r="A7" s="4">
         <v>6</v>
       </c>
       <c r="B7" s="30" t="s">
@@ -6041,7 +6142,7 @@
       <c r="K7" s="55"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="58">
+      <c r="A8" s="4">
         <v>7</v>
       </c>
       <c r="B8" s="30" t="s">
@@ -6074,7 +6175,7 @@
       <c r="K8" s="55"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="58">
+      <c r="A9" s="4">
         <v>8</v>
       </c>
       <c r="B9" s="30" t="s">
@@ -6107,7 +6208,7 @@
       <c r="K9" s="55"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="58">
+      <c r="A10" s="4">
         <v>9</v>
       </c>
       <c r="B10" s="30" t="s">
@@ -6140,7 +6241,7 @@
       <c r="K10" s="55"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="58">
+      <c r="A11" s="4">
         <v>10</v>
       </c>
       <c r="B11" s="30" t="s">
@@ -6173,7 +6274,7 @@
       <c r="K11" s="55"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="58">
+      <c r="A12" s="4">
         <v>11</v>
       </c>
       <c r="B12" s="30" t="s">
@@ -6206,7 +6307,7 @@
       <c r="K12" s="55"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="58">
+      <c r="A13" s="4">
         <v>12</v>
       </c>
       <c r="B13" s="30" t="s">
@@ -6239,7 +6340,7 @@
       <c r="K13" s="55"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="58">
+      <c r="A14" s="4">
         <v>13</v>
       </c>
       <c r="B14" s="30" t="s">
@@ -6272,7 +6373,7 @@
       <c r="K14" s="55"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="58">
+      <c r="A15" s="4">
         <v>14</v>
       </c>
       <c r="B15" s="30" t="s">
@@ -6305,7 +6406,7 @@
       <c r="K15" s="55"/>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="58">
+      <c r="A16" s="4">
         <v>15</v>
       </c>
       <c r="B16" s="30" t="s">
@@ -6339,7 +6440,7 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="4">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>24</v>
@@ -6372,7 +6473,7 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="4">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>26</v>
@@ -6387,7 +6488,7 @@
         <v>21</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>30</v>
@@ -6405,7 +6506,7 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="4">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>32</v>
@@ -6436,7 +6537,7 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="4">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>32</v>
@@ -6467,7 +6568,7 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>955</v>
@@ -6502,7 +6603,7 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="4">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>955</v>
@@ -6537,7 +6638,7 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="4">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>26</v>
@@ -6570,7 +6671,7 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="4">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>10</v>
@@ -6605,7 +6706,7 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="4">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B25" s="10" t="s">
         <v>26</v>
@@ -6638,7 +6739,7 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="4">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>42</v>
@@ -6668,7 +6769,7 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="4">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>42</v>
@@ -6701,7 +6802,7 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="4">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>32</v>
@@ -6734,7 +6835,7 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="4">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>32</v>
@@ -6767,7 +6868,7 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="4">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>32</v>
@@ -6802,7 +6903,7 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="4">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>32</v>
@@ -6835,7 +6936,7 @@
     </row>
     <row r="32" spans="1:11" ht="15.75" customHeight="1">
       <c r="A32" s="4">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>32</v>
@@ -6868,7 +6969,7 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="4">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>32</v>
@@ -6880,17 +6981,15 @@
         <v>54</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>76</v>
+        <v>21</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>967</v>
+        <v>23</v>
       </c>
       <c r="G33" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H33" s="4" t="s">
-        <v>1345</v>
-      </c>
+      <c r="H33" s="4"/>
       <c r="I33" s="9">
         <v>45652</v>
       </c>
@@ -6903,7 +7002,7 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="4">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>32</v>
@@ -6936,7 +7035,7 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="4">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>58</v>
@@ -6969,7 +7068,7 @@
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="4">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>58</v>
@@ -6999,7 +7098,7 @@
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="4">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>58</v>
@@ -7029,7 +7128,7 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="4">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>58</v>
@@ -7062,7 +7161,7 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="4">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>66</v>
@@ -7095,7 +7194,7 @@
     </row>
     <row r="40" spans="1:11">
       <c r="A40" s="4">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>69</v>
@@ -7128,7 +7227,7 @@
     </row>
     <row r="41" spans="1:11">
       <c r="A41" s="4">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>24</v>
@@ -7161,7 +7260,7 @@
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="4">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>10</v>
@@ -7194,7 +7293,7 @@
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="4">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>10</v>
@@ -7227,7 +7326,7 @@
     </row>
     <row r="44" spans="1:11">
       <c r="A44" s="4">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>10</v>
@@ -7262,7 +7361,7 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="4">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>79</v>
@@ -7295,7 +7394,7 @@
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="4">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>82</v>
@@ -7328,7 +7427,7 @@
     </row>
     <row r="47" spans="1:11">
       <c r="A47" s="4">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>10</v>
@@ -7358,7 +7457,7 @@
     </row>
     <row r="48" spans="1:11">
       <c r="A48" s="4">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>42</v>
@@ -7391,7 +7490,7 @@
     </row>
     <row r="49" spans="1:11">
       <c r="A49" s="4">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>42</v>
@@ -7424,7 +7523,7 @@
     </row>
     <row r="50" spans="1:11">
       <c r="A50" s="4">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>42</v>
@@ -7457,7 +7556,7 @@
     </row>
     <row r="51" spans="1:11">
       <c r="A51" s="4">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>42</v>
@@ -7490,7 +7589,7 @@
     </row>
     <row r="52" spans="1:11">
       <c r="A52" s="4">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>42</v>
@@ -7523,7 +7622,7 @@
     </row>
     <row r="53" spans="1:11">
       <c r="A53" s="4">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>96</v>
@@ -7556,7 +7655,7 @@
     </row>
     <row r="54" spans="1:11">
       <c r="A54" s="4">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>99</v>
@@ -7589,7 +7688,7 @@
     </row>
     <row r="55" spans="1:11">
       <c r="A55" s="4">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>96</v>
@@ -7619,7 +7718,7 @@
     </row>
     <row r="56" spans="1:11">
       <c r="A56" s="4">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>103</v>
@@ -7652,7 +7751,7 @@
     </row>
     <row r="57" spans="1:11">
       <c r="A57" s="4">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>106</v>
@@ -7685,7 +7784,7 @@
     </row>
     <row r="58" spans="1:11">
       <c r="A58" s="4">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>106</v>
@@ -7718,7 +7817,7 @@
     </row>
     <row r="59" spans="1:11">
       <c r="A59" s="4">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>106</v>
@@ -7748,7 +7847,7 @@
     </row>
     <row r="60" spans="1:11">
       <c r="A60" s="4">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>106</v>
@@ -7778,7 +7877,7 @@
     </row>
     <row r="61" spans="1:11">
       <c r="A61" s="4">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>106</v>
@@ -7811,7 +7910,7 @@
     </row>
     <row r="62" spans="1:11">
       <c r="A62" s="4">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>956</v>
@@ -7846,7 +7945,7 @@
     </row>
     <row r="63" spans="1:11">
       <c r="A63" s="4">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>957</v>
@@ -7881,7 +7980,7 @@
     </row>
     <row r="64" spans="1:11">
       <c r="A64" s="4">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>958</v>
@@ -7916,7 +8015,7 @@
     </row>
     <row r="65" spans="1:11">
       <c r="A65" s="4">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>115</v>
@@ -7946,7 +8045,7 @@
     </row>
     <row r="66" spans="1:11">
       <c r="A66" s="4">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>117</v>
@@ -7976,7 +8075,7 @@
     </row>
     <row r="67" spans="1:11">
       <c r="A67" s="4">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>117</v>
@@ -8006,7 +8105,7 @@
     </row>
     <row r="68" spans="1:11">
       <c r="A68" s="4">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>117</v>
@@ -8036,7 +8135,7 @@
     </row>
     <row r="69" spans="1:11">
       <c r="A69" s="4">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>117</v>
@@ -8066,7 +8165,7 @@
     </row>
     <row r="70" spans="1:11">
       <c r="A70" s="4">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>117</v>
@@ -8096,7 +8195,7 @@
     </row>
     <row r="71" spans="1:11">
       <c r="A71" s="4">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>117</v>
@@ -8129,7 +8228,7 @@
     </row>
     <row r="72" spans="1:11">
       <c r="A72" s="4">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>103</v>
@@ -8162,7 +8261,7 @@
     </row>
     <row r="73" spans="1:11">
       <c r="A73" s="4">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>127</v>
@@ -8192,7 +8291,7 @@
     </row>
     <row r="74" spans="1:11">
       <c r="A74" s="4">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>129</v>
@@ -8225,7 +8324,7 @@
     </row>
     <row r="75" spans="1:11">
       <c r="A75" s="4">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>132</v>
@@ -8255,7 +8354,7 @@
     </row>
     <row r="76" spans="1:11">
       <c r="A76" s="4">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>134</v>
@@ -8285,7 +8384,7 @@
     </row>
     <row r="77" spans="1:11">
       <c r="A77" s="4">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>134</v>
@@ -8315,7 +8414,7 @@
     </row>
     <row r="78" spans="1:11">
       <c r="A78" s="4">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>134</v>
@@ -8345,7 +8444,7 @@
     </row>
     <row r="79" spans="1:11">
       <c r="A79" s="4">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>138</v>
@@ -8378,7 +8477,7 @@
     </row>
     <row r="80" spans="1:11">
       <c r="A80" s="4">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>66</v>
@@ -8411,7 +8510,7 @@
     </row>
     <row r="81" spans="1:11">
       <c r="A81" s="4">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>143</v>
@@ -8441,7 +8540,7 @@
     </row>
     <row r="82" spans="1:11">
       <c r="A82" s="4">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>32</v>
@@ -8476,7 +8575,7 @@
     </row>
     <row r="83" spans="1:11">
       <c r="A83" s="4">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>145</v>
@@ -8509,7 +8608,7 @@
     </row>
     <row r="84" spans="1:11">
       <c r="A84" s="4">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>148</v>
@@ -8542,7 +8641,7 @@
     </row>
     <row r="85" spans="1:11">
       <c r="A85" s="4">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>151</v>
@@ -8572,7 +8671,7 @@
     </row>
     <row r="86" spans="1:11">
       <c r="A86" s="4">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>153</v>
@@ -8605,7 +8704,7 @@
     </row>
     <row r="87" spans="1:11">
       <c r="A87" s="4">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>155</v>
@@ -8638,7 +8737,7 @@
     </row>
     <row r="88" spans="1:11">
       <c r="A88" s="4">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>58</v>
@@ -8671,7 +8770,7 @@
     </row>
     <row r="89" spans="1:11">
       <c r="A89" s="4">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>58</v>
@@ -8704,7 +8803,7 @@
     </row>
     <row r="90" spans="1:11">
       <c r="A90" s="4">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>26</v>
@@ -8737,7 +8836,7 @@
     </row>
     <row r="91" spans="1:11">
       <c r="A91" s="4">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>26</v>
@@ -8770,7 +8869,7 @@
     </row>
     <row r="92" spans="1:11">
       <c r="A92" s="4">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>26</v>
@@ -8797,7 +8896,7 @@
     </row>
     <row r="93" spans="1:11">
       <c r="A93" s="4">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>26</v>
@@ -8824,7 +8923,7 @@
     </row>
     <row r="94" spans="1:11">
       <c r="A94" s="4">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>26</v>
@@ -8851,7 +8950,7 @@
     </row>
     <row r="95" spans="1:11">
       <c r="A95" s="4">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>26</v>
@@ -8884,7 +8983,7 @@
     </row>
     <row r="96" spans="1:11">
       <c r="A96" s="4">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>26</v>
@@ -8917,7 +9016,7 @@
     </row>
     <row r="97" spans="1:11">
       <c r="A97" s="4">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>26</v>
@@ -8950,7 +9049,7 @@
     </row>
     <row r="98" spans="1:11">
       <c r="A98" s="4">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>26</v>
@@ -8983,7 +9082,7 @@
     </row>
     <row r="99" spans="1:11">
       <c r="A99" s="4">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>26</v>
@@ -9013,7 +9112,7 @@
     </row>
     <row r="100" spans="1:11">
       <c r="A100" s="4">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>26</v>
@@ -9046,7 +9145,7 @@
     </row>
     <row r="101" spans="1:11">
       <c r="A101" s="4">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>26</v>
@@ -9079,7 +9178,7 @@
     </row>
     <row r="102" spans="1:11">
       <c r="A102" s="4">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>26</v>
@@ -9106,7 +9205,7 @@
     </row>
     <row r="103" spans="1:11">
       <c r="A103" s="4">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>26</v>
@@ -9133,7 +9232,7 @@
     </row>
     <row r="104" spans="1:11">
       <c r="A104" s="4">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>183</v>
@@ -9166,7 +9265,7 @@
     </row>
     <row r="105" spans="1:11">
       <c r="A105" s="4">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>26</v>
@@ -9196,7 +9295,7 @@
     </row>
     <row r="106" spans="1:11">
       <c r="A106" s="4">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>32</v>
@@ -9228,7 +9327,7 @@
     </row>
     <row r="107" spans="1:11">
       <c r="A107" s="4">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>32</v>
@@ -9258,7 +9357,7 @@
     </row>
     <row r="108" spans="1:11">
       <c r="A108" s="4">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>32</v>
@@ -9288,7 +9387,7 @@
     </row>
     <row r="109" spans="1:11">
       <c r="A109" s="4">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>42</v>
@@ -9323,7 +9422,7 @@
     </row>
     <row r="110" spans="1:11">
       <c r="A110" s="4">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>32</v>
@@ -9356,7 +9455,7 @@
     </row>
     <row r="111" spans="1:11">
       <c r="A111" s="4">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>32</v>
@@ -9389,7 +9488,7 @@
     </row>
     <row r="112" spans="1:11">
       <c r="A112" s="4">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>32</v>
@@ -9401,10 +9500,10 @@
         <v>200</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>76</v>
+        <v>21</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>1090</v>
+        <v>23</v>
       </c>
       <c r="G112" s="4" t="s">
         <v>14</v>
@@ -9424,7 +9523,7 @@
     </row>
     <row r="113" spans="1:11">
       <c r="A113" s="4">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>32</v>
@@ -9457,7 +9556,7 @@
     </row>
     <row r="114" spans="1:11">
       <c r="A114" s="4">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>32</v>
@@ -9490,7 +9589,7 @@
     </row>
     <row r="115" spans="1:11">
       <c r="A115" s="4">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>32</v>
@@ -9523,7 +9622,7 @@
     </row>
     <row r="116" spans="1:11">
       <c r="A116" s="4">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>32</v>
@@ -9556,7 +9655,7 @@
     </row>
     <row r="117" spans="1:11">
       <c r="A117" s="4">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>32</v>
@@ -9589,7 +9688,7 @@
     </row>
     <row r="118" spans="1:11">
       <c r="A118" s="4">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>32</v>
@@ -9618,7 +9717,7 @@
     </row>
     <row r="119" spans="1:11">
       <c r="A119" s="4">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>32</v>
@@ -9651,7 +9750,7 @@
     </row>
     <row r="120" spans="1:11">
       <c r="A120" s="4">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>58</v>
@@ -9684,7 +9783,7 @@
     </row>
     <row r="121" spans="1:11">
       <c r="A121" s="4">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>58</v>
@@ -9717,7 +9816,7 @@
     </row>
     <row r="122" spans="1:11">
       <c r="A122" s="4">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>58</v>
@@ -9750,7 +9849,7 @@
     </row>
     <row r="123" spans="1:11">
       <c r="A123" s="4">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>58</v>
@@ -9783,7 +9882,7 @@
     </row>
     <row r="124" spans="1:11">
       <c r="A124" s="4">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>58</v>
@@ -9816,7 +9915,7 @@
     </row>
     <row r="125" spans="1:11">
       <c r="A125" s="4">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>58</v>
@@ -9849,7 +9948,7 @@
     </row>
     <row r="126" spans="1:11">
       <c r="A126" s="4">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>58</v>
@@ -9882,7 +9981,7 @@
     </row>
     <row r="127" spans="1:11">
       <c r="A127" s="4">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>58</v>
@@ -9915,7 +10014,7 @@
     </row>
     <row r="128" spans="1:11">
       <c r="A128" s="4">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>58</v>
@@ -9948,7 +10047,7 @@
     </row>
     <row r="129" spans="1:11">
       <c r="A129" s="4">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>58</v>
@@ -9981,7 +10080,7 @@
     </row>
     <row r="130" spans="1:11">
       <c r="A130" s="4">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>145</v>
@@ -10014,7 +10113,7 @@
     </row>
     <row r="131" spans="1:11">
       <c r="A131" s="4">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>145</v>
@@ -10047,7 +10146,7 @@
     </row>
     <row r="132" spans="1:11">
       <c r="A132" s="4">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>24</v>
@@ -10080,7 +10179,7 @@
     </row>
     <row r="133" spans="1:11">
       <c r="A133" s="4">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>24</v>
@@ -10113,7 +10212,7 @@
     </row>
     <row r="134" spans="1:11">
       <c r="A134" s="4">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>26</v>
@@ -10148,7 +10247,7 @@
     </row>
     <row r="135" spans="1:11">
       <c r="A135" s="4">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>24</v>
@@ -10183,7 +10282,7 @@
     </row>
     <row r="136" spans="1:11">
       <c r="A136" s="4">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>26</v>
@@ -10218,7 +10317,7 @@
     </row>
     <row r="137" spans="1:11">
       <c r="A137" s="4">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>26</v>
@@ -10251,7 +10350,7 @@
     </row>
     <row r="138" spans="1:11">
       <c r="A138" s="4">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="B138" s="11" t="s">
         <v>32</v>
@@ -10284,7 +10383,7 @@
     </row>
     <row r="139" spans="1:11">
       <c r="A139" s="4">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>26</v>
@@ -10317,7 +10416,7 @@
     </row>
     <row r="140" spans="1:11">
       <c r="A140" s="4">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>226</v>
@@ -10350,7 +10449,7 @@
     </row>
     <row r="141" spans="1:11">
       <c r="A141" s="4">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>32</v>
@@ -10383,7 +10482,7 @@
     </row>
     <row r="142" spans="1:11">
       <c r="A142" s="4">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>32</v>
@@ -10418,7 +10517,7 @@
     </row>
     <row r="143" spans="1:11">
       <c r="A143" s="4">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>32</v>
@@ -10453,7 +10552,7 @@
     </row>
     <row r="144" spans="1:11">
       <c r="A144" s="4">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>32</v>
@@ -10488,7 +10587,7 @@
     </row>
     <row r="145" spans="1:11">
       <c r="A145" s="4">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>32</v>
@@ -10521,7 +10620,7 @@
     </row>
     <row r="146" spans="1:11">
       <c r="A146" s="4">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>32</v>
@@ -10556,7 +10655,7 @@
     </row>
     <row r="147" spans="1:11">
       <c r="A147" s="4">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>32</v>
@@ -10589,7 +10688,7 @@
     </row>
     <row r="148" spans="1:11">
       <c r="A148" s="4">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>32</v>
@@ -10622,7 +10721,7 @@
     </row>
     <row r="149" spans="1:11">
       <c r="A149" s="4">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>32</v>
@@ -10655,7 +10754,7 @@
     </row>
     <row r="150" spans="1:11">
       <c r="A150" s="4">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>58</v>
@@ -10688,7 +10787,7 @@
     </row>
     <row r="151" spans="1:11">
       <c r="A151" s="4">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>32</v>
@@ -10721,7 +10820,7 @@
     </row>
     <row r="152" spans="1:11">
       <c r="A152" s="4">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>242</v>
@@ -10754,7 +10853,7 @@
     </row>
     <row r="153" spans="1:11">
       <c r="A153" s="4">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>1259</v>
@@ -10787,7 +10886,7 @@
     </row>
     <row r="154" spans="1:11">
       <c r="A154" s="4">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>244</v>
@@ -10822,7 +10921,7 @@
     </row>
     <row r="155" spans="1:11">
       <c r="A155" s="4">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>244</v>
@@ -10857,7 +10956,7 @@
     </row>
     <row r="156" spans="1:11">
       <c r="A156" s="4">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>244</v>
@@ -10892,7 +10991,7 @@
     </row>
     <row r="157" spans="1:11">
       <c r="A157" s="4">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>244</v>
@@ -10927,7 +11026,7 @@
     </row>
     <row r="158" spans="1:11">
       <c r="A158" s="4">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>244</v>
@@ -10962,7 +11061,7 @@
     </row>
     <row r="159" spans="1:11">
       <c r="A159" s="4">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>244</v>
@@ -10997,7 +11096,7 @@
     </row>
     <row r="160" spans="1:11">
       <c r="A160" s="4">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>244</v>
@@ -11032,7 +11131,7 @@
     </row>
     <row r="161" spans="1:11">
       <c r="A161" s="4">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>244</v>
@@ -11067,7 +11166,7 @@
     </row>
     <row r="162" spans="1:11">
       <c r="A162" s="4">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>244</v>
@@ -11100,7 +11199,7 @@
     </row>
     <row r="163" spans="1:11">
       <c r="A163" s="4">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>244</v>
@@ -11133,7 +11232,7 @@
     </row>
     <row r="164" spans="1:11">
       <c r="A164" s="4">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>244</v>
@@ -11168,7 +11267,7 @@
     </row>
     <row r="165" spans="1:11">
       <c r="A165" s="4">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>244</v>
@@ -11203,7 +11302,7 @@
     </row>
     <row r="166" spans="1:11">
       <c r="A166" s="4">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>244</v>
@@ -11238,7 +11337,7 @@
     </row>
     <row r="167" spans="1:11">
       <c r="A167" s="4">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>244</v>
@@ -11273,7 +11372,7 @@
     </row>
     <row r="168" spans="1:11">
       <c r="A168" s="4">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>244</v>
@@ -11306,7 +11405,7 @@
     </row>
     <row r="169" spans="1:11">
       <c r="A169" s="4">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>626</v>
@@ -11339,7 +11438,7 @@
     </row>
     <row r="170" spans="1:11">
       <c r="A170" s="4">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="B170" s="2" t="s">
         <v>248</v>
@@ -11372,7 +11471,7 @@
     </row>
     <row r="171" spans="1:11">
       <c r="A171" s="4">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="B171" s="2" t="s">
         <v>10</v>
@@ -11405,7 +11504,7 @@
     </row>
     <row r="172" spans="1:11">
       <c r="A172" s="4">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="B172" s="2" t="s">
         <v>10</v>
@@ -11440,7 +11539,7 @@
     </row>
     <row r="173" spans="1:11">
       <c r="A173" s="4">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="B173" s="2" t="s">
         <v>10</v>
@@ -11473,7 +11572,7 @@
     </row>
     <row r="174" spans="1:11">
       <c r="A174" s="4">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>10</v>
@@ -11506,7 +11605,7 @@
     </row>
     <row r="175" spans="1:11">
       <c r="A175" s="4">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>10</v>
@@ -11541,7 +11640,7 @@
     </row>
     <row r="176" spans="1:11">
       <c r="A176" s="4">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="B176" s="2" t="s">
         <v>10</v>
@@ -11571,7 +11670,7 @@
     </row>
     <row r="177" spans="1:11">
       <c r="A177" s="4">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="B177" s="2" t="s">
         <v>10</v>
@@ -11601,7 +11700,7 @@
     </row>
     <row r="178" spans="1:11">
       <c r="A178" s="4">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="B178" s="2" t="s">
         <v>226</v>
@@ -11629,7 +11728,7 @@
     </row>
     <row r="179" spans="1:11">
       <c r="A179" s="4">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>263</v>
@@ -11664,7 +11763,7 @@
     </row>
     <row r="180" spans="1:11">
       <c r="A180" s="4">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="B180" s="2" t="s">
         <v>265</v>
@@ -11694,7 +11793,7 @@
     </row>
     <row r="181" spans="1:11">
       <c r="A181" s="4">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="B181" s="2" t="s">
         <v>268</v>
@@ -11727,7 +11826,7 @@
     </row>
     <row r="182" spans="1:11">
       <c r="A182" s="4">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="B182" s="5" t="s">
         <v>58</v>
@@ -11760,7 +11859,7 @@
     </row>
     <row r="183" spans="1:11">
       <c r="A183" s="4">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="B183" s="2" t="s">
         <v>145</v>
@@ -11793,7 +11892,7 @@
     </row>
     <row r="184" spans="1:11">
       <c r="A184" s="4">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="B184" s="2" t="s">
         <v>273</v>
@@ -11826,7 +11925,7 @@
     </row>
     <row r="185" spans="1:11">
       <c r="A185" s="4">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="B185" s="2" t="s">
         <v>277</v>
@@ -11856,7 +11955,7 @@
     </row>
     <row r="186" spans="1:11">
       <c r="A186" s="4">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>10</v>
@@ -11886,7 +11985,7 @@
     </row>
     <row r="187" spans="1:11">
       <c r="A187" s="4">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="B187" s="5" t="s">
         <v>187</v>
@@ -11919,7 +12018,7 @@
     </row>
     <row r="188" spans="1:11">
       <c r="A188" s="4">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="B188" s="2" t="s">
         <v>187</v>
@@ -11946,7 +12045,7 @@
     </row>
     <row r="189" spans="1:11">
       <c r="A189" s="4">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="B189" s="2" t="s">
         <v>187</v>
@@ -11977,7 +12076,7 @@
     </row>
     <row r="190" spans="1:11">
       <c r="A190" s="4">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="B190" s="2" t="s">
         <v>242</v>
@@ -12012,7 +12111,7 @@
     </row>
     <row r="191" spans="1:11">
       <c r="A191" s="4">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="B191" s="2" t="s">
         <v>285</v>
@@ -12042,7 +12141,7 @@
     </row>
     <row r="192" spans="1:11">
       <c r="A192" s="4">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="B192" s="2" t="s">
         <v>285</v>
@@ -12075,7 +12174,7 @@
     </row>
     <row r="193" spans="1:10">
       <c r="A193" s="4">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="B193" s="2" t="s">
         <v>32</v>
@@ -12105,7 +12204,7 @@
     </row>
     <row r="194" spans="1:10">
       <c r="A194" s="4">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="B194" s="2" t="s">
         <v>288</v>
@@ -12135,7 +12234,7 @@
     </row>
     <row r="195" spans="1:10">
       <c r="A195" s="4">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="B195" s="2" t="s">
         <v>288</v>
@@ -12165,7 +12264,7 @@
     </row>
     <row r="196" spans="1:10">
       <c r="A196" s="4">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="B196" s="2" t="s">
         <v>288</v>
@@ -12195,7 +12294,7 @@
     </row>
     <row r="197" spans="1:10">
       <c r="A197" s="4">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="B197" s="2" t="s">
         <v>288</v>
@@ -12225,7 +12324,7 @@
     </row>
     <row r="198" spans="1:10">
       <c r="A198" s="4">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="B198" s="2" t="s">
         <v>288</v>
@@ -12255,7 +12354,7 @@
     </row>
     <row r="199" spans="1:10">
       <c r="A199" s="4">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="B199" s="2" t="s">
         <v>288</v>
@@ -12285,7 +12384,7 @@
     </row>
     <row r="200" spans="1:10">
       <c r="A200" s="4">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="B200" s="2" t="s">
         <v>288</v>
@@ -12315,7 +12414,7 @@
     </row>
     <row r="201" spans="1:10">
       <c r="A201" s="4">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="B201" s="2" t="s">
         <v>288</v>
@@ -12345,7 +12444,7 @@
     </row>
     <row r="202" spans="1:10">
       <c r="A202" s="4">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="B202" s="2" t="s">
         <v>288</v>
@@ -12375,7 +12474,7 @@
     </row>
     <row r="203" spans="1:10">
       <c r="A203" s="4">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="B203" s="2" t="s">
         <v>288</v>
@@ -12405,7 +12504,7 @@
     </row>
     <row r="204" spans="1:10">
       <c r="A204" s="4">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="B204" s="2" t="s">
         <v>288</v>
@@ -12435,7 +12534,7 @@
     </row>
     <row r="205" spans="1:10">
       <c r="A205" s="4">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="B205" s="2" t="s">
         <v>288</v>
@@ -12465,7 +12564,7 @@
     </row>
     <row r="206" spans="1:10">
       <c r="A206" s="4">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="B206" s="2" t="s">
         <v>288</v>
@@ -12495,7 +12594,7 @@
     </row>
     <row r="207" spans="1:10">
       <c r="A207" s="4">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="B207" s="2" t="s">
         <v>288</v>
@@ -12525,7 +12624,7 @@
     </row>
     <row r="208" spans="1:10">
       <c r="A208" s="4">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="B208" s="2" t="s">
         <v>288</v>
@@ -12555,7 +12654,7 @@
     </row>
     <row r="209" spans="1:11">
       <c r="A209" s="4">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="B209" s="2" t="s">
         <v>288</v>
@@ -12585,7 +12684,7 @@
     </row>
     <row r="210" spans="1:11">
       <c r="A210" s="4">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="B210" s="2" t="s">
         <v>288</v>
@@ -12615,7 +12714,7 @@
     </row>
     <row r="211" spans="1:11">
       <c r="A211" s="4">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="B211" s="2" t="s">
         <v>288</v>
@@ -12645,7 +12744,7 @@
     </row>
     <row r="212" spans="1:11">
       <c r="A212" s="4">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B212" s="2" t="s">
         <v>288</v>
@@ -12675,7 +12774,7 @@
     </row>
     <row r="213" spans="1:11">
       <c r="A213" s="4">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="B213" s="2" t="s">
         <v>288</v>
@@ -12705,7 +12804,7 @@
     </row>
     <row r="214" spans="1:11">
       <c r="A214" s="4">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="B214" s="2" t="s">
         <v>288</v>
@@ -12735,7 +12834,7 @@
     </row>
     <row r="215" spans="1:11">
       <c r="A215" s="4">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="B215" s="2" t="s">
         <v>310</v>
@@ -12768,7 +12867,7 @@
     </row>
     <row r="216" spans="1:11">
       <c r="A216" s="4">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="B216" s="2" t="s">
         <v>310</v>
@@ -12801,7 +12900,7 @@
     </row>
     <row r="217" spans="1:11">
       <c r="A217" s="4">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="B217" s="3" t="s">
         <v>313</v>
@@ -12834,7 +12933,7 @@
     </row>
     <row r="218" spans="1:11">
       <c r="A218" s="4">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="B218" s="5" t="s">
         <v>106</v>
@@ -12867,7 +12966,7 @@
     </row>
     <row r="219" spans="1:11">
       <c r="A219" s="4">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="B219" s="2" t="s">
         <v>66</v>
@@ -12898,7 +12997,7 @@
     </row>
     <row r="220" spans="1:11">
       <c r="A220" s="4">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="B220" s="2" t="s">
         <v>66</v>
@@ -12931,7 +13030,7 @@
     </row>
     <row r="221" spans="1:11">
       <c r="A221" s="4">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="B221" s="2" t="s">
         <v>66</v>
@@ -12964,7 +13063,7 @@
     </row>
     <row r="222" spans="1:11">
       <c r="A222" s="4">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="B222" s="3" t="s">
         <v>32</v>
@@ -12997,7 +13096,7 @@
     </row>
     <row r="223" spans="1:11">
       <c r="A223" s="4">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="B223" s="3" t="s">
         <v>32</v>
@@ -13009,10 +13108,10 @@
         <v>319</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>1036</v>
+        <v>967</v>
       </c>
       <c r="G223" s="4" t="s">
         <v>14</v>
@@ -13032,7 +13131,7 @@
     </row>
     <row r="224" spans="1:11">
       <c r="A224" s="4">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="B224" s="3" t="s">
         <v>58</v>
@@ -13065,7 +13164,7 @@
     </row>
     <row r="225" spans="1:11">
       <c r="A225" s="4">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="B225" s="2" t="s">
         <v>10</v>
@@ -13100,7 +13199,7 @@
     </row>
     <row r="226" spans="1:11">
       <c r="A226" s="4">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="B226" s="2" t="s">
         <v>26</v>
@@ -13135,7 +13234,7 @@
     </row>
     <row r="227" spans="1:11">
       <c r="A227" s="4">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="B227" s="2" t="s">
         <v>26</v>
@@ -13168,7 +13267,7 @@
     </row>
     <row r="228" spans="1:11">
       <c r="A228" s="4">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="B228" s="2" t="s">
         <v>32</v>
@@ -13201,7 +13300,7 @@
     </row>
     <row r="229" spans="1:11">
       <c r="A229" s="4">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="B229" s="2" t="s">
         <v>32</v>
@@ -13213,10 +13312,10 @@
         <v>326</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>1050</v>
+        <v>23</v>
       </c>
       <c r="G229" s="4" t="s">
         <v>14</v>
@@ -13236,7 +13335,7 @@
     </row>
     <row r="230" spans="1:11">
       <c r="A230" s="4">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="B230" s="2" t="s">
         <v>32</v>
@@ -13271,7 +13370,7 @@
     </row>
     <row r="231" spans="1:11">
       <c r="A231" s="4">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B231" s="2" t="s">
         <v>32</v>
@@ -13306,7 +13405,7 @@
     </row>
     <row r="232" spans="1:11">
       <c r="A232" s="4">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="B232" s="2" t="s">
         <v>32</v>
@@ -13318,10 +13417,10 @@
         <v>329</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>23</v>
+        <v>1090</v>
       </c>
       <c r="G232" s="4" t="s">
         <v>14</v>
@@ -13339,7 +13438,7 @@
     </row>
     <row r="233" spans="1:11">
       <c r="A233" s="4">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="B233" s="5" t="s">
         <v>32</v>
@@ -13372,7 +13471,7 @@
     </row>
     <row r="234" spans="1:11">
       <c r="A234" s="4">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="B234" s="2" t="s">
         <v>32</v>
@@ -13405,7 +13504,7 @@
     </row>
     <row r="235" spans="1:11">
       <c r="A235" s="4">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="B235" s="2" t="s">
         <v>32</v>
@@ -13438,7 +13537,7 @@
     </row>
     <row r="236" spans="1:11">
       <c r="A236" s="4">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="B236" s="2" t="s">
         <v>32</v>
@@ -13471,7 +13570,7 @@
     </row>
     <row r="237" spans="1:11">
       <c r="A237" s="4">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="B237" s="2" t="s">
         <v>32</v>
@@ -13504,7 +13603,7 @@
     </row>
     <row r="238" spans="1:11">
       <c r="A238" s="4">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="B238" s="2" t="s">
         <v>32</v>
@@ -13539,7 +13638,7 @@
     </row>
     <row r="239" spans="1:11">
       <c r="A239" s="4">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="B239" s="2" t="s">
         <v>32</v>
@@ -13572,7 +13671,7 @@
     </row>
     <row r="240" spans="1:11">
       <c r="A240" s="4">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="B240" s="2" t="s">
         <v>32</v>
@@ -13607,7 +13706,7 @@
     </row>
     <row r="241" spans="1:11">
       <c r="A241" s="4">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="B241" s="2" t="s">
         <v>32</v>
@@ -13640,7 +13739,7 @@
     </row>
     <row r="242" spans="1:11">
       <c r="A242" s="4">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B242" s="2" t="s">
         <v>32</v>
@@ -13652,16 +13751,16 @@
         <v>343</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>1072</v>
+        <v>606</v>
       </c>
       <c r="G242" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H242" s="1" t="s">
-        <v>1340</v>
+        <v>1442</v>
       </c>
       <c r="I242" s="9">
         <v>45636</v>
@@ -13675,7 +13774,7 @@
     </row>
     <row r="243" spans="1:11">
       <c r="A243" s="4">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="B243" s="2" t="s">
         <v>32</v>
@@ -13708,7 +13807,7 @@
     </row>
     <row r="244" spans="1:11">
       <c r="A244" s="4">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="B244" s="2" t="s">
         <v>32</v>
@@ -13741,7 +13840,7 @@
     </row>
     <row r="245" spans="1:11">
       <c r="A245" s="4">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="B245" s="2" t="s">
         <v>244</v>
@@ -13776,7 +13875,7 @@
     </row>
     <row r="246" spans="1:11">
       <c r="A246" s="4">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="B246" s="2" t="s">
         <v>32</v>
@@ -13809,7 +13908,7 @@
     </row>
     <row r="247" spans="1:11">
       <c r="A247" s="4">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="B247" s="2" t="s">
         <v>66</v>
@@ -13844,7 +13943,7 @@
     </row>
     <row r="248" spans="1:11">
       <c r="A248" s="4">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="B248" s="2" t="s">
         <v>32</v>
@@ -13877,7 +13976,7 @@
     </row>
     <row r="249" spans="1:11">
       <c r="A249" s="4">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="B249" s="2" t="s">
         <v>32</v>
@@ -13910,7 +14009,7 @@
     </row>
     <row r="250" spans="1:11">
       <c r="A250" s="4">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="B250" s="2" t="s">
         <v>32</v>
@@ -13943,7 +14042,7 @@
     </row>
     <row r="251" spans="1:11">
       <c r="A251" s="4">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="B251" s="2" t="s">
         <v>32</v>
@@ -13978,7 +14077,7 @@
     </row>
     <row r="252" spans="1:11">
       <c r="A252" s="4">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="B252" s="2" t="s">
         <v>32</v>
@@ -14013,7 +14112,7 @@
     </row>
     <row r="253" spans="1:11" ht="15.6">
       <c r="A253" s="4">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="B253" s="2" t="s">
         <v>32</v>
@@ -14025,10 +14124,10 @@
         <v>358</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F253" s="50" t="s">
-        <v>1032</v>
+        <v>23</v>
       </c>
       <c r="G253" s="4" t="s">
         <v>14</v>
@@ -14048,7 +14147,7 @@
     </row>
     <row r="254" spans="1:11">
       <c r="A254" s="4">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="B254" s="2" t="s">
         <v>32</v>
@@ -14083,7 +14182,7 @@
     </row>
     <row r="255" spans="1:11">
       <c r="A255" s="4">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="B255" s="51" t="s">
         <v>32</v>
@@ -14118,7 +14217,7 @@
     </row>
     <row r="256" spans="1:11">
       <c r="A256" s="4">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="B256" s="2" t="s">
         <v>32</v>
@@ -14153,7 +14252,7 @@
     </row>
     <row r="257" spans="1:11">
       <c r="A257" s="4">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="B257" s="2" t="s">
         <v>362</v>
@@ -14188,7 +14287,7 @@
     </row>
     <row r="258" spans="1:11">
       <c r="A258" s="4">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="B258" s="2" t="s">
         <v>558</v>
@@ -14219,7 +14318,7 @@
     </row>
     <row r="259" spans="1:11">
       <c r="A259" s="4">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="B259" s="2" t="s">
         <v>558</v>
@@ -14252,7 +14351,7 @@
     </row>
     <row r="260" spans="1:11">
       <c r="A260" s="4">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="B260" s="2" t="s">
         <v>364</v>
@@ -14287,7 +14386,7 @@
     </row>
     <row r="261" spans="1:11">
       <c r="A261" s="4">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="B261" s="2" t="s">
         <v>364</v>
@@ -14299,16 +14398,16 @@
         <v>366</v>
       </c>
       <c r="E261" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>1059</v>
+        <v>23</v>
       </c>
       <c r="G261" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H261" s="1" t="s">
-        <v>1373</v>
+        <v>1395</v>
       </c>
       <c r="I261" s="9">
         <v>45870</v>
@@ -14322,7 +14421,7 @@
     </row>
     <row r="262" spans="1:11">
       <c r="A262" s="4">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B262" s="2" t="s">
         <v>364</v>
@@ -14342,7 +14441,9 @@
       <c r="G262" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H262" s="1"/>
+      <c r="H262" s="1" t="s">
+        <v>1396</v>
+      </c>
       <c r="I262" s="9">
         <v>45917</v>
       </c>
@@ -14355,7 +14456,7 @@
     </row>
     <row r="263" spans="1:11">
       <c r="A263" s="4">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="B263" s="2" t="s">
         <v>955</v>
@@ -14388,7 +14489,7 @@
     </row>
     <row r="264" spans="1:11">
       <c r="A264" s="4">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="B264" s="2" t="s">
         <v>369</v>
@@ -14418,7 +14519,7 @@
     </row>
     <row r="265" spans="1:11">
       <c r="A265" s="4">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="B265" s="2" t="s">
         <v>371</v>
@@ -14451,7 +14552,7 @@
     </row>
     <row r="266" spans="1:11">
       <c r="A266" s="4">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="B266" s="2" t="s">
         <v>268</v>
@@ -14484,7 +14585,7 @@
     </row>
     <row r="267" spans="1:11">
       <c r="A267" s="4">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="B267" s="2" t="s">
         <v>374</v>
@@ -14517,7 +14618,7 @@
     </row>
     <row r="268" spans="1:11">
       <c r="A268" s="4">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="B268" s="2" t="s">
         <v>26</v>
@@ -14547,7 +14648,7 @@
     </row>
     <row r="269" spans="1:11">
       <c r="A269" s="4">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="B269" s="10" t="s">
         <v>26</v>
@@ -14580,7 +14681,7 @@
     </row>
     <row r="270" spans="1:11">
       <c r="A270" s="4">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="B270" s="10" t="s">
         <v>26</v>
@@ -14610,7 +14711,7 @@
     </row>
     <row r="271" spans="1:11">
       <c r="A271" s="4">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="B271" s="10" t="s">
         <v>26</v>
@@ -14640,7 +14741,7 @@
     </row>
     <row r="272" spans="1:11">
       <c r="A272" s="4">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="B272" s="10" t="s">
         <v>268</v>
@@ -14673,7 +14774,7 @@
     </row>
     <row r="273" spans="1:11">
       <c r="A273" s="4">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="B273" s="10" t="s">
         <v>268</v>
@@ -14706,7 +14807,7 @@
     </row>
     <row r="274" spans="1:11">
       <c r="A274" s="4">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="B274" s="2" t="s">
         <v>96</v>
@@ -14741,7 +14842,7 @@
     </row>
     <row r="275" spans="1:11">
       <c r="A275" s="4">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="B275" s="2" t="s">
         <v>244</v>
@@ -14776,7 +14877,7 @@
     </row>
     <row r="276" spans="1:11">
       <c r="A276" s="4">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="B276" s="2" t="s">
         <v>32</v>
@@ -14809,7 +14910,7 @@
     </row>
     <row r="277" spans="1:11">
       <c r="A277" s="4">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="B277" s="2" t="s">
         <v>390</v>
@@ -14842,7 +14943,7 @@
     </row>
     <row r="278" spans="1:11">
       <c r="A278" s="4">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="B278" s="2" t="s">
         <v>390</v>
@@ -14875,7 +14976,7 @@
     </row>
     <row r="279" spans="1:11">
       <c r="A279" s="4">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="B279" s="2" t="s">
         <v>390</v>
@@ -14908,7 +15009,7 @@
     </row>
     <row r="280" spans="1:11">
       <c r="A280" s="4">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="B280" s="2" t="s">
         <v>390</v>
@@ -14941,7 +15042,7 @@
     </row>
     <row r="281" spans="1:11">
       <c r="A281" s="4">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="B281" s="2" t="s">
         <v>390</v>
@@ -14974,7 +15075,7 @@
     </row>
     <row r="282" spans="1:11">
       <c r="A282" s="4">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="B282" s="2" t="s">
         <v>32</v>
@@ -15007,7 +15108,7 @@
     </row>
     <row r="283" spans="1:11">
       <c r="A283" s="4">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="B283" s="2" t="s">
         <v>32</v>
@@ -15040,7 +15141,7 @@
     </row>
     <row r="284" spans="1:11">
       <c r="A284" s="4">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="B284" s="2" t="s">
         <v>400</v>
@@ -15073,7 +15174,7 @@
     </row>
     <row r="285" spans="1:11">
       <c r="A285" s="4">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="B285" s="2" t="s">
         <v>402</v>
@@ -15106,7 +15207,7 @@
     </row>
     <row r="286" spans="1:11">
       <c r="A286" s="4">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="B286" s="2" t="s">
         <v>244</v>
@@ -15141,7 +15242,7 @@
     </row>
     <row r="287" spans="1:11">
       <c r="A287" s="4">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="B287" s="2" t="s">
         <v>96</v>
@@ -15174,7 +15275,7 @@
     </row>
     <row r="288" spans="1:11">
       <c r="A288" s="4">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="B288" s="2" t="s">
         <v>32</v>
@@ -15207,7 +15308,7 @@
     </row>
     <row r="289" spans="1:11">
       <c r="A289" s="4">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="B289" s="2" t="s">
         <v>58</v>
@@ -15240,7 +15341,7 @@
     </row>
     <row r="290" spans="1:11">
       <c r="A290" s="4">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="B290" s="31" t="s">
         <v>414</v>
@@ -15275,7 +15376,7 @@
     </row>
     <row r="291" spans="1:11">
       <c r="A291" s="4">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="B291" s="31" t="s">
         <v>414</v>
@@ -15310,7 +15411,7 @@
     </row>
     <row r="292" spans="1:11">
       <c r="A292" s="4">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="B292" s="31" t="s">
         <v>414</v>
@@ -15345,7 +15446,7 @@
     </row>
     <row r="293" spans="1:11">
       <c r="A293" s="4">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="B293" s="31" t="s">
         <v>414</v>
@@ -15380,7 +15481,7 @@
     </row>
     <row r="294" spans="1:11">
       <c r="A294" s="4">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="B294" s="31" t="s">
         <v>414</v>
@@ -15415,7 +15516,7 @@
     </row>
     <row r="295" spans="1:11">
       <c r="A295" s="4">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="B295" s="31" t="s">
         <v>414</v>
@@ -15450,7 +15551,7 @@
     </row>
     <row r="296" spans="1:11">
       <c r="A296" s="4">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="B296" s="31" t="s">
         <v>414</v>
@@ -15485,7 +15586,7 @@
     </row>
     <row r="297" spans="1:11">
       <c r="A297" s="4">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="B297" s="31" t="s">
         <v>414</v>
@@ -15520,7 +15621,7 @@
     </row>
     <row r="298" spans="1:11">
       <c r="A298" s="4">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="B298" s="31" t="s">
         <v>414</v>
@@ -15555,7 +15656,7 @@
     </row>
     <row r="299" spans="1:11">
       <c r="A299" s="4">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="B299" s="31" t="s">
         <v>414</v>
@@ -15590,7 +15691,7 @@
     </row>
     <row r="300" spans="1:11">
       <c r="A300" s="4">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="B300" s="31" t="s">
         <v>414</v>
@@ -15625,7 +15726,7 @@
     </row>
     <row r="301" spans="1:11">
       <c r="A301" s="4">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="B301" s="31" t="s">
         <v>414</v>
@@ -15660,7 +15761,7 @@
     </row>
     <row r="302" spans="1:11">
       <c r="A302" s="4">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="B302" s="31" t="s">
         <v>414</v>
@@ -15695,7 +15796,7 @@
     </row>
     <row r="303" spans="1:11">
       <c r="A303" s="4">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="B303" s="31" t="s">
         <v>414</v>
@@ -15730,7 +15831,7 @@
     </row>
     <row r="304" spans="1:11">
       <c r="A304" s="4">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="B304" s="31" t="s">
         <v>414</v>
@@ -15765,7 +15866,7 @@
     </row>
     <row r="305" spans="1:11">
       <c r="A305" s="4">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="B305" s="31" t="s">
         <v>414</v>
@@ -15800,7 +15901,7 @@
     </row>
     <row r="306" spans="1:11">
       <c r="A306" s="4">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B306" s="31" t="s">
         <v>414</v>
@@ -15835,7 +15936,7 @@
     </row>
     <row r="307" spans="1:11">
       <c r="A307" s="4">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="B307" s="31" t="s">
         <v>414</v>
@@ -15870,7 +15971,7 @@
     </row>
     <row r="308" spans="1:11">
       <c r="A308" s="4">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="B308" s="31" t="s">
         <v>414</v>
@@ -15905,7 +16006,7 @@
     </row>
     <row r="309" spans="1:11">
       <c r="A309" s="4">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="B309" s="31" t="s">
         <v>414</v>
@@ -15940,7 +16041,7 @@
     </row>
     <row r="310" spans="1:11">
       <c r="A310" s="4">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="B310" s="31" t="s">
         <v>414</v>
@@ -15975,7 +16076,7 @@
     </row>
     <row r="311" spans="1:11">
       <c r="A311" s="4">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="B311" s="31" t="s">
         <v>414</v>
@@ -16010,7 +16111,7 @@
     </row>
     <row r="312" spans="1:11">
       <c r="A312" s="4">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="B312" s="31" t="s">
         <v>414</v>
@@ -16045,7 +16146,7 @@
     </row>
     <row r="313" spans="1:11">
       <c r="A313" s="4">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B313" s="31" t="s">
         <v>414</v>
@@ -16080,7 +16181,7 @@
     </row>
     <row r="314" spans="1:11">
       <c r="A314" s="4">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="B314" s="31" t="s">
         <v>414</v>
@@ -16115,7 +16216,7 @@
     </row>
     <row r="315" spans="1:11">
       <c r="A315" s="4">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="B315" s="31" t="s">
         <v>414</v>
@@ -16150,7 +16251,7 @@
     </row>
     <row r="316" spans="1:11">
       <c r="A316" s="4">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="B316" s="31" t="s">
         <v>414</v>
@@ -16185,7 +16286,7 @@
     </row>
     <row r="317" spans="1:11">
       <c r="A317" s="4">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="B317" s="31" t="s">
         <v>414</v>
@@ -16220,7 +16321,7 @@
     </row>
     <row r="318" spans="1:11">
       <c r="A318" s="4">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="B318" s="31" t="s">
         <v>414</v>
@@ -16255,7 +16356,7 @@
     </row>
     <row r="319" spans="1:11">
       <c r="A319" s="4">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="B319" s="31" t="s">
         <v>414</v>
@@ -16290,7 +16391,7 @@
     </row>
     <row r="320" spans="1:11">
       <c r="A320" s="4">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="B320" s="31" t="s">
         <v>414</v>
@@ -16325,7 +16426,7 @@
     </row>
     <row r="321" spans="1:11">
       <c r="A321" s="4">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="B321" s="31" t="s">
         <v>414</v>
@@ -16360,7 +16461,7 @@
     </row>
     <row r="322" spans="1:11">
       <c r="A322" s="4">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="B322" s="31" t="s">
         <v>414</v>
@@ -16395,7 +16496,7 @@
     </row>
     <row r="323" spans="1:11">
       <c r="A323" s="4">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="B323" s="31" t="s">
         <v>414</v>
@@ -16430,7 +16531,7 @@
     </row>
     <row r="324" spans="1:11">
       <c r="A324" s="4">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="B324" s="31" t="s">
         <v>414</v>
@@ -16465,7 +16566,7 @@
     </row>
     <row r="325" spans="1:11">
       <c r="A325" s="4">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="B325" s="31" t="s">
         <v>414</v>
@@ -16500,7 +16601,7 @@
     </row>
     <row r="326" spans="1:11">
       <c r="A326" s="4">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="B326" s="31" t="s">
         <v>414</v>
@@ -16535,7 +16636,7 @@
     </row>
     <row r="327" spans="1:11">
       <c r="A327" s="4">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="B327" s="31" t="s">
         <v>414</v>
@@ -16570,7 +16671,7 @@
     </row>
     <row r="328" spans="1:11">
       <c r="A328" s="4">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="B328" s="31" t="s">
         <v>414</v>
@@ -16603,7 +16704,7 @@
     </row>
     <row r="329" spans="1:11">
       <c r="A329" s="4">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="B329" s="31" t="s">
         <v>414</v>
@@ -16636,7 +16737,7 @@
     </row>
     <row r="330" spans="1:11">
       <c r="A330" s="4">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="B330" s="31" t="s">
         <v>414</v>
@@ -16669,7 +16770,7 @@
     </row>
     <row r="331" spans="1:11">
       <c r="A331" s="4">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="B331" s="31" t="s">
         <v>414</v>
@@ -16702,7 +16803,7 @@
     </row>
     <row r="332" spans="1:11">
       <c r="A332" s="4">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="B332" s="31" t="s">
         <v>414</v>
@@ -16735,7 +16836,7 @@
     </row>
     <row r="333" spans="1:11">
       <c r="A333" s="4">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="B333" s="31" t="s">
         <v>414</v>
@@ -16770,7 +16871,7 @@
     </row>
     <row r="334" spans="1:11">
       <c r="A334" s="4">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="B334" s="31" t="s">
         <v>414</v>
@@ -16803,7 +16904,7 @@
     </row>
     <row r="335" spans="1:11">
       <c r="A335" s="4">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="B335" s="31" t="s">
         <v>414</v>
@@ -16836,7 +16937,7 @@
     </row>
     <row r="336" spans="1:11">
       <c r="A336" s="4">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="B336" s="31" t="s">
         <v>414</v>
@@ -16869,7 +16970,7 @@
     </row>
     <row r="337" spans="1:11">
       <c r="A337" s="4">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B337" s="31" t="s">
         <v>414</v>
@@ -16904,7 +17005,7 @@
     </row>
     <row r="338" spans="1:11">
       <c r="A338" s="4">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="B338" s="31" t="s">
         <v>414</v>
@@ -16939,7 +17040,7 @@
     </row>
     <row r="339" spans="1:11">
       <c r="A339" s="4">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="B339" s="31" t="s">
         <v>414</v>
@@ -16974,7 +17075,7 @@
     </row>
     <row r="340" spans="1:11">
       <c r="A340" s="4">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="B340" s="31" t="s">
         <v>414</v>
@@ -17009,7 +17110,7 @@
     </row>
     <row r="341" spans="1:11">
       <c r="A341" s="4">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="B341" s="31" t="s">
         <v>414</v>
@@ -17044,7 +17145,7 @@
     </row>
     <row r="342" spans="1:11">
       <c r="A342" s="4">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="B342" s="31" t="s">
         <v>414</v>
@@ -17079,7 +17180,7 @@
     </row>
     <row r="343" spans="1:11">
       <c r="A343" s="4">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="B343" s="31" t="s">
         <v>414</v>
@@ -17114,7 +17215,7 @@
     </row>
     <row r="344" spans="1:11">
       <c r="A344" s="4">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="B344" s="31" t="s">
         <v>414</v>
@@ -17149,7 +17250,7 @@
     </row>
     <row r="345" spans="1:11">
       <c r="A345" s="4">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="B345" s="31" t="s">
         <v>414</v>
@@ -17184,7 +17285,7 @@
     </row>
     <row r="346" spans="1:11">
       <c r="A346" s="4">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="B346" s="31" t="s">
         <v>414</v>
@@ -17219,7 +17320,7 @@
     </row>
     <row r="347" spans="1:11">
       <c r="A347" s="4">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="B347" s="31" t="s">
         <v>414</v>
@@ -17254,7 +17355,7 @@
     </row>
     <row r="348" spans="1:11">
       <c r="A348" s="4">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="B348" s="31" t="s">
         <v>414</v>
@@ -17289,7 +17390,7 @@
     </row>
     <row r="349" spans="1:11">
       <c r="A349" s="4">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="B349" s="31" t="s">
         <v>414</v>
@@ -17324,7 +17425,7 @@
     </row>
     <row r="350" spans="1:11">
       <c r="A350" s="4">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="B350" s="31" t="s">
         <v>414</v>
@@ -17359,7 +17460,7 @@
     </row>
     <row r="351" spans="1:11">
       <c r="A351" s="4">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="B351" s="31" t="s">
         <v>414</v>
@@ -17394,7 +17495,7 @@
     </row>
     <row r="352" spans="1:11">
       <c r="A352" s="4">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="B352" s="31" t="s">
         <v>414</v>
@@ -17429,7 +17530,7 @@
     </row>
     <row r="353" spans="1:11">
       <c r="A353" s="4">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="B353" s="31" t="s">
         <v>414</v>
@@ -17464,7 +17565,7 @@
     </row>
     <row r="354" spans="1:11">
       <c r="A354" s="4">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="B354" s="31" t="s">
         <v>414</v>
@@ -17499,7 +17600,7 @@
     </row>
     <row r="355" spans="1:11">
       <c r="A355" s="4">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="B355" s="31" t="s">
         <v>414</v>
@@ -17534,7 +17635,7 @@
     </row>
     <row r="356" spans="1:11">
       <c r="A356" s="4">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="B356" s="31" t="s">
         <v>414</v>
@@ -17569,7 +17670,7 @@
     </row>
     <row r="357" spans="1:11">
       <c r="A357" s="4">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="B357" s="31" t="s">
         <v>414</v>
@@ -17604,7 +17705,7 @@
     </row>
     <row r="358" spans="1:11">
       <c r="A358" s="4">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="B358" s="31" t="s">
         <v>414</v>
@@ -17639,7 +17740,7 @@
     </row>
     <row r="359" spans="1:11">
       <c r="A359" s="4">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="B359" s="31" t="s">
         <v>414</v>
@@ -17674,7 +17775,7 @@
     </row>
     <row r="360" spans="1:11">
       <c r="A360" s="4">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="B360" s="31" t="s">
         <v>414</v>
@@ -17709,7 +17810,7 @@
     </row>
     <row r="361" spans="1:11">
       <c r="A361" s="4">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="B361" s="31" t="s">
         <v>414</v>
@@ -17744,7 +17845,7 @@
     </row>
     <row r="362" spans="1:11">
       <c r="A362" s="4">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="B362" s="31" t="s">
         <v>414</v>
@@ -17779,7 +17880,7 @@
     </row>
     <row r="363" spans="1:11">
       <c r="A363" s="4">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="B363" s="31" t="s">
         <v>414</v>
@@ -17814,7 +17915,7 @@
     </row>
     <row r="364" spans="1:11">
       <c r="A364" s="4">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="B364" s="31" t="s">
         <v>414</v>
@@ -17849,7 +17950,7 @@
     </row>
     <row r="365" spans="1:11">
       <c r="A365" s="4">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="B365" s="31" t="s">
         <v>414</v>
@@ -17882,7 +17983,7 @@
     </row>
     <row r="366" spans="1:11">
       <c r="A366" s="4">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="B366" s="32" t="s">
         <v>414</v>
@@ -17917,7 +18018,7 @@
     </row>
     <row r="367" spans="1:11">
       <c r="A367" s="4">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="B367" s="32" t="s">
         <v>414</v>
@@ -17952,7 +18053,7 @@
     </row>
     <row r="368" spans="1:11">
       <c r="A368" s="4">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="B368" s="30" t="s">
         <v>414</v>
@@ -17987,7 +18088,7 @@
     </row>
     <row r="369" spans="1:11">
       <c r="A369" s="4">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="B369" s="30" t="s">
         <v>414</v>
@@ -18022,7 +18123,7 @@
     </row>
     <row r="370" spans="1:11">
       <c r="A370" s="4">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="B370" s="30" t="s">
         <v>414</v>
@@ -18057,7 +18158,7 @@
     </row>
     <row r="371" spans="1:11">
       <c r="A371" s="4">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="B371" s="30" t="s">
         <v>414</v>
@@ -18092,7 +18193,7 @@
     </row>
     <row r="372" spans="1:11">
       <c r="A372" s="4">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="B372" s="30" t="s">
         <v>414</v>
@@ -18127,7 +18228,7 @@
     </row>
     <row r="373" spans="1:11">
       <c r="A373" s="4">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="B373" s="30" t="s">
         <v>414</v>
@@ -18162,7 +18263,7 @@
     </row>
     <row r="374" spans="1:11">
       <c r="A374" s="4">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="B374" s="30" t="s">
         <v>414</v>
@@ -18197,7 +18298,7 @@
     </row>
     <row r="375" spans="1:11">
       <c r="A375" s="4">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="B375" s="30" t="s">
         <v>414</v>
@@ -18232,7 +18333,7 @@
     </row>
     <row r="376" spans="1:11">
       <c r="A376" s="4">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="B376" s="30" t="s">
         <v>414</v>
@@ -18267,7 +18368,7 @@
     </row>
     <row r="377" spans="1:11">
       <c r="A377" s="4">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="B377" s="30" t="s">
         <v>414</v>
@@ -18302,7 +18403,7 @@
     </row>
     <row r="378" spans="1:11">
       <c r="A378" s="4">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="B378" s="30" t="s">
         <v>414</v>
@@ -18337,7 +18438,7 @@
     </row>
     <row r="379" spans="1:11">
       <c r="A379" s="4">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="B379" s="30" t="s">
         <v>414</v>
@@ -18372,7 +18473,7 @@
     </row>
     <row r="380" spans="1:11">
       <c r="A380" s="4">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="B380" s="30" t="s">
         <v>414</v>
@@ -18407,7 +18508,7 @@
     </row>
     <row r="381" spans="1:11">
       <c r="A381" s="4">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="B381" s="30" t="s">
         <v>414</v>
@@ -18442,7 +18543,7 @@
     </row>
     <row r="382" spans="1:11">
       <c r="A382" s="4">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="B382" s="30" t="s">
         <v>414</v>
@@ -18477,7 +18578,7 @@
     </row>
     <row r="383" spans="1:11">
       <c r="A383" s="4">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="B383" s="30" t="s">
         <v>414</v>
@@ -18512,7 +18613,7 @@
     </row>
     <row r="384" spans="1:11">
       <c r="A384" s="4">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="B384" s="30" t="s">
         <v>414</v>
@@ -18547,7 +18648,7 @@
     </row>
     <row r="385" spans="1:11">
       <c r="A385" s="4">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="B385" s="30" t="s">
         <v>414</v>
@@ -18582,7 +18683,7 @@
     </row>
     <row r="386" spans="1:11">
       <c r="A386" s="4">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="B386" s="30" t="s">
         <v>414</v>
@@ -18617,7 +18718,7 @@
     </row>
     <row r="387" spans="1:11">
       <c r="A387" s="4">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="B387" s="30" t="s">
         <v>414</v>
@@ -18652,7 +18753,7 @@
     </row>
     <row r="388" spans="1:11">
       <c r="A388" s="4">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="B388" s="30" t="s">
         <v>414</v>
@@ -18687,7 +18788,7 @@
     </row>
     <row r="389" spans="1:11">
       <c r="A389" s="4">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="B389" s="30" t="s">
         <v>414</v>
@@ -18722,7 +18823,7 @@
     </row>
     <row r="390" spans="1:11">
       <c r="A390" s="4">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="B390" s="30" t="s">
         <v>414</v>
@@ -18757,7 +18858,7 @@
     </row>
     <row r="391" spans="1:11">
       <c r="A391" s="4">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="B391" s="30" t="s">
         <v>414</v>
@@ -18792,7 +18893,7 @@
     </row>
     <row r="392" spans="1:11">
       <c r="A392" s="4">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="B392" s="56" t="s">
         <v>1380</v>
@@ -18827,7 +18928,7 @@
     </row>
     <row r="393" spans="1:11">
       <c r="A393" s="4">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="B393" s="56" t="s">
         <v>1380</v>
@@ -18862,7 +18963,7 @@
     </row>
     <row r="394" spans="1:11">
       <c r="A394" s="4">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="B394" s="56" t="s">
         <v>1380</v>
@@ -18895,7 +18996,7 @@
     </row>
     <row r="395" spans="1:11">
       <c r="A395" s="4">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="B395" s="56" t="s">
         <v>1380</v>
@@ -18928,7 +19029,7 @@
     </row>
     <row r="396" spans="1:11">
       <c r="A396" s="4">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="B396" s="56" t="s">
         <v>1380</v>
@@ -18961,7 +19062,7 @@
     </row>
     <row r="397" spans="1:11">
       <c r="A397" s="4">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="B397" s="25" t="s">
         <v>712</v>
@@ -18996,7 +19097,7 @@
     </row>
     <row r="398" spans="1:11">
       <c r="A398" s="4">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="B398" s="25" t="s">
         <v>712</v>
@@ -19031,7 +19132,7 @@
     </row>
     <row r="399" spans="1:11">
       <c r="A399" s="4">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="B399" s="25" t="s">
         <v>712</v>
@@ -19066,7 +19167,7 @@
     </row>
     <row r="400" spans="1:11">
       <c r="A400" s="4">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="B400" s="25" t="s">
         <v>712</v>
@@ -19101,7 +19202,7 @@
     </row>
     <row r="401" spans="1:11">
       <c r="A401" s="4">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="B401" s="25" t="s">
         <v>712</v>
@@ -19136,7 +19237,7 @@
     </row>
     <row r="402" spans="1:11">
       <c r="A402" s="4">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="B402" s="25" t="s">
         <v>712</v>
@@ -19171,7 +19272,7 @@
     </row>
     <row r="403" spans="1:11">
       <c r="A403" s="4">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="B403" s="25" t="s">
         <v>712</v>
@@ -19206,7 +19307,7 @@
     </row>
     <row r="404" spans="1:11">
       <c r="A404" s="4">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="B404" s="25" t="s">
         <v>712</v>
@@ -19241,7 +19342,7 @@
     </row>
     <row r="405" spans="1:11">
       <c r="A405" s="4">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="B405" s="25" t="s">
         <v>712</v>
@@ -19276,7 +19377,7 @@
     </row>
     <row r="406" spans="1:11">
       <c r="A406" s="4">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="B406" s="25" t="s">
         <v>712</v>
@@ -19311,7 +19412,7 @@
     </row>
     <row r="407" spans="1:11">
       <c r="A407" s="4">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="B407" s="25" t="s">
         <v>712</v>
@@ -19346,7 +19447,7 @@
     </row>
     <row r="408" spans="1:11">
       <c r="A408" s="4">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="B408" s="25" t="s">
         <v>712</v>
@@ -19381,7 +19482,7 @@
     </row>
     <row r="409" spans="1:11">
       <c r="A409" s="4">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="B409" s="25" t="s">
         <v>712</v>
@@ -19416,7 +19517,7 @@
     </row>
     <row r="410" spans="1:11">
       <c r="A410" s="4">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="B410" s="26" t="s">
         <v>712</v>
@@ -19451,7 +19552,7 @@
     </row>
     <row r="411" spans="1:11">
       <c r="A411" s="4">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="B411" s="27" t="s">
         <v>38</v>
@@ -19484,7 +19585,7 @@
     </row>
     <row r="412" spans="1:11">
       <c r="A412" s="4">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="B412" s="27" t="s">
         <v>38</v>
@@ -19519,7 +19620,7 @@
     </row>
     <row r="413" spans="1:11">
       <c r="A413" s="4">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="B413" s="27" t="s">
         <v>38</v>
@@ -19554,7 +19655,7 @@
     </row>
     <row r="414" spans="1:11">
       <c r="A414" s="4">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="B414" s="27" t="s">
         <v>38</v>
@@ -19589,7 +19690,7 @@
     </row>
     <row r="415" spans="1:11">
       <c r="A415" s="4">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="B415" s="27" t="s">
         <v>38</v>
@@ -19624,7 +19725,7 @@
     </row>
     <row r="416" spans="1:11">
       <c r="A416" s="4">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="B416" s="27" t="s">
         <v>38</v>
@@ -19657,7 +19758,7 @@
     </row>
     <row r="417" spans="1:11">
       <c r="A417" s="4">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="B417" s="27" t="s">
         <v>38</v>
@@ -19692,7 +19793,7 @@
     </row>
     <row r="418" spans="1:11">
       <c r="A418" s="4">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="B418" s="27" t="s">
         <v>38</v>
@@ -19727,7 +19828,7 @@
     </row>
     <row r="419" spans="1:11">
       <c r="A419" s="4">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="B419" s="27" t="s">
         <v>38</v>
@@ -19762,7 +19863,7 @@
     </row>
     <row r="420" spans="1:11">
       <c r="A420" s="4">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="B420" s="28" t="s">
         <v>735</v>
@@ -19797,7 +19898,7 @@
     </row>
     <row r="421" spans="1:11">
       <c r="A421" s="4">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="B421" s="28" t="s">
         <v>735</v>
@@ -19832,7 +19933,7 @@
     </row>
     <row r="422" spans="1:11">
       <c r="A422" s="4">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="B422" s="28" t="s">
         <v>735</v>
@@ -19867,7 +19968,7 @@
     </row>
     <row r="423" spans="1:11">
       <c r="A423" s="4">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="B423" s="28" t="s">
         <v>735</v>
@@ -19902,7 +20003,7 @@
     </row>
     <row r="424" spans="1:11">
       <c r="A424" s="4">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="B424" s="28" t="s">
         <v>735</v>
@@ -19937,7 +20038,7 @@
     </row>
     <row r="425" spans="1:11">
       <c r="A425" s="4">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="B425" s="28" t="s">
         <v>735</v>
@@ -19972,7 +20073,7 @@
     </row>
     <row r="426" spans="1:11">
       <c r="A426" s="4">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="B426" s="28" t="s">
         <v>735</v>
@@ -20007,7 +20108,7 @@
     </row>
     <row r="427" spans="1:11">
       <c r="A427" s="4">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="B427" s="28" t="s">
         <v>735</v>
@@ -20042,7 +20143,7 @@
     </row>
     <row r="428" spans="1:11">
       <c r="A428" s="4">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="B428" s="28" t="s">
         <v>735</v>
@@ -20077,7 +20178,7 @@
     </row>
     <row r="429" spans="1:11">
       <c r="A429" s="4">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="B429" s="28" t="s">
         <v>735</v>
@@ -20112,7 +20213,7 @@
     </row>
     <row r="430" spans="1:11">
       <c r="A430" s="4">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="B430" s="28" t="s">
         <v>735</v>
@@ -20147,7 +20248,7 @@
     </row>
     <row r="431" spans="1:11">
       <c r="A431" s="4">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="B431" s="28" t="s">
         <v>735</v>
@@ -20182,7 +20283,7 @@
     </row>
     <row r="432" spans="1:11">
       <c r="A432" s="4">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="B432" s="28" t="s">
         <v>735</v>
@@ -20217,7 +20318,7 @@
     </row>
     <row r="433" spans="1:11">
       <c r="A433" s="4">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="B433" s="28" t="s">
         <v>735</v>
@@ -20252,7 +20353,7 @@
     </row>
     <row r="434" spans="1:11">
       <c r="A434" s="4">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="B434" s="28" t="s">
         <v>735</v>
@@ -20261,19 +20362,19 @@
         <v>11</v>
       </c>
       <c r="D434" s="2" t="s">
-        <v>1360</v>
+        <v>1402</v>
       </c>
       <c r="E434" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F434" s="1" t="s">
-        <v>521</v>
+        <v>1405</v>
       </c>
       <c r="G434" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H434" s="1" t="s">
-        <v>1361</v>
+        <v>1349</v>
       </c>
       <c r="I434" s="54">
         <v>46279</v>
@@ -20285,7 +20386,7 @@
     </row>
     <row r="435" spans="1:11">
       <c r="A435" s="4">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="B435" s="28" t="s">
         <v>735</v>
@@ -20294,19 +20395,19 @@
         <v>11</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>1360</v>
+        <v>1399</v>
       </c>
       <c r="E435" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F435" s="1" t="s">
-        <v>521</v>
+        <v>1398</v>
       </c>
       <c r="G435" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H435" s="1" t="s">
-        <v>1361</v>
+        <v>1349</v>
       </c>
       <c r="I435" s="54">
         <v>46279</v>
@@ -20318,7 +20419,7 @@
     </row>
     <row r="436" spans="1:11">
       <c r="A436" s="4">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="B436" s="28" t="s">
         <v>735</v>
@@ -20327,19 +20428,19 @@
         <v>11</v>
       </c>
       <c r="D436" s="2" t="s">
-        <v>1360</v>
+        <v>1407</v>
       </c>
       <c r="E436" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F436" s="1" t="s">
-        <v>521</v>
+        <v>1406</v>
       </c>
       <c r="G436" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H436" s="1" t="s">
-        <v>1361</v>
+        <v>1349</v>
       </c>
       <c r="I436" s="54">
         <v>46279</v>
@@ -20351,7 +20452,7 @@
     </row>
     <row r="437" spans="1:11">
       <c r="A437" s="4">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="B437" s="28" t="s">
         <v>735</v>
@@ -20360,19 +20461,19 @@
         <v>11</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>1360</v>
+        <v>1409</v>
       </c>
       <c r="E437" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F437" s="1" t="s">
-        <v>521</v>
+        <v>1408</v>
       </c>
       <c r="G437" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H437" s="1" t="s">
-        <v>1361</v>
+        <v>1349</v>
       </c>
       <c r="I437" s="54">
         <v>46279</v>
@@ -20384,7 +20485,7 @@
     </row>
     <row r="438" spans="1:11">
       <c r="A438" s="4">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="B438" s="28" t="s">
         <v>735</v>
@@ -20393,19 +20494,19 @@
         <v>11</v>
       </c>
       <c r="D438" s="2" t="s">
-        <v>1360</v>
+        <v>1404</v>
       </c>
       <c r="E438" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F438" s="1" t="s">
-        <v>521</v>
+        <v>1410</v>
       </c>
       <c r="G438" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H438" s="1" t="s">
-        <v>1361</v>
+        <v>1349</v>
       </c>
       <c r="I438" s="54">
         <v>46279</v>
@@ -20417,7 +20518,7 @@
     </row>
     <row r="439" spans="1:11">
       <c r="A439" s="4">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="B439" s="28" t="s">
         <v>735</v>
@@ -20426,19 +20527,19 @@
         <v>11</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>1360</v>
+        <v>1412</v>
       </c>
       <c r="E439" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F439" s="1" t="s">
-        <v>521</v>
+        <v>1411</v>
       </c>
       <c r="G439" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H439" s="1" t="s">
-        <v>1361</v>
+        <v>1349</v>
       </c>
       <c r="I439" s="54">
         <v>46279</v>
@@ -20450,7 +20551,7 @@
     </row>
     <row r="440" spans="1:11">
       <c r="A440" s="4">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="B440" s="28" t="s">
         <v>735</v>
@@ -20459,19 +20560,19 @@
         <v>11</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>1360</v>
+        <v>1413</v>
       </c>
       <c r="E440" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F440" s="1" t="s">
-        <v>521</v>
+        <v>1414</v>
       </c>
       <c r="G440" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H440" s="1" t="s">
-        <v>1361</v>
+        <v>1349</v>
       </c>
       <c r="I440" s="54">
         <v>46279</v>
@@ -20483,7 +20584,7 @@
     </row>
     <row r="441" spans="1:11">
       <c r="A441" s="4">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="B441" s="28" t="s">
         <v>735</v>
@@ -20492,19 +20593,19 @@
         <v>11</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>1360</v>
+        <v>1415</v>
       </c>
       <c r="E441" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F441" s="1" t="s">
-        <v>521</v>
+        <v>1416</v>
       </c>
       <c r="G441" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H441" s="1" t="s">
-        <v>1361</v>
+        <v>1349</v>
       </c>
       <c r="I441" s="54">
         <v>46279</v>
@@ -20516,7 +20617,7 @@
     </row>
     <row r="442" spans="1:11">
       <c r="A442" s="4">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="B442" s="28" t="s">
         <v>735</v>
@@ -20525,19 +20626,19 @@
         <v>11</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>1360</v>
+        <v>1400</v>
       </c>
       <c r="E442" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F442" s="1" t="s">
-        <v>521</v>
+        <v>1417</v>
       </c>
       <c r="G442" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H442" s="1" t="s">
-        <v>1361</v>
+        <v>1435</v>
       </c>
       <c r="I442" s="54">
         <v>46279</v>
@@ -20549,7 +20650,7 @@
     </row>
     <row r="443" spans="1:11">
       <c r="A443" s="4">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="B443" s="28" t="s">
         <v>735</v>
@@ -20558,19 +20659,19 @@
         <v>11</v>
       </c>
       <c r="D443" s="2" t="s">
-        <v>1360</v>
+        <v>1427</v>
       </c>
       <c r="E443" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F443" s="1" t="s">
-        <v>521</v>
+        <v>1418</v>
       </c>
       <c r="G443" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H443" s="1" t="s">
-        <v>1361</v>
+        <v>1435</v>
       </c>
       <c r="I443" s="54">
         <v>46279</v>
@@ -20582,7 +20683,7 @@
     </row>
     <row r="444" spans="1:11">
       <c r="A444" s="4">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="B444" s="28" t="s">
         <v>735</v>
@@ -20591,19 +20692,19 @@
         <v>11</v>
       </c>
       <c r="D444" s="2" t="s">
-        <v>1360</v>
+        <v>1428</v>
       </c>
       <c r="E444" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F444" s="1" t="s">
-        <v>521</v>
+        <v>1419</v>
       </c>
       <c r="G444" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H444" s="1" t="s">
-        <v>1361</v>
+        <v>1435</v>
       </c>
       <c r="I444" s="54">
         <v>46279</v>
@@ -20615,7 +20716,7 @@
     </row>
     <row r="445" spans="1:11">
       <c r="A445" s="4">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="B445" s="28" t="s">
         <v>735</v>
@@ -20624,19 +20725,19 @@
         <v>11</v>
       </c>
       <c r="D445" s="2" t="s">
-        <v>1360</v>
+        <v>1429</v>
       </c>
       <c r="E445" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F445" s="1" t="s">
-        <v>521</v>
+        <v>1420</v>
       </c>
       <c r="G445" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H445" s="1" t="s">
-        <v>1361</v>
+        <v>1435</v>
       </c>
       <c r="I445" s="54">
         <v>46279</v>
@@ -20648,7 +20749,7 @@
     </row>
     <row r="446" spans="1:11">
       <c r="A446" s="4">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="B446" s="28" t="s">
         <v>735</v>
@@ -20657,19 +20758,19 @@
         <v>11</v>
       </c>
       <c r="D446" s="2" t="s">
-        <v>1360</v>
+        <v>1430</v>
       </c>
       <c r="E446" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F446" s="1" t="s">
-        <v>521</v>
+        <v>1421</v>
       </c>
       <c r="G446" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H446" s="1" t="s">
-        <v>1361</v>
+        <v>1435</v>
       </c>
       <c r="I446" s="54">
         <v>46279</v>
@@ -20681,7 +20782,7 @@
     </row>
     <row r="447" spans="1:11">
       <c r="A447" s="4">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="B447" s="28" t="s">
         <v>735</v>
@@ -20690,19 +20791,19 @@
         <v>11</v>
       </c>
       <c r="D447" s="2" t="s">
-        <v>1360</v>
+        <v>1431</v>
       </c>
       <c r="E447" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F447" s="1" t="s">
-        <v>521</v>
+        <v>1422</v>
       </c>
       <c r="G447" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H447" s="1" t="s">
-        <v>1361</v>
+        <v>1435</v>
       </c>
       <c r="I447" s="54">
         <v>46279</v>
@@ -20714,7 +20815,7 @@
     </row>
     <row r="448" spans="1:11">
       <c r="A448" s="4">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="B448" s="28" t="s">
         <v>735</v>
@@ -20723,19 +20824,19 @@
         <v>11</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>1360</v>
+        <v>1401</v>
       </c>
       <c r="E448" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F448" s="1" t="s">
-        <v>521</v>
+        <v>1423</v>
       </c>
       <c r="G448" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H448" s="1" t="s">
-        <v>1361</v>
+        <v>1435</v>
       </c>
       <c r="I448" s="54">
         <v>46279</v>
@@ -20747,7 +20848,7 @@
     </row>
     <row r="449" spans="1:11">
       <c r="A449" s="4">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="B449" s="28" t="s">
         <v>735</v>
@@ -20756,19 +20857,19 @@
         <v>11</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>1360</v>
+        <v>1432</v>
       </c>
       <c r="E449" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F449" s="1" t="s">
-        <v>521</v>
+        <v>1424</v>
       </c>
       <c r="G449" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H449" s="1" t="s">
-        <v>1361</v>
+        <v>1435</v>
       </c>
       <c r="I449" s="54">
         <v>46279</v>
@@ -20780,7 +20881,7 @@
     </row>
     <row r="450" spans="1:11">
       <c r="A450" s="4">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="B450" s="28" t="s">
         <v>735</v>
@@ -20789,19 +20890,19 @@
         <v>11</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>1360</v>
+        <v>1437</v>
       </c>
       <c r="E450" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F450" s="1" t="s">
-        <v>521</v>
+        <v>1425</v>
       </c>
       <c r="G450" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H450" s="1" t="s">
-        <v>1361</v>
+        <v>1435</v>
       </c>
       <c r="I450" s="54">
         <v>46279</v>
@@ -20813,7 +20914,7 @@
     </row>
     <row r="451" spans="1:11">
       <c r="A451" s="4">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="B451" s="28" t="s">
         <v>735</v>
@@ -20822,19 +20923,19 @@
         <v>11</v>
       </c>
       <c r="D451" s="2" t="s">
-        <v>1360</v>
+        <v>1403</v>
       </c>
       <c r="E451" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F451" s="1" t="s">
-        <v>521</v>
+        <v>1426</v>
       </c>
       <c r="G451" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H451" s="1" t="s">
-        <v>1361</v>
+        <v>1435</v>
       </c>
       <c r="I451" s="54">
         <v>46279</v>
@@ -20846,7 +20947,7 @@
     </row>
     <row r="452" spans="1:11">
       <c r="A452" s="4">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="B452" s="28" t="s">
         <v>735</v>
@@ -20855,19 +20956,19 @@
         <v>11</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>1360</v>
+        <v>1436</v>
       </c>
       <c r="E452" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F452" s="1" t="s">
-        <v>521</v>
+        <v>1434</v>
       </c>
       <c r="G452" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H452" s="1" t="s">
-        <v>1361</v>
+        <v>1435</v>
       </c>
       <c r="I452" s="54">
         <v>46279</v>
@@ -20879,7 +20980,7 @@
     </row>
     <row r="453" spans="1:11">
       <c r="A453" s="4">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="B453" s="28" t="s">
         <v>735</v>
@@ -20888,16 +20989,16 @@
         <v>11</v>
       </c>
       <c r="D453" s="2" t="s">
-        <v>1360</v>
+        <v>1433</v>
       </c>
       <c r="E453" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F453" s="1" t="s">
-        <v>521</v>
+        <v>1397</v>
       </c>
       <c r="G453" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H453" s="1" t="s">
         <v>1361</v>
@@ -20912,7 +21013,7 @@
     </row>
     <row r="454" spans="1:11">
       <c r="A454" s="4">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="B454" s="29" t="s">
         <v>736</v>
@@ -20945,7 +21046,7 @@
     </row>
     <row r="455" spans="1:11">
       <c r="A455" s="4">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="B455" s="29" t="s">
         <v>736</v>
@@ -20978,7 +21079,7 @@
     </row>
     <row r="456" spans="1:11">
       <c r="A456" s="4">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="B456" s="29" t="s">
         <v>736</v>
@@ -21011,7 +21112,7 @@
     </row>
     <row r="457" spans="1:11">
       <c r="A457" s="4">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="B457" s="29" t="s">
         <v>736</v>
@@ -21044,7 +21145,7 @@
     </row>
     <row r="458" spans="1:11">
       <c r="A458" s="4">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="B458" s="29" t="s">
         <v>736</v>
@@ -21077,7 +21178,7 @@
     </row>
     <row r="459" spans="1:11">
       <c r="A459" s="4">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="B459" s="29" t="s">
         <v>736</v>
@@ -21110,7 +21211,7 @@
     </row>
     <row r="460" spans="1:11">
       <c r="A460" s="4">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="B460" s="29" t="s">
         <v>736</v>
@@ -21143,7 +21244,7 @@
     </row>
     <row r="461" spans="1:11">
       <c r="A461" s="4">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B461" s="29" t="s">
         <v>736</v>
@@ -21176,7 +21277,7 @@
     </row>
     <row r="462" spans="1:11">
       <c r="A462" s="4">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="B462" s="29" t="s">
         <v>736</v>
@@ -21209,7 +21310,7 @@
     </row>
     <row r="463" spans="1:11">
       <c r="A463" s="4">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="B463" s="29" t="s">
         <v>736</v>
@@ -21242,7 +21343,7 @@
     </row>
     <row r="464" spans="1:11">
       <c r="A464" s="4">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="B464" s="29" t="s">
         <v>736</v>
@@ -21275,7 +21376,7 @@
     </row>
     <row r="465" spans="1:11">
       <c r="A465" s="4">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="B465" s="29" t="s">
         <v>736</v>
@@ -21308,7 +21409,7 @@
     </row>
     <row r="466" spans="1:11">
       <c r="A466" s="4">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="B466" s="29" t="s">
         <v>736</v>
@@ -21341,7 +21442,7 @@
     </row>
     <row r="467" spans="1:11">
       <c r="A467" s="4">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="B467" s="29" t="s">
         <v>736</v>
@@ -21374,7 +21475,7 @@
     </row>
     <row r="468" spans="1:11">
       <c r="A468" s="4">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="B468" s="29" t="s">
         <v>736</v>
@@ -21407,7 +21508,7 @@
     </row>
     <row r="469" spans="1:11">
       <c r="A469" s="4">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="B469" s="29" t="s">
         <v>736</v>
@@ -21440,7 +21541,7 @@
     </row>
     <row r="470" spans="1:11">
       <c r="A470" s="4">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="B470" s="29" t="s">
         <v>736</v>
@@ -21472,7 +21573,9 @@
       <c r="K470" s="55"/>
     </row>
     <row r="471" spans="1:11">
-      <c r="A471" s="60"/>
+      <c r="A471" s="4">
+        <v>470</v>
+      </c>
       <c r="B471" s="29" t="s">
         <v>736</v>
       </c>
@@ -21494,17 +21597,17 @@
       <c r="H471" s="1" t="s">
         <v>1361</v>
       </c>
-      <c r="I471" s="61">
+      <c r="I471" s="54">
         <v>46288</v>
       </c>
-      <c r="J471" s="63" t="s">
-        <v>574</v>
-      </c>
-      <c r="K471" s="62"/>
+      <c r="J471" s="9" t="s">
+        <v>574</v>
+      </c>
+      <c r="K471" s="55"/>
     </row>
     <row r="472" spans="1:11">
       <c r="A472" s="4">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="B472" s="29" t="s">
         <v>736</v>
@@ -21537,7 +21640,7 @@
     </row>
     <row r="473" spans="1:11">
       <c r="A473" s="4">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="B473" s="29" t="s">
         <v>736</v>
@@ -21572,7 +21675,7 @@
     </row>
     <row r="474" spans="1:11">
       <c r="A474" s="4">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="B474" s="29" t="s">
         <v>736</v>
@@ -21607,7 +21710,7 @@
     </row>
     <row r="475" spans="1:11">
       <c r="A475" s="4">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="B475" s="29" t="s">
         <v>736</v>
@@ -21642,7 +21745,7 @@
     </row>
     <row r="476" spans="1:11">
       <c r="A476" s="4">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="B476" s="29" t="s">
         <v>736</v>
@@ -21677,7 +21780,7 @@
     </row>
     <row r="477" spans="1:11">
       <c r="A477" s="4">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="B477" s="29" t="s">
         <v>736</v>
@@ -21712,7 +21815,7 @@
     </row>
     <row r="478" spans="1:11">
       <c r="A478" s="4">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="B478" s="29" t="s">
         <v>736</v>
@@ -21747,7 +21850,7 @@
     </row>
     <row r="479" spans="1:11">
       <c r="A479" s="4">
-        <v>467</v>
+        <v>478</v>
       </c>
       <c r="B479" s="29" t="s">
         <v>736</v>
@@ -21782,7 +21885,7 @@
     </row>
     <row r="480" spans="1:11">
       <c r="A480" s="4">
-        <v>468</v>
+        <v>479</v>
       </c>
       <c r="B480" s="29" t="s">
         <v>736</v>
@@ -21817,7 +21920,7 @@
     </row>
     <row r="481" spans="1:11">
       <c r="A481" s="4">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="B481" s="29" t="s">
         <v>736</v>
@@ -21852,7 +21955,7 @@
     </row>
     <row r="482" spans="1:11">
       <c r="A482" s="4">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="B482" s="29" t="s">
         <v>736</v>
@@ -21887,7 +21990,7 @@
     </row>
     <row r="483" spans="1:11">
       <c r="A483" s="4">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="B483" s="29" t="s">
         <v>736</v>
@@ -21922,7 +22025,7 @@
     </row>
     <row r="484" spans="1:11">
       <c r="A484" s="4">
-        <v>472</v>
+        <v>483</v>
       </c>
       <c r="B484" s="29" t="s">
         <v>736</v>
@@ -21957,7 +22060,7 @@
     </row>
     <row r="485" spans="1:11">
       <c r="A485" s="4">
-        <v>473</v>
+        <v>484</v>
       </c>
       <c r="B485" s="29" t="s">
         <v>736</v>
@@ -21992,7 +22095,7 @@
     </row>
     <row r="486" spans="1:11">
       <c r="A486" s="4">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="B486" s="29" t="s">
         <v>736</v>
@@ -22027,7 +22130,7 @@
     </row>
     <row r="487" spans="1:11">
       <c r="A487" s="4">
-        <v>475</v>
+        <v>486</v>
       </c>
       <c r="B487" s="29" t="s">
         <v>736</v>
@@ -22062,7 +22165,7 @@
     </row>
     <row r="488" spans="1:11">
       <c r="A488" s="4">
-        <v>476</v>
+        <v>487</v>
       </c>
       <c r="B488" s="29" t="s">
         <v>736</v>
@@ -22097,7 +22200,7 @@
     </row>
     <row r="489" spans="1:11">
       <c r="A489" s="4">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="B489" s="29" t="s">
         <v>736</v>
@@ -22132,7 +22235,7 @@
     </row>
     <row r="490" spans="1:11">
       <c r="A490" s="4">
-        <v>478</v>
+        <v>489</v>
       </c>
       <c r="B490" s="29" t="s">
         <v>736</v>
@@ -22165,7 +22268,7 @@
     </row>
     <row r="491" spans="1:11">
       <c r="A491" s="4">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="B491" s="29" t="s">
         <v>736</v>
@@ -22200,7 +22303,7 @@
     </row>
     <row r="492" spans="1:11">
       <c r="A492" s="4">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="B492" s="40" t="s">
         <v>849</v>
@@ -22235,7 +22338,7 @@
     </row>
     <row r="493" spans="1:11">
       <c r="A493" s="4">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="B493" s="40" t="s">
         <v>849</v>
@@ -22270,7 +22373,7 @@
     </row>
     <row r="494" spans="1:11">
       <c r="A494" s="4">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="B494" s="40" t="s">
         <v>849</v>
@@ -22305,7 +22408,7 @@
     </row>
     <row r="495" spans="1:11">
       <c r="A495" s="4">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="B495" s="40" t="s">
         <v>849</v>
@@ -22340,7 +22443,7 @@
     </row>
     <row r="496" spans="1:11">
       <c r="A496" s="4">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="B496" s="40" t="s">
         <v>849</v>
@@ -22375,7 +22478,7 @@
     </row>
     <row r="497" spans="1:11">
       <c r="A497" s="4">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="B497" s="31" t="s">
         <v>835</v>
@@ -22410,7 +22513,7 @@
     </row>
     <row r="498" spans="1:11">
       <c r="A498" s="4">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="B498" s="31" t="s">
         <v>835</v>
@@ -22445,7 +22548,7 @@
     </row>
     <row r="499" spans="1:11">
       <c r="A499" s="4">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="B499" s="31" t="s">
         <v>835</v>
@@ -22480,7 +22583,7 @@
     </row>
     <row r="500" spans="1:11">
       <c r="A500" s="4">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="B500" s="31" t="s">
         <v>835</v>
@@ -22515,7 +22618,7 @@
     </row>
     <row r="501" spans="1:11">
       <c r="A501" s="4">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="B501" s="31" t="s">
         <v>835</v>
@@ -22550,7 +22653,7 @@
     </row>
     <row r="502" spans="1:11">
       <c r="A502" s="4">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="B502" s="52" t="s">
         <v>643</v>
@@ -22583,7 +22686,7 @@
     </row>
     <row r="503" spans="1:11">
       <c r="A503" s="4">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="B503" s="53" t="s">
         <v>1062</v>
@@ -22618,7 +22721,7 @@
     </row>
     <row r="504" spans="1:11">
       <c r="A504" s="4">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="B504" s="53" t="s">
         <v>1062</v>
@@ -22651,7 +22754,7 @@
     </row>
     <row r="505" spans="1:11">
       <c r="A505" s="4">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="B505" s="53" t="s">
         <v>1062</v>
@@ -22684,7 +22787,7 @@
     </row>
     <row r="506" spans="1:11">
       <c r="A506" s="4">
-        <v>494</v>
+        <v>505</v>
       </c>
       <c r="B506" s="53" t="s">
         <v>1062</v>
@@ -22717,7 +22820,7 @@
     </row>
     <row r="507" spans="1:11">
       <c r="A507" s="4">
-        <v>495</v>
+        <v>506</v>
       </c>
       <c r="B507" s="53" t="s">
         <v>1062</v>
@@ -22750,7 +22853,7 @@
     </row>
     <row r="508" spans="1:11">
       <c r="A508" s="4">
-        <v>496</v>
+        <v>507</v>
       </c>
       <c r="B508" s="53" t="s">
         <v>1062</v>
@@ -22783,7 +22886,7 @@
     </row>
     <row r="509" spans="1:11">
       <c r="A509" s="4">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="B509" s="53" t="s">
         <v>1062</v>
@@ -22816,7 +22919,7 @@
     </row>
     <row r="510" spans="1:11">
       <c r="A510" s="4">
-        <v>498</v>
+        <v>509</v>
       </c>
       <c r="B510" s="53" t="s">
         <v>1062</v>
@@ -22849,7 +22952,7 @@
     </row>
     <row r="511" spans="1:11">
       <c r="A511" s="4">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="B511" s="53" t="s">
         <v>1062</v>
@@ -22882,7 +22985,7 @@
     </row>
     <row r="512" spans="1:11">
       <c r="A512" s="4">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="B512" s="53" t="s">
         <v>1062</v>
@@ -22915,7 +23018,7 @@
     </row>
     <row r="513" spans="1:11">
       <c r="A513" s="4">
-        <v>501</v>
+        <v>512</v>
       </c>
       <c r="B513" s="53" t="s">
         <v>1062</v>
@@ -22948,7 +23051,7 @@
     </row>
     <row r="514" spans="1:11">
       <c r="A514" s="4">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B514" s="53" t="s">
         <v>1062</v>
@@ -22981,7 +23084,7 @@
     </row>
     <row r="515" spans="1:11">
       <c r="A515" s="4">
-        <v>503</v>
+        <v>514</v>
       </c>
       <c r="B515" s="53" t="s">
         <v>1062</v>
@@ -23014,7 +23117,7 @@
     </row>
     <row r="516" spans="1:11">
       <c r="A516" s="4">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="B516" s="53" t="s">
         <v>1062</v>
@@ -23047,7 +23150,7 @@
     </row>
     <row r="517" spans="1:11">
       <c r="A517" s="4">
-        <v>505</v>
+        <v>516</v>
       </c>
       <c r="B517" s="53" t="s">
         <v>1062</v>
@@ -23080,7 +23183,7 @@
     </row>
     <row r="518" spans="1:11">
       <c r="A518" s="4">
-        <v>506</v>
+        <v>517</v>
       </c>
       <c r="B518" s="52" t="s">
         <v>1063</v>
@@ -23115,7 +23218,7 @@
     </row>
     <row r="519" spans="1:11">
       <c r="A519" s="4">
-        <v>507</v>
+        <v>518</v>
       </c>
       <c r="B519" s="52" t="s">
         <v>1063</v>
@@ -23148,7 +23251,7 @@
     </row>
     <row r="520" spans="1:11">
       <c r="A520" s="4">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="B520" s="52" t="s">
         <v>1063</v>
@@ -23181,7 +23284,7 @@
     </row>
     <row r="521" spans="1:11">
       <c r="A521" s="4">
-        <v>509</v>
+        <v>520</v>
       </c>
       <c r="B521" s="52" t="s">
         <v>1063</v>
@@ -23216,7 +23319,7 @@
     </row>
     <row r="522" spans="1:11">
       <c r="A522" s="4">
-        <v>510</v>
+        <v>521</v>
       </c>
       <c r="B522" s="52" t="s">
         <v>1063</v>
@@ -23249,7 +23352,7 @@
     </row>
     <row r="523" spans="1:11">
       <c r="A523" s="4">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="B523" s="52" t="s">
         <v>1063</v>
@@ -23282,7 +23385,7 @@
     </row>
     <row r="524" spans="1:11">
       <c r="A524" s="4">
-        <v>512</v>
+        <v>523</v>
       </c>
       <c r="B524" s="52" t="s">
         <v>1063</v>
@@ -23315,7 +23418,7 @@
     </row>
     <row r="525" spans="1:11">
       <c r="A525" s="4">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="B525" s="52" t="s">
         <v>1063</v>
@@ -23350,7 +23453,7 @@
     </row>
     <row r="526" spans="1:11">
       <c r="A526" s="4">
-        <v>514</v>
+        <v>525</v>
       </c>
       <c r="B526" s="52" t="s">
         <v>1063</v>
@@ -23383,7 +23486,7 @@
     </row>
     <row r="527" spans="1:11">
       <c r="A527" s="4">
-        <v>515</v>
+        <v>526</v>
       </c>
       <c r="B527" s="52" t="s">
         <v>1063</v>
@@ -23416,7 +23519,7 @@
     </row>
     <row r="528" spans="1:11">
       <c r="A528" s="4">
-        <v>516</v>
+        <v>527</v>
       </c>
       <c r="B528" s="52" t="s">
         <v>1063</v>
@@ -23449,7 +23552,7 @@
     </row>
     <row r="529" spans="1:11">
       <c r="A529" s="4">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="B529" s="52" t="s">
         <v>1063</v>
@@ -23482,7 +23585,7 @@
     </row>
     <row r="530" spans="1:11">
       <c r="A530" s="4">
-        <v>518</v>
+        <v>529</v>
       </c>
       <c r="B530" s="52" t="s">
         <v>1063</v>
@@ -23515,7 +23618,7 @@
     </row>
     <row r="531" spans="1:11">
       <c r="A531" s="4">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="B531" s="52" t="s">
         <v>1063</v>
@@ -23548,7 +23651,7 @@
     </row>
     <row r="532" spans="1:11">
       <c r="A532" s="4">
-        <v>520</v>
+        <v>531</v>
       </c>
       <c r="B532" s="52" t="s">
         <v>1063</v>
@@ -23581,7 +23684,7 @@
     </row>
     <row r="533" spans="1:11">
       <c r="A533" s="4">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="B533" s="52" t="s">
         <v>1063</v>
@@ -23614,7 +23717,7 @@
     </row>
     <row r="534" spans="1:11">
       <c r="A534" s="4">
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="B534" s="52" t="s">
         <v>1063</v>
@@ -23647,7 +23750,7 @@
     </row>
     <row r="535" spans="1:11">
       <c r="A535" s="4">
-        <v>523</v>
+        <v>534</v>
       </c>
       <c r="B535" s="52" t="s">
         <v>1063</v>
@@ -23680,7 +23783,7 @@
     </row>
     <row r="536" spans="1:11">
       <c r="A536" s="4">
-        <v>524</v>
+        <v>535</v>
       </c>
       <c r="B536" s="52" t="s">
         <v>1063</v>
@@ -23713,7 +23816,7 @@
     </row>
     <row r="537" spans="1:11">
       <c r="A537" s="4">
-        <v>525</v>
+        <v>536</v>
       </c>
       <c r="B537" s="52" t="s">
         <v>1063</v>
@@ -23746,7 +23849,7 @@
     </row>
     <row r="538" spans="1:11">
       <c r="A538" s="4">
-        <v>526</v>
+        <v>537</v>
       </c>
       <c r="B538" s="52" t="s">
         <v>1063</v>
@@ -23781,7 +23884,7 @@
     </row>
     <row r="539" spans="1:11">
       <c r="A539" s="4">
-        <v>527</v>
+        <v>538</v>
       </c>
       <c r="B539" s="52" t="s">
         <v>1063</v>
@@ -23814,7 +23917,7 @@
     </row>
     <row r="540" spans="1:11">
       <c r="A540" s="4">
-        <v>528</v>
+        <v>539</v>
       </c>
       <c r="B540" s="52" t="s">
         <v>1063</v>
@@ -23847,7 +23950,7 @@
     </row>
     <row r="541" spans="1:11">
       <c r="A541" s="4">
-        <v>529</v>
+        <v>540</v>
       </c>
       <c r="B541" s="52" t="s">
         <v>1063</v>
@@ -23880,7 +23983,7 @@
     </row>
     <row r="542" spans="1:11">
       <c r="A542" s="4">
-        <v>530</v>
+        <v>541</v>
       </c>
       <c r="B542" s="52" t="s">
         <v>1063</v>
@@ -23913,7 +24016,7 @@
     </row>
     <row r="543" spans="1:11">
       <c r="A543" s="4">
-        <v>531</v>
+        <v>542</v>
       </c>
       <c r="B543" s="52" t="s">
         <v>1063</v>
@@ -23946,7 +24049,7 @@
     </row>
     <row r="544" spans="1:11">
       <c r="A544" s="4">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c r="B544" s="52" t="s">
         <v>1063</v>
@@ -23979,7 +24082,7 @@
     </row>
     <row r="545" spans="1:11">
       <c r="A545" s="4">
-        <v>533</v>
+        <v>544</v>
       </c>
       <c r="B545" s="52" t="s">
         <v>1063</v>
@@ -24012,7 +24115,7 @@
     </row>
     <row r="546" spans="1:11">
       <c r="A546" s="4">
-        <v>534</v>
+        <v>545</v>
       </c>
       <c r="B546" s="52" t="s">
         <v>1063</v>
@@ -24045,7 +24148,7 @@
     </row>
     <row r="547" spans="1:11">
       <c r="A547" s="4">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="B547" s="52" t="s">
         <v>1063</v>
@@ -24078,7 +24181,7 @@
     </row>
     <row r="548" spans="1:11">
       <c r="A548" s="4">
-        <v>536</v>
+        <v>547</v>
       </c>
       <c r="B548" s="52" t="s">
         <v>1063</v>
@@ -24113,7 +24216,7 @@
     </row>
     <row r="549" spans="1:11">
       <c r="A549" s="4">
-        <v>537</v>
+        <v>548</v>
       </c>
       <c r="B549" s="52" t="s">
         <v>1063</v>
@@ -24146,7 +24249,7 @@
     </row>
     <row r="550" spans="1:11">
       <c r="A550" s="4">
-        <v>538</v>
+        <v>549</v>
       </c>
       <c r="B550" s="52" t="s">
         <v>1063</v>
@@ -24179,7 +24282,7 @@
     </row>
     <row r="551" spans="1:11">
       <c r="A551" s="4">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="B551" s="52" t="s">
         <v>1063</v>
@@ -24212,7 +24315,7 @@
     </row>
     <row r="552" spans="1:11">
       <c r="A552" s="4">
-        <v>540</v>
+        <v>551</v>
       </c>
       <c r="B552" s="52" t="s">
         <v>1063</v>
@@ -24247,7 +24350,7 @@
     </row>
     <row r="553" spans="1:11">
       <c r="A553" s="4">
-        <v>541</v>
+        <v>552</v>
       </c>
       <c r="B553" s="52" t="s">
         <v>1063</v>
@@ -24280,7 +24383,7 @@
     </row>
     <row r="554" spans="1:11">
       <c r="A554" s="4">
-        <v>542</v>
+        <v>553</v>
       </c>
       <c r="B554" s="52" t="s">
         <v>1063</v>
@@ -24315,7 +24418,7 @@
     </row>
     <row r="555" spans="1:11">
       <c r="A555" s="4">
-        <v>543</v>
+        <v>554</v>
       </c>
       <c r="B555" s="52" t="s">
         <v>1063</v>
@@ -24348,7 +24451,7 @@
     </row>
     <row r="556" spans="1:11">
       <c r="A556" s="4">
-        <v>544</v>
+        <v>555</v>
       </c>
       <c r="B556" s="52" t="s">
         <v>1063</v>
@@ -24381,7 +24484,7 @@
     </row>
     <row r="557" spans="1:11">
       <c r="A557" s="4">
-        <v>545</v>
+        <v>556</v>
       </c>
       <c r="B557" s="52" t="s">
         <v>1063</v>
@@ -24414,7 +24517,7 @@
     </row>
     <row r="558" spans="1:11">
       <c r="A558" s="4">
-        <v>546</v>
+        <v>557</v>
       </c>
       <c r="B558" s="52" t="s">
         <v>1063</v>
@@ -24423,31 +24526,31 @@
         <v>11</v>
       </c>
       <c r="D558" s="2" t="s">
-        <v>1360</v>
+        <v>1438</v>
       </c>
       <c r="E558" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F558" s="1" t="s">
-        <v>521</v>
+        <v>1050</v>
       </c>
       <c r="G558" s="1" t="s">
         <v>30</v>
       </c>
       <c r="H558" s="1" t="s">
-        <v>1361</v>
+        <v>1340</v>
       </c>
       <c r="I558" s="54">
-        <v>46279</v>
+        <v>46293</v>
       </c>
       <c r="J558" s="4" t="s">
-        <v>574</v>
+        <v>645</v>
       </c>
       <c r="K558" s="55"/>
     </row>
     <row r="559" spans="1:11">
       <c r="A559" s="4">
-        <v>547</v>
+        <v>558</v>
       </c>
       <c r="B559" s="52" t="s">
         <v>1063</v>
@@ -24456,31 +24559,31 @@
         <v>11</v>
       </c>
       <c r="D559" s="2" t="s">
-        <v>1360</v>
+        <v>1439</v>
       </c>
       <c r="E559" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F559" s="1" t="s">
-        <v>521</v>
+        <v>1072</v>
       </c>
       <c r="G559" s="1" t="s">
         <v>30</v>
       </c>
       <c r="H559" s="1" t="s">
-        <v>1361</v>
+        <v>1340</v>
       </c>
       <c r="I559" s="54">
-        <v>46279</v>
+        <v>46293</v>
       </c>
       <c r="J559" s="4" t="s">
-        <v>574</v>
+        <v>645</v>
       </c>
       <c r="K559" s="55"/>
     </row>
-    <row r="560" spans="1:11">
+    <row r="560" spans="1:11" ht="15.6">
       <c r="A560" s="4">
-        <v>548</v>
+        <v>559</v>
       </c>
       <c r="B560" s="52" t="s">
         <v>1063</v>
@@ -24489,22 +24592,22 @@
         <v>11</v>
       </c>
       <c r="D560" s="2" t="s">
-        <v>1360</v>
+        <v>1440</v>
       </c>
       <c r="E560" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F560" s="1" t="s">
-        <v>521</v>
+        <v>19</v>
+      </c>
+      <c r="F560" s="50" t="s">
+        <v>1032</v>
       </c>
       <c r="G560" s="1" t="s">
         <v>30</v>
       </c>
       <c r="H560" s="1" t="s">
-        <v>1361</v>
+        <v>1340</v>
       </c>
       <c r="I560" s="54">
-        <v>46279</v>
+        <v>46293</v>
       </c>
       <c r="J560" s="4" t="s">
         <v>574</v>
@@ -24513,7 +24616,7 @@
     </row>
     <row r="561" spans="1:11">
       <c r="A561" s="4">
-        <v>549</v>
+        <v>560</v>
       </c>
       <c r="B561" s="52" t="s">
         <v>1063</v>
@@ -24522,31 +24625,31 @@
         <v>11</v>
       </c>
       <c r="D561" s="2" t="s">
-        <v>1360</v>
+        <v>1441</v>
       </c>
       <c r="E561" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F561" s="1" t="s">
-        <v>521</v>
+        <v>1036</v>
       </c>
       <c r="G561" s="1" t="s">
         <v>30</v>
       </c>
       <c r="H561" s="1" t="s">
-        <v>1361</v>
+        <v>1340</v>
       </c>
       <c r="I561" s="54">
-        <v>46279</v>
+        <v>46293</v>
       </c>
       <c r="J561" s="4" t="s">
-        <v>574</v>
+        <v>645</v>
       </c>
       <c r="K561" s="55"/>
     </row>
     <row r="562" spans="1:11">
       <c r="A562" s="4">
-        <v>550</v>
+        <v>561</v>
       </c>
       <c r="B562" s="52" t="s">
         <v>1063</v>
@@ -24578,7 +24681,9 @@
       <c r="K562" s="55"/>
     </row>
     <row r="563" spans="1:11">
-      <c r="A563" s="60"/>
+      <c r="A563" s="4">
+        <v>562</v>
+      </c>
       <c r="B563" s="52" t="s">
         <v>1063</v>
       </c>
@@ -24600,16 +24705,18 @@
       <c r="H563" s="1" t="s">
         <v>1361</v>
       </c>
-      <c r="I563" s="61">
+      <c r="I563" s="54">
         <v>46287</v>
       </c>
       <c r="J563" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="K563" s="62"/>
+      <c r="K563" s="55"/>
     </row>
     <row r="564" spans="1:11">
-      <c r="A564" s="60"/>
+      <c r="A564" s="4">
+        <v>563</v>
+      </c>
       <c r="B564" s="52" t="s">
         <v>1063</v>
       </c>
@@ -24631,16 +24738,18 @@
       <c r="H564" s="1" t="s">
         <v>1361</v>
       </c>
-      <c r="I564" s="61">
+      <c r="I564" s="54">
         <v>46287</v>
       </c>
       <c r="J564" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="K564" s="62"/>
+      <c r="K564" s="55"/>
     </row>
     <row r="565" spans="1:11">
-      <c r="A565" s="60"/>
+      <c r="A565" s="4">
+        <v>564</v>
+      </c>
       <c r="B565" s="52" t="s">
         <v>1063</v>
       </c>
@@ -24662,16 +24771,18 @@
       <c r="H565" s="1" t="s">
         <v>1361</v>
       </c>
-      <c r="I565" s="61">
+      <c r="I565" s="54">
         <v>46287</v>
       </c>
       <c r="J565" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="K565" s="62"/>
+      <c r="K565" s="55"/>
     </row>
     <row r="566" spans="1:11">
-      <c r="A566" s="60"/>
+      <c r="A566" s="4">
+        <v>565</v>
+      </c>
       <c r="B566" s="52" t="s">
         <v>1063</v>
       </c>
@@ -24693,16 +24804,18 @@
       <c r="H566" s="1" t="s">
         <v>1361</v>
       </c>
-      <c r="I566" s="61">
+      <c r="I566" s="54">
         <v>46287</v>
       </c>
       <c r="J566" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="K566" s="62"/>
+      <c r="K566" s="55"/>
     </row>
     <row r="567" spans="1:11">
-      <c r="A567" s="60"/>
+      <c r="A567" s="4">
+        <v>566</v>
+      </c>
       <c r="B567" s="52" t="s">
         <v>1063</v>
       </c>
@@ -24724,16 +24837,18 @@
       <c r="H567" s="1" t="s">
         <v>1361</v>
       </c>
-      <c r="I567" s="61">
+      <c r="I567" s="54">
         <v>46287</v>
       </c>
       <c r="J567" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="K567" s="62"/>
+      <c r="K567" s="55"/>
     </row>
     <row r="568" spans="1:11">
-      <c r="A568" s="60"/>
+      <c r="A568" s="4">
+        <v>567</v>
+      </c>
       <c r="B568" s="52" t="s">
         <v>1063</v>
       </c>
@@ -24755,16 +24870,18 @@
       <c r="H568" s="1" t="s">
         <v>1361</v>
       </c>
-      <c r="I568" s="61">
+      <c r="I568" s="54">
         <v>46287</v>
       </c>
       <c r="J568" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="K568" s="62"/>
+      <c r="K568" s="55"/>
     </row>
     <row r="569" spans="1:11">
-      <c r="A569" s="60"/>
+      <c r="A569" s="4">
+        <v>568</v>
+      </c>
       <c r="B569" s="52" t="s">
         <v>1063</v>
       </c>
@@ -24786,16 +24903,18 @@
       <c r="H569" s="1" t="s">
         <v>1361</v>
       </c>
-      <c r="I569" s="61">
+      <c r="I569" s="54">
         <v>46287</v>
       </c>
       <c r="J569" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="K569" s="62"/>
+      <c r="K569" s="55"/>
     </row>
     <row r="570" spans="1:11">
-      <c r="A570" s="60"/>
+      <c r="A570" s="4">
+        <v>569</v>
+      </c>
       <c r="B570" s="52" t="s">
         <v>1063</v>
       </c>
@@ -24817,16 +24936,18 @@
       <c r="H570" s="1" t="s">
         <v>1361</v>
       </c>
-      <c r="I570" s="61">
+      <c r="I570" s="54">
         <v>46287</v>
       </c>
       <c r="J570" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="K570" s="62"/>
+      <c r="K570" s="55"/>
     </row>
     <row r="571" spans="1:11">
-      <c r="A571" s="60"/>
+      <c r="A571" s="4">
+        <v>570</v>
+      </c>
       <c r="B571" s="52" t="s">
         <v>1063</v>
       </c>
@@ -24848,16 +24969,18 @@
       <c r="H571" s="1" t="s">
         <v>1361</v>
       </c>
-      <c r="I571" s="61">
+      <c r="I571" s="54">
         <v>46287</v>
       </c>
       <c r="J571" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="K571" s="62"/>
+      <c r="K571" s="55"/>
     </row>
     <row r="572" spans="1:11">
-      <c r="A572" s="60"/>
+      <c r="A572" s="4">
+        <v>571</v>
+      </c>
       <c r="B572" s="52" t="s">
         <v>1063</v>
       </c>
@@ -24879,16 +25002,18 @@
       <c r="H572" s="1" t="s">
         <v>1361</v>
       </c>
-      <c r="I572" s="61">
+      <c r="I572" s="54">
         <v>46287</v>
       </c>
       <c r="J572" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="K572" s="62"/>
+      <c r="K572" s="55"/>
     </row>
     <row r="573" spans="1:11">
-      <c r="A573" s="60"/>
+      <c r="A573" s="4">
+        <v>572</v>
+      </c>
       <c r="B573" s="52" t="s">
         <v>1063</v>
       </c>
@@ -24910,16 +25035,18 @@
       <c r="H573" s="1" t="s">
         <v>1361</v>
       </c>
-      <c r="I573" s="61">
+      <c r="I573" s="54">
         <v>46287</v>
       </c>
       <c r="J573" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="K573" s="62"/>
+      <c r="K573" s="55"/>
     </row>
     <row r="574" spans="1:11">
-      <c r="A574" s="60"/>
+      <c r="A574" s="4">
+        <v>573</v>
+      </c>
       <c r="B574" s="52" t="s">
         <v>1063</v>
       </c>
@@ -24941,16 +25068,18 @@
       <c r="H574" s="1" t="s">
         <v>1361</v>
       </c>
-      <c r="I574" s="61">
+      <c r="I574" s="54">
         <v>46287</v>
       </c>
       <c r="J574" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="K574" s="62"/>
+      <c r="K574" s="55"/>
     </row>
     <row r="575" spans="1:11">
-      <c r="A575" s="60"/>
+      <c r="A575" s="4">
+        <v>574</v>
+      </c>
       <c r="B575" s="52" t="s">
         <v>1063</v>
       </c>
@@ -24972,16 +25101,18 @@
       <c r="H575" s="1" t="s">
         <v>1361</v>
       </c>
-      <c r="I575" s="61">
+      <c r="I575" s="54">
         <v>46287</v>
       </c>
       <c r="J575" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="K575" s="62"/>
+      <c r="K575" s="55"/>
     </row>
     <row r="576" spans="1:11">
-      <c r="A576" s="60"/>
+      <c r="A576" s="4">
+        <v>575</v>
+      </c>
       <c r="B576" s="52" t="s">
         <v>1063</v>
       </c>
@@ -25003,16 +25134,18 @@
       <c r="H576" s="1" t="s">
         <v>1361</v>
       </c>
-      <c r="I576" s="61">
+      <c r="I576" s="54">
         <v>46287</v>
       </c>
       <c r="J576" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="K576" s="62"/>
+      <c r="K576" s="55"/>
     </row>
     <row r="577" spans="1:11">
-      <c r="A577" s="60"/>
+      <c r="A577" s="4">
+        <v>576</v>
+      </c>
       <c r="B577" s="52" t="s">
         <v>1063</v>
       </c>
@@ -25034,16 +25167,18 @@
       <c r="H577" s="1" t="s">
         <v>1361</v>
       </c>
-      <c r="I577" s="61">
+      <c r="I577" s="54">
         <v>46287</v>
       </c>
       <c r="J577" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="K577" s="62"/>
+      <c r="K577" s="55"/>
     </row>
     <row r="578" spans="1:11">
-      <c r="A578" s="60"/>
+      <c r="A578" s="4">
+        <v>577</v>
+      </c>
       <c r="B578" s="52" t="s">
         <v>1063</v>
       </c>
@@ -25065,17 +25200,17 @@
       <c r="H578" s="1" t="s">
         <v>1361</v>
       </c>
-      <c r="I578" s="61">
+      <c r="I578" s="54">
         <v>46287</v>
       </c>
       <c r="J578" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="K578" s="62"/>
+      <c r="K578" s="55"/>
     </row>
     <row r="579" spans="1:11">
       <c r="A579" s="4">
-        <v>551</v>
+        <v>578</v>
       </c>
       <c r="B579" s="2" t="s">
         <v>1212</v>
@@ -25106,7 +25241,7 @@
     </row>
     <row r="580" spans="1:11">
       <c r="A580" s="4">
-        <v>552</v>
+        <v>579</v>
       </c>
       <c r="B580" s="2" t="s">
         <v>1261</v>
@@ -25138,96 +25273,81 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="duplicateValues" dxfId="44" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D268">
-    <cfRule type="duplicateValues" dxfId="43" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D366">
-    <cfRule type="duplicateValues" dxfId="40" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D367">
-    <cfRule type="duplicateValues" dxfId="39" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D502 D2:D367">
-    <cfRule type="duplicateValues" dxfId="38" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="93"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:E258 G215 E525:E1048576">
-    <cfRule type="cellIs" dxfId="37" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="23" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E260:E524">
-    <cfRule type="cellIs" dxfId="36" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="19" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F252 F254:F255 F257:F1048576">
-    <cfRule type="cellIs" dxfId="35" priority="15" operator="equal">
+  <conditionalFormatting sqref="F254:F255 F257:F559 F561:F1048576 F1:F252">
+    <cfRule type="cellIs" dxfId="32" priority="15" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="16" operator="equal">
       <formula>"DOADORA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="24" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="25" operator="equal">
       <formula>"DEPOSITO SOLAGOS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F366">
-    <cfRule type="cellIs" dxfId="31" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="20" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="21" operator="equal">
       <formula>"DEPOSITO SOLAGOS"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K215">
-    <cfRule type="cellIs" dxfId="29" priority="10" operator="equal">
-      <formula>"MANUTENÇÃO"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="11" operator="equal">
-      <formula>"DOADORA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="12" operator="equal">
-      <formula>"MANUTENÇÃO"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="13" operator="equal">
-      <formula>"DEPOSITO SOLAGOS"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H258 H526:H580">
-    <cfRule type="cellIs" dxfId="25" priority="6" operator="equal">
+  <conditionalFormatting sqref="H1:H258">
+    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H260:H524">
-    <cfRule type="cellIs" dxfId="24" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H305">
-    <cfRule type="cellIs" dxfId="23" priority="4" operator="equal">
+  <conditionalFormatting sqref="H526:H580">
+    <cfRule type="cellIs" dxfId="24" priority="6" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H374">
-    <cfRule type="cellIs" dxfId="22" priority="3" operator="equal">
-      <formula>"SOLAGOS DEPOSITO"</formula>
+  <conditionalFormatting sqref="K215">
+    <cfRule type="cellIs" dxfId="23" priority="10" operator="equal">
+      <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H389">
-    <cfRule type="cellIs" dxfId="21" priority="2" operator="equal">
-      <formula>"SOLAGOS DEPOSITO"</formula>
+    <cfRule type="cellIs" dxfId="22" priority="11" operator="equal">
+      <formula>"DOADORA"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H1">
-    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
-      <formula>"SOLAGOS DEPOSITO"</formula>
+    <cfRule type="cellIs" dxfId="21" priority="12" operator="equal">
+      <formula>"MANUTENÇÃO"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="20" priority="13" operator="equal">
+      <formula>"DEPOSITO SOLAGOS"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -27693,10 +27813,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="59" t="s">
+      <c r="B1" s="58" t="s">
         <v>1387</v>
       </c>
       <c r="C1" t="s">

--- a/data_printer.xlsx
+++ b/data_printer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erick\Desktop\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC1F28D6-A10F-4E85-BC78-81B0CEDE9CCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41EB6BF8-9C2D-4B0F-AE13-E522B4FE54BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A8AA41B5-7AA1-4FF7-A9B8-54B8A4E1AF28}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5317" uniqueCount="1443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5318" uniqueCount="1445">
   <si>
     <t>INDICE</t>
   </si>
@@ -4377,6 +4377,12 @@
   </si>
   <si>
     <t>CANIBALIZADA</t>
+  </si>
+  <si>
+    <t>XC75053807</t>
+  </si>
+  <si>
+    <t>BOA</t>
   </si>
 </sst>
 </file>
@@ -5539,7 +5545,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}" name="Controle_Inventario_Impressoras" displayName="Controle_Inventario_Impressoras" ref="A1:K580" tableType="queryTable" totalsRowShown="0" headerRowDxfId="67" dataDxfId="66">
-  <autoFilter ref="A1:K580" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}"/>
+  <autoFilter ref="A1:K580" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="SEDUC"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K37">
     <sortCondition ref="A23"/>
   </sortState>
@@ -5943,7 +5955,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" hidden="1">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -5976,7 +5988,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" hidden="1">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -6009,7 +6021,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" hidden="1">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -6042,7 +6054,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" hidden="1">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -6075,7 +6087,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" hidden="1">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -6108,7 +6120,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" hidden="1">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -6141,7 +6153,7 @@
       </c>
       <c r="K7" s="55"/>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" hidden="1">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -6174,7 +6186,7 @@
       </c>
       <c r="K8" s="55"/>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" hidden="1">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -6207,7 +6219,7 @@
       </c>
       <c r="K9" s="55"/>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" hidden="1">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -6240,7 +6252,7 @@
       </c>
       <c r="K10" s="55"/>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" hidden="1">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -6273,7 +6285,7 @@
       </c>
       <c r="K11" s="55"/>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" hidden="1">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -6306,7 +6318,7 @@
       </c>
       <c r="K12" s="55"/>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" hidden="1">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -6339,7 +6351,7 @@
       </c>
       <c r="K13" s="55"/>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" hidden="1">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -6372,7 +6384,7 @@
       </c>
       <c r="K14" s="55"/>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" hidden="1">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -6405,7 +6417,7 @@
       </c>
       <c r="K15" s="55"/>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" hidden="1">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -6438,7 +6450,7 @@
       </c>
       <c r="K16" s="55"/>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" hidden="1">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -6471,7 +6483,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" hidden="1">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -6504,7 +6516,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" hidden="1">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -6535,7 +6547,7 @@
       </c>
       <c r="K19" s="7"/>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" hidden="1">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -6566,7 +6578,7 @@
       </c>
       <c r="K20" s="7"/>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" hidden="1">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -6601,7 +6613,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" hidden="1">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -6636,7 +6648,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" hidden="1">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -6669,7 +6681,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" hidden="1">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -6704,7 +6716,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" hidden="1">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -6737,7 +6749,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" hidden="1">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -6767,7 +6779,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" hidden="1">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -6800,7 +6812,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" hidden="1">
       <c r="A28" s="4">
         <v>27</v>
       </c>
@@ -6833,7 +6845,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" hidden="1">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -6901,7 +6913,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" hidden="1">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -6934,7 +6946,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="15.75" customHeight="1">
+    <row r="32" spans="1:11" ht="15.75" hidden="1" customHeight="1">
       <c r="A32" s="4">
         <v>31</v>
       </c>
@@ -6967,7 +6979,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" hidden="1">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -7000,7 +7012,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" hidden="1">
       <c r="A34" s="4">
         <v>33</v>
       </c>
@@ -7033,7 +7045,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" hidden="1">
       <c r="A35" s="4">
         <v>34</v>
       </c>
@@ -7066,7 +7078,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" hidden="1">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -7096,7 +7108,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" hidden="1">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -7126,7 +7138,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" hidden="1">
       <c r="A38" s="4">
         <v>37</v>
       </c>
@@ -7159,7 +7171,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" hidden="1">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -7192,7 +7204,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" hidden="1">
       <c r="A40" s="4">
         <v>39</v>
       </c>
@@ -7225,7 +7237,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" hidden="1">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -7258,7 +7270,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" hidden="1">
       <c r="A42" s="4">
         <v>41</v>
       </c>
@@ -7291,7 +7303,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" hidden="1">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -7359,7 +7371,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" hidden="1">
       <c r="A45" s="4">
         <v>44</v>
       </c>
@@ -7392,7 +7404,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" hidden="1">
       <c r="A46" s="4">
         <v>45</v>
       </c>
@@ -7425,7 +7437,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" hidden="1">
       <c r="A47" s="4">
         <v>46</v>
       </c>
@@ -7455,7 +7467,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" hidden="1">
       <c r="A48" s="4">
         <v>47</v>
       </c>
@@ -7488,7 +7500,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:11" hidden="1">
       <c r="A49" s="4">
         <v>48</v>
       </c>
@@ -7521,7 +7533,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:11" hidden="1">
       <c r="A50" s="4">
         <v>49</v>
       </c>
@@ -7554,7 +7566,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:11" hidden="1">
       <c r="A51" s="4">
         <v>50</v>
       </c>
@@ -7587,7 +7599,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:11" hidden="1">
       <c r="A52" s="4">
         <v>51</v>
       </c>
@@ -7620,7 +7632,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:11" hidden="1">
       <c r="A53" s="4">
         <v>52</v>
       </c>
@@ -7653,7 +7665,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:11" hidden="1">
       <c r="A54" s="4">
         <v>53</v>
       </c>
@@ -7686,7 +7698,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:11" hidden="1">
       <c r="A55" s="4">
         <v>54</v>
       </c>
@@ -7716,7 +7728,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:11" hidden="1">
       <c r="A56" s="4">
         <v>55</v>
       </c>
@@ -7749,7 +7761,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:11" hidden="1">
       <c r="A57" s="4">
         <v>56</v>
       </c>
@@ -7782,7 +7794,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:11" hidden="1">
       <c r="A58" s="4">
         <v>57</v>
       </c>
@@ -7815,7 +7827,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:11" hidden="1">
       <c r="A59" s="4">
         <v>58</v>
       </c>
@@ -7845,7 +7857,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60" spans="1:11" hidden="1">
       <c r="A60" s="4">
         <v>59</v>
       </c>
@@ -7875,7 +7887,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61" spans="1:11" hidden="1">
       <c r="A61" s="4">
         <v>60</v>
       </c>
@@ -7908,7 +7920,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="62" spans="1:11">
+    <row r="62" spans="1:11" hidden="1">
       <c r="A62" s="4">
         <v>61</v>
       </c>
@@ -7943,7 +7955,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:11" hidden="1">
       <c r="A63" s="4">
         <v>62</v>
       </c>
@@ -7978,7 +7990,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64" spans="1:11" hidden="1">
       <c r="A64" s="4">
         <v>63</v>
       </c>
@@ -8013,7 +8025,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="65" spans="1:11">
+    <row r="65" spans="1:11" hidden="1">
       <c r="A65" s="4">
         <v>64</v>
       </c>
@@ -8043,7 +8055,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="66" spans="1:11">
+    <row r="66" spans="1:11" hidden="1">
       <c r="A66" s="4">
         <v>65</v>
       </c>
@@ -8073,7 +8085,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="67" spans="1:11">
+    <row r="67" spans="1:11" hidden="1">
       <c r="A67" s="4">
         <v>66</v>
       </c>
@@ -8103,7 +8115,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="68" spans="1:11">
+    <row r="68" spans="1:11" hidden="1">
       <c r="A68" s="4">
         <v>67</v>
       </c>
@@ -8133,7 +8145,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="69" spans="1:11">
+    <row r="69" spans="1:11" hidden="1">
       <c r="A69" s="4">
         <v>68</v>
       </c>
@@ -8163,7 +8175,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="70" spans="1:11">
+    <row r="70" spans="1:11" hidden="1">
       <c r="A70" s="4">
         <v>69</v>
       </c>
@@ -8193,7 +8205,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="71" spans="1:11">
+    <row r="71" spans="1:11" hidden="1">
       <c r="A71" s="4">
         <v>70</v>
       </c>
@@ -8226,7 +8238,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="72" spans="1:11">
+    <row r="72" spans="1:11" hidden="1">
       <c r="A72" s="4">
         <v>71</v>
       </c>
@@ -8259,7 +8271,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="73" spans="1:11">
+    <row r="73" spans="1:11" hidden="1">
       <c r="A73" s="4">
         <v>72</v>
       </c>
@@ -8289,7 +8301,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="74" spans="1:11">
+    <row r="74" spans="1:11" hidden="1">
       <c r="A74" s="4">
         <v>73</v>
       </c>
@@ -8322,7 +8334,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="75" spans="1:11">
+    <row r="75" spans="1:11" hidden="1">
       <c r="A75" s="4">
         <v>74</v>
       </c>
@@ -8352,7 +8364,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="76" spans="1:11">
+    <row r="76" spans="1:11" hidden="1">
       <c r="A76" s="4">
         <v>75</v>
       </c>
@@ -8382,7 +8394,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="77" spans="1:11">
+    <row r="77" spans="1:11" hidden="1">
       <c r="A77" s="4">
         <v>76</v>
       </c>
@@ -8412,7 +8424,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="78" spans="1:11">
+    <row r="78" spans="1:11" hidden="1">
       <c r="A78" s="4">
         <v>77</v>
       </c>
@@ -8442,7 +8454,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="79" spans="1:11">
+    <row r="79" spans="1:11" hidden="1">
       <c r="A79" s="4">
         <v>78</v>
       </c>
@@ -8475,7 +8487,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80" spans="1:11" hidden="1">
       <c r="A80" s="4">
         <v>79</v>
       </c>
@@ -8508,7 +8520,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="81" spans="1:11">
+    <row r="81" spans="1:11" hidden="1">
       <c r="A81" s="4">
         <v>80</v>
       </c>
@@ -8573,7 +8585,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="83" spans="1:11">
+    <row r="83" spans="1:11" hidden="1">
       <c r="A83" s="4">
         <v>82</v>
       </c>
@@ -8606,7 +8618,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="84" spans="1:11">
+    <row r="84" spans="1:11" hidden="1">
       <c r="A84" s="4">
         <v>83</v>
       </c>
@@ -8639,7 +8651,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="85" spans="1:11">
+    <row r="85" spans="1:11" hidden="1">
       <c r="A85" s="4">
         <v>84</v>
       </c>
@@ -8669,7 +8681,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="86" spans="1:11">
+    <row r="86" spans="1:11" hidden="1">
       <c r="A86" s="4">
         <v>85</v>
       </c>
@@ -8702,7 +8714,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="87" spans="1:11">
+    <row r="87" spans="1:11" hidden="1">
       <c r="A87" s="4">
         <v>86</v>
       </c>
@@ -8735,7 +8747,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="88" spans="1:11">
+    <row r="88" spans="1:11" hidden="1">
       <c r="A88" s="4">
         <v>87</v>
       </c>
@@ -8768,7 +8780,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="89" spans="1:11">
+    <row r="89" spans="1:11" hidden="1">
       <c r="A89" s="4">
         <v>88</v>
       </c>
@@ -8801,7 +8813,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="90" spans="1:11">
+    <row r="90" spans="1:11" hidden="1">
       <c r="A90" s="4">
         <v>89</v>
       </c>
@@ -8834,7 +8846,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="91" spans="1:11">
+    <row r="91" spans="1:11" hidden="1">
       <c r="A91" s="4">
         <v>90</v>
       </c>
@@ -8867,7 +8879,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="92" spans="1:11">
+    <row r="92" spans="1:11" hidden="1">
       <c r="A92" s="4">
         <v>91</v>
       </c>
@@ -8894,7 +8906,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="93" spans="1:11">
+    <row r="93" spans="1:11" hidden="1">
       <c r="A93" s="4">
         <v>92</v>
       </c>
@@ -8921,7 +8933,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="94" spans="1:11">
+    <row r="94" spans="1:11" hidden="1">
       <c r="A94" s="4">
         <v>93</v>
       </c>
@@ -8948,7 +8960,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="95" spans="1:11">
+    <row r="95" spans="1:11" hidden="1">
       <c r="A95" s="4">
         <v>94</v>
       </c>
@@ -8981,7 +8993,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="96" spans="1:11">
+    <row r="96" spans="1:11" hidden="1">
       <c r="A96" s="4">
         <v>95</v>
       </c>
@@ -9028,15 +9040,17 @@
         <v>1187</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>605</v>
+        <v>1048</v>
       </c>
       <c r="G97" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H97" s="1"/>
+      <c r="H97" s="1" t="s">
+        <v>1373</v>
+      </c>
       <c r="I97" s="9">
         <v>45707</v>
       </c>
@@ -9047,7 +9061,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="98" spans="1:11">
+    <row r="98" spans="1:11" hidden="1">
       <c r="A98" s="4">
         <v>97</v>
       </c>
@@ -9080,7 +9094,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="99" spans="1:11">
+    <row r="99" spans="1:11" hidden="1">
       <c r="A99" s="4">
         <v>98</v>
       </c>
@@ -9110,7 +9124,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="100" spans="1:11">
+    <row r="100" spans="1:11" hidden="1">
       <c r="A100" s="4">
         <v>99</v>
       </c>
@@ -9143,7 +9157,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="101" spans="1:11">
+    <row r="101" spans="1:11" hidden="1">
       <c r="A101" s="4">
         <v>100</v>
       </c>
@@ -9176,7 +9190,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="102" spans="1:11">
+    <row r="102" spans="1:11" hidden="1">
       <c r="A102" s="4">
         <v>101</v>
       </c>
@@ -9203,7 +9217,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="103" spans="1:11">
+    <row r="103" spans="1:11" hidden="1">
       <c r="A103" s="4">
         <v>102</v>
       </c>
@@ -9230,7 +9244,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="104" spans="1:11">
+    <row r="104" spans="1:11" hidden="1">
       <c r="A104" s="4">
         <v>103</v>
       </c>
@@ -9263,7 +9277,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="105" spans="1:11">
+    <row r="105" spans="1:11" hidden="1">
       <c r="A105" s="4">
         <v>104</v>
       </c>
@@ -9293,7 +9307,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="106" spans="1:11">
+    <row r="106" spans="1:11" hidden="1">
       <c r="A106" s="4">
         <v>105</v>
       </c>
@@ -9325,7 +9339,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="107" spans="1:11">
+    <row r="107" spans="1:11" hidden="1">
       <c r="A107" s="4">
         <v>106</v>
       </c>
@@ -9355,7 +9369,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="108" spans="1:11">
+    <row r="108" spans="1:11" hidden="1">
       <c r="A108" s="4">
         <v>107</v>
       </c>
@@ -9399,16 +9413,16 @@
         <v>194</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>1048</v>
+        <v>23</v>
       </c>
       <c r="G109" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>1373</v>
+        <v>1444</v>
       </c>
       <c r="I109" s="9">
         <v>45652</v>
@@ -9420,7 +9434,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="110" spans="1:11">
+    <row r="110" spans="1:11" hidden="1">
       <c r="A110" s="4">
         <v>109</v>
       </c>
@@ -9453,7 +9467,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="111" spans="1:11">
+    <row r="111" spans="1:11" hidden="1">
       <c r="A111" s="4">
         <v>110</v>
       </c>
@@ -9486,7 +9500,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="112" spans="1:11">
+    <row r="112" spans="1:11" hidden="1">
       <c r="A112" s="4">
         <v>111</v>
       </c>
@@ -9521,7 +9535,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="113" spans="1:11">
+    <row r="113" spans="1:11" hidden="1">
       <c r="A113" s="4">
         <v>112</v>
       </c>
@@ -9554,7 +9568,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="114" spans="1:11">
+    <row r="114" spans="1:11" hidden="1">
       <c r="A114" s="4">
         <v>113</v>
       </c>
@@ -9587,7 +9601,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="115" spans="1:11">
+    <row r="115" spans="1:11" hidden="1">
       <c r="A115" s="4">
         <v>114</v>
       </c>
@@ -9620,7 +9634,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="116" spans="1:11">
+    <row r="116" spans="1:11" hidden="1">
       <c r="A116" s="4">
         <v>115</v>
       </c>
@@ -9653,7 +9667,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="117" spans="1:11">
+    <row r="117" spans="1:11" hidden="1">
       <c r="A117" s="4">
         <v>116</v>
       </c>
@@ -9686,7 +9700,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="118" spans="1:11">
+    <row r="118" spans="1:11" hidden="1">
       <c r="A118" s="4">
         <v>117</v>
       </c>
@@ -9715,7 +9729,7 @@
       </c>
       <c r="K118" s="24"/>
     </row>
-    <row r="119" spans="1:11">
+    <row r="119" spans="1:11" hidden="1">
       <c r="A119" s="4">
         <v>118</v>
       </c>
@@ -9748,7 +9762,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="120" spans="1:11">
+    <row r="120" spans="1:11" hidden="1">
       <c r="A120" s="4">
         <v>119</v>
       </c>
@@ -9781,7 +9795,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="121" spans="1:11">
+    <row r="121" spans="1:11" hidden="1">
       <c r="A121" s="4">
         <v>120</v>
       </c>
@@ -9814,7 +9828,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="122" spans="1:11">
+    <row r="122" spans="1:11" hidden="1">
       <c r="A122" s="4">
         <v>121</v>
       </c>
@@ -9847,7 +9861,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="123" spans="1:11">
+    <row r="123" spans="1:11" hidden="1">
       <c r="A123" s="4">
         <v>122</v>
       </c>
@@ -9880,7 +9894,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="124" spans="1:11">
+    <row r="124" spans="1:11" hidden="1">
       <c r="A124" s="4">
         <v>123</v>
       </c>
@@ -9913,7 +9927,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="125" spans="1:11">
+    <row r="125" spans="1:11" hidden="1">
       <c r="A125" s="4">
         <v>124</v>
       </c>
@@ -9946,7 +9960,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="126" spans="1:11">
+    <row r="126" spans="1:11" hidden="1">
       <c r="A126" s="4">
         <v>125</v>
       </c>
@@ -9979,7 +9993,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="127" spans="1:11">
+    <row r="127" spans="1:11" hidden="1">
       <c r="A127" s="4">
         <v>126</v>
       </c>
@@ -10012,7 +10026,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="128" spans="1:11">
+    <row r="128" spans="1:11" hidden="1">
       <c r="A128" s="4">
         <v>127</v>
       </c>
@@ -10045,7 +10059,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="129" spans="1:11">
+    <row r="129" spans="1:11" hidden="1">
       <c r="A129" s="4">
         <v>128</v>
       </c>
@@ -10078,7 +10092,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="130" spans="1:11">
+    <row r="130" spans="1:11" hidden="1">
       <c r="A130" s="4">
         <v>129</v>
       </c>
@@ -10111,7 +10125,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="131" spans="1:11">
+    <row r="131" spans="1:11" hidden="1">
       <c r="A131" s="4">
         <v>130</v>
       </c>
@@ -10144,7 +10158,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="132" spans="1:11">
+    <row r="132" spans="1:11" hidden="1">
       <c r="A132" s="4">
         <v>131</v>
       </c>
@@ -10177,7 +10191,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="133" spans="1:11">
+    <row r="133" spans="1:11" hidden="1">
       <c r="A133" s="4">
         <v>132</v>
       </c>
@@ -10210,7 +10224,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="134" spans="1:11">
+    <row r="134" spans="1:11" hidden="1">
       <c r="A134" s="4">
         <v>133</v>
       </c>
@@ -10245,7 +10259,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="135" spans="1:11">
+    <row r="135" spans="1:11" hidden="1">
       <c r="A135" s="4">
         <v>134</v>
       </c>
@@ -10315,7 +10329,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="137" spans="1:11">
+    <row r="137" spans="1:11" hidden="1">
       <c r="A137" s="4">
         <v>136</v>
       </c>
@@ -10348,7 +10362,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="138" spans="1:11">
+    <row r="138" spans="1:11" hidden="1">
       <c r="A138" s="4">
         <v>137</v>
       </c>
@@ -10381,7 +10395,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="139" spans="1:11">
+    <row r="139" spans="1:11" hidden="1">
       <c r="A139" s="4">
         <v>138</v>
       </c>
@@ -10414,7 +10428,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="140" spans="1:11">
+    <row r="140" spans="1:11" hidden="1">
       <c r="A140" s="4">
         <v>139</v>
       </c>
@@ -10447,7 +10461,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="141" spans="1:11">
+    <row r="141" spans="1:11" hidden="1">
       <c r="A141" s="4">
         <v>140</v>
       </c>
@@ -10585,7 +10599,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="145" spans="1:11">
+    <row r="145" spans="1:11" hidden="1">
       <c r="A145" s="4">
         <v>144</v>
       </c>
@@ -10653,7 +10667,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="147" spans="1:11">
+    <row r="147" spans="1:11" hidden="1">
       <c r="A147" s="4">
         <v>146</v>
       </c>
@@ -10686,7 +10700,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="148" spans="1:11">
+    <row r="148" spans="1:11" hidden="1">
       <c r="A148" s="4">
         <v>147</v>
       </c>
@@ -10719,7 +10733,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="149" spans="1:11">
+    <row r="149" spans="1:11" hidden="1">
       <c r="A149" s="4">
         <v>148</v>
       </c>
@@ -10752,7 +10766,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="150" spans="1:11">
+    <row r="150" spans="1:11" hidden="1">
       <c r="A150" s="4">
         <v>149</v>
       </c>
@@ -10785,7 +10799,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="151" spans="1:11">
+    <row r="151" spans="1:11" hidden="1">
       <c r="A151" s="4">
         <v>150</v>
       </c>
@@ -10818,7 +10832,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="152" spans="1:11">
+    <row r="152" spans="1:11" hidden="1">
       <c r="A152" s="4">
         <v>151</v>
       </c>
@@ -10851,7 +10865,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="153" spans="1:11">
+    <row r="153" spans="1:11" hidden="1">
       <c r="A153" s="4">
         <v>152</v>
       </c>
@@ -10884,7 +10898,7 @@
       </c>
       <c r="K153" s="24"/>
     </row>
-    <row r="154" spans="1:11">
+    <row r="154" spans="1:11" hidden="1">
       <c r="A154" s="4">
         <v>153</v>
       </c>
@@ -10919,7 +10933,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="155" spans="1:11">
+    <row r="155" spans="1:11" hidden="1">
       <c r="A155" s="4">
         <v>154</v>
       </c>
@@ -10954,7 +10968,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="156" spans="1:11">
+    <row r="156" spans="1:11" hidden="1">
       <c r="A156" s="4">
         <v>155</v>
       </c>
@@ -11024,7 +11038,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="158" spans="1:11">
+    <row r="158" spans="1:11" hidden="1">
       <c r="A158" s="4">
         <v>157</v>
       </c>
@@ -11059,7 +11073,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="159" spans="1:11">
+    <row r="159" spans="1:11" hidden="1">
       <c r="A159" s="4">
         <v>158</v>
       </c>
@@ -11265,7 +11279,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="165" spans="1:11">
+    <row r="165" spans="1:11" hidden="1">
       <c r="A165" s="4">
         <v>164</v>
       </c>
@@ -11300,7 +11314,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="166" spans="1:11">
+    <row r="166" spans="1:11" hidden="1">
       <c r="A166" s="4">
         <v>165</v>
       </c>
@@ -11335,7 +11349,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="167" spans="1:11">
+    <row r="167" spans="1:11" hidden="1">
       <c r="A167" s="4">
         <v>166</v>
       </c>
@@ -11370,7 +11384,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="168" spans="1:11">
+    <row r="168" spans="1:11" hidden="1">
       <c r="A168" s="4">
         <v>167</v>
       </c>
@@ -11403,7 +11417,7 @@
       </c>
       <c r="K168" s="55"/>
     </row>
-    <row r="169" spans="1:11">
+    <row r="169" spans="1:11" hidden="1">
       <c r="A169" s="4">
         <v>168</v>
       </c>
@@ -11436,7 +11450,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="170" spans="1:11">
+    <row r="170" spans="1:11" hidden="1">
       <c r="A170" s="4">
         <v>169</v>
       </c>
@@ -11469,7 +11483,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="171" spans="1:11">
+    <row r="171" spans="1:11" hidden="1">
       <c r="A171" s="4">
         <v>170</v>
       </c>
@@ -11502,7 +11516,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="172" spans="1:11">
+    <row r="172" spans="1:11" hidden="1">
       <c r="A172" s="4">
         <v>171</v>
       </c>
@@ -11537,7 +11551,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="173" spans="1:11">
+    <row r="173" spans="1:11" hidden="1">
       <c r="A173" s="4">
         <v>172</v>
       </c>
@@ -11570,7 +11584,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="174" spans="1:11">
+    <row r="174" spans="1:11" hidden="1">
       <c r="A174" s="4">
         <v>173</v>
       </c>
@@ -11603,7 +11617,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="175" spans="1:11">
+    <row r="175" spans="1:11" hidden="1">
       <c r="A175" s="4">
         <v>174</v>
       </c>
@@ -11638,7 +11652,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="176" spans="1:11">
+    <row r="176" spans="1:11" hidden="1">
       <c r="A176" s="4">
         <v>175</v>
       </c>
@@ -11668,7 +11682,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="177" spans="1:11">
+    <row r="177" spans="1:11" hidden="1">
       <c r="A177" s="4">
         <v>176</v>
       </c>
@@ -11698,7 +11712,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="178" spans="1:11">
+    <row r="178" spans="1:11" hidden="1">
       <c r="A178" s="4">
         <v>177</v>
       </c>
@@ -11726,7 +11740,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="179" spans="1:11">
+    <row r="179" spans="1:11" hidden="1">
       <c r="A179" s="4">
         <v>178</v>
       </c>
@@ -11761,7 +11775,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="180" spans="1:11">
+    <row r="180" spans="1:11" hidden="1">
       <c r="A180" s="4">
         <v>179</v>
       </c>
@@ -11791,7 +11805,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="181" spans="1:11">
+    <row r="181" spans="1:11" hidden="1">
       <c r="A181" s="4">
         <v>180</v>
       </c>
@@ -11824,7 +11838,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="182" spans="1:11">
+    <row r="182" spans="1:11" hidden="1">
       <c r="A182" s="4">
         <v>181</v>
       </c>
@@ -11857,7 +11871,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="183" spans="1:11">
+    <row r="183" spans="1:11" hidden="1">
       <c r="A183" s="4">
         <v>182</v>
       </c>
@@ -11890,7 +11904,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="184" spans="1:11">
+    <row r="184" spans="1:11" hidden="1">
       <c r="A184" s="4">
         <v>183</v>
       </c>
@@ -11923,7 +11937,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="185" spans="1:11">
+    <row r="185" spans="1:11" hidden="1">
       <c r="A185" s="4">
         <v>184</v>
       </c>
@@ -11953,7 +11967,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="186" spans="1:11">
+    <row r="186" spans="1:11" hidden="1">
       <c r="A186" s="4">
         <v>185</v>
       </c>
@@ -11983,7 +11997,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="187" spans="1:11">
+    <row r="187" spans="1:11" hidden="1">
       <c r="A187" s="4">
         <v>186</v>
       </c>
@@ -12016,7 +12030,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="188" spans="1:11">
+    <row r="188" spans="1:11" hidden="1">
       <c r="A188" s="4">
         <v>187</v>
       </c>
@@ -12043,7 +12057,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="189" spans="1:11">
+    <row r="189" spans="1:11" hidden="1">
       <c r="A189" s="4">
         <v>188</v>
       </c>
@@ -12074,7 +12088,7 @@
       </c>
       <c r="K189" s="24"/>
     </row>
-    <row r="190" spans="1:11">
+    <row r="190" spans="1:11" hidden="1">
       <c r="A190" s="4">
         <v>189</v>
       </c>
@@ -12109,7 +12123,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="191" spans="1:11">
+    <row r="191" spans="1:11" hidden="1">
       <c r="A191" s="4">
         <v>190</v>
       </c>
@@ -12139,7 +12153,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="192" spans="1:11">
+    <row r="192" spans="1:11" hidden="1">
       <c r="A192" s="4">
         <v>191</v>
       </c>
@@ -12172,7 +12186,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="193" spans="1:10">
+    <row r="193" spans="1:10" hidden="1">
       <c r="A193" s="4">
         <v>192</v>
       </c>
@@ -12202,7 +12216,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="194" spans="1:10">
+    <row r="194" spans="1:10" hidden="1">
       <c r="A194" s="4">
         <v>193</v>
       </c>
@@ -12232,7 +12246,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="195" spans="1:10">
+    <row r="195" spans="1:10" hidden="1">
       <c r="A195" s="4">
         <v>194</v>
       </c>
@@ -12262,7 +12276,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="196" spans="1:10">
+    <row r="196" spans="1:10" hidden="1">
       <c r="A196" s="4">
         <v>195</v>
       </c>
@@ -12292,7 +12306,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="197" spans="1:10">
+    <row r="197" spans="1:10" hidden="1">
       <c r="A197" s="4">
         <v>196</v>
       </c>
@@ -12322,7 +12336,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="198" spans="1:10">
+    <row r="198" spans="1:10" hidden="1">
       <c r="A198" s="4">
         <v>197</v>
       </c>
@@ -12352,7 +12366,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="199" spans="1:10">
+    <row r="199" spans="1:10" hidden="1">
       <c r="A199" s="4">
         <v>198</v>
       </c>
@@ -12382,7 +12396,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="200" spans="1:10">
+    <row r="200" spans="1:10" hidden="1">
       <c r="A200" s="4">
         <v>199</v>
       </c>
@@ -12412,7 +12426,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="201" spans="1:10">
+    <row r="201" spans="1:10" hidden="1">
       <c r="A201" s="4">
         <v>200</v>
       </c>
@@ -12442,7 +12456,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="202" spans="1:10">
+    <row r="202" spans="1:10" hidden="1">
       <c r="A202" s="4">
         <v>201</v>
       </c>
@@ -12472,7 +12486,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="203" spans="1:10">
+    <row r="203" spans="1:10" hidden="1">
       <c r="A203" s="4">
         <v>202</v>
       </c>
@@ -12502,7 +12516,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="204" spans="1:10">
+    <row r="204" spans="1:10" hidden="1">
       <c r="A204" s="4">
         <v>203</v>
       </c>
@@ -12532,7 +12546,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="205" spans="1:10">
+    <row r="205" spans="1:10" hidden="1">
       <c r="A205" s="4">
         <v>204</v>
       </c>
@@ -12562,7 +12576,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="206" spans="1:10">
+    <row r="206" spans="1:10" hidden="1">
       <c r="A206" s="4">
         <v>205</v>
       </c>
@@ -12592,7 +12606,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="207" spans="1:10">
+    <row r="207" spans="1:10" hidden="1">
       <c r="A207" s="4">
         <v>206</v>
       </c>
@@ -12622,7 +12636,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="208" spans="1:10">
+    <row r="208" spans="1:10" hidden="1">
       <c r="A208" s="4">
         <v>207</v>
       </c>
@@ -12652,7 +12666,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="209" spans="1:11">
+    <row r="209" spans="1:11" hidden="1">
       <c r="A209" s="4">
         <v>208</v>
       </c>
@@ -12682,7 +12696,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="210" spans="1:11">
+    <row r="210" spans="1:11" hidden="1">
       <c r="A210" s="4">
         <v>209</v>
       </c>
@@ -12712,7 +12726,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="211" spans="1:11">
+    <row r="211" spans="1:11" hidden="1">
       <c r="A211" s="4">
         <v>210</v>
       </c>
@@ -12742,7 +12756,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="212" spans="1:11">
+    <row r="212" spans="1:11" hidden="1">
       <c r="A212" s="4">
         <v>211</v>
       </c>
@@ -12772,7 +12786,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="213" spans="1:11">
+    <row r="213" spans="1:11" hidden="1">
       <c r="A213" s="4">
         <v>212</v>
       </c>
@@ -12802,7 +12816,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="214" spans="1:11">
+    <row r="214" spans="1:11" hidden="1">
       <c r="A214" s="4">
         <v>213</v>
       </c>
@@ -12832,7 +12846,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="215" spans="1:11">
+    <row r="215" spans="1:11" hidden="1">
       <c r="A215" s="4">
         <v>214</v>
       </c>
@@ -12865,7 +12879,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="216" spans="1:11">
+    <row r="216" spans="1:11" hidden="1">
       <c r="A216" s="4">
         <v>215</v>
       </c>
@@ -12898,7 +12912,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="217" spans="1:11">
+    <row r="217" spans="1:11" hidden="1">
       <c r="A217" s="4">
         <v>216</v>
       </c>
@@ -12931,7 +12945,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="218" spans="1:11">
+    <row r="218" spans="1:11" hidden="1">
       <c r="A218" s="4">
         <v>217</v>
       </c>
@@ -12964,7 +12978,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="219" spans="1:11">
+    <row r="219" spans="1:11" hidden="1">
       <c r="A219" s="4">
         <v>218</v>
       </c>
@@ -12995,7 +13009,7 @@
       </c>
       <c r="K219" s="24"/>
     </row>
-    <row r="220" spans="1:11">
+    <row r="220" spans="1:11" hidden="1">
       <c r="A220" s="4">
         <v>219</v>
       </c>
@@ -13028,7 +13042,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="221" spans="1:11">
+    <row r="221" spans="1:11" hidden="1">
       <c r="A221" s="4">
         <v>220</v>
       </c>
@@ -13061,7 +13075,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="222" spans="1:11">
+    <row r="222" spans="1:11" hidden="1">
       <c r="A222" s="4">
         <v>221</v>
       </c>
@@ -13094,7 +13108,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="223" spans="1:11">
+    <row r="223" spans="1:11" hidden="1">
       <c r="A223" s="4">
         <v>222</v>
       </c>
@@ -13129,7 +13143,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="224" spans="1:11">
+    <row r="224" spans="1:11" hidden="1">
       <c r="A224" s="4">
         <v>223</v>
       </c>
@@ -13162,7 +13176,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="225" spans="1:11">
+    <row r="225" spans="1:11" hidden="1">
       <c r="A225" s="4">
         <v>224</v>
       </c>
@@ -13197,7 +13211,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="226" spans="1:11">
+    <row r="226" spans="1:11" hidden="1">
       <c r="A226" s="4">
         <v>225</v>
       </c>
@@ -13232,7 +13246,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="227" spans="1:11">
+    <row r="227" spans="1:11" hidden="1">
       <c r="A227" s="4">
         <v>226</v>
       </c>
@@ -13265,7 +13279,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="228" spans="1:11">
+    <row r="228" spans="1:11" hidden="1">
       <c r="A228" s="4">
         <v>227</v>
       </c>
@@ -13298,7 +13312,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="229" spans="1:11">
+    <row r="229" spans="1:11" hidden="1">
       <c r="A229" s="4">
         <v>228</v>
       </c>
@@ -13368,7 +13382,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="231" spans="1:11">
+    <row r="231" spans="1:11" hidden="1">
       <c r="A231" s="4">
         <v>230</v>
       </c>
@@ -13403,7 +13417,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="232" spans="1:11">
+    <row r="232" spans="1:11" hidden="1">
       <c r="A232" s="4">
         <v>231</v>
       </c>
@@ -13436,7 +13450,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="233" spans="1:11">
+    <row r="233" spans="1:11" hidden="1">
       <c r="A233" s="4">
         <v>232</v>
       </c>
@@ -13469,7 +13483,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="234" spans="1:11">
+    <row r="234" spans="1:11" hidden="1">
       <c r="A234" s="4">
         <v>233</v>
       </c>
@@ -13502,7 +13516,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="235" spans="1:11">
+    <row r="235" spans="1:11" hidden="1">
       <c r="A235" s="4">
         <v>234</v>
       </c>
@@ -13535,7 +13549,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="236" spans="1:11">
+    <row r="236" spans="1:11" hidden="1">
       <c r="A236" s="4">
         <v>235</v>
       </c>
@@ -13568,7 +13582,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="237" spans="1:11">
+    <row r="237" spans="1:11" hidden="1">
       <c r="A237" s="4">
         <v>236</v>
       </c>
@@ -13636,7 +13650,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="239" spans="1:11">
+    <row r="239" spans="1:11" hidden="1">
       <c r="A239" s="4">
         <v>238</v>
       </c>
@@ -13669,7 +13683,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="240" spans="1:11">
+    <row r="240" spans="1:11" hidden="1">
       <c r="A240" s="4">
         <v>239</v>
       </c>
@@ -13683,10 +13697,10 @@
         <v>341</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>1054</v>
+        <v>23</v>
       </c>
       <c r="G240" s="4" t="s">
         <v>14</v>
@@ -13704,7 +13718,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="241" spans="1:11">
+    <row r="241" spans="1:11" hidden="1">
       <c r="A241" s="4">
         <v>240</v>
       </c>
@@ -13737,7 +13751,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="242" spans="1:11">
+    <row r="242" spans="1:11" hidden="1">
       <c r="A242" s="4">
         <v>241</v>
       </c>
@@ -13772,7 +13786,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="243" spans="1:11">
+    <row r="243" spans="1:11" hidden="1">
       <c r="A243" s="4">
         <v>242</v>
       </c>
@@ -13805,7 +13819,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="244" spans="1:11">
+    <row r="244" spans="1:11" hidden="1">
       <c r="A244" s="4">
         <v>243</v>
       </c>
@@ -13873,7 +13887,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="246" spans="1:11">
+    <row r="246" spans="1:11" hidden="1">
       <c r="A246" s="4">
         <v>245</v>
       </c>
@@ -13906,7 +13920,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="247" spans="1:11">
+    <row r="247" spans="1:11" hidden="1">
       <c r="A247" s="4">
         <v>246</v>
       </c>
@@ -13941,7 +13955,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="248" spans="1:11">
+    <row r="248" spans="1:11" hidden="1">
       <c r="A248" s="4">
         <v>247</v>
       </c>
@@ -13974,7 +13988,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="249" spans="1:11">
+    <row r="249" spans="1:11" hidden="1">
       <c r="A249" s="4">
         <v>248</v>
       </c>
@@ -14007,7 +14021,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="250" spans="1:11">
+    <row r="250" spans="1:11" hidden="1">
       <c r="A250" s="4">
         <v>249</v>
       </c>
@@ -14040,7 +14054,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="251" spans="1:11">
+    <row r="251" spans="1:11" hidden="1">
       <c r="A251" s="4">
         <v>250</v>
       </c>
@@ -14110,7 +14124,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="253" spans="1:11" ht="15.6">
+    <row r="253" spans="1:11" ht="15.6" hidden="1">
       <c r="A253" s="4">
         <v>252</v>
       </c>
@@ -14250,7 +14264,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="257" spans="1:11">
+    <row r="257" spans="1:11" hidden="1">
       <c r="A257" s="4">
         <v>256</v>
       </c>
@@ -14285,7 +14299,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="258" spans="1:11">
+    <row r="258" spans="1:11" hidden="1">
       <c r="A258" s="4">
         <v>257</v>
       </c>
@@ -14316,7 +14330,7 @@
       </c>
       <c r="K258" s="20"/>
     </row>
-    <row r="259" spans="1:11">
+    <row r="259" spans="1:11" hidden="1">
       <c r="A259" s="4">
         <v>258</v>
       </c>
@@ -14349,7 +14363,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="260" spans="1:11">
+    <row r="260" spans="1:11" hidden="1">
       <c r="A260" s="4">
         <v>259</v>
       </c>
@@ -14384,7 +14398,7 @@
         <v>1312</v>
       </c>
     </row>
-    <row r="261" spans="1:11">
+    <row r="261" spans="1:11" hidden="1">
       <c r="A261" s="4">
         <v>260</v>
       </c>
@@ -14419,7 +14433,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="262" spans="1:11">
+    <row r="262" spans="1:11" hidden="1">
       <c r="A262" s="4">
         <v>261</v>
       </c>
@@ -14454,7 +14468,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="263" spans="1:11">
+    <row r="263" spans="1:11" hidden="1">
       <c r="A263" s="4">
         <v>262</v>
       </c>
@@ -14487,7 +14501,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="264" spans="1:11">
+    <row r="264" spans="1:11" hidden="1">
       <c r="A264" s="4">
         <v>263</v>
       </c>
@@ -14517,7 +14531,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="265" spans="1:11">
+    <row r="265" spans="1:11" hidden="1">
       <c r="A265" s="4">
         <v>264</v>
       </c>
@@ -14550,7 +14564,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="266" spans="1:11">
+    <row r="266" spans="1:11" hidden="1">
       <c r="A266" s="4">
         <v>265</v>
       </c>
@@ -14583,7 +14597,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="267" spans="1:11">
+    <row r="267" spans="1:11" hidden="1">
       <c r="A267" s="4">
         <v>266</v>
       </c>
@@ -14616,7 +14630,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="268" spans="1:11">
+    <row r="268" spans="1:11" hidden="1">
       <c r="A268" s="4">
         <v>267</v>
       </c>
@@ -14646,7 +14660,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="269" spans="1:11">
+    <row r="269" spans="1:11" hidden="1">
       <c r="A269" s="4">
         <v>268</v>
       </c>
@@ -14679,7 +14693,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="270" spans="1:11">
+    <row r="270" spans="1:11" hidden="1">
       <c r="A270" s="4">
         <v>269</v>
       </c>
@@ -14709,7 +14723,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="271" spans="1:11">
+    <row r="271" spans="1:11" hidden="1">
       <c r="A271" s="4">
         <v>270</v>
       </c>
@@ -14739,7 +14753,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="272" spans="1:11">
+    <row r="272" spans="1:11" hidden="1">
       <c r="A272" s="4">
         <v>271</v>
       </c>
@@ -14772,7 +14786,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="273" spans="1:11">
+    <row r="273" spans="1:11" hidden="1">
       <c r="A273" s="4">
         <v>272</v>
       </c>
@@ -14875,7 +14889,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="276" spans="1:11">
+    <row r="276" spans="1:11" hidden="1">
       <c r="A276" s="4">
         <v>275</v>
       </c>
@@ -14908,7 +14922,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="277" spans="1:11">
+    <row r="277" spans="1:11" hidden="1">
       <c r="A277" s="4">
         <v>276</v>
       </c>
@@ -14941,7 +14955,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="278" spans="1:11">
+    <row r="278" spans="1:11" hidden="1">
       <c r="A278" s="4">
         <v>277</v>
       </c>
@@ -14974,7 +14988,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="279" spans="1:11">
+    <row r="279" spans="1:11" hidden="1">
       <c r="A279" s="4">
         <v>278</v>
       </c>
@@ -15007,7 +15021,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="280" spans="1:11">
+    <row r="280" spans="1:11" hidden="1">
       <c r="A280" s="4">
         <v>279</v>
       </c>
@@ -15040,7 +15054,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="281" spans="1:11">
+    <row r="281" spans="1:11" hidden="1">
       <c r="A281" s="4">
         <v>280</v>
       </c>
@@ -15073,7 +15087,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="282" spans="1:11">
+    <row r="282" spans="1:11" hidden="1">
       <c r="A282" s="4">
         <v>281</v>
       </c>
@@ -15106,7 +15120,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="283" spans="1:11">
+    <row r="283" spans="1:11" hidden="1">
       <c r="A283" s="4">
         <v>282</v>
       </c>
@@ -15139,7 +15153,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="284" spans="1:11">
+    <row r="284" spans="1:11" hidden="1">
       <c r="A284" s="4">
         <v>283</v>
       </c>
@@ -15172,7 +15186,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="285" spans="1:11">
+    <row r="285" spans="1:11" hidden="1">
       <c r="A285" s="4">
         <v>284</v>
       </c>
@@ -15205,7 +15219,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="286" spans="1:11">
+    <row r="286" spans="1:11" hidden="1">
       <c r="A286" s="4">
         <v>285</v>
       </c>
@@ -15240,7 +15254,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="287" spans="1:11">
+    <row r="287" spans="1:11" hidden="1">
       <c r="A287" s="4">
         <v>286</v>
       </c>
@@ -15273,7 +15287,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="288" spans="1:11">
+    <row r="288" spans="1:11" hidden="1">
       <c r="A288" s="4">
         <v>287</v>
       </c>
@@ -15306,7 +15320,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="289" spans="1:11">
+    <row r="289" spans="1:11" hidden="1">
       <c r="A289" s="4">
         <v>288</v>
       </c>
@@ -15339,7 +15353,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="290" spans="1:11">
+    <row r="290" spans="1:11" hidden="1">
       <c r="A290" s="4">
         <v>289</v>
       </c>
@@ -15374,7 +15388,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="291" spans="1:11">
+    <row r="291" spans="1:11" hidden="1">
       <c r="A291" s="4">
         <v>290</v>
       </c>
@@ -15409,7 +15423,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="292" spans="1:11">
+    <row r="292" spans="1:11" hidden="1">
       <c r="A292" s="4">
         <v>291</v>
       </c>
@@ -15444,7 +15458,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="293" spans="1:11">
+    <row r="293" spans="1:11" hidden="1">
       <c r="A293" s="4">
         <v>292</v>
       </c>
@@ -15479,7 +15493,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="294" spans="1:11">
+    <row r="294" spans="1:11" hidden="1">
       <c r="A294" s="4">
         <v>293</v>
       </c>
@@ -15514,7 +15528,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="295" spans="1:11">
+    <row r="295" spans="1:11" hidden="1">
       <c r="A295" s="4">
         <v>294</v>
       </c>
@@ -15549,7 +15563,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="296" spans="1:11">
+    <row r="296" spans="1:11" hidden="1">
       <c r="A296" s="4">
         <v>295</v>
       </c>
@@ -15584,7 +15598,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="297" spans="1:11">
+    <row r="297" spans="1:11" hidden="1">
       <c r="A297" s="4">
         <v>296</v>
       </c>
@@ -15619,7 +15633,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="298" spans="1:11">
+    <row r="298" spans="1:11" hidden="1">
       <c r="A298" s="4">
         <v>297</v>
       </c>
@@ -15654,7 +15668,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="299" spans="1:11">
+    <row r="299" spans="1:11" hidden="1">
       <c r="A299" s="4">
         <v>298</v>
       </c>
@@ -15689,7 +15703,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="300" spans="1:11">
+    <row r="300" spans="1:11" hidden="1">
       <c r="A300" s="4">
         <v>299</v>
       </c>
@@ -15724,7 +15738,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="301" spans="1:11">
+    <row r="301" spans="1:11" hidden="1">
       <c r="A301" s="4">
         <v>300</v>
       </c>
@@ -15759,7 +15773,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="302" spans="1:11">
+    <row r="302" spans="1:11" hidden="1">
       <c r="A302" s="4">
         <v>301</v>
       </c>
@@ -15794,7 +15808,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="303" spans="1:11">
+    <row r="303" spans="1:11" hidden="1">
       <c r="A303" s="4">
         <v>302</v>
       </c>
@@ -15829,7 +15843,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="304" spans="1:11">
+    <row r="304" spans="1:11" hidden="1">
       <c r="A304" s="4">
         <v>303</v>
       </c>
@@ -15864,7 +15878,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="305" spans="1:11">
+    <row r="305" spans="1:11" hidden="1">
       <c r="A305" s="4">
         <v>304</v>
       </c>
@@ -15899,7 +15913,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="306" spans="1:11">
+    <row r="306" spans="1:11" hidden="1">
       <c r="A306" s="4">
         <v>305</v>
       </c>
@@ -15934,7 +15948,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="307" spans="1:11">
+    <row r="307" spans="1:11" hidden="1">
       <c r="A307" s="4">
         <v>306</v>
       </c>
@@ -15969,7 +15983,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="308" spans="1:11">
+    <row r="308" spans="1:11" hidden="1">
       <c r="A308" s="4">
         <v>307</v>
       </c>
@@ -16004,7 +16018,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="309" spans="1:11">
+    <row r="309" spans="1:11" hidden="1">
       <c r="A309" s="4">
         <v>308</v>
       </c>
@@ -16039,7 +16053,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="310" spans="1:11">
+    <row r="310" spans="1:11" hidden="1">
       <c r="A310" s="4">
         <v>309</v>
       </c>
@@ -16074,7 +16088,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="311" spans="1:11">
+    <row r="311" spans="1:11" hidden="1">
       <c r="A311" s="4">
         <v>310</v>
       </c>
@@ -16109,7 +16123,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="312" spans="1:11">
+    <row r="312" spans="1:11" hidden="1">
       <c r="A312" s="4">
         <v>311</v>
       </c>
@@ -16144,7 +16158,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="313" spans="1:11">
+    <row r="313" spans="1:11" hidden="1">
       <c r="A313" s="4">
         <v>312</v>
       </c>
@@ -16179,7 +16193,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="314" spans="1:11">
+    <row r="314" spans="1:11" hidden="1">
       <c r="A314" s="4">
         <v>313</v>
       </c>
@@ -16214,7 +16228,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="315" spans="1:11">
+    <row r="315" spans="1:11" hidden="1">
       <c r="A315" s="4">
         <v>314</v>
       </c>
@@ -16249,7 +16263,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="316" spans="1:11">
+    <row r="316" spans="1:11" hidden="1">
       <c r="A316" s="4">
         <v>315</v>
       </c>
@@ -16284,7 +16298,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="317" spans="1:11">
+    <row r="317" spans="1:11" hidden="1">
       <c r="A317" s="4">
         <v>316</v>
       </c>
@@ -16319,7 +16333,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="318" spans="1:11">
+    <row r="318" spans="1:11" hidden="1">
       <c r="A318" s="4">
         <v>317</v>
       </c>
@@ -16354,7 +16368,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="319" spans="1:11">
+    <row r="319" spans="1:11" hidden="1">
       <c r="A319" s="4">
         <v>318</v>
       </c>
@@ -16389,7 +16403,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="320" spans="1:11">
+    <row r="320" spans="1:11" hidden="1">
       <c r="A320" s="4">
         <v>319</v>
       </c>
@@ -16424,7 +16438,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="321" spans="1:11">
+    <row r="321" spans="1:11" hidden="1">
       <c r="A321" s="4">
         <v>320</v>
       </c>
@@ -16459,7 +16473,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="322" spans="1:11">
+    <row r="322" spans="1:11" hidden="1">
       <c r="A322" s="4">
         <v>321</v>
       </c>
@@ -16494,7 +16508,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="323" spans="1:11">
+    <row r="323" spans="1:11" hidden="1">
       <c r="A323" s="4">
         <v>322</v>
       </c>
@@ -16529,7 +16543,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="324" spans="1:11">
+    <row r="324" spans="1:11" hidden="1">
       <c r="A324" s="4">
         <v>323</v>
       </c>
@@ -16564,7 +16578,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="325" spans="1:11">
+    <row r="325" spans="1:11" hidden="1">
       <c r="A325" s="4">
         <v>324</v>
       </c>
@@ -16599,7 +16613,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="326" spans="1:11">
+    <row r="326" spans="1:11" hidden="1">
       <c r="A326" s="4">
         <v>325</v>
       </c>
@@ -16634,7 +16648,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="327" spans="1:11">
+    <row r="327" spans="1:11" hidden="1">
       <c r="A327" s="4">
         <v>326</v>
       </c>
@@ -16669,7 +16683,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="328" spans="1:11">
+    <row r="328" spans="1:11" hidden="1">
       <c r="A328" s="4">
         <v>327</v>
       </c>
@@ -16702,7 +16716,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="329" spans="1:11">
+    <row r="329" spans="1:11" hidden="1">
       <c r="A329" s="4">
         <v>328</v>
       </c>
@@ -16735,7 +16749,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="330" spans="1:11">
+    <row r="330" spans="1:11" hidden="1">
       <c r="A330" s="4">
         <v>329</v>
       </c>
@@ -16768,7 +16782,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="331" spans="1:11">
+    <row r="331" spans="1:11" hidden="1">
       <c r="A331" s="4">
         <v>330</v>
       </c>
@@ -16801,7 +16815,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="332" spans="1:11">
+    <row r="332" spans="1:11" hidden="1">
       <c r="A332" s="4">
         <v>331</v>
       </c>
@@ -16834,7 +16848,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="333" spans="1:11">
+    <row r="333" spans="1:11" hidden="1">
       <c r="A333" s="4">
         <v>332</v>
       </c>
@@ -16869,7 +16883,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="334" spans="1:11">
+    <row r="334" spans="1:11" hidden="1">
       <c r="A334" s="4">
         <v>333</v>
       </c>
@@ -16902,7 +16916,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="335" spans="1:11">
+    <row r="335" spans="1:11" hidden="1">
       <c r="A335" s="4">
         <v>334</v>
       </c>
@@ -16935,7 +16949,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="336" spans="1:11">
+    <row r="336" spans="1:11" hidden="1">
       <c r="A336" s="4">
         <v>335</v>
       </c>
@@ -16968,7 +16982,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="337" spans="1:11">
+    <row r="337" spans="1:11" hidden="1">
       <c r="A337" s="4">
         <v>336</v>
       </c>
@@ -17003,7 +17017,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="338" spans="1:11">
+    <row r="338" spans="1:11" hidden="1">
       <c r="A338" s="4">
         <v>337</v>
       </c>
@@ -17038,7 +17052,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="339" spans="1:11">
+    <row r="339" spans="1:11" hidden="1">
       <c r="A339" s="4">
         <v>338</v>
       </c>
@@ -17073,7 +17087,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="340" spans="1:11">
+    <row r="340" spans="1:11" hidden="1">
       <c r="A340" s="4">
         <v>339</v>
       </c>
@@ -17108,7 +17122,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="341" spans="1:11">
+    <row r="341" spans="1:11" hidden="1">
       <c r="A341" s="4">
         <v>340</v>
       </c>
@@ -17143,7 +17157,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="342" spans="1:11">
+    <row r="342" spans="1:11" hidden="1">
       <c r="A342" s="4">
         <v>341</v>
       </c>
@@ -17178,7 +17192,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="343" spans="1:11">
+    <row r="343" spans="1:11" hidden="1">
       <c r="A343" s="4">
         <v>342</v>
       </c>
@@ -17213,7 +17227,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="344" spans="1:11">
+    <row r="344" spans="1:11" hidden="1">
       <c r="A344" s="4">
         <v>343</v>
       </c>
@@ -17248,7 +17262,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="345" spans="1:11">
+    <row r="345" spans="1:11" hidden="1">
       <c r="A345" s="4">
         <v>344</v>
       </c>
@@ -17283,7 +17297,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="346" spans="1:11">
+    <row r="346" spans="1:11" hidden="1">
       <c r="A346" s="4">
         <v>345</v>
       </c>
@@ -17318,7 +17332,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="347" spans="1:11">
+    <row r="347" spans="1:11" hidden="1">
       <c r="A347" s="4">
         <v>346</v>
       </c>
@@ -17353,7 +17367,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="348" spans="1:11">
+    <row r="348" spans="1:11" hidden="1">
       <c r="A348" s="4">
         <v>347</v>
       </c>
@@ -17388,7 +17402,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="349" spans="1:11">
+    <row r="349" spans="1:11" hidden="1">
       <c r="A349" s="4">
         <v>348</v>
       </c>
@@ -17423,7 +17437,7 @@
         <v>1296</v>
       </c>
     </row>
-    <row r="350" spans="1:11">
+    <row r="350" spans="1:11" hidden="1">
       <c r="A350" s="4">
         <v>349</v>
       </c>
@@ -17458,7 +17472,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="351" spans="1:11">
+    <row r="351" spans="1:11" hidden="1">
       <c r="A351" s="4">
         <v>350</v>
       </c>
@@ -17493,7 +17507,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="352" spans="1:11">
+    <row r="352" spans="1:11" hidden="1">
       <c r="A352" s="4">
         <v>351</v>
       </c>
@@ -17528,7 +17542,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="353" spans="1:11">
+    <row r="353" spans="1:11" hidden="1">
       <c r="A353" s="4">
         <v>352</v>
       </c>
@@ -17563,7 +17577,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="354" spans="1:11">
+    <row r="354" spans="1:11" hidden="1">
       <c r="A354" s="4">
         <v>353</v>
       </c>
@@ -17598,7 +17612,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="355" spans="1:11">
+    <row r="355" spans="1:11" hidden="1">
       <c r="A355" s="4">
         <v>354</v>
       </c>
@@ -17633,7 +17647,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="356" spans="1:11">
+    <row r="356" spans="1:11" hidden="1">
       <c r="A356" s="4">
         <v>355</v>
       </c>
@@ -17668,7 +17682,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="357" spans="1:11">
+    <row r="357" spans="1:11" hidden="1">
       <c r="A357" s="4">
         <v>356</v>
       </c>
@@ -17703,7 +17717,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="358" spans="1:11">
+    <row r="358" spans="1:11" hidden="1">
       <c r="A358" s="4">
         <v>357</v>
       </c>
@@ -17738,7 +17752,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="359" spans="1:11">
+    <row r="359" spans="1:11" hidden="1">
       <c r="A359" s="4">
         <v>358</v>
       </c>
@@ -17773,7 +17787,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="360" spans="1:11">
+    <row r="360" spans="1:11" hidden="1">
       <c r="A360" s="4">
         <v>359</v>
       </c>
@@ -17808,7 +17822,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="361" spans="1:11">
+    <row r="361" spans="1:11" hidden="1">
       <c r="A361" s="4">
         <v>360</v>
       </c>
@@ -17843,7 +17857,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="362" spans="1:11">
+    <row r="362" spans="1:11" hidden="1">
       <c r="A362" s="4">
         <v>361</v>
       </c>
@@ -17878,7 +17892,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="363" spans="1:11">
+    <row r="363" spans="1:11" hidden="1">
       <c r="A363" s="4">
         <v>362</v>
       </c>
@@ -17913,7 +17927,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="364" spans="1:11">
+    <row r="364" spans="1:11" hidden="1">
       <c r="A364" s="4">
         <v>363</v>
       </c>
@@ -17948,7 +17962,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="365" spans="1:11">
+    <row r="365" spans="1:11" hidden="1">
       <c r="A365" s="4">
         <v>364</v>
       </c>
@@ -17981,7 +17995,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="366" spans="1:11">
+    <row r="366" spans="1:11" hidden="1">
       <c r="A366" s="4">
         <v>365</v>
       </c>
@@ -18016,7 +18030,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="367" spans="1:11">
+    <row r="367" spans="1:11" hidden="1">
       <c r="A367" s="4">
         <v>366</v>
       </c>
@@ -18051,7 +18065,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="368" spans="1:11">
+    <row r="368" spans="1:11" hidden="1">
       <c r="A368" s="4">
         <v>367</v>
       </c>
@@ -18086,7 +18100,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="369" spans="1:11">
+    <row r="369" spans="1:11" hidden="1">
       <c r="A369" s="4">
         <v>368</v>
       </c>
@@ -18121,7 +18135,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="370" spans="1:11">
+    <row r="370" spans="1:11" hidden="1">
       <c r="A370" s="4">
         <v>369</v>
       </c>
@@ -18156,7 +18170,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="371" spans="1:11">
+    <row r="371" spans="1:11" hidden="1">
       <c r="A371" s="4">
         <v>370</v>
       </c>
@@ -18191,7 +18205,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="372" spans="1:11">
+    <row r="372" spans="1:11" hidden="1">
       <c r="A372" s="4">
         <v>371</v>
       </c>
@@ -18226,7 +18240,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="373" spans="1:11">
+    <row r="373" spans="1:11" hidden="1">
       <c r="A373" s="4">
         <v>372</v>
       </c>
@@ -18261,7 +18275,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="374" spans="1:11">
+    <row r="374" spans="1:11" hidden="1">
       <c r="A374" s="4">
         <v>373</v>
       </c>
@@ -18296,7 +18310,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="375" spans="1:11">
+    <row r="375" spans="1:11" hidden="1">
       <c r="A375" s="4">
         <v>374</v>
       </c>
@@ -18331,7 +18345,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="376" spans="1:11">
+    <row r="376" spans="1:11" hidden="1">
       <c r="A376" s="4">
         <v>375</v>
       </c>
@@ -18366,7 +18380,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="377" spans="1:11">
+    <row r="377" spans="1:11" hidden="1">
       <c r="A377" s="4">
         <v>376</v>
       </c>
@@ -18401,7 +18415,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="378" spans="1:11">
+    <row r="378" spans="1:11" hidden="1">
       <c r="A378" s="4">
         <v>377</v>
       </c>
@@ -18436,7 +18450,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="379" spans="1:11">
+    <row r="379" spans="1:11" hidden="1">
       <c r="A379" s="4">
         <v>378</v>
       </c>
@@ -18471,7 +18485,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="380" spans="1:11">
+    <row r="380" spans="1:11" hidden="1">
       <c r="A380" s="4">
         <v>379</v>
       </c>
@@ -18506,7 +18520,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="381" spans="1:11">
+    <row r="381" spans="1:11" hidden="1">
       <c r="A381" s="4">
         <v>380</v>
       </c>
@@ -18541,7 +18555,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="382" spans="1:11">
+    <row r="382" spans="1:11" hidden="1">
       <c r="A382" s="4">
         <v>381</v>
       </c>
@@ -18576,7 +18590,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="383" spans="1:11">
+    <row r="383" spans="1:11" hidden="1">
       <c r="A383" s="4">
         <v>382</v>
       </c>
@@ -18611,7 +18625,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="384" spans="1:11">
+    <row r="384" spans="1:11" hidden="1">
       <c r="A384" s="4">
         <v>383</v>
       </c>
@@ -18646,7 +18660,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="385" spans="1:11">
+    <row r="385" spans="1:11" hidden="1">
       <c r="A385" s="4">
         <v>384</v>
       </c>
@@ -18681,7 +18695,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="386" spans="1:11">
+    <row r="386" spans="1:11" hidden="1">
       <c r="A386" s="4">
         <v>385</v>
       </c>
@@ -18716,7 +18730,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="387" spans="1:11">
+    <row r="387" spans="1:11" hidden="1">
       <c r="A387" s="4">
         <v>386</v>
       </c>
@@ -18751,7 +18765,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="388" spans="1:11">
+    <row r="388" spans="1:11" hidden="1">
       <c r="A388" s="4">
         <v>387</v>
       </c>
@@ -18786,7 +18800,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="389" spans="1:11">
+    <row r="389" spans="1:11" hidden="1">
       <c r="A389" s="4">
         <v>388</v>
       </c>
@@ -18821,7 +18835,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="390" spans="1:11">
+    <row r="390" spans="1:11" hidden="1">
       <c r="A390" s="4">
         <v>389</v>
       </c>
@@ -18856,7 +18870,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="391" spans="1:11">
+    <row r="391" spans="1:11" hidden="1">
       <c r="A391" s="4">
         <v>390</v>
       </c>
@@ -18891,7 +18905,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="392" spans="1:11">
+    <row r="392" spans="1:11" hidden="1">
       <c r="A392" s="4">
         <v>391</v>
       </c>
@@ -18961,7 +18975,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="394" spans="1:11">
+    <row r="394" spans="1:11" hidden="1">
       <c r="A394" s="4">
         <v>393</v>
       </c>
@@ -18994,7 +19008,7 @@
       </c>
       <c r="K394" s="55"/>
     </row>
-    <row r="395" spans="1:11">
+    <row r="395" spans="1:11" hidden="1">
       <c r="A395" s="4">
         <v>394</v>
       </c>
@@ -19027,7 +19041,7 @@
       </c>
       <c r="K395" s="55"/>
     </row>
-    <row r="396" spans="1:11">
+    <row r="396" spans="1:11" hidden="1">
       <c r="A396" s="4">
         <v>395</v>
       </c>
@@ -19060,7 +19074,7 @@
       </c>
       <c r="K396" s="55"/>
     </row>
-    <row r="397" spans="1:11">
+    <row r="397" spans="1:11" hidden="1">
       <c r="A397" s="4">
         <v>396</v>
       </c>
@@ -19095,7 +19109,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="398" spans="1:11">
+    <row r="398" spans="1:11" hidden="1">
       <c r="A398" s="4">
         <v>397</v>
       </c>
@@ -19130,7 +19144,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="399" spans="1:11">
+    <row r="399" spans="1:11" hidden="1">
       <c r="A399" s="4">
         <v>398</v>
       </c>
@@ -19165,7 +19179,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="400" spans="1:11">
+    <row r="400" spans="1:11" hidden="1">
       <c r="A400" s="4">
         <v>399</v>
       </c>
@@ -19235,7 +19249,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="402" spans="1:11">
+    <row r="402" spans="1:11" hidden="1">
       <c r="A402" s="4">
         <v>401</v>
       </c>
@@ -19270,7 +19284,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="403" spans="1:11">
+    <row r="403" spans="1:11" hidden="1">
       <c r="A403" s="4">
         <v>402</v>
       </c>
@@ -19305,7 +19319,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="404" spans="1:11">
+    <row r="404" spans="1:11" hidden="1">
       <c r="A404" s="4">
         <v>403</v>
       </c>
@@ -19340,7 +19354,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="405" spans="1:11">
+    <row r="405" spans="1:11" hidden="1">
       <c r="A405" s="4">
         <v>404</v>
       </c>
@@ -19375,7 +19389,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="406" spans="1:11">
+    <row r="406" spans="1:11" hidden="1">
       <c r="A406" s="4">
         <v>405</v>
       </c>
@@ -19410,7 +19424,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="407" spans="1:11">
+    <row r="407" spans="1:11" hidden="1">
       <c r="A407" s="4">
         <v>406</v>
       </c>
@@ -19445,7 +19459,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="408" spans="1:11">
+    <row r="408" spans="1:11" hidden="1">
       <c r="A408" s="4">
         <v>407</v>
       </c>
@@ -19480,7 +19494,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="409" spans="1:11">
+    <row r="409" spans="1:11" hidden="1">
       <c r="A409" s="4">
         <v>408</v>
       </c>
@@ -19515,7 +19529,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="410" spans="1:11">
+    <row r="410" spans="1:11" hidden="1">
       <c r="A410" s="4">
         <v>409</v>
       </c>
@@ -19550,7 +19564,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="411" spans="1:11">
+    <row r="411" spans="1:11" hidden="1">
       <c r="A411" s="4">
         <v>410</v>
       </c>
@@ -19583,7 +19597,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="412" spans="1:11">
+    <row r="412" spans="1:11" hidden="1">
       <c r="A412" s="4">
         <v>411</v>
       </c>
@@ -19618,7 +19632,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="413" spans="1:11">
+    <row r="413" spans="1:11" hidden="1">
       <c r="A413" s="4">
         <v>412</v>
       </c>
@@ -19653,7 +19667,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="414" spans="1:11">
+    <row r="414" spans="1:11" hidden="1">
       <c r="A414" s="4">
         <v>413</v>
       </c>
@@ -19688,7 +19702,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="415" spans="1:11">
+    <row r="415" spans="1:11" hidden="1">
       <c r="A415" s="4">
         <v>414</v>
       </c>
@@ -19723,7 +19737,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="416" spans="1:11">
+    <row r="416" spans="1:11" hidden="1">
       <c r="A416" s="4">
         <v>415</v>
       </c>
@@ -19756,7 +19770,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="417" spans="1:11">
+    <row r="417" spans="1:11" hidden="1">
       <c r="A417" s="4">
         <v>416</v>
       </c>
@@ -19791,7 +19805,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="418" spans="1:11">
+    <row r="418" spans="1:11" hidden="1">
       <c r="A418" s="4">
         <v>417</v>
       </c>
@@ -19826,7 +19840,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="419" spans="1:11">
+    <row r="419" spans="1:11" hidden="1">
       <c r="A419" s="4">
         <v>418</v>
       </c>
@@ -19861,7 +19875,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="420" spans="1:11">
+    <row r="420" spans="1:11" hidden="1">
       <c r="A420" s="4">
         <v>419</v>
       </c>
@@ -19896,7 +19910,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="421" spans="1:11">
+    <row r="421" spans="1:11" hidden="1">
       <c r="A421" s="4">
         <v>420</v>
       </c>
@@ -19931,7 +19945,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="422" spans="1:11">
+    <row r="422" spans="1:11" hidden="1">
       <c r="A422" s="4">
         <v>421</v>
       </c>
@@ -19966,7 +19980,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="423" spans="1:11">
+    <row r="423" spans="1:11" hidden="1">
       <c r="A423" s="4">
         <v>422</v>
       </c>
@@ -20001,7 +20015,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="424" spans="1:11">
+    <row r="424" spans="1:11" hidden="1">
       <c r="A424" s="4">
         <v>423</v>
       </c>
@@ -20036,7 +20050,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="425" spans="1:11">
+    <row r="425" spans="1:11" hidden="1">
       <c r="A425" s="4">
         <v>424</v>
       </c>
@@ -20071,7 +20085,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="426" spans="1:11">
+    <row r="426" spans="1:11" hidden="1">
       <c r="A426" s="4">
         <v>425</v>
       </c>
@@ -20106,7 +20120,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="427" spans="1:11">
+    <row r="427" spans="1:11" hidden="1">
       <c r="A427" s="4">
         <v>426</v>
       </c>
@@ -20141,7 +20155,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="428" spans="1:11">
+    <row r="428" spans="1:11" hidden="1">
       <c r="A428" s="4">
         <v>427</v>
       </c>
@@ -20176,7 +20190,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="429" spans="1:11">
+    <row r="429" spans="1:11" hidden="1">
       <c r="A429" s="4">
         <v>428</v>
       </c>
@@ -20211,7 +20225,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="430" spans="1:11">
+    <row r="430" spans="1:11" hidden="1">
       <c r="A430" s="4">
         <v>429</v>
       </c>
@@ -20246,7 +20260,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="431" spans="1:11">
+    <row r="431" spans="1:11" hidden="1">
       <c r="A431" s="4">
         <v>430</v>
       </c>
@@ -20281,7 +20295,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="432" spans="1:11">
+    <row r="432" spans="1:11" hidden="1">
       <c r="A432" s="4">
         <v>431</v>
       </c>
@@ -20316,7 +20330,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="433" spans="1:11">
+    <row r="433" spans="1:11" hidden="1">
       <c r="A433" s="4">
         <v>432</v>
       </c>
@@ -20351,7 +20365,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="434" spans="1:11">
+    <row r="434" spans="1:11" hidden="1">
       <c r="A434" s="4">
         <v>433</v>
       </c>
@@ -20384,7 +20398,7 @@
       </c>
       <c r="K434" s="55"/>
     </row>
-    <row r="435" spans="1:11">
+    <row r="435" spans="1:11" hidden="1">
       <c r="A435" s="4">
         <v>434</v>
       </c>
@@ -20417,7 +20431,7 @@
       </c>
       <c r="K435" s="55"/>
     </row>
-    <row r="436" spans="1:11">
+    <row r="436" spans="1:11" hidden="1">
       <c r="A436" s="4">
         <v>435</v>
       </c>
@@ -20450,7 +20464,7 @@
       </c>
       <c r="K436" s="55"/>
     </row>
-    <row r="437" spans="1:11">
+    <row r="437" spans="1:11" hidden="1">
       <c r="A437" s="4">
         <v>436</v>
       </c>
@@ -20483,7 +20497,7 @@
       </c>
       <c r="K437" s="55"/>
     </row>
-    <row r="438" spans="1:11">
+    <row r="438" spans="1:11" hidden="1">
       <c r="A438" s="4">
         <v>437</v>
       </c>
@@ -20516,7 +20530,7 @@
       </c>
       <c r="K438" s="55"/>
     </row>
-    <row r="439" spans="1:11">
+    <row r="439" spans="1:11" hidden="1">
       <c r="A439" s="4">
         <v>438</v>
       </c>
@@ -20549,7 +20563,7 @@
       </c>
       <c r="K439" s="55"/>
     </row>
-    <row r="440" spans="1:11">
+    <row r="440" spans="1:11" hidden="1">
       <c r="A440" s="4">
         <v>439</v>
       </c>
@@ -20582,7 +20596,7 @@
       </c>
       <c r="K440" s="55"/>
     </row>
-    <row r="441" spans="1:11">
+    <row r="441" spans="1:11" hidden="1">
       <c r="A441" s="4">
         <v>440</v>
       </c>
@@ -20615,7 +20629,7 @@
       </c>
       <c r="K441" s="55"/>
     </row>
-    <row r="442" spans="1:11">
+    <row r="442" spans="1:11" hidden="1">
       <c r="A442" s="4">
         <v>441</v>
       </c>
@@ -20648,7 +20662,7 @@
       </c>
       <c r="K442" s="55"/>
     </row>
-    <row r="443" spans="1:11">
+    <row r="443" spans="1:11" hidden="1">
       <c r="A443" s="4">
         <v>442</v>
       </c>
@@ -20681,7 +20695,7 @@
       </c>
       <c r="K443" s="55"/>
     </row>
-    <row r="444" spans="1:11">
+    <row r="444" spans="1:11" hidden="1">
       <c r="A444" s="4">
         <v>443</v>
       </c>
@@ -20714,7 +20728,7 @@
       </c>
       <c r="K444" s="55"/>
     </row>
-    <row r="445" spans="1:11">
+    <row r="445" spans="1:11" hidden="1">
       <c r="A445" s="4">
         <v>444</v>
       </c>
@@ -20747,7 +20761,7 @@
       </c>
       <c r="K445" s="55"/>
     </row>
-    <row r="446" spans="1:11">
+    <row r="446" spans="1:11" hidden="1">
       <c r="A446" s="4">
         <v>445</v>
       </c>
@@ -20780,7 +20794,7 @@
       </c>
       <c r="K446" s="55"/>
     </row>
-    <row r="447" spans="1:11">
+    <row r="447" spans="1:11" hidden="1">
       <c r="A447" s="4">
         <v>446</v>
       </c>
@@ -20813,7 +20827,7 @@
       </c>
       <c r="K447" s="55"/>
     </row>
-    <row r="448" spans="1:11">
+    <row r="448" spans="1:11" hidden="1">
       <c r="A448" s="4">
         <v>447</v>
       </c>
@@ -20846,7 +20860,7 @@
       </c>
       <c r="K448" s="55"/>
     </row>
-    <row r="449" spans="1:11">
+    <row r="449" spans="1:11" hidden="1">
       <c r="A449" s="4">
         <v>448</v>
       </c>
@@ -20879,7 +20893,7 @@
       </c>
       <c r="K449" s="55"/>
     </row>
-    <row r="450" spans="1:11">
+    <row r="450" spans="1:11" hidden="1">
       <c r="A450" s="4">
         <v>449</v>
       </c>
@@ -20912,7 +20926,7 @@
       </c>
       <c r="K450" s="55"/>
     </row>
-    <row r="451" spans="1:11">
+    <row r="451" spans="1:11" hidden="1">
       <c r="A451" s="4">
         <v>450</v>
       </c>
@@ -20945,7 +20959,7 @@
       </c>
       <c r="K451" s="55"/>
     </row>
-    <row r="452" spans="1:11">
+    <row r="452" spans="1:11" hidden="1">
       <c r="A452" s="4">
         <v>451</v>
       </c>
@@ -20978,7 +20992,7 @@
       </c>
       <c r="K452" s="55"/>
     </row>
-    <row r="453" spans="1:11">
+    <row r="453" spans="1:11" hidden="1">
       <c r="A453" s="4">
         <v>452</v>
       </c>
@@ -21011,7 +21025,7 @@
       </c>
       <c r="K453" s="55"/>
     </row>
-    <row r="454" spans="1:11">
+    <row r="454" spans="1:11" hidden="1">
       <c r="A454" s="4">
         <v>453</v>
       </c>
@@ -21044,7 +21058,7 @@
       </c>
       <c r="K454" s="55"/>
     </row>
-    <row r="455" spans="1:11">
+    <row r="455" spans="1:11" hidden="1">
       <c r="A455" s="4">
         <v>454</v>
       </c>
@@ -21077,7 +21091,7 @@
       </c>
       <c r="K455" s="55"/>
     </row>
-    <row r="456" spans="1:11">
+    <row r="456" spans="1:11" hidden="1">
       <c r="A456" s="4">
         <v>455</v>
       </c>
@@ -21110,7 +21124,7 @@
       </c>
       <c r="K456" s="55"/>
     </row>
-    <row r="457" spans="1:11">
+    <row r="457" spans="1:11" hidden="1">
       <c r="A457" s="4">
         <v>456</v>
       </c>
@@ -21143,7 +21157,7 @@
       </c>
       <c r="K457" s="55"/>
     </row>
-    <row r="458" spans="1:11">
+    <row r="458" spans="1:11" hidden="1">
       <c r="A458" s="4">
         <v>457</v>
       </c>
@@ -21176,7 +21190,7 @@
       </c>
       <c r="K458" s="55"/>
     </row>
-    <row r="459" spans="1:11">
+    <row r="459" spans="1:11" hidden="1">
       <c r="A459" s="4">
         <v>458</v>
       </c>
@@ -21209,7 +21223,7 @@
       </c>
       <c r="K459" s="55"/>
     </row>
-    <row r="460" spans="1:11">
+    <row r="460" spans="1:11" hidden="1">
       <c r="A460" s="4">
         <v>459</v>
       </c>
@@ -21242,7 +21256,7 @@
       </c>
       <c r="K460" s="55"/>
     </row>
-    <row r="461" spans="1:11">
+    <row r="461" spans="1:11" hidden="1">
       <c r="A461" s="4">
         <v>460</v>
       </c>
@@ -21275,7 +21289,7 @@
       </c>
       <c r="K461" s="55"/>
     </row>
-    <row r="462" spans="1:11">
+    <row r="462" spans="1:11" hidden="1">
       <c r="A462" s="4">
         <v>461</v>
       </c>
@@ -21308,7 +21322,7 @@
       </c>
       <c r="K462" s="55"/>
     </row>
-    <row r="463" spans="1:11">
+    <row r="463" spans="1:11" hidden="1">
       <c r="A463" s="4">
         <v>462</v>
       </c>
@@ -21341,7 +21355,7 @@
       </c>
       <c r="K463" s="55"/>
     </row>
-    <row r="464" spans="1:11">
+    <row r="464" spans="1:11" hidden="1">
       <c r="A464" s="4">
         <v>463</v>
       </c>
@@ -21374,7 +21388,7 @@
       </c>
       <c r="K464" s="55"/>
     </row>
-    <row r="465" spans="1:11">
+    <row r="465" spans="1:11" hidden="1">
       <c r="A465" s="4">
         <v>464</v>
       </c>
@@ -21407,7 +21421,7 @@
       </c>
       <c r="K465" s="55"/>
     </row>
-    <row r="466" spans="1:11">
+    <row r="466" spans="1:11" hidden="1">
       <c r="A466" s="4">
         <v>465</v>
       </c>
@@ -21440,7 +21454,7 @@
       </c>
       <c r="K466" s="55"/>
     </row>
-    <row r="467" spans="1:11">
+    <row r="467" spans="1:11" hidden="1">
       <c r="A467" s="4">
         <v>466</v>
       </c>
@@ -21473,7 +21487,7 @@
       </c>
       <c r="K467" s="55"/>
     </row>
-    <row r="468" spans="1:11">
+    <row r="468" spans="1:11" hidden="1">
       <c r="A468" s="4">
         <v>467</v>
       </c>
@@ -21506,7 +21520,7 @@
       </c>
       <c r="K468" s="55"/>
     </row>
-    <row r="469" spans="1:11">
+    <row r="469" spans="1:11" hidden="1">
       <c r="A469" s="4">
         <v>468</v>
       </c>
@@ -21539,7 +21553,7 @@
       </c>
       <c r="K469" s="55"/>
     </row>
-    <row r="470" spans="1:11">
+    <row r="470" spans="1:11" hidden="1">
       <c r="A470" s="4">
         <v>469</v>
       </c>
@@ -21572,7 +21586,7 @@
       </c>
       <c r="K470" s="55"/>
     </row>
-    <row r="471" spans="1:11">
+    <row r="471" spans="1:11" hidden="1">
       <c r="A471" s="4">
         <v>470</v>
       </c>
@@ -21605,7 +21619,7 @@
       </c>
       <c r="K471" s="55"/>
     </row>
-    <row r="472" spans="1:11">
+    <row r="472" spans="1:11" hidden="1">
       <c r="A472" s="4">
         <v>471</v>
       </c>
@@ -21638,7 +21652,7 @@
       </c>
       <c r="K472" s="55"/>
     </row>
-    <row r="473" spans="1:11">
+    <row r="473" spans="1:11" hidden="1">
       <c r="A473" s="4">
         <v>472</v>
       </c>
@@ -21673,7 +21687,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="474" spans="1:11">
+    <row r="474" spans="1:11" hidden="1">
       <c r="A474" s="4">
         <v>473</v>
       </c>
@@ -21708,7 +21722,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="475" spans="1:11">
+    <row r="475" spans="1:11" hidden="1">
       <c r="A475" s="4">
         <v>474</v>
       </c>
@@ -21743,7 +21757,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="476" spans="1:11">
+    <row r="476" spans="1:11" hidden="1">
       <c r="A476" s="4">
         <v>475</v>
       </c>
@@ -21778,7 +21792,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="477" spans="1:11">
+    <row r="477" spans="1:11" hidden="1">
       <c r="A477" s="4">
         <v>476</v>
       </c>
@@ -21813,7 +21827,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="478" spans="1:11">
+    <row r="478" spans="1:11" hidden="1">
       <c r="A478" s="4">
         <v>477</v>
       </c>
@@ -21848,7 +21862,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="479" spans="1:11">
+    <row r="479" spans="1:11" hidden="1">
       <c r="A479" s="4">
         <v>478</v>
       </c>
@@ -21883,7 +21897,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="480" spans="1:11">
+    <row r="480" spans="1:11" hidden="1">
       <c r="A480" s="4">
         <v>479</v>
       </c>
@@ -21918,7 +21932,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="481" spans="1:11">
+    <row r="481" spans="1:11" hidden="1">
       <c r="A481" s="4">
         <v>480</v>
       </c>
@@ -21953,7 +21967,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="482" spans="1:11">
+    <row r="482" spans="1:11" hidden="1">
       <c r="A482" s="4">
         <v>481</v>
       </c>
@@ -21988,7 +22002,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="483" spans="1:11">
+    <row r="483" spans="1:11" hidden="1">
       <c r="A483" s="4">
         <v>482</v>
       </c>
@@ -22023,7 +22037,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="484" spans="1:11">
+    <row r="484" spans="1:11" hidden="1">
       <c r="A484" s="4">
         <v>483</v>
       </c>
@@ -22058,7 +22072,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="485" spans="1:11">
+    <row r="485" spans="1:11" hidden="1">
       <c r="A485" s="4">
         <v>484</v>
       </c>
@@ -22093,7 +22107,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="486" spans="1:11">
+    <row r="486" spans="1:11" hidden="1">
       <c r="A486" s="4">
         <v>485</v>
       </c>
@@ -22128,7 +22142,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="487" spans="1:11">
+    <row r="487" spans="1:11" hidden="1">
       <c r="A487" s="4">
         <v>486</v>
       </c>
@@ -22163,7 +22177,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="488" spans="1:11">
+    <row r="488" spans="1:11" hidden="1">
       <c r="A488" s="4">
         <v>487</v>
       </c>
@@ -22198,7 +22212,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="489" spans="1:11">
+    <row r="489" spans="1:11" hidden="1">
       <c r="A489" s="4">
         <v>488</v>
       </c>
@@ -22233,7 +22247,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="490" spans="1:11">
+    <row r="490" spans="1:11" hidden="1">
       <c r="A490" s="4">
         <v>489</v>
       </c>
@@ -22266,7 +22280,7 @@
       </c>
       <c r="K490" s="24"/>
     </row>
-    <row r="491" spans="1:11">
+    <row r="491" spans="1:11" hidden="1">
       <c r="A491" s="4">
         <v>490</v>
       </c>
@@ -22301,7 +22315,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="492" spans="1:11">
+    <row r="492" spans="1:11" hidden="1">
       <c r="A492" s="4">
         <v>491</v>
       </c>
@@ -22336,7 +22350,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="493" spans="1:11">
+    <row r="493" spans="1:11" hidden="1">
       <c r="A493" s="4">
         <v>492</v>
       </c>
@@ -22371,7 +22385,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="494" spans="1:11">
+    <row r="494" spans="1:11" hidden="1">
       <c r="A494" s="4">
         <v>493</v>
       </c>
@@ -22406,7 +22420,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="495" spans="1:11">
+    <row r="495" spans="1:11" hidden="1">
       <c r="A495" s="4">
         <v>494</v>
       </c>
@@ -22441,7 +22455,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="496" spans="1:11">
+    <row r="496" spans="1:11" hidden="1">
       <c r="A496" s="4">
         <v>495</v>
       </c>
@@ -22476,7 +22490,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="497" spans="1:11">
+    <row r="497" spans="1:11" hidden="1">
       <c r="A497" s="4">
         <v>496</v>
       </c>
@@ -22511,7 +22525,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="498" spans="1:11">
+    <row r="498" spans="1:11" hidden="1">
       <c r="A498" s="4">
         <v>497</v>
       </c>
@@ -22546,7 +22560,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="499" spans="1:11">
+    <row r="499" spans="1:11" hidden="1">
       <c r="A499" s="4">
         <v>498</v>
       </c>
@@ -22581,7 +22595,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="500" spans="1:11">
+    <row r="500" spans="1:11" hidden="1">
       <c r="A500" s="4">
         <v>499</v>
       </c>
@@ -22616,7 +22630,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="501" spans="1:11">
+    <row r="501" spans="1:11" hidden="1">
       <c r="A501" s="4">
         <v>500</v>
       </c>
@@ -22651,7 +22665,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="502" spans="1:11">
+    <row r="502" spans="1:11" hidden="1">
       <c r="A502" s="4">
         <v>501</v>
       </c>
@@ -22719,7 +22733,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="504" spans="1:11">
+    <row r="504" spans="1:11" hidden="1">
       <c r="A504" s="4">
         <v>503</v>
       </c>
@@ -22752,7 +22766,7 @@
       </c>
       <c r="K504" s="24"/>
     </row>
-    <row r="505" spans="1:11">
+    <row r="505" spans="1:11" hidden="1">
       <c r="A505" s="4">
         <v>504</v>
       </c>
@@ -22785,7 +22799,7 @@
       </c>
       <c r="K505" s="24"/>
     </row>
-    <row r="506" spans="1:11">
+    <row r="506" spans="1:11" hidden="1">
       <c r="A506" s="4">
         <v>505</v>
       </c>
@@ -22818,7 +22832,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="507" spans="1:11">
+    <row r="507" spans="1:11" hidden="1">
       <c r="A507" s="4">
         <v>506</v>
       </c>
@@ -22950,7 +22964,7 @@
       </c>
       <c r="K510" s="24"/>
     </row>
-    <row r="511" spans="1:11">
+    <row r="511" spans="1:11" hidden="1">
       <c r="A511" s="4">
         <v>510</v>
       </c>
@@ -22983,7 +22997,7 @@
       </c>
       <c r="K511" s="24"/>
     </row>
-    <row r="512" spans="1:11">
+    <row r="512" spans="1:11" hidden="1">
       <c r="A512" s="4">
         <v>511</v>
       </c>
@@ -23016,7 +23030,7 @@
       </c>
       <c r="K512" s="24"/>
     </row>
-    <row r="513" spans="1:11">
+    <row r="513" spans="1:11" hidden="1">
       <c r="A513" s="4">
         <v>512</v>
       </c>
@@ -23049,7 +23063,7 @@
       </c>
       <c r="K513" s="55"/>
     </row>
-    <row r="514" spans="1:11">
+    <row r="514" spans="1:11" hidden="1">
       <c r="A514" s="4">
         <v>513</v>
       </c>
@@ -23082,7 +23096,7 @@
       </c>
       <c r="K514" s="55"/>
     </row>
-    <row r="515" spans="1:11">
+    <row r="515" spans="1:11" hidden="1">
       <c r="A515" s="4">
         <v>514</v>
       </c>
@@ -23115,7 +23129,7 @@
       </c>
       <c r="K515" s="55"/>
     </row>
-    <row r="516" spans="1:11">
+    <row r="516" spans="1:11" hidden="1">
       <c r="A516" s="4">
         <v>515</v>
       </c>
@@ -23148,7 +23162,7 @@
       </c>
       <c r="K516" s="55"/>
     </row>
-    <row r="517" spans="1:11">
+    <row r="517" spans="1:11" hidden="1">
       <c r="A517" s="4">
         <v>516</v>
       </c>
@@ -24416,7 +24430,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="555" spans="1:11">
+    <row r="555" spans="1:11" hidden="1">
       <c r="A555" s="4">
         <v>554</v>
       </c>
@@ -24625,7 +24639,7 @@
         <v>11</v>
       </c>
       <c r="D561" s="2" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="E561" s="1" t="s">
         <v>19</v>
@@ -24658,29 +24672,29 @@
         <v>11</v>
       </c>
       <c r="D562" s="2" t="s">
-        <v>1360</v>
+        <v>1441</v>
       </c>
       <c r="E562" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F562" s="1" t="s">
-        <v>521</v>
+        <v>1054</v>
       </c>
       <c r="G562" s="1" t="s">
         <v>30</v>
       </c>
       <c r="H562" s="1" t="s">
-        <v>1361</v>
+        <v>1340</v>
       </c>
       <c r="I562" s="54">
         <v>46279</v>
       </c>
       <c r="J562" s="4" t="s">
-        <v>574</v>
+        <v>645</v>
       </c>
       <c r="K562" s="55"/>
     </row>
-    <row r="563" spans="1:11">
+    <row r="563" spans="1:11" hidden="1">
       <c r="A563" s="4">
         <v>562</v>
       </c>
@@ -24713,7 +24727,7 @@
       </c>
       <c r="K563" s="55"/>
     </row>
-    <row r="564" spans="1:11">
+    <row r="564" spans="1:11" hidden="1">
       <c r="A564" s="4">
         <v>563</v>
       </c>
@@ -24746,7 +24760,7 @@
       </c>
       <c r="K564" s="55"/>
     </row>
-    <row r="565" spans="1:11">
+    <row r="565" spans="1:11" hidden="1">
       <c r="A565" s="4">
         <v>564</v>
       </c>
@@ -24779,7 +24793,7 @@
       </c>
       <c r="K565" s="55"/>
     </row>
-    <row r="566" spans="1:11">
+    <row r="566" spans="1:11" hidden="1">
       <c r="A566" s="4">
         <v>565</v>
       </c>
@@ -24812,7 +24826,7 @@
       </c>
       <c r="K566" s="55"/>
     </row>
-    <row r="567" spans="1:11">
+    <row r="567" spans="1:11" hidden="1">
       <c r="A567" s="4">
         <v>566</v>
       </c>
@@ -24845,7 +24859,7 @@
       </c>
       <c r="K567" s="55"/>
     </row>
-    <row r="568" spans="1:11">
+    <row r="568" spans="1:11" hidden="1">
       <c r="A568" s="4">
         <v>567</v>
       </c>
@@ -24878,7 +24892,7 @@
       </c>
       <c r="K568" s="55"/>
     </row>
-    <row r="569" spans="1:11">
+    <row r="569" spans="1:11" hidden="1">
       <c r="A569" s="4">
         <v>568</v>
       </c>
@@ -24911,7 +24925,7 @@
       </c>
       <c r="K569" s="55"/>
     </row>
-    <row r="570" spans="1:11">
+    <row r="570" spans="1:11" hidden="1">
       <c r="A570" s="4">
         <v>569</v>
       </c>
@@ -24944,7 +24958,7 @@
       </c>
       <c r="K570" s="55"/>
     </row>
-    <row r="571" spans="1:11">
+    <row r="571" spans="1:11" hidden="1">
       <c r="A571" s="4">
         <v>570</v>
       </c>
@@ -24977,7 +24991,7 @@
       </c>
       <c r="K571" s="55"/>
     </row>
-    <row r="572" spans="1:11">
+    <row r="572" spans="1:11" hidden="1">
       <c r="A572" s="4">
         <v>571</v>
       </c>
@@ -25010,7 +25024,7 @@
       </c>
       <c r="K572" s="55"/>
     </row>
-    <row r="573" spans="1:11">
+    <row r="573" spans="1:11" hidden="1">
       <c r="A573" s="4">
         <v>572</v>
       </c>
@@ -25043,7 +25057,7 @@
       </c>
       <c r="K573" s="55"/>
     </row>
-    <row r="574" spans="1:11">
+    <row r="574" spans="1:11" hidden="1">
       <c r="A574" s="4">
         <v>573</v>
       </c>
@@ -25076,7 +25090,7 @@
       </c>
       <c r="K574" s="55"/>
     </row>
-    <row r="575" spans="1:11">
+    <row r="575" spans="1:11" hidden="1">
       <c r="A575" s="4">
         <v>574</v>
       </c>
@@ -25109,7 +25123,7 @@
       </c>
       <c r="K575" s="55"/>
     </row>
-    <row r="576" spans="1:11">
+    <row r="576" spans="1:11" hidden="1">
       <c r="A576" s="4">
         <v>575</v>
       </c>
@@ -25142,7 +25156,7 @@
       </c>
       <c r="K576" s="55"/>
     </row>
-    <row r="577" spans="1:11">
+    <row r="577" spans="1:11" hidden="1">
       <c r="A577" s="4">
         <v>576</v>
       </c>
@@ -25175,7 +25189,7 @@
       </c>
       <c r="K577" s="55"/>
     </row>
-    <row r="578" spans="1:11">
+    <row r="578" spans="1:11" hidden="1">
       <c r="A578" s="4">
         <v>577</v>
       </c>
@@ -25208,7 +25222,7 @@
       </c>
       <c r="K578" s="55"/>
     </row>
-    <row r="579" spans="1:11">
+    <row r="579" spans="1:11" hidden="1">
       <c r="A579" s="4">
         <v>578</v>
       </c>
@@ -25222,10 +25236,10 @@
         <v>1239</v>
       </c>
       <c r="E579" s="1" t="s">
-        <v>960</v>
+        <v>21</v>
       </c>
       <c r="F579" s="1" t="s">
-        <v>373</v>
+        <v>605</v>
       </c>
       <c r="G579" s="1" t="s">
         <v>30</v>
@@ -25239,7 +25253,7 @@
       </c>
       <c r="K579" s="24"/>
     </row>
-    <row r="580" spans="1:11">
+    <row r="580" spans="1:11" hidden="1">
       <c r="A580" s="4">
         <v>579</v>
       </c>
@@ -25253,10 +25267,10 @@
         <v>1262</v>
       </c>
       <c r="E580" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F580" s="1" t="s">
-        <v>23</v>
+        <v>605</v>
       </c>
       <c r="G580" s="1" t="s">
         <v>30</v>
@@ -25306,6 +25320,8 @@
     <cfRule type="cellIs" dxfId="31" priority="16" operator="equal">
       <formula>"DOADORA"</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F254:F255 F561:F1048576 F1:F252">
     <cfRule type="cellIs" dxfId="30" priority="24" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
@@ -25313,7 +25329,7 @@
       <formula>"DEPOSITO SOLAGOS"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F366">
+  <conditionalFormatting sqref="F257:F559">
     <cfRule type="cellIs" dxfId="28" priority="20" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>

--- a/data_printer.xlsx
+++ b/data_printer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erick\Desktop\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41EB6BF8-9C2D-4B0F-AE13-E522B4FE54BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{933AE2F3-B21E-4CE0-B010-F688021A3E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A8AA41B5-7AA1-4FF7-A9B8-54B8A4E1AF28}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{A8AA41B5-7AA1-4FF7-A9B8-54B8A4E1AF28}"/>
   </bookViews>
   <sheets>
     <sheet name="PRINTERS_INVENTORY" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5318" uniqueCount="1445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5344" uniqueCount="1455">
   <si>
     <t>INDICE</t>
   </si>
@@ -4241,9 +4241,6 @@
     <t>E. CAMARON</t>
   </si>
   <si>
-    <t>INFORMATICA</t>
-  </si>
-  <si>
     <t>UPA - CONSULTORIO 02</t>
   </si>
   <si>
@@ -4373,9 +4370,6 @@
     <t>XC75053941</t>
   </si>
   <si>
-    <t>XC750539</t>
-  </si>
-  <si>
     <t>CANIBALIZADA</t>
   </si>
   <si>
@@ -4383,6 +4377,42 @@
   </si>
   <si>
     <t>BOA</t>
+  </si>
+  <si>
+    <t>XC75053780</t>
+  </si>
+  <si>
+    <t>XC75053947</t>
+  </si>
+  <si>
+    <t>XC75053944</t>
+  </si>
+  <si>
+    <t>XC75053942</t>
+  </si>
+  <si>
+    <t>XC75053777</t>
+  </si>
+  <si>
+    <t>XC75053810</t>
+  </si>
+  <si>
+    <t>XC75053939</t>
+  </si>
+  <si>
+    <t>XC75053</t>
+  </si>
+  <si>
+    <t>SESAU - INFORMATICA</t>
+  </si>
+  <si>
+    <t>SUCATA</t>
+  </si>
+  <si>
+    <t>SEDUC FINANCEIRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEIXOU ENTRAR AGUA NA IMPRESSORA </t>
   </si>
 </sst>
 </file>
@@ -4594,7 +4624,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4750,6 +4780,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -5545,13 +5578,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}" name="Controle_Inventario_Impressoras" displayName="Controle_Inventario_Impressoras" ref="A1:K580" tableType="queryTable" totalsRowShown="0" headerRowDxfId="67" dataDxfId="66">
-  <autoFilter ref="A1:K580" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="SEDUC"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:K580" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K37">
     <sortCondition ref="A23"/>
   </sortState>
@@ -5955,7 +5982,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" hidden="1">
+    <row r="2" spans="1:11">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -5988,7 +6015,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="3" spans="1:11" hidden="1">
+    <row r="3" spans="1:11">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -6021,7 +6048,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:11" hidden="1">
+    <row r="4" spans="1:11">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -6054,7 +6081,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="5" spans="1:11" hidden="1">
+    <row r="5" spans="1:11">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -6087,7 +6114,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="6" spans="1:11" hidden="1">
+    <row r="6" spans="1:11">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -6120,7 +6147,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="7" spans="1:11" hidden="1">
+    <row r="7" spans="1:11">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -6153,7 +6180,7 @@
       </c>
       <c r="K7" s="55"/>
     </row>
-    <row r="8" spans="1:11" hidden="1">
+    <row r="8" spans="1:11">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -6186,7 +6213,7 @@
       </c>
       <c r="K8" s="55"/>
     </row>
-    <row r="9" spans="1:11" hidden="1">
+    <row r="9" spans="1:11">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -6219,7 +6246,7 @@
       </c>
       <c r="K9" s="55"/>
     </row>
-    <row r="10" spans="1:11" hidden="1">
+    <row r="10" spans="1:11">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -6252,7 +6279,7 @@
       </c>
       <c r="K10" s="55"/>
     </row>
-    <row r="11" spans="1:11" hidden="1">
+    <row r="11" spans="1:11">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -6285,7 +6312,7 @@
       </c>
       <c r="K11" s="55"/>
     </row>
-    <row r="12" spans="1:11" hidden="1">
+    <row r="12" spans="1:11">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -6318,7 +6345,7 @@
       </c>
       <c r="K12" s="55"/>
     </row>
-    <row r="13" spans="1:11" hidden="1">
+    <row r="13" spans="1:11">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -6351,7 +6378,7 @@
       </c>
       <c r="K13" s="55"/>
     </row>
-    <row r="14" spans="1:11" hidden="1">
+    <row r="14" spans="1:11">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -6384,7 +6411,7 @@
       </c>
       <c r="K14" s="55"/>
     </row>
-    <row r="15" spans="1:11" hidden="1">
+    <row r="15" spans="1:11">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -6417,7 +6444,7 @@
       </c>
       <c r="K15" s="55"/>
     </row>
-    <row r="16" spans="1:11" hidden="1">
+    <row r="16" spans="1:11">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -6450,7 +6477,7 @@
       </c>
       <c r="K16" s="55"/>
     </row>
-    <row r="17" spans="1:11" hidden="1">
+    <row r="17" spans="1:11">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -6483,7 +6510,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="18" spans="1:11" hidden="1">
+    <row r="18" spans="1:11">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -6516,7 +6543,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:11" hidden="1">
+    <row r="19" spans="1:11">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -6547,7 +6574,7 @@
       </c>
       <c r="K19" s="7"/>
     </row>
-    <row r="20" spans="1:11" hidden="1">
+    <row r="20" spans="1:11">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -6578,7 +6605,7 @@
       </c>
       <c r="K20" s="7"/>
     </row>
-    <row r="21" spans="1:11" hidden="1">
+    <row r="21" spans="1:11">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -6613,7 +6640,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="22" spans="1:11" hidden="1">
+    <row r="22" spans="1:11">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -6648,7 +6675,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="23" spans="1:11" hidden="1">
+    <row r="23" spans="1:11">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -6681,7 +6708,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="24" spans="1:11" hidden="1">
+    <row r="24" spans="1:11">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -6716,7 +6743,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="25" spans="1:11" hidden="1">
+    <row r="25" spans="1:11">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -6749,7 +6776,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="26" spans="1:11" hidden="1">
+    <row r="26" spans="1:11">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -6779,7 +6806,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="27" spans="1:11" hidden="1">
+    <row r="27" spans="1:11">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -6812,7 +6839,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:11" hidden="1">
+    <row r="28" spans="1:11">
       <c r="A28" s="4">
         <v>27</v>
       </c>
@@ -6845,7 +6872,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:11" hidden="1">
+    <row r="29" spans="1:11">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -6892,10 +6919,10 @@
         <v>50</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>1047</v>
+        <v>23</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>14</v>
@@ -6913,7 +6940,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="31" spans="1:11" hidden="1">
+    <row r="31" spans="1:11">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -6946,7 +6973,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="15.75" hidden="1" customHeight="1">
+    <row r="32" spans="1:11" ht="15.75" customHeight="1">
       <c r="A32" s="4">
         <v>31</v>
       </c>
@@ -6979,7 +7006,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="33" spans="1:11" hidden="1">
+    <row r="33" spans="1:11">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -7012,7 +7039,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="34" spans="1:11" hidden="1">
+    <row r="34" spans="1:11">
       <c r="A34" s="4">
         <v>33</v>
       </c>
@@ -7045,7 +7072,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="35" spans="1:11" hidden="1">
+    <row r="35" spans="1:11">
       <c r="A35" s="4">
         <v>34</v>
       </c>
@@ -7078,7 +7105,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="36" spans="1:11" hidden="1">
+    <row r="36" spans="1:11">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -7108,7 +7135,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="37" spans="1:11" hidden="1">
+    <row r="37" spans="1:11">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -7138,7 +7165,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="38" spans="1:11" hidden="1">
+    <row r="38" spans="1:11">
       <c r="A38" s="4">
         <v>37</v>
       </c>
@@ -7171,7 +7198,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="39" spans="1:11" hidden="1">
+    <row r="39" spans="1:11">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -7204,7 +7231,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="40" spans="1:11" hidden="1">
+    <row r="40" spans="1:11">
       <c r="A40" s="4">
         <v>39</v>
       </c>
@@ -7237,7 +7264,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="41" spans="1:11" hidden="1">
+    <row r="41" spans="1:11">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -7270,7 +7297,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="42" spans="1:11" hidden="1">
+    <row r="42" spans="1:11">
       <c r="A42" s="4">
         <v>41</v>
       </c>
@@ -7303,7 +7330,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="43" spans="1:11" hidden="1">
+    <row r="43" spans="1:11">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -7371,7 +7398,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="45" spans="1:11" hidden="1">
+    <row r="45" spans="1:11">
       <c r="A45" s="4">
         <v>44</v>
       </c>
@@ -7404,7 +7431,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="46" spans="1:11" hidden="1">
+    <row r="46" spans="1:11">
       <c r="A46" s="4">
         <v>45</v>
       </c>
@@ -7437,7 +7464,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="47" spans="1:11" hidden="1">
+    <row r="47" spans="1:11">
       <c r="A47" s="4">
         <v>46</v>
       </c>
@@ -7467,7 +7494,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="48" spans="1:11" hidden="1">
+    <row r="48" spans="1:11">
       <c r="A48" s="4">
         <v>47</v>
       </c>
@@ -7500,7 +7527,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="49" spans="1:11" hidden="1">
+    <row r="49" spans="1:11">
       <c r="A49" s="4">
         <v>48</v>
       </c>
@@ -7533,7 +7560,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="50" spans="1:11" hidden="1">
+    <row r="50" spans="1:11">
       <c r="A50" s="4">
         <v>49</v>
       </c>
@@ -7566,7 +7593,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="51" spans="1:11" hidden="1">
+    <row r="51" spans="1:11">
       <c r="A51" s="4">
         <v>50</v>
       </c>
@@ -7599,7 +7626,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="52" spans="1:11" hidden="1">
+    <row r="52" spans="1:11">
       <c r="A52" s="4">
         <v>51</v>
       </c>
@@ -7632,7 +7659,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="53" spans="1:11" hidden="1">
+    <row r="53" spans="1:11">
       <c r="A53" s="4">
         <v>52</v>
       </c>
@@ -7665,7 +7692,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="54" spans="1:11" hidden="1">
+    <row r="54" spans="1:11">
       <c r="A54" s="4">
         <v>53</v>
       </c>
@@ -7698,7 +7725,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="55" spans="1:11" hidden="1">
+    <row r="55" spans="1:11">
       <c r="A55" s="4">
         <v>54</v>
       </c>
@@ -7728,7 +7755,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="56" spans="1:11" hidden="1">
+    <row r="56" spans="1:11">
       <c r="A56" s="4">
         <v>55</v>
       </c>
@@ -7761,7 +7788,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="57" spans="1:11" hidden="1">
+    <row r="57" spans="1:11">
       <c r="A57" s="4">
         <v>56</v>
       </c>
@@ -7794,7 +7821,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="58" spans="1:11" hidden="1">
+    <row r="58" spans="1:11">
       <c r="A58" s="4">
         <v>57</v>
       </c>
@@ -7827,7 +7854,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="59" spans="1:11" hidden="1">
+    <row r="59" spans="1:11">
       <c r="A59" s="4">
         <v>58</v>
       </c>
@@ -7857,7 +7884,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="60" spans="1:11" hidden="1">
+    <row r="60" spans="1:11">
       <c r="A60" s="4">
         <v>59</v>
       </c>
@@ -7887,7 +7914,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="61" spans="1:11" hidden="1">
+    <row r="61" spans="1:11">
       <c r="A61" s="4">
         <v>60</v>
       </c>
@@ -7920,7 +7947,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="62" spans="1:11" hidden="1">
+    <row r="62" spans="1:11">
       <c r="A62" s="4">
         <v>61</v>
       </c>
@@ -7955,7 +7982,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="63" spans="1:11" hidden="1">
+    <row r="63" spans="1:11">
       <c r="A63" s="4">
         <v>62</v>
       </c>
@@ -7990,7 +8017,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="64" spans="1:11" hidden="1">
+    <row r="64" spans="1:11">
       <c r="A64" s="4">
         <v>63</v>
       </c>
@@ -8025,7 +8052,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="65" spans="1:11" hidden="1">
+    <row r="65" spans="1:11">
       <c r="A65" s="4">
         <v>64</v>
       </c>
@@ -8055,7 +8082,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="66" spans="1:11" hidden="1">
+    <row r="66" spans="1:11">
       <c r="A66" s="4">
         <v>65</v>
       </c>
@@ -8085,7 +8112,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="67" spans="1:11" hidden="1">
+    <row r="67" spans="1:11">
       <c r="A67" s="4">
         <v>66</v>
       </c>
@@ -8115,7 +8142,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="68" spans="1:11" hidden="1">
+    <row r="68" spans="1:11">
       <c r="A68" s="4">
         <v>67</v>
       </c>
@@ -8145,7 +8172,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="69" spans="1:11" hidden="1">
+    <row r="69" spans="1:11">
       <c r="A69" s="4">
         <v>68</v>
       </c>
@@ -8175,7 +8202,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="70" spans="1:11" hidden="1">
+    <row r="70" spans="1:11">
       <c r="A70" s="4">
         <v>69</v>
       </c>
@@ -8205,7 +8232,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="71" spans="1:11" hidden="1">
+    <row r="71" spans="1:11">
       <c r="A71" s="4">
         <v>70</v>
       </c>
@@ -8238,7 +8265,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="72" spans="1:11" hidden="1">
+    <row r="72" spans="1:11">
       <c r="A72" s="4">
         <v>71</v>
       </c>
@@ -8271,7 +8298,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="73" spans="1:11" hidden="1">
+    <row r="73" spans="1:11">
       <c r="A73" s="4">
         <v>72</v>
       </c>
@@ -8301,7 +8328,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="74" spans="1:11" hidden="1">
+    <row r="74" spans="1:11">
       <c r="A74" s="4">
         <v>73</v>
       </c>
@@ -8334,7 +8361,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="75" spans="1:11" hidden="1">
+    <row r="75" spans="1:11">
       <c r="A75" s="4">
         <v>74</v>
       </c>
@@ -8364,7 +8391,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="76" spans="1:11" hidden="1">
+    <row r="76" spans="1:11">
       <c r="A76" s="4">
         <v>75</v>
       </c>
@@ -8394,7 +8421,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="77" spans="1:11" hidden="1">
+    <row r="77" spans="1:11">
       <c r="A77" s="4">
         <v>76</v>
       </c>
@@ -8424,7 +8451,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="78" spans="1:11" hidden="1">
+    <row r="78" spans="1:11">
       <c r="A78" s="4">
         <v>77</v>
       </c>
@@ -8454,7 +8481,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="79" spans="1:11" hidden="1">
+    <row r="79" spans="1:11">
       <c r="A79" s="4">
         <v>78</v>
       </c>
@@ -8487,7 +8514,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="80" spans="1:11" hidden="1">
+    <row r="80" spans="1:11">
       <c r="A80" s="4">
         <v>79</v>
       </c>
@@ -8520,7 +8547,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="81" spans="1:11" hidden="1">
+    <row r="81" spans="1:11">
       <c r="A81" s="4">
         <v>80</v>
       </c>
@@ -8564,10 +8591,10 @@
         <v>144</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>1039</v>
+        <v>23</v>
       </c>
       <c r="G82" s="4" t="s">
         <v>14</v>
@@ -8585,7 +8612,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="83" spans="1:11" hidden="1">
+    <row r="83" spans="1:11">
       <c r="A83" s="4">
         <v>82</v>
       </c>
@@ -8618,7 +8645,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="84" spans="1:11" hidden="1">
+    <row r="84" spans="1:11">
       <c r="A84" s="4">
         <v>83</v>
       </c>
@@ -8651,7 +8678,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="85" spans="1:11" hidden="1">
+    <row r="85" spans="1:11">
       <c r="A85" s="4">
         <v>84</v>
       </c>
@@ -8681,7 +8708,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="86" spans="1:11" hidden="1">
+    <row r="86" spans="1:11">
       <c r="A86" s="4">
         <v>85</v>
       </c>
@@ -8714,7 +8741,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="87" spans="1:11" hidden="1">
+    <row r="87" spans="1:11">
       <c r="A87" s="4">
         <v>86</v>
       </c>
@@ -8747,7 +8774,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="88" spans="1:11" hidden="1">
+    <row r="88" spans="1:11">
       <c r="A88" s="4">
         <v>87</v>
       </c>
@@ -8780,7 +8807,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="89" spans="1:11" hidden="1">
+    <row r="89" spans="1:11">
       <c r="A89" s="4">
         <v>88</v>
       </c>
@@ -8813,7 +8840,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="90" spans="1:11" hidden="1">
+    <row r="90" spans="1:11">
       <c r="A90" s="4">
         <v>89</v>
       </c>
@@ -8846,7 +8873,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="91" spans="1:11" hidden="1">
+    <row r="91" spans="1:11">
       <c r="A91" s="4">
         <v>90</v>
       </c>
@@ -8879,7 +8906,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="92" spans="1:11" hidden="1">
+    <row r="92" spans="1:11">
       <c r="A92" s="4">
         <v>91</v>
       </c>
@@ -8906,7 +8933,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="93" spans="1:11" hidden="1">
+    <row r="93" spans="1:11">
       <c r="A93" s="4">
         <v>92</v>
       </c>
@@ -8933,7 +8960,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="94" spans="1:11" hidden="1">
+    <row r="94" spans="1:11">
       <c r="A94" s="4">
         <v>93</v>
       </c>
@@ -8960,7 +8987,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="95" spans="1:11" hidden="1">
+    <row r="95" spans="1:11">
       <c r="A95" s="4">
         <v>94</v>
       </c>
@@ -8993,7 +9020,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="96" spans="1:11" hidden="1">
+    <row r="96" spans="1:11">
       <c r="A96" s="4">
         <v>95</v>
       </c>
@@ -9061,7 +9088,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="98" spans="1:11" hidden="1">
+    <row r="98" spans="1:11">
       <c r="A98" s="4">
         <v>97</v>
       </c>
@@ -9094,7 +9121,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="99" spans="1:11" hidden="1">
+    <row r="99" spans="1:11">
       <c r="A99" s="4">
         <v>98</v>
       </c>
@@ -9124,7 +9151,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="100" spans="1:11" hidden="1">
+    <row r="100" spans="1:11">
       <c r="A100" s="4">
         <v>99</v>
       </c>
@@ -9157,7 +9184,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="101" spans="1:11" hidden="1">
+    <row r="101" spans="1:11">
       <c r="A101" s="4">
         <v>100</v>
       </c>
@@ -9190,7 +9217,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="102" spans="1:11" hidden="1">
+    <row r="102" spans="1:11">
       <c r="A102" s="4">
         <v>101</v>
       </c>
@@ -9217,7 +9244,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="103" spans="1:11" hidden="1">
+    <row r="103" spans="1:11">
       <c r="A103" s="4">
         <v>102</v>
       </c>
@@ -9244,7 +9271,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="104" spans="1:11" hidden="1">
+    <row r="104" spans="1:11">
       <c r="A104" s="4">
         <v>103</v>
       </c>
@@ -9277,7 +9304,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="105" spans="1:11" hidden="1">
+    <row r="105" spans="1:11">
       <c r="A105" s="4">
         <v>104</v>
       </c>
@@ -9307,7 +9334,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="106" spans="1:11" hidden="1">
+    <row r="106" spans="1:11">
       <c r="A106" s="4">
         <v>105</v>
       </c>
@@ -9339,7 +9366,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="107" spans="1:11" hidden="1">
+    <row r="107" spans="1:11">
       <c r="A107" s="4">
         <v>106</v>
       </c>
@@ -9369,7 +9396,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="108" spans="1:11" hidden="1">
+    <row r="108" spans="1:11">
       <c r="A108" s="4">
         <v>107</v>
       </c>
@@ -9422,7 +9449,7 @@
         <v>14</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
       <c r="I109" s="9">
         <v>45652</v>
@@ -9434,7 +9461,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="110" spans="1:11" hidden="1">
+    <row r="110" spans="1:11">
       <c r="A110" s="4">
         <v>109</v>
       </c>
@@ -9467,7 +9494,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="111" spans="1:11" hidden="1">
+    <row r="111" spans="1:11">
       <c r="A111" s="4">
         <v>110</v>
       </c>
@@ -9500,7 +9527,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="112" spans="1:11" hidden="1">
+    <row r="112" spans="1:11">
       <c r="A112" s="4">
         <v>111</v>
       </c>
@@ -9535,7 +9562,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="113" spans="1:11" hidden="1">
+    <row r="113" spans="1:11">
       <c r="A113" s="4">
         <v>112</v>
       </c>
@@ -9568,7 +9595,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="114" spans="1:11" hidden="1">
+    <row r="114" spans="1:11">
       <c r="A114" s="4">
         <v>113</v>
       </c>
@@ -9601,7 +9628,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="115" spans="1:11" hidden="1">
+    <row r="115" spans="1:11">
       <c r="A115" s="4">
         <v>114</v>
       </c>
@@ -9634,7 +9661,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="116" spans="1:11" hidden="1">
+    <row r="116" spans="1:11">
       <c r="A116" s="4">
         <v>115</v>
       </c>
@@ -9667,7 +9694,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="117" spans="1:11" hidden="1">
+    <row r="117" spans="1:11">
       <c r="A117" s="4">
         <v>116</v>
       </c>
@@ -9700,7 +9727,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="118" spans="1:11" hidden="1">
+    <row r="118" spans="1:11">
       <c r="A118" s="4">
         <v>117</v>
       </c>
@@ -9729,7 +9756,7 @@
       </c>
       <c r="K118" s="24"/>
     </row>
-    <row r="119" spans="1:11" hidden="1">
+    <row r="119" spans="1:11">
       <c r="A119" s="4">
         <v>118</v>
       </c>
@@ -9762,7 +9789,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="120" spans="1:11" hidden="1">
+    <row r="120" spans="1:11">
       <c r="A120" s="4">
         <v>119</v>
       </c>
@@ -9795,7 +9822,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="121" spans="1:11" hidden="1">
+    <row r="121" spans="1:11">
       <c r="A121" s="4">
         <v>120</v>
       </c>
@@ -9828,7 +9855,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="122" spans="1:11" hidden="1">
+    <row r="122" spans="1:11">
       <c r="A122" s="4">
         <v>121</v>
       </c>
@@ -9861,7 +9888,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="123" spans="1:11" hidden="1">
+    <row r="123" spans="1:11">
       <c r="A123" s="4">
         <v>122</v>
       </c>
@@ -9894,7 +9921,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="124" spans="1:11" hidden="1">
+    <row r="124" spans="1:11">
       <c r="A124" s="4">
         <v>123</v>
       </c>
@@ -9927,7 +9954,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="125" spans="1:11" hidden="1">
+    <row r="125" spans="1:11">
       <c r="A125" s="4">
         <v>124</v>
       </c>
@@ -9960,7 +9987,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="126" spans="1:11" hidden="1">
+    <row r="126" spans="1:11">
       <c r="A126" s="4">
         <v>125</v>
       </c>
@@ -9993,7 +10020,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="127" spans="1:11" hidden="1">
+    <row r="127" spans="1:11">
       <c r="A127" s="4">
         <v>126</v>
       </c>
@@ -10026,7 +10053,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="128" spans="1:11" hidden="1">
+    <row r="128" spans="1:11">
       <c r="A128" s="4">
         <v>127</v>
       </c>
@@ -10059,7 +10086,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="129" spans="1:11" hidden="1">
+    <row r="129" spans="1:11">
       <c r="A129" s="4">
         <v>128</v>
       </c>
@@ -10092,7 +10119,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="130" spans="1:11" hidden="1">
+    <row r="130" spans="1:11">
       <c r="A130" s="4">
         <v>129</v>
       </c>
@@ -10125,7 +10152,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="131" spans="1:11" hidden="1">
+    <row r="131" spans="1:11">
       <c r="A131" s="4">
         <v>130</v>
       </c>
@@ -10158,7 +10185,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="132" spans="1:11" hidden="1">
+    <row r="132" spans="1:11">
       <c r="A132" s="4">
         <v>131</v>
       </c>
@@ -10191,7 +10218,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="133" spans="1:11" hidden="1">
+    <row r="133" spans="1:11">
       <c r="A133" s="4">
         <v>132</v>
       </c>
@@ -10224,7 +10251,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="134" spans="1:11" hidden="1">
+    <row r="134" spans="1:11">
       <c r="A134" s="4">
         <v>133</v>
       </c>
@@ -10259,7 +10286,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="135" spans="1:11" hidden="1">
+    <row r="135" spans="1:11">
       <c r="A135" s="4">
         <v>134</v>
       </c>
@@ -10329,7 +10356,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="137" spans="1:11" hidden="1">
+    <row r="137" spans="1:11">
       <c r="A137" s="4">
         <v>136</v>
       </c>
@@ -10362,7 +10389,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="138" spans="1:11" hidden="1">
+    <row r="138" spans="1:11">
       <c r="A138" s="4">
         <v>137</v>
       </c>
@@ -10395,7 +10422,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="139" spans="1:11" hidden="1">
+    <row r="139" spans="1:11">
       <c r="A139" s="4">
         <v>138</v>
       </c>
@@ -10428,7 +10455,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="140" spans="1:11" hidden="1">
+    <row r="140" spans="1:11">
       <c r="A140" s="4">
         <v>139</v>
       </c>
@@ -10461,7 +10488,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="141" spans="1:11" hidden="1">
+    <row r="141" spans="1:11">
       <c r="A141" s="4">
         <v>140</v>
       </c>
@@ -10543,10 +10570,10 @@
         <v>231</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>1046</v>
+        <v>23</v>
       </c>
       <c r="G143" s="4" t="s">
         <v>14</v>
@@ -10578,10 +10605,10 @@
         <v>232</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>1053</v>
+        <v>23</v>
       </c>
       <c r="G144" s="4" t="s">
         <v>14</v>
@@ -10599,7 +10626,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="145" spans="1:11" hidden="1">
+    <row r="145" spans="1:11">
       <c r="A145" s="4">
         <v>144</v>
       </c>
@@ -10667,7 +10694,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="147" spans="1:11" hidden="1">
+    <row r="147" spans="1:11">
       <c r="A147" s="4">
         <v>146</v>
       </c>
@@ -10700,7 +10727,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="148" spans="1:11" hidden="1">
+    <row r="148" spans="1:11">
       <c r="A148" s="4">
         <v>147</v>
       </c>
@@ -10733,7 +10760,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="149" spans="1:11" hidden="1">
+    <row r="149" spans="1:11">
       <c r="A149" s="4">
         <v>148</v>
       </c>
@@ -10766,7 +10793,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="150" spans="1:11" hidden="1">
+    <row r="150" spans="1:11">
       <c r="A150" s="4">
         <v>149</v>
       </c>
@@ -10799,7 +10826,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="151" spans="1:11" hidden="1">
+    <row r="151" spans="1:11">
       <c r="A151" s="4">
         <v>150</v>
       </c>
@@ -10832,7 +10859,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="152" spans="1:11" hidden="1">
+    <row r="152" spans="1:11">
       <c r="A152" s="4">
         <v>151</v>
       </c>
@@ -10865,7 +10892,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="153" spans="1:11" hidden="1">
+    <row r="153" spans="1:11">
       <c r="A153" s="4">
         <v>152</v>
       </c>
@@ -10898,7 +10925,7 @@
       </c>
       <c r="K153" s="24"/>
     </row>
-    <row r="154" spans="1:11" hidden="1">
+    <row r="154" spans="1:11">
       <c r="A154" s="4">
         <v>153</v>
       </c>
@@ -10933,7 +10960,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="155" spans="1:11" hidden="1">
+    <row r="155" spans="1:11">
       <c r="A155" s="4">
         <v>154</v>
       </c>
@@ -10968,7 +10995,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="156" spans="1:11" hidden="1">
+    <row r="156" spans="1:11">
       <c r="A156" s="4">
         <v>155</v>
       </c>
@@ -11038,7 +11065,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="158" spans="1:11" hidden="1">
+    <row r="158" spans="1:11">
       <c r="A158" s="4">
         <v>157</v>
       </c>
@@ -11073,7 +11100,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="159" spans="1:11" hidden="1">
+    <row r="159" spans="1:11">
       <c r="A159" s="4">
         <v>158</v>
       </c>
@@ -11279,7 +11306,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="165" spans="1:11" hidden="1">
+    <row r="165" spans="1:11">
       <c r="A165" s="4">
         <v>164</v>
       </c>
@@ -11314,7 +11341,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="166" spans="1:11" hidden="1">
+    <row r="166" spans="1:11">
       <c r="A166" s="4">
         <v>165</v>
       </c>
@@ -11349,7 +11376,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="167" spans="1:11" hidden="1">
+    <row r="167" spans="1:11">
       <c r="A167" s="4">
         <v>166</v>
       </c>
@@ -11384,7 +11411,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="168" spans="1:11" hidden="1">
+    <row r="168" spans="1:11">
       <c r="A168" s="4">
         <v>167</v>
       </c>
@@ -11417,7 +11444,7 @@
       </c>
       <c r="K168" s="55"/>
     </row>
-    <row r="169" spans="1:11" hidden="1">
+    <row r="169" spans="1:11">
       <c r="A169" s="4">
         <v>168</v>
       </c>
@@ -11450,7 +11477,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="170" spans="1:11" hidden="1">
+    <row r="170" spans="1:11">
       <c r="A170" s="4">
         <v>169</v>
       </c>
@@ -11483,7 +11510,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="171" spans="1:11" hidden="1">
+    <row r="171" spans="1:11">
       <c r="A171" s="4">
         <v>170</v>
       </c>
@@ -11516,7 +11543,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="172" spans="1:11" hidden="1">
+    <row r="172" spans="1:11">
       <c r="A172" s="4">
         <v>171</v>
       </c>
@@ -11551,7 +11578,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="173" spans="1:11" hidden="1">
+    <row r="173" spans="1:11">
       <c r="A173" s="4">
         <v>172</v>
       </c>
@@ -11584,7 +11611,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="174" spans="1:11" hidden="1">
+    <row r="174" spans="1:11">
       <c r="A174" s="4">
         <v>173</v>
       </c>
@@ -11617,7 +11644,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="175" spans="1:11" hidden="1">
+    <row r="175" spans="1:11">
       <c r="A175" s="4">
         <v>174</v>
       </c>
@@ -11652,7 +11679,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="176" spans="1:11" hidden="1">
+    <row r="176" spans="1:11">
       <c r="A176" s="4">
         <v>175</v>
       </c>
@@ -11682,7 +11709,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="177" spans="1:11" hidden="1">
+    <row r="177" spans="1:11">
       <c r="A177" s="4">
         <v>176</v>
       </c>
@@ -11712,7 +11739,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="178" spans="1:11" hidden="1">
+    <row r="178" spans="1:11">
       <c r="A178" s="4">
         <v>177</v>
       </c>
@@ -11740,7 +11767,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="179" spans="1:11" hidden="1">
+    <row r="179" spans="1:11">
       <c r="A179" s="4">
         <v>178</v>
       </c>
@@ -11775,7 +11802,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="180" spans="1:11" hidden="1">
+    <row r="180" spans="1:11">
       <c r="A180" s="4">
         <v>179</v>
       </c>
@@ -11805,7 +11832,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="181" spans="1:11" hidden="1">
+    <row r="181" spans="1:11">
       <c r="A181" s="4">
         <v>180</v>
       </c>
@@ -11838,7 +11865,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="182" spans="1:11" hidden="1">
+    <row r="182" spans="1:11">
       <c r="A182" s="4">
         <v>181</v>
       </c>
@@ -11871,7 +11898,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="183" spans="1:11" hidden="1">
+    <row r="183" spans="1:11">
       <c r="A183" s="4">
         <v>182</v>
       </c>
@@ -11904,7 +11931,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="184" spans="1:11" hidden="1">
+    <row r="184" spans="1:11">
       <c r="A184" s="4">
         <v>183</v>
       </c>
@@ -11937,7 +11964,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="185" spans="1:11" hidden="1">
+    <row r="185" spans="1:11">
       <c r="A185" s="4">
         <v>184</v>
       </c>
@@ -11967,7 +11994,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="186" spans="1:11" hidden="1">
+    <row r="186" spans="1:11">
       <c r="A186" s="4">
         <v>185</v>
       </c>
@@ -11997,7 +12024,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="187" spans="1:11" hidden="1">
+    <row r="187" spans="1:11">
       <c r="A187" s="4">
         <v>186</v>
       </c>
@@ -12030,7 +12057,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="188" spans="1:11" hidden="1">
+    <row r="188" spans="1:11">
       <c r="A188" s="4">
         <v>187</v>
       </c>
@@ -12057,7 +12084,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="189" spans="1:11" hidden="1">
+    <row r="189" spans="1:11">
       <c r="A189" s="4">
         <v>188</v>
       </c>
@@ -12088,7 +12115,7 @@
       </c>
       <c r="K189" s="24"/>
     </row>
-    <row r="190" spans="1:11" hidden="1">
+    <row r="190" spans="1:11">
       <c r="A190" s="4">
         <v>189</v>
       </c>
@@ -12123,7 +12150,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="191" spans="1:11" hidden="1">
+    <row r="191" spans="1:11">
       <c r="A191" s="4">
         <v>190</v>
       </c>
@@ -12153,7 +12180,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="192" spans="1:11" hidden="1">
+    <row r="192" spans="1:11">
       <c r="A192" s="4">
         <v>191</v>
       </c>
@@ -12186,7 +12213,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="193" spans="1:10" hidden="1">
+    <row r="193" spans="1:10">
       <c r="A193" s="4">
         <v>192</v>
       </c>
@@ -12216,7 +12243,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="194" spans="1:10" hidden="1">
+    <row r="194" spans="1:10">
       <c r="A194" s="4">
         <v>193</v>
       </c>
@@ -12238,7 +12265,9 @@
       <c r="G194" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H194" s="1"/>
+      <c r="H194" s="1" t="s">
+        <v>1452</v>
+      </c>
       <c r="I194" s="9">
         <v>45687</v>
       </c>
@@ -12246,7 +12275,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="195" spans="1:10" hidden="1">
+    <row r="195" spans="1:10">
       <c r="A195" s="4">
         <v>194</v>
       </c>
@@ -12268,7 +12297,9 @@
       <c r="G195" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H195" s="1"/>
+      <c r="H195" s="1" t="s">
+        <v>1452</v>
+      </c>
       <c r="I195" s="9">
         <v>45687</v>
       </c>
@@ -12276,7 +12307,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="196" spans="1:10" hidden="1">
+    <row r="196" spans="1:10">
       <c r="A196" s="4">
         <v>195</v>
       </c>
@@ -12298,7 +12329,9 @@
       <c r="G196" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H196" s="1"/>
+      <c r="H196" s="1" t="s">
+        <v>1452</v>
+      </c>
       <c r="I196" s="9">
         <v>45687</v>
       </c>
@@ -12306,7 +12339,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="197" spans="1:10" hidden="1">
+    <row r="197" spans="1:10">
       <c r="A197" s="4">
         <v>196</v>
       </c>
@@ -12328,7 +12361,9 @@
       <c r="G197" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H197" s="1"/>
+      <c r="H197" s="1" t="s">
+        <v>1452</v>
+      </c>
       <c r="I197" s="9">
         <v>45687</v>
       </c>
@@ -12336,7 +12371,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="198" spans="1:10" hidden="1">
+    <row r="198" spans="1:10">
       <c r="A198" s="4">
         <v>197</v>
       </c>
@@ -12358,7 +12393,9 @@
       <c r="G198" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H198" s="1"/>
+      <c r="H198" s="1" t="s">
+        <v>1452</v>
+      </c>
       <c r="I198" s="9">
         <v>45687</v>
       </c>
@@ -12366,7 +12403,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="199" spans="1:10" hidden="1">
+    <row r="199" spans="1:10">
       <c r="A199" s="4">
         <v>198</v>
       </c>
@@ -12388,7 +12425,9 @@
       <c r="G199" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H199" s="1"/>
+      <c r="H199" s="1" t="s">
+        <v>1452</v>
+      </c>
       <c r="I199" s="9">
         <v>45687</v>
       </c>
@@ -12396,7 +12435,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="200" spans="1:10" hidden="1">
+    <row r="200" spans="1:10">
       <c r="A200" s="4">
         <v>199</v>
       </c>
@@ -12418,7 +12457,9 @@
       <c r="G200" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H200" s="1"/>
+      <c r="H200" s="1" t="s">
+        <v>1452</v>
+      </c>
       <c r="I200" s="9">
         <v>45687</v>
       </c>
@@ -12426,7 +12467,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="201" spans="1:10" hidden="1">
+    <row r="201" spans="1:10">
       <c r="A201" s="4">
         <v>200</v>
       </c>
@@ -12448,7 +12489,9 @@
       <c r="G201" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H201" s="1"/>
+      <c r="H201" s="1" t="s">
+        <v>1452</v>
+      </c>
       <c r="I201" s="9">
         <v>45687</v>
       </c>
@@ -12456,7 +12499,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="202" spans="1:10" hidden="1">
+    <row r="202" spans="1:10">
       <c r="A202" s="4">
         <v>201</v>
       </c>
@@ -12478,7 +12521,9 @@
       <c r="G202" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H202" s="1"/>
+      <c r="H202" s="1" t="s">
+        <v>1452</v>
+      </c>
       <c r="I202" s="9">
         <v>45687</v>
       </c>
@@ -12486,7 +12531,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="203" spans="1:10" hidden="1">
+    <row r="203" spans="1:10">
       <c r="A203" s="4">
         <v>202</v>
       </c>
@@ -12508,7 +12553,9 @@
       <c r="G203" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H203" s="1"/>
+      <c r="H203" s="1" t="s">
+        <v>1452</v>
+      </c>
       <c r="I203" s="9">
         <v>45687</v>
       </c>
@@ -12516,7 +12563,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="204" spans="1:10" hidden="1">
+    <row r="204" spans="1:10">
       <c r="A204" s="4">
         <v>203</v>
       </c>
@@ -12538,7 +12585,9 @@
       <c r="G204" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H204" s="1"/>
+      <c r="H204" s="1" t="s">
+        <v>1452</v>
+      </c>
       <c r="I204" s="9">
         <v>45687</v>
       </c>
@@ -12546,7 +12595,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="205" spans="1:10" hidden="1">
+    <row r="205" spans="1:10">
       <c r="A205" s="4">
         <v>204</v>
       </c>
@@ -12568,7 +12617,9 @@
       <c r="G205" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H205" s="1"/>
+      <c r="H205" s="1" t="s">
+        <v>1452</v>
+      </c>
       <c r="I205" s="9">
         <v>45687</v>
       </c>
@@ -12576,7 +12627,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="206" spans="1:10" hidden="1">
+    <row r="206" spans="1:10">
       <c r="A206" s="4">
         <v>205</v>
       </c>
@@ -12598,7 +12649,9 @@
       <c r="G206" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H206" s="1"/>
+      <c r="H206" s="1" t="s">
+        <v>1452</v>
+      </c>
       <c r="I206" s="9">
         <v>45687</v>
       </c>
@@ -12606,7 +12659,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="207" spans="1:10" hidden="1">
+    <row r="207" spans="1:10">
       <c r="A207" s="4">
         <v>206</v>
       </c>
@@ -12628,7 +12681,9 @@
       <c r="G207" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H207" s="1"/>
+      <c r="H207" s="1" t="s">
+        <v>1452</v>
+      </c>
       <c r="I207" s="9">
         <v>45687</v>
       </c>
@@ -12636,7 +12691,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="208" spans="1:10" hidden="1">
+    <row r="208" spans="1:10">
       <c r="A208" s="4">
         <v>207</v>
       </c>
@@ -12658,7 +12713,9 @@
       <c r="G208" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H208" s="1"/>
+      <c r="H208" s="1" t="s">
+        <v>1452</v>
+      </c>
       <c r="I208" s="9">
         <v>45687</v>
       </c>
@@ -12666,7 +12723,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="209" spans="1:11" hidden="1">
+    <row r="209" spans="1:11">
       <c r="A209" s="4">
         <v>208</v>
       </c>
@@ -12688,7 +12745,9 @@
       <c r="G209" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H209" s="1"/>
+      <c r="H209" s="1" t="s">
+        <v>1452</v>
+      </c>
       <c r="I209" s="9">
         <v>45687</v>
       </c>
@@ -12696,7 +12755,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="210" spans="1:11" hidden="1">
+    <row r="210" spans="1:11">
       <c r="A210" s="4">
         <v>209</v>
       </c>
@@ -12718,7 +12777,9 @@
       <c r="G210" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H210" s="1"/>
+      <c r="H210" s="1" t="s">
+        <v>1452</v>
+      </c>
       <c r="I210" s="9">
         <v>45687</v>
       </c>
@@ -12726,7 +12787,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="211" spans="1:11" hidden="1">
+    <row r="211" spans="1:11">
       <c r="A211" s="4">
         <v>210</v>
       </c>
@@ -12748,7 +12809,9 @@
       <c r="G211" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H211" s="1"/>
+      <c r="H211" s="1" t="s">
+        <v>1452</v>
+      </c>
       <c r="I211" s="9">
         <v>45687</v>
       </c>
@@ -12756,7 +12819,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="212" spans="1:11" hidden="1">
+    <row r="212" spans="1:11">
       <c r="A212" s="4">
         <v>211</v>
       </c>
@@ -12778,7 +12841,9 @@
       <c r="G212" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H212" s="1"/>
+      <c r="H212" s="1" t="s">
+        <v>1452</v>
+      </c>
       <c r="I212" s="9">
         <v>45687</v>
       </c>
@@ -12786,7 +12851,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="213" spans="1:11" hidden="1">
+    <row r="213" spans="1:11">
       <c r="A213" s="4">
         <v>212</v>
       </c>
@@ -12808,7 +12873,9 @@
       <c r="G213" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H213" s="1"/>
+      <c r="H213" s="1" t="s">
+        <v>1452</v>
+      </c>
       <c r="I213" s="9">
         <v>45687</v>
       </c>
@@ -12816,7 +12883,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="214" spans="1:11" hidden="1">
+    <row r="214" spans="1:11">
       <c r="A214" s="4">
         <v>213</v>
       </c>
@@ -12838,7 +12905,9 @@
       <c r="G214" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H214" s="1"/>
+      <c r="H214" s="1" t="s">
+        <v>1452</v>
+      </c>
       <c r="I214" s="9">
         <v>45687</v>
       </c>
@@ -12846,7 +12915,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="215" spans="1:11" hidden="1">
+    <row r="215" spans="1:11">
       <c r="A215" s="4">
         <v>214</v>
       </c>
@@ -12868,7 +12937,9 @@
       <c r="G215" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H215" s="1"/>
+      <c r="H215" s="1" t="s">
+        <v>1452</v>
+      </c>
       <c r="I215" s="9">
         <v>45687</v>
       </c>
@@ -12879,7 +12950,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="216" spans="1:11" hidden="1">
+    <row r="216" spans="1:11">
       <c r="A216" s="4">
         <v>215</v>
       </c>
@@ -12901,7 +12972,9 @@
       <c r="G216" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H216" s="1"/>
+      <c r="H216" s="1" t="s">
+        <v>1452</v>
+      </c>
       <c r="I216" s="9">
         <v>45652</v>
       </c>
@@ -12912,7 +12985,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="217" spans="1:11" hidden="1">
+    <row r="217" spans="1:11">
       <c r="A217" s="4">
         <v>216</v>
       </c>
@@ -12945,7 +13018,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="218" spans="1:11" hidden="1">
+    <row r="218" spans="1:11">
       <c r="A218" s="4">
         <v>217</v>
       </c>
@@ -12978,7 +13051,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="219" spans="1:11" hidden="1">
+    <row r="219" spans="1:11">
       <c r="A219" s="4">
         <v>218</v>
       </c>
@@ -13009,7 +13082,7 @@
       </c>
       <c r="K219" s="24"/>
     </row>
-    <row r="220" spans="1:11" hidden="1">
+    <row r="220" spans="1:11">
       <c r="A220" s="4">
         <v>219</v>
       </c>
@@ -13042,7 +13115,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="221" spans="1:11" hidden="1">
+    <row r="221" spans="1:11">
       <c r="A221" s="4">
         <v>220</v>
       </c>
@@ -13075,7 +13148,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="222" spans="1:11" hidden="1">
+    <row r="222" spans="1:11">
       <c r="A222" s="4">
         <v>221</v>
       </c>
@@ -13108,7 +13181,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="223" spans="1:11" hidden="1">
+    <row r="223" spans="1:11">
       <c r="A223" s="4">
         <v>222</v>
       </c>
@@ -13143,7 +13216,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="224" spans="1:11" hidden="1">
+    <row r="224" spans="1:11">
       <c r="A224" s="4">
         <v>223</v>
       </c>
@@ -13176,7 +13249,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="225" spans="1:11" hidden="1">
+    <row r="225" spans="1:11">
       <c r="A225" s="4">
         <v>224</v>
       </c>
@@ -13211,7 +13284,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="226" spans="1:11" hidden="1">
+    <row r="226" spans="1:11">
       <c r="A226" s="4">
         <v>225</v>
       </c>
@@ -13246,7 +13319,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="227" spans="1:11" hidden="1">
+    <row r="227" spans="1:11">
       <c r="A227" s="4">
         <v>226</v>
       </c>
@@ -13279,7 +13352,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="228" spans="1:11" hidden="1">
+    <row r="228" spans="1:11">
       <c r="A228" s="4">
         <v>227</v>
       </c>
@@ -13312,7 +13385,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="229" spans="1:11" hidden="1">
+    <row r="229" spans="1:11">
       <c r="A229" s="4">
         <v>228</v>
       </c>
@@ -13382,7 +13455,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="231" spans="1:11" hidden="1">
+    <row r="231" spans="1:11">
       <c r="A231" s="4">
         <v>230</v>
       </c>
@@ -13417,7 +13490,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="232" spans="1:11" hidden="1">
+    <row r="232" spans="1:11">
       <c r="A232" s="4">
         <v>231</v>
       </c>
@@ -13450,7 +13523,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="233" spans="1:11" hidden="1">
+    <row r="233" spans="1:11">
       <c r="A233" s="4">
         <v>232</v>
       </c>
@@ -13483,7 +13556,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="234" spans="1:11" hidden="1">
+    <row r="234" spans="1:11">
       <c r="A234" s="4">
         <v>233</v>
       </c>
@@ -13516,7 +13589,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="235" spans="1:11" hidden="1">
+    <row r="235" spans="1:11">
       <c r="A235" s="4">
         <v>234</v>
       </c>
@@ -13549,7 +13622,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="236" spans="1:11" hidden="1">
+    <row r="236" spans="1:11">
       <c r="A236" s="4">
         <v>235</v>
       </c>
@@ -13582,7 +13655,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="237" spans="1:11" hidden="1">
+    <row r="237" spans="1:11">
       <c r="A237" s="4">
         <v>236</v>
       </c>
@@ -13629,10 +13702,10 @@
         <v>338</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>1041</v>
+        <v>23</v>
       </c>
       <c r="G238" s="4" t="s">
         <v>14</v>
@@ -13650,7 +13723,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="239" spans="1:11" hidden="1">
+    <row r="239" spans="1:11">
       <c r="A239" s="4">
         <v>238</v>
       </c>
@@ -13683,7 +13756,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="240" spans="1:11" hidden="1">
+    <row r="240" spans="1:11">
       <c r="A240" s="4">
         <v>239</v>
       </c>
@@ -13718,7 +13791,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="241" spans="1:11" hidden="1">
+    <row r="241" spans="1:11">
       <c r="A241" s="4">
         <v>240</v>
       </c>
@@ -13751,7 +13824,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="242" spans="1:11" hidden="1">
+    <row r="242" spans="1:11">
       <c r="A242" s="4">
         <v>241</v>
       </c>
@@ -13774,7 +13847,7 @@
         <v>14</v>
       </c>
       <c r="H242" s="1" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="I242" s="9">
         <v>45636</v>
@@ -13786,7 +13859,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="243" spans="1:11" hidden="1">
+    <row r="243" spans="1:11">
       <c r="A243" s="4">
         <v>242</v>
       </c>
@@ -13819,7 +13892,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="244" spans="1:11" hidden="1">
+    <row r="244" spans="1:11">
       <c r="A244" s="4">
         <v>243</v>
       </c>
@@ -13887,7 +13960,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="246" spans="1:11" hidden="1">
+    <row r="246" spans="1:11">
       <c r="A246" s="4">
         <v>245</v>
       </c>
@@ -13920,7 +13993,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="247" spans="1:11" hidden="1">
+    <row r="247" spans="1:11">
       <c r="A247" s="4">
         <v>246</v>
       </c>
@@ -13955,7 +14028,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="248" spans="1:11" hidden="1">
+    <row r="248" spans="1:11">
       <c r="A248" s="4">
         <v>247</v>
       </c>
@@ -13988,7 +14061,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="249" spans="1:11" hidden="1">
+    <row r="249" spans="1:11">
       <c r="A249" s="4">
         <v>248</v>
       </c>
@@ -14021,7 +14094,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="250" spans="1:11" hidden="1">
+    <row r="250" spans="1:11">
       <c r="A250" s="4">
         <v>249</v>
       </c>
@@ -14054,7 +14127,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="251" spans="1:11" hidden="1">
+    <row r="251" spans="1:11">
       <c r="A251" s="4">
         <v>250</v>
       </c>
@@ -14124,7 +14197,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="253" spans="1:11" ht="15.6" hidden="1">
+    <row r="253" spans="1:11" ht="15.6">
       <c r="A253" s="4">
         <v>252</v>
       </c>
@@ -14173,10 +14246,10 @@
         <v>359</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>1055</v>
+        <v>23</v>
       </c>
       <c r="G254" s="4" t="s">
         <v>14</v>
@@ -14243,10 +14316,10 @@
         <v>361</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F256" s="41" t="s">
-        <v>1051</v>
+        <v>23</v>
       </c>
       <c r="G256" s="4" t="s">
         <v>14</v>
@@ -14264,7 +14337,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="257" spans="1:11" hidden="1">
+    <row r="257" spans="1:11">
       <c r="A257" s="4">
         <v>256</v>
       </c>
@@ -14299,7 +14372,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="258" spans="1:11" hidden="1">
+    <row r="258" spans="1:11">
       <c r="A258" s="4">
         <v>257</v>
       </c>
@@ -14330,7 +14403,7 @@
       </c>
       <c r="K258" s="20"/>
     </row>
-    <row r="259" spans="1:11" hidden="1">
+    <row r="259" spans="1:11">
       <c r="A259" s="4">
         <v>258</v>
       </c>
@@ -14363,7 +14436,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="260" spans="1:11" hidden="1">
+    <row r="260" spans="1:11">
       <c r="A260" s="4">
         <v>259</v>
       </c>
@@ -14398,7 +14471,7 @@
         <v>1312</v>
       </c>
     </row>
-    <row r="261" spans="1:11" hidden="1">
+    <row r="261" spans="1:11">
       <c r="A261" s="4">
         <v>260</v>
       </c>
@@ -14433,7 +14506,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="262" spans="1:11" hidden="1">
+    <row r="262" spans="1:11">
       <c r="A262" s="4">
         <v>261</v>
       </c>
@@ -14468,7 +14541,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="263" spans="1:11" hidden="1">
+    <row r="263" spans="1:11">
       <c r="A263" s="4">
         <v>262</v>
       </c>
@@ -14501,7 +14574,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="264" spans="1:11" hidden="1">
+    <row r="264" spans="1:11">
       <c r="A264" s="4">
         <v>263</v>
       </c>
@@ -14531,7 +14604,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="265" spans="1:11" hidden="1">
+    <row r="265" spans="1:11">
       <c r="A265" s="4">
         <v>264</v>
       </c>
@@ -14564,7 +14637,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="266" spans="1:11" hidden="1">
+    <row r="266" spans="1:11">
       <c r="A266" s="4">
         <v>265</v>
       </c>
@@ -14597,7 +14670,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="267" spans="1:11" hidden="1">
+    <row r="267" spans="1:11">
       <c r="A267" s="4">
         <v>266</v>
       </c>
@@ -14630,7 +14703,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="268" spans="1:11" hidden="1">
+    <row r="268" spans="1:11">
       <c r="A268" s="4">
         <v>267</v>
       </c>
@@ -14660,7 +14733,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="269" spans="1:11" hidden="1">
+    <row r="269" spans="1:11">
       <c r="A269" s="4">
         <v>268</v>
       </c>
@@ -14693,7 +14766,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="270" spans="1:11" hidden="1">
+    <row r="270" spans="1:11">
       <c r="A270" s="4">
         <v>269</v>
       </c>
@@ -14723,7 +14796,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="271" spans="1:11" hidden="1">
+    <row r="271" spans="1:11">
       <c r="A271" s="4">
         <v>270</v>
       </c>
@@ -14753,7 +14826,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="272" spans="1:11" hidden="1">
+    <row r="272" spans="1:11">
       <c r="A272" s="4">
         <v>271</v>
       </c>
@@ -14786,7 +14859,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="273" spans="1:11" hidden="1">
+    <row r="273" spans="1:11">
       <c r="A273" s="4">
         <v>272</v>
       </c>
@@ -14889,7 +14962,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="276" spans="1:11" hidden="1">
+    <row r="276" spans="1:11">
       <c r="A276" s="4">
         <v>275</v>
       </c>
@@ -14922,7 +14995,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="277" spans="1:11" hidden="1">
+    <row r="277" spans="1:11">
       <c r="A277" s="4">
         <v>276</v>
       </c>
@@ -14955,7 +15028,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="278" spans="1:11" hidden="1">
+    <row r="278" spans="1:11">
       <c r="A278" s="4">
         <v>277</v>
       </c>
@@ -14988,7 +15061,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="279" spans="1:11" hidden="1">
+    <row r="279" spans="1:11">
       <c r="A279" s="4">
         <v>278</v>
       </c>
@@ -15021,7 +15094,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="280" spans="1:11" hidden="1">
+    <row r="280" spans="1:11">
       <c r="A280" s="4">
         <v>279</v>
       </c>
@@ -15054,7 +15127,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="281" spans="1:11" hidden="1">
+    <row r="281" spans="1:11">
       <c r="A281" s="4">
         <v>280</v>
       </c>
@@ -15087,7 +15160,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="282" spans="1:11" hidden="1">
+    <row r="282" spans="1:11">
       <c r="A282" s="4">
         <v>281</v>
       </c>
@@ -15120,7 +15193,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="283" spans="1:11" hidden="1">
+    <row r="283" spans="1:11">
       <c r="A283" s="4">
         <v>282</v>
       </c>
@@ -15153,7 +15226,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="284" spans="1:11" hidden="1">
+    <row r="284" spans="1:11">
       <c r="A284" s="4">
         <v>283</v>
       </c>
@@ -15186,7 +15259,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="285" spans="1:11" hidden="1">
+    <row r="285" spans="1:11">
       <c r="A285" s="4">
         <v>284</v>
       </c>
@@ -15219,7 +15292,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="286" spans="1:11" hidden="1">
+    <row r="286" spans="1:11">
       <c r="A286" s="4">
         <v>285</v>
       </c>
@@ -15254,7 +15327,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="287" spans="1:11" hidden="1">
+    <row r="287" spans="1:11">
       <c r="A287" s="4">
         <v>286</v>
       </c>
@@ -15287,7 +15360,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="288" spans="1:11" hidden="1">
+    <row r="288" spans="1:11">
       <c r="A288" s="4">
         <v>287</v>
       </c>
@@ -15320,7 +15393,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="289" spans="1:11" hidden="1">
+    <row r="289" spans="1:11">
       <c r="A289" s="4">
         <v>288</v>
       </c>
@@ -15353,7 +15426,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="290" spans="1:11" hidden="1">
+    <row r="290" spans="1:11">
       <c r="A290" s="4">
         <v>289</v>
       </c>
@@ -15388,7 +15461,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="291" spans="1:11" hidden="1">
+    <row r="291" spans="1:11">
       <c r="A291" s="4">
         <v>290</v>
       </c>
@@ -15423,7 +15496,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="292" spans="1:11" hidden="1">
+    <row r="292" spans="1:11">
       <c r="A292" s="4">
         <v>291</v>
       </c>
@@ -15458,7 +15531,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="293" spans="1:11" hidden="1">
+    <row r="293" spans="1:11">
       <c r="A293" s="4">
         <v>292</v>
       </c>
@@ -15493,7 +15566,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="294" spans="1:11" hidden="1">
+    <row r="294" spans="1:11">
       <c r="A294" s="4">
         <v>293</v>
       </c>
@@ -15528,7 +15601,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="295" spans="1:11" hidden="1">
+    <row r="295" spans="1:11">
       <c r="A295" s="4">
         <v>294</v>
       </c>
@@ -15563,7 +15636,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="296" spans="1:11" hidden="1">
+    <row r="296" spans="1:11">
       <c r="A296" s="4">
         <v>295</v>
       </c>
@@ -15598,7 +15671,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="297" spans="1:11" hidden="1">
+    <row r="297" spans="1:11">
       <c r="A297" s="4">
         <v>296</v>
       </c>
@@ -15633,7 +15706,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="298" spans="1:11" hidden="1">
+    <row r="298" spans="1:11">
       <c r="A298" s="4">
         <v>297</v>
       </c>
@@ -15668,7 +15741,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="299" spans="1:11" hidden="1">
+    <row r="299" spans="1:11">
       <c r="A299" s="4">
         <v>298</v>
       </c>
@@ -15703,7 +15776,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="300" spans="1:11" hidden="1">
+    <row r="300" spans="1:11">
       <c r="A300" s="4">
         <v>299</v>
       </c>
@@ -15738,7 +15811,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="301" spans="1:11" hidden="1">
+    <row r="301" spans="1:11">
       <c r="A301" s="4">
         <v>300</v>
       </c>
@@ -15773,7 +15846,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="302" spans="1:11" hidden="1">
+    <row r="302" spans="1:11">
       <c r="A302" s="4">
         <v>301</v>
       </c>
@@ -15808,7 +15881,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="303" spans="1:11" hidden="1">
+    <row r="303" spans="1:11">
       <c r="A303" s="4">
         <v>302</v>
       </c>
@@ -15843,7 +15916,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="304" spans="1:11" hidden="1">
+    <row r="304" spans="1:11">
       <c r="A304" s="4">
         <v>303</v>
       </c>
@@ -15878,7 +15951,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="305" spans="1:11" hidden="1">
+    <row r="305" spans="1:11">
       <c r="A305" s="4">
         <v>304</v>
       </c>
@@ -15913,7 +15986,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="306" spans="1:11" hidden="1">
+    <row r="306" spans="1:11">
       <c r="A306" s="4">
         <v>305</v>
       </c>
@@ -15948,7 +16021,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="307" spans="1:11" hidden="1">
+    <row r="307" spans="1:11">
       <c r="A307" s="4">
         <v>306</v>
       </c>
@@ -15983,7 +16056,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="308" spans="1:11" hidden="1">
+    <row r="308" spans="1:11">
       <c r="A308" s="4">
         <v>307</v>
       </c>
@@ -16018,7 +16091,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="309" spans="1:11" hidden="1">
+    <row r="309" spans="1:11">
       <c r="A309" s="4">
         <v>308</v>
       </c>
@@ -16053,7 +16126,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="310" spans="1:11" hidden="1">
+    <row r="310" spans="1:11">
       <c r="A310" s="4">
         <v>309</v>
       </c>
@@ -16088,7 +16161,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="311" spans="1:11" hidden="1">
+    <row r="311" spans="1:11">
       <c r="A311" s="4">
         <v>310</v>
       </c>
@@ -16123,7 +16196,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="312" spans="1:11" hidden="1">
+    <row r="312" spans="1:11">
       <c r="A312" s="4">
         <v>311</v>
       </c>
@@ -16158,7 +16231,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="313" spans="1:11" hidden="1">
+    <row r="313" spans="1:11">
       <c r="A313" s="4">
         <v>312</v>
       </c>
@@ -16193,7 +16266,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="314" spans="1:11" hidden="1">
+    <row r="314" spans="1:11">
       <c r="A314" s="4">
         <v>313</v>
       </c>
@@ -16228,7 +16301,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="315" spans="1:11" hidden="1">
+    <row r="315" spans="1:11">
       <c r="A315" s="4">
         <v>314</v>
       </c>
@@ -16263,7 +16336,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="316" spans="1:11" hidden="1">
+    <row r="316" spans="1:11">
       <c r="A316" s="4">
         <v>315</v>
       </c>
@@ -16298,7 +16371,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="317" spans="1:11" hidden="1">
+    <row r="317" spans="1:11">
       <c r="A317" s="4">
         <v>316</v>
       </c>
@@ -16333,7 +16406,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="318" spans="1:11" hidden="1">
+    <row r="318" spans="1:11">
       <c r="A318" s="4">
         <v>317</v>
       </c>
@@ -16368,7 +16441,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="319" spans="1:11" hidden="1">
+    <row r="319" spans="1:11">
       <c r="A319" s="4">
         <v>318</v>
       </c>
@@ -16403,7 +16476,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="320" spans="1:11" hidden="1">
+    <row r="320" spans="1:11">
       <c r="A320" s="4">
         <v>319</v>
       </c>
@@ -16438,7 +16511,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="321" spans="1:11" hidden="1">
+    <row r="321" spans="1:11">
       <c r="A321" s="4">
         <v>320</v>
       </c>
@@ -16473,7 +16546,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="322" spans="1:11" hidden="1">
+    <row r="322" spans="1:11">
       <c r="A322" s="4">
         <v>321</v>
       </c>
@@ -16508,7 +16581,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="323" spans="1:11" hidden="1">
+    <row r="323" spans="1:11">
       <c r="A323" s="4">
         <v>322</v>
       </c>
@@ -16543,7 +16616,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="324" spans="1:11" hidden="1">
+    <row r="324" spans="1:11">
       <c r="A324" s="4">
         <v>323</v>
       </c>
@@ -16578,7 +16651,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="325" spans="1:11" hidden="1">
+    <row r="325" spans="1:11">
       <c r="A325" s="4">
         <v>324</v>
       </c>
@@ -16613,7 +16686,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="326" spans="1:11" hidden="1">
+    <row r="326" spans="1:11">
       <c r="A326" s="4">
         <v>325</v>
       </c>
@@ -16648,7 +16721,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="327" spans="1:11" hidden="1">
+    <row r="327" spans="1:11">
       <c r="A327" s="4">
         <v>326</v>
       </c>
@@ -16683,7 +16756,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="328" spans="1:11" hidden="1">
+    <row r="328" spans="1:11">
       <c r="A328" s="4">
         <v>327</v>
       </c>
@@ -16716,7 +16789,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="329" spans="1:11" hidden="1">
+    <row r="329" spans="1:11">
       <c r="A329" s="4">
         <v>328</v>
       </c>
@@ -16749,7 +16822,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="330" spans="1:11" hidden="1">
+    <row r="330" spans="1:11">
       <c r="A330" s="4">
         <v>329</v>
       </c>
@@ -16782,7 +16855,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="331" spans="1:11" hidden="1">
+    <row r="331" spans="1:11">
       <c r="A331" s="4">
         <v>330</v>
       </c>
@@ -16815,7 +16888,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="332" spans="1:11" hidden="1">
+    <row r="332" spans="1:11">
       <c r="A332" s="4">
         <v>331</v>
       </c>
@@ -16848,7 +16921,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="333" spans="1:11" hidden="1">
+    <row r="333" spans="1:11">
       <c r="A333" s="4">
         <v>332</v>
       </c>
@@ -16883,7 +16956,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="334" spans="1:11" hidden="1">
+    <row r="334" spans="1:11">
       <c r="A334" s="4">
         <v>333</v>
       </c>
@@ -16916,7 +16989,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="335" spans="1:11" hidden="1">
+    <row r="335" spans="1:11">
       <c r="A335" s="4">
         <v>334</v>
       </c>
@@ -16949,7 +17022,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="336" spans="1:11" hidden="1">
+    <row r="336" spans="1:11">
       <c r="A336" s="4">
         <v>335</v>
       </c>
@@ -16982,7 +17055,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="337" spans="1:11" hidden="1">
+    <row r="337" spans="1:11">
       <c r="A337" s="4">
         <v>336</v>
       </c>
@@ -17017,7 +17090,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="338" spans="1:11" hidden="1">
+    <row r="338" spans="1:11">
       <c r="A338" s="4">
         <v>337</v>
       </c>
@@ -17052,7 +17125,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="339" spans="1:11" hidden="1">
+    <row r="339" spans="1:11">
       <c r="A339" s="4">
         <v>338</v>
       </c>
@@ -17087,7 +17160,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="340" spans="1:11" hidden="1">
+    <row r="340" spans="1:11">
       <c r="A340" s="4">
         <v>339</v>
       </c>
@@ -17122,7 +17195,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="341" spans="1:11" hidden="1">
+    <row r="341" spans="1:11">
       <c r="A341" s="4">
         <v>340</v>
       </c>
@@ -17157,7 +17230,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="342" spans="1:11" hidden="1">
+    <row r="342" spans="1:11">
       <c r="A342" s="4">
         <v>341</v>
       </c>
@@ -17192,7 +17265,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="343" spans="1:11" hidden="1">
+    <row r="343" spans="1:11">
       <c r="A343" s="4">
         <v>342</v>
       </c>
@@ -17227,7 +17300,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="344" spans="1:11" hidden="1">
+    <row r="344" spans="1:11">
       <c r="A344" s="4">
         <v>343</v>
       </c>
@@ -17262,7 +17335,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="345" spans="1:11" hidden="1">
+    <row r="345" spans="1:11">
       <c r="A345" s="4">
         <v>344</v>
       </c>
@@ -17297,7 +17370,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="346" spans="1:11" hidden="1">
+    <row r="346" spans="1:11">
       <c r="A346" s="4">
         <v>345</v>
       </c>
@@ -17332,7 +17405,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="347" spans="1:11" hidden="1">
+    <row r="347" spans="1:11">
       <c r="A347" s="4">
         <v>346</v>
       </c>
@@ -17367,7 +17440,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="348" spans="1:11" hidden="1">
+    <row r="348" spans="1:11">
       <c r="A348" s="4">
         <v>347</v>
       </c>
@@ -17402,7 +17475,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="349" spans="1:11" hidden="1">
+    <row r="349" spans="1:11">
       <c r="A349" s="4">
         <v>348</v>
       </c>
@@ -17437,7 +17510,7 @@
         <v>1296</v>
       </c>
     </row>
-    <row r="350" spans="1:11" hidden="1">
+    <row r="350" spans="1:11">
       <c r="A350" s="4">
         <v>349</v>
       </c>
@@ -17472,7 +17545,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="351" spans="1:11" hidden="1">
+    <row r="351" spans="1:11">
       <c r="A351" s="4">
         <v>350</v>
       </c>
@@ -17507,7 +17580,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="352" spans="1:11" hidden="1">
+    <row r="352" spans="1:11">
       <c r="A352" s="4">
         <v>351</v>
       </c>
@@ -17542,7 +17615,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="353" spans="1:11" hidden="1">
+    <row r="353" spans="1:11">
       <c r="A353" s="4">
         <v>352</v>
       </c>
@@ -17577,7 +17650,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="354" spans="1:11" hidden="1">
+    <row r="354" spans="1:11">
       <c r="A354" s="4">
         <v>353</v>
       </c>
@@ -17612,7 +17685,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="355" spans="1:11" hidden="1">
+    <row r="355" spans="1:11">
       <c r="A355" s="4">
         <v>354</v>
       </c>
@@ -17647,7 +17720,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="356" spans="1:11" hidden="1">
+    <row r="356" spans="1:11">
       <c r="A356" s="4">
         <v>355</v>
       </c>
@@ -17682,7 +17755,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="357" spans="1:11" hidden="1">
+    <row r="357" spans="1:11">
       <c r="A357" s="4">
         <v>356</v>
       </c>
@@ -17717,7 +17790,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="358" spans="1:11" hidden="1">
+    <row r="358" spans="1:11">
       <c r="A358" s="4">
         <v>357</v>
       </c>
@@ -17752,7 +17825,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="359" spans="1:11" hidden="1">
+    <row r="359" spans="1:11">
       <c r="A359" s="4">
         <v>358</v>
       </c>
@@ -17787,7 +17860,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="360" spans="1:11" hidden="1">
+    <row r="360" spans="1:11">
       <c r="A360" s="4">
         <v>359</v>
       </c>
@@ -17822,7 +17895,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="361" spans="1:11" hidden="1">
+    <row r="361" spans="1:11">
       <c r="A361" s="4">
         <v>360</v>
       </c>
@@ -17857,7 +17930,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="362" spans="1:11" hidden="1">
+    <row r="362" spans="1:11">
       <c r="A362" s="4">
         <v>361</v>
       </c>
@@ -17892,7 +17965,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="363" spans="1:11" hidden="1">
+    <row r="363" spans="1:11">
       <c r="A363" s="4">
         <v>362</v>
       </c>
@@ -17927,7 +18000,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="364" spans="1:11" hidden="1">
+    <row r="364" spans="1:11">
       <c r="A364" s="4">
         <v>363</v>
       </c>
@@ -17962,7 +18035,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="365" spans="1:11" hidden="1">
+    <row r="365" spans="1:11">
       <c r="A365" s="4">
         <v>364</v>
       </c>
@@ -17995,7 +18068,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="366" spans="1:11" hidden="1">
+    <row r="366" spans="1:11">
       <c r="A366" s="4">
         <v>365</v>
       </c>
@@ -18030,7 +18103,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="367" spans="1:11" hidden="1">
+    <row r="367" spans="1:11">
       <c r="A367" s="4">
         <v>366</v>
       </c>
@@ -18065,7 +18138,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="368" spans="1:11" hidden="1">
+    <row r="368" spans="1:11">
       <c r="A368" s="4">
         <v>367</v>
       </c>
@@ -18100,7 +18173,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="369" spans="1:11" hidden="1">
+    <row r="369" spans="1:11">
       <c r="A369" s="4">
         <v>368</v>
       </c>
@@ -18135,7 +18208,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="370" spans="1:11" hidden="1">
+    <row r="370" spans="1:11">
       <c r="A370" s="4">
         <v>369</v>
       </c>
@@ -18170,7 +18243,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="371" spans="1:11" hidden="1">
+    <row r="371" spans="1:11">
       <c r="A371" s="4">
         <v>370</v>
       </c>
@@ -18205,7 +18278,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="372" spans="1:11" hidden="1">
+    <row r="372" spans="1:11">
       <c r="A372" s="4">
         <v>371</v>
       </c>
@@ -18240,7 +18313,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="373" spans="1:11" hidden="1">
+    <row r="373" spans="1:11">
       <c r="A373" s="4">
         <v>372</v>
       </c>
@@ -18275,7 +18348,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="374" spans="1:11" hidden="1">
+    <row r="374" spans="1:11">
       <c r="A374" s="4">
         <v>373</v>
       </c>
@@ -18310,7 +18383,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="375" spans="1:11" hidden="1">
+    <row r="375" spans="1:11">
       <c r="A375" s="4">
         <v>374</v>
       </c>
@@ -18345,7 +18418,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="376" spans="1:11" hidden="1">
+    <row r="376" spans="1:11">
       <c r="A376" s="4">
         <v>375</v>
       </c>
@@ -18380,7 +18453,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="377" spans="1:11" hidden="1">
+    <row r="377" spans="1:11">
       <c r="A377" s="4">
         <v>376</v>
       </c>
@@ -18415,7 +18488,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="378" spans="1:11" hidden="1">
+    <row r="378" spans="1:11">
       <c r="A378" s="4">
         <v>377</v>
       </c>
@@ -18450,7 +18523,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="379" spans="1:11" hidden="1">
+    <row r="379" spans="1:11">
       <c r="A379" s="4">
         <v>378</v>
       </c>
@@ -18485,7 +18558,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="380" spans="1:11" hidden="1">
+    <row r="380" spans="1:11">
       <c r="A380" s="4">
         <v>379</v>
       </c>
@@ -18520,7 +18593,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="381" spans="1:11" hidden="1">
+    <row r="381" spans="1:11">
       <c r="A381" s="4">
         <v>380</v>
       </c>
@@ -18555,7 +18628,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="382" spans="1:11" hidden="1">
+    <row r="382" spans="1:11">
       <c r="A382" s="4">
         <v>381</v>
       </c>
@@ -18590,7 +18663,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="383" spans="1:11" hidden="1">
+    <row r="383" spans="1:11">
       <c r="A383" s="4">
         <v>382</v>
       </c>
@@ -18625,7 +18698,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="384" spans="1:11" hidden="1">
+    <row r="384" spans="1:11">
       <c r="A384" s="4">
         <v>383</v>
       </c>
@@ -18660,7 +18733,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="385" spans="1:11" hidden="1">
+    <row r="385" spans="1:11">
       <c r="A385" s="4">
         <v>384</v>
       </c>
@@ -18695,7 +18768,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="386" spans="1:11" hidden="1">
+    <row r="386" spans="1:11">
       <c r="A386" s="4">
         <v>385</v>
       </c>
@@ -18730,7 +18803,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="387" spans="1:11" hidden="1">
+    <row r="387" spans="1:11">
       <c r="A387" s="4">
         <v>386</v>
       </c>
@@ -18765,7 +18838,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="388" spans="1:11" hidden="1">
+    <row r="388" spans="1:11">
       <c r="A388" s="4">
         <v>387</v>
       </c>
@@ -18800,7 +18873,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="389" spans="1:11" hidden="1">
+    <row r="389" spans="1:11">
       <c r="A389" s="4">
         <v>388</v>
       </c>
@@ -18835,7 +18908,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="390" spans="1:11" hidden="1">
+    <row r="390" spans="1:11">
       <c r="A390" s="4">
         <v>389</v>
       </c>
@@ -18870,7 +18943,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="391" spans="1:11" hidden="1">
+    <row r="391" spans="1:11">
       <c r="A391" s="4">
         <v>390</v>
       </c>
@@ -18905,7 +18978,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="392" spans="1:11" hidden="1">
+    <row r="392" spans="1:11">
       <c r="A392" s="4">
         <v>391</v>
       </c>
@@ -18975,7 +19048,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="394" spans="1:11" hidden="1">
+    <row r="394" spans="1:11">
       <c r="A394" s="4">
         <v>393</v>
       </c>
@@ -19008,7 +19081,7 @@
       </c>
       <c r="K394" s="55"/>
     </row>
-    <row r="395" spans="1:11" hidden="1">
+    <row r="395" spans="1:11">
       <c r="A395" s="4">
         <v>394</v>
       </c>
@@ -19041,7 +19114,7 @@
       </c>
       <c r="K395" s="55"/>
     </row>
-    <row r="396" spans="1:11" hidden="1">
+    <row r="396" spans="1:11">
       <c r="A396" s="4">
         <v>395</v>
       </c>
@@ -19074,7 +19147,7 @@
       </c>
       <c r="K396" s="55"/>
     </row>
-    <row r="397" spans="1:11" hidden="1">
+    <row r="397" spans="1:11">
       <c r="A397" s="4">
         <v>396</v>
       </c>
@@ -19109,7 +19182,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="398" spans="1:11" hidden="1">
+    <row r="398" spans="1:11">
       <c r="A398" s="4">
         <v>397</v>
       </c>
@@ -19144,7 +19217,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="399" spans="1:11" hidden="1">
+    <row r="399" spans="1:11">
       <c r="A399" s="4">
         <v>398</v>
       </c>
@@ -19179,7 +19252,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="400" spans="1:11" hidden="1">
+    <row r="400" spans="1:11">
       <c r="A400" s="4">
         <v>399</v>
       </c>
@@ -19249,7 +19322,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="402" spans="1:11" hidden="1">
+    <row r="402" spans="1:11">
       <c r="A402" s="4">
         <v>401</v>
       </c>
@@ -19284,7 +19357,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="403" spans="1:11" hidden="1">
+    <row r="403" spans="1:11">
       <c r="A403" s="4">
         <v>402</v>
       </c>
@@ -19319,7 +19392,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="404" spans="1:11" hidden="1">
+    <row r="404" spans="1:11">
       <c r="A404" s="4">
         <v>403</v>
       </c>
@@ -19354,7 +19427,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="405" spans="1:11" hidden="1">
+    <row r="405" spans="1:11">
       <c r="A405" s="4">
         <v>404</v>
       </c>
@@ -19389,7 +19462,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="406" spans="1:11" hidden="1">
+    <row r="406" spans="1:11">
       <c r="A406" s="4">
         <v>405</v>
       </c>
@@ -19424,7 +19497,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="407" spans="1:11" hidden="1">
+    <row r="407" spans="1:11">
       <c r="A407" s="4">
         <v>406</v>
       </c>
@@ -19459,7 +19532,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="408" spans="1:11" hidden="1">
+    <row r="408" spans="1:11">
       <c r="A408" s="4">
         <v>407</v>
       </c>
@@ -19494,7 +19567,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="409" spans="1:11" hidden="1">
+    <row r="409" spans="1:11">
       <c r="A409" s="4">
         <v>408</v>
       </c>
@@ -19529,7 +19602,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="410" spans="1:11" hidden="1">
+    <row r="410" spans="1:11">
       <c r="A410" s="4">
         <v>409</v>
       </c>
@@ -19564,7 +19637,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="411" spans="1:11" hidden="1">
+    <row r="411" spans="1:11">
       <c r="A411" s="4">
         <v>410</v>
       </c>
@@ -19597,7 +19670,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="412" spans="1:11" hidden="1">
+    <row r="412" spans="1:11">
       <c r="A412" s="4">
         <v>411</v>
       </c>
@@ -19632,7 +19705,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="413" spans="1:11" hidden="1">
+    <row r="413" spans="1:11">
       <c r="A413" s="4">
         <v>412</v>
       </c>
@@ -19667,7 +19740,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="414" spans="1:11" hidden="1">
+    <row r="414" spans="1:11">
       <c r="A414" s="4">
         <v>413</v>
       </c>
@@ -19702,7 +19775,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="415" spans="1:11" hidden="1">
+    <row r="415" spans="1:11">
       <c r="A415" s="4">
         <v>414</v>
       </c>
@@ -19737,7 +19810,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="416" spans="1:11" hidden="1">
+    <row r="416" spans="1:11">
       <c r="A416" s="4">
         <v>415</v>
       </c>
@@ -19770,7 +19843,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="417" spans="1:11" hidden="1">
+    <row r="417" spans="1:11">
       <c r="A417" s="4">
         <v>416</v>
       </c>
@@ -19805,7 +19878,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="418" spans="1:11" hidden="1">
+    <row r="418" spans="1:11">
       <c r="A418" s="4">
         <v>417</v>
       </c>
@@ -19840,7 +19913,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="419" spans="1:11" hidden="1">
+    <row r="419" spans="1:11">
       <c r="A419" s="4">
         <v>418</v>
       </c>
@@ -19875,7 +19948,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="420" spans="1:11" hidden="1">
+    <row r="420" spans="1:11">
       <c r="A420" s="4">
         <v>419</v>
       </c>
@@ -19910,7 +19983,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="421" spans="1:11" hidden="1">
+    <row r="421" spans="1:11">
       <c r="A421" s="4">
         <v>420</v>
       </c>
@@ -19945,7 +20018,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="422" spans="1:11" hidden="1">
+    <row r="422" spans="1:11">
       <c r="A422" s="4">
         <v>421</v>
       </c>
@@ -19980,7 +20053,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="423" spans="1:11" hidden="1">
+    <row r="423" spans="1:11">
       <c r="A423" s="4">
         <v>422</v>
       </c>
@@ -20015,7 +20088,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="424" spans="1:11" hidden="1">
+    <row r="424" spans="1:11">
       <c r="A424" s="4">
         <v>423</v>
       </c>
@@ -20050,7 +20123,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="425" spans="1:11" hidden="1">
+    <row r="425" spans="1:11">
       <c r="A425" s="4">
         <v>424</v>
       </c>
@@ -20085,7 +20158,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="426" spans="1:11" hidden="1">
+    <row r="426" spans="1:11">
       <c r="A426" s="4">
         <v>425</v>
       </c>
@@ -20120,7 +20193,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="427" spans="1:11" hidden="1">
+    <row r="427" spans="1:11">
       <c r="A427" s="4">
         <v>426</v>
       </c>
@@ -20155,7 +20228,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="428" spans="1:11" hidden="1">
+    <row r="428" spans="1:11">
       <c r="A428" s="4">
         <v>427</v>
       </c>
@@ -20190,7 +20263,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="429" spans="1:11" hidden="1">
+    <row r="429" spans="1:11">
       <c r="A429" s="4">
         <v>428</v>
       </c>
@@ -20225,7 +20298,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="430" spans="1:11" hidden="1">
+    <row r="430" spans="1:11">
       <c r="A430" s="4">
         <v>429</v>
       </c>
@@ -20260,7 +20333,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="431" spans="1:11" hidden="1">
+    <row r="431" spans="1:11">
       <c r="A431" s="4">
         <v>430</v>
       </c>
@@ -20295,7 +20368,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="432" spans="1:11" hidden="1">
+    <row r="432" spans="1:11">
       <c r="A432" s="4">
         <v>431</v>
       </c>
@@ -20330,7 +20403,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="433" spans="1:11" hidden="1">
+    <row r="433" spans="1:11">
       <c r="A433" s="4">
         <v>432</v>
       </c>
@@ -20365,7 +20438,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="434" spans="1:11" hidden="1">
+    <row r="434" spans="1:11">
       <c r="A434" s="4">
         <v>433</v>
       </c>
@@ -20376,13 +20449,13 @@
         <v>11</v>
       </c>
       <c r="D434" s="2" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="E434" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F434" s="1" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="G434" s="1" t="s">
         <v>14</v>
@@ -20398,7 +20471,7 @@
       </c>
       <c r="K434" s="55"/>
     </row>
-    <row r="435" spans="1:11" hidden="1">
+    <row r="435" spans="1:11">
       <c r="A435" s="4">
         <v>434</v>
       </c>
@@ -20409,13 +20482,13 @@
         <v>11</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="E435" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F435" s="1" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="G435" s="1" t="s">
         <v>14</v>
@@ -20431,7 +20504,7 @@
       </c>
       <c r="K435" s="55"/>
     </row>
-    <row r="436" spans="1:11" hidden="1">
+    <row r="436" spans="1:11">
       <c r="A436" s="4">
         <v>435</v>
       </c>
@@ -20442,13 +20515,13 @@
         <v>11</v>
       </c>
       <c r="D436" s="2" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="E436" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F436" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="G436" s="1" t="s">
         <v>14</v>
@@ -20464,7 +20537,7 @@
       </c>
       <c r="K436" s="55"/>
     </row>
-    <row r="437" spans="1:11" hidden="1">
+    <row r="437" spans="1:11">
       <c r="A437" s="4">
         <v>436</v>
       </c>
@@ -20475,13 +20548,13 @@
         <v>11</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="E437" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F437" s="1" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="G437" s="1" t="s">
         <v>14</v>
@@ -20497,7 +20570,7 @@
       </c>
       <c r="K437" s="55"/>
     </row>
-    <row r="438" spans="1:11" hidden="1">
+    <row r="438" spans="1:11">
       <c r="A438" s="4">
         <v>437</v>
       </c>
@@ -20508,13 +20581,13 @@
         <v>11</v>
       </c>
       <c r="D438" s="2" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="E438" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F438" s="1" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="G438" s="1" t="s">
         <v>14</v>
@@ -20530,7 +20603,7 @@
       </c>
       <c r="K438" s="55"/>
     </row>
-    <row r="439" spans="1:11" hidden="1">
+    <row r="439" spans="1:11">
       <c r="A439" s="4">
         <v>438</v>
       </c>
@@ -20541,13 +20614,13 @@
         <v>11</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="E439" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F439" s="1" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="G439" s="1" t="s">
         <v>14</v>
@@ -20563,7 +20636,7 @@
       </c>
       <c r="K439" s="55"/>
     </row>
-    <row r="440" spans="1:11" hidden="1">
+    <row r="440" spans="1:11">
       <c r="A440" s="4">
         <v>439</v>
       </c>
@@ -20574,13 +20647,13 @@
         <v>11</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="E440" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F440" s="1" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="G440" s="1" t="s">
         <v>14</v>
@@ -20596,7 +20669,7 @@
       </c>
       <c r="K440" s="55"/>
     </row>
-    <row r="441" spans="1:11" hidden="1">
+    <row r="441" spans="1:11">
       <c r="A441" s="4">
         <v>440</v>
       </c>
@@ -20607,13 +20680,13 @@
         <v>11</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="E441" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F441" s="1" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="G441" s="1" t="s">
         <v>14</v>
@@ -20629,7 +20702,7 @@
       </c>
       <c r="K441" s="55"/>
     </row>
-    <row r="442" spans="1:11" hidden="1">
+    <row r="442" spans="1:11">
       <c r="A442" s="4">
         <v>441</v>
       </c>
@@ -20640,19 +20713,19 @@
         <v>11</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="E442" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F442" s="1" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="G442" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H442" s="1" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="I442" s="54">
         <v>46279</v>
@@ -20662,7 +20735,7 @@
       </c>
       <c r="K442" s="55"/>
     </row>
-    <row r="443" spans="1:11" hidden="1">
+    <row r="443" spans="1:11">
       <c r="A443" s="4">
         <v>442</v>
       </c>
@@ -20673,19 +20746,19 @@
         <v>11</v>
       </c>
       <c r="D443" s="2" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="E443" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F443" s="1" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="G443" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H443" s="1" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="I443" s="54">
         <v>46279</v>
@@ -20695,7 +20768,7 @@
       </c>
       <c r="K443" s="55"/>
     </row>
-    <row r="444" spans="1:11" hidden="1">
+    <row r="444" spans="1:11">
       <c r="A444" s="4">
         <v>443</v>
       </c>
@@ -20706,19 +20779,19 @@
         <v>11</v>
       </c>
       <c r="D444" s="2" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="E444" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F444" s="1" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="G444" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H444" s="1" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="I444" s="54">
         <v>46279</v>
@@ -20728,7 +20801,7 @@
       </c>
       <c r="K444" s="55"/>
     </row>
-    <row r="445" spans="1:11" hidden="1">
+    <row r="445" spans="1:11">
       <c r="A445" s="4">
         <v>444</v>
       </c>
@@ -20739,19 +20812,19 @@
         <v>11</v>
       </c>
       <c r="D445" s="2" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="E445" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F445" s="1" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="G445" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H445" s="1" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="I445" s="54">
         <v>46279</v>
@@ -20761,7 +20834,7 @@
       </c>
       <c r="K445" s="55"/>
     </row>
-    <row r="446" spans="1:11" hidden="1">
+    <row r="446" spans="1:11">
       <c r="A446" s="4">
         <v>445</v>
       </c>
@@ -20772,19 +20845,19 @@
         <v>11</v>
       </c>
       <c r="D446" s="2" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="E446" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F446" s="1" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="G446" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H446" s="1" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="I446" s="54">
         <v>46279</v>
@@ -20794,7 +20867,7 @@
       </c>
       <c r="K446" s="55"/>
     </row>
-    <row r="447" spans="1:11" hidden="1">
+    <row r="447" spans="1:11">
       <c r="A447" s="4">
         <v>446</v>
       </c>
@@ -20805,19 +20878,19 @@
         <v>11</v>
       </c>
       <c r="D447" s="2" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="E447" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F447" s="1" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="G447" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H447" s="1" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="I447" s="54">
         <v>46279</v>
@@ -20827,7 +20900,7 @@
       </c>
       <c r="K447" s="55"/>
     </row>
-    <row r="448" spans="1:11" hidden="1">
+    <row r="448" spans="1:11">
       <c r="A448" s="4">
         <v>447</v>
       </c>
@@ -20838,19 +20911,19 @@
         <v>11</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="E448" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F448" s="1" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="G448" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H448" s="1" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="I448" s="54">
         <v>46279</v>
@@ -20860,7 +20933,7 @@
       </c>
       <c r="K448" s="55"/>
     </row>
-    <row r="449" spans="1:11" hidden="1">
+    <row r="449" spans="1:11">
       <c r="A449" s="4">
         <v>448</v>
       </c>
@@ -20871,19 +20944,19 @@
         <v>11</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="E449" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F449" s="1" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="G449" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H449" s="1" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="I449" s="54">
         <v>46279</v>
@@ -20893,7 +20966,7 @@
       </c>
       <c r="K449" s="55"/>
     </row>
-    <row r="450" spans="1:11" hidden="1">
+    <row r="450" spans="1:11">
       <c r="A450" s="4">
         <v>449</v>
       </c>
@@ -20904,19 +20977,19 @@
         <v>11</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="E450" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F450" s="1" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="G450" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H450" s="1" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="I450" s="54">
         <v>46279</v>
@@ -20926,7 +20999,7 @@
       </c>
       <c r="K450" s="55"/>
     </row>
-    <row r="451" spans="1:11" hidden="1">
+    <row r="451" spans="1:11">
       <c r="A451" s="4">
         <v>450</v>
       </c>
@@ -20937,19 +21010,19 @@
         <v>11</v>
       </c>
       <c r="D451" s="2" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="E451" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F451" s="1" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="G451" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H451" s="1" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="I451" s="54">
         <v>46279</v>
@@ -20959,7 +21032,7 @@
       </c>
       <c r="K451" s="55"/>
     </row>
-    <row r="452" spans="1:11" hidden="1">
+    <row r="452" spans="1:11">
       <c r="A452" s="4">
         <v>451</v>
       </c>
@@ -20970,19 +21043,19 @@
         <v>11</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E452" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F452" s="1" t="s">
+        <v>1433</v>
+      </c>
+      <c r="G452" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H452" s="1" t="s">
         <v>1434</v>
-      </c>
-      <c r="G452" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H452" s="1" t="s">
-        <v>1435</v>
       </c>
       <c r="I452" s="54">
         <v>46279</v>
@@ -20992,7 +21065,7 @@
       </c>
       <c r="K452" s="55"/>
     </row>
-    <row r="453" spans="1:11" hidden="1">
+    <row r="453" spans="1:11">
       <c r="A453" s="4">
         <v>452</v>
       </c>
@@ -21003,19 +21076,19 @@
         <v>11</v>
       </c>
       <c r="D453" s="2" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="E453" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F453" s="1" t="s">
-        <v>1397</v>
+        <v>1451</v>
       </c>
       <c r="G453" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H453" s="1" t="s">
-        <v>1361</v>
+        <v>1347</v>
       </c>
       <c r="I453" s="54">
         <v>46279</v>
@@ -21025,7 +21098,7 @@
       </c>
       <c r="K453" s="55"/>
     </row>
-    <row r="454" spans="1:11" hidden="1">
+    <row r="454" spans="1:11">
       <c r="A454" s="4">
         <v>453</v>
       </c>
@@ -21058,7 +21131,7 @@
       </c>
       <c r="K454" s="55"/>
     </row>
-    <row r="455" spans="1:11" hidden="1">
+    <row r="455" spans="1:11">
       <c r="A455" s="4">
         <v>454</v>
       </c>
@@ -21091,7 +21164,7 @@
       </c>
       <c r="K455" s="55"/>
     </row>
-    <row r="456" spans="1:11" hidden="1">
+    <row r="456" spans="1:11">
       <c r="A456" s="4">
         <v>455</v>
       </c>
@@ -21124,7 +21197,7 @@
       </c>
       <c r="K456" s="55"/>
     </row>
-    <row r="457" spans="1:11" hidden="1">
+    <row r="457" spans="1:11">
       <c r="A457" s="4">
         <v>456</v>
       </c>
@@ -21157,7 +21230,7 @@
       </c>
       <c r="K457" s="55"/>
     </row>
-    <row r="458" spans="1:11" hidden="1">
+    <row r="458" spans="1:11">
       <c r="A458" s="4">
         <v>457</v>
       </c>
@@ -21190,7 +21263,7 @@
       </c>
       <c r="K458" s="55"/>
     </row>
-    <row r="459" spans="1:11" hidden="1">
+    <row r="459" spans="1:11">
       <c r="A459" s="4">
         <v>458</v>
       </c>
@@ -21223,7 +21296,7 @@
       </c>
       <c r="K459" s="55"/>
     </row>
-    <row r="460" spans="1:11" hidden="1">
+    <row r="460" spans="1:11">
       <c r="A460" s="4">
         <v>459</v>
       </c>
@@ -21256,7 +21329,7 @@
       </c>
       <c r="K460" s="55"/>
     </row>
-    <row r="461" spans="1:11" hidden="1">
+    <row r="461" spans="1:11">
       <c r="A461" s="4">
         <v>460</v>
       </c>
@@ -21289,7 +21362,7 @@
       </c>
       <c r="K461" s="55"/>
     </row>
-    <row r="462" spans="1:11" hidden="1">
+    <row r="462" spans="1:11">
       <c r="A462" s="4">
         <v>461</v>
       </c>
@@ -21322,7 +21395,7 @@
       </c>
       <c r="K462" s="55"/>
     </row>
-    <row r="463" spans="1:11" hidden="1">
+    <row r="463" spans="1:11">
       <c r="A463" s="4">
         <v>462</v>
       </c>
@@ -21355,7 +21428,7 @@
       </c>
       <c r="K463" s="55"/>
     </row>
-    <row r="464" spans="1:11" hidden="1">
+    <row r="464" spans="1:11">
       <c r="A464" s="4">
         <v>463</v>
       </c>
@@ -21388,7 +21461,7 @@
       </c>
       <c r="K464" s="55"/>
     </row>
-    <row r="465" spans="1:11" hidden="1">
+    <row r="465" spans="1:11">
       <c r="A465" s="4">
         <v>464</v>
       </c>
@@ -21421,7 +21494,7 @@
       </c>
       <c r="K465" s="55"/>
     </row>
-    <row r="466" spans="1:11" hidden="1">
+    <row r="466" spans="1:11">
       <c r="A466" s="4">
         <v>465</v>
       </c>
@@ -21454,7 +21527,7 @@
       </c>
       <c r="K466" s="55"/>
     </row>
-    <row r="467" spans="1:11" hidden="1">
+    <row r="467" spans="1:11">
       <c r="A467" s="4">
         <v>466</v>
       </c>
@@ -21487,7 +21560,7 @@
       </c>
       <c r="K467" s="55"/>
     </row>
-    <row r="468" spans="1:11" hidden="1">
+    <row r="468" spans="1:11">
       <c r="A468" s="4">
         <v>467</v>
       </c>
@@ -21520,7 +21593,7 @@
       </c>
       <c r="K468" s="55"/>
     </row>
-    <row r="469" spans="1:11" hidden="1">
+    <row r="469" spans="1:11">
       <c r="A469" s="4">
         <v>468</v>
       </c>
@@ -21553,7 +21626,7 @@
       </c>
       <c r="K469" s="55"/>
     </row>
-    <row r="470" spans="1:11" hidden="1">
+    <row r="470" spans="1:11">
       <c r="A470" s="4">
         <v>469</v>
       </c>
@@ -21586,7 +21659,7 @@
       </c>
       <c r="K470" s="55"/>
     </row>
-    <row r="471" spans="1:11" hidden="1">
+    <row r="471" spans="1:11">
       <c r="A471" s="4">
         <v>470</v>
       </c>
@@ -21619,7 +21692,7 @@
       </c>
       <c r="K471" s="55"/>
     </row>
-    <row r="472" spans="1:11" hidden="1">
+    <row r="472" spans="1:11">
       <c r="A472" s="4">
         <v>471</v>
       </c>
@@ -21652,7 +21725,7 @@
       </c>
       <c r="K472" s="55"/>
     </row>
-    <row r="473" spans="1:11" hidden="1">
+    <row r="473" spans="1:11">
       <c r="A473" s="4">
         <v>472</v>
       </c>
@@ -21687,7 +21760,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="474" spans="1:11" hidden="1">
+    <row r="474" spans="1:11">
       <c r="A474" s="4">
         <v>473</v>
       </c>
@@ -21722,7 +21795,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="475" spans="1:11" hidden="1">
+    <row r="475" spans="1:11">
       <c r="A475" s="4">
         <v>474</v>
       </c>
@@ -21757,7 +21830,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="476" spans="1:11" hidden="1">
+    <row r="476" spans="1:11">
       <c r="A476" s="4">
         <v>475</v>
       </c>
@@ -21792,7 +21865,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="477" spans="1:11" hidden="1">
+    <row r="477" spans="1:11">
       <c r="A477" s="4">
         <v>476</v>
       </c>
@@ -21827,7 +21900,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="478" spans="1:11" hidden="1">
+    <row r="478" spans="1:11">
       <c r="A478" s="4">
         <v>477</v>
       </c>
@@ -21862,7 +21935,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="479" spans="1:11" hidden="1">
+    <row r="479" spans="1:11">
       <c r="A479" s="4">
         <v>478</v>
       </c>
@@ -21897,7 +21970,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="480" spans="1:11" hidden="1">
+    <row r="480" spans="1:11">
       <c r="A480" s="4">
         <v>479</v>
       </c>
@@ -21932,7 +22005,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="481" spans="1:11" hidden="1">
+    <row r="481" spans="1:11">
       <c r="A481" s="4">
         <v>480</v>
       </c>
@@ -21967,7 +22040,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="482" spans="1:11" hidden="1">
+    <row r="482" spans="1:11">
       <c r="A482" s="4">
         <v>481</v>
       </c>
@@ -22002,7 +22075,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="483" spans="1:11" hidden="1">
+    <row r="483" spans="1:11">
       <c r="A483" s="4">
         <v>482</v>
       </c>
@@ -22037,7 +22110,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="484" spans="1:11" hidden="1">
+    <row r="484" spans="1:11">
       <c r="A484" s="4">
         <v>483</v>
       </c>
@@ -22072,7 +22145,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="485" spans="1:11" hidden="1">
+    <row r="485" spans="1:11">
       <c r="A485" s="4">
         <v>484</v>
       </c>
@@ -22107,7 +22180,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="486" spans="1:11" hidden="1">
+    <row r="486" spans="1:11">
       <c r="A486" s="4">
         <v>485</v>
       </c>
@@ -22142,7 +22215,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="487" spans="1:11" hidden="1">
+    <row r="487" spans="1:11">
       <c r="A487" s="4">
         <v>486</v>
       </c>
@@ -22177,7 +22250,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="488" spans="1:11" hidden="1">
+    <row r="488" spans="1:11">
       <c r="A488" s="4">
         <v>487</v>
       </c>
@@ -22212,7 +22285,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="489" spans="1:11" hidden="1">
+    <row r="489" spans="1:11">
       <c r="A489" s="4">
         <v>488</v>
       </c>
@@ -22247,7 +22320,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="490" spans="1:11" hidden="1">
+    <row r="490" spans="1:11">
       <c r="A490" s="4">
         <v>489</v>
       </c>
@@ -22280,7 +22353,7 @@
       </c>
       <c r="K490" s="24"/>
     </row>
-    <row r="491" spans="1:11" hidden="1">
+    <row r="491" spans="1:11">
       <c r="A491" s="4">
         <v>490</v>
       </c>
@@ -22315,7 +22388,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="492" spans="1:11" hidden="1">
+    <row r="492" spans="1:11">
       <c r="A492" s="4">
         <v>491</v>
       </c>
@@ -22350,7 +22423,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="493" spans="1:11" hidden="1">
+    <row r="493" spans="1:11">
       <c r="A493" s="4">
         <v>492</v>
       </c>
@@ -22385,7 +22458,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="494" spans="1:11" hidden="1">
+    <row r="494" spans="1:11">
       <c r="A494" s="4">
         <v>493</v>
       </c>
@@ -22420,7 +22493,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="495" spans="1:11" hidden="1">
+    <row r="495" spans="1:11">
       <c r="A495" s="4">
         <v>494</v>
       </c>
@@ -22455,7 +22528,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="496" spans="1:11" hidden="1">
+    <row r="496" spans="1:11">
       <c r="A496" s="4">
         <v>495</v>
       </c>
@@ -22490,7 +22563,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="497" spans="1:11" hidden="1">
+    <row r="497" spans="1:11">
       <c r="A497" s="4">
         <v>496</v>
       </c>
@@ -22525,7 +22598,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="498" spans="1:11" hidden="1">
+    <row r="498" spans="1:11">
       <c r="A498" s="4">
         <v>497</v>
       </c>
@@ -22560,7 +22633,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="499" spans="1:11" hidden="1">
+    <row r="499" spans="1:11">
       <c r="A499" s="4">
         <v>498</v>
       </c>
@@ -22595,7 +22668,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="500" spans="1:11" hidden="1">
+    <row r="500" spans="1:11">
       <c r="A500" s="4">
         <v>499</v>
       </c>
@@ -22630,7 +22703,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="501" spans="1:11" hidden="1">
+    <row r="501" spans="1:11">
       <c r="A501" s="4">
         <v>500</v>
       </c>
@@ -22665,7 +22738,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="502" spans="1:11" hidden="1">
+    <row r="502" spans="1:11">
       <c r="A502" s="4">
         <v>501</v>
       </c>
@@ -22733,7 +22806,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="504" spans="1:11" hidden="1">
+    <row r="504" spans="1:11">
       <c r="A504" s="4">
         <v>503</v>
       </c>
@@ -22766,7 +22839,7 @@
       </c>
       <c r="K504" s="24"/>
     </row>
-    <row r="505" spans="1:11" hidden="1">
+    <row r="505" spans="1:11">
       <c r="A505" s="4">
         <v>504</v>
       </c>
@@ -22799,7 +22872,7 @@
       </c>
       <c r="K505" s="24"/>
     </row>
-    <row r="506" spans="1:11" hidden="1">
+    <row r="506" spans="1:11">
       <c r="A506" s="4">
         <v>505</v>
       </c>
@@ -22832,7 +22905,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="507" spans="1:11" hidden="1">
+    <row r="507" spans="1:11">
       <c r="A507" s="4">
         <v>506</v>
       </c>
@@ -22964,7 +23037,7 @@
       </c>
       <c r="K510" s="24"/>
     </row>
-    <row r="511" spans="1:11" hidden="1">
+    <row r="511" spans="1:11">
       <c r="A511" s="4">
         <v>510</v>
       </c>
@@ -22997,7 +23070,7 @@
       </c>
       <c r="K511" s="24"/>
     </row>
-    <row r="512" spans="1:11" hidden="1">
+    <row r="512" spans="1:11">
       <c r="A512" s="4">
         <v>511</v>
       </c>
@@ -23030,7 +23103,7 @@
       </c>
       <c r="K512" s="24"/>
     </row>
-    <row r="513" spans="1:11" hidden="1">
+    <row r="513" spans="1:11">
       <c r="A513" s="4">
         <v>512</v>
       </c>
@@ -23063,7 +23136,7 @@
       </c>
       <c r="K513" s="55"/>
     </row>
-    <row r="514" spans="1:11" hidden="1">
+    <row r="514" spans="1:11">
       <c r="A514" s="4">
         <v>513</v>
       </c>
@@ -23096,7 +23169,7 @@
       </c>
       <c r="K514" s="55"/>
     </row>
-    <row r="515" spans="1:11" hidden="1">
+    <row r="515" spans="1:11">
       <c r="A515" s="4">
         <v>514</v>
       </c>
@@ -23129,7 +23202,7 @@
       </c>
       <c r="K515" s="55"/>
     </row>
-    <row r="516" spans="1:11" hidden="1">
+    <row r="516" spans="1:11">
       <c r="A516" s="4">
         <v>515</v>
       </c>
@@ -23162,7 +23235,7 @@
       </c>
       <c r="K516" s="55"/>
     </row>
-    <row r="517" spans="1:11" hidden="1">
+    <row r="517" spans="1:11">
       <c r="A517" s="4">
         <v>516</v>
       </c>
@@ -24430,7 +24503,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="555" spans="1:11" hidden="1">
+    <row r="555" spans="1:11">
       <c r="A555" s="4">
         <v>554</v>
       </c>
@@ -24540,7 +24613,7 @@
         <v>11</v>
       </c>
       <c r="D558" s="2" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="E558" s="1" t="s">
         <v>19</v>
@@ -24573,7 +24646,7 @@
         <v>11</v>
       </c>
       <c r="D559" s="2" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="E559" s="1" t="s">
         <v>19</v>
@@ -24606,7 +24679,7 @@
         <v>11</v>
       </c>
       <c r="D560" s="2" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="E560" s="1" t="s">
         <v>19</v>
@@ -24639,7 +24712,7 @@
         <v>11</v>
       </c>
       <c r="D561" s="2" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="E561" s="1" t="s">
         <v>19</v>
@@ -24672,7 +24745,7 @@
         <v>11</v>
       </c>
       <c r="D562" s="2" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="E562" s="1" t="s">
         <v>19</v>
@@ -24694,7 +24767,7 @@
       </c>
       <c r="K562" s="55"/>
     </row>
-    <row r="563" spans="1:11" hidden="1">
+    <row r="563" spans="1:11">
       <c r="A563" s="4">
         <v>562</v>
       </c>
@@ -24705,19 +24778,19 @@
         <v>11</v>
       </c>
       <c r="D563" s="2" t="s">
-        <v>1360</v>
+        <v>1444</v>
       </c>
       <c r="E563" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F563" s="1" t="s">
-        <v>521</v>
+        <v>19</v>
+      </c>
+      <c r="F563" s="41" t="s">
+        <v>1051</v>
       </c>
       <c r="G563" s="1" t="s">
         <v>30</v>
       </c>
       <c r="H563" s="1" t="s">
-        <v>1361</v>
+        <v>1340</v>
       </c>
       <c r="I563" s="54">
         <v>46287</v>
@@ -24727,7 +24800,7 @@
       </c>
       <c r="K563" s="55"/>
     </row>
-    <row r="564" spans="1:11" hidden="1">
+    <row r="564" spans="1:11">
       <c r="A564" s="4">
         <v>563</v>
       </c>
@@ -24738,19 +24811,19 @@
         <v>11</v>
       </c>
       <c r="D564" s="2" t="s">
-        <v>1360</v>
+        <v>1445</v>
       </c>
       <c r="E564" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F564" s="1" t="s">
-        <v>521</v>
+        <v>1039</v>
       </c>
       <c r="G564" s="1" t="s">
         <v>30</v>
       </c>
       <c r="H564" s="1" t="s">
-        <v>1361</v>
+        <v>1340</v>
       </c>
       <c r="I564" s="54">
         <v>46287</v>
@@ -24760,7 +24833,7 @@
       </c>
       <c r="K564" s="55"/>
     </row>
-    <row r="565" spans="1:11" hidden="1">
+    <row r="565" spans="1:11">
       <c r="A565" s="4">
         <v>564</v>
       </c>
@@ -24771,19 +24844,19 @@
         <v>11</v>
       </c>
       <c r="D565" s="2" t="s">
-        <v>1360</v>
+        <v>1446</v>
       </c>
       <c r="E565" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F565" s="1" t="s">
-        <v>521</v>
+        <v>1041</v>
       </c>
       <c r="G565" s="1" t="s">
         <v>30</v>
       </c>
       <c r="H565" s="1" t="s">
-        <v>1361</v>
+        <v>1340</v>
       </c>
       <c r="I565" s="54">
         <v>46287</v>
@@ -24793,7 +24866,7 @@
       </c>
       <c r="K565" s="55"/>
     </row>
-    <row r="566" spans="1:11" hidden="1">
+    <row r="566" spans="1:11">
       <c r="A566" s="4">
         <v>565</v>
       </c>
@@ -24804,19 +24877,19 @@
         <v>11</v>
       </c>
       <c r="D566" s="2" t="s">
-        <v>1360</v>
+        <v>1447</v>
       </c>
       <c r="E566" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F566" s="1" t="s">
-        <v>521</v>
+        <v>19</v>
+      </c>
+      <c r="F566" s="4" t="s">
+        <v>1047</v>
       </c>
       <c r="G566" s="1" t="s">
         <v>30</v>
       </c>
       <c r="H566" s="1" t="s">
-        <v>1361</v>
+        <v>1340</v>
       </c>
       <c r="I566" s="54">
         <v>46287</v>
@@ -24826,7 +24899,7 @@
       </c>
       <c r="K566" s="55"/>
     </row>
-    <row r="567" spans="1:11" hidden="1">
+    <row r="567" spans="1:11">
       <c r="A567" s="4">
         <v>566</v>
       </c>
@@ -24837,19 +24910,19 @@
         <v>11</v>
       </c>
       <c r="D567" s="2" t="s">
-        <v>1360</v>
+        <v>1448</v>
       </c>
       <c r="E567" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F567" s="1" t="s">
-        <v>521</v>
+        <v>1053</v>
       </c>
       <c r="G567" s="1" t="s">
         <v>30</v>
       </c>
       <c r="H567" s="1" t="s">
-        <v>1361</v>
+        <v>1340</v>
       </c>
       <c r="I567" s="54">
         <v>46287</v>
@@ -24859,7 +24932,7 @@
       </c>
       <c r="K567" s="55"/>
     </row>
-    <row r="568" spans="1:11" hidden="1">
+    <row r="568" spans="1:11">
       <c r="A568" s="4">
         <v>567</v>
       </c>
@@ -24870,19 +24943,19 @@
         <v>11</v>
       </c>
       <c r="D568" s="2" t="s">
-        <v>1360</v>
+        <v>1449</v>
       </c>
       <c r="E568" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F568" s="1" t="s">
-        <v>521</v>
+        <v>1055</v>
       </c>
       <c r="G568" s="1" t="s">
         <v>30</v>
       </c>
       <c r="H568" s="1" t="s">
-        <v>1361</v>
+        <v>1340</v>
       </c>
       <c r="I568" s="54">
         <v>46287</v>
@@ -24892,7 +24965,7 @@
       </c>
       <c r="K568" s="55"/>
     </row>
-    <row r="569" spans="1:11" hidden="1">
+    <row r="569" spans="1:11">
       <c r="A569" s="4">
         <v>568</v>
       </c>
@@ -24903,19 +24976,19 @@
         <v>11</v>
       </c>
       <c r="D569" s="2" t="s">
-        <v>1360</v>
+        <v>1450</v>
       </c>
       <c r="E569" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F569" s="1" t="s">
-        <v>521</v>
+        <v>1046</v>
       </c>
       <c r="G569" s="1" t="s">
         <v>30</v>
       </c>
       <c r="H569" s="1" t="s">
-        <v>1361</v>
+        <v>1340</v>
       </c>
       <c r="I569" s="54">
         <v>46287</v>
@@ -24925,7 +24998,7 @@
       </c>
       <c r="K569" s="55"/>
     </row>
-    <row r="570" spans="1:11" hidden="1">
+    <row r="570" spans="1:11">
       <c r="A570" s="4">
         <v>569</v>
       </c>
@@ -24958,7 +25031,7 @@
       </c>
       <c r="K570" s="55"/>
     </row>
-    <row r="571" spans="1:11" hidden="1">
+    <row r="571" spans="1:11">
       <c r="A571" s="4">
         <v>570</v>
       </c>
@@ -24991,7 +25064,7 @@
       </c>
       <c r="K571" s="55"/>
     </row>
-    <row r="572" spans="1:11" hidden="1">
+    <row r="572" spans="1:11">
       <c r="A572" s="4">
         <v>571</v>
       </c>
@@ -25024,7 +25097,7 @@
       </c>
       <c r="K572" s="55"/>
     </row>
-    <row r="573" spans="1:11" hidden="1">
+    <row r="573" spans="1:11">
       <c r="A573" s="4">
         <v>572</v>
       </c>
@@ -25057,7 +25130,7 @@
       </c>
       <c r="K573" s="55"/>
     </row>
-    <row r="574" spans="1:11" hidden="1">
+    <row r="574" spans="1:11">
       <c r="A574" s="4">
         <v>573</v>
       </c>
@@ -25090,7 +25163,7 @@
       </c>
       <c r="K574" s="55"/>
     </row>
-    <row r="575" spans="1:11" hidden="1">
+    <row r="575" spans="1:11">
       <c r="A575" s="4">
         <v>574</v>
       </c>
@@ -25123,7 +25196,7 @@
       </c>
       <c r="K575" s="55"/>
     </row>
-    <row r="576" spans="1:11" hidden="1">
+    <row r="576" spans="1:11">
       <c r="A576" s="4">
         <v>575</v>
       </c>
@@ -25156,7 +25229,7 @@
       </c>
       <c r="K576" s="55"/>
     </row>
-    <row r="577" spans="1:11" hidden="1">
+    <row r="577" spans="1:11">
       <c r="A577" s="4">
         <v>576</v>
       </c>
@@ -25189,7 +25262,7 @@
       </c>
       <c r="K577" s="55"/>
     </row>
-    <row r="578" spans="1:11" hidden="1">
+    <row r="578" spans="1:11">
       <c r="A578" s="4">
         <v>577</v>
       </c>
@@ -25222,7 +25295,7 @@
       </c>
       <c r="K578" s="55"/>
     </row>
-    <row r="579" spans="1:11" hidden="1">
+    <row r="579" spans="1:11">
       <c r="A579" s="4">
         <v>578</v>
       </c>
@@ -25253,7 +25326,7 @@
       </c>
       <c r="K579" s="24"/>
     </row>
-    <row r="580" spans="1:11" hidden="1">
+    <row r="580" spans="1:11">
       <c r="A580" s="4">
         <v>579</v>
       </c>
@@ -25313,7 +25386,7 @@
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F254:F255 F257:F559 F561:F1048576 F1:F252">
+  <conditionalFormatting sqref="F1:F252 F254:F255 F257:F559 F561:F562 F564:F1048576">
     <cfRule type="cellIs" dxfId="32" priority="15" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
@@ -25321,7 +25394,7 @@
       <formula>"DOADORA"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F254:F255 F561:F1048576 F1:F252">
+  <conditionalFormatting sqref="F1:F252 F254:F255 F561:F562 F564:F1048576">
     <cfRule type="cellIs" dxfId="30" priority="24" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
@@ -27818,7 +27891,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34C555F1-9084-4660-9D55-C0341FAEDEDD}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
@@ -27947,13 +28020,30 @@
         <v>1390</v>
       </c>
     </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="59" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C8">
+        <v>5899</v>
+      </c>
+      <c r="D8" s="34">
+        <v>46295</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1454</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
     <cfRule type="cellIs" dxfId="4" priority="23" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B7">
+  <conditionalFormatting sqref="B1:B8">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>

--- a/data_printer.xlsx
+++ b/data_printer.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erick\Desktop\New folder\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{933AE2F3-B21E-4CE0-B010-F688021A3E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7021E894-DC95-48D8-80ED-01F8985C9075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{A8AA41B5-7AA1-4FF7-A9B8-54B8A4E1AF28}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160" xr2:uid="{A8AA41B5-7AA1-4FF7-A9B8-54B8A4E1AF28}"/>
   </bookViews>
   <sheets>
     <sheet name="PRINTERS_INVENTORY" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5344" uniqueCount="1455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5345" uniqueCount="1459">
   <si>
     <t>INDICE</t>
   </si>
@@ -3893,9 +3893,6 @@
     <t>ESTAVA NO ATACAREJO FEITA RETIRADA DIA 30/08/2024;  PROBLEMA NA UNIDADE DE FUSÃO; FOI PARA WP PARA FAZER REPAROS 08/01/2025; RICOH IM C4500 FOI SUBSTITUIDA POR 3004; INSTALADA SEC. SAUDE GABINETE FABRICIO SECRETARIO; RETIRADA DO SESAU GABINETE 01/12/2025; RETIRADA DA SEPOL GABINETE POR MOTIVO DE FUSAO 01/06/2026;</t>
   </si>
   <si>
-    <t>E.M. DR. FABIO SIQUEIRA</t>
-  </si>
-  <si>
     <t>FERNANDO</t>
   </si>
   <si>
@@ -4202,9 +4199,6 @@
     <t>XF7A006359</t>
   </si>
   <si>
-    <t>PLANEJAMENTO</t>
-  </si>
-  <si>
     <t>GABINETE - REC</t>
   </si>
   <si>
@@ -4400,9 +4394,6 @@
     <t>XC75053939</t>
   </si>
   <si>
-    <t>XC75053</t>
-  </si>
-  <si>
     <t>SESAU - INFORMATICA</t>
   </si>
   <si>
@@ -4413,6 +4404,27 @@
   </si>
   <si>
     <t xml:space="preserve">DEIXOU ENTRAR AGUA NA IMPRESSORA </t>
+  </si>
+  <si>
+    <t>XC75049067</t>
+  </si>
+  <si>
+    <t>XC75053948</t>
+  </si>
+  <si>
+    <t>XC75053943</t>
+  </si>
+  <si>
+    <t>XC75053954</t>
+  </si>
+  <si>
+    <t>XC75049043</t>
+  </si>
+  <si>
+    <t>E.M. PROF. FABIO SIQUEIRA</t>
+  </si>
+  <si>
+    <t>SEDUC - PLANEJAMENTO</t>
   </si>
 </sst>
 </file>
@@ -4624,7 +4636,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4782,15 +4794,42 @@
     <xf numFmtId="0" fontId="11" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="68">
+  <dxfs count="71">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -5577,23 +5616,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}" name="Controle_Inventario_Impressoras" displayName="Controle_Inventario_Impressoras" ref="A1:K580" tableType="queryTable" totalsRowShown="0" headerRowDxfId="67" dataDxfId="66">
-  <autoFilter ref="A1:K580" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}" name="Controle_Inventario_Impressoras" displayName="Controle_Inventario_Impressoras" ref="A1:K580" tableType="queryTable" totalsRowShown="0" headerRowDxfId="70" dataDxfId="69">
+  <autoFilter ref="A1:K580" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="SEDUC"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K37">
     <sortCondition ref="A23"/>
   </sortState>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F8E3D681-C494-47F2-8429-052381C12AF1}" uniqueName="1" name="INDICE" queryTableFieldId="1" dataDxfId="65"/>
-    <tableColumn id="2" xr3:uid="{EE2E8FA5-A99D-4573-9868-408DB8FD4417}" uniqueName="2" name="MODELO" queryTableFieldId="2" dataDxfId="64"/>
-    <tableColumn id="11" xr3:uid="{CB5196C0-CCA1-4329-825F-D71E0948A542}" uniqueName="11" name="TIPO" queryTableFieldId="16390" dataDxfId="63"/>
-    <tableColumn id="3" xr3:uid="{27BC8F35-CC2C-44A1-BAF7-B0390B09477F}" uniqueName="3" name="NUMERO DE SERIE" queryTableFieldId="3" dataDxfId="62"/>
-    <tableColumn id="4" xr3:uid="{552F7A6E-6277-4DC1-9CDA-EA7FDCCE8E36}" uniqueName="4" name="LOCALIZAÇÃO" queryTableFieldId="4" dataDxfId="61"/>
-    <tableColumn id="5" xr3:uid="{4C8345F1-6E01-4566-9030-039665486C03}" uniqueName="5" name="SETOR" queryTableFieldId="5" dataDxfId="60"/>
-    <tableColumn id="9" xr3:uid="{10436F87-F6F1-46C4-A81A-8D144AC72FDF}" uniqueName="9" name="EMPRESA" queryTableFieldId="16389" dataDxfId="59"/>
-    <tableColumn id="13" xr3:uid="{40F07CF2-DF5F-4979-A5BB-71FA79C89740}" uniqueName="13" name="GRUPO" queryTableFieldId="16393" dataDxfId="58"/>
-    <tableColumn id="6" xr3:uid="{B7941BA2-3E1C-476B-A3C7-BA155A35A2D0}" uniqueName="6" name="ATUALIZADO" queryTableFieldId="6" dataDxfId="57"/>
-    <tableColumn id="7" xr3:uid="{4338F703-CE4B-4443-8A10-74F64ED8CD42}" uniqueName="7" name="PRINTWAY" queryTableFieldId="16391" dataDxfId="56"/>
-    <tableColumn id="8" xr3:uid="{02B7C1FB-8EA9-4F22-BCCF-3D1809FFEDCC}" uniqueName="8" name="OBSERVAÇÃO" queryTableFieldId="8" dataDxfId="55"/>
+    <tableColumn id="1" xr3:uid="{F8E3D681-C494-47F2-8429-052381C12AF1}" uniqueName="1" name="INDICE" queryTableFieldId="1" dataDxfId="68"/>
+    <tableColumn id="2" xr3:uid="{EE2E8FA5-A99D-4573-9868-408DB8FD4417}" uniqueName="2" name="MODELO" queryTableFieldId="2" dataDxfId="67"/>
+    <tableColumn id="11" xr3:uid="{CB5196C0-CCA1-4329-825F-D71E0948A542}" uniqueName="11" name="TIPO" queryTableFieldId="16390" dataDxfId="66"/>
+    <tableColumn id="3" xr3:uid="{27BC8F35-CC2C-44A1-BAF7-B0390B09477F}" uniqueName="3" name="NUMERO DE SERIE" queryTableFieldId="3" dataDxfId="65"/>
+    <tableColumn id="4" xr3:uid="{552F7A6E-6277-4DC1-9CDA-EA7FDCCE8E36}" uniqueName="4" name="LOCALIZAÇÃO" queryTableFieldId="4" dataDxfId="64"/>
+    <tableColumn id="5" xr3:uid="{4C8345F1-6E01-4566-9030-039665486C03}" uniqueName="5" name="SETOR" queryTableFieldId="5" dataDxfId="63"/>
+    <tableColumn id="9" xr3:uid="{10436F87-F6F1-46C4-A81A-8D144AC72FDF}" uniqueName="9" name="EMPRESA" queryTableFieldId="16389" dataDxfId="62"/>
+    <tableColumn id="13" xr3:uid="{40F07CF2-DF5F-4979-A5BB-71FA79C89740}" uniqueName="13" name="GRUPO" queryTableFieldId="16393" dataDxfId="61"/>
+    <tableColumn id="6" xr3:uid="{B7941BA2-3E1C-476B-A3C7-BA155A35A2D0}" uniqueName="6" name="ATUALIZADO" queryTableFieldId="6" dataDxfId="60"/>
+    <tableColumn id="7" xr3:uid="{4338F703-CE4B-4443-8A10-74F64ED8CD42}" uniqueName="7" name="PRINTWAY" queryTableFieldId="16391" dataDxfId="59"/>
+    <tableColumn id="8" xr3:uid="{02B7C1FB-8EA9-4F22-BCCF-3D1809FFEDCC}" uniqueName="8" name="OBSERVAÇÃO" queryTableFieldId="8" dataDxfId="58"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5608,26 +5653,26 @@
     <tableColumn id="3" xr3:uid="{95A3DCD3-FE19-4A74-9940-661D6BB94B25}" name="MODELO"/>
     <tableColumn id="4" xr3:uid="{521C03E5-7FA9-4789-8198-9E0781F3ABC7}" name="DESCRIÇÃO"/>
     <tableColumn id="5" xr3:uid="{579D81F0-AA4C-4609-BF35-AF838B2B149B}" name="COR"/>
-    <tableColumn id="6" xr3:uid="{19487D13-EF31-43DA-89CA-4AA1E1029C34}" name="QUANTIDADE" dataDxfId="54"/>
+    <tableColumn id="6" xr3:uid="{19487D13-EF31-43DA-89CA-4AA1E1029C34}" name="QUANTIDADE" dataDxfId="57"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FBC7B6D1-65BC-435E-B4FF-CC495249D6BD}" name="Tabela4" displayName="Tabela4" ref="A1:J51" insertRowShift="1" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FBC7B6D1-65BC-435E-B4FF-CC495249D6BD}" name="Tabela4" displayName="Tabela4" ref="A1:J51" insertRowShift="1" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
   <autoFilter ref="A1:J51" xr:uid="{FBC7B6D1-65BC-435E-B4FF-CC495249D6BD}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{A3ABFE90-9D3C-42DA-8CF0-D71D91CAB9BB}" name="INDICE" dataDxfId="51"/>
-    <tableColumn id="2" xr3:uid="{A733301C-FC8A-4542-8BA2-BBEA67F3D424}" name="MODELO" dataDxfId="50"/>
-    <tableColumn id="3" xr3:uid="{C6E07CD7-A3F4-4433-BB55-99FA29AE99FA}" name="TIPO" dataDxfId="49"/>
-    <tableColumn id="4" xr3:uid="{007A788B-09E3-480D-A6BC-6718BD4566C1}" name="SERIAL" dataDxfId="48"/>
-    <tableColumn id="5" xr3:uid="{ACA8BAA3-86EA-4046-9E8D-0C6E6216A0B1}" name="LOCALIDADE" dataDxfId="47"/>
-    <tableColumn id="6" xr3:uid="{D2E86C5C-2786-4CA5-9B36-02C6270BDE33}" name="SETOR" dataDxfId="46"/>
-    <tableColumn id="7" xr3:uid="{3F4C4914-DB98-431A-AD17-7760541C7F42}" name="EMPRESA" dataDxfId="45"/>
-    <tableColumn id="8" xr3:uid="{4F681722-ADFE-4A58-BC0F-8623348ECD33}" name="DATA" dataDxfId="44"/>
-    <tableColumn id="9" xr3:uid="{13FFF32F-FC49-429E-BD6E-76ADCE6F7534}" name="MONIT." dataDxfId="43"/>
-    <tableColumn id="10" xr3:uid="{F4255CFF-6FAD-434F-93D8-3A0C54269527}" name="DETALHES" dataDxfId="42"/>
+    <tableColumn id="1" xr3:uid="{A3ABFE90-9D3C-42DA-8CF0-D71D91CAB9BB}" name="INDICE" dataDxfId="54"/>
+    <tableColumn id="2" xr3:uid="{A733301C-FC8A-4542-8BA2-BBEA67F3D424}" name="MODELO" dataDxfId="53"/>
+    <tableColumn id="3" xr3:uid="{C6E07CD7-A3F4-4433-BB55-99FA29AE99FA}" name="TIPO" dataDxfId="52"/>
+    <tableColumn id="4" xr3:uid="{007A788B-09E3-480D-A6BC-6718BD4566C1}" name="SERIAL" dataDxfId="51"/>
+    <tableColumn id="5" xr3:uid="{ACA8BAA3-86EA-4046-9E8D-0C6E6216A0B1}" name="LOCALIDADE" dataDxfId="50"/>
+    <tableColumn id="6" xr3:uid="{D2E86C5C-2786-4CA5-9B36-02C6270BDE33}" name="SETOR" dataDxfId="49"/>
+    <tableColumn id="7" xr3:uid="{3F4C4914-DB98-431A-AD17-7760541C7F42}" name="EMPRESA" dataDxfId="48"/>
+    <tableColumn id="8" xr3:uid="{4F681722-ADFE-4A58-BC0F-8623348ECD33}" name="DATA" dataDxfId="47"/>
+    <tableColumn id="9" xr3:uid="{13FFF32F-FC49-429E-BD6E-76ADCE6F7534}" name="MONIT." dataDxfId="46"/>
+    <tableColumn id="10" xr3:uid="{F4255CFF-6FAD-434F-93D8-3A0C54269527}" name="DETALHES" dataDxfId="45"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5931,20 +5976,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD39631B-97B8-405A-AA43-14CDFBC77F92}">
   <dimension ref="A1:K580"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="22" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="41.109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="255.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.109375" style="3"/>
+    <col min="6" max="6" width="41.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="255.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -5970,7 +6015,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>7</v>
@@ -5982,7 +6027,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" hidden="1">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -6015,7 +6060,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" hidden="1">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -6048,7 +6093,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" hidden="1">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -6081,7 +6126,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" hidden="1">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -6114,7 +6159,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" hidden="1">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -6147,18 +6192,18 @@
         <v>561</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" hidden="1">
       <c r="A7" s="4">
         <v>6</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>21</v>
@@ -6170,7 +6215,7 @@
         <v>14</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I7" s="54">
         <v>46282</v>
@@ -6180,18 +6225,18 @@
       </c>
       <c r="K7" s="55"/>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" hidden="1">
       <c r="A8" s="4">
         <v>7</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>21</v>
@@ -6203,7 +6248,7 @@
         <v>14</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I8" s="54">
         <v>46282</v>
@@ -6213,18 +6258,18 @@
       </c>
       <c r="K8" s="55"/>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" hidden="1">
       <c r="A9" s="4">
         <v>8</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>21</v>
@@ -6236,7 +6281,7 @@
         <v>14</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I9" s="54">
         <v>46282</v>
@@ -6246,18 +6291,18 @@
       </c>
       <c r="K9" s="55"/>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" hidden="1">
       <c r="A10" s="4">
         <v>9</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>21</v>
@@ -6269,7 +6314,7 @@
         <v>14</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I10" s="54">
         <v>46282</v>
@@ -6279,18 +6324,18 @@
       </c>
       <c r="K10" s="55"/>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" hidden="1">
       <c r="A11" s="4">
         <v>10</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>21</v>
@@ -6302,7 +6347,7 @@
         <v>14</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I11" s="54">
         <v>46282</v>
@@ -6312,18 +6357,18 @@
       </c>
       <c r="K11" s="55"/>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" hidden="1">
       <c r="A12" s="4">
         <v>11</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>21</v>
@@ -6335,7 +6380,7 @@
         <v>14</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I12" s="54">
         <v>46282</v>
@@ -6345,18 +6390,18 @@
       </c>
       <c r="K12" s="55"/>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" hidden="1">
       <c r="A13" s="4">
         <v>12</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>21</v>
@@ -6368,7 +6413,7 @@
         <v>14</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I13" s="54">
         <v>46282</v>
@@ -6378,18 +6423,18 @@
       </c>
       <c r="K13" s="55"/>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" hidden="1">
       <c r="A14" s="4">
         <v>13</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>21</v>
@@ -6401,7 +6446,7 @@
         <v>14</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I14" s="54">
         <v>46282</v>
@@ -6411,18 +6456,18 @@
       </c>
       <c r="K14" s="55"/>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" hidden="1">
       <c r="A15" s="4">
         <v>14</v>
       </c>
       <c r="B15" s="30" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>21</v>
@@ -6434,7 +6479,7 @@
         <v>14</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I15" s="54">
         <v>46282</v>
@@ -6444,18 +6489,18 @@
       </c>
       <c r="K15" s="55"/>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" hidden="1">
       <c r="A16" s="4">
         <v>15</v>
       </c>
       <c r="B16" s="30" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>21</v>
@@ -6467,7 +6512,7 @@
         <v>14</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I16" s="54">
         <v>46282</v>
@@ -6477,7 +6522,7 @@
       </c>
       <c r="K16" s="55"/>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" hidden="1">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -6524,15 +6569,17 @@
         <v>27</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>1082</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="H18" s="4"/>
+      <c r="H18" s="1" t="s">
+        <v>1372</v>
+      </c>
       <c r="I18" s="6">
         <v>45797</v>
       </c>
@@ -6543,7 +6590,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" hidden="1">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -6574,7 +6621,7 @@
       </c>
       <c r="K19" s="7"/>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" hidden="1">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -6605,7 +6652,7 @@
       </c>
       <c r="K20" s="7"/>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" hidden="1">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -6628,7 +6675,7 @@
         <v>19</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="I21" s="9">
         <v>45575</v>
@@ -6640,7 +6687,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" hidden="1">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -6657,13 +6704,13 @@
         <v>854</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>19</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="I22" s="9">
         <v>45950</v>
@@ -6675,7 +6722,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" hidden="1">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -6708,7 +6755,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" hidden="1">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -6731,7 +6778,7 @@
         <v>14</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="I24" s="9">
         <v>45964</v>
@@ -6743,7 +6790,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" hidden="1">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -6776,7 +6823,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" hidden="1">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -6806,7 +6853,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" hidden="1">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -6839,7 +6886,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" hidden="1">
       <c r="A28" s="4">
         <v>27</v>
       </c>
@@ -6872,7 +6919,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" hidden="1">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -6905,7 +6952,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" hidden="1">
       <c r="A30" s="4">
         <v>29</v>
       </c>
@@ -6928,7 +6975,7 @@
         <v>14</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I30" s="9">
         <v>45941</v>
@@ -6940,7 +6987,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" hidden="1">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -6973,7 +7020,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="15.75" customHeight="1">
+    <row r="32" spans="1:11" ht="15.75" hidden="1" customHeight="1">
       <c r="A32" s="4">
         <v>31</v>
       </c>
@@ -7006,7 +7053,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" hidden="1">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -7039,7 +7086,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" hidden="1">
       <c r="A34" s="4">
         <v>33</v>
       </c>
@@ -7072,7 +7119,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" hidden="1">
       <c r="A35" s="4">
         <v>34</v>
       </c>
@@ -7105,7 +7152,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" hidden="1">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -7135,7 +7182,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" hidden="1">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -7165,7 +7212,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" hidden="1">
       <c r="A38" s="4">
         <v>37</v>
       </c>
@@ -7198,7 +7245,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" hidden="1">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -7231,7 +7278,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" hidden="1">
       <c r="A40" s="4">
         <v>39</v>
       </c>
@@ -7264,7 +7311,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" hidden="1">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -7297,7 +7344,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" hidden="1">
       <c r="A42" s="4">
         <v>41</v>
       </c>
@@ -7330,7 +7377,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" hidden="1">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -7380,13 +7427,13 @@
         <v>19</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="G44" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="I44" s="9">
         <v>45733</v>
@@ -7395,10 +7442,10 @@
         <v>574</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>1303</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" hidden="1">
       <c r="A45" s="4">
         <v>44</v>
       </c>
@@ -7431,7 +7478,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" hidden="1">
       <c r="A46" s="4">
         <v>45</v>
       </c>
@@ -7464,7 +7511,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" hidden="1">
       <c r="A47" s="4">
         <v>46</v>
       </c>
@@ -7494,7 +7541,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" hidden="1">
       <c r="A48" s="4">
         <v>47</v>
       </c>
@@ -7527,7 +7574,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:11" hidden="1">
       <c r="A49" s="4">
         <v>48</v>
       </c>
@@ -7560,7 +7607,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:11" hidden="1">
       <c r="A50" s="4">
         <v>49</v>
       </c>
@@ -7593,7 +7640,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:11" hidden="1">
       <c r="A51" s="4">
         <v>50</v>
       </c>
@@ -7626,7 +7673,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:11" hidden="1">
       <c r="A52" s="4">
         <v>51</v>
       </c>
@@ -7659,7 +7706,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:11" hidden="1">
       <c r="A53" s="4">
         <v>52</v>
       </c>
@@ -7692,7 +7739,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:11" hidden="1">
       <c r="A54" s="4">
         <v>53</v>
       </c>
@@ -7725,7 +7772,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:11" hidden="1">
       <c r="A55" s="4">
         <v>54</v>
       </c>
@@ -7755,7 +7802,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:11" hidden="1">
       <c r="A56" s="4">
         <v>55</v>
       </c>
@@ -7788,7 +7835,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:11" hidden="1">
       <c r="A57" s="4">
         <v>56</v>
       </c>
@@ -7821,7 +7868,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:11" hidden="1">
       <c r="A58" s="4">
         <v>57</v>
       </c>
@@ -7854,7 +7901,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:11" hidden="1">
       <c r="A59" s="4">
         <v>58</v>
       </c>
@@ -7884,7 +7931,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60" spans="1:11" hidden="1">
       <c r="A60" s="4">
         <v>59</v>
       </c>
@@ -7914,7 +7961,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61" spans="1:11" hidden="1">
       <c r="A61" s="4">
         <v>60</v>
       </c>
@@ -7947,7 +7994,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="62" spans="1:11">
+    <row r="62" spans="1:11" hidden="1">
       <c r="A62" s="4">
         <v>61</v>
       </c>
@@ -7970,7 +8017,7 @@
         <v>68</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="I62" s="15">
         <v>45897</v>
@@ -7982,7 +8029,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:11" hidden="1">
       <c r="A63" s="4">
         <v>62</v>
       </c>
@@ -8005,7 +8052,7 @@
         <v>68</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="I63" s="9">
         <v>45897</v>
@@ -8017,7 +8064,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64" spans="1:11" hidden="1">
       <c r="A64" s="4">
         <v>63</v>
       </c>
@@ -8040,7 +8087,7 @@
         <v>68</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="I64" s="23">
         <v>45950</v>
@@ -8052,7 +8099,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="65" spans="1:11">
+    <row r="65" spans="1:11" hidden="1">
       <c r="A65" s="4">
         <v>64</v>
       </c>
@@ -8063,7 +8110,7 @@
         <v>11</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>21</v>
@@ -8082,7 +8129,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="66" spans="1:11">
+    <row r="66" spans="1:11" hidden="1">
       <c r="A66" s="4">
         <v>65</v>
       </c>
@@ -8112,7 +8159,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="67" spans="1:11">
+    <row r="67" spans="1:11" hidden="1">
       <c r="A67" s="4">
         <v>66</v>
       </c>
@@ -8142,7 +8189,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="68" spans="1:11">
+    <row r="68" spans="1:11" hidden="1">
       <c r="A68" s="4">
         <v>67</v>
       </c>
@@ -8172,7 +8219,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="69" spans="1:11">
+    <row r="69" spans="1:11" hidden="1">
       <c r="A69" s="4">
         <v>68</v>
       </c>
@@ -8202,7 +8249,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="70" spans="1:11">
+    <row r="70" spans="1:11" hidden="1">
       <c r="A70" s="4">
         <v>69</v>
       </c>
@@ -8232,7 +8279,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="71" spans="1:11">
+    <row r="71" spans="1:11" hidden="1">
       <c r="A71" s="4">
         <v>70</v>
       </c>
@@ -8265,7 +8312,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="72" spans="1:11">
+    <row r="72" spans="1:11" hidden="1">
       <c r="A72" s="4">
         <v>71</v>
       </c>
@@ -8298,7 +8345,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="73" spans="1:11">
+    <row r="73" spans="1:11" hidden="1">
       <c r="A73" s="4">
         <v>72</v>
       </c>
@@ -8328,7 +8375,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="74" spans="1:11">
+    <row r="74" spans="1:11" hidden="1">
       <c r="A74" s="4">
         <v>73</v>
       </c>
@@ -8361,7 +8408,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="75" spans="1:11">
+    <row r="75" spans="1:11" hidden="1">
       <c r="A75" s="4">
         <v>74</v>
       </c>
@@ -8391,7 +8438,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="76" spans="1:11">
+    <row r="76" spans="1:11" hidden="1">
       <c r="A76" s="4">
         <v>75</v>
       </c>
@@ -8421,7 +8468,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="77" spans="1:11">
+    <row r="77" spans="1:11" hidden="1">
       <c r="A77" s="4">
         <v>76</v>
       </c>
@@ -8451,7 +8498,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="78" spans="1:11">
+    <row r="78" spans="1:11" hidden="1">
       <c r="A78" s="4">
         <v>77</v>
       </c>
@@ -8481,7 +8528,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="79" spans="1:11">
+    <row r="79" spans="1:11" hidden="1">
       <c r="A79" s="4">
         <v>78</v>
       </c>
@@ -8514,7 +8561,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80" spans="1:11" hidden="1">
       <c r="A80" s="4">
         <v>79</v>
       </c>
@@ -8547,7 +8594,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="81" spans="1:11">
+    <row r="81" spans="1:11" hidden="1">
       <c r="A81" s="4">
         <v>80</v>
       </c>
@@ -8558,7 +8605,7 @@
         <v>11</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>21</v>
@@ -8577,7 +8624,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="82" spans="1:11">
+    <row r="82" spans="1:11" hidden="1">
       <c r="A82" s="4">
         <v>81</v>
       </c>
@@ -8600,7 +8647,7 @@
         <v>14</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I82" s="9">
         <v>45953</v>
@@ -8612,7 +8659,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="83" spans="1:11">
+    <row r="83" spans="1:11" hidden="1">
       <c r="A83" s="4">
         <v>82</v>
       </c>
@@ -8645,7 +8692,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="84" spans="1:11">
+    <row r="84" spans="1:11" hidden="1">
       <c r="A84" s="4">
         <v>83</v>
       </c>
@@ -8678,7 +8725,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="85" spans="1:11">
+    <row r="85" spans="1:11" hidden="1">
       <c r="A85" s="4">
         <v>84</v>
       </c>
@@ -8708,7 +8755,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="86" spans="1:11">
+    <row r="86" spans="1:11" hidden="1">
       <c r="A86" s="4">
         <v>85</v>
       </c>
@@ -8741,7 +8788,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="87" spans="1:11">
+    <row r="87" spans="1:11" hidden="1">
       <c r="A87" s="4">
         <v>86</v>
       </c>
@@ -8774,7 +8821,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="88" spans="1:11">
+    <row r="88" spans="1:11" hidden="1">
       <c r="A88" s="4">
         <v>87</v>
       </c>
@@ -8807,7 +8854,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="89" spans="1:11">
+    <row r="89" spans="1:11" hidden="1">
       <c r="A89" s="4">
         <v>88</v>
       </c>
@@ -8840,7 +8887,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="90" spans="1:11">
+    <row r="90" spans="1:11" hidden="1">
       <c r="A90" s="4">
         <v>89</v>
       </c>
@@ -8873,7 +8920,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="91" spans="1:11">
+    <row r="91" spans="1:11" hidden="1">
       <c r="A91" s="4">
         <v>90</v>
       </c>
@@ -8906,7 +8953,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="92" spans="1:11">
+    <row r="92" spans="1:11" hidden="1">
       <c r="A92" s="4">
         <v>91</v>
       </c>
@@ -8933,7 +8980,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="93" spans="1:11">
+    <row r="93" spans="1:11" hidden="1">
       <c r="A93" s="4">
         <v>92</v>
       </c>
@@ -8960,7 +9007,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="94" spans="1:11">
+    <row r="94" spans="1:11" hidden="1">
       <c r="A94" s="4">
         <v>93</v>
       </c>
@@ -8987,7 +9034,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="95" spans="1:11">
+    <row r="95" spans="1:11" hidden="1">
       <c r="A95" s="4">
         <v>94</v>
       </c>
@@ -9020,7 +9067,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="96" spans="1:11">
+    <row r="96" spans="1:11" hidden="1">
       <c r="A96" s="4">
         <v>95</v>
       </c>
@@ -9076,7 +9123,7 @@
         <v>30</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="I97" s="9">
         <v>45707</v>
@@ -9088,7 +9135,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="98" spans="1:11">
+    <row r="98" spans="1:11" hidden="1">
       <c r="A98" s="4">
         <v>97</v>
       </c>
@@ -9121,7 +9168,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="99" spans="1:11">
+    <row r="99" spans="1:11" hidden="1">
       <c r="A99" s="4">
         <v>98</v>
       </c>
@@ -9151,7 +9198,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="100" spans="1:11">
+    <row r="100" spans="1:11" hidden="1">
       <c r="A100" s="4">
         <v>99</v>
       </c>
@@ -9184,7 +9231,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="101" spans="1:11">
+    <row r="101" spans="1:11" hidden="1">
       <c r="A101" s="4">
         <v>100</v>
       </c>
@@ -9217,7 +9264,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="102" spans="1:11">
+    <row r="102" spans="1:11" hidden="1">
       <c r="A102" s="4">
         <v>101</v>
       </c>
@@ -9244,7 +9291,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="103" spans="1:11">
+    <row r="103" spans="1:11" hidden="1">
       <c r="A103" s="4">
         <v>102</v>
       </c>
@@ -9271,7 +9318,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="104" spans="1:11">
+    <row r="104" spans="1:11" hidden="1">
       <c r="A104" s="4">
         <v>103</v>
       </c>
@@ -9304,7 +9351,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="105" spans="1:11">
+    <row r="105" spans="1:11" hidden="1">
       <c r="A105" s="4">
         <v>104</v>
       </c>
@@ -9334,7 +9381,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="106" spans="1:11">
+    <row r="106" spans="1:11" hidden="1">
       <c r="A106" s="4">
         <v>105</v>
       </c>
@@ -9357,7 +9404,7 @@
         <v>14</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="I106" s="9">
         <v>45653</v>
@@ -9366,7 +9413,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="107" spans="1:11">
+    <row r="107" spans="1:11" hidden="1">
       <c r="A107" s="4">
         <v>106</v>
       </c>
@@ -9396,7 +9443,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="108" spans="1:11">
+    <row r="108" spans="1:11" hidden="1">
       <c r="A108" s="4">
         <v>107</v>
       </c>
@@ -9426,7 +9473,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="109" spans="1:11">
+    <row r="109" spans="1:11" hidden="1">
       <c r="A109" s="4">
         <v>108</v>
       </c>
@@ -9449,7 +9496,7 @@
         <v>14</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="I109" s="9">
         <v>45652</v>
@@ -9461,7 +9508,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="110" spans="1:11">
+    <row r="110" spans="1:11" hidden="1">
       <c r="A110" s="4">
         <v>109</v>
       </c>
@@ -9494,7 +9541,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="111" spans="1:11">
+    <row r="111" spans="1:11" hidden="1">
       <c r="A111" s="4">
         <v>110</v>
       </c>
@@ -9527,7 +9574,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="112" spans="1:11">
+    <row r="112" spans="1:11" hidden="1">
       <c r="A112" s="4">
         <v>111</v>
       </c>
@@ -9550,7 +9597,7 @@
         <v>14</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="I112" s="9">
         <v>45966</v>
@@ -9562,7 +9609,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="113" spans="1:11">
+    <row r="113" spans="1:11" hidden="1">
       <c r="A113" s="4">
         <v>112</v>
       </c>
@@ -9595,7 +9642,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="114" spans="1:11">
+    <row r="114" spans="1:11" hidden="1">
       <c r="A114" s="4">
         <v>113</v>
       </c>
@@ -9628,7 +9675,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="115" spans="1:11">
+    <row r="115" spans="1:11" hidden="1">
       <c r="A115" s="4">
         <v>114</v>
       </c>
@@ -9661,7 +9708,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="116" spans="1:11">
+    <row r="116" spans="1:11" hidden="1">
       <c r="A116" s="4">
         <v>115</v>
       </c>
@@ -9694,7 +9741,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="117" spans="1:11">
+    <row r="117" spans="1:11" hidden="1">
       <c r="A117" s="4">
         <v>116</v>
       </c>
@@ -9727,7 +9774,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="118" spans="1:11">
+    <row r="118" spans="1:11" hidden="1">
       <c r="A118" s="4">
         <v>117</v>
       </c>
@@ -9756,7 +9803,7 @@
       </c>
       <c r="K118" s="24"/>
     </row>
-    <row r="119" spans="1:11">
+    <row r="119" spans="1:11" hidden="1">
       <c r="A119" s="4">
         <v>118</v>
       </c>
@@ -9789,7 +9836,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="120" spans="1:11">
+    <row r="120" spans="1:11" hidden="1">
       <c r="A120" s="4">
         <v>119</v>
       </c>
@@ -9822,7 +9869,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="121" spans="1:11">
+    <row r="121" spans="1:11" hidden="1">
       <c r="A121" s="4">
         <v>120</v>
       </c>
@@ -9855,7 +9902,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="122" spans="1:11">
+    <row r="122" spans="1:11" hidden="1">
       <c r="A122" s="4">
         <v>121</v>
       </c>
@@ -9888,7 +9935,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="123" spans="1:11">
+    <row r="123" spans="1:11" hidden="1">
       <c r="A123" s="4">
         <v>122</v>
       </c>
@@ -9921,7 +9968,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="124" spans="1:11">
+    <row r="124" spans="1:11" hidden="1">
       <c r="A124" s="4">
         <v>123</v>
       </c>
@@ -9954,7 +10001,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="125" spans="1:11">
+    <row r="125" spans="1:11" hidden="1">
       <c r="A125" s="4">
         <v>124</v>
       </c>
@@ -9987,7 +10034,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="126" spans="1:11">
+    <row r="126" spans="1:11" hidden="1">
       <c r="A126" s="4">
         <v>125</v>
       </c>
@@ -10020,7 +10067,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="127" spans="1:11">
+    <row r="127" spans="1:11" hidden="1">
       <c r="A127" s="4">
         <v>126</v>
       </c>
@@ -10053,7 +10100,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="128" spans="1:11">
+    <row r="128" spans="1:11" hidden="1">
       <c r="A128" s="4">
         <v>127</v>
       </c>
@@ -10086,7 +10133,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="129" spans="1:11">
+    <row r="129" spans="1:11" hidden="1">
       <c r="A129" s="4">
         <v>128</v>
       </c>
@@ -10119,7 +10166,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="130" spans="1:11">
+    <row r="130" spans="1:11" hidden="1">
       <c r="A130" s="4">
         <v>129</v>
       </c>
@@ -10152,7 +10199,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="131" spans="1:11">
+    <row r="131" spans="1:11" hidden="1">
       <c r="A131" s="4">
         <v>130</v>
       </c>
@@ -10185,7 +10232,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="132" spans="1:11">
+    <row r="132" spans="1:11" hidden="1">
       <c r="A132" s="4">
         <v>131</v>
       </c>
@@ -10218,7 +10265,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="133" spans="1:11">
+    <row r="133" spans="1:11" hidden="1">
       <c r="A133" s="4">
         <v>132</v>
       </c>
@@ -10251,7 +10298,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="134" spans="1:11">
+    <row r="134" spans="1:11" hidden="1">
       <c r="A134" s="4">
         <v>133</v>
       </c>
@@ -10274,7 +10321,7 @@
         <v>30</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="I134" s="9">
         <v>45744</v>
@@ -10286,7 +10333,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="135" spans="1:11">
+    <row r="135" spans="1:11" hidden="1">
       <c r="A135" s="4">
         <v>134</v>
       </c>
@@ -10309,7 +10356,7 @@
         <v>14</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="I135" s="9">
         <v>45797</v>
@@ -10344,7 +10391,7 @@
         <v>30</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I136" s="9">
         <v>45614</v>
@@ -10356,7 +10403,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="137" spans="1:11">
+    <row r="137" spans="1:11" hidden="1">
       <c r="A137" s="4">
         <v>136</v>
       </c>
@@ -10389,7 +10436,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="138" spans="1:11">
+    <row r="138" spans="1:11" hidden="1">
       <c r="A138" s="4">
         <v>137</v>
       </c>
@@ -10422,7 +10469,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="139" spans="1:11">
+    <row r="139" spans="1:11" hidden="1">
       <c r="A139" s="4">
         <v>138</v>
       </c>
@@ -10455,7 +10502,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="140" spans="1:11">
+    <row r="140" spans="1:11" hidden="1">
       <c r="A140" s="4">
         <v>139</v>
       </c>
@@ -10488,7 +10535,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="141" spans="1:11">
+    <row r="141" spans="1:11" hidden="1">
       <c r="A141" s="4">
         <v>140</v>
       </c>
@@ -10521,7 +10568,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="142" spans="1:11">
+    <row r="142" spans="1:11" hidden="1">
       <c r="A142" s="4">
         <v>141</v>
       </c>
@@ -10535,16 +10582,16 @@
         <v>230</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>1281</v>
+        <v>23</v>
       </c>
       <c r="G142" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I142" s="9">
         <v>45870</v>
@@ -10556,7 +10603,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="143" spans="1:11">
+    <row r="143" spans="1:11" hidden="1">
       <c r="A143" s="4">
         <v>142</v>
       </c>
@@ -10579,7 +10626,7 @@
         <v>14</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I143" s="9">
         <v>46038</v>
@@ -10591,7 +10638,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="144" spans="1:11">
+    <row r="144" spans="1:11" hidden="1">
       <c r="A144" s="4">
         <v>143</v>
       </c>
@@ -10614,7 +10661,7 @@
         <v>14</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I144" s="9">
         <v>45936</v>
@@ -10626,7 +10673,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="145" spans="1:11">
+    <row r="145" spans="1:11" hidden="1">
       <c r="A145" s="4">
         <v>144</v>
       </c>
@@ -10659,7 +10706,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="146" spans="1:11">
+    <row r="146" spans="1:11" hidden="1">
       <c r="A146" s="4">
         <v>145</v>
       </c>
@@ -10673,16 +10720,16 @@
         <v>234</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>1061</v>
+        <v>23</v>
       </c>
       <c r="G146" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I146" s="9">
         <v>45936</v>
@@ -10694,7 +10741,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="147" spans="1:11">
+    <row r="147" spans="1:11" hidden="1">
       <c r="A147" s="4">
         <v>146</v>
       </c>
@@ -10727,7 +10774,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="148" spans="1:11">
+    <row r="148" spans="1:11" hidden="1">
       <c r="A148" s="4">
         <v>147</v>
       </c>
@@ -10757,10 +10804,10 @@
         <v>574</v>
       </c>
       <c r="K148" s="3" t="s">
-        <v>1295</v>
-      </c>
-    </row>
-    <row r="149" spans="1:11">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" hidden="1">
       <c r="A149" s="4">
         <v>148</v>
       </c>
@@ -10793,7 +10840,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="150" spans="1:11">
+    <row r="150" spans="1:11" hidden="1">
       <c r="A150" s="4">
         <v>149</v>
       </c>
@@ -10826,7 +10873,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="151" spans="1:11">
+    <row r="151" spans="1:11" hidden="1">
       <c r="A151" s="4">
         <v>150</v>
       </c>
@@ -10856,10 +10903,10 @@
         <v>574</v>
       </c>
       <c r="K151" s="12" t="s">
-        <v>1301</v>
-      </c>
-    </row>
-    <row r="152" spans="1:11">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" hidden="1">
       <c r="A152" s="4">
         <v>151</v>
       </c>
@@ -10889,10 +10936,10 @@
         <v>574</v>
       </c>
       <c r="K152" s="3" t="s">
-        <v>1294</v>
-      </c>
-    </row>
-    <row r="153" spans="1:11">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" hidden="1">
       <c r="A153" s="4">
         <v>152</v>
       </c>
@@ -10915,7 +10962,7 @@
         <v>68</v>
       </c>
       <c r="H153" s="1" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="I153" s="23">
         <v>46156</v>
@@ -10925,7 +10972,7 @@
       </c>
       <c r="K153" s="24"/>
     </row>
-    <row r="154" spans="1:11">
+    <row r="154" spans="1:11" hidden="1">
       <c r="A154" s="4">
         <v>153</v>
       </c>
@@ -10948,7 +10995,7 @@
         <v>14</v>
       </c>
       <c r="H154" s="1" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="I154" s="9">
         <v>45600</v>
@@ -10960,7 +11007,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="155" spans="1:11">
+    <row r="155" spans="1:11" hidden="1">
       <c r="A155" s="4">
         <v>154</v>
       </c>
@@ -10983,7 +11030,7 @@
         <v>14</v>
       </c>
       <c r="H155" s="1" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="I155" s="9">
         <v>46031</v>
@@ -10995,7 +11042,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="156" spans="1:11">
+    <row r="156" spans="1:11" hidden="1">
       <c r="A156" s="4">
         <v>155</v>
       </c>
@@ -11018,7 +11065,7 @@
         <v>14</v>
       </c>
       <c r="H156" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="I156" s="15">
         <v>45714</v>
@@ -11053,7 +11100,7 @@
         <v>14</v>
       </c>
       <c r="H157" s="4" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="I157" s="15">
         <v>45742</v>
@@ -11065,7 +11112,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="158" spans="1:11">
+    <row r="158" spans="1:11" hidden="1">
       <c r="A158" s="4">
         <v>157</v>
       </c>
@@ -11088,7 +11135,7 @@
         <v>14</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I158" s="15">
         <v>45905</v>
@@ -11100,7 +11147,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="159" spans="1:11">
+    <row r="159" spans="1:11" hidden="1">
       <c r="A159" s="4">
         <v>158</v>
       </c>
@@ -11123,7 +11170,7 @@
         <v>14</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I159" s="15">
         <v>45867</v>
@@ -11158,7 +11205,7 @@
         <v>14</v>
       </c>
       <c r="H160" s="4" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="I160" s="23">
         <v>46162</v>
@@ -11193,7 +11240,7 @@
         <v>14</v>
       </c>
       <c r="H161" s="4" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="I161" s="23">
         <v>46164</v>
@@ -11228,7 +11275,7 @@
         <v>14</v>
       </c>
       <c r="H162" s="4" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="I162" s="23">
         <v>46154</v>
@@ -11261,7 +11308,7 @@
         <v>14</v>
       </c>
       <c r="H163" s="4" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="I163" s="23">
         <v>46154</v>
@@ -11294,7 +11341,7 @@
         <v>14</v>
       </c>
       <c r="H164" s="4" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="I164" s="23">
         <v>46150</v>
@@ -11306,7 +11353,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="165" spans="1:11">
+    <row r="165" spans="1:11" hidden="1">
       <c r="A165" s="4">
         <v>164</v>
       </c>
@@ -11317,19 +11364,19 @@
         <v>83</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="G165" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H165" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="I165" s="23">
         <v>46930</v>
@@ -11338,10 +11385,10 @@
         <v>574</v>
       </c>
       <c r="K165" s="3" t="s">
-        <v>1289</v>
-      </c>
-    </row>
-    <row r="166" spans="1:11">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" hidden="1">
       <c r="A166" s="4">
         <v>165</v>
       </c>
@@ -11352,19 +11399,19 @@
         <v>83</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="G166" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H166" s="1" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="I166" s="23">
         <v>46930</v>
@@ -11373,10 +11420,10 @@
         <v>574</v>
       </c>
       <c r="K166" s="3" t="s">
-        <v>1292</v>
-      </c>
-    </row>
-    <row r="167" spans="1:11">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11" hidden="1">
       <c r="A167" s="4">
         <v>166</v>
       </c>
@@ -11387,19 +11434,19 @@
         <v>83</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="G167" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="I167" s="9">
         <v>46211</v>
@@ -11408,10 +11455,10 @@
         <v>574</v>
       </c>
       <c r="K167" s="3" t="s">
-        <v>1298</v>
-      </c>
-    </row>
-    <row r="168" spans="1:11">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" hidden="1">
       <c r="A168" s="4">
         <v>167</v>
       </c>
@@ -11422,19 +11469,19 @@
         <v>83</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="G168" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="I168" s="54">
         <v>46248</v>
@@ -11444,7 +11491,7 @@
       </c>
       <c r="K168" s="55"/>
     </row>
-    <row r="169" spans="1:11">
+    <row r="169" spans="1:11" hidden="1">
       <c r="A169" s="4">
         <v>168</v>
       </c>
@@ -11477,7 +11524,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="170" spans="1:11">
+    <row r="170" spans="1:11" hidden="1">
       <c r="A170" s="4">
         <v>169</v>
       </c>
@@ -11510,7 +11557,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="171" spans="1:11">
+    <row r="171" spans="1:11" hidden="1">
       <c r="A171" s="4">
         <v>170</v>
       </c>
@@ -11543,7 +11590,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="172" spans="1:11">
+    <row r="172" spans="1:11" hidden="1">
       <c r="A172" s="4">
         <v>171</v>
       </c>
@@ -11566,7 +11613,7 @@
         <v>14</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="I172" s="9">
         <v>45643</v>
@@ -11578,7 +11625,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="173" spans="1:11">
+    <row r="173" spans="1:11" hidden="1">
       <c r="A173" s="4">
         <v>172</v>
       </c>
@@ -11611,7 +11658,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="174" spans="1:11">
+    <row r="174" spans="1:11" hidden="1">
       <c r="A174" s="4">
         <v>173</v>
       </c>
@@ -11644,7 +11691,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="175" spans="1:11">
+    <row r="175" spans="1:11" hidden="1">
       <c r="A175" s="4">
         <v>174</v>
       </c>
@@ -11667,7 +11714,7 @@
         <v>14</v>
       </c>
       <c r="H175" s="4" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="I175" s="9">
         <v>45959</v>
@@ -11679,7 +11726,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="176" spans="1:11">
+    <row r="176" spans="1:11" hidden="1">
       <c r="A176" s="4">
         <v>175</v>
       </c>
@@ -11709,7 +11756,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="177" spans="1:11">
+    <row r="177" spans="1:11" hidden="1">
       <c r="A177" s="4">
         <v>176</v>
       </c>
@@ -11739,7 +11786,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="178" spans="1:11">
+    <row r="178" spans="1:11" hidden="1">
       <c r="A178" s="4">
         <v>177</v>
       </c>
@@ -11767,7 +11814,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="179" spans="1:11">
+    <row r="179" spans="1:11" hidden="1">
       <c r="A179" s="4">
         <v>178</v>
       </c>
@@ -11790,7 +11837,7 @@
         <v>14</v>
       </c>
       <c r="H179" s="1" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="I179" s="9">
         <v>45698</v>
@@ -11802,7 +11849,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="180" spans="1:11">
+    <row r="180" spans="1:11" hidden="1">
       <c r="A180" s="4">
         <v>179</v>
       </c>
@@ -11832,7 +11879,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="181" spans="1:11">
+    <row r="181" spans="1:11" hidden="1">
       <c r="A181" s="4">
         <v>180</v>
       </c>
@@ -11865,7 +11912,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="182" spans="1:11">
+    <row r="182" spans="1:11" hidden="1">
       <c r="A182" s="4">
         <v>181</v>
       </c>
@@ -11898,7 +11945,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="183" spans="1:11">
+    <row r="183" spans="1:11" hidden="1">
       <c r="A183" s="4">
         <v>182</v>
       </c>
@@ -11931,7 +11978,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="184" spans="1:11">
+    <row r="184" spans="1:11" hidden="1">
       <c r="A184" s="4">
         <v>183</v>
       </c>
@@ -11964,7 +12011,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="185" spans="1:11">
+    <row r="185" spans="1:11" hidden="1">
       <c r="A185" s="4">
         <v>184</v>
       </c>
@@ -11994,7 +12041,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="186" spans="1:11">
+    <row r="186" spans="1:11" hidden="1">
       <c r="A186" s="4">
         <v>185</v>
       </c>
@@ -12024,7 +12071,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="187" spans="1:11">
+    <row r="187" spans="1:11" hidden="1">
       <c r="A187" s="4">
         <v>186</v>
       </c>
@@ -12057,7 +12104,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="188" spans="1:11">
+    <row r="188" spans="1:11" hidden="1">
       <c r="A188" s="4">
         <v>187</v>
       </c>
@@ -12084,7 +12131,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="189" spans="1:11">
+    <row r="189" spans="1:11" hidden="1">
       <c r="A189" s="4">
         <v>188</v>
       </c>
@@ -12115,7 +12162,7 @@
       </c>
       <c r="K189" s="24"/>
     </row>
-    <row r="190" spans="1:11">
+    <row r="190" spans="1:11" hidden="1">
       <c r="A190" s="4">
         <v>189</v>
       </c>
@@ -12138,7 +12185,7 @@
         <v>14</v>
       </c>
       <c r="H190" s="1" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="I190" s="9">
         <v>45653</v>
@@ -12150,7 +12197,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="191" spans="1:11">
+    <row r="191" spans="1:11" hidden="1">
       <c r="A191" s="4">
         <v>190</v>
       </c>
@@ -12180,7 +12227,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="192" spans="1:11">
+    <row r="192" spans="1:11" hidden="1">
       <c r="A192" s="4">
         <v>191</v>
       </c>
@@ -12213,7 +12260,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="193" spans="1:10">
+    <row r="193" spans="1:10" hidden="1">
       <c r="A193" s="4">
         <v>192</v>
       </c>
@@ -12243,7 +12290,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="194" spans="1:10">
+    <row r="194" spans="1:10" hidden="1">
       <c r="A194" s="4">
         <v>193</v>
       </c>
@@ -12266,7 +12313,7 @@
         <v>14</v>
       </c>
       <c r="H194" s="1" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="I194" s="9">
         <v>45687</v>
@@ -12275,7 +12322,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="195" spans="1:10">
+    <row r="195" spans="1:10" hidden="1">
       <c r="A195" s="4">
         <v>194</v>
       </c>
@@ -12298,7 +12345,7 @@
         <v>14</v>
       </c>
       <c r="H195" s="1" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="I195" s="9">
         <v>45687</v>
@@ -12307,7 +12354,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="196" spans="1:10">
+    <row r="196" spans="1:10" hidden="1">
       <c r="A196" s="4">
         <v>195</v>
       </c>
@@ -12330,7 +12377,7 @@
         <v>14</v>
       </c>
       <c r="H196" s="1" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="I196" s="9">
         <v>45687</v>
@@ -12339,7 +12386,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="197" spans="1:10">
+    <row r="197" spans="1:10" hidden="1">
       <c r="A197" s="4">
         <v>196</v>
       </c>
@@ -12362,7 +12409,7 @@
         <v>14</v>
       </c>
       <c r="H197" s="1" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="I197" s="9">
         <v>45687</v>
@@ -12371,7 +12418,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="198" spans="1:10">
+    <row r="198" spans="1:10" hidden="1">
       <c r="A198" s="4">
         <v>197</v>
       </c>
@@ -12394,7 +12441,7 @@
         <v>14</v>
       </c>
       <c r="H198" s="1" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="I198" s="9">
         <v>45687</v>
@@ -12403,7 +12450,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="199" spans="1:10">
+    <row r="199" spans="1:10" hidden="1">
       <c r="A199" s="4">
         <v>198</v>
       </c>
@@ -12426,7 +12473,7 @@
         <v>14</v>
       </c>
       <c r="H199" s="1" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="I199" s="9">
         <v>45687</v>
@@ -12435,7 +12482,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="200" spans="1:10">
+    <row r="200" spans="1:10" hidden="1">
       <c r="A200" s="4">
         <v>199</v>
       </c>
@@ -12458,7 +12505,7 @@
         <v>14</v>
       </c>
       <c r="H200" s="1" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="I200" s="9">
         <v>45687</v>
@@ -12467,7 +12514,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="201" spans="1:10">
+    <row r="201" spans="1:10" hidden="1">
       <c r="A201" s="4">
         <v>200</v>
       </c>
@@ -12490,7 +12537,7 @@
         <v>14</v>
       </c>
       <c r="H201" s="1" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="I201" s="9">
         <v>45687</v>
@@ -12499,7 +12546,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="202" spans="1:10">
+    <row r="202" spans="1:10" hidden="1">
       <c r="A202" s="4">
         <v>201</v>
       </c>
@@ -12522,7 +12569,7 @@
         <v>14</v>
       </c>
       <c r="H202" s="1" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="I202" s="9">
         <v>45687</v>
@@ -12531,7 +12578,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="203" spans="1:10">
+    <row r="203" spans="1:10" hidden="1">
       <c r="A203" s="4">
         <v>202</v>
       </c>
@@ -12554,7 +12601,7 @@
         <v>14</v>
       </c>
       <c r="H203" s="1" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="I203" s="9">
         <v>45687</v>
@@ -12563,7 +12610,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="204" spans="1:10">
+    <row r="204" spans="1:10" hidden="1">
       <c r="A204" s="4">
         <v>203</v>
       </c>
@@ -12586,7 +12633,7 @@
         <v>14</v>
       </c>
       <c r="H204" s="1" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="I204" s="9">
         <v>45687</v>
@@ -12595,7 +12642,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="205" spans="1:10">
+    <row r="205" spans="1:10" hidden="1">
       <c r="A205" s="4">
         <v>204</v>
       </c>
@@ -12618,7 +12665,7 @@
         <v>14</v>
       </c>
       <c r="H205" s="1" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="I205" s="9">
         <v>45687</v>
@@ -12627,7 +12674,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="206" spans="1:10">
+    <row r="206" spans="1:10" hidden="1">
       <c r="A206" s="4">
         <v>205</v>
       </c>
@@ -12650,7 +12697,7 @@
         <v>14</v>
       </c>
       <c r="H206" s="1" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="I206" s="9">
         <v>45687</v>
@@ -12659,7 +12706,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="207" spans="1:10">
+    <row r="207" spans="1:10" hidden="1">
       <c r="A207" s="4">
         <v>206</v>
       </c>
@@ -12682,7 +12729,7 @@
         <v>14</v>
       </c>
       <c r="H207" s="1" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="I207" s="9">
         <v>45687</v>
@@ -12691,7 +12738,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="208" spans="1:10">
+    <row r="208" spans="1:10" hidden="1">
       <c r="A208" s="4">
         <v>207</v>
       </c>
@@ -12714,7 +12761,7 @@
         <v>14</v>
       </c>
       <c r="H208" s="1" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="I208" s="9">
         <v>45687</v>
@@ -12723,7 +12770,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="209" spans="1:11">
+    <row r="209" spans="1:11" hidden="1">
       <c r="A209" s="4">
         <v>208</v>
       </c>
@@ -12746,7 +12793,7 @@
         <v>14</v>
       </c>
       <c r="H209" s="1" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="I209" s="9">
         <v>45687</v>
@@ -12755,7 +12802,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="210" spans="1:11">
+    <row r="210" spans="1:11" hidden="1">
       <c r="A210" s="4">
         <v>209</v>
       </c>
@@ -12778,7 +12825,7 @@
         <v>14</v>
       </c>
       <c r="H210" s="1" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="I210" s="9">
         <v>45687</v>
@@ -12787,7 +12834,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="211" spans="1:11">
+    <row r="211" spans="1:11" hidden="1">
       <c r="A211" s="4">
         <v>210</v>
       </c>
@@ -12810,7 +12857,7 @@
         <v>14</v>
       </c>
       <c r="H211" s="1" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="I211" s="9">
         <v>45687</v>
@@ -12819,7 +12866,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="212" spans="1:11">
+    <row r="212" spans="1:11" hidden="1">
       <c r="A212" s="4">
         <v>211</v>
       </c>
@@ -12842,7 +12889,7 @@
         <v>14</v>
       </c>
       <c r="H212" s="1" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="I212" s="9">
         <v>45687</v>
@@ -12851,7 +12898,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="213" spans="1:11">
+    <row r="213" spans="1:11" hidden="1">
       <c r="A213" s="4">
         <v>212</v>
       </c>
@@ -12874,7 +12921,7 @@
         <v>14</v>
       </c>
       <c r="H213" s="1" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="I213" s="9">
         <v>45687</v>
@@ -12883,7 +12930,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="214" spans="1:11">
+    <row r="214" spans="1:11" hidden="1">
       <c r="A214" s="4">
         <v>213</v>
       </c>
@@ -12906,7 +12953,7 @@
         <v>14</v>
       </c>
       <c r="H214" s="1" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="I214" s="9">
         <v>45687</v>
@@ -12915,7 +12962,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="215" spans="1:11">
+    <row r="215" spans="1:11" hidden="1">
       <c r="A215" s="4">
         <v>214</v>
       </c>
@@ -12938,7 +12985,7 @@
         <v>14</v>
       </c>
       <c r="H215" s="1" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="I215" s="9">
         <v>45687</v>
@@ -12950,7 +12997,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="216" spans="1:11">
+    <row r="216" spans="1:11" hidden="1">
       <c r="A216" s="4">
         <v>215</v>
       </c>
@@ -12973,7 +13020,7 @@
         <v>14</v>
       </c>
       <c r="H216" s="1" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="I216" s="9">
         <v>45652</v>
@@ -12985,7 +13032,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="217" spans="1:11">
+    <row r="217" spans="1:11" hidden="1">
       <c r="A217" s="4">
         <v>216</v>
       </c>
@@ -13018,7 +13065,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="218" spans="1:11">
+    <row r="218" spans="1:11" hidden="1">
       <c r="A218" s="4">
         <v>217</v>
       </c>
@@ -13051,7 +13098,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="219" spans="1:11">
+    <row r="219" spans="1:11" hidden="1">
       <c r="A219" s="4">
         <v>218</v>
       </c>
@@ -13082,7 +13129,7 @@
       </c>
       <c r="K219" s="24"/>
     </row>
-    <row r="220" spans="1:11">
+    <row r="220" spans="1:11" hidden="1">
       <c r="A220" s="4">
         <v>219</v>
       </c>
@@ -13115,7 +13162,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="221" spans="1:11">
+    <row r="221" spans="1:11" hidden="1">
       <c r="A221" s="4">
         <v>220</v>
       </c>
@@ -13148,7 +13195,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="222" spans="1:11">
+    <row r="222" spans="1:11" hidden="1">
       <c r="A222" s="4">
         <v>221</v>
       </c>
@@ -13181,7 +13228,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="223" spans="1:11">
+    <row r="223" spans="1:11" hidden="1">
       <c r="A223" s="4">
         <v>222</v>
       </c>
@@ -13204,7 +13251,7 @@
         <v>14</v>
       </c>
       <c r="H223" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I223" s="9">
         <v>45649</v>
@@ -13216,7 +13263,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="224" spans="1:11">
+    <row r="224" spans="1:11" hidden="1">
       <c r="A224" s="4">
         <v>223</v>
       </c>
@@ -13249,7 +13296,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="225" spans="1:11">
+    <row r="225" spans="1:11" hidden="1">
       <c r="A225" s="4">
         <v>224</v>
       </c>
@@ -13266,13 +13313,13 @@
         <v>68</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="G225" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H225" s="4" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I225" s="9">
         <v>45714</v>
@@ -13281,10 +13328,10 @@
         <v>574</v>
       </c>
       <c r="K225" s="3" t="s">
-        <v>1305</v>
-      </c>
-    </row>
-    <row r="226" spans="1:11">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="226" spans="1:11" hidden="1">
       <c r="A226" s="4">
         <v>225</v>
       </c>
@@ -13307,7 +13354,7 @@
         <v>30</v>
       </c>
       <c r="H226" s="1" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="I226" s="9">
         <v>45707</v>
@@ -13319,7 +13366,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="227" spans="1:11">
+    <row r="227" spans="1:11" hidden="1">
       <c r="A227" s="4">
         <v>226</v>
       </c>
@@ -13352,7 +13399,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="228" spans="1:11">
+    <row r="228" spans="1:11" hidden="1">
       <c r="A228" s="4">
         <v>227</v>
       </c>
@@ -13385,7 +13432,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="229" spans="1:11">
+    <row r="229" spans="1:11" hidden="1">
       <c r="A229" s="4">
         <v>228</v>
       </c>
@@ -13408,7 +13455,7 @@
         <v>14</v>
       </c>
       <c r="H229" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I229" s="9">
         <v>45873</v>
@@ -13420,7 +13467,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="230" spans="1:11">
+    <row r="230" spans="1:11" hidden="1">
       <c r="A230" s="4">
         <v>229</v>
       </c>
@@ -13434,16 +13481,16 @@
         <v>327</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>1045</v>
+        <v>23</v>
       </c>
       <c r="G230" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H230" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I230" s="9">
         <v>45936</v>
@@ -13455,7 +13502,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="231" spans="1:11">
+    <row r="231" spans="1:11" hidden="1">
       <c r="A231" s="4">
         <v>230</v>
       </c>
@@ -13478,7 +13525,7 @@
         <v>14</v>
       </c>
       <c r="H231" s="1" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="I231" s="9">
         <v>45942</v>
@@ -13490,7 +13537,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="232" spans="1:11">
+    <row r="232" spans="1:11" hidden="1">
       <c r="A232" s="4">
         <v>231</v>
       </c>
@@ -13523,7 +13570,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="233" spans="1:11">
+    <row r="233" spans="1:11" hidden="1">
       <c r="A233" s="4">
         <v>232</v>
       </c>
@@ -13556,7 +13603,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="234" spans="1:11">
+    <row r="234" spans="1:11" hidden="1">
       <c r="A234" s="4">
         <v>233</v>
       </c>
@@ -13589,7 +13636,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="235" spans="1:11">
+    <row r="235" spans="1:11" hidden="1">
       <c r="A235" s="4">
         <v>234</v>
       </c>
@@ -13622,7 +13669,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="236" spans="1:11">
+    <row r="236" spans="1:11" hidden="1">
       <c r="A236" s="4">
         <v>235</v>
       </c>
@@ -13655,7 +13702,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="237" spans="1:11">
+    <row r="237" spans="1:11" hidden="1">
       <c r="A237" s="4">
         <v>236</v>
       </c>
@@ -13688,7 +13735,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="238" spans="1:11">
+    <row r="238" spans="1:11" hidden="1">
       <c r="A238" s="4">
         <v>237</v>
       </c>
@@ -13711,7 +13758,7 @@
         <v>14</v>
       </c>
       <c r="H238" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I238" s="9">
         <v>45932</v>
@@ -13723,7 +13770,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="239" spans="1:11">
+    <row r="239" spans="1:11" hidden="1">
       <c r="A239" s="4">
         <v>238</v>
       </c>
@@ -13756,7 +13803,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="240" spans="1:11">
+    <row r="240" spans="1:11" hidden="1">
       <c r="A240" s="4">
         <v>239</v>
       </c>
@@ -13779,7 +13826,7 @@
         <v>14</v>
       </c>
       <c r="H240" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I240" s="9">
         <v>45933</v>
@@ -13791,7 +13838,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="241" spans="1:11">
+    <row r="241" spans="1:11" hidden="1">
       <c r="A241" s="4">
         <v>240</v>
       </c>
@@ -13824,7 +13871,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="242" spans="1:11">
+    <row r="242" spans="1:11" hidden="1">
       <c r="A242" s="4">
         <v>241</v>
       </c>
@@ -13847,7 +13894,7 @@
         <v>14</v>
       </c>
       <c r="H242" s="1" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="I242" s="9">
         <v>45636</v>
@@ -13859,7 +13906,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="243" spans="1:11">
+    <row r="243" spans="1:11" hidden="1">
       <c r="A243" s="4">
         <v>242</v>
       </c>
@@ -13892,7 +13939,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="244" spans="1:11">
+    <row r="244" spans="1:11" hidden="1">
       <c r="A244" s="4">
         <v>243</v>
       </c>
@@ -13948,7 +13995,7 @@
         <v>14</v>
       </c>
       <c r="H245" s="4" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="I245" s="9">
         <v>46164</v>
@@ -13960,7 +14007,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="246" spans="1:11">
+    <row r="246" spans="1:11" hidden="1">
       <c r="A246" s="4">
         <v>245</v>
       </c>
@@ -13993,7 +14040,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="247" spans="1:11">
+    <row r="247" spans="1:11" hidden="1">
       <c r="A247" s="4">
         <v>246</v>
       </c>
@@ -14016,7 +14063,7 @@
         <v>14</v>
       </c>
       <c r="H247" s="1" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="I247" s="9">
         <v>45791</v>
@@ -14028,7 +14075,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="248" spans="1:11">
+    <row r="248" spans="1:11" hidden="1">
       <c r="A248" s="4">
         <v>247</v>
       </c>
@@ -14061,7 +14108,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="249" spans="1:11">
+    <row r="249" spans="1:11" hidden="1">
       <c r="A249" s="4">
         <v>248</v>
       </c>
@@ -14094,7 +14141,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="250" spans="1:11">
+    <row r="250" spans="1:11" hidden="1">
       <c r="A250" s="4">
         <v>249</v>
       </c>
@@ -14127,7 +14174,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="251" spans="1:11">
+    <row r="251" spans="1:11" hidden="1">
       <c r="A251" s="4">
         <v>250</v>
       </c>
@@ -14150,7 +14197,7 @@
         <v>14</v>
       </c>
       <c r="H251" s="1" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="I251" s="6">
         <v>45955</v>
@@ -14162,7 +14209,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="252" spans="1:11">
+    <row r="252" spans="1:11" hidden="1">
       <c r="A252" s="4">
         <v>251</v>
       </c>
@@ -14176,16 +14223,16 @@
         <v>356</v>
       </c>
       <c r="E252" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>1056</v>
+        <v>23</v>
       </c>
       <c r="G252" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H252" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I252" s="6">
         <v>45665</v>
@@ -14197,7 +14244,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="253" spans="1:11" ht="15.6">
+    <row r="253" spans="1:11" ht="15.75" hidden="1">
       <c r="A253" s="4">
         <v>252</v>
       </c>
@@ -14220,7 +14267,7 @@
         <v>14</v>
       </c>
       <c r="H253" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I253" s="6">
         <v>46055</v>
@@ -14232,7 +14279,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="254" spans="1:11">
+    <row r="254" spans="1:11" hidden="1">
       <c r="A254" s="4">
         <v>253</v>
       </c>
@@ -14255,7 +14302,7 @@
         <v>14</v>
       </c>
       <c r="H254" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I254" s="9">
         <v>44127</v>
@@ -14290,7 +14337,7 @@
         <v>14</v>
       </c>
       <c r="H255" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I255" s="9">
         <v>45870</v>
@@ -14302,7 +14349,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="256" spans="1:11">
+    <row r="256" spans="1:11" hidden="1">
       <c r="A256" s="4">
         <v>255</v>
       </c>
@@ -14325,7 +14372,7 @@
         <v>14</v>
       </c>
       <c r="H256" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I256" s="6">
         <v>46085</v>
@@ -14337,7 +14384,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="257" spans="1:11">
+    <row r="257" spans="1:11" hidden="1">
       <c r="A257" s="4">
         <v>256</v>
       </c>
@@ -14360,7 +14407,7 @@
         <v>14</v>
       </c>
       <c r="H257" s="1" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="I257" s="15">
         <v>45705</v>
@@ -14372,7 +14419,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="258" spans="1:11">
+    <row r="258" spans="1:11" hidden="1">
       <c r="A258" s="4">
         <v>257</v>
       </c>
@@ -14403,7 +14450,7 @@
       </c>
       <c r="K258" s="20"/>
     </row>
-    <row r="259" spans="1:11">
+    <row r="259" spans="1:11" hidden="1">
       <c r="A259" s="4">
         <v>258</v>
       </c>
@@ -14420,7 +14467,7 @@
         <v>854</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="G259" s="13" t="s">
         <v>14</v>
@@ -14436,7 +14483,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="260" spans="1:11">
+    <row r="260" spans="1:11" hidden="1">
       <c r="A260" s="4">
         <v>259</v>
       </c>
@@ -14453,13 +14500,13 @@
         <v>68</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="G260" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H260" s="1" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="I260" s="9">
         <v>45652</v>
@@ -14468,10 +14515,10 @@
         <v>574</v>
       </c>
       <c r="K260" s="3" t="s">
-        <v>1312</v>
-      </c>
-    </row>
-    <row r="261" spans="1:11">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="261" spans="1:11" hidden="1">
       <c r="A261" s="4">
         <v>260</v>
       </c>
@@ -14494,7 +14541,7 @@
         <v>14</v>
       </c>
       <c r="H261" s="1" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="I261" s="9">
         <v>45870</v>
@@ -14503,10 +14550,10 @@
         <v>574</v>
       </c>
       <c r="K261" s="3" t="s">
-        <v>1377</v>
-      </c>
-    </row>
-    <row r="262" spans="1:11">
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="262" spans="1:11" hidden="1">
       <c r="A262" s="4">
         <v>261</v>
       </c>
@@ -14529,7 +14576,7 @@
         <v>14</v>
       </c>
       <c r="H262" s="1" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="I262" s="9">
         <v>45917</v>
@@ -14538,10 +14585,10 @@
         <v>574</v>
       </c>
       <c r="K262" s="3" t="s">
-        <v>1313</v>
-      </c>
-    </row>
-    <row r="263" spans="1:11">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="263" spans="1:11" hidden="1">
       <c r="A263" s="4">
         <v>262</v>
       </c>
@@ -14574,7 +14621,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="264" spans="1:11">
+    <row r="264" spans="1:11" hidden="1">
       <c r="A264" s="4">
         <v>263</v>
       </c>
@@ -14604,7 +14651,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="265" spans="1:11">
+    <row r="265" spans="1:11" hidden="1">
       <c r="A265" s="4">
         <v>264</v>
       </c>
@@ -14621,7 +14668,7 @@
         <v>854</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="G265" s="4" t="s">
         <v>14</v>
@@ -14637,7 +14684,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="266" spans="1:11">
+    <row r="266" spans="1:11" hidden="1">
       <c r="A266" s="4">
         <v>265</v>
       </c>
@@ -14670,7 +14717,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="267" spans="1:11">
+    <row r="267" spans="1:11" hidden="1">
       <c r="A267" s="4">
         <v>266</v>
       </c>
@@ -14703,7 +14750,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="268" spans="1:11">
+    <row r="268" spans="1:11" hidden="1">
       <c r="A268" s="4">
         <v>267</v>
       </c>
@@ -14733,7 +14780,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="269" spans="1:11">
+    <row r="269" spans="1:11" hidden="1">
       <c r="A269" s="4">
         <v>268</v>
       </c>
@@ -14766,7 +14813,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="270" spans="1:11">
+    <row r="270" spans="1:11" hidden="1">
       <c r="A270" s="4">
         <v>269</v>
       </c>
@@ -14796,7 +14843,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="271" spans="1:11">
+    <row r="271" spans="1:11" hidden="1">
       <c r="A271" s="4">
         <v>270</v>
       </c>
@@ -14826,7 +14873,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="272" spans="1:11">
+    <row r="272" spans="1:11" hidden="1">
       <c r="A272" s="4">
         <v>271</v>
       </c>
@@ -14859,7 +14906,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="273" spans="1:11">
+    <row r="273" spans="1:11" hidden="1">
       <c r="A273" s="4">
         <v>272</v>
       </c>
@@ -14915,7 +14962,7 @@
         <v>14</v>
       </c>
       <c r="H274" s="4" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="I274" s="9">
         <v>46167</v>
@@ -14950,7 +14997,7 @@
         <v>14</v>
       </c>
       <c r="H275" s="4" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="I275" s="9">
         <v>46164</v>
@@ -14962,7 +15009,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="276" spans="1:11">
+    <row r="276" spans="1:11" hidden="1">
       <c r="A276" s="4">
         <v>275</v>
       </c>
@@ -14995,7 +15042,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="277" spans="1:11">
+    <row r="277" spans="1:11" hidden="1">
       <c r="A277" s="4">
         <v>276</v>
       </c>
@@ -15028,7 +15075,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="278" spans="1:11">
+    <row r="278" spans="1:11" hidden="1">
       <c r="A278" s="4">
         <v>277</v>
       </c>
@@ -15061,7 +15108,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="279" spans="1:11">
+    <row r="279" spans="1:11" hidden="1">
       <c r="A279" s="4">
         <v>278</v>
       </c>
@@ -15094,7 +15141,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="280" spans="1:11">
+    <row r="280" spans="1:11" hidden="1">
       <c r="A280" s="4">
         <v>279</v>
       </c>
@@ -15127,7 +15174,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="281" spans="1:11">
+    <row r="281" spans="1:11" hidden="1">
       <c r="A281" s="4">
         <v>280</v>
       </c>
@@ -15160,7 +15207,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="282" spans="1:11">
+    <row r="282" spans="1:11" hidden="1">
       <c r="A282" s="4">
         <v>281</v>
       </c>
@@ -15193,7 +15240,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="283" spans="1:11">
+    <row r="283" spans="1:11" hidden="1">
       <c r="A283" s="4">
         <v>282</v>
       </c>
@@ -15226,7 +15273,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="284" spans="1:11">
+    <row r="284" spans="1:11" hidden="1">
       <c r="A284" s="4">
         <v>283</v>
       </c>
@@ -15256,10 +15303,10 @@
         <v>574</v>
       </c>
       <c r="K284" s="3" t="s">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="285" spans="1:11">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="285" spans="1:11" hidden="1">
       <c r="A285" s="4">
         <v>284</v>
       </c>
@@ -15292,7 +15339,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="286" spans="1:11">
+    <row r="286" spans="1:11" hidden="1">
       <c r="A286" s="4">
         <v>285</v>
       </c>
@@ -15309,13 +15356,13 @@
         <v>68</v>
       </c>
       <c r="F286" s="4" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="G286" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H286" s="1" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="I286" s="9">
         <v>45698</v>
@@ -15327,7 +15374,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="287" spans="1:11">
+    <row r="287" spans="1:11" hidden="1">
       <c r="A287" s="4">
         <v>286</v>
       </c>
@@ -15360,7 +15407,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="288" spans="1:11">
+    <row r="288" spans="1:11" hidden="1">
       <c r="A288" s="4">
         <v>287</v>
       </c>
@@ -15393,7 +15440,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="289" spans="1:11">
+    <row r="289" spans="1:11" hidden="1">
       <c r="A289" s="4">
         <v>288</v>
       </c>
@@ -15426,7 +15473,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="290" spans="1:11">
+    <row r="290" spans="1:11" hidden="1">
       <c r="A290" s="4">
         <v>289</v>
       </c>
@@ -15449,7 +15496,7 @@
         <v>14</v>
       </c>
       <c r="H290" s="1" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="I290" s="9">
         <v>45763</v>
@@ -15461,7 +15508,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="291" spans="1:11">
+    <row r="291" spans="1:11" hidden="1">
       <c r="A291" s="4">
         <v>290</v>
       </c>
@@ -15484,7 +15531,7 @@
         <v>14</v>
       </c>
       <c r="H291" s="1" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="I291" s="9">
         <v>45590</v>
@@ -15496,7 +15543,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="292" spans="1:11">
+    <row r="292" spans="1:11" hidden="1">
       <c r="A292" s="4">
         <v>291</v>
       </c>
@@ -15519,7 +15566,7 @@
         <v>14</v>
       </c>
       <c r="H292" s="1" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I292" s="9">
         <v>45832</v>
@@ -15531,7 +15578,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="293" spans="1:11">
+    <row r="293" spans="1:11" hidden="1">
       <c r="A293" s="4">
         <v>292</v>
       </c>
@@ -15554,7 +15601,7 @@
         <v>14</v>
       </c>
       <c r="H293" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="I293" s="9">
         <v>45590</v>
@@ -15566,7 +15613,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="294" spans="1:11">
+    <row r="294" spans="1:11" hidden="1">
       <c r="A294" s="4">
         <v>293</v>
       </c>
@@ -15589,7 +15636,7 @@
         <v>14</v>
       </c>
       <c r="H294" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="I294" s="9">
         <v>45588</v>
@@ -15601,7 +15648,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="295" spans="1:11">
+    <row r="295" spans="1:11" hidden="1">
       <c r="A295" s="4">
         <v>294</v>
       </c>
@@ -15624,7 +15671,7 @@
         <v>14</v>
       </c>
       <c r="H295" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="I295" s="9">
         <v>45588</v>
@@ -15636,7 +15683,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="296" spans="1:11">
+    <row r="296" spans="1:11" hidden="1">
       <c r="A296" s="4">
         <v>295</v>
       </c>
@@ -15659,7 +15706,7 @@
         <v>14</v>
       </c>
       <c r="H296" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="I296" s="9">
         <v>45594</v>
@@ -15671,7 +15718,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="297" spans="1:11">
+    <row r="297" spans="1:11" hidden="1">
       <c r="A297" s="4">
         <v>296</v>
       </c>
@@ -15694,7 +15741,7 @@
         <v>14</v>
       </c>
       <c r="H297" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="I297" s="9">
         <v>45594</v>
@@ -15706,7 +15753,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="298" spans="1:11">
+    <row r="298" spans="1:11" hidden="1">
       <c r="A298" s="4">
         <v>297</v>
       </c>
@@ -15729,7 +15776,7 @@
         <v>14</v>
       </c>
       <c r="H298" s="1" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="I298" s="9">
         <v>45594</v>
@@ -15741,7 +15788,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="299" spans="1:11">
+    <row r="299" spans="1:11" hidden="1">
       <c r="A299" s="4">
         <v>298</v>
       </c>
@@ -15764,7 +15811,7 @@
         <v>14</v>
       </c>
       <c r="H299" s="1" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="I299" s="9">
         <v>45594</v>
@@ -15776,7 +15823,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="300" spans="1:11">
+    <row r="300" spans="1:11" hidden="1">
       <c r="A300" s="4">
         <v>299</v>
       </c>
@@ -15799,7 +15846,7 @@
         <v>14</v>
       </c>
       <c r="H300" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="I300" s="9">
         <v>45596</v>
@@ -15811,7 +15858,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="301" spans="1:11">
+    <row r="301" spans="1:11" hidden="1">
       <c r="A301" s="4">
         <v>300</v>
       </c>
@@ -15834,7 +15881,7 @@
         <v>14</v>
       </c>
       <c r="H301" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="I301" s="9">
         <v>45596</v>
@@ -15846,7 +15893,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="302" spans="1:11">
+    <row r="302" spans="1:11" hidden="1">
       <c r="A302" s="4">
         <v>301</v>
       </c>
@@ -15869,7 +15916,7 @@
         <v>14</v>
       </c>
       <c r="H302" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="I302" s="9">
         <v>45596</v>
@@ -15881,7 +15928,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="303" spans="1:11">
+    <row r="303" spans="1:11" hidden="1">
       <c r="A303" s="4">
         <v>302</v>
       </c>
@@ -15904,7 +15951,7 @@
         <v>14</v>
       </c>
       <c r="H303" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="I303" s="9">
         <v>45597</v>
@@ -15916,7 +15963,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="304" spans="1:11">
+    <row r="304" spans="1:11" hidden="1">
       <c r="A304" s="4">
         <v>303</v>
       </c>
@@ -15939,7 +15986,7 @@
         <v>14</v>
       </c>
       <c r="H304" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="I304" s="9">
         <v>45597</v>
@@ -15951,7 +15998,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="305" spans="1:11">
+    <row r="305" spans="1:11" hidden="1">
       <c r="A305" s="4">
         <v>304</v>
       </c>
@@ -15974,7 +16021,7 @@
         <v>14</v>
       </c>
       <c r="H305" s="1" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="I305" s="9">
         <v>45597</v>
@@ -15986,7 +16033,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="306" spans="1:11">
+    <row r="306" spans="1:11" hidden="1">
       <c r="A306" s="4">
         <v>305</v>
       </c>
@@ -16009,7 +16056,7 @@
         <v>14</v>
       </c>
       <c r="H306" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="I306" s="9">
         <v>45597</v>
@@ -16021,7 +16068,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="307" spans="1:11">
+    <row r="307" spans="1:11" hidden="1">
       <c r="A307" s="4">
         <v>306</v>
       </c>
@@ -16044,7 +16091,7 @@
         <v>14</v>
       </c>
       <c r="H307" s="1" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="I307" s="9">
         <v>45603</v>
@@ -16056,7 +16103,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="308" spans="1:11">
+    <row r="308" spans="1:11" hidden="1">
       <c r="A308" s="4">
         <v>307</v>
       </c>
@@ -16079,7 +16126,7 @@
         <v>14</v>
       </c>
       <c r="H308" s="1" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="I308" s="9">
         <v>45603</v>
@@ -16091,7 +16138,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="309" spans="1:11">
+    <row r="309" spans="1:11" hidden="1">
       <c r="A309" s="4">
         <v>308</v>
       </c>
@@ -16114,7 +16161,7 @@
         <v>14</v>
       </c>
       <c r="H309" s="1" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="I309" s="9">
         <v>45604</v>
@@ -16126,7 +16173,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="310" spans="1:11">
+    <row r="310" spans="1:11" hidden="1">
       <c r="A310" s="4">
         <v>309</v>
       </c>
@@ -16149,7 +16196,7 @@
         <v>14</v>
       </c>
       <c r="H310" s="1" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="I310" s="9">
         <v>45607</v>
@@ -16161,7 +16208,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="311" spans="1:11">
+    <row r="311" spans="1:11" hidden="1">
       <c r="A311" s="4">
         <v>310</v>
       </c>
@@ -16184,7 +16231,7 @@
         <v>14</v>
       </c>
       <c r="H311" s="1" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="I311" s="9">
         <v>45607</v>
@@ -16196,7 +16243,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="312" spans="1:11">
+    <row r="312" spans="1:11" hidden="1">
       <c r="A312" s="4">
         <v>311</v>
       </c>
@@ -16219,7 +16266,7 @@
         <v>14</v>
       </c>
       <c r="H312" s="1" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="I312" s="9">
         <v>45607</v>
@@ -16231,7 +16278,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="313" spans="1:11">
+    <row r="313" spans="1:11" hidden="1">
       <c r="A313" s="4">
         <v>312</v>
       </c>
@@ -16254,7 +16301,7 @@
         <v>14</v>
       </c>
       <c r="H313" s="1" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="I313" s="9">
         <v>45614</v>
@@ -16266,7 +16313,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="314" spans="1:11">
+    <row r="314" spans="1:11" hidden="1">
       <c r="A314" s="4">
         <v>313</v>
       </c>
@@ -16289,7 +16336,7 @@
         <v>14</v>
       </c>
       <c r="H314" s="1" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="I314" s="9">
         <v>45614</v>
@@ -16301,7 +16348,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="315" spans="1:11">
+    <row r="315" spans="1:11" hidden="1">
       <c r="A315" s="4">
         <v>314</v>
       </c>
@@ -16324,7 +16371,7 @@
         <v>14</v>
       </c>
       <c r="H315" s="1" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="I315" s="9">
         <v>45615</v>
@@ -16336,7 +16383,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="316" spans="1:11">
+    <row r="316" spans="1:11" hidden="1">
       <c r="A316" s="4">
         <v>315</v>
       </c>
@@ -16359,7 +16406,7 @@
         <v>14</v>
       </c>
       <c r="H316" s="1" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="I316" s="9">
         <v>45615</v>
@@ -16371,7 +16418,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="317" spans="1:11">
+    <row r="317" spans="1:11" hidden="1">
       <c r="A317" s="4">
         <v>316</v>
       </c>
@@ -16394,7 +16441,7 @@
         <v>14</v>
       </c>
       <c r="H317" s="1" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="I317" s="9">
         <v>45615</v>
@@ -16406,7 +16453,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="318" spans="1:11">
+    <row r="318" spans="1:11" hidden="1">
       <c r="A318" s="4">
         <v>317</v>
       </c>
@@ -16429,7 +16476,7 @@
         <v>14</v>
       </c>
       <c r="H318" s="1" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="I318" s="9">
         <v>45617</v>
@@ -16441,7 +16488,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="319" spans="1:11">
+    <row r="319" spans="1:11" hidden="1">
       <c r="A319" s="4">
         <v>318</v>
       </c>
@@ -16464,7 +16511,7 @@
         <v>14</v>
       </c>
       <c r="H319" s="1" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="I319" s="9">
         <v>45617</v>
@@ -16476,7 +16523,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="320" spans="1:11">
+    <row r="320" spans="1:11" hidden="1">
       <c r="A320" s="4">
         <v>319</v>
       </c>
@@ -16499,7 +16546,7 @@
         <v>14</v>
       </c>
       <c r="H320" s="1" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="I320" s="9">
         <v>45618</v>
@@ -16511,7 +16558,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="321" spans="1:11">
+    <row r="321" spans="1:11" hidden="1">
       <c r="A321" s="4">
         <v>320</v>
       </c>
@@ -16534,7 +16581,7 @@
         <v>14</v>
       </c>
       <c r="H321" s="1" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="I321" s="9">
         <v>45621</v>
@@ -16546,7 +16593,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="322" spans="1:11">
+    <row r="322" spans="1:11" hidden="1">
       <c r="A322" s="4">
         <v>321</v>
       </c>
@@ -16569,7 +16616,7 @@
         <v>14</v>
       </c>
       <c r="H322" s="1" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="I322" s="9">
         <v>45621</v>
@@ -16581,7 +16628,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="323" spans="1:11">
+    <row r="323" spans="1:11" hidden="1">
       <c r="A323" s="4">
         <v>322</v>
       </c>
@@ -16604,7 +16651,7 @@
         <v>14</v>
       </c>
       <c r="H323" s="1" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="I323" s="9">
         <v>45618</v>
@@ -16616,7 +16663,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="324" spans="1:11">
+    <row r="324" spans="1:11" hidden="1">
       <c r="A324" s="4">
         <v>323</v>
       </c>
@@ -16639,7 +16686,7 @@
         <v>14</v>
       </c>
       <c r="H324" s="1" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="I324" s="9">
         <v>45618</v>
@@ -16651,7 +16698,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="325" spans="1:11">
+    <row r="325" spans="1:11" hidden="1">
       <c r="A325" s="4">
         <v>324</v>
       </c>
@@ -16674,7 +16721,7 @@
         <v>14</v>
       </c>
       <c r="H325" s="1" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="I325" s="9">
         <v>45618</v>
@@ -16686,7 +16733,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="326" spans="1:11">
+    <row r="326" spans="1:11" hidden="1">
       <c r="A326" s="4">
         <v>325</v>
       </c>
@@ -16709,7 +16756,7 @@
         <v>14</v>
       </c>
       <c r="H326" s="1" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="I326" s="9">
         <v>45621</v>
@@ -16721,7 +16768,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="327" spans="1:11">
+    <row r="327" spans="1:11" hidden="1">
       <c r="A327" s="4">
         <v>326</v>
       </c>
@@ -16744,7 +16791,7 @@
         <v>14</v>
       </c>
       <c r="H327" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I327" s="9">
         <v>45622</v>
@@ -16756,7 +16803,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="328" spans="1:11">
+    <row r="328" spans="1:11" hidden="1">
       <c r="A328" s="4">
         <v>327</v>
       </c>
@@ -16789,7 +16836,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="329" spans="1:11">
+    <row r="329" spans="1:11" hidden="1">
       <c r="A329" s="4">
         <v>328</v>
       </c>
@@ -16822,7 +16869,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="330" spans="1:11">
+    <row r="330" spans="1:11" hidden="1">
       <c r="A330" s="4">
         <v>329</v>
       </c>
@@ -16855,7 +16902,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="331" spans="1:11">
+    <row r="331" spans="1:11" hidden="1">
       <c r="A331" s="4">
         <v>330</v>
       </c>
@@ -16888,7 +16935,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="332" spans="1:11">
+    <row r="332" spans="1:11" hidden="1">
       <c r="A332" s="4">
         <v>331</v>
       </c>
@@ -16921,7 +16968,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="333" spans="1:11">
+    <row r="333" spans="1:11" hidden="1">
       <c r="A333" s="4">
         <v>332</v>
       </c>
@@ -16944,7 +16991,7 @@
         <v>14</v>
       </c>
       <c r="H333" s="1" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="I333" s="9">
         <v>45867</v>
@@ -16956,7 +17003,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="334" spans="1:11">
+    <row r="334" spans="1:11" hidden="1">
       <c r="A334" s="4">
         <v>333</v>
       </c>
@@ -16989,7 +17036,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="335" spans="1:11">
+    <row r="335" spans="1:11" hidden="1">
       <c r="A335" s="4">
         <v>334</v>
       </c>
@@ -17022,7 +17069,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="336" spans="1:11">
+    <row r="336" spans="1:11" hidden="1">
       <c r="A336" s="4">
         <v>335</v>
       </c>
@@ -17055,7 +17102,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="337" spans="1:11">
+    <row r="337" spans="1:11" hidden="1">
       <c r="A337" s="4">
         <v>336</v>
       </c>
@@ -17078,7 +17125,7 @@
         <v>14</v>
       </c>
       <c r="H337" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="I337" s="9">
         <v>45667</v>
@@ -17090,7 +17137,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="338" spans="1:11">
+    <row r="338" spans="1:11" hidden="1">
       <c r="A338" s="4">
         <v>337</v>
       </c>
@@ -17113,7 +17160,7 @@
         <v>14</v>
       </c>
       <c r="H338" s="1" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="I338" s="9">
         <v>45842</v>
@@ -17125,7 +17172,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="339" spans="1:11">
+    <row r="339" spans="1:11" hidden="1">
       <c r="A339" s="4">
         <v>338</v>
       </c>
@@ -17148,7 +17195,7 @@
         <v>14</v>
       </c>
       <c r="H339" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="I339" s="9">
         <v>45702</v>
@@ -17160,7 +17207,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="340" spans="1:11">
+    <row r="340" spans="1:11" hidden="1">
       <c r="A340" s="4">
         <v>339</v>
       </c>
@@ -17195,7 +17242,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="341" spans="1:11">
+    <row r="341" spans="1:11" hidden="1">
       <c r="A341" s="4">
         <v>340</v>
       </c>
@@ -17230,7 +17277,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="342" spans="1:11">
+    <row r="342" spans="1:11" hidden="1">
       <c r="A342" s="4">
         <v>341</v>
       </c>
@@ -17253,7 +17300,7 @@
         <v>14</v>
       </c>
       <c r="H342" s="1" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="I342" s="9">
         <v>45705</v>
@@ -17265,7 +17312,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="343" spans="1:11">
+    <row r="343" spans="1:11" hidden="1">
       <c r="A343" s="4">
         <v>342</v>
       </c>
@@ -17288,7 +17335,7 @@
         <v>14</v>
       </c>
       <c r="H343" s="1" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="I343" s="9">
         <v>45726</v>
@@ -17300,7 +17347,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="344" spans="1:11">
+    <row r="344" spans="1:11" hidden="1">
       <c r="A344" s="4">
         <v>343</v>
       </c>
@@ -17323,7 +17370,7 @@
         <v>14</v>
       </c>
       <c r="H344" s="4" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I344" s="9">
         <v>45726</v>
@@ -17335,7 +17382,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="345" spans="1:11">
+    <row r="345" spans="1:11" hidden="1">
       <c r="A345" s="4">
         <v>344</v>
       </c>
@@ -17358,7 +17405,7 @@
         <v>14</v>
       </c>
       <c r="H345" s="4" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I345" s="9">
         <v>45726</v>
@@ -17370,7 +17417,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="346" spans="1:11">
+    <row r="346" spans="1:11" hidden="1">
       <c r="A346" s="4">
         <v>345</v>
       </c>
@@ -17393,7 +17440,7 @@
         <v>14</v>
       </c>
       <c r="H346" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="I346" s="9">
         <v>45653</v>
@@ -17405,7 +17452,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="347" spans="1:11">
+    <row r="347" spans="1:11" hidden="1">
       <c r="A347" s="4">
         <v>346</v>
       </c>
@@ -17428,7 +17475,7 @@
         <v>14</v>
       </c>
       <c r="H347" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="I347" s="9">
         <v>45817</v>
@@ -17440,7 +17487,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="348" spans="1:11">
+    <row r="348" spans="1:11" hidden="1">
       <c r="A348" s="4">
         <v>347</v>
       </c>
@@ -17463,7 +17510,7 @@
         <v>14</v>
       </c>
       <c r="H348" s="1" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="I348" s="9">
         <v>45653</v>
@@ -17475,7 +17522,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="349" spans="1:11">
+    <row r="349" spans="1:11" hidden="1">
       <c r="A349" s="4">
         <v>348</v>
       </c>
@@ -17498,7 +17545,7 @@
         <v>14</v>
       </c>
       <c r="H349" s="1" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="I349" s="9">
         <v>45844</v>
@@ -17507,10 +17554,10 @@
         <v>574</v>
       </c>
       <c r="K349" s="3" t="s">
-        <v>1296</v>
-      </c>
-    </row>
-    <row r="350" spans="1:11">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="350" spans="1:11" hidden="1">
       <c r="A350" s="4">
         <v>349</v>
       </c>
@@ -17533,7 +17580,7 @@
         <v>14</v>
       </c>
       <c r="H350" s="1" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="I350" s="9">
         <v>45838</v>
@@ -17545,7 +17592,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="351" spans="1:11">
+    <row r="351" spans="1:11" hidden="1">
       <c r="A351" s="4">
         <v>350</v>
       </c>
@@ -17568,7 +17615,7 @@
         <v>14</v>
       </c>
       <c r="H351" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="I351" s="9">
         <v>45842</v>
@@ -17580,7 +17627,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="352" spans="1:11">
+    <row r="352" spans="1:11" hidden="1">
       <c r="A352" s="4">
         <v>351</v>
       </c>
@@ -17603,7 +17650,7 @@
         <v>14</v>
       </c>
       <c r="H352" s="1" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="I352" s="9">
         <v>45852</v>
@@ -17615,7 +17662,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="353" spans="1:11">
+    <row r="353" spans="1:11" hidden="1">
       <c r="A353" s="4">
         <v>352</v>
       </c>
@@ -17638,7 +17685,7 @@
         <v>14</v>
       </c>
       <c r="H353" s="1" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="I353" s="9">
         <v>45853</v>
@@ -17650,7 +17697,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="354" spans="1:11">
+    <row r="354" spans="1:11" hidden="1">
       <c r="A354" s="4">
         <v>353</v>
       </c>
@@ -17673,7 +17720,7 @@
         <v>14</v>
       </c>
       <c r="H354" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="I354" s="9">
         <v>45870</v>
@@ -17685,7 +17732,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="355" spans="1:11">
+    <row r="355" spans="1:11" hidden="1">
       <c r="A355" s="4">
         <v>354</v>
       </c>
@@ -17708,7 +17755,7 @@
         <v>14</v>
       </c>
       <c r="H355" s="1" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="I355" s="9">
         <v>45870</v>
@@ -17720,7 +17767,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="356" spans="1:11">
+    <row r="356" spans="1:11" hidden="1">
       <c r="A356" s="4">
         <v>355</v>
       </c>
@@ -17743,7 +17790,7 @@
         <v>14</v>
       </c>
       <c r="H356" s="1" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="I356" s="9">
         <v>45876</v>
@@ -17755,7 +17802,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="357" spans="1:11">
+    <row r="357" spans="1:11" hidden="1">
       <c r="A357" s="4">
         <v>356</v>
       </c>
@@ -17778,7 +17825,7 @@
         <v>14</v>
       </c>
       <c r="H357" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="I357" s="9">
         <v>45884</v>
@@ -17790,7 +17837,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="358" spans="1:11">
+    <row r="358" spans="1:11" hidden="1">
       <c r="A358" s="4">
         <v>357</v>
       </c>
@@ -17813,7 +17860,7 @@
         <v>14</v>
       </c>
       <c r="H358" s="1" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="I358" s="9">
         <v>45884</v>
@@ -17825,7 +17872,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="359" spans="1:11">
+    <row r="359" spans="1:11" hidden="1">
       <c r="A359" s="4">
         <v>358</v>
       </c>
@@ -17848,7 +17895,7 @@
         <v>14</v>
       </c>
       <c r="H359" s="1" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="I359" s="9">
         <v>45653</v>
@@ -17860,7 +17907,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="360" spans="1:11">
+    <row r="360" spans="1:11" hidden="1">
       <c r="A360" s="4">
         <v>359</v>
       </c>
@@ -17883,7 +17930,7 @@
         <v>14</v>
       </c>
       <c r="H360" s="1" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="I360" s="9">
         <v>45929</v>
@@ -17895,7 +17942,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="361" spans="1:11">
+    <row r="361" spans="1:11" hidden="1">
       <c r="A361" s="4">
         <v>360</v>
       </c>
@@ -17918,7 +17965,7 @@
         <v>14</v>
       </c>
       <c r="H361" s="1" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="I361" s="9">
         <v>45931</v>
@@ -17930,7 +17977,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="362" spans="1:11">
+    <row r="362" spans="1:11" hidden="1">
       <c r="A362" s="4">
         <v>361</v>
       </c>
@@ -17953,7 +18000,7 @@
         <v>14</v>
       </c>
       <c r="H362" s="1" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="I362" s="9">
         <v>45931</v>
@@ -17965,7 +18012,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="363" spans="1:11">
+    <row r="363" spans="1:11" hidden="1">
       <c r="A363" s="4">
         <v>362</v>
       </c>
@@ -17988,7 +18035,7 @@
         <v>14</v>
       </c>
       <c r="H363" s="1" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="I363" s="9">
         <v>40452</v>
@@ -18000,7 +18047,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="364" spans="1:11">
+    <row r="364" spans="1:11" hidden="1">
       <c r="A364" s="4">
         <v>363</v>
       </c>
@@ -18023,7 +18070,7 @@
         <v>14</v>
       </c>
       <c r="H364" s="1" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="I364" s="9">
         <v>45932</v>
@@ -18035,7 +18082,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="365" spans="1:11">
+    <row r="365" spans="1:11" hidden="1">
       <c r="A365" s="4">
         <v>364</v>
       </c>
@@ -18068,7 +18115,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="366" spans="1:11">
+    <row r="366" spans="1:11" hidden="1">
       <c r="A366" s="4">
         <v>365</v>
       </c>
@@ -18091,7 +18138,7 @@
         <v>14</v>
       </c>
       <c r="H366" s="1" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="I366" s="15">
         <v>45604</v>
@@ -18103,7 +18150,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="367" spans="1:11">
+    <row r="367" spans="1:11" hidden="1">
       <c r="A367" s="4">
         <v>366</v>
       </c>
@@ -18126,7 +18173,7 @@
         <v>14</v>
       </c>
       <c r="H367" s="1" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="I367" s="15">
         <v>45768</v>
@@ -18138,7 +18185,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="368" spans="1:11">
+    <row r="368" spans="1:11" hidden="1">
       <c r="A368" s="4">
         <v>367</v>
       </c>
@@ -18161,7 +18208,7 @@
         <v>14</v>
       </c>
       <c r="H368" s="1" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="I368" s="9">
         <v>45937</v>
@@ -18173,7 +18220,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="369" spans="1:11">
+    <row r="369" spans="1:11" hidden="1">
       <c r="A369" s="4">
         <v>368</v>
       </c>
@@ -18196,7 +18243,7 @@
         <v>14</v>
       </c>
       <c r="H369" s="1" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="I369" s="9">
         <v>45937</v>
@@ -18208,7 +18255,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="370" spans="1:11">
+    <row r="370" spans="1:11" hidden="1">
       <c r="A370" s="4">
         <v>369</v>
       </c>
@@ -18231,7 +18278,7 @@
         <v>14</v>
       </c>
       <c r="H370" s="1" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="I370" s="9">
         <v>45937</v>
@@ -18243,7 +18290,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="371" spans="1:11">
+    <row r="371" spans="1:11" hidden="1">
       <c r="A371" s="4">
         <v>370</v>
       </c>
@@ -18266,7 +18313,7 @@
         <v>14</v>
       </c>
       <c r="H371" s="1" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="I371" s="23">
         <v>45939</v>
@@ -18278,7 +18325,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="372" spans="1:11">
+    <row r="372" spans="1:11" hidden="1">
       <c r="A372" s="4">
         <v>371</v>
       </c>
@@ -18301,7 +18348,7 @@
         <v>14</v>
       </c>
       <c r="H372" s="1" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="I372" s="23">
         <v>45939</v>
@@ -18313,7 +18360,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="373" spans="1:11">
+    <row r="373" spans="1:11" hidden="1">
       <c r="A373" s="4">
         <v>372</v>
       </c>
@@ -18336,7 +18383,7 @@
         <v>14</v>
       </c>
       <c r="H373" s="1" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="I373" s="23">
         <v>45942</v>
@@ -18348,7 +18395,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="374" spans="1:11">
+    <row r="374" spans="1:11" hidden="1">
       <c r="A374" s="4">
         <v>373</v>
       </c>
@@ -18371,7 +18418,7 @@
         <v>14</v>
       </c>
       <c r="H374" s="1" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="I374" s="9">
         <v>45947</v>
@@ -18383,7 +18430,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="375" spans="1:11">
+    <row r="375" spans="1:11" hidden="1">
       <c r="A375" s="4">
         <v>374</v>
       </c>
@@ -18406,7 +18453,7 @@
         <v>14</v>
       </c>
       <c r="H375" s="1" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="I375" s="23">
         <v>45946</v>
@@ -18418,7 +18465,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="376" spans="1:11">
+    <row r="376" spans="1:11" hidden="1">
       <c r="A376" s="4">
         <v>375</v>
       </c>
@@ -18441,7 +18488,7 @@
         <v>14</v>
       </c>
       <c r="H376" s="1" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="I376" s="23">
         <v>45945</v>
@@ -18453,7 +18500,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="377" spans="1:11">
+    <row r="377" spans="1:11" hidden="1">
       <c r="A377" s="4">
         <v>376</v>
       </c>
@@ -18476,7 +18523,7 @@
         <v>14</v>
       </c>
       <c r="H377" s="1" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="I377" s="23">
         <v>45942</v>
@@ -18485,10 +18532,10 @@
         <v>574</v>
       </c>
       <c r="K377" s="3" t="s">
-        <v>1286</v>
-      </c>
-    </row>
-    <row r="378" spans="1:11">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="378" spans="1:11" hidden="1">
       <c r="A378" s="4">
         <v>377</v>
       </c>
@@ -18511,7 +18558,7 @@
         <v>14</v>
       </c>
       <c r="H378" s="1" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="I378" s="23">
         <v>45946</v>
@@ -18523,7 +18570,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="379" spans="1:11">
+    <row r="379" spans="1:11" hidden="1">
       <c r="A379" s="4">
         <v>378</v>
       </c>
@@ -18546,7 +18593,7 @@
         <v>14</v>
       </c>
       <c r="H379" s="1" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="I379" s="23">
         <v>45946</v>
@@ -18558,7 +18605,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="380" spans="1:11">
+    <row r="380" spans="1:11" hidden="1">
       <c r="A380" s="4">
         <v>379</v>
       </c>
@@ -18581,7 +18628,7 @@
         <v>14</v>
       </c>
       <c r="H380" s="1" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="I380" s="23">
         <v>45942</v>
@@ -18593,7 +18640,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="381" spans="1:11">
+    <row r="381" spans="1:11" hidden="1">
       <c r="A381" s="4">
         <v>380</v>
       </c>
@@ -18616,7 +18663,7 @@
         <v>14</v>
       </c>
       <c r="H381" s="1" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="I381" s="23">
         <v>45945</v>
@@ -18628,7 +18675,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="382" spans="1:11">
+    <row r="382" spans="1:11" hidden="1">
       <c r="A382" s="4">
         <v>381</v>
       </c>
@@ -18651,7 +18698,7 @@
         <v>14</v>
       </c>
       <c r="H382" s="1" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="I382" s="23">
         <v>46036</v>
@@ -18663,7 +18710,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="383" spans="1:11">
+    <row r="383" spans="1:11" hidden="1">
       <c r="A383" s="4">
         <v>382</v>
       </c>
@@ -18686,7 +18733,7 @@
         <v>14</v>
       </c>
       <c r="H383" s="1" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="I383" s="23">
         <v>45968</v>
@@ -18698,7 +18745,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="384" spans="1:11">
+    <row r="384" spans="1:11" hidden="1">
       <c r="A384" s="4">
         <v>383</v>
       </c>
@@ -18721,7 +18768,7 @@
         <v>14</v>
       </c>
       <c r="H384" s="1" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="I384" s="23">
         <v>45994</v>
@@ -18733,7 +18780,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="385" spans="1:11">
+    <row r="385" spans="1:11" hidden="1">
       <c r="A385" s="4">
         <v>384</v>
       </c>
@@ -18756,7 +18803,7 @@
         <v>14</v>
       </c>
       <c r="H385" s="1" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="I385" s="23">
         <v>45968</v>
@@ -18768,7 +18815,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="386" spans="1:11">
+    <row r="386" spans="1:11" hidden="1">
       <c r="A386" s="4">
         <v>385</v>
       </c>
@@ -18791,7 +18838,7 @@
         <v>14</v>
       </c>
       <c r="H386" s="1" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="I386" s="23">
         <v>45968</v>
@@ -18803,7 +18850,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="387" spans="1:11">
+    <row r="387" spans="1:11" hidden="1">
       <c r="A387" s="4">
         <v>386</v>
       </c>
@@ -18826,7 +18873,7 @@
         <v>14</v>
       </c>
       <c r="H387" s="1" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="I387" s="23">
         <v>45968</v>
@@ -18838,7 +18885,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="388" spans="1:11">
+    <row r="388" spans="1:11" hidden="1">
       <c r="A388" s="4">
         <v>387</v>
       </c>
@@ -18861,7 +18908,7 @@
         <v>14</v>
       </c>
       <c r="H388" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="I388" s="23">
         <v>45968</v>
@@ -18873,7 +18920,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="389" spans="1:11">
+    <row r="389" spans="1:11" hidden="1">
       <c r="A389" s="4">
         <v>388</v>
       </c>
@@ -18896,7 +18943,7 @@
         <v>14</v>
       </c>
       <c r="H389" s="1" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="I389" s="23">
         <v>45968</v>
@@ -18908,7 +18955,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="390" spans="1:11">
+    <row r="390" spans="1:11" hidden="1">
       <c r="A390" s="4">
         <v>389</v>
       </c>
@@ -18931,7 +18978,7 @@
         <v>14</v>
       </c>
       <c r="H390" s="1" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="I390" s="23">
         <v>45968</v>
@@ -18943,7 +18990,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="391" spans="1:11">
+    <row r="391" spans="1:11" hidden="1">
       <c r="A391" s="4">
         <v>390</v>
       </c>
@@ -18966,7 +19013,7 @@
         <v>14</v>
       </c>
       <c r="H391" s="1" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="I391" s="23">
         <v>45971</v>
@@ -18978,30 +19025,30 @@
         <v>891</v>
       </c>
     </row>
-    <row r="392" spans="1:11">
+    <row r="392" spans="1:11" hidden="1">
       <c r="A392" s="4">
         <v>391</v>
       </c>
       <c r="B392" s="56" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D392" s="2" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="E392" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="G392" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H392" s="1" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="I392" s="54">
         <v>46279</v>
@@ -19010,7 +19057,7 @@
         <v>574</v>
       </c>
       <c r="K392" s="3" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="393" spans="1:11">
@@ -19018,25 +19065,25 @@
         <v>392</v>
       </c>
       <c r="B393" s="56" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="E393" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F393" s="1" t="s">
-        <v>1384</v>
+        <v>1458</v>
       </c>
       <c r="G393" s="1" t="s">
         <v>30</v>
       </c>
       <c r="H393" s="1" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="I393" s="54">
         <v>46279</v>
@@ -19045,21 +19092,21 @@
         <v>574</v>
       </c>
       <c r="K393" s="3" t="s">
-        <v>1386</v>
-      </c>
-    </row>
-    <row r="394" spans="1:11">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="394" spans="1:11" hidden="1">
       <c r="A394" s="4">
         <v>393</v>
       </c>
       <c r="B394" s="56" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D394" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E394" s="1" t="s">
         <v>21</v>
@@ -19071,7 +19118,7 @@
         <v>30</v>
       </c>
       <c r="H394" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I394" s="54">
         <v>46279</v>
@@ -19081,18 +19128,18 @@
       </c>
       <c r="K394" s="55"/>
     </row>
-    <row r="395" spans="1:11">
+    <row r="395" spans="1:11" hidden="1">
       <c r="A395" s="4">
         <v>394</v>
       </c>
       <c r="B395" s="56" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D395" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E395" s="1" t="s">
         <v>21</v>
@@ -19104,7 +19151,7 @@
         <v>30</v>
       </c>
       <c r="H395" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I395" s="54">
         <v>46279</v>
@@ -19114,18 +19161,18 @@
       </c>
       <c r="K395" s="55"/>
     </row>
-    <row r="396" spans="1:11">
+    <row r="396" spans="1:11" hidden="1">
       <c r="A396" s="4">
         <v>395</v>
       </c>
       <c r="B396" s="56" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D396" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E396" s="1" t="s">
         <v>21</v>
@@ -19137,7 +19184,7 @@
         <v>30</v>
       </c>
       <c r="H396" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I396" s="54">
         <v>46279</v>
@@ -19147,7 +19194,7 @@
       </c>
       <c r="K396" s="55"/>
     </row>
-    <row r="397" spans="1:11">
+    <row r="397" spans="1:11" hidden="1">
       <c r="A397" s="4">
         <v>396</v>
       </c>
@@ -19170,7 +19217,7 @@
         <v>14</v>
       </c>
       <c r="H397" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="I397" s="23">
         <v>45945</v>
@@ -19182,7 +19229,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="398" spans="1:11">
+    <row r="398" spans="1:11" hidden="1">
       <c r="A398" s="4">
         <v>397</v>
       </c>
@@ -19205,7 +19252,7 @@
         <v>14</v>
       </c>
       <c r="H398" s="1" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="I398" s="23">
         <v>45945</v>
@@ -19217,7 +19264,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="399" spans="1:11">
+    <row r="399" spans="1:11" hidden="1">
       <c r="A399" s="4">
         <v>398</v>
       </c>
@@ -19240,7 +19287,7 @@
         <v>14</v>
       </c>
       <c r="H399" s="1" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="I399" s="23">
         <v>45945</v>
@@ -19252,7 +19299,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="400" spans="1:11">
+    <row r="400" spans="1:11" hidden="1">
       <c r="A400" s="4">
         <v>399</v>
       </c>
@@ -19275,7 +19322,7 @@
         <v>14</v>
       </c>
       <c r="H400" s="1" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="I400" s="23">
         <v>45992</v>
@@ -19310,7 +19357,7 @@
         <v>14</v>
       </c>
       <c r="H401" s="1" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="I401" s="23">
         <v>46129</v>
@@ -19319,10 +19366,10 @@
         <v>645</v>
       </c>
       <c r="K401" s="3" t="s">
-        <v>1319</v>
-      </c>
-    </row>
-    <row r="402" spans="1:11">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="402" spans="1:11" hidden="1">
       <c r="A402" s="4">
         <v>401</v>
       </c>
@@ -19357,7 +19404,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="403" spans="1:11">
+    <row r="403" spans="1:11" hidden="1">
       <c r="A403" s="4">
         <v>402</v>
       </c>
@@ -19374,13 +19421,13 @@
         <v>76</v>
       </c>
       <c r="F403" s="1" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="G403" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H403" s="1" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="I403" s="23">
         <v>45945</v>
@@ -19392,7 +19439,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="404" spans="1:11">
+    <row r="404" spans="1:11" hidden="1">
       <c r="A404" s="4">
         <v>403</v>
       </c>
@@ -19415,7 +19462,7 @@
         <v>14</v>
       </c>
       <c r="H404" s="1" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="I404" s="23">
         <v>46098</v>
@@ -19427,7 +19474,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="405" spans="1:11">
+    <row r="405" spans="1:11" hidden="1">
       <c r="A405" s="4">
         <v>404</v>
       </c>
@@ -19450,7 +19497,7 @@
         <v>14</v>
       </c>
       <c r="H405" s="1" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="I405" s="23">
         <v>45941</v>
@@ -19462,7 +19509,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="406" spans="1:11">
+    <row r="406" spans="1:11" hidden="1">
       <c r="A406" s="4">
         <v>405</v>
       </c>
@@ -19485,7 +19532,7 @@
         <v>14</v>
       </c>
       <c r="H406" s="1" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="I406" s="23">
         <v>45941</v>
@@ -19497,7 +19544,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="407" spans="1:11">
+    <row r="407" spans="1:11" hidden="1">
       <c r="A407" s="4">
         <v>406</v>
       </c>
@@ -19520,7 +19567,7 @@
         <v>14</v>
       </c>
       <c r="H407" s="1" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="I407" s="23">
         <v>45952</v>
@@ -19532,7 +19579,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="408" spans="1:11">
+    <row r="408" spans="1:11" hidden="1">
       <c r="A408" s="4">
         <v>407</v>
       </c>
@@ -19555,7 +19602,7 @@
         <v>14</v>
       </c>
       <c r="H408" s="1" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="I408" s="23">
         <v>45950</v>
@@ -19567,7 +19614,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="409" spans="1:11">
+    <row r="409" spans="1:11" hidden="1">
       <c r="A409" s="4">
         <v>408</v>
       </c>
@@ -19590,7 +19637,7 @@
         <v>14</v>
       </c>
       <c r="H409" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="I409" s="23">
         <v>45996</v>
@@ -19602,7 +19649,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="410" spans="1:11">
+    <row r="410" spans="1:11" hidden="1">
       <c r="A410" s="4">
         <v>409</v>
       </c>
@@ -19625,7 +19672,7 @@
         <v>14</v>
       </c>
       <c r="H410" s="1" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="I410" s="9">
         <v>45941</v>
@@ -19637,7 +19684,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="411" spans="1:11">
+    <row r="411" spans="1:11" hidden="1">
       <c r="A411" s="4">
         <v>410</v>
       </c>
@@ -19670,7 +19717,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="412" spans="1:11">
+    <row r="412" spans="1:11" hidden="1">
       <c r="A412" s="4">
         <v>411</v>
       </c>
@@ -19687,13 +19734,13 @@
         <v>76</v>
       </c>
       <c r="F412" s="1" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="G412" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H412" s="1" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="I412" s="23">
         <v>45952</v>
@@ -19702,10 +19749,10 @@
         <v>574</v>
       </c>
       <c r="K412" s="3" t="s">
-        <v>1285</v>
-      </c>
-    </row>
-    <row r="413" spans="1:11">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="413" spans="1:11" hidden="1">
       <c r="A413" s="4">
         <v>412</v>
       </c>
@@ -19728,7 +19775,7 @@
         <v>14</v>
       </c>
       <c r="H413" s="1" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="I413" s="23">
         <v>45959</v>
@@ -19740,7 +19787,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="414" spans="1:11">
+    <row r="414" spans="1:11" hidden="1">
       <c r="A414" s="4">
         <v>413</v>
       </c>
@@ -19763,7 +19810,7 @@
         <v>14</v>
       </c>
       <c r="H414" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="I414" s="23">
         <v>45960</v>
@@ -19775,7 +19822,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="415" spans="1:11">
+    <row r="415" spans="1:11" hidden="1">
       <c r="A415" s="4">
         <v>414</v>
       </c>
@@ -19798,7 +19845,7 @@
         <v>14</v>
       </c>
       <c r="H415" s="1" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I415" s="23">
         <v>45945</v>
@@ -19810,7 +19857,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="416" spans="1:11">
+    <row r="416" spans="1:11" hidden="1">
       <c r="A416" s="4">
         <v>415</v>
       </c>
@@ -19843,7 +19890,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="417" spans="1:11">
+    <row r="417" spans="1:11" hidden="1">
       <c r="A417" s="4">
         <v>416</v>
       </c>
@@ -19866,7 +19913,7 @@
         <v>14</v>
       </c>
       <c r="H417" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="I417" s="23">
         <v>45945</v>
@@ -19878,7 +19925,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="418" spans="1:11">
+    <row r="418" spans="1:11" hidden="1">
       <c r="A418" s="4">
         <v>417</v>
       </c>
@@ -19901,7 +19948,7 @@
         <v>14</v>
       </c>
       <c r="H418" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I418" s="23">
         <v>45945</v>
@@ -19913,7 +19960,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="419" spans="1:11">
+    <row r="419" spans="1:11" hidden="1">
       <c r="A419" s="4">
         <v>418</v>
       </c>
@@ -19936,7 +19983,7 @@
         <v>14</v>
       </c>
       <c r="H419" s="1" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I419" s="23">
         <v>45945</v>
@@ -19948,7 +19995,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="420" spans="1:11">
+    <row r="420" spans="1:11" hidden="1">
       <c r="A420" s="4">
         <v>419</v>
       </c>
@@ -19971,7 +20018,7 @@
         <v>14</v>
       </c>
       <c r="H420" s="1" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="I420" s="23">
         <v>45940</v>
@@ -19983,7 +20030,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="421" spans="1:11">
+    <row r="421" spans="1:11" hidden="1">
       <c r="A421" s="4">
         <v>420</v>
       </c>
@@ -20006,7 +20053,7 @@
         <v>14</v>
       </c>
       <c r="H421" s="1" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="I421" s="23">
         <v>45940</v>
@@ -20018,7 +20065,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="422" spans="1:11">
+    <row r="422" spans="1:11" hidden="1">
       <c r="A422" s="4">
         <v>421</v>
       </c>
@@ -20041,7 +20088,7 @@
         <v>14</v>
       </c>
       <c r="H422" s="1" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="I422" s="23">
         <v>45940</v>
@@ -20053,7 +20100,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="423" spans="1:11">
+    <row r="423" spans="1:11" hidden="1">
       <c r="A423" s="4">
         <v>422</v>
       </c>
@@ -20076,7 +20123,7 @@
         <v>14</v>
       </c>
       <c r="H423" s="1" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="I423" s="23">
         <v>45939</v>
@@ -20088,7 +20135,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="424" spans="1:11">
+    <row r="424" spans="1:11" hidden="1">
       <c r="A424" s="4">
         <v>423</v>
       </c>
@@ -20111,7 +20158,7 @@
         <v>14</v>
       </c>
       <c r="H424" s="1" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="I424" s="23">
         <v>45939</v>
@@ -20123,7 +20170,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="425" spans="1:11">
+    <row r="425" spans="1:11" hidden="1">
       <c r="A425" s="4">
         <v>424</v>
       </c>
@@ -20146,7 +20193,7 @@
         <v>14</v>
       </c>
       <c r="H425" s="1" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="I425" s="23">
         <v>45938</v>
@@ -20158,7 +20205,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="426" spans="1:11">
+    <row r="426" spans="1:11" hidden="1">
       <c r="A426" s="4">
         <v>425</v>
       </c>
@@ -20181,7 +20228,7 @@
         <v>14</v>
       </c>
       <c r="H426" s="1" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="I426" s="23">
         <v>45938</v>
@@ -20193,7 +20240,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="427" spans="1:11">
+    <row r="427" spans="1:11" hidden="1">
       <c r="A427" s="4">
         <v>426</v>
       </c>
@@ -20216,7 +20263,7 @@
         <v>14</v>
       </c>
       <c r="H427" s="1" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="I427" s="23">
         <v>45939</v>
@@ -20228,7 +20275,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="428" spans="1:11">
+    <row r="428" spans="1:11" hidden="1">
       <c r="A428" s="4">
         <v>427</v>
       </c>
@@ -20251,7 +20298,7 @@
         <v>14</v>
       </c>
       <c r="H428" s="1" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="I428" s="23">
         <v>45939</v>
@@ -20263,7 +20310,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="429" spans="1:11">
+    <row r="429" spans="1:11" hidden="1">
       <c r="A429" s="4">
         <v>428</v>
       </c>
@@ -20286,7 +20333,7 @@
         <v>14</v>
       </c>
       <c r="H429" s="1" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="I429" s="23">
         <v>45985</v>
@@ -20298,7 +20345,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="430" spans="1:11">
+    <row r="430" spans="1:11" hidden="1">
       <c r="A430" s="4">
         <v>429</v>
       </c>
@@ -20321,7 +20368,7 @@
         <v>14</v>
       </c>
       <c r="H430" s="1" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="I430" s="23">
         <v>45992</v>
@@ -20333,7 +20380,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="431" spans="1:11">
+    <row r="431" spans="1:11" hidden="1">
       <c r="A431" s="4">
         <v>430</v>
       </c>
@@ -20356,7 +20403,7 @@
         <v>14</v>
       </c>
       <c r="H431" s="1" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="I431" s="23">
         <v>45996</v>
@@ -20368,7 +20415,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="432" spans="1:11">
+    <row r="432" spans="1:11" hidden="1">
       <c r="A432" s="4">
         <v>431</v>
       </c>
@@ -20391,7 +20438,7 @@
         <v>14</v>
       </c>
       <c r="H432" s="1" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="I432" s="23">
         <v>45996</v>
@@ -20403,7 +20450,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="433" spans="1:11">
+    <row r="433" spans="1:11" hidden="1">
       <c r="A433" s="4">
         <v>432</v>
       </c>
@@ -20426,7 +20473,7 @@
         <v>14</v>
       </c>
       <c r="H433" s="1" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="I433" s="23">
         <v>45985</v>
@@ -20438,7 +20485,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="434" spans="1:11">
+    <row r="434" spans="1:11" hidden="1">
       <c r="A434" s="4">
         <v>433</v>
       </c>
@@ -20449,19 +20496,19 @@
         <v>11</v>
       </c>
       <c r="D434" s="2" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="E434" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F434" s="1" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="G434" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H434" s="1" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="I434" s="54">
         <v>46279</v>
@@ -20471,7 +20518,7 @@
       </c>
       <c r="K434" s="55"/>
     </row>
-    <row r="435" spans="1:11">
+    <row r="435" spans="1:11" hidden="1">
       <c r="A435" s="4">
         <v>434</v>
       </c>
@@ -20482,19 +20529,19 @@
         <v>11</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="E435" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F435" s="1" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="G435" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H435" s="1" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="I435" s="54">
         <v>46279</v>
@@ -20504,7 +20551,7 @@
       </c>
       <c r="K435" s="55"/>
     </row>
-    <row r="436" spans="1:11">
+    <row r="436" spans="1:11" hidden="1">
       <c r="A436" s="4">
         <v>435</v>
       </c>
@@ -20515,19 +20562,19 @@
         <v>11</v>
       </c>
       <c r="D436" s="2" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="E436" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F436" s="1" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="G436" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H436" s="1" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="I436" s="54">
         <v>46279</v>
@@ -20537,7 +20584,7 @@
       </c>
       <c r="K436" s="55"/>
     </row>
-    <row r="437" spans="1:11">
+    <row r="437" spans="1:11" hidden="1">
       <c r="A437" s="4">
         <v>436</v>
       </c>
@@ -20548,19 +20595,19 @@
         <v>11</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="E437" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F437" s="1" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="G437" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H437" s="1" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="I437" s="54">
         <v>46279</v>
@@ -20570,7 +20617,7 @@
       </c>
       <c r="K437" s="55"/>
     </row>
-    <row r="438" spans="1:11">
+    <row r="438" spans="1:11" hidden="1">
       <c r="A438" s="4">
         <v>437</v>
       </c>
@@ -20581,19 +20628,19 @@
         <v>11</v>
       </c>
       <c r="D438" s="2" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="E438" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F438" s="1" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="G438" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H438" s="1" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="I438" s="54">
         <v>46279</v>
@@ -20603,7 +20650,7 @@
       </c>
       <c r="K438" s="55"/>
     </row>
-    <row r="439" spans="1:11">
+    <row r="439" spans="1:11" hidden="1">
       <c r="A439" s="4">
         <v>438</v>
       </c>
@@ -20614,19 +20661,19 @@
         <v>11</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="E439" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F439" s="1" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="G439" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H439" s="1" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="I439" s="54">
         <v>46279</v>
@@ -20636,7 +20683,7 @@
       </c>
       <c r="K439" s="55"/>
     </row>
-    <row r="440" spans="1:11">
+    <row r="440" spans="1:11" hidden="1">
       <c r="A440" s="4">
         <v>439</v>
       </c>
@@ -20647,19 +20694,19 @@
         <v>11</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="E440" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F440" s="1" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="G440" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H440" s="1" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="I440" s="54">
         <v>46279</v>
@@ -20669,7 +20716,7 @@
       </c>
       <c r="K440" s="55"/>
     </row>
-    <row r="441" spans="1:11">
+    <row r="441" spans="1:11" hidden="1">
       <c r="A441" s="4">
         <v>440</v>
       </c>
@@ -20680,19 +20727,19 @@
         <v>11</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="E441" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F441" s="1" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="G441" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H441" s="1" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="I441" s="54">
         <v>46279</v>
@@ -20702,7 +20749,7 @@
       </c>
       <c r="K441" s="55"/>
     </row>
-    <row r="442" spans="1:11">
+    <row r="442" spans="1:11" hidden="1">
       <c r="A442" s="4">
         <v>441</v>
       </c>
@@ -20713,19 +20760,19 @@
         <v>11</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="E442" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F442" s="1" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="G442" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H442" s="1" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="I442" s="54">
         <v>46279</v>
@@ -20735,7 +20782,7 @@
       </c>
       <c r="K442" s="55"/>
     </row>
-    <row r="443" spans="1:11">
+    <row r="443" spans="1:11" hidden="1">
       <c r="A443" s="4">
         <v>442</v>
       </c>
@@ -20746,19 +20793,19 @@
         <v>11</v>
       </c>
       <c r="D443" s="2" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="E443" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F443" s="1" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="G443" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H443" s="1" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="I443" s="54">
         <v>46279</v>
@@ -20768,7 +20815,7 @@
       </c>
       <c r="K443" s="55"/>
     </row>
-    <row r="444" spans="1:11">
+    <row r="444" spans="1:11" hidden="1">
       <c r="A444" s="4">
         <v>443</v>
       </c>
@@ -20779,19 +20826,19 @@
         <v>11</v>
       </c>
       <c r="D444" s="2" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="E444" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F444" s="1" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="G444" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H444" s="1" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="I444" s="54">
         <v>46279</v>
@@ -20801,7 +20848,7 @@
       </c>
       <c r="K444" s="55"/>
     </row>
-    <row r="445" spans="1:11">
+    <row r="445" spans="1:11" hidden="1">
       <c r="A445" s="4">
         <v>444</v>
       </c>
@@ -20812,19 +20859,19 @@
         <v>11</v>
       </c>
       <c r="D445" s="2" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="E445" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F445" s="1" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="G445" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H445" s="1" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="I445" s="54">
         <v>46279</v>
@@ -20834,7 +20881,7 @@
       </c>
       <c r="K445" s="55"/>
     </row>
-    <row r="446" spans="1:11">
+    <row r="446" spans="1:11" hidden="1">
       <c r="A446" s="4">
         <v>445</v>
       </c>
@@ -20845,19 +20892,19 @@
         <v>11</v>
       </c>
       <c r="D446" s="2" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="E446" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F446" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="G446" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H446" s="1" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="I446" s="54">
         <v>46279</v>
@@ -20867,7 +20914,7 @@
       </c>
       <c r="K446" s="55"/>
     </row>
-    <row r="447" spans="1:11">
+    <row r="447" spans="1:11" hidden="1">
       <c r="A447" s="4">
         <v>446</v>
       </c>
@@ -20878,19 +20925,19 @@
         <v>11</v>
       </c>
       <c r="D447" s="2" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="E447" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F447" s="1" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="G447" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H447" s="1" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="I447" s="54">
         <v>46279</v>
@@ -20900,7 +20947,7 @@
       </c>
       <c r="K447" s="55"/>
     </row>
-    <row r="448" spans="1:11">
+    <row r="448" spans="1:11" hidden="1">
       <c r="A448" s="4">
         <v>447</v>
       </c>
@@ -20911,19 +20958,19 @@
         <v>11</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="E448" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F448" s="1" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="G448" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H448" s="1" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="I448" s="54">
         <v>46279</v>
@@ -20933,7 +20980,7 @@
       </c>
       <c r="K448" s="55"/>
     </row>
-    <row r="449" spans="1:11">
+    <row r="449" spans="1:11" hidden="1">
       <c r="A449" s="4">
         <v>448</v>
       </c>
@@ -20944,19 +20991,19 @@
         <v>11</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="E449" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F449" s="1" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="G449" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H449" s="1" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="I449" s="54">
         <v>46279</v>
@@ -20966,7 +21013,7 @@
       </c>
       <c r="K449" s="55"/>
     </row>
-    <row r="450" spans="1:11">
+    <row r="450" spans="1:11" hidden="1">
       <c r="A450" s="4">
         <v>449</v>
       </c>
@@ -20977,19 +21024,19 @@
         <v>11</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="E450" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F450" s="1" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="G450" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H450" s="1" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="I450" s="54">
         <v>46279</v>
@@ -20999,7 +21046,7 @@
       </c>
       <c r="K450" s="55"/>
     </row>
-    <row r="451" spans="1:11">
+    <row r="451" spans="1:11" hidden="1">
       <c r="A451" s="4">
         <v>450</v>
       </c>
@@ -21010,19 +21057,19 @@
         <v>11</v>
       </c>
       <c r="D451" s="2" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="E451" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F451" s="1" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="G451" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H451" s="1" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="I451" s="54">
         <v>46279</v>
@@ -21032,7 +21079,7 @@
       </c>
       <c r="K451" s="55"/>
     </row>
-    <row r="452" spans="1:11">
+    <row r="452" spans="1:11" hidden="1">
       <c r="A452" s="4">
         <v>451</v>
       </c>
@@ -21043,19 +21090,19 @@
         <v>11</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="E452" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F452" s="1" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="G452" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H452" s="1" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="I452" s="54">
         <v>46279</v>
@@ -21065,7 +21112,7 @@
       </c>
       <c r="K452" s="55"/>
     </row>
-    <row r="453" spans="1:11">
+    <row r="453" spans="1:11" hidden="1">
       <c r="A453" s="4">
         <v>452</v>
       </c>
@@ -21076,19 +21123,19 @@
         <v>11</v>
       </c>
       <c r="D453" s="2" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="E453" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F453" s="1" t="s">
-        <v>1451</v>
+        <v>1448</v>
       </c>
       <c r="G453" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H453" s="1" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="I453" s="54">
         <v>46279</v>
@@ -21098,7 +21145,7 @@
       </c>
       <c r="K453" s="55"/>
     </row>
-    <row r="454" spans="1:11">
+    <row r="454" spans="1:11" hidden="1">
       <c r="A454" s="4">
         <v>453</v>
       </c>
@@ -21109,7 +21156,7 @@
         <v>11</v>
       </c>
       <c r="D454" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E454" s="1" t="s">
         <v>21</v>
@@ -21121,7 +21168,7 @@
         <v>30</v>
       </c>
       <c r="H454" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I454" s="54">
         <v>46279</v>
@@ -21131,7 +21178,7 @@
       </c>
       <c r="K454" s="55"/>
     </row>
-    <row r="455" spans="1:11">
+    <row r="455" spans="1:11" hidden="1">
       <c r="A455" s="4">
         <v>454</v>
       </c>
@@ -21142,7 +21189,7 @@
         <v>11</v>
       </c>
       <c r="D455" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E455" s="1" t="s">
         <v>21</v>
@@ -21154,7 +21201,7 @@
         <v>30</v>
       </c>
       <c r="H455" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I455" s="54">
         <v>46279</v>
@@ -21164,7 +21211,7 @@
       </c>
       <c r="K455" s="55"/>
     </row>
-    <row r="456" spans="1:11">
+    <row r="456" spans="1:11" hidden="1">
       <c r="A456" s="4">
         <v>455</v>
       </c>
@@ -21175,7 +21222,7 @@
         <v>11</v>
       </c>
       <c r="D456" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E456" s="1" t="s">
         <v>21</v>
@@ -21187,7 +21234,7 @@
         <v>30</v>
       </c>
       <c r="H456" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I456" s="54">
         <v>46279</v>
@@ -21197,7 +21244,7 @@
       </c>
       <c r="K456" s="55"/>
     </row>
-    <row r="457" spans="1:11">
+    <row r="457" spans="1:11" hidden="1">
       <c r="A457" s="4">
         <v>456</v>
       </c>
@@ -21208,7 +21255,7 @@
         <v>11</v>
       </c>
       <c r="D457" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E457" s="1" t="s">
         <v>21</v>
@@ -21220,7 +21267,7 @@
         <v>30</v>
       </c>
       <c r="H457" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I457" s="54">
         <v>46279</v>
@@ -21230,7 +21277,7 @@
       </c>
       <c r="K457" s="55"/>
     </row>
-    <row r="458" spans="1:11">
+    <row r="458" spans="1:11" hidden="1">
       <c r="A458" s="4">
         <v>457</v>
       </c>
@@ -21241,7 +21288,7 @@
         <v>11</v>
       </c>
       <c r="D458" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E458" s="1" t="s">
         <v>21</v>
@@ -21253,7 +21300,7 @@
         <v>30</v>
       </c>
       <c r="H458" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I458" s="54">
         <v>46279</v>
@@ -21263,7 +21310,7 @@
       </c>
       <c r="K458" s="55"/>
     </row>
-    <row r="459" spans="1:11">
+    <row r="459" spans="1:11" hidden="1">
       <c r="A459" s="4">
         <v>458</v>
       </c>
@@ -21274,7 +21321,7 @@
         <v>11</v>
       </c>
       <c r="D459" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E459" s="1" t="s">
         <v>21</v>
@@ -21286,7 +21333,7 @@
         <v>30</v>
       </c>
       <c r="H459" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I459" s="54">
         <v>46279</v>
@@ -21296,7 +21343,7 @@
       </c>
       <c r="K459" s="55"/>
     </row>
-    <row r="460" spans="1:11">
+    <row r="460" spans="1:11" hidden="1">
       <c r="A460" s="4">
         <v>459</v>
       </c>
@@ -21307,7 +21354,7 @@
         <v>11</v>
       </c>
       <c r="D460" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E460" s="1" t="s">
         <v>21</v>
@@ -21319,7 +21366,7 @@
         <v>30</v>
       </c>
       <c r="H460" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I460" s="54">
         <v>46279</v>
@@ -21329,7 +21376,7 @@
       </c>
       <c r="K460" s="55"/>
     </row>
-    <row r="461" spans="1:11">
+    <row r="461" spans="1:11" hidden="1">
       <c r="A461" s="4">
         <v>460</v>
       </c>
@@ -21340,7 +21387,7 @@
         <v>11</v>
       </c>
       <c r="D461" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E461" s="1" t="s">
         <v>21</v>
@@ -21352,7 +21399,7 @@
         <v>30</v>
       </c>
       <c r="H461" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I461" s="54">
         <v>46279</v>
@@ -21362,7 +21409,7 @@
       </c>
       <c r="K461" s="55"/>
     </row>
-    <row r="462" spans="1:11">
+    <row r="462" spans="1:11" hidden="1">
       <c r="A462" s="4">
         <v>461</v>
       </c>
@@ -21373,7 +21420,7 @@
         <v>11</v>
       </c>
       <c r="D462" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E462" s="1" t="s">
         <v>21</v>
@@ -21385,7 +21432,7 @@
         <v>30</v>
       </c>
       <c r="H462" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I462" s="54">
         <v>46279</v>
@@ -21395,7 +21442,7 @@
       </c>
       <c r="K462" s="55"/>
     </row>
-    <row r="463" spans="1:11">
+    <row r="463" spans="1:11" hidden="1">
       <c r="A463" s="4">
         <v>462</v>
       </c>
@@ -21406,7 +21453,7 @@
         <v>11</v>
       </c>
       <c r="D463" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E463" s="1" t="s">
         <v>21</v>
@@ -21418,7 +21465,7 @@
         <v>30</v>
       </c>
       <c r="H463" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I463" s="54">
         <v>46279</v>
@@ -21428,7 +21475,7 @@
       </c>
       <c r="K463" s="55"/>
     </row>
-    <row r="464" spans="1:11">
+    <row r="464" spans="1:11" hidden="1">
       <c r="A464" s="4">
         <v>463</v>
       </c>
@@ -21439,7 +21486,7 @@
         <v>11</v>
       </c>
       <c r="D464" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E464" s="1" t="s">
         <v>21</v>
@@ -21451,7 +21498,7 @@
         <v>30</v>
       </c>
       <c r="H464" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I464" s="54">
         <v>46279</v>
@@ -21461,7 +21508,7 @@
       </c>
       <c r="K464" s="55"/>
     </row>
-    <row r="465" spans="1:11">
+    <row r="465" spans="1:11" hidden="1">
       <c r="A465" s="4">
         <v>464</v>
       </c>
@@ -21472,7 +21519,7 @@
         <v>11</v>
       </c>
       <c r="D465" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E465" s="1" t="s">
         <v>21</v>
@@ -21484,7 +21531,7 @@
         <v>30</v>
       </c>
       <c r="H465" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I465" s="54">
         <v>46279</v>
@@ -21494,7 +21541,7 @@
       </c>
       <c r="K465" s="55"/>
     </row>
-    <row r="466" spans="1:11">
+    <row r="466" spans="1:11" hidden="1">
       <c r="A466" s="4">
         <v>465</v>
       </c>
@@ -21505,7 +21552,7 @@
         <v>11</v>
       </c>
       <c r="D466" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E466" s="1" t="s">
         <v>21</v>
@@ -21517,7 +21564,7 @@
         <v>30</v>
       </c>
       <c r="H466" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I466" s="54">
         <v>46279</v>
@@ -21527,7 +21574,7 @@
       </c>
       <c r="K466" s="55"/>
     </row>
-    <row r="467" spans="1:11">
+    <row r="467" spans="1:11" hidden="1">
       <c r="A467" s="4">
         <v>466</v>
       </c>
@@ -21538,7 +21585,7 @@
         <v>11</v>
       </c>
       <c r="D467" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E467" s="1" t="s">
         <v>21</v>
@@ -21550,7 +21597,7 @@
         <v>30</v>
       </c>
       <c r="H467" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I467" s="54">
         <v>46279</v>
@@ -21560,7 +21607,7 @@
       </c>
       <c r="K467" s="55"/>
     </row>
-    <row r="468" spans="1:11">
+    <row r="468" spans="1:11" hidden="1">
       <c r="A468" s="4">
         <v>467</v>
       </c>
@@ -21571,7 +21618,7 @@
         <v>11</v>
       </c>
       <c r="D468" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E468" s="1" t="s">
         <v>21</v>
@@ -21583,7 +21630,7 @@
         <v>30</v>
       </c>
       <c r="H468" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I468" s="54">
         <v>46279</v>
@@ -21593,7 +21640,7 @@
       </c>
       <c r="K468" s="55"/>
     </row>
-    <row r="469" spans="1:11">
+    <row r="469" spans="1:11" hidden="1">
       <c r="A469" s="4">
         <v>468</v>
       </c>
@@ -21604,7 +21651,7 @@
         <v>11</v>
       </c>
       <c r="D469" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E469" s="1" t="s">
         <v>21</v>
@@ -21616,7 +21663,7 @@
         <v>30</v>
       </c>
       <c r="H469" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I469" s="54">
         <v>46279</v>
@@ -21626,7 +21673,7 @@
       </c>
       <c r="K469" s="55"/>
     </row>
-    <row r="470" spans="1:11">
+    <row r="470" spans="1:11" hidden="1">
       <c r="A470" s="4">
         <v>469</v>
       </c>
@@ -21637,7 +21684,7 @@
         <v>11</v>
       </c>
       <c r="D470" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E470" s="1" t="s">
         <v>21</v>
@@ -21649,7 +21696,7 @@
         <v>30</v>
       </c>
       <c r="H470" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I470" s="54">
         <v>46279</v>
@@ -21659,7 +21706,7 @@
       </c>
       <c r="K470" s="55"/>
     </row>
-    <row r="471" spans="1:11">
+    <row r="471" spans="1:11" hidden="1">
       <c r="A471" s="4">
         <v>470</v>
       </c>
@@ -21670,7 +21717,7 @@
         <v>11</v>
       </c>
       <c r="D471" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E471" s="1" t="s">
         <v>21</v>
@@ -21682,7 +21729,7 @@
         <v>30</v>
       </c>
       <c r="H471" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I471" s="54">
         <v>46288</v>
@@ -21692,7 +21739,7 @@
       </c>
       <c r="K471" s="55"/>
     </row>
-    <row r="472" spans="1:11">
+    <row r="472" spans="1:11" hidden="1">
       <c r="A472" s="4">
         <v>471</v>
       </c>
@@ -21703,7 +21750,7 @@
         <v>11</v>
       </c>
       <c r="D472" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E472" s="1" t="s">
         <v>21</v>
@@ -21715,7 +21762,7 @@
         <v>30</v>
       </c>
       <c r="H472" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I472" s="54">
         <v>46279</v>
@@ -21725,7 +21772,7 @@
       </c>
       <c r="K472" s="55"/>
     </row>
-    <row r="473" spans="1:11">
+    <row r="473" spans="1:11" hidden="1">
       <c r="A473" s="4">
         <v>472</v>
       </c>
@@ -21748,7 +21795,7 @@
         <v>14</v>
       </c>
       <c r="H473" s="1" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="I473" s="23">
         <v>45940</v>
@@ -21760,7 +21807,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="474" spans="1:11">
+    <row r="474" spans="1:11" hidden="1">
       <c r="A474" s="4">
         <v>473</v>
       </c>
@@ -21783,7 +21830,7 @@
         <v>14</v>
       </c>
       <c r="H474" s="1" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="I474" s="23">
         <v>45940</v>
@@ -21795,7 +21842,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="475" spans="1:11">
+    <row r="475" spans="1:11" hidden="1">
       <c r="A475" s="4">
         <v>474</v>
       </c>
@@ -21818,7 +21865,7 @@
         <v>14</v>
       </c>
       <c r="H475" s="1" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="I475" s="23">
         <v>45940</v>
@@ -21830,7 +21877,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="476" spans="1:11">
+    <row r="476" spans="1:11" hidden="1">
       <c r="A476" s="4">
         <v>475</v>
       </c>
@@ -21853,7 +21900,7 @@
         <v>14</v>
       </c>
       <c r="H476" s="1" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="I476" s="23">
         <v>45945</v>
@@ -21865,7 +21912,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="477" spans="1:11">
+    <row r="477" spans="1:11" hidden="1">
       <c r="A477" s="4">
         <v>476</v>
       </c>
@@ -21888,7 +21935,7 @@
         <v>14</v>
       </c>
       <c r="H477" s="1" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="I477" s="23">
         <v>45950</v>
@@ -21900,7 +21947,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="478" spans="1:11">
+    <row r="478" spans="1:11" hidden="1">
       <c r="A478" s="4">
         <v>477</v>
       </c>
@@ -21923,7 +21970,7 @@
         <v>14</v>
       </c>
       <c r="H478" s="1" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="I478" s="23">
         <v>45950</v>
@@ -21935,7 +21982,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="479" spans="1:11">
+    <row r="479" spans="1:11" hidden="1">
       <c r="A479" s="4">
         <v>478</v>
       </c>
@@ -21958,7 +22005,7 @@
         <v>14</v>
       </c>
       <c r="H479" s="1" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="I479" s="23">
         <v>45952</v>
@@ -21970,7 +22017,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="480" spans="1:11">
+    <row r="480" spans="1:11" hidden="1">
       <c r="A480" s="4">
         <v>479</v>
       </c>
@@ -21993,7 +22040,7 @@
         <v>14</v>
       </c>
       <c r="H480" s="1" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="I480" s="23">
         <v>45952</v>
@@ -22005,7 +22052,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="481" spans="1:11">
+    <row r="481" spans="1:11" hidden="1">
       <c r="A481" s="4">
         <v>480</v>
       </c>
@@ -22028,7 +22075,7 @@
         <v>14</v>
       </c>
       <c r="H481" s="1" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="I481" s="23">
         <v>45960</v>
@@ -22040,7 +22087,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="482" spans="1:11">
+    <row r="482" spans="1:11" hidden="1">
       <c r="A482" s="4">
         <v>481</v>
       </c>
@@ -22063,7 +22110,7 @@
         <v>14</v>
       </c>
       <c r="H482" s="1" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="I482" s="23">
         <v>45992</v>
@@ -22075,7 +22122,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="483" spans="1:11">
+    <row r="483" spans="1:11" hidden="1">
       <c r="A483" s="4">
         <v>482</v>
       </c>
@@ -22098,7 +22145,7 @@
         <v>14</v>
       </c>
       <c r="H483" s="1" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="I483" s="23">
         <v>45992</v>
@@ -22110,7 +22157,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="484" spans="1:11">
+    <row r="484" spans="1:11" hidden="1">
       <c r="A484" s="4">
         <v>483</v>
       </c>
@@ -22133,7 +22180,7 @@
         <v>14</v>
       </c>
       <c r="H484" s="1" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="I484" s="23">
         <v>45975</v>
@@ -22145,7 +22192,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="485" spans="1:11">
+    <row r="485" spans="1:11" hidden="1">
       <c r="A485" s="4">
         <v>484</v>
       </c>
@@ -22168,7 +22215,7 @@
         <v>14</v>
       </c>
       <c r="H485" s="1" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="I485" s="23">
         <v>45975</v>
@@ -22180,7 +22227,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="486" spans="1:11">
+    <row r="486" spans="1:11" hidden="1">
       <c r="A486" s="4">
         <v>485</v>
       </c>
@@ -22203,7 +22250,7 @@
         <v>14</v>
       </c>
       <c r="H486" s="1" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="I486" s="23">
         <v>45975</v>
@@ -22215,7 +22262,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="487" spans="1:11">
+    <row r="487" spans="1:11" hidden="1">
       <c r="A487" s="4">
         <v>486</v>
       </c>
@@ -22238,7 +22285,7 @@
         <v>14</v>
       </c>
       <c r="H487" s="1" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="I487" s="23">
         <v>46001</v>
@@ -22250,7 +22297,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="488" spans="1:11">
+    <row r="488" spans="1:11" hidden="1">
       <c r="A488" s="4">
         <v>487</v>
       </c>
@@ -22273,7 +22320,7 @@
         <v>14</v>
       </c>
       <c r="H488" s="1" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="I488" s="23">
         <v>46036</v>
@@ -22285,7 +22332,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="489" spans="1:11">
+    <row r="489" spans="1:11" hidden="1">
       <c r="A489" s="4">
         <v>488</v>
       </c>
@@ -22308,7 +22355,7 @@
         <v>14</v>
       </c>
       <c r="H489" s="1" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="I489" s="23">
         <v>46037</v>
@@ -22320,7 +22367,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="490" spans="1:11">
+    <row r="490" spans="1:11" hidden="1">
       <c r="A490" s="4">
         <v>489</v>
       </c>
@@ -22343,7 +22390,7 @@
         <v>14</v>
       </c>
       <c r="H490" s="1" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="I490" s="23">
         <v>46001</v>
@@ -22353,7 +22400,7 @@
       </c>
       <c r="K490" s="24"/>
     </row>
-    <row r="491" spans="1:11">
+    <row r="491" spans="1:11" hidden="1">
       <c r="A491" s="4">
         <v>490</v>
       </c>
@@ -22376,7 +22423,7 @@
         <v>14</v>
       </c>
       <c r="H491" s="1" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="I491" s="23">
         <v>46041</v>
@@ -22388,7 +22435,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="492" spans="1:11">
+    <row r="492" spans="1:11" hidden="1">
       <c r="A492" s="4">
         <v>491</v>
       </c>
@@ -22411,7 +22458,7 @@
         <v>14</v>
       </c>
       <c r="H492" s="1" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="I492" s="23">
         <v>46041</v>
@@ -22423,7 +22470,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="493" spans="1:11">
+    <row r="493" spans="1:11" hidden="1">
       <c r="A493" s="4">
         <v>492</v>
       </c>
@@ -22446,7 +22493,7 @@
         <v>14</v>
       </c>
       <c r="H493" s="1" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="I493" s="23">
         <v>45957</v>
@@ -22458,7 +22505,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="494" spans="1:11">
+    <row r="494" spans="1:11" hidden="1">
       <c r="A494" s="4">
         <v>493</v>
       </c>
@@ -22481,7 +22528,7 @@
         <v>14</v>
       </c>
       <c r="H494" s="1" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="I494" s="23">
         <v>46034</v>
@@ -22493,7 +22540,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="495" spans="1:11">
+    <row r="495" spans="1:11" hidden="1">
       <c r="A495" s="4">
         <v>494</v>
       </c>
@@ -22528,7 +22575,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="496" spans="1:11">
+    <row r="496" spans="1:11" hidden="1">
       <c r="A496" s="4">
         <v>495</v>
       </c>
@@ -22551,7 +22598,7 @@
         <v>14</v>
       </c>
       <c r="H496" s="1" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="I496" s="23">
         <v>46036</v>
@@ -22563,7 +22610,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="497" spans="1:11">
+    <row r="497" spans="1:11" hidden="1">
       <c r="A497" s="4">
         <v>496</v>
       </c>
@@ -22586,7 +22633,7 @@
         <v>30</v>
       </c>
       <c r="H497" s="1" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="I497" s="23">
         <v>45950</v>
@@ -22598,7 +22645,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="498" spans="1:11">
+    <row r="498" spans="1:11" hidden="1">
       <c r="A498" s="4">
         <v>497</v>
       </c>
@@ -22621,7 +22668,7 @@
         <v>30</v>
       </c>
       <c r="H498" s="1" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="I498" s="23">
         <v>45950</v>
@@ -22633,7 +22680,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="499" spans="1:11">
+    <row r="499" spans="1:11" hidden="1">
       <c r="A499" s="4">
         <v>498</v>
       </c>
@@ -22656,7 +22703,7 @@
         <v>30</v>
       </c>
       <c r="H499" s="1" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="I499" s="23">
         <v>45952</v>
@@ -22668,7 +22715,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="500" spans="1:11">
+    <row r="500" spans="1:11" hidden="1">
       <c r="A500" s="4">
         <v>499</v>
       </c>
@@ -22691,7 +22738,7 @@
         <v>30</v>
       </c>
       <c r="H500" s="1" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="I500" s="23">
         <v>46048</v>
@@ -22703,7 +22750,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="501" spans="1:11">
+    <row r="501" spans="1:11" hidden="1">
       <c r="A501" s="4">
         <v>500</v>
       </c>
@@ -22726,7 +22773,7 @@
         <v>30</v>
       </c>
       <c r="H501" s="1" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="I501" s="23">
         <v>46050</v>
@@ -22738,7 +22785,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="502" spans="1:11">
+    <row r="502" spans="1:11" hidden="1">
       <c r="A502" s="4">
         <v>501</v>
       </c>
@@ -22794,7 +22841,7 @@
         <v>30</v>
       </c>
       <c r="H503" s="1" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="I503" s="23">
         <v>45712</v>
@@ -22806,7 +22853,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="504" spans="1:11">
+    <row r="504" spans="1:11" hidden="1">
       <c r="A504" s="4">
         <v>503</v>
       </c>
@@ -22829,7 +22876,7 @@
         <v>30</v>
       </c>
       <c r="H504" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="I504" s="23">
         <v>46142</v>
@@ -22839,7 +22886,7 @@
       </c>
       <c r="K504" s="24"/>
     </row>
-    <row r="505" spans="1:11">
+    <row r="505" spans="1:11" hidden="1">
       <c r="A505" s="4">
         <v>504</v>
       </c>
@@ -22862,7 +22909,7 @@
         <v>30</v>
       </c>
       <c r="H505" s="1" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="I505" s="23">
         <v>46174</v>
@@ -22872,7 +22919,7 @@
       </c>
       <c r="K505" s="24"/>
     </row>
-    <row r="506" spans="1:11">
+    <row r="506" spans="1:11" hidden="1">
       <c r="A506" s="4">
         <v>505</v>
       </c>
@@ -22889,7 +22936,7 @@
         <v>951</v>
       </c>
       <c r="F506" s="1" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="G506" s="1" t="s">
         <v>30</v>
@@ -22902,10 +22949,10 @@
         <v>574</v>
       </c>
       <c r="K506" s="3" t="s">
-        <v>1283</v>
-      </c>
-    </row>
-    <row r="507" spans="1:11">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="507" spans="1:11" hidden="1">
       <c r="A507" s="4">
         <v>506</v>
       </c>
@@ -22928,7 +22975,7 @@
         <v>30</v>
       </c>
       <c r="H507" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="I507" s="23">
         <v>46063</v>
@@ -22961,7 +23008,7 @@
         <v>30</v>
       </c>
       <c r="H508" s="1" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="I508" s="23">
         <v>46104</v>
@@ -22994,7 +23041,7 @@
         <v>30</v>
       </c>
       <c r="H509" s="1" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="I509" s="23">
         <v>46129</v>
@@ -23027,7 +23074,7 @@
         <v>30</v>
       </c>
       <c r="H510" s="1" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="I510" s="23">
         <v>46081</v>
@@ -23037,7 +23084,7 @@
       </c>
       <c r="K510" s="24"/>
     </row>
-    <row r="511" spans="1:11">
+    <row r="511" spans="1:11" hidden="1">
       <c r="A511" s="4">
         <v>510</v>
       </c>
@@ -23060,7 +23107,7 @@
         <v>30</v>
       </c>
       <c r="H511" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="I511" s="23">
         <v>46146</v>
@@ -23070,7 +23117,7 @@
       </c>
       <c r="K511" s="24"/>
     </row>
-    <row r="512" spans="1:11">
+    <row r="512" spans="1:11" hidden="1">
       <c r="A512" s="4">
         <v>511</v>
       </c>
@@ -23093,7 +23140,7 @@
         <v>30</v>
       </c>
       <c r="H512" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="I512" s="23">
         <v>46081</v>
@@ -23103,7 +23150,7 @@
       </c>
       <c r="K512" s="24"/>
     </row>
-    <row r="513" spans="1:11">
+    <row r="513" spans="1:11" hidden="1">
       <c r="A513" s="4">
         <v>512</v>
       </c>
@@ -23114,7 +23161,7 @@
         <v>83</v>
       </c>
       <c r="D513" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E513" s="1" t="s">
         <v>21</v>
@@ -23126,7 +23173,7 @@
         <v>30</v>
       </c>
       <c r="H513" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I513" s="54">
         <v>46279</v>
@@ -23136,7 +23183,7 @@
       </c>
       <c r="K513" s="55"/>
     </row>
-    <row r="514" spans="1:11">
+    <row r="514" spans="1:11" hidden="1">
       <c r="A514" s="4">
         <v>513</v>
       </c>
@@ -23147,7 +23194,7 @@
         <v>83</v>
       </c>
       <c r="D514" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E514" s="1" t="s">
         <v>21</v>
@@ -23159,7 +23206,7 @@
         <v>30</v>
       </c>
       <c r="H514" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I514" s="54">
         <v>46279</v>
@@ -23169,7 +23216,7 @@
       </c>
       <c r="K514" s="55"/>
     </row>
-    <row r="515" spans="1:11">
+    <row r="515" spans="1:11" hidden="1">
       <c r="A515" s="4">
         <v>514</v>
       </c>
@@ -23180,7 +23227,7 @@
         <v>83</v>
       </c>
       <c r="D515" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E515" s="1" t="s">
         <v>21</v>
@@ -23192,7 +23239,7 @@
         <v>30</v>
       </c>
       <c r="H515" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I515" s="54">
         <v>46279</v>
@@ -23202,7 +23249,7 @@
       </c>
       <c r="K515" s="55"/>
     </row>
-    <row r="516" spans="1:11">
+    <row r="516" spans="1:11" hidden="1">
       <c r="A516" s="4">
         <v>515</v>
       </c>
@@ -23213,7 +23260,7 @@
         <v>83</v>
       </c>
       <c r="D516" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E516" s="1" t="s">
         <v>21</v>
@@ -23225,7 +23272,7 @@
         <v>30</v>
       </c>
       <c r="H516" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I516" s="54">
         <v>46279</v>
@@ -23235,7 +23282,7 @@
       </c>
       <c r="K516" s="55"/>
     </row>
-    <row r="517" spans="1:11">
+    <row r="517" spans="1:11" hidden="1">
       <c r="A517" s="4">
         <v>516</v>
       </c>
@@ -23246,7 +23293,7 @@
         <v>83</v>
       </c>
       <c r="D517" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E517" s="1" t="s">
         <v>21</v>
@@ -23258,7 +23305,7 @@
         <v>30</v>
       </c>
       <c r="H517" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I517" s="54">
         <v>46279</v>
@@ -23268,7 +23315,7 @@
       </c>
       <c r="K517" s="55"/>
     </row>
-    <row r="518" spans="1:11">
+    <row r="518" spans="1:11" hidden="1">
       <c r="A518" s="4">
         <v>517</v>
       </c>
@@ -23282,16 +23329,16 @@
         <v>1081</v>
       </c>
       <c r="E518" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F518" s="1" t="s">
-        <v>1082</v>
+        <v>23</v>
       </c>
       <c r="G518" s="1" t="s">
         <v>30</v>
       </c>
       <c r="H518" s="1" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="I518" s="23">
         <v>46091</v>
@@ -23300,7 +23347,7 @@
         <v>645</v>
       </c>
       <c r="K518" s="3" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="519" spans="1:11">
@@ -23326,7 +23373,7 @@
         <v>30</v>
       </c>
       <c r="H519" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I519" s="23">
         <v>46098</v>
@@ -23359,7 +23406,7 @@
         <v>30</v>
       </c>
       <c r="H520" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I520" s="23">
         <v>46099</v>
@@ -23392,7 +23439,7 @@
         <v>30</v>
       </c>
       <c r="H521" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I521" s="23">
         <v>46099</v>
@@ -23401,7 +23448,7 @@
         <v>574</v>
       </c>
       <c r="K521" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="522" spans="1:11">
@@ -23427,7 +23474,7 @@
         <v>30</v>
       </c>
       <c r="H522" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I522" s="23">
         <v>46099</v>
@@ -23460,7 +23507,7 @@
         <v>30</v>
       </c>
       <c r="H523" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I523" s="23">
         <v>46099</v>
@@ -23493,7 +23540,7 @@
         <v>30</v>
       </c>
       <c r="H524" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I524" s="23">
         <v>46081</v>
@@ -23526,7 +23573,7 @@
         <v>30</v>
       </c>
       <c r="H525" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="I525" s="23">
         <v>46105</v>
@@ -23535,7 +23582,7 @@
         <v>645</v>
       </c>
       <c r="K525" s="3" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="526" spans="1:11">
@@ -23561,7 +23608,7 @@
         <v>30</v>
       </c>
       <c r="H526" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I526" s="23">
         <v>46105</v>
@@ -23594,7 +23641,7 @@
         <v>30</v>
       </c>
       <c r="H527" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I527" s="23">
         <v>46108</v>
@@ -23627,7 +23674,7 @@
         <v>30</v>
       </c>
       <c r="H528" s="1" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="I528" s="23">
         <v>46108</v>
@@ -23660,7 +23707,7 @@
         <v>30</v>
       </c>
       <c r="H529" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I529" s="23">
         <v>46111</v>
@@ -23693,7 +23740,7 @@
         <v>30</v>
       </c>
       <c r="H530" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I530" s="23">
         <v>46113</v>
@@ -23726,7 +23773,7 @@
         <v>30</v>
       </c>
       <c r="H531" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I531" s="23">
         <v>46114</v>
@@ -23759,7 +23806,7 @@
         <v>30</v>
       </c>
       <c r="H532" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I532" s="23">
         <v>46114</v>
@@ -23792,7 +23839,7 @@
         <v>30</v>
       </c>
       <c r="H533" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I533" s="23">
         <v>46118</v>
@@ -23825,7 +23872,7 @@
         <v>30</v>
       </c>
       <c r="H534" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I534" s="23">
         <v>46119</v>
@@ -23858,7 +23905,7 @@
         <v>30</v>
       </c>
       <c r="H535" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I535" s="23">
         <v>46120</v>
@@ -23891,7 +23938,7 @@
         <v>30</v>
       </c>
       <c r="H536" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I536" s="23">
         <v>46120</v>
@@ -23924,7 +23971,7 @@
         <v>30</v>
       </c>
       <c r="H537" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I537" s="23">
         <v>46120</v>
@@ -23957,7 +24004,7 @@
         <v>30</v>
       </c>
       <c r="H538" s="1" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="I538" s="23">
         <v>46121</v>
@@ -23966,7 +24013,7 @@
         <v>574</v>
       </c>
       <c r="K538" s="3" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="539" spans="1:11">
@@ -23992,7 +24039,7 @@
         <v>30</v>
       </c>
       <c r="H539" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I539" s="23">
         <v>46126</v>
@@ -24025,7 +24072,7 @@
         <v>30</v>
       </c>
       <c r="H540" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I540" s="23">
         <v>46126</v>
@@ -24058,7 +24105,7 @@
         <v>30</v>
       </c>
       <c r="H541" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I541" s="23">
         <v>46126</v>
@@ -24091,7 +24138,7 @@
         <v>30</v>
       </c>
       <c r="H542" s="1" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="I542" s="23">
         <v>46128</v>
@@ -24124,7 +24171,7 @@
         <v>30</v>
       </c>
       <c r="H543" s="1" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="I543" s="23">
         <v>46081</v>
@@ -24157,7 +24204,7 @@
         <v>30</v>
       </c>
       <c r="H544" s="1" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="I544" s="23">
         <v>46081</v>
@@ -24190,7 +24237,7 @@
         <v>30</v>
       </c>
       <c r="H545" s="1" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="I545" s="23">
         <v>46134</v>
@@ -24223,7 +24270,7 @@
         <v>30</v>
       </c>
       <c r="H546" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I546" s="23">
         <v>46134</v>
@@ -24256,7 +24303,7 @@
         <v>30</v>
       </c>
       <c r="H547" s="4" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="I547" s="23">
         <v>46142</v>
@@ -24289,7 +24336,7 @@
         <v>30</v>
       </c>
       <c r="H548" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I548" s="23">
         <v>46148</v>
@@ -24298,7 +24345,7 @@
         <v>574</v>
       </c>
       <c r="K548" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="549" spans="1:11">
@@ -24324,7 +24371,7 @@
         <v>30</v>
       </c>
       <c r="H549" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I549" s="23">
         <v>46148</v>
@@ -24357,7 +24404,7 @@
         <v>30</v>
       </c>
       <c r="H550" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I550" s="23">
         <v>46148</v>
@@ -24390,7 +24437,7 @@
         <v>30</v>
       </c>
       <c r="H551" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I551" s="23">
         <v>46161</v>
@@ -24423,7 +24470,7 @@
         <v>30</v>
       </c>
       <c r="H552" s="1" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="I552" s="23">
         <v>46164</v>
@@ -24432,7 +24479,7 @@
         <v>645</v>
       </c>
       <c r="K552" s="3" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="553" spans="1:11">
@@ -24458,7 +24505,7 @@
         <v>30</v>
       </c>
       <c r="H553" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I553" s="23">
         <v>46164</v>
@@ -24479,7 +24526,7 @@
         <v>11</v>
       </c>
       <c r="D554" s="2" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="E554" s="1" t="s">
         <v>19</v>
@@ -24491,7 +24538,7 @@
         <v>30</v>
       </c>
       <c r="H554" s="1" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="I554" s="23">
         <v>46081</v>
@@ -24500,10 +24547,10 @@
         <v>574</v>
       </c>
       <c r="K554" s="3" t="s">
-        <v>1315</v>
-      </c>
-    </row>
-    <row r="555" spans="1:11">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="555" spans="1:11" hidden="1">
       <c r="A555" s="4">
         <v>554</v>
       </c>
@@ -24514,7 +24561,7 @@
         <v>11</v>
       </c>
       <c r="D555" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E555" s="1" t="s">
         <v>21</v>
@@ -24526,7 +24573,7 @@
         <v>30</v>
       </c>
       <c r="H555" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I555" s="23">
         <v>46081</v>
@@ -24547,7 +24594,7 @@
         <v>11</v>
       </c>
       <c r="D556" s="2" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="E556" s="1" t="s">
         <v>19</v>
@@ -24559,7 +24606,7 @@
         <v>30</v>
       </c>
       <c r="H556" s="1" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="I556" s="23">
         <v>46215</v>
@@ -24592,7 +24639,7 @@
         <v>30</v>
       </c>
       <c r="H557" s="1" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="I557" s="23">
         <v>46149</v>
@@ -24613,7 +24660,7 @@
         <v>11</v>
       </c>
       <c r="D558" s="2" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="E558" s="1" t="s">
         <v>19</v>
@@ -24625,7 +24672,7 @@
         <v>30</v>
       </c>
       <c r="H558" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I558" s="54">
         <v>46293</v>
@@ -24646,7 +24693,7 @@
         <v>11</v>
       </c>
       <c r="D559" s="2" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="E559" s="1" t="s">
         <v>19</v>
@@ -24658,7 +24705,7 @@
         <v>30</v>
       </c>
       <c r="H559" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I559" s="54">
         <v>46293</v>
@@ -24668,7 +24715,7 @@
       </c>
       <c r="K559" s="55"/>
     </row>
-    <row r="560" spans="1:11" ht="15.6">
+    <row r="560" spans="1:11" ht="15.75">
       <c r="A560" s="4">
         <v>559</v>
       </c>
@@ -24679,7 +24726,7 @@
         <v>11</v>
       </c>
       <c r="D560" s="2" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
       <c r="E560" s="1" t="s">
         <v>19</v>
@@ -24691,7 +24738,7 @@
         <v>30</v>
       </c>
       <c r="H560" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I560" s="54">
         <v>46293</v>
@@ -24712,7 +24759,7 @@
         <v>11</v>
       </c>
       <c r="D561" s="2" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="E561" s="1" t="s">
         <v>19</v>
@@ -24724,7 +24771,7 @@
         <v>30</v>
       </c>
       <c r="H561" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I561" s="54">
         <v>46293</v>
@@ -24745,7 +24792,7 @@
         <v>11</v>
       </c>
       <c r="D562" s="2" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="E562" s="1" t="s">
         <v>19</v>
@@ -24757,7 +24804,7 @@
         <v>30</v>
       </c>
       <c r="H562" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I562" s="54">
         <v>46279</v>
@@ -24778,7 +24825,7 @@
         <v>11</v>
       </c>
       <c r="D563" s="2" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
       <c r="E563" s="1" t="s">
         <v>19</v>
@@ -24790,7 +24837,7 @@
         <v>30</v>
       </c>
       <c r="H563" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I563" s="54">
         <v>46287</v>
@@ -24811,7 +24858,7 @@
         <v>11</v>
       </c>
       <c r="D564" s="2" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="E564" s="1" t="s">
         <v>19</v>
@@ -24823,7 +24870,7 @@
         <v>30</v>
       </c>
       <c r="H564" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I564" s="54">
         <v>46287</v>
@@ -24844,7 +24891,7 @@
         <v>11</v>
       </c>
       <c r="D565" s="2" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="E565" s="1" t="s">
         <v>19</v>
@@ -24856,7 +24903,7 @@
         <v>30</v>
       </c>
       <c r="H565" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I565" s="54">
         <v>46287</v>
@@ -24877,7 +24924,7 @@
         <v>11</v>
       </c>
       <c r="D566" s="2" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="E566" s="1" t="s">
         <v>19</v>
@@ -24889,7 +24936,7 @@
         <v>30</v>
       </c>
       <c r="H566" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I566" s="54">
         <v>46287</v>
@@ -24910,7 +24957,7 @@
         <v>11</v>
       </c>
       <c r="D567" s="2" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="E567" s="1" t="s">
         <v>19</v>
@@ -24922,7 +24969,7 @@
         <v>30</v>
       </c>
       <c r="H567" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I567" s="54">
         <v>46287</v>
@@ -24943,7 +24990,7 @@
         <v>11</v>
       </c>
       <c r="D568" s="2" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="E568" s="1" t="s">
         <v>19</v>
@@ -24955,7 +25002,7 @@
         <v>30</v>
       </c>
       <c r="H568" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I568" s="54">
         <v>46287</v>
@@ -24976,7 +25023,7 @@
         <v>11</v>
       </c>
       <c r="D569" s="2" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="E569" s="1" t="s">
         <v>19</v>
@@ -24988,7 +25035,7 @@
         <v>30</v>
       </c>
       <c r="H569" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I569" s="54">
         <v>46287</v>
@@ -25009,19 +25056,19 @@
         <v>11</v>
       </c>
       <c r="D570" s="2" t="s">
-        <v>1360</v>
+        <v>1453</v>
       </c>
       <c r="E570" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F570" s="1" t="s">
-        <v>521</v>
+        <v>1457</v>
       </c>
       <c r="G570" s="1" t="s">
         <v>30</v>
       </c>
       <c r="H570" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I570" s="54">
         <v>46287</v>
@@ -25042,19 +25089,19 @@
         <v>11</v>
       </c>
       <c r="D571" s="2" t="s">
-        <v>1360</v>
+        <v>1454</v>
       </c>
       <c r="E571" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F571" s="1" t="s">
-        <v>521</v>
+        <v>1056</v>
       </c>
       <c r="G571" s="1" t="s">
         <v>30</v>
       </c>
       <c r="H571" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I571" s="54">
         <v>46287</v>
@@ -25075,19 +25122,19 @@
         <v>11</v>
       </c>
       <c r="D572" s="2" t="s">
-        <v>1360</v>
+        <v>1455</v>
       </c>
       <c r="E572" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F572" s="1" t="s">
-        <v>521</v>
+        <v>1045</v>
       </c>
       <c r="G572" s="1" t="s">
         <v>30</v>
       </c>
       <c r="H572" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I572" s="54">
         <v>46287</v>
@@ -25108,19 +25155,19 @@
         <v>11</v>
       </c>
       <c r="D573" s="2" t="s">
-        <v>1360</v>
+        <v>1456</v>
       </c>
       <c r="E573" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F573" s="1" t="s">
-        <v>521</v>
+        <v>1061</v>
       </c>
       <c r="G573" s="1" t="s">
         <v>30</v>
       </c>
       <c r="H573" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I573" s="54">
         <v>46287</v>
@@ -25130,7 +25177,7 @@
       </c>
       <c r="K573" s="55"/>
     </row>
-    <row r="574" spans="1:11">
+    <row r="574" spans="1:11" hidden="1">
       <c r="A574" s="4">
         <v>573</v>
       </c>
@@ -25141,7 +25188,7 @@
         <v>11</v>
       </c>
       <c r="D574" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E574" s="1" t="s">
         <v>21</v>
@@ -25153,7 +25200,7 @@
         <v>30</v>
       </c>
       <c r="H574" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I574" s="54">
         <v>46287</v>
@@ -25163,7 +25210,7 @@
       </c>
       <c r="K574" s="55"/>
     </row>
-    <row r="575" spans="1:11">
+    <row r="575" spans="1:11" hidden="1">
       <c r="A575" s="4">
         <v>574</v>
       </c>
@@ -25174,7 +25221,7 @@
         <v>11</v>
       </c>
       <c r="D575" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E575" s="1" t="s">
         <v>21</v>
@@ -25186,7 +25233,7 @@
         <v>30</v>
       </c>
       <c r="H575" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I575" s="54">
         <v>46287</v>
@@ -25196,7 +25243,7 @@
       </c>
       <c r="K575" s="55"/>
     </row>
-    <row r="576" spans="1:11">
+    <row r="576" spans="1:11" hidden="1">
       <c r="A576" s="4">
         <v>575</v>
       </c>
@@ -25207,7 +25254,7 @@
         <v>11</v>
       </c>
       <c r="D576" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E576" s="1" t="s">
         <v>21</v>
@@ -25219,7 +25266,7 @@
         <v>30</v>
       </c>
       <c r="H576" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I576" s="54">
         <v>46287</v>
@@ -25229,7 +25276,7 @@
       </c>
       <c r="K576" s="55"/>
     </row>
-    <row r="577" spans="1:11">
+    <row r="577" spans="1:11" hidden="1">
       <c r="A577" s="4">
         <v>576</v>
       </c>
@@ -25240,7 +25287,7 @@
         <v>11</v>
       </c>
       <c r="D577" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E577" s="1" t="s">
         <v>21</v>
@@ -25252,7 +25299,7 @@
         <v>30</v>
       </c>
       <c r="H577" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I577" s="54">
         <v>46287</v>
@@ -25262,7 +25309,7 @@
       </c>
       <c r="K577" s="55"/>
     </row>
-    <row r="578" spans="1:11">
+    <row r="578" spans="1:11" hidden="1">
       <c r="A578" s="4">
         <v>577</v>
       </c>
@@ -25273,7 +25320,7 @@
         <v>11</v>
       </c>
       <c r="D578" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E578" s="1" t="s">
         <v>21</v>
@@ -25285,7 +25332,7 @@
         <v>30</v>
       </c>
       <c r="H578" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I578" s="54">
         <v>46287</v>
@@ -25295,7 +25342,7 @@
       </c>
       <c r="K578" s="55"/>
     </row>
-    <row r="579" spans="1:11">
+    <row r="579" spans="1:11" hidden="1">
       <c r="A579" s="4">
         <v>578</v>
       </c>
@@ -25326,7 +25373,7 @@
       </c>
       <c r="K579" s="24"/>
     </row>
-    <row r="580" spans="1:11">
+    <row r="580" spans="1:11" hidden="1">
       <c r="A580" s="4">
         <v>579</v>
       </c>
@@ -25360,83 +25407,96 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="duplicateValues" dxfId="41" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D268">
-    <cfRule type="duplicateValues" dxfId="40" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D366">
-    <cfRule type="duplicateValues" dxfId="37" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D367">
-    <cfRule type="duplicateValues" dxfId="36" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="105"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D502 D2:D367">
-    <cfRule type="duplicateValues" dxfId="35" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:E258 G215 E525:E1048576">
-    <cfRule type="cellIs" dxfId="34" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="26" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E260:E524">
-    <cfRule type="cellIs" dxfId="33" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="22" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F252 F254:F255 F257:F559 F561:F562 F564:F1048576">
-    <cfRule type="cellIs" dxfId="32" priority="15" operator="equal">
+  <conditionalFormatting sqref="F254:F255 F257:F559 F561:F562 F564:F1048576 F1:F252">
+    <cfRule type="cellIs" dxfId="35" priority="18" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="19" operator="equal">
       <formula>"DOADORA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F252 F254:F255 F561:F562 F564:F1048576">
-    <cfRule type="cellIs" dxfId="30" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="27" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="28" operator="equal">
       <formula>"DEPOSITO SOLAGOS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F257:F559">
-    <cfRule type="cellIs" dxfId="28" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="23" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="24" operator="equal">
       <formula>"DEPOSITO SOLAGOS"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H1:H258">
-    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
+  <conditionalFormatting sqref="H1:H17 H19:H258">
+    <cfRule type="cellIs" dxfId="29" priority="4" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H260:H524">
-    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="5" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H526:H580">
-    <cfRule type="cellIs" dxfId="24" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="9" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K215">
-    <cfRule type="cellIs" dxfId="23" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="13" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="14" operator="equal">
       <formula>"DOADORA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="15" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="16" operator="equal">
       <formula>"DEPOSITO SOLAGOS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F18">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+      <formula>"MANUTENÇÃO"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+      <formula>"DEPOSITO SOLAGOS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H18">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -25450,13 +25510,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6771508-02DF-4FAC-B7A7-A6278CE7AE5B}">
   <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -26072,21 +26132,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD4931DD-77FA-4EF6-BAB3-744C5E5D53EC}">
   <dimension ref="A1:XFC75"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.21875" style="33" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="68.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.28515625" style="33" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="68.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="0" hidden="1" customWidth="1"/>
-    <col min="14" max="16383" width="8.77734375" hidden="1"/>
-    <col min="16384" max="16384" width="16.21875" hidden="1" customWidth="1"/>
+    <col min="14" max="16383" width="8.7109375" hidden="1"/>
+    <col min="16384" max="16384" width="16.28515625" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -27834,51 +27894,51 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="D2:D51">
-    <cfRule type="duplicateValues" dxfId="19" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D52">
-    <cfRule type="duplicateValues" dxfId="18" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D53">
-    <cfRule type="duplicateValues" dxfId="17" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E51">
-    <cfRule type="cellIs" dxfId="14" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="16" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E52:E53">
-    <cfRule type="cellIs" dxfId="13" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="5" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F51">
-    <cfRule type="cellIs" dxfId="12" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="17" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="18" operator="equal">
       <formula>"DOADORA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="20" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="21" operator="equal">
       <formula>"DEPOSITO SOLAGOS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F52:F53">
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="3" operator="equal">
       <formula>"DOADORA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="7" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="8" operator="equal">
       <formula>"DEPOSITO SOLAGOS"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27892,13 +27952,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34C555F1-9084-4660-9D55-C0341FAEDEDD}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="64.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="64.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -27906,16 +27966,16 @@
         <v>4</v>
       </c>
       <c r="B1" s="58" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="C1" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="D1" t="s">
         <v>690</v>
       </c>
       <c r="E1" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -27932,7 +27992,7 @@
         <v>46132</v>
       </c>
       <c r="E2" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -27949,7 +28009,7 @@
         <v>46147</v>
       </c>
       <c r="E3" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -27966,7 +28026,7 @@
         <v>46244</v>
       </c>
       <c r="E4" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -27983,7 +28043,7 @@
         <v>46264</v>
       </c>
       <c r="E5" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -28000,7 +28060,7 @@
         <v>46279</v>
       </c>
       <c r="E6" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -28017,15 +28077,15 @@
         <v>46282</v>
       </c>
       <c r="E7" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="59" t="s">
-        <v>1453</v>
+      <c r="B8" s="1" t="s">
+        <v>1450</v>
       </c>
       <c r="C8">
         <v>5899</v>
@@ -28034,26 +28094,26 @@
         <v>46295</v>
       </c>
       <c r="E8" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
-    <cfRule type="cellIs" dxfId="4" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="23" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B8">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
       <formula>"DOADORA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>"DEPOSITO SOLAGOS"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/data_printer.xlsx
+++ b/data_printer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erick\Desktop\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2255EE2C-1A6C-412B-8B85-E8E1DE2FEC96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{026F155A-2F18-4AAB-B29F-233B4FC32608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A8AA41B5-7AA1-4FF7-A9B8-54B8A4E1AF28}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5381" uniqueCount="1463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5381" uniqueCount="1468">
   <si>
     <t>INDICE</t>
   </si>
@@ -4437,6 +4437,21 @@
   </si>
   <si>
     <t>EXPO</t>
+  </si>
+  <si>
+    <t>X67Y01</t>
+  </si>
+  <si>
+    <t>X5TL010816</t>
+  </si>
+  <si>
+    <t>X5TL010230</t>
+  </si>
+  <si>
+    <t>UBS -  PONTE DOS LEITES</t>
+  </si>
+  <si>
+    <t>UBS - PARACATU</t>
   </si>
 </sst>
 </file>
@@ -4648,7 +4663,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4806,33 +4821,12 @@
     <xf numFmtId="0" fontId="11" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="74">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="73">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -5045,26 +5039,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
@@ -5078,16 +5052,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5143,6 +5107,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="1"/>
       </font>
       <fill>
@@ -5172,6 +5146,19 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
@@ -5185,6 +5172,23 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5659,23 +5663,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}" name="Controle_Inventario_Impressoras" displayName="Controle_Inventario_Impressoras" ref="A1:K584" tableType="queryTable" totalsRowShown="0" headerRowDxfId="73" dataDxfId="72">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}" name="Controle_Inventario_Impressoras" displayName="Controle_Inventario_Impressoras" ref="A1:K584" tableType="queryTable" totalsRowShown="0" headerRowDxfId="72" dataDxfId="71">
   <autoFilter ref="A1:K584" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K37">
     <sortCondition ref="A23"/>
   </sortState>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F8E3D681-C494-47F2-8429-052381C12AF1}" uniqueName="1" name="INDICE" queryTableFieldId="1" dataDxfId="71"/>
-    <tableColumn id="2" xr3:uid="{EE2E8FA5-A99D-4573-9868-408DB8FD4417}" uniqueName="2" name="MODELO" queryTableFieldId="2" dataDxfId="70"/>
-    <tableColumn id="11" xr3:uid="{CB5196C0-CCA1-4329-825F-D71E0948A542}" uniqueName="11" name="TIPO" queryTableFieldId="16390" dataDxfId="69"/>
-    <tableColumn id="3" xr3:uid="{27BC8F35-CC2C-44A1-BAF7-B0390B09477F}" uniqueName="3" name="NUMERO DE SERIE" queryTableFieldId="3" dataDxfId="68"/>
-    <tableColumn id="4" xr3:uid="{552F7A6E-6277-4DC1-9CDA-EA7FDCCE8E36}" uniqueName="4" name="LOCALIZAÇÃO" queryTableFieldId="4" dataDxfId="67"/>
-    <tableColumn id="5" xr3:uid="{4C8345F1-6E01-4566-9030-039665486C03}" uniqueName="5" name="SETOR" queryTableFieldId="5" dataDxfId="66"/>
-    <tableColumn id="9" xr3:uid="{10436F87-F6F1-46C4-A81A-8D144AC72FDF}" uniqueName="9" name="EMPRESA" queryTableFieldId="16389" dataDxfId="65"/>
-    <tableColumn id="13" xr3:uid="{40F07CF2-DF5F-4979-A5BB-71FA79C89740}" uniqueName="13" name="GRUPO" queryTableFieldId="16393" dataDxfId="64"/>
-    <tableColumn id="6" xr3:uid="{B7941BA2-3E1C-476B-A3C7-BA155A35A2D0}" uniqueName="6" name="ATUALIZADO" queryTableFieldId="6" dataDxfId="63"/>
-    <tableColumn id="7" xr3:uid="{4338F703-CE4B-4443-8A10-74F64ED8CD42}" uniqueName="7" name="PRINTWAY" queryTableFieldId="16391" dataDxfId="62"/>
-    <tableColumn id="8" xr3:uid="{02B7C1FB-8EA9-4F22-BCCF-3D1809FFEDCC}" uniqueName="8" name="OBSERVAÇÃO" queryTableFieldId="8" dataDxfId="61"/>
+    <tableColumn id="1" xr3:uid="{F8E3D681-C494-47F2-8429-052381C12AF1}" uniqueName="1" name="INDICE" queryTableFieldId="1" dataDxfId="70"/>
+    <tableColumn id="2" xr3:uid="{EE2E8FA5-A99D-4573-9868-408DB8FD4417}" uniqueName="2" name="MODELO" queryTableFieldId="2" dataDxfId="69"/>
+    <tableColumn id="11" xr3:uid="{CB5196C0-CCA1-4329-825F-D71E0948A542}" uniqueName="11" name="TIPO" queryTableFieldId="16390" dataDxfId="68"/>
+    <tableColumn id="3" xr3:uid="{27BC8F35-CC2C-44A1-BAF7-B0390B09477F}" uniqueName="3" name="NUMERO DE SERIE" queryTableFieldId="3" dataDxfId="67"/>
+    <tableColumn id="4" xr3:uid="{552F7A6E-6277-4DC1-9CDA-EA7FDCCE8E36}" uniqueName="4" name="LOCALIZAÇÃO" queryTableFieldId="4" dataDxfId="66"/>
+    <tableColumn id="5" xr3:uid="{4C8345F1-6E01-4566-9030-039665486C03}" uniqueName="5" name="SETOR" queryTableFieldId="5" dataDxfId="65"/>
+    <tableColumn id="9" xr3:uid="{10436F87-F6F1-46C4-A81A-8D144AC72FDF}" uniqueName="9" name="EMPRESA" queryTableFieldId="16389" dataDxfId="64"/>
+    <tableColumn id="13" xr3:uid="{40F07CF2-DF5F-4979-A5BB-71FA79C89740}" uniqueName="13" name="GRUPO" queryTableFieldId="16393" dataDxfId="63"/>
+    <tableColumn id="6" xr3:uid="{B7941BA2-3E1C-476B-A3C7-BA155A35A2D0}" uniqueName="6" name="ATUALIZADO" queryTableFieldId="6" dataDxfId="62"/>
+    <tableColumn id="7" xr3:uid="{4338F703-CE4B-4443-8A10-74F64ED8CD42}" uniqueName="7" name="PRINTWAY" queryTableFieldId="16391" dataDxfId="61"/>
+    <tableColumn id="8" xr3:uid="{02B7C1FB-8EA9-4F22-BCCF-3D1809FFEDCC}" uniqueName="8" name="OBSERVAÇÃO" queryTableFieldId="8" dataDxfId="60"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5690,26 +5694,26 @@
     <tableColumn id="3" xr3:uid="{95A3DCD3-FE19-4A74-9940-661D6BB94B25}" name="MODELO"/>
     <tableColumn id="4" xr3:uid="{521C03E5-7FA9-4789-8198-9E0781F3ABC7}" name="DESCRIÇÃO"/>
     <tableColumn id="5" xr3:uid="{579D81F0-AA4C-4609-BF35-AF838B2B149B}" name="COR"/>
-    <tableColumn id="6" xr3:uid="{19487D13-EF31-43DA-89CA-4AA1E1029C34}" name="QUANTIDADE" dataDxfId="60"/>
+    <tableColumn id="6" xr3:uid="{19487D13-EF31-43DA-89CA-4AA1E1029C34}" name="QUANTIDADE" dataDxfId="59"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FBC7B6D1-65BC-435E-B4FF-CC495249D6BD}" name="Tabela4" displayName="Tabela4" ref="A1:J51" insertRowShift="1" totalsRowShown="0" headerRowDxfId="59" dataDxfId="58">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FBC7B6D1-65BC-435E-B4FF-CC495249D6BD}" name="Tabela4" displayName="Tabela4" ref="A1:J51" insertRowShift="1" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57">
   <autoFilter ref="A1:J51" xr:uid="{FBC7B6D1-65BC-435E-B4FF-CC495249D6BD}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{A3ABFE90-9D3C-42DA-8CF0-D71D91CAB9BB}" name="INDICE" dataDxfId="57"/>
-    <tableColumn id="2" xr3:uid="{A733301C-FC8A-4542-8BA2-BBEA67F3D424}" name="MODELO" dataDxfId="56"/>
-    <tableColumn id="3" xr3:uid="{C6E07CD7-A3F4-4433-BB55-99FA29AE99FA}" name="TIPO" dataDxfId="55"/>
-    <tableColumn id="4" xr3:uid="{007A788B-09E3-480D-A6BC-6718BD4566C1}" name="SERIAL" dataDxfId="54"/>
-    <tableColumn id="5" xr3:uid="{ACA8BAA3-86EA-4046-9E8D-0C6E6216A0B1}" name="LOCALIDADE" dataDxfId="53"/>
-    <tableColumn id="6" xr3:uid="{D2E86C5C-2786-4CA5-9B36-02C6270BDE33}" name="SETOR" dataDxfId="52"/>
-    <tableColumn id="7" xr3:uid="{3F4C4914-DB98-431A-AD17-7760541C7F42}" name="EMPRESA" dataDxfId="51"/>
-    <tableColumn id="8" xr3:uid="{4F681722-ADFE-4A58-BC0F-8623348ECD33}" name="DATA" dataDxfId="50"/>
-    <tableColumn id="9" xr3:uid="{13FFF32F-FC49-429E-BD6E-76ADCE6F7534}" name="MONIT." dataDxfId="49"/>
-    <tableColumn id="10" xr3:uid="{F4255CFF-6FAD-434F-93D8-3A0C54269527}" name="DETALHES" dataDxfId="48"/>
+    <tableColumn id="1" xr3:uid="{A3ABFE90-9D3C-42DA-8CF0-D71D91CAB9BB}" name="INDICE" dataDxfId="56"/>
+    <tableColumn id="2" xr3:uid="{A733301C-FC8A-4542-8BA2-BBEA67F3D424}" name="MODELO" dataDxfId="55"/>
+    <tableColumn id="3" xr3:uid="{C6E07CD7-A3F4-4433-BB55-99FA29AE99FA}" name="TIPO" dataDxfId="54"/>
+    <tableColumn id="4" xr3:uid="{007A788B-09E3-480D-A6BC-6718BD4566C1}" name="SERIAL" dataDxfId="53"/>
+    <tableColumn id="5" xr3:uid="{ACA8BAA3-86EA-4046-9E8D-0C6E6216A0B1}" name="LOCALIDADE" dataDxfId="52"/>
+    <tableColumn id="6" xr3:uid="{D2E86C5C-2786-4CA5-9B36-02C6270BDE33}" name="SETOR" dataDxfId="51"/>
+    <tableColumn id="7" xr3:uid="{3F4C4914-DB98-431A-AD17-7760541C7F42}" name="EMPRESA" dataDxfId="50"/>
+    <tableColumn id="8" xr3:uid="{4F681722-ADFE-4A58-BC0F-8623348ECD33}" name="DATA" dataDxfId="49"/>
+    <tableColumn id="9" xr3:uid="{13FFF32F-FC49-429E-BD6E-76ADCE6F7534}" name="MONIT." dataDxfId="48"/>
+    <tableColumn id="10" xr3:uid="{F4255CFF-6FAD-434F-93D8-3A0C54269527}" name="DETALHES" dataDxfId="47"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -21162,7 +21166,7 @@
         <v>11</v>
       </c>
       <c r="D453" s="2" t="s">
-        <v>1428</v>
+        <v>1463</v>
       </c>
       <c r="E453" s="1" t="s">
         <v>76</v>
@@ -21195,22 +21199,22 @@
         <v>11</v>
       </c>
       <c r="D454" s="2" t="s">
-        <v>1357</v>
+        <v>1464</v>
       </c>
       <c r="E454" s="1" t="s">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="F454" s="1" t="s">
-        <v>521</v>
+        <v>1466</v>
       </c>
       <c r="G454" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H454" s="1" t="s">
-        <v>1358</v>
+        <v>1341</v>
       </c>
       <c r="I454" s="54">
-        <v>46279</v>
+        <v>44854</v>
       </c>
       <c r="J454" s="4" t="s">
         <v>574</v>
@@ -21228,22 +21232,22 @@
         <v>11</v>
       </c>
       <c r="D455" s="2" t="s">
-        <v>1357</v>
+        <v>1465</v>
       </c>
       <c r="E455" s="1" t="s">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="F455" s="1" t="s">
-        <v>521</v>
+        <v>1467</v>
       </c>
       <c r="G455" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H455" s="1" t="s">
-        <v>1358</v>
+        <v>1341</v>
       </c>
       <c r="I455" s="54">
-        <v>46279</v>
+        <v>46315</v>
       </c>
       <c r="J455" s="4" t="s">
         <v>574</v>
@@ -25414,7 +25418,7 @@
       <c r="J579" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="K579" s="59"/>
+      <c r="K579" s="55"/>
     </row>
     <row r="580" spans="1:11">
       <c r="A580" s="4">
@@ -25447,7 +25451,7 @@
       <c r="J580" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="K580" s="59"/>
+      <c r="K580" s="55"/>
     </row>
     <row r="581" spans="1:11">
       <c r="A581" s="4">
@@ -25480,7 +25484,7 @@
       <c r="J581" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="K581" s="59"/>
+      <c r="K581" s="55"/>
     </row>
     <row r="582" spans="1:11">
       <c r="A582" s="4">
@@ -25513,7 +25517,7 @@
       <c r="J582" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="K582" s="59"/>
+      <c r="K582" s="55"/>
     </row>
     <row r="583" spans="1:11">
       <c r="A583" s="4">
@@ -25584,36 +25588,33 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="duplicateValues" dxfId="47" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D268">
-    <cfRule type="duplicateValues" dxfId="46" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D366">
-    <cfRule type="duplicateValues" dxfId="43" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D367">
-    <cfRule type="duplicateValues" dxfId="42" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="109"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D502 D2:D367">
-    <cfRule type="duplicateValues" dxfId="41" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:E258 G215 E525:E1048576">
-    <cfRule type="cellIs" dxfId="40" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="30" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E260:E524">
-    <cfRule type="cellIs" dxfId="39" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="26" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F254:F255 F561:F562 F257:F387 F564:F1048576 F1:F252 F389:F559">
-    <cfRule type="cellIs" dxfId="38" priority="22" operator="equal">
-      <formula>"MANUTENÇÃO"</formula>
-    </cfRule>
+  <conditionalFormatting sqref="F1:F252 F254:F255 F257:F387 F389:F559 F561:F562 F564:F1048576">
     <cfRule type="cellIs" dxfId="37" priority="23" operator="equal">
       <formula>"DOADORA"</formula>
     </cfRule>
@@ -25623,73 +25624,77 @@
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F1:F252 F389:F559 F254:F255 F257:F387 F561:F562 F564:F1048576">
+    <cfRule type="cellIs" dxfId="35" priority="22" operator="equal">
+      <formula>"MANUTENÇÃO"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F1:F252">
-    <cfRule type="cellIs" dxfId="35" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="2" operator="equal">
       <formula>"DEPOSITO SOLAGOS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F18">
-    <cfRule type="cellIs" dxfId="34" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="6" operator="equal">
+      <formula>"MANUTENÇÃO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25">
+    <cfRule type="cellIs" dxfId="32" priority="1" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F254:F255 F561:F562 F564:F1048576">
-    <cfRule type="cellIs" dxfId="33" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="32" operator="equal">
       <formula>"DEPOSITO SOLAGOS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F257:F387 F389:F559">
-    <cfRule type="cellIs" dxfId="32" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="27" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="28" operator="equal">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F257:F387">
+    <cfRule type="cellIs" dxfId="29" priority="28" operator="equal">
       <formula>"DEPOSITO SOLAGOS"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H1:H230 H252:H258 H232:H250">
-    <cfRule type="cellIs" dxfId="30" priority="5" operator="equal">
+  <conditionalFormatting sqref="F389:F559">
+    <cfRule type="cellIs" dxfId="28" priority="4" operator="equal">
+      <formula>"DEPOSITO SOLAGOS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F555">
+    <cfRule type="cellIs" dxfId="27" priority="3" operator="equal">
+      <formula>"MANUTENÇÃO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1:H258">
+    <cfRule type="cellIs" dxfId="26" priority="5" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H260:H524 H251 H231">
-    <cfRule type="cellIs" dxfId="29" priority="9" operator="equal">
+  <conditionalFormatting sqref="H260:H524">
+    <cfRule type="cellIs" dxfId="25" priority="9" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H526:H584">
-    <cfRule type="cellIs" dxfId="28" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="13" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K215">
-    <cfRule type="cellIs" dxfId="27" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="17" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="18" operator="equal">
       <formula>"DOADORA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="19" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="20" operator="equal">
-      <formula>"DEPOSITO SOLAGOS"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F555">
-    <cfRule type="cellIs" dxfId="23" priority="3" operator="equal">
-      <formula>"MANUTENÇÃO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F555">
-    <cfRule type="cellIs" dxfId="22" priority="4" operator="equal">
-      <formula>"DEPOSITO SOLAGOS"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F25">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
-      <formula>"MANUTENÇÃO"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="20" operator="equal">
       <formula>"DEPOSITO SOLAGOS"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28088,51 +28093,51 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="D2:D51">
-    <cfRule type="duplicateValues" dxfId="21" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D52">
-    <cfRule type="duplicateValues" dxfId="20" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D53">
-    <cfRule type="duplicateValues" dxfId="19" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E51">
-    <cfRule type="cellIs" dxfId="16" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="16" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E52:E53">
-    <cfRule type="cellIs" dxfId="15" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="5" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F51">
-    <cfRule type="cellIs" dxfId="14" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="17" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="18" operator="equal">
       <formula>"DOADORA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="20" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="21" operator="equal">
       <formula>"DEPOSITO SOLAGOS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F52:F53">
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
       <formula>"DOADORA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="8" operator="equal">
       <formula>"DEPOSITO SOLAGOS"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28293,21 +28298,21 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
-    <cfRule type="cellIs" dxfId="6" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="23" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B8">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"DOADORA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"DEPOSITO SOLAGOS"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/data_printer.xlsx
+++ b/data_printer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erick\Desktop\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{026F155A-2F18-4AAB-B29F-233B4FC32608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E77478D-A735-4341-A59E-918972BD96BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A8AA41B5-7AA1-4FF7-A9B8-54B8A4E1AF28}"/>
   </bookViews>
@@ -3950,9 +3950,6 @@
     <t xml:space="preserve">ESTAVA NA PROG 2 - PAÇO; ESTAVA NO DARCY RIBEIRO; RETIRADA MAESTRO KIKO ERRO 673-10  23/10/2025; TROCA DE UNIDADE DE IMAGEM CILINDRO LAMINA DE LIMPEZA PRC ROLO TRANSMISSOR FUSÃO ROLETES 23/10/2025; INSTALADA NO UNNOMED -SPA 24/10/2025; </t>
   </si>
   <si>
-    <t>BATALHAO 42º</t>
-  </si>
-  <si>
     <t>PROBLEMA NA UNIDADE DE FUSÃO; RETIRADA PAIVA MACHARETE 10/06/2026; INSTALADA NA 42º BATALHAO ARARUAMA 05/08/2026;</t>
   </si>
   <si>
@@ -4169,15 +4166,9 @@
     <t xml:space="preserve">Impressora foi danificada por deixar impressora na sala sem telhado onde choveu e queimou a mesma, </t>
   </si>
   <si>
-    <t>após quedas de energia  a impressora queimou na unidade.</t>
-  </si>
-  <si>
     <t>ESTAVA FMAS TESOURARIA; COLOCADA SEDUC RH 01/08/2025; RETIRADA DA SEDUC RH 16/04/2026; INSTALADA NA ESCOLA Afranio Valladares para;</t>
   </si>
   <si>
-    <t xml:space="preserve">impressora danificada por travamento na cabeça de impressao assim arrebentado a correia de tracionamento; </t>
-  </si>
-  <si>
     <t>RICOH M 320F</t>
   </si>
   <si>
@@ -4452,6 +4443,15 @@
   </si>
   <si>
     <t>UBS - PARACATU</t>
+  </si>
+  <si>
+    <t>impressora danificada por travamento na cabeça de impressao assim arrebentado a correia de tracionamento cabeça de impreção Darcy Ribeiro;</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> após quedas de energia  a impressora queimou na unidade de placa AFranio Valladares.</t>
+  </si>
+  <si>
+    <t>LOCACAO</t>
   </si>
 </sst>
 </file>
@@ -4826,7 +4826,37 @@
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="73">
+  <dxfs count="76">
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -5663,23 +5693,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}" name="Controle_Inventario_Impressoras" displayName="Controle_Inventario_Impressoras" ref="A1:K584" tableType="queryTable" totalsRowShown="0" headerRowDxfId="72" dataDxfId="71">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}" name="Controle_Inventario_Impressoras" displayName="Controle_Inventario_Impressoras" ref="A1:K584" tableType="queryTable" totalsRowShown="0" headerRowDxfId="75" dataDxfId="74">
   <autoFilter ref="A1:K584" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K37">
     <sortCondition ref="A23"/>
   </sortState>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F8E3D681-C494-47F2-8429-052381C12AF1}" uniqueName="1" name="INDICE" queryTableFieldId="1" dataDxfId="70"/>
-    <tableColumn id="2" xr3:uid="{EE2E8FA5-A99D-4573-9868-408DB8FD4417}" uniqueName="2" name="MODELO" queryTableFieldId="2" dataDxfId="69"/>
-    <tableColumn id="11" xr3:uid="{CB5196C0-CCA1-4329-825F-D71E0948A542}" uniqueName="11" name="TIPO" queryTableFieldId="16390" dataDxfId="68"/>
-    <tableColumn id="3" xr3:uid="{27BC8F35-CC2C-44A1-BAF7-B0390B09477F}" uniqueName="3" name="NUMERO DE SERIE" queryTableFieldId="3" dataDxfId="67"/>
-    <tableColumn id="4" xr3:uid="{552F7A6E-6277-4DC1-9CDA-EA7FDCCE8E36}" uniqueName="4" name="LOCALIZAÇÃO" queryTableFieldId="4" dataDxfId="66"/>
-    <tableColumn id="5" xr3:uid="{4C8345F1-6E01-4566-9030-039665486C03}" uniqueName="5" name="SETOR" queryTableFieldId="5" dataDxfId="65"/>
-    <tableColumn id="9" xr3:uid="{10436F87-F6F1-46C4-A81A-8D144AC72FDF}" uniqueName="9" name="EMPRESA" queryTableFieldId="16389" dataDxfId="64"/>
-    <tableColumn id="13" xr3:uid="{40F07CF2-DF5F-4979-A5BB-71FA79C89740}" uniqueName="13" name="GRUPO" queryTableFieldId="16393" dataDxfId="63"/>
-    <tableColumn id="6" xr3:uid="{B7941BA2-3E1C-476B-A3C7-BA155A35A2D0}" uniqueName="6" name="ATUALIZADO" queryTableFieldId="6" dataDxfId="62"/>
-    <tableColumn id="7" xr3:uid="{4338F703-CE4B-4443-8A10-74F64ED8CD42}" uniqueName="7" name="PRINTWAY" queryTableFieldId="16391" dataDxfId="61"/>
-    <tableColumn id="8" xr3:uid="{02B7C1FB-8EA9-4F22-BCCF-3D1809FFEDCC}" uniqueName="8" name="OBSERVAÇÃO" queryTableFieldId="8" dataDxfId="60"/>
+    <tableColumn id="1" xr3:uid="{F8E3D681-C494-47F2-8429-052381C12AF1}" uniqueName="1" name="INDICE" queryTableFieldId="1" dataDxfId="73"/>
+    <tableColumn id="2" xr3:uid="{EE2E8FA5-A99D-4573-9868-408DB8FD4417}" uniqueName="2" name="MODELO" queryTableFieldId="2" dataDxfId="72"/>
+    <tableColumn id="11" xr3:uid="{CB5196C0-CCA1-4329-825F-D71E0948A542}" uniqueName="11" name="TIPO" queryTableFieldId="16390" dataDxfId="71"/>
+    <tableColumn id="3" xr3:uid="{27BC8F35-CC2C-44A1-BAF7-B0390B09477F}" uniqueName="3" name="NUMERO DE SERIE" queryTableFieldId="3" dataDxfId="70"/>
+    <tableColumn id="4" xr3:uid="{552F7A6E-6277-4DC1-9CDA-EA7FDCCE8E36}" uniqueName="4" name="LOCALIZAÇÃO" queryTableFieldId="4" dataDxfId="69"/>
+    <tableColumn id="5" xr3:uid="{4C8345F1-6E01-4566-9030-039665486C03}" uniqueName="5" name="SETOR" queryTableFieldId="5" dataDxfId="68"/>
+    <tableColumn id="9" xr3:uid="{10436F87-F6F1-46C4-A81A-8D144AC72FDF}" uniqueName="9" name="EMPRESA" queryTableFieldId="16389" dataDxfId="67"/>
+    <tableColumn id="13" xr3:uid="{40F07CF2-DF5F-4979-A5BB-71FA79C89740}" uniqueName="13" name="GRUPO" queryTableFieldId="16393" dataDxfId="66"/>
+    <tableColumn id="6" xr3:uid="{B7941BA2-3E1C-476B-A3C7-BA155A35A2D0}" uniqueName="6" name="ATUALIZADO" queryTableFieldId="6" dataDxfId="65"/>
+    <tableColumn id="7" xr3:uid="{4338F703-CE4B-4443-8A10-74F64ED8CD42}" uniqueName="7" name="PRINTWAY" queryTableFieldId="16391" dataDxfId="64"/>
+    <tableColumn id="8" xr3:uid="{02B7C1FB-8EA9-4F22-BCCF-3D1809FFEDCC}" uniqueName="8" name="OBSERVAÇÃO" queryTableFieldId="8" dataDxfId="63"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5694,26 +5724,26 @@
     <tableColumn id="3" xr3:uid="{95A3DCD3-FE19-4A74-9940-661D6BB94B25}" name="MODELO"/>
     <tableColumn id="4" xr3:uid="{521C03E5-7FA9-4789-8198-9E0781F3ABC7}" name="DESCRIÇÃO"/>
     <tableColumn id="5" xr3:uid="{579D81F0-AA4C-4609-BF35-AF838B2B149B}" name="COR"/>
-    <tableColumn id="6" xr3:uid="{19487D13-EF31-43DA-89CA-4AA1E1029C34}" name="QUANTIDADE" dataDxfId="59"/>
+    <tableColumn id="6" xr3:uid="{19487D13-EF31-43DA-89CA-4AA1E1029C34}" name="QUANTIDADE" dataDxfId="62"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FBC7B6D1-65BC-435E-B4FF-CC495249D6BD}" name="Tabela4" displayName="Tabela4" ref="A1:J51" insertRowShift="1" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FBC7B6D1-65BC-435E-B4FF-CC495249D6BD}" name="Tabela4" displayName="Tabela4" ref="A1:J51" insertRowShift="1" totalsRowShown="0" headerRowDxfId="61" dataDxfId="60">
   <autoFilter ref="A1:J51" xr:uid="{FBC7B6D1-65BC-435E-B4FF-CC495249D6BD}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{A3ABFE90-9D3C-42DA-8CF0-D71D91CAB9BB}" name="INDICE" dataDxfId="56"/>
-    <tableColumn id="2" xr3:uid="{A733301C-FC8A-4542-8BA2-BBEA67F3D424}" name="MODELO" dataDxfId="55"/>
-    <tableColumn id="3" xr3:uid="{C6E07CD7-A3F4-4433-BB55-99FA29AE99FA}" name="TIPO" dataDxfId="54"/>
-    <tableColumn id="4" xr3:uid="{007A788B-09E3-480D-A6BC-6718BD4566C1}" name="SERIAL" dataDxfId="53"/>
-    <tableColumn id="5" xr3:uid="{ACA8BAA3-86EA-4046-9E8D-0C6E6216A0B1}" name="LOCALIDADE" dataDxfId="52"/>
-    <tableColumn id="6" xr3:uid="{D2E86C5C-2786-4CA5-9B36-02C6270BDE33}" name="SETOR" dataDxfId="51"/>
-    <tableColumn id="7" xr3:uid="{3F4C4914-DB98-431A-AD17-7760541C7F42}" name="EMPRESA" dataDxfId="50"/>
-    <tableColumn id="8" xr3:uid="{4F681722-ADFE-4A58-BC0F-8623348ECD33}" name="DATA" dataDxfId="49"/>
-    <tableColumn id="9" xr3:uid="{13FFF32F-FC49-429E-BD6E-76ADCE6F7534}" name="MONIT." dataDxfId="48"/>
-    <tableColumn id="10" xr3:uid="{F4255CFF-6FAD-434F-93D8-3A0C54269527}" name="DETALHES" dataDxfId="47"/>
+    <tableColumn id="1" xr3:uid="{A3ABFE90-9D3C-42DA-8CF0-D71D91CAB9BB}" name="INDICE" dataDxfId="59"/>
+    <tableColumn id="2" xr3:uid="{A733301C-FC8A-4542-8BA2-BBEA67F3D424}" name="MODELO" dataDxfId="58"/>
+    <tableColumn id="3" xr3:uid="{C6E07CD7-A3F4-4433-BB55-99FA29AE99FA}" name="TIPO" dataDxfId="57"/>
+    <tableColumn id="4" xr3:uid="{007A788B-09E3-480D-A6BC-6718BD4566C1}" name="SERIAL" dataDxfId="56"/>
+    <tableColumn id="5" xr3:uid="{ACA8BAA3-86EA-4046-9E8D-0C6E6216A0B1}" name="LOCALIDADE" dataDxfId="55"/>
+    <tableColumn id="6" xr3:uid="{D2E86C5C-2786-4CA5-9B36-02C6270BDE33}" name="SETOR" dataDxfId="54"/>
+    <tableColumn id="7" xr3:uid="{3F4C4914-DB98-431A-AD17-7760541C7F42}" name="EMPRESA" dataDxfId="53"/>
+    <tableColumn id="8" xr3:uid="{4F681722-ADFE-4A58-BC0F-8623348ECD33}" name="DATA" dataDxfId="52"/>
+    <tableColumn id="9" xr3:uid="{13FFF32F-FC49-429E-BD6E-76ADCE6F7534}" name="MONIT." dataDxfId="51"/>
+    <tableColumn id="10" xr3:uid="{F4255CFF-6FAD-434F-93D8-3A0C54269527}" name="DETALHES" dataDxfId="50"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6056,7 +6086,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>7</v>
@@ -6238,13 +6268,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>1376</v>
+        <v>1373</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>21</v>
@@ -6256,7 +6286,7 @@
         <v>14</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I7" s="54">
         <v>46282</v>
@@ -6271,13 +6301,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>1376</v>
+        <v>1373</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>21</v>
@@ -6289,7 +6319,7 @@
         <v>14</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I8" s="54">
         <v>46282</v>
@@ -6304,13 +6334,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>1376</v>
+        <v>1373</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>21</v>
@@ -6322,7 +6352,7 @@
         <v>14</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I9" s="54">
         <v>46282</v>
@@ -6337,13 +6367,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>1376</v>
+        <v>1373</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>21</v>
@@ -6355,7 +6385,7 @@
         <v>14</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I10" s="54">
         <v>46282</v>
@@ -6370,13 +6400,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>1376</v>
+        <v>1373</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>21</v>
@@ -6388,7 +6418,7 @@
         <v>14</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I11" s="54">
         <v>46282</v>
@@ -6403,13 +6433,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>1376</v>
+        <v>1373</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>21</v>
@@ -6421,7 +6451,7 @@
         <v>14</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I12" s="54">
         <v>46282</v>
@@ -6436,13 +6466,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>1376</v>
+        <v>1373</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>21</v>
@@ -6454,7 +6484,7 @@
         <v>14</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I13" s="54">
         <v>46282</v>
@@ -6469,13 +6499,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>1376</v>
+        <v>1373</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>21</v>
@@ -6487,7 +6517,7 @@
         <v>14</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I14" s="54">
         <v>46282</v>
@@ -6502,13 +6532,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="30" t="s">
-        <v>1376</v>
+        <v>1373</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>21</v>
@@ -6520,7 +6550,7 @@
         <v>14</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I15" s="54">
         <v>46282</v>
@@ -6535,13 +6565,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="30" t="s">
-        <v>1376</v>
+        <v>1373</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>21</v>
@@ -6553,7 +6583,7 @@
         <v>14</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I16" s="54">
         <v>46282</v>
@@ -6619,7 +6649,7 @@
         <v>30</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="I18" s="6">
         <v>45797</v>
@@ -6716,7 +6746,7 @@
         <v>19</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
       <c r="I21" s="9">
         <v>45575</v>
@@ -6745,13 +6775,13 @@
         <v>854</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>19</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
       <c r="I22" s="9">
         <v>45950</v>
@@ -6819,7 +6849,7 @@
         <v>14</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="I24" s="9">
         <v>45964</v>
@@ -6854,7 +6884,7 @@
         <v>30</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="I25" s="9">
         <v>45545</v>
@@ -7018,7 +7048,7 @@
         <v>14</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I30" s="9">
         <v>45941</v>
@@ -7467,16 +7497,16 @@
         <v>78</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>1300</v>
+        <v>23</v>
       </c>
       <c r="G44" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>1339</v>
+        <v>1467</v>
       </c>
       <c r="I44" s="9">
         <v>45733</v>
@@ -7485,7 +7515,7 @@
         <v>574</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -8060,7 +8090,7 @@
         <v>68</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
       <c r="I62" s="15">
         <v>45897</v>
@@ -8095,7 +8125,7 @@
         <v>68</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
       <c r="I63" s="9">
         <v>45897</v>
@@ -8130,7 +8160,7 @@
         <v>68</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
       <c r="I64" s="23">
         <v>45950</v>
@@ -8153,7 +8183,7 @@
         <v>11</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>21</v>
@@ -8648,7 +8678,7 @@
         <v>11</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>21</v>
@@ -8690,7 +8720,7 @@
         <v>14</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I82" s="9">
         <v>45953</v>
@@ -9166,7 +9196,7 @@
         <v>30</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="I97" s="9">
         <v>45707</v>
@@ -9447,7 +9477,7 @@
         <v>14</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="I106" s="9">
         <v>45653</v>
@@ -9539,7 +9569,7 @@
         <v>14</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>1438</v>
+        <v>1435</v>
       </c>
       <c r="I109" s="9">
         <v>45652</v>
@@ -9640,7 +9670,7 @@
         <v>14</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="I112" s="9">
         <v>45966</v>
@@ -10364,7 +10394,7 @@
         <v>30</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="I134" s="9">
         <v>45744</v>
@@ -10399,7 +10429,7 @@
         <v>14</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="I135" s="9">
         <v>45797</v>
@@ -10434,7 +10464,7 @@
         <v>30</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I136" s="9">
         <v>45614</v>
@@ -10634,7 +10664,7 @@
         <v>14</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I142" s="9">
         <v>45870</v>
@@ -10669,7 +10699,7 @@
         <v>14</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I143" s="9">
         <v>46038</v>
@@ -10704,7 +10734,7 @@
         <v>14</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I144" s="9">
         <v>45936</v>
@@ -10772,7 +10802,7 @@
         <v>14</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I146" s="9">
         <v>45936</v>
@@ -11005,7 +11035,7 @@
         <v>68</v>
       </c>
       <c r="H153" s="1" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
       <c r="I153" s="23">
         <v>46156</v>
@@ -11038,7 +11068,7 @@
         <v>14</v>
       </c>
       <c r="H154" s="1" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="I154" s="9">
         <v>45600</v>
@@ -11073,7 +11103,7 @@
         <v>14</v>
       </c>
       <c r="H155" s="1" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="I155" s="9">
         <v>46031</v>
@@ -11108,7 +11138,7 @@
         <v>14</v>
       </c>
       <c r="H156" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="I156" s="15">
         <v>45714</v>
@@ -11143,7 +11173,7 @@
         <v>14</v>
       </c>
       <c r="H157" s="4" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="I157" s="15">
         <v>45742</v>
@@ -11178,7 +11208,7 @@
         <v>14</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="I158" s="15">
         <v>45905</v>
@@ -11213,7 +11243,7 @@
         <v>14</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="I159" s="15">
         <v>45867</v>
@@ -11248,7 +11278,7 @@
         <v>14</v>
       </c>
       <c r="H160" s="4" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="I160" s="23">
         <v>46162</v>
@@ -11283,7 +11313,7 @@
         <v>14</v>
       </c>
       <c r="H161" s="4" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="I161" s="23">
         <v>46164</v>
@@ -11318,7 +11348,7 @@
         <v>14</v>
       </c>
       <c r="H162" s="4" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="I162" s="23">
         <v>46154</v>
@@ -11351,7 +11381,7 @@
         <v>14</v>
       </c>
       <c r="H163" s="4" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="I163" s="23">
         <v>46154</v>
@@ -11384,7 +11414,7 @@
         <v>14</v>
       </c>
       <c r="H164" s="4" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="I164" s="23">
         <v>46150</v>
@@ -11419,7 +11449,7 @@
         <v>14</v>
       </c>
       <c r="H165" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="I165" s="23">
         <v>46930</v>
@@ -11454,7 +11484,7 @@
         <v>14</v>
       </c>
       <c r="H166" s="1" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="I166" s="23">
         <v>46930</v>
@@ -11489,7 +11519,7 @@
         <v>14</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="I167" s="9">
         <v>46211</v>
@@ -11512,19 +11542,19 @@
         <v>83</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="G168" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="I168" s="54">
         <v>46248</v>
@@ -11656,7 +11686,7 @@
         <v>14</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="I172" s="9">
         <v>45643</v>
@@ -11757,7 +11787,7 @@
         <v>14</v>
       </c>
       <c r="H175" s="4" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="I175" s="9">
         <v>45959</v>
@@ -11880,7 +11910,7 @@
         <v>14</v>
       </c>
       <c r="H179" s="1" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="I179" s="9">
         <v>45698</v>
@@ -12228,7 +12258,7 @@
         <v>14</v>
       </c>
       <c r="H190" s="1" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="I190" s="9">
         <v>45653</v>
@@ -12356,7 +12386,7 @@
         <v>14</v>
       </c>
       <c r="H194" s="1" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="I194" s="9">
         <v>45687</v>
@@ -12388,7 +12418,7 @@
         <v>14</v>
       </c>
       <c r="H195" s="1" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="I195" s="9">
         <v>45687</v>
@@ -12420,7 +12450,7 @@
         <v>14</v>
       </c>
       <c r="H196" s="1" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="I196" s="9">
         <v>45687</v>
@@ -12452,7 +12482,7 @@
         <v>14</v>
       </c>
       <c r="H197" s="1" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="I197" s="9">
         <v>45687</v>
@@ -12484,7 +12514,7 @@
         <v>14</v>
       </c>
       <c r="H198" s="1" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="I198" s="9">
         <v>45687</v>
@@ -12516,7 +12546,7 @@
         <v>14</v>
       </c>
       <c r="H199" s="1" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="I199" s="9">
         <v>45687</v>
@@ -12548,7 +12578,7 @@
         <v>14</v>
       </c>
       <c r="H200" s="1" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="I200" s="9">
         <v>45687</v>
@@ -12580,7 +12610,7 @@
         <v>14</v>
       </c>
       <c r="H201" s="1" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="I201" s="9">
         <v>45687</v>
@@ -12612,7 +12642,7 @@
         <v>14</v>
       </c>
       <c r="H202" s="1" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="I202" s="9">
         <v>45687</v>
@@ -12644,7 +12674,7 @@
         <v>14</v>
       </c>
       <c r="H203" s="1" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="I203" s="9">
         <v>45687</v>
@@ -12676,7 +12706,7 @@
         <v>14</v>
       </c>
       <c r="H204" s="1" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="I204" s="9">
         <v>45687</v>
@@ -12708,7 +12738,7 @@
         <v>14</v>
       </c>
       <c r="H205" s="1" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="I205" s="9">
         <v>45687</v>
@@ -12740,7 +12770,7 @@
         <v>14</v>
       </c>
       <c r="H206" s="1" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="I206" s="9">
         <v>45687</v>
@@ -12772,7 +12802,7 @@
         <v>14</v>
       </c>
       <c r="H207" s="1" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="I207" s="9">
         <v>45687</v>
@@ -12804,7 +12834,7 @@
         <v>14</v>
       </c>
       <c r="H208" s="1" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="I208" s="9">
         <v>45687</v>
@@ -12836,7 +12866,7 @@
         <v>14</v>
       </c>
       <c r="H209" s="1" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="I209" s="9">
         <v>45687</v>
@@ -12868,7 +12898,7 @@
         <v>14</v>
       </c>
       <c r="H210" s="1" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="I210" s="9">
         <v>45687</v>
@@ -12900,7 +12930,7 @@
         <v>14</v>
       </c>
       <c r="H211" s="1" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="I211" s="9">
         <v>45687</v>
@@ -12932,7 +12962,7 @@
         <v>14</v>
       </c>
       <c r="H212" s="1" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="I212" s="9">
         <v>45687</v>
@@ -12964,7 +12994,7 @@
         <v>14</v>
       </c>
       <c r="H213" s="1" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="I213" s="9">
         <v>45687</v>
@@ -12996,7 +13026,7 @@
         <v>14</v>
       </c>
       <c r="H214" s="1" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="I214" s="9">
         <v>45687</v>
@@ -13028,7 +13058,7 @@
         <v>14</v>
       </c>
       <c r="H215" s="1" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="I215" s="9">
         <v>45687</v>
@@ -13063,7 +13093,7 @@
         <v>14</v>
       </c>
       <c r="H216" s="1" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="I216" s="9">
         <v>45652</v>
@@ -13294,7 +13324,7 @@
         <v>14</v>
       </c>
       <c r="H223" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I223" s="9">
         <v>45649</v>
@@ -13356,13 +13386,13 @@
         <v>68</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="G225" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H225" s="4" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I225" s="9">
         <v>45714</v>
@@ -13371,7 +13401,7 @@
         <v>574</v>
       </c>
       <c r="K225" s="3" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="226" spans="1:11">
@@ -13397,7 +13427,7 @@
         <v>30</v>
       </c>
       <c r="H226" s="1" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="I226" s="9">
         <v>45707</v>
@@ -13498,7 +13528,7 @@
         <v>14</v>
       </c>
       <c r="H229" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I229" s="9">
         <v>45873</v>
@@ -13533,7 +13563,7 @@
         <v>14</v>
       </c>
       <c r="H230" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I230" s="9">
         <v>45936</v>
@@ -13568,7 +13598,7 @@
         <v>14</v>
       </c>
       <c r="H231" s="1" t="s">
-        <v>1459</v>
+        <v>1456</v>
       </c>
       <c r="I231" s="9">
         <v>45942</v>
@@ -13801,7 +13831,7 @@
         <v>14</v>
       </c>
       <c r="H238" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I238" s="9">
         <v>45932</v>
@@ -13869,7 +13899,7 @@
         <v>14</v>
       </c>
       <c r="H240" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I240" s="9">
         <v>45933</v>
@@ -13937,7 +13967,7 @@
         <v>14</v>
       </c>
       <c r="H242" s="1" t="s">
-        <v>1436</v>
+        <v>1433</v>
       </c>
       <c r="I242" s="9">
         <v>45636</v>
@@ -14038,7 +14068,7 @@
         <v>14</v>
       </c>
       <c r="H245" s="4" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="I245" s="9">
         <v>46164</v>
@@ -14106,7 +14136,7 @@
         <v>14</v>
       </c>
       <c r="H247" s="1" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="I247" s="9">
         <v>45791</v>
@@ -14240,7 +14270,7 @@
         <v>14</v>
       </c>
       <c r="H251" s="1" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="I251" s="6">
         <v>45955</v>
@@ -14275,7 +14305,7 @@
         <v>14</v>
       </c>
       <c r="H252" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I252" s="6">
         <v>45665</v>
@@ -14310,7 +14340,7 @@
         <v>14</v>
       </c>
       <c r="H253" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I253" s="6">
         <v>46055</v>
@@ -14345,7 +14375,7 @@
         <v>14</v>
       </c>
       <c r="H254" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I254" s="9">
         <v>44127</v>
@@ -14380,7 +14410,7 @@
         <v>14</v>
       </c>
       <c r="H255" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I255" s="9">
         <v>45870</v>
@@ -14415,7 +14445,7 @@
         <v>14</v>
       </c>
       <c r="H256" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I256" s="6">
         <v>46085</v>
@@ -14450,7 +14480,7 @@
         <v>14</v>
       </c>
       <c r="H257" s="1" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="I257" s="15">
         <v>45705</v>
@@ -14510,7 +14540,7 @@
         <v>854</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="G259" s="13" t="s">
         <v>14</v>
@@ -14543,13 +14573,13 @@
         <v>68</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="G260" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H260" s="1" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="I260" s="9">
         <v>45652</v>
@@ -14558,7 +14588,7 @@
         <v>574</v>
       </c>
       <c r="K260" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="261" spans="1:11">
@@ -14584,7 +14614,7 @@
         <v>14</v>
       </c>
       <c r="H261" s="1" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="I261" s="9">
         <v>45870</v>
@@ -14593,7 +14623,7 @@
         <v>574</v>
       </c>
       <c r="K261" s="3" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="262" spans="1:11">
@@ -14619,7 +14649,7 @@
         <v>14</v>
       </c>
       <c r="H262" s="1" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="I262" s="9">
         <v>45917</v>
@@ -14628,7 +14658,7 @@
         <v>574</v>
       </c>
       <c r="K262" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="263" spans="1:11">
@@ -14711,7 +14741,7 @@
         <v>854</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="G265" s="4" t="s">
         <v>14</v>
@@ -15005,7 +15035,7 @@
         <v>14</v>
       </c>
       <c r="H274" s="4" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="I274" s="9">
         <v>46167</v>
@@ -15040,7 +15070,7 @@
         <v>14</v>
       </c>
       <c r="H275" s="4" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="I275" s="9">
         <v>46164</v>
@@ -15405,7 +15435,7 @@
         <v>14</v>
       </c>
       <c r="H286" s="1" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="I286" s="9">
         <v>45698</v>
@@ -15539,7 +15569,7 @@
         <v>14</v>
       </c>
       <c r="H290" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I290" s="9">
         <v>45763</v>
@@ -15574,7 +15604,7 @@
         <v>14</v>
       </c>
       <c r="H291" s="1" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="I291" s="9">
         <v>45590</v>
@@ -15609,7 +15639,7 @@
         <v>14</v>
       </c>
       <c r="H292" s="1" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I292" s="9">
         <v>45832</v>
@@ -15644,7 +15674,7 @@
         <v>14</v>
       </c>
       <c r="H293" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="I293" s="9">
         <v>45590</v>
@@ -15679,7 +15709,7 @@
         <v>14</v>
       </c>
       <c r="H294" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="I294" s="9">
         <v>45588</v>
@@ -15714,7 +15744,7 @@
         <v>14</v>
       </c>
       <c r="H295" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="I295" s="9">
         <v>45588</v>
@@ -15749,7 +15779,7 @@
         <v>14</v>
       </c>
       <c r="H296" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="I296" s="9">
         <v>45594</v>
@@ -15784,7 +15814,7 @@
         <v>14</v>
       </c>
       <c r="H297" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="I297" s="9">
         <v>45594</v>
@@ -15819,7 +15849,7 @@
         <v>14</v>
       </c>
       <c r="H298" s="1" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="I298" s="9">
         <v>45594</v>
@@ -15854,7 +15884,7 @@
         <v>14</v>
       </c>
       <c r="H299" s="1" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="I299" s="9">
         <v>45594</v>
@@ -15889,7 +15919,7 @@
         <v>14</v>
       </c>
       <c r="H300" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="I300" s="9">
         <v>45596</v>
@@ -15924,7 +15954,7 @@
         <v>14</v>
       </c>
       <c r="H301" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="I301" s="9">
         <v>45596</v>
@@ -15959,7 +15989,7 @@
         <v>14</v>
       </c>
       <c r="H302" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="I302" s="9">
         <v>45596</v>
@@ -15994,7 +16024,7 @@
         <v>14</v>
       </c>
       <c r="H303" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="I303" s="9">
         <v>45597</v>
@@ -16029,7 +16059,7 @@
         <v>14</v>
       </c>
       <c r="H304" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="I304" s="9">
         <v>45597</v>
@@ -16064,7 +16094,7 @@
         <v>14</v>
       </c>
       <c r="H305" s="1" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="I305" s="9">
         <v>45597</v>
@@ -16099,7 +16129,7 @@
         <v>14</v>
       </c>
       <c r="H306" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="I306" s="9">
         <v>45597</v>
@@ -16134,7 +16164,7 @@
         <v>14</v>
       </c>
       <c r="H307" s="1" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I307" s="9">
         <v>45603</v>
@@ -16169,7 +16199,7 @@
         <v>14</v>
       </c>
       <c r="H308" s="1" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="I308" s="9">
         <v>45603</v>
@@ -16204,7 +16234,7 @@
         <v>14</v>
       </c>
       <c r="H309" s="1" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="I309" s="9">
         <v>45604</v>
@@ -16239,7 +16269,7 @@
         <v>14</v>
       </c>
       <c r="H310" s="1" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="I310" s="9">
         <v>45607</v>
@@ -16274,7 +16304,7 @@
         <v>14</v>
       </c>
       <c r="H311" s="1" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="I311" s="9">
         <v>45607</v>
@@ -16309,7 +16339,7 @@
         <v>14</v>
       </c>
       <c r="H312" s="1" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="I312" s="9">
         <v>45607</v>
@@ -16344,7 +16374,7 @@
         <v>14</v>
       </c>
       <c r="H313" s="1" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="I313" s="9">
         <v>45614</v>
@@ -16379,7 +16409,7 @@
         <v>14</v>
       </c>
       <c r="H314" s="1" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="I314" s="9">
         <v>45614</v>
@@ -16414,7 +16444,7 @@
         <v>14</v>
       </c>
       <c r="H315" s="1" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="I315" s="9">
         <v>45615</v>
@@ -16449,7 +16479,7 @@
         <v>14</v>
       </c>
       <c r="H316" s="1" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="I316" s="9">
         <v>45615</v>
@@ -16484,7 +16514,7 @@
         <v>14</v>
       </c>
       <c r="H317" s="1" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="I317" s="9">
         <v>45615</v>
@@ -16519,7 +16549,7 @@
         <v>14</v>
       </c>
       <c r="H318" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I318" s="9">
         <v>45617</v>
@@ -16554,7 +16584,7 @@
         <v>14</v>
       </c>
       <c r="H319" s="1" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="I319" s="9">
         <v>45617</v>
@@ -16589,7 +16619,7 @@
         <v>14</v>
       </c>
       <c r="H320" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I320" s="9">
         <v>45618</v>
@@ -16624,7 +16654,7 @@
         <v>14</v>
       </c>
       <c r="H321" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I321" s="9">
         <v>45621</v>
@@ -16659,7 +16689,7 @@
         <v>14</v>
       </c>
       <c r="H322" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I322" s="9">
         <v>45621</v>
@@ -16694,7 +16724,7 @@
         <v>14</v>
       </c>
       <c r="H323" s="1" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="I323" s="9">
         <v>45618</v>
@@ -16729,7 +16759,7 @@
         <v>14</v>
       </c>
       <c r="H324" s="1" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="I324" s="9">
         <v>45618</v>
@@ -16764,7 +16794,7 @@
         <v>14</v>
       </c>
       <c r="H325" s="1" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="I325" s="9">
         <v>45618</v>
@@ -16799,7 +16829,7 @@
         <v>14</v>
       </c>
       <c r="H326" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="I326" s="9">
         <v>45621</v>
@@ -16834,7 +16864,7 @@
         <v>14</v>
       </c>
       <c r="H327" s="1" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="I327" s="9">
         <v>45622</v>
@@ -17034,7 +17064,7 @@
         <v>14</v>
       </c>
       <c r="H333" s="1" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="I333" s="9">
         <v>45867</v>
@@ -17168,7 +17198,7 @@
         <v>14</v>
       </c>
       <c r="H337" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="I337" s="9">
         <v>45667</v>
@@ -17203,7 +17233,7 @@
         <v>14</v>
       </c>
       <c r="H338" s="1" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="I338" s="9">
         <v>45842</v>
@@ -17238,7 +17268,7 @@
         <v>14</v>
       </c>
       <c r="H339" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="I339" s="9">
         <v>45702</v>
@@ -17343,7 +17373,7 @@
         <v>14</v>
       </c>
       <c r="H342" s="1" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="I342" s="9">
         <v>45705</v>
@@ -17378,7 +17408,7 @@
         <v>14</v>
       </c>
       <c r="H343" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="I343" s="9">
         <v>45726</v>
@@ -17413,7 +17443,7 @@
         <v>14</v>
       </c>
       <c r="H344" s="4" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I344" s="9">
         <v>45726</v>
@@ -17448,7 +17478,7 @@
         <v>14</v>
       </c>
       <c r="H345" s="4" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I345" s="9">
         <v>45726</v>
@@ -17483,7 +17513,7 @@
         <v>14</v>
       </c>
       <c r="H346" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="I346" s="9">
         <v>45653</v>
@@ -17518,7 +17548,7 @@
         <v>14</v>
       </c>
       <c r="H347" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="I347" s="9">
         <v>45817</v>
@@ -17553,7 +17583,7 @@
         <v>14</v>
       </c>
       <c r="H348" s="1" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="I348" s="9">
         <v>45653</v>
@@ -17588,7 +17618,7 @@
         <v>14</v>
       </c>
       <c r="H349" s="1" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="I349" s="9">
         <v>45844</v>
@@ -17623,7 +17653,7 @@
         <v>14</v>
       </c>
       <c r="H350" s="1" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="I350" s="9">
         <v>45838</v>
@@ -17658,7 +17688,7 @@
         <v>14</v>
       </c>
       <c r="H351" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="I351" s="9">
         <v>45842</v>
@@ -17693,7 +17723,7 @@
         <v>14</v>
       </c>
       <c r="H352" s="1" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="I352" s="9">
         <v>45852</v>
@@ -17728,7 +17758,7 @@
         <v>14</v>
       </c>
       <c r="H353" s="1" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="I353" s="9">
         <v>45853</v>
@@ -17763,7 +17793,7 @@
         <v>14</v>
       </c>
       <c r="H354" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="I354" s="9">
         <v>45870</v>
@@ -17798,7 +17828,7 @@
         <v>14</v>
       </c>
       <c r="H355" s="1" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="I355" s="9">
         <v>45870</v>
@@ -17833,7 +17863,7 @@
         <v>14</v>
       </c>
       <c r="H356" s="1" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="I356" s="9">
         <v>45876</v>
@@ -17868,7 +17898,7 @@
         <v>14</v>
       </c>
       <c r="H357" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="I357" s="9">
         <v>45884</v>
@@ -17903,7 +17933,7 @@
         <v>14</v>
       </c>
       <c r="H358" s="1" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="I358" s="9">
         <v>45884</v>
@@ -17938,7 +17968,7 @@
         <v>14</v>
       </c>
       <c r="H359" s="1" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="I359" s="9">
         <v>45653</v>
@@ -17973,7 +18003,7 @@
         <v>14</v>
       </c>
       <c r="H360" s="1" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="I360" s="9">
         <v>45929</v>
@@ -18008,7 +18038,7 @@
         <v>14</v>
       </c>
       <c r="H361" s="1" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="I361" s="9">
         <v>45931</v>
@@ -18043,7 +18073,7 @@
         <v>14</v>
       </c>
       <c r="H362" s="1" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="I362" s="9">
         <v>45931</v>
@@ -18078,7 +18108,7 @@
         <v>14</v>
       </c>
       <c r="H363" s="1" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="I363" s="9">
         <v>40452</v>
@@ -18113,7 +18143,7 @@
         <v>14</v>
       </c>
       <c r="H364" s="1" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="I364" s="9">
         <v>45932</v>
@@ -18181,7 +18211,7 @@
         <v>14</v>
       </c>
       <c r="H366" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I366" s="15">
         <v>45604</v>
@@ -18216,7 +18246,7 @@
         <v>14</v>
       </c>
       <c r="H367" s="1" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="I367" s="15">
         <v>45768</v>
@@ -18251,7 +18281,7 @@
         <v>14</v>
       </c>
       <c r="H368" s="1" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="I368" s="9">
         <v>45937</v>
@@ -18286,7 +18316,7 @@
         <v>14</v>
       </c>
       <c r="H369" s="1" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="I369" s="9">
         <v>45937</v>
@@ -18321,7 +18351,7 @@
         <v>14</v>
       </c>
       <c r="H370" s="1" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="I370" s="9">
         <v>45937</v>
@@ -18356,7 +18386,7 @@
         <v>14</v>
       </c>
       <c r="H371" s="1" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="I371" s="23">
         <v>45939</v>
@@ -18391,7 +18421,7 @@
         <v>14</v>
       </c>
       <c r="H372" s="1" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="I372" s="23">
         <v>45939</v>
@@ -18426,7 +18456,7 @@
         <v>14</v>
       </c>
       <c r="H373" s="1" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="I373" s="23">
         <v>45942</v>
@@ -18461,7 +18491,7 @@
         <v>14</v>
       </c>
       <c r="H374" s="1" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="I374" s="9">
         <v>45947</v>
@@ -18496,7 +18526,7 @@
         <v>14</v>
       </c>
       <c r="H375" s="1" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="I375" s="23">
         <v>45946</v>
@@ -18531,7 +18561,7 @@
         <v>14</v>
       </c>
       <c r="H376" s="1" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="I376" s="23">
         <v>45945</v>
@@ -18566,7 +18596,7 @@
         <v>14</v>
       </c>
       <c r="H377" s="1" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="I377" s="23">
         <v>45942</v>
@@ -18601,7 +18631,7 @@
         <v>14</v>
       </c>
       <c r="H378" s="1" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="I378" s="23">
         <v>45946</v>
@@ -18636,7 +18666,7 @@
         <v>14</v>
       </c>
       <c r="H379" s="1" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="I379" s="23">
         <v>45946</v>
@@ -18671,7 +18701,7 @@
         <v>14</v>
       </c>
       <c r="H380" s="1" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="I380" s="23">
         <v>45942</v>
@@ -18706,7 +18736,7 @@
         <v>14</v>
       </c>
       <c r="H381" s="1" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="I381" s="23">
         <v>45945</v>
@@ -18741,7 +18771,7 @@
         <v>14</v>
       </c>
       <c r="H382" s="1" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="I382" s="23">
         <v>46036</v>
@@ -18776,7 +18806,7 @@
         <v>14</v>
       </c>
       <c r="H383" s="1" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="I383" s="23">
         <v>45968</v>
@@ -18811,7 +18841,7 @@
         <v>14</v>
       </c>
       <c r="H384" s="1" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="I384" s="23">
         <v>45994</v>
@@ -18846,7 +18876,7 @@
         <v>14</v>
       </c>
       <c r="H385" s="1" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="I385" s="23">
         <v>45968</v>
@@ -18881,7 +18911,7 @@
         <v>14</v>
       </c>
       <c r="H386" s="1" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="I386" s="23">
         <v>45968</v>
@@ -18916,7 +18946,7 @@
         <v>14</v>
       </c>
       <c r="H387" s="1" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="I387" s="23">
         <v>45968</v>
@@ -18951,7 +18981,7 @@
         <v>14</v>
       </c>
       <c r="H388" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="I388" s="23">
         <v>45968</v>
@@ -18960,7 +18990,7 @@
         <v>574</v>
       </c>
       <c r="K388" s="3" t="s">
-        <v>1460</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="389" spans="1:11">
@@ -18986,7 +19016,7 @@
         <v>14</v>
       </c>
       <c r="H389" s="1" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="I389" s="23">
         <v>45968</v>
@@ -19021,7 +19051,7 @@
         <v>14</v>
       </c>
       <c r="H390" s="1" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="I390" s="23">
         <v>45968</v>
@@ -19056,7 +19086,7 @@
         <v>14</v>
       </c>
       <c r="H391" s="1" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="I391" s="23">
         <v>45971</v>
@@ -19073,25 +19103,25 @@
         <v>391</v>
       </c>
       <c r="B392" s="56" t="s">
-        <v>1377</v>
+        <v>1374</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D392" s="2" t="s">
-        <v>1378</v>
+        <v>1375</v>
       </c>
       <c r="E392" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>1381</v>
+        <v>1378</v>
       </c>
       <c r="G392" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H392" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I392" s="54">
         <v>46279</v>
@@ -19100,7 +19130,7 @@
         <v>574</v>
       </c>
       <c r="K392" s="3" t="s">
-        <v>1379</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="393" spans="1:11">
@@ -19108,25 +19138,25 @@
         <v>392</v>
       </c>
       <c r="B393" s="56" t="s">
-        <v>1377</v>
+        <v>1374</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>1380</v>
+        <v>1377</v>
       </c>
       <c r="E393" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F393" s="1" t="s">
-        <v>1456</v>
+        <v>1453</v>
       </c>
       <c r="G393" s="1" t="s">
         <v>30</v>
       </c>
       <c r="H393" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I393" s="54">
         <v>46279</v>
@@ -19135,7 +19165,7 @@
         <v>574</v>
       </c>
       <c r="K393" s="3" t="s">
-        <v>1382</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="394" spans="1:11">
@@ -19143,13 +19173,13 @@
         <v>393</v>
       </c>
       <c r="B394" s="56" t="s">
-        <v>1377</v>
+        <v>1374</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D394" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E394" s="1" t="s">
         <v>21</v>
@@ -19161,7 +19191,7 @@
         <v>30</v>
       </c>
       <c r="H394" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I394" s="54">
         <v>46279</v>
@@ -19176,13 +19206,13 @@
         <v>394</v>
       </c>
       <c r="B395" s="56" t="s">
-        <v>1377</v>
+        <v>1374</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D395" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E395" s="1" t="s">
         <v>21</v>
@@ -19194,7 +19224,7 @@
         <v>30</v>
       </c>
       <c r="H395" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I395" s="54">
         <v>46279</v>
@@ -19209,13 +19239,13 @@
         <v>395</v>
       </c>
       <c r="B396" s="56" t="s">
-        <v>1377</v>
+        <v>1374</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D396" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E396" s="1" t="s">
         <v>21</v>
@@ -19227,7 +19257,7 @@
         <v>30</v>
       </c>
       <c r="H396" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I396" s="54">
         <v>46279</v>
@@ -19260,7 +19290,7 @@
         <v>14</v>
       </c>
       <c r="H397" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="I397" s="23">
         <v>45945</v>
@@ -19295,7 +19325,7 @@
         <v>14</v>
       </c>
       <c r="H398" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I398" s="23">
         <v>45945</v>
@@ -19330,7 +19360,7 @@
         <v>14</v>
       </c>
       <c r="H399" s="1" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="I399" s="23">
         <v>45945</v>
@@ -19365,7 +19395,7 @@
         <v>14</v>
       </c>
       <c r="H400" s="1" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="I400" s="23">
         <v>45992</v>
@@ -19400,7 +19430,7 @@
         <v>14</v>
       </c>
       <c r="H401" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I401" s="23">
         <v>46129</v>
@@ -19409,7 +19439,7 @@
         <v>645</v>
       </c>
       <c r="K401" s="3" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="402" spans="1:11">
@@ -19464,13 +19494,13 @@
         <v>76</v>
       </c>
       <c r="F403" s="1" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="G403" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H403" s="1" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="I403" s="23">
         <v>45945</v>
@@ -19505,7 +19535,7 @@
         <v>14</v>
       </c>
       <c r="H404" s="1" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="I404" s="23">
         <v>46098</v>
@@ -19540,7 +19570,7 @@
         <v>14</v>
       </c>
       <c r="H405" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I405" s="23">
         <v>45941</v>
@@ -19575,7 +19605,7 @@
         <v>14</v>
       </c>
       <c r="H406" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I406" s="23">
         <v>45941</v>
@@ -19610,7 +19640,7 @@
         <v>14</v>
       </c>
       <c r="H407" s="1" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="I407" s="23">
         <v>45952</v>
@@ -19645,7 +19675,7 @@
         <v>14</v>
       </c>
       <c r="H408" s="1" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="I408" s="23">
         <v>45950</v>
@@ -19680,7 +19710,7 @@
         <v>14</v>
       </c>
       <c r="H409" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="I409" s="23">
         <v>45996</v>
@@ -19715,7 +19745,7 @@
         <v>14</v>
       </c>
       <c r="H410" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I410" s="9">
         <v>45941</v>
@@ -19783,7 +19813,7 @@
         <v>14</v>
       </c>
       <c r="H412" s="1" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="I412" s="23">
         <v>45952</v>
@@ -19818,7 +19848,7 @@
         <v>14</v>
       </c>
       <c r="H413" s="1" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="I413" s="23">
         <v>45959</v>
@@ -19853,7 +19883,7 @@
         <v>14</v>
       </c>
       <c r="H414" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="I414" s="23">
         <v>45960</v>
@@ -19888,7 +19918,7 @@
         <v>14</v>
       </c>
       <c r="H415" s="1" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="I415" s="23">
         <v>45945</v>
@@ -19956,7 +19986,7 @@
         <v>14</v>
       </c>
       <c r="H417" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="I417" s="23">
         <v>45945</v>
@@ -19991,7 +20021,7 @@
         <v>14</v>
       </c>
       <c r="H418" s="1" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="I418" s="23">
         <v>45945</v>
@@ -20026,7 +20056,7 @@
         <v>14</v>
       </c>
       <c r="H419" s="1" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="I419" s="23">
         <v>45945</v>
@@ -20061,7 +20091,7 @@
         <v>14</v>
       </c>
       <c r="H420" s="1" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="I420" s="23">
         <v>45940</v>
@@ -20096,7 +20126,7 @@
         <v>14</v>
       </c>
       <c r="H421" s="1" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="I421" s="23">
         <v>45940</v>
@@ -20131,7 +20161,7 @@
         <v>14</v>
       </c>
       <c r="H422" s="1" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="I422" s="23">
         <v>45940</v>
@@ -20166,7 +20196,7 @@
         <v>14</v>
       </c>
       <c r="H423" s="1" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="I423" s="23">
         <v>45939</v>
@@ -20201,7 +20231,7 @@
         <v>14</v>
       </c>
       <c r="H424" s="1" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="I424" s="23">
         <v>45939</v>
@@ -20236,7 +20266,7 @@
         <v>14</v>
       </c>
       <c r="H425" s="1" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="I425" s="23">
         <v>45938</v>
@@ -20271,7 +20301,7 @@
         <v>14</v>
       </c>
       <c r="H426" s="1" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="I426" s="23">
         <v>45938</v>
@@ -20306,7 +20336,7 @@
         <v>14</v>
       </c>
       <c r="H427" s="1" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="I427" s="23">
         <v>45939</v>
@@ -20341,7 +20371,7 @@
         <v>14</v>
       </c>
       <c r="H428" s="1" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="I428" s="23">
         <v>45939</v>
@@ -20376,7 +20406,7 @@
         <v>14</v>
       </c>
       <c r="H429" s="1" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="I429" s="23">
         <v>45985</v>
@@ -20411,7 +20441,7 @@
         <v>14</v>
       </c>
       <c r="H430" s="1" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="I430" s="23">
         <v>45992</v>
@@ -20446,7 +20476,7 @@
         <v>14</v>
       </c>
       <c r="H431" s="1" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="I431" s="23">
         <v>45996</v>
@@ -20481,7 +20511,7 @@
         <v>14</v>
       </c>
       <c r="H432" s="1" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="I432" s="23">
         <v>45996</v>
@@ -20516,7 +20546,7 @@
         <v>14</v>
       </c>
       <c r="H433" s="1" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="I433" s="23">
         <v>45985</v>
@@ -20539,19 +20569,19 @@
         <v>11</v>
       </c>
       <c r="D434" s="2" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="E434" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F434" s="1" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
       <c r="G434" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H434" s="1" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="I434" s="54">
         <v>46279</v>
@@ -20572,19 +20602,19 @@
         <v>11</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="E435" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F435" s="1" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="G435" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H435" s="1" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="I435" s="54">
         <v>46279</v>
@@ -20605,19 +20635,19 @@
         <v>11</v>
       </c>
       <c r="D436" s="2" t="s">
-        <v>1402</v>
+        <v>1399</v>
       </c>
       <c r="E436" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F436" s="1" t="s">
-        <v>1401</v>
+        <v>1398</v>
       </c>
       <c r="G436" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H436" s="1" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="I436" s="54">
         <v>46279</v>
@@ -20638,19 +20668,19 @@
         <v>11</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>1404</v>
+        <v>1401</v>
       </c>
       <c r="E437" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F437" s="1" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
       <c r="G437" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H437" s="1" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="I437" s="54">
         <v>46279</v>
@@ -20671,19 +20701,19 @@
         <v>11</v>
       </c>
       <c r="D438" s="2" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="E438" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F438" s="1" t="s">
-        <v>1405</v>
+        <v>1402</v>
       </c>
       <c r="G438" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H438" s="1" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="I438" s="54">
         <v>46279</v>
@@ -20704,19 +20734,19 @@
         <v>11</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="E439" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F439" s="1" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="G439" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H439" s="1" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="I439" s="54">
         <v>46279</v>
@@ -20737,19 +20767,19 @@
         <v>11</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>1408</v>
+        <v>1405</v>
       </c>
       <c r="E440" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F440" s="1" t="s">
-        <v>1409</v>
+        <v>1406</v>
       </c>
       <c r="G440" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H440" s="1" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="I440" s="54">
         <v>46279</v>
@@ -20770,19 +20800,19 @@
         <v>11</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>1410</v>
+        <v>1407</v>
       </c>
       <c r="E441" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F441" s="1" t="s">
-        <v>1411</v>
+        <v>1408</v>
       </c>
       <c r="G441" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H441" s="1" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="I441" s="54">
         <v>46279</v>
@@ -20803,19 +20833,19 @@
         <v>11</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="E442" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F442" s="1" t="s">
-        <v>1412</v>
+        <v>1409</v>
       </c>
       <c r="G442" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H442" s="1" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="I442" s="54">
         <v>46279</v>
@@ -20836,19 +20866,19 @@
         <v>11</v>
       </c>
       <c r="D443" s="2" t="s">
-        <v>1422</v>
+        <v>1419</v>
       </c>
       <c r="E443" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F443" s="1" t="s">
-        <v>1413</v>
+        <v>1410</v>
       </c>
       <c r="G443" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H443" s="1" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="I443" s="54">
         <v>46279</v>
@@ -20869,19 +20899,19 @@
         <v>11</v>
       </c>
       <c r="D444" s="2" t="s">
-        <v>1423</v>
+        <v>1420</v>
       </c>
       <c r="E444" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F444" s="1" t="s">
-        <v>1414</v>
+        <v>1411</v>
       </c>
       <c r="G444" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H444" s="1" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="I444" s="54">
         <v>46279</v>
@@ -20902,19 +20932,19 @@
         <v>11</v>
       </c>
       <c r="D445" s="2" t="s">
-        <v>1424</v>
+        <v>1421</v>
       </c>
       <c r="E445" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F445" s="1" t="s">
-        <v>1415</v>
+        <v>1412</v>
       </c>
       <c r="G445" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H445" s="1" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="I445" s="54">
         <v>46279</v>
@@ -20935,19 +20965,19 @@
         <v>11</v>
       </c>
       <c r="D446" s="2" t="s">
-        <v>1425</v>
+        <v>1422</v>
       </c>
       <c r="E446" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F446" s="1" t="s">
-        <v>1416</v>
+        <v>1413</v>
       </c>
       <c r="G446" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H446" s="1" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="I446" s="54">
         <v>46279</v>
@@ -20968,19 +20998,19 @@
         <v>11</v>
       </c>
       <c r="D447" s="2" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
       <c r="E447" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F447" s="1" t="s">
-        <v>1417</v>
+        <v>1414</v>
       </c>
       <c r="G447" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H447" s="1" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="I447" s="54">
         <v>46279</v>
@@ -21001,19 +21031,19 @@
         <v>11</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="E448" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F448" s="1" t="s">
-        <v>1418</v>
+        <v>1415</v>
       </c>
       <c r="G448" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H448" s="1" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="I448" s="54">
         <v>46279</v>
@@ -21034,19 +21064,19 @@
         <v>11</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
       <c r="E449" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F449" s="1" t="s">
-        <v>1419</v>
+        <v>1416</v>
       </c>
       <c r="G449" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H449" s="1" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="I449" s="54">
         <v>46279</v>
@@ -21067,19 +21097,19 @@
         <v>11</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>1432</v>
+        <v>1429</v>
       </c>
       <c r="E450" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F450" s="1" t="s">
-        <v>1420</v>
+        <v>1417</v>
       </c>
       <c r="G450" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H450" s="1" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="I450" s="54">
         <v>46279</v>
@@ -21100,19 +21130,19 @@
         <v>11</v>
       </c>
       <c r="D451" s="2" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="E451" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F451" s="1" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
       <c r="G451" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H451" s="1" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="I451" s="54">
         <v>46279</v>
@@ -21133,19 +21163,19 @@
         <v>11</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
       <c r="E452" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F452" s="1" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
       <c r="G452" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H452" s="1" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="I452" s="54">
         <v>46279</v>
@@ -21166,19 +21196,19 @@
         <v>11</v>
       </c>
       <c r="D453" s="2" t="s">
-        <v>1463</v>
+        <v>1460</v>
       </c>
       <c r="E453" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F453" s="1" t="s">
-        <v>1446</v>
+        <v>1443</v>
       </c>
       <c r="G453" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H453" s="1" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="I453" s="54">
         <v>46279</v>
@@ -21199,19 +21229,19 @@
         <v>11</v>
       </c>
       <c r="D454" s="2" t="s">
-        <v>1464</v>
+        <v>1461</v>
       </c>
       <c r="E454" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F454" s="1" t="s">
-        <v>1466</v>
+        <v>1463</v>
       </c>
       <c r="G454" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H454" s="1" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="I454" s="54">
         <v>44854</v>
@@ -21232,19 +21262,19 @@
         <v>11</v>
       </c>
       <c r="D455" s="2" t="s">
-        <v>1465</v>
+        <v>1462</v>
       </c>
       <c r="E455" s="1" t="s">
         <v>76</v>
       </c>
       <c r="F455" s="1" t="s">
-        <v>1467</v>
+        <v>1464</v>
       </c>
       <c r="G455" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H455" s="1" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="I455" s="54">
         <v>46315</v>
@@ -21265,7 +21295,7 @@
         <v>11</v>
       </c>
       <c r="D456" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E456" s="1" t="s">
         <v>21</v>
@@ -21277,7 +21307,7 @@
         <v>30</v>
       </c>
       <c r="H456" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I456" s="54">
         <v>46279</v>
@@ -21298,7 +21328,7 @@
         <v>11</v>
       </c>
       <c r="D457" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E457" s="1" t="s">
         <v>21</v>
@@ -21310,7 +21340,7 @@
         <v>30</v>
       </c>
       <c r="H457" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I457" s="54">
         <v>46279</v>
@@ -21331,7 +21361,7 @@
         <v>11</v>
       </c>
       <c r="D458" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E458" s="1" t="s">
         <v>21</v>
@@ -21343,7 +21373,7 @@
         <v>30</v>
       </c>
       <c r="H458" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I458" s="54">
         <v>46279</v>
@@ -21364,7 +21394,7 @@
         <v>11</v>
       </c>
       <c r="D459" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E459" s="1" t="s">
         <v>21</v>
@@ -21376,7 +21406,7 @@
         <v>30</v>
       </c>
       <c r="H459" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I459" s="54">
         <v>46279</v>
@@ -21397,7 +21427,7 @@
         <v>11</v>
       </c>
       <c r="D460" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E460" s="1" t="s">
         <v>21</v>
@@ -21409,7 +21439,7 @@
         <v>30</v>
       </c>
       <c r="H460" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I460" s="54">
         <v>46279</v>
@@ -21430,7 +21460,7 @@
         <v>11</v>
       </c>
       <c r="D461" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E461" s="1" t="s">
         <v>21</v>
@@ -21442,7 +21472,7 @@
         <v>30</v>
       </c>
       <c r="H461" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I461" s="54">
         <v>46279</v>
@@ -21463,7 +21493,7 @@
         <v>11</v>
       </c>
       <c r="D462" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E462" s="1" t="s">
         <v>21</v>
@@ -21475,7 +21505,7 @@
         <v>30</v>
       </c>
       <c r="H462" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I462" s="54">
         <v>46279</v>
@@ -21496,7 +21526,7 @@
         <v>11</v>
       </c>
       <c r="D463" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E463" s="1" t="s">
         <v>21</v>
@@ -21508,7 +21538,7 @@
         <v>30</v>
       </c>
       <c r="H463" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I463" s="54">
         <v>46279</v>
@@ -21529,7 +21559,7 @@
         <v>11</v>
       </c>
       <c r="D464" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E464" s="1" t="s">
         <v>21</v>
@@ -21541,7 +21571,7 @@
         <v>30</v>
       </c>
       <c r="H464" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I464" s="54">
         <v>46279</v>
@@ -21562,7 +21592,7 @@
         <v>11</v>
       </c>
       <c r="D465" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E465" s="1" t="s">
         <v>21</v>
@@ -21574,7 +21604,7 @@
         <v>30</v>
       </c>
       <c r="H465" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I465" s="54">
         <v>46279</v>
@@ -21595,7 +21625,7 @@
         <v>11</v>
       </c>
       <c r="D466" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E466" s="1" t="s">
         <v>21</v>
@@ -21607,7 +21637,7 @@
         <v>30</v>
       </c>
       <c r="H466" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I466" s="54">
         <v>46279</v>
@@ -21628,7 +21658,7 @@
         <v>11</v>
       </c>
       <c r="D467" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E467" s="1" t="s">
         <v>21</v>
@@ -21640,7 +21670,7 @@
         <v>30</v>
       </c>
       <c r="H467" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I467" s="54">
         <v>46279</v>
@@ -21661,7 +21691,7 @@
         <v>11</v>
       </c>
       <c r="D468" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E468" s="1" t="s">
         <v>21</v>
@@ -21673,7 +21703,7 @@
         <v>30</v>
       </c>
       <c r="H468" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I468" s="54">
         <v>46279</v>
@@ -21694,7 +21724,7 @@
         <v>11</v>
       </c>
       <c r="D469" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E469" s="1" t="s">
         <v>21</v>
@@ -21706,7 +21736,7 @@
         <v>30</v>
       </c>
       <c r="H469" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I469" s="54">
         <v>46279</v>
@@ -21727,7 +21757,7 @@
         <v>11</v>
       </c>
       <c r="D470" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E470" s="1" t="s">
         <v>21</v>
@@ -21739,7 +21769,7 @@
         <v>30</v>
       </c>
       <c r="H470" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I470" s="54">
         <v>46279</v>
@@ -21760,7 +21790,7 @@
         <v>11</v>
       </c>
       <c r="D471" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E471" s="1" t="s">
         <v>21</v>
@@ -21772,7 +21802,7 @@
         <v>30</v>
       </c>
       <c r="H471" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I471" s="54">
         <v>46288</v>
@@ -21793,19 +21823,19 @@
         <v>11</v>
       </c>
       <c r="D472" s="2" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
       <c r="E472" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F472" s="1" t="s">
-        <v>1461</v>
+        <v>1458</v>
       </c>
       <c r="G472" s="1" t="s">
         <v>30</v>
       </c>
       <c r="H472" s="1" t="s">
-        <v>1462</v>
+        <v>1459</v>
       </c>
       <c r="I472" s="54">
         <v>46279</v>
@@ -21838,7 +21868,7 @@
         <v>14</v>
       </c>
       <c r="H473" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I473" s="23">
         <v>45940</v>
@@ -21873,7 +21903,7 @@
         <v>14</v>
       </c>
       <c r="H474" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I474" s="23">
         <v>45940</v>
@@ -21908,7 +21938,7 @@
         <v>14</v>
       </c>
       <c r="H475" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I475" s="23">
         <v>45940</v>
@@ -21943,7 +21973,7 @@
         <v>14</v>
       </c>
       <c r="H476" s="1" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="I476" s="23">
         <v>45945</v>
@@ -21978,7 +22008,7 @@
         <v>14</v>
       </c>
       <c r="H477" s="1" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="I477" s="23">
         <v>45950</v>
@@ -22013,7 +22043,7 @@
         <v>14</v>
       </c>
       <c r="H478" s="1" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="I478" s="23">
         <v>45950</v>
@@ -22048,7 +22078,7 @@
         <v>14</v>
       </c>
       <c r="H479" s="1" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="I479" s="23">
         <v>45952</v>
@@ -22083,7 +22113,7 @@
         <v>14</v>
       </c>
       <c r="H480" s="1" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="I480" s="23">
         <v>45952</v>
@@ -22118,7 +22148,7 @@
         <v>14</v>
       </c>
       <c r="H481" s="1" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="I481" s="23">
         <v>45960</v>
@@ -22153,7 +22183,7 @@
         <v>14</v>
       </c>
       <c r="H482" s="1" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="I482" s="23">
         <v>45992</v>
@@ -22188,7 +22218,7 @@
         <v>14</v>
       </c>
       <c r="H483" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I483" s="23">
         <v>45992</v>
@@ -22223,7 +22253,7 @@
         <v>14</v>
       </c>
       <c r="H484" s="1" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="I484" s="23">
         <v>45975</v>
@@ -22258,7 +22288,7 @@
         <v>14</v>
       </c>
       <c r="H485" s="1" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="I485" s="23">
         <v>45975</v>
@@ -22293,7 +22323,7 @@
         <v>14</v>
       </c>
       <c r="H486" s="1" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="I486" s="23">
         <v>45975</v>
@@ -22328,7 +22358,7 @@
         <v>14</v>
       </c>
       <c r="H487" s="1" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="I487" s="23">
         <v>46001</v>
@@ -22363,7 +22393,7 @@
         <v>14</v>
       </c>
       <c r="H488" s="1" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="I488" s="23">
         <v>46036</v>
@@ -22398,7 +22428,7 @@
         <v>14</v>
       </c>
       <c r="H489" s="1" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="I489" s="23">
         <v>46037</v>
@@ -22433,7 +22463,7 @@
         <v>14</v>
       </c>
       <c r="H490" s="1" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="I490" s="23">
         <v>46001</v>
@@ -22466,7 +22496,7 @@
         <v>14</v>
       </c>
       <c r="H491" s="1" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="I491" s="23">
         <v>46041</v>
@@ -22501,7 +22531,7 @@
         <v>14</v>
       </c>
       <c r="H492" s="1" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="I492" s="23">
         <v>46041</v>
@@ -22536,7 +22566,7 @@
         <v>14</v>
       </c>
       <c r="H493" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I493" s="23">
         <v>45957</v>
@@ -22571,7 +22601,7 @@
         <v>14</v>
       </c>
       <c r="H494" s="1" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="I494" s="23">
         <v>46034</v>
@@ -22641,7 +22671,7 @@
         <v>14</v>
       </c>
       <c r="H496" s="1" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="I496" s="23">
         <v>46036</v>
@@ -22676,7 +22706,7 @@
         <v>30</v>
       </c>
       <c r="H497" s="1" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="I497" s="23">
         <v>45950</v>
@@ -22711,7 +22741,7 @@
         <v>30</v>
       </c>
       <c r="H498" s="1" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="I498" s="23">
         <v>45950</v>
@@ -22746,7 +22776,7 @@
         <v>30</v>
       </c>
       <c r="H499" s="1" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="I499" s="23">
         <v>45952</v>
@@ -22781,7 +22811,7 @@
         <v>30</v>
       </c>
       <c r="H500" s="1" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="I500" s="23">
         <v>46048</v>
@@ -22816,7 +22846,7 @@
         <v>30</v>
       </c>
       <c r="H501" s="1" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="I501" s="23">
         <v>46050</v>
@@ -22884,7 +22914,7 @@
         <v>30</v>
       </c>
       <c r="H503" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I503" s="23">
         <v>45712</v>
@@ -22919,7 +22949,7 @@
         <v>30</v>
       </c>
       <c r="H504" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="I504" s="23">
         <v>46142</v>
@@ -22952,7 +22982,7 @@
         <v>30</v>
       </c>
       <c r="H505" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="I505" s="23">
         <v>46174</v>
@@ -23018,7 +23048,7 @@
         <v>30</v>
       </c>
       <c r="H507" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="I507" s="23">
         <v>46063</v>
@@ -23051,7 +23081,7 @@
         <v>30</v>
       </c>
       <c r="H508" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I508" s="23">
         <v>46104</v>
@@ -23084,7 +23114,7 @@
         <v>30</v>
       </c>
       <c r="H509" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I509" s="23">
         <v>46129</v>
@@ -23117,7 +23147,7 @@
         <v>30</v>
       </c>
       <c r="H510" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I510" s="23">
         <v>46081</v>
@@ -23150,7 +23180,7 @@
         <v>30</v>
       </c>
       <c r="H511" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="I511" s="23">
         <v>46146</v>
@@ -23183,7 +23213,7 @@
         <v>30</v>
       </c>
       <c r="H512" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="I512" s="23">
         <v>46081</v>
@@ -23204,7 +23234,7 @@
         <v>83</v>
       </c>
       <c r="D513" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E513" s="1" t="s">
         <v>21</v>
@@ -23216,7 +23246,7 @@
         <v>30</v>
       </c>
       <c r="H513" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I513" s="54">
         <v>46279</v>
@@ -23237,7 +23267,7 @@
         <v>83</v>
       </c>
       <c r="D514" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E514" s="1" t="s">
         <v>21</v>
@@ -23249,7 +23279,7 @@
         <v>30</v>
       </c>
       <c r="H514" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I514" s="54">
         <v>46279</v>
@@ -23270,7 +23300,7 @@
         <v>83</v>
       </c>
       <c r="D515" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E515" s="1" t="s">
         <v>21</v>
@@ -23282,7 +23312,7 @@
         <v>30</v>
       </c>
       <c r="H515" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I515" s="54">
         <v>46279</v>
@@ -23303,7 +23333,7 @@
         <v>83</v>
       </c>
       <c r="D516" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E516" s="1" t="s">
         <v>21</v>
@@ -23315,7 +23345,7 @@
         <v>30</v>
       </c>
       <c r="H516" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I516" s="54">
         <v>46279</v>
@@ -23336,7 +23366,7 @@
         <v>83</v>
       </c>
       <c r="D517" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E517" s="1" t="s">
         <v>21</v>
@@ -23348,7 +23378,7 @@
         <v>30</v>
       </c>
       <c r="H517" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I517" s="54">
         <v>46279</v>
@@ -23369,28 +23399,28 @@
         <v>11</v>
       </c>
       <c r="D518" s="2" t="s">
-        <v>1080</v>
+        <v>1192</v>
       </c>
       <c r="E518" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F518" s="1" t="s">
-        <v>23</v>
+        <v>606</v>
       </c>
       <c r="G518" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H518" s="1" t="s">
-        <v>1370</v>
+      <c r="H518" s="2" t="s">
+        <v>1444</v>
       </c>
       <c r="I518" s="23">
         <v>46091</v>
       </c>
       <c r="J518" s="4" t="s">
-        <v>645</v>
+        <v>574</v>
       </c>
       <c r="K518" s="3" t="s">
-        <v>1375</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="519" spans="1:11">
@@ -23416,7 +23446,7 @@
         <v>30</v>
       </c>
       <c r="H519" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I519" s="23">
         <v>46098</v>
@@ -23449,7 +23479,7 @@
         <v>30</v>
       </c>
       <c r="H520" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I520" s="23">
         <v>46099</v>
@@ -23482,7 +23512,7 @@
         <v>30</v>
       </c>
       <c r="H521" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I521" s="23">
         <v>46099</v>
@@ -23491,7 +23521,7 @@
         <v>574</v>
       </c>
       <c r="K521" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="522" spans="1:11">
@@ -23517,7 +23547,7 @@
         <v>30</v>
       </c>
       <c r="H522" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I522" s="23">
         <v>46099</v>
@@ -23550,7 +23580,7 @@
         <v>30</v>
       </c>
       <c r="H523" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I523" s="23">
         <v>46099</v>
@@ -23583,7 +23613,7 @@
         <v>30</v>
       </c>
       <c r="H524" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I524" s="23">
         <v>46081</v>
@@ -23616,7 +23646,7 @@
         <v>30</v>
       </c>
       <c r="H525" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="I525" s="23">
         <v>46105</v>
@@ -23625,7 +23655,7 @@
         <v>645</v>
       </c>
       <c r="K525" s="3" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="526" spans="1:11">
@@ -23651,7 +23681,7 @@
         <v>30</v>
       </c>
       <c r="H526" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I526" s="23">
         <v>46105</v>
@@ -23684,7 +23714,7 @@
         <v>30</v>
       </c>
       <c r="H527" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I527" s="23">
         <v>46108</v>
@@ -23717,7 +23747,7 @@
         <v>30</v>
       </c>
       <c r="H528" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I528" s="23">
         <v>46108</v>
@@ -23750,7 +23780,7 @@
         <v>30</v>
       </c>
       <c r="H529" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I529" s="23">
         <v>46111</v>
@@ -23783,7 +23813,7 @@
         <v>30</v>
       </c>
       <c r="H530" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I530" s="23">
         <v>46113</v>
@@ -23816,7 +23846,7 @@
         <v>30</v>
       </c>
       <c r="H531" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I531" s="23">
         <v>46114</v>
@@ -23849,7 +23879,7 @@
         <v>30</v>
       </c>
       <c r="H532" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I532" s="23">
         <v>46114</v>
@@ -23882,7 +23912,7 @@
         <v>30</v>
       </c>
       <c r="H533" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I533" s="23">
         <v>46118</v>
@@ -23915,7 +23945,7 @@
         <v>30</v>
       </c>
       <c r="H534" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I534" s="23">
         <v>46119</v>
@@ -23948,7 +23978,7 @@
         <v>30</v>
       </c>
       <c r="H535" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I535" s="23">
         <v>46120</v>
@@ -23981,7 +24011,7 @@
         <v>30</v>
       </c>
       <c r="H536" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I536" s="23">
         <v>46120</v>
@@ -24014,7 +24044,7 @@
         <v>30</v>
       </c>
       <c r="H537" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I537" s="23">
         <v>46120</v>
@@ -24047,7 +24077,7 @@
         <v>30</v>
       </c>
       <c r="H538" s="1" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="I538" s="23">
         <v>46121</v>
@@ -24056,7 +24086,7 @@
         <v>574</v>
       </c>
       <c r="K538" s="3" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="539" spans="1:11">
@@ -24082,7 +24112,7 @@
         <v>30</v>
       </c>
       <c r="H539" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I539" s="23">
         <v>46126</v>
@@ -24115,7 +24145,7 @@
         <v>30</v>
       </c>
       <c r="H540" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I540" s="23">
         <v>46126</v>
@@ -24148,7 +24178,7 @@
         <v>30</v>
       </c>
       <c r="H541" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I541" s="23">
         <v>46126</v>
@@ -24181,7 +24211,7 @@
         <v>30</v>
       </c>
       <c r="H542" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I542" s="23">
         <v>46128</v>
@@ -24214,7 +24244,7 @@
         <v>30</v>
       </c>
       <c r="H543" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I543" s="23">
         <v>46081</v>
@@ -24247,7 +24277,7 @@
         <v>30</v>
       </c>
       <c r="H544" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I544" s="23">
         <v>46081</v>
@@ -24280,7 +24310,7 @@
         <v>30</v>
       </c>
       <c r="H545" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I545" s="23">
         <v>46134</v>
@@ -24313,7 +24343,7 @@
         <v>30</v>
       </c>
       <c r="H546" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I546" s="23">
         <v>46134</v>
@@ -24346,7 +24376,7 @@
         <v>30</v>
       </c>
       <c r="H547" s="4" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="I547" s="23">
         <v>46142</v>
@@ -24379,7 +24409,7 @@
         <v>30</v>
       </c>
       <c r="H548" s="1" t="s">
-        <v>1338</v>
+        <v>1369</v>
       </c>
       <c r="I548" s="23">
         <v>46148</v>
@@ -24388,7 +24418,7 @@
         <v>574</v>
       </c>
       <c r="K548" s="3" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="549" spans="1:11">
@@ -24414,7 +24444,7 @@
         <v>30</v>
       </c>
       <c r="H549" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I549" s="23">
         <v>46148</v>
@@ -24447,7 +24477,7 @@
         <v>30</v>
       </c>
       <c r="H550" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I550" s="23">
         <v>46148</v>
@@ -24480,7 +24510,7 @@
         <v>30</v>
       </c>
       <c r="H551" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I551" s="23">
         <v>46161</v>
@@ -24501,7 +24531,7 @@
         <v>11</v>
       </c>
       <c r="D552" s="2" t="s">
-        <v>1192</v>
+        <v>1080</v>
       </c>
       <c r="E552" s="1" t="s">
         <v>19</v>
@@ -24513,7 +24543,7 @@
         <v>30</v>
       </c>
       <c r="H552" s="1" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="I552" s="23">
         <v>46164</v>
@@ -24522,7 +24552,7 @@
         <v>645</v>
       </c>
       <c r="K552" s="3" t="s">
-        <v>1373</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="553" spans="1:11">
@@ -24548,7 +24578,7 @@
         <v>30</v>
       </c>
       <c r="H553" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I553" s="23">
         <v>46164</v>
@@ -24569,7 +24599,7 @@
         <v>11</v>
       </c>
       <c r="D554" s="2" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E554" s="1" t="s">
         <v>19</v>
@@ -24581,7 +24611,7 @@
         <v>30</v>
       </c>
       <c r="H554" s="1" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="I554" s="23">
         <v>46081</v>
@@ -24590,7 +24620,7 @@
         <v>574</v>
       </c>
       <c r="K554" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="555" spans="1:11">
@@ -24604,7 +24634,7 @@
         <v>11</v>
       </c>
       <c r="D555" s="2" t="s">
-        <v>1458</v>
+        <v>1455</v>
       </c>
       <c r="E555" s="1" t="s">
         <v>19</v>
@@ -24616,7 +24646,7 @@
         <v>30</v>
       </c>
       <c r="H555" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I555" s="54">
         <v>46287</v>
@@ -24637,7 +24667,7 @@
         <v>11</v>
       </c>
       <c r="D556" s="2" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="E556" s="1" t="s">
         <v>19</v>
@@ -24649,7 +24679,7 @@
         <v>30</v>
       </c>
       <c r="H556" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I556" s="23">
         <v>46215</v>
@@ -24682,7 +24712,7 @@
         <v>30</v>
       </c>
       <c r="H557" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="I557" s="23">
         <v>46149</v>
@@ -24703,7 +24733,7 @@
         <v>11</v>
       </c>
       <c r="D558" s="2" t="s">
-        <v>1433</v>
+        <v>1430</v>
       </c>
       <c r="E558" s="1" t="s">
         <v>19</v>
@@ -24715,7 +24745,7 @@
         <v>30</v>
       </c>
       <c r="H558" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I558" s="54">
         <v>46293</v>
@@ -24736,7 +24766,7 @@
         <v>11</v>
       </c>
       <c r="D559" s="2" t="s">
-        <v>1434</v>
+        <v>1431</v>
       </c>
       <c r="E559" s="1" t="s">
         <v>19</v>
@@ -24748,7 +24778,7 @@
         <v>30</v>
       </c>
       <c r="H559" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I559" s="54">
         <v>46293</v>
@@ -24769,7 +24799,7 @@
         <v>11</v>
       </c>
       <c r="D560" s="2" t="s">
-        <v>1435</v>
+        <v>1432</v>
       </c>
       <c r="E560" s="1" t="s">
         <v>19</v>
@@ -24781,7 +24811,7 @@
         <v>30</v>
       </c>
       <c r="H560" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I560" s="54">
         <v>46293</v>
@@ -24802,7 +24832,7 @@
         <v>11</v>
       </c>
       <c r="D561" s="2" t="s">
-        <v>1437</v>
+        <v>1434</v>
       </c>
       <c r="E561" s="1" t="s">
         <v>19</v>
@@ -24814,7 +24844,7 @@
         <v>30</v>
       </c>
       <c r="H561" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I561" s="54">
         <v>46293</v>
@@ -24835,7 +24865,7 @@
         <v>11</v>
       </c>
       <c r="D562" s="2" t="s">
-        <v>1439</v>
+        <v>1436</v>
       </c>
       <c r="E562" s="1" t="s">
         <v>19</v>
@@ -24847,7 +24877,7 @@
         <v>30</v>
       </c>
       <c r="H562" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I562" s="54">
         <v>46279</v>
@@ -24868,7 +24898,7 @@
         <v>11</v>
       </c>
       <c r="D563" s="2" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="E563" s="1" t="s">
         <v>19</v>
@@ -24880,7 +24910,7 @@
         <v>30</v>
       </c>
       <c r="H563" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I563" s="54">
         <v>46287</v>
@@ -24901,7 +24931,7 @@
         <v>11</v>
       </c>
       <c r="D564" s="2" t="s">
-        <v>1441</v>
+        <v>1438</v>
       </c>
       <c r="E564" s="1" t="s">
         <v>19</v>
@@ -24913,7 +24943,7 @@
         <v>30</v>
       </c>
       <c r="H564" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I564" s="54">
         <v>46287</v>
@@ -24934,7 +24964,7 @@
         <v>11</v>
       </c>
       <c r="D565" s="2" t="s">
-        <v>1442</v>
+        <v>1439</v>
       </c>
       <c r="E565" s="1" t="s">
         <v>19</v>
@@ -24946,7 +24976,7 @@
         <v>30</v>
       </c>
       <c r="H565" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I565" s="54">
         <v>46287</v>
@@ -24967,7 +24997,7 @@
         <v>11</v>
       </c>
       <c r="D566" s="2" t="s">
-        <v>1443</v>
+        <v>1440</v>
       </c>
       <c r="E566" s="1" t="s">
         <v>19</v>
@@ -24979,7 +25009,7 @@
         <v>30</v>
       </c>
       <c r="H566" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I566" s="54">
         <v>46287</v>
@@ -25000,7 +25030,7 @@
         <v>11</v>
       </c>
       <c r="D567" s="2" t="s">
-        <v>1444</v>
+        <v>1441</v>
       </c>
       <c r="E567" s="1" t="s">
         <v>19</v>
@@ -25012,7 +25042,7 @@
         <v>30</v>
       </c>
       <c r="H567" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I567" s="54">
         <v>46287</v>
@@ -25033,7 +25063,7 @@
         <v>11</v>
       </c>
       <c r="D568" s="2" t="s">
-        <v>1445</v>
+        <v>1442</v>
       </c>
       <c r="E568" s="1" t="s">
         <v>19</v>
@@ -25045,7 +25075,7 @@
         <v>30</v>
       </c>
       <c r="H568" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I568" s="54">
         <v>46287</v>
@@ -25066,7 +25096,7 @@
         <v>11</v>
       </c>
       <c r="D569" s="2" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
       <c r="E569" s="1" t="s">
         <v>19</v>
@@ -25078,7 +25108,7 @@
         <v>30</v>
       </c>
       <c r="H569" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I569" s="54">
         <v>46287</v>
@@ -25099,19 +25129,19 @@
         <v>11</v>
       </c>
       <c r="D570" s="2" t="s">
-        <v>1451</v>
+        <v>1448</v>
       </c>
       <c r="E570" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F570" s="1" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
       <c r="G570" s="1" t="s">
         <v>30</v>
       </c>
       <c r="H570" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I570" s="54">
         <v>46287</v>
@@ -25132,7 +25162,7 @@
         <v>11</v>
       </c>
       <c r="D571" s="2" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="E571" s="1" t="s">
         <v>21</v>
@@ -25144,7 +25174,7 @@
         <v>30</v>
       </c>
       <c r="H571" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I571" s="54">
         <v>46287</v>
@@ -25153,7 +25183,7 @@
         <v>574</v>
       </c>
       <c r="K571" s="3" t="s">
-        <v>1457</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="572" spans="1:11">
@@ -25167,7 +25197,7 @@
         <v>11</v>
       </c>
       <c r="D572" s="2" t="s">
-        <v>1453</v>
+        <v>1450</v>
       </c>
       <c r="E572" s="1" t="s">
         <v>19</v>
@@ -25179,7 +25209,7 @@
         <v>30</v>
       </c>
       <c r="H572" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I572" s="54">
         <v>46287</v>
@@ -25200,7 +25230,7 @@
         <v>11</v>
       </c>
       <c r="D573" s="2" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
       <c r="E573" s="1" t="s">
         <v>19</v>
@@ -25212,7 +25242,7 @@
         <v>30</v>
       </c>
       <c r="H573" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I573" s="54">
         <v>46287</v>
@@ -25233,7 +25263,7 @@
         <v>11</v>
       </c>
       <c r="D574" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E574" s="1" t="s">
         <v>21</v>
@@ -25245,7 +25275,7 @@
         <v>30</v>
       </c>
       <c r="H574" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I574" s="54">
         <v>46287</v>
@@ -25266,7 +25296,7 @@
         <v>11</v>
       </c>
       <c r="D575" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E575" s="1" t="s">
         <v>21</v>
@@ -25278,7 +25308,7 @@
         <v>30</v>
       </c>
       <c r="H575" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I575" s="54">
         <v>46287</v>
@@ -25299,7 +25329,7 @@
         <v>11</v>
       </c>
       <c r="D576" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E576" s="1" t="s">
         <v>21</v>
@@ -25311,7 +25341,7 @@
         <v>30</v>
       </c>
       <c r="H576" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I576" s="54">
         <v>46287</v>
@@ -25332,7 +25362,7 @@
         <v>11</v>
       </c>
       <c r="D577" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E577" s="1" t="s">
         <v>21</v>
@@ -25344,7 +25374,7 @@
         <v>30</v>
       </c>
       <c r="H577" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I577" s="54">
         <v>46287</v>
@@ -25365,7 +25395,7 @@
         <v>11</v>
       </c>
       <c r="D578" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E578" s="1" t="s">
         <v>21</v>
@@ -25377,7 +25407,7 @@
         <v>30</v>
       </c>
       <c r="H578" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I578" s="54">
         <v>46287</v>
@@ -25398,7 +25428,7 @@
         <v>11</v>
       </c>
       <c r="D579" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E579" s="1" t="s">
         <v>21</v>
@@ -25410,7 +25440,7 @@
         <v>30</v>
       </c>
       <c r="H579" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I579" s="54">
         <v>46287</v>
@@ -25431,7 +25461,7 @@
         <v>11</v>
       </c>
       <c r="D580" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E580" s="1" t="s">
         <v>21</v>
@@ -25443,7 +25473,7 @@
         <v>30</v>
       </c>
       <c r="H580" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I580" s="54">
         <v>46287</v>
@@ -25464,7 +25494,7 @@
         <v>11</v>
       </c>
       <c r="D581" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E581" s="1" t="s">
         <v>21</v>
@@ -25476,7 +25506,7 @@
         <v>30</v>
       </c>
       <c r="H581" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I581" s="54">
         <v>46287</v>
@@ -25497,7 +25527,7 @@
         <v>11</v>
       </c>
       <c r="D582" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E582" s="1" t="s">
         <v>21</v>
@@ -25509,7 +25539,7 @@
         <v>30</v>
       </c>
       <c r="H582" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="I582" s="54">
         <v>46287</v>
@@ -25542,7 +25572,7 @@
         <v>30</v>
       </c>
       <c r="H583" s="1" t="s">
-        <v>1459</v>
+        <v>1456</v>
       </c>
       <c r="I583" s="23">
         <v>46063</v>
@@ -25575,7 +25605,7 @@
         <v>30</v>
       </c>
       <c r="H584" s="1" t="s">
-        <v>1459</v>
+        <v>1456</v>
       </c>
       <c r="I584" s="23">
         <v>46161</v>
@@ -25587,116 +25617,127 @@
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="duplicateValues" dxfId="46" priority="21"/>
+  <conditionalFormatting sqref="D1:D517 D519:D1048576">
+    <cfRule type="duplicateValues" dxfId="49" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D268">
-    <cfRule type="duplicateValues" dxfId="45" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D366">
-    <cfRule type="duplicateValues" dxfId="42" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D367">
-    <cfRule type="duplicateValues" dxfId="41" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="112"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D502 D2:D367">
-    <cfRule type="duplicateValues" dxfId="40" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="103"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:E258 G215 E525:E1048576">
-    <cfRule type="cellIs" dxfId="39" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="33" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E260:E524">
-    <cfRule type="cellIs" dxfId="38" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="29" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F252 F254:F255 F257:F387 F389:F559 F561:F562 F564:F1048576">
-    <cfRule type="cellIs" dxfId="37" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="26" operator="equal">
       <formula>"DOADORA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F252 F254:F255 F561:F562 F564:F1048576">
-    <cfRule type="cellIs" dxfId="36" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="34" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F252 F389:F559 F254:F255 F257:F387 F561:F562 F564:F1048576">
-    <cfRule type="cellIs" dxfId="35" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="25" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F252">
-    <cfRule type="cellIs" dxfId="34" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="5" operator="equal">
       <formula>"DEPOSITO SOLAGOS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F18">
-    <cfRule type="cellIs" dxfId="33" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="9" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F25">
-    <cfRule type="cellIs" dxfId="32" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="4" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F254:F255 F561:F562 F564:F1048576">
-    <cfRule type="cellIs" dxfId="31" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="35" operator="equal">
       <formula>"DEPOSITO SOLAGOS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F257:F387 F389:F559">
-    <cfRule type="cellIs" dxfId="30" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="30" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F257:F387">
-    <cfRule type="cellIs" dxfId="29" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="31" operator="equal">
       <formula>"DEPOSITO SOLAGOS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F389:F559">
-    <cfRule type="cellIs" dxfId="28" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="7" operator="equal">
       <formula>"DEPOSITO SOLAGOS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F555">
-    <cfRule type="cellIs" dxfId="27" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="6" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:H258">
-    <cfRule type="cellIs" dxfId="26" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="8" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H260:H524">
-    <cfRule type="cellIs" dxfId="25" priority="9" operator="equal">
+  <conditionalFormatting sqref="H260:H517 H519:H524">
+    <cfRule type="cellIs" dxfId="28" priority="12" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H526:H584">
-    <cfRule type="cellIs" dxfId="24" priority="13" operator="equal">
+  <conditionalFormatting sqref="H526:H547 H549:H584">
+    <cfRule type="cellIs" dxfId="27" priority="16" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K215">
-    <cfRule type="cellIs" dxfId="23" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="20" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="21" operator="equal">
       <formula>"DOADORA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="22" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="23" operator="equal">
       <formula>"DEPOSITO SOLAGOS"</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H548">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"SOLAGOS DEPOSITO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H518">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D518">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -28093,51 +28134,51 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="D2:D51">
-    <cfRule type="duplicateValues" dxfId="19" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D52">
-    <cfRule type="duplicateValues" dxfId="18" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D53">
-    <cfRule type="duplicateValues" dxfId="17" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E51">
-    <cfRule type="cellIs" dxfId="14" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="16" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E52:E53">
-    <cfRule type="cellIs" dxfId="13" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="5" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F51">
-    <cfRule type="cellIs" dxfId="12" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="17" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="18" operator="equal">
       <formula>"DOADORA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="20" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="21" operator="equal">
       <formula>"DEPOSITO SOLAGOS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F52:F53">
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="3" operator="equal">
       <formula>"DOADORA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="7" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="8" operator="equal">
       <formula>"DEPOSITO SOLAGOS"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28165,16 +28206,16 @@
         <v>4</v>
       </c>
       <c r="B1" s="58" t="s">
-        <v>1383</v>
+        <v>1380</v>
       </c>
       <c r="C1" t="s">
-        <v>1384</v>
+        <v>1381</v>
       </c>
       <c r="D1" t="s">
         <v>690</v>
       </c>
       <c r="E1" t="s">
-        <v>1385</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -28191,7 +28232,7 @@
         <v>46132</v>
       </c>
       <c r="E2" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -28208,7 +28249,7 @@
         <v>46147</v>
       </c>
       <c r="E3" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -28225,7 +28266,7 @@
         <v>46244</v>
       </c>
       <c r="E4" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -28242,7 +28283,7 @@
         <v>46264</v>
       </c>
       <c r="E5" t="s">
-        <v>1386</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -28259,7 +28300,7 @@
         <v>46279</v>
       </c>
       <c r="E6" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -28276,7 +28317,7 @@
         <v>46282</v>
       </c>
       <c r="E7" t="s">
-        <v>1386</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -28284,7 +28325,7 @@
         <v>19</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
       <c r="C8">
         <v>5899</v>
@@ -28293,26 +28334,26 @@
         <v>46295</v>
       </c>
       <c r="E8" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
-    <cfRule type="cellIs" dxfId="4" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="23" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B8">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
       <formula>"DOADORA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>"DEPOSITO SOLAGOS"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/data_printer.xlsx
+++ b/data_printer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erick\Desktop\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E77478D-A735-4341-A59E-918972BD96BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E698F25-CFBD-4F43-9F14-8760F0AC7BF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A8AA41B5-7AA1-4FF7-A9B8-54B8A4E1AF28}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5381" uniqueCount="1468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5382" uniqueCount="1472">
   <si>
     <t>INDICE</t>
   </si>
@@ -4452,6 +4452,18 @@
   </si>
   <si>
     <t>LOCACAO</t>
+  </si>
+  <si>
+    <t>XBJZ037402</t>
+  </si>
+  <si>
+    <t>XBJZ037398</t>
+  </si>
+  <si>
+    <t>SEDUC - EDUCAÇÃO INFANTIL</t>
+  </si>
+  <si>
+    <t>OPERACIONAL</t>
   </si>
 </sst>
 </file>
@@ -4826,37 +4838,7 @@
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="76">
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="75">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -5097,6 +5079,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -5239,6 +5231,16 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5693,23 +5695,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}" name="Controle_Inventario_Impressoras" displayName="Controle_Inventario_Impressoras" ref="A1:K584" tableType="queryTable" totalsRowShown="0" headerRowDxfId="75" dataDxfId="74">
-  <autoFilter ref="A1:K584" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}" name="Controle_Inventario_Impressoras" displayName="Controle_Inventario_Impressoras" ref="A1:K584" tableType="queryTable" totalsRowShown="0" headerRowDxfId="74" dataDxfId="73">
+  <autoFilter ref="A1:K584" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="SEDUC"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K37">
     <sortCondition ref="A23"/>
   </sortState>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F8E3D681-C494-47F2-8429-052381C12AF1}" uniqueName="1" name="INDICE" queryTableFieldId="1" dataDxfId="73"/>
-    <tableColumn id="2" xr3:uid="{EE2E8FA5-A99D-4573-9868-408DB8FD4417}" uniqueName="2" name="MODELO" queryTableFieldId="2" dataDxfId="72"/>
-    <tableColumn id="11" xr3:uid="{CB5196C0-CCA1-4329-825F-D71E0948A542}" uniqueName="11" name="TIPO" queryTableFieldId="16390" dataDxfId="71"/>
-    <tableColumn id="3" xr3:uid="{27BC8F35-CC2C-44A1-BAF7-B0390B09477F}" uniqueName="3" name="NUMERO DE SERIE" queryTableFieldId="3" dataDxfId="70"/>
-    <tableColumn id="4" xr3:uid="{552F7A6E-6277-4DC1-9CDA-EA7FDCCE8E36}" uniqueName="4" name="LOCALIZAÇÃO" queryTableFieldId="4" dataDxfId="69"/>
-    <tableColumn id="5" xr3:uid="{4C8345F1-6E01-4566-9030-039665486C03}" uniqueName="5" name="SETOR" queryTableFieldId="5" dataDxfId="68"/>
-    <tableColumn id="9" xr3:uid="{10436F87-F6F1-46C4-A81A-8D144AC72FDF}" uniqueName="9" name="EMPRESA" queryTableFieldId="16389" dataDxfId="67"/>
-    <tableColumn id="13" xr3:uid="{40F07CF2-DF5F-4979-A5BB-71FA79C89740}" uniqueName="13" name="GRUPO" queryTableFieldId="16393" dataDxfId="66"/>
-    <tableColumn id="6" xr3:uid="{B7941BA2-3E1C-476B-A3C7-BA155A35A2D0}" uniqueName="6" name="ATUALIZADO" queryTableFieldId="6" dataDxfId="65"/>
-    <tableColumn id="7" xr3:uid="{4338F703-CE4B-4443-8A10-74F64ED8CD42}" uniqueName="7" name="PRINTWAY" queryTableFieldId="16391" dataDxfId="64"/>
-    <tableColumn id="8" xr3:uid="{02B7C1FB-8EA9-4F22-BCCF-3D1809FFEDCC}" uniqueName="8" name="OBSERVAÇÃO" queryTableFieldId="8" dataDxfId="63"/>
+    <tableColumn id="1" xr3:uid="{F8E3D681-C494-47F2-8429-052381C12AF1}" uniqueName="1" name="INDICE" queryTableFieldId="1" dataDxfId="72"/>
+    <tableColumn id="2" xr3:uid="{EE2E8FA5-A99D-4573-9868-408DB8FD4417}" uniqueName="2" name="MODELO" queryTableFieldId="2" dataDxfId="71"/>
+    <tableColumn id="11" xr3:uid="{CB5196C0-CCA1-4329-825F-D71E0948A542}" uniqueName="11" name="TIPO" queryTableFieldId="16390" dataDxfId="70"/>
+    <tableColumn id="3" xr3:uid="{27BC8F35-CC2C-44A1-BAF7-B0390B09477F}" uniqueName="3" name="NUMERO DE SERIE" queryTableFieldId="3" dataDxfId="69"/>
+    <tableColumn id="4" xr3:uid="{552F7A6E-6277-4DC1-9CDA-EA7FDCCE8E36}" uniqueName="4" name="LOCALIZAÇÃO" queryTableFieldId="4" dataDxfId="68"/>
+    <tableColumn id="5" xr3:uid="{4C8345F1-6E01-4566-9030-039665486C03}" uniqueName="5" name="SETOR" queryTableFieldId="5" dataDxfId="67"/>
+    <tableColumn id="9" xr3:uid="{10436F87-F6F1-46C4-A81A-8D144AC72FDF}" uniqueName="9" name="EMPRESA" queryTableFieldId="16389" dataDxfId="66"/>
+    <tableColumn id="13" xr3:uid="{40F07CF2-DF5F-4979-A5BB-71FA79C89740}" uniqueName="13" name="GRUPO" queryTableFieldId="16393" dataDxfId="65"/>
+    <tableColumn id="6" xr3:uid="{B7941BA2-3E1C-476B-A3C7-BA155A35A2D0}" uniqueName="6" name="ATUALIZADO" queryTableFieldId="6" dataDxfId="64"/>
+    <tableColumn id="7" xr3:uid="{4338F703-CE4B-4443-8A10-74F64ED8CD42}" uniqueName="7" name="PRINTWAY" queryTableFieldId="16391" dataDxfId="63"/>
+    <tableColumn id="8" xr3:uid="{02B7C1FB-8EA9-4F22-BCCF-3D1809FFEDCC}" uniqueName="8" name="OBSERVAÇÃO" queryTableFieldId="8" dataDxfId="62"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5724,26 +5732,26 @@
     <tableColumn id="3" xr3:uid="{95A3DCD3-FE19-4A74-9940-661D6BB94B25}" name="MODELO"/>
     <tableColumn id="4" xr3:uid="{521C03E5-7FA9-4789-8198-9E0781F3ABC7}" name="DESCRIÇÃO"/>
     <tableColumn id="5" xr3:uid="{579D81F0-AA4C-4609-BF35-AF838B2B149B}" name="COR"/>
-    <tableColumn id="6" xr3:uid="{19487D13-EF31-43DA-89CA-4AA1E1029C34}" name="QUANTIDADE" dataDxfId="62"/>
+    <tableColumn id="6" xr3:uid="{19487D13-EF31-43DA-89CA-4AA1E1029C34}" name="QUANTIDADE" dataDxfId="61"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FBC7B6D1-65BC-435E-B4FF-CC495249D6BD}" name="Tabela4" displayName="Tabela4" ref="A1:J51" insertRowShift="1" totalsRowShown="0" headerRowDxfId="61" dataDxfId="60">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FBC7B6D1-65BC-435E-B4FF-CC495249D6BD}" name="Tabela4" displayName="Tabela4" ref="A1:J51" insertRowShift="1" totalsRowShown="0" headerRowDxfId="60" dataDxfId="59">
   <autoFilter ref="A1:J51" xr:uid="{FBC7B6D1-65BC-435E-B4FF-CC495249D6BD}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{A3ABFE90-9D3C-42DA-8CF0-D71D91CAB9BB}" name="INDICE" dataDxfId="59"/>
-    <tableColumn id="2" xr3:uid="{A733301C-FC8A-4542-8BA2-BBEA67F3D424}" name="MODELO" dataDxfId="58"/>
-    <tableColumn id="3" xr3:uid="{C6E07CD7-A3F4-4433-BB55-99FA29AE99FA}" name="TIPO" dataDxfId="57"/>
-    <tableColumn id="4" xr3:uid="{007A788B-09E3-480D-A6BC-6718BD4566C1}" name="SERIAL" dataDxfId="56"/>
-    <tableColumn id="5" xr3:uid="{ACA8BAA3-86EA-4046-9E8D-0C6E6216A0B1}" name="LOCALIDADE" dataDxfId="55"/>
-    <tableColumn id="6" xr3:uid="{D2E86C5C-2786-4CA5-9B36-02C6270BDE33}" name="SETOR" dataDxfId="54"/>
-    <tableColumn id="7" xr3:uid="{3F4C4914-DB98-431A-AD17-7760541C7F42}" name="EMPRESA" dataDxfId="53"/>
-    <tableColumn id="8" xr3:uid="{4F681722-ADFE-4A58-BC0F-8623348ECD33}" name="DATA" dataDxfId="52"/>
-    <tableColumn id="9" xr3:uid="{13FFF32F-FC49-429E-BD6E-76ADCE6F7534}" name="MONIT." dataDxfId="51"/>
-    <tableColumn id="10" xr3:uid="{F4255CFF-6FAD-434F-93D8-3A0C54269527}" name="DETALHES" dataDxfId="50"/>
+    <tableColumn id="1" xr3:uid="{A3ABFE90-9D3C-42DA-8CF0-D71D91CAB9BB}" name="INDICE" dataDxfId="58"/>
+    <tableColumn id="2" xr3:uid="{A733301C-FC8A-4542-8BA2-BBEA67F3D424}" name="MODELO" dataDxfId="57"/>
+    <tableColumn id="3" xr3:uid="{C6E07CD7-A3F4-4433-BB55-99FA29AE99FA}" name="TIPO" dataDxfId="56"/>
+    <tableColumn id="4" xr3:uid="{007A788B-09E3-480D-A6BC-6718BD4566C1}" name="SERIAL" dataDxfId="55"/>
+    <tableColumn id="5" xr3:uid="{ACA8BAA3-86EA-4046-9E8D-0C6E6216A0B1}" name="LOCALIDADE" dataDxfId="54"/>
+    <tableColumn id="6" xr3:uid="{D2E86C5C-2786-4CA5-9B36-02C6270BDE33}" name="SETOR" dataDxfId="53"/>
+    <tableColumn id="7" xr3:uid="{3F4C4914-DB98-431A-AD17-7760541C7F42}" name="EMPRESA" dataDxfId="52"/>
+    <tableColumn id="8" xr3:uid="{4F681722-ADFE-4A58-BC0F-8623348ECD33}" name="DATA" dataDxfId="51"/>
+    <tableColumn id="9" xr3:uid="{13FFF32F-FC49-429E-BD6E-76ADCE6F7534}" name="MONIT." dataDxfId="50"/>
+    <tableColumn id="10" xr3:uid="{F4255CFF-6FAD-434F-93D8-3A0C54269527}" name="DETALHES" dataDxfId="49"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6098,7 +6106,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" hidden="1">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -6131,7 +6139,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" hidden="1">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -6164,7 +6172,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" hidden="1">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -6197,7 +6205,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" hidden="1">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -6230,7 +6238,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" hidden="1">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -6263,7 +6271,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" hidden="1">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -6296,7 +6304,7 @@
       </c>
       <c r="K7" s="55"/>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" hidden="1">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -6329,7 +6337,7 @@
       </c>
       <c r="K8" s="55"/>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" hidden="1">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -6362,7 +6370,7 @@
       </c>
       <c r="K9" s="55"/>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" hidden="1">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -6395,7 +6403,7 @@
       </c>
       <c r="K10" s="55"/>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" hidden="1">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -6428,7 +6436,7 @@
       </c>
       <c r="K11" s="55"/>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" hidden="1">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -6461,7 +6469,7 @@
       </c>
       <c r="K12" s="55"/>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" hidden="1">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -6494,7 +6502,7 @@
       </c>
       <c r="K13" s="55"/>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" hidden="1">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -6527,7 +6535,7 @@
       </c>
       <c r="K14" s="55"/>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" hidden="1">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -6560,7 +6568,7 @@
       </c>
       <c r="K15" s="55"/>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" hidden="1">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -6593,7 +6601,7 @@
       </c>
       <c r="K16" s="55"/>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" hidden="1">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -6661,7 +6669,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" hidden="1">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -6692,7 +6700,7 @@
       </c>
       <c r="K19" s="7"/>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" hidden="1">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -6723,7 +6731,7 @@
       </c>
       <c r="K20" s="7"/>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" hidden="1">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -6758,7 +6766,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" hidden="1">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -6793,7 +6801,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" hidden="1">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -6826,7 +6834,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" hidden="1">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -6861,7 +6869,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" hidden="1">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -6896,7 +6904,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" hidden="1">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -6926,7 +6934,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" hidden="1">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -6959,7 +6967,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" hidden="1">
       <c r="A28" s="4">
         <v>27</v>
       </c>
@@ -6992,7 +7000,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" hidden="1">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -7025,7 +7033,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" hidden="1">
       <c r="A30" s="4">
         <v>29</v>
       </c>
@@ -7060,7 +7068,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" hidden="1">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -7093,7 +7101,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="15.75" customHeight="1">
+    <row r="32" spans="1:11" ht="15.75" hidden="1" customHeight="1">
       <c r="A32" s="4">
         <v>31</v>
       </c>
@@ -7126,7 +7134,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" hidden="1">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -7159,7 +7167,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" hidden="1">
       <c r="A34" s="4">
         <v>33</v>
       </c>
@@ -7192,7 +7200,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" hidden="1">
       <c r="A35" s="4">
         <v>34</v>
       </c>
@@ -7225,7 +7233,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" hidden="1">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -7255,7 +7263,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" hidden="1">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -7285,7 +7293,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" hidden="1">
       <c r="A38" s="4">
         <v>37</v>
       </c>
@@ -7318,7 +7326,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" hidden="1">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -7351,7 +7359,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" hidden="1">
       <c r="A40" s="4">
         <v>39</v>
       </c>
@@ -7384,7 +7392,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" hidden="1">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -7417,7 +7425,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" hidden="1">
       <c r="A42" s="4">
         <v>41</v>
       </c>
@@ -7450,7 +7458,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" hidden="1">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -7483,7 +7491,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" hidden="1">
       <c r="A44" s="4">
         <v>43</v>
       </c>
@@ -7518,7 +7526,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" hidden="1">
       <c r="A45" s="4">
         <v>44</v>
       </c>
@@ -7551,7 +7559,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" hidden="1">
       <c r="A46" s="4">
         <v>45</v>
       </c>
@@ -7584,7 +7592,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" hidden="1">
       <c r="A47" s="4">
         <v>46</v>
       </c>
@@ -7614,7 +7622,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" hidden="1">
       <c r="A48" s="4">
         <v>47</v>
       </c>
@@ -7647,7 +7655,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:11" hidden="1">
       <c r="A49" s="4">
         <v>48</v>
       </c>
@@ -7680,7 +7688,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:11" hidden="1">
       <c r="A50" s="4">
         <v>49</v>
       </c>
@@ -7713,7 +7721,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:11" hidden="1">
       <c r="A51" s="4">
         <v>50</v>
       </c>
@@ -7746,7 +7754,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:11" hidden="1">
       <c r="A52" s="4">
         <v>51</v>
       </c>
@@ -7779,7 +7787,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:11" hidden="1">
       <c r="A53" s="4">
         <v>52</v>
       </c>
@@ -7812,7 +7820,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:11" hidden="1">
       <c r="A54" s="4">
         <v>53</v>
       </c>
@@ -7845,7 +7853,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:11" hidden="1">
       <c r="A55" s="4">
         <v>54</v>
       </c>
@@ -7875,7 +7883,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:11" hidden="1">
       <c r="A56" s="4">
         <v>55</v>
       </c>
@@ -7908,7 +7916,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:11" hidden="1">
       <c r="A57" s="4">
         <v>56</v>
       </c>
@@ -7941,7 +7949,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:11" hidden="1">
       <c r="A58" s="4">
         <v>57</v>
       </c>
@@ -7974,7 +7982,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:11" hidden="1">
       <c r="A59" s="4">
         <v>58</v>
       </c>
@@ -8004,7 +8012,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60" spans="1:11" hidden="1">
       <c r="A60" s="4">
         <v>59</v>
       </c>
@@ -8034,7 +8042,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61" spans="1:11" hidden="1">
       <c r="A61" s="4">
         <v>60</v>
       </c>
@@ -8067,7 +8075,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="62" spans="1:11">
+    <row r="62" spans="1:11" hidden="1">
       <c r="A62" s="4">
         <v>61</v>
       </c>
@@ -8102,7 +8110,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:11" hidden="1">
       <c r="A63" s="4">
         <v>62</v>
       </c>
@@ -8137,7 +8145,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64" spans="1:11" hidden="1">
       <c r="A64" s="4">
         <v>63</v>
       </c>
@@ -8172,7 +8180,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="65" spans="1:11">
+    <row r="65" spans="1:11" hidden="1">
       <c r="A65" s="4">
         <v>64</v>
       </c>
@@ -8202,7 +8210,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="66" spans="1:11">
+    <row r="66" spans="1:11" hidden="1">
       <c r="A66" s="4">
         <v>65</v>
       </c>
@@ -8232,7 +8240,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="67" spans="1:11">
+    <row r="67" spans="1:11" hidden="1">
       <c r="A67" s="4">
         <v>66</v>
       </c>
@@ -8262,7 +8270,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="68" spans="1:11">
+    <row r="68" spans="1:11" hidden="1">
       <c r="A68" s="4">
         <v>67</v>
       </c>
@@ -8292,7 +8300,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="69" spans="1:11">
+    <row r="69" spans="1:11" hidden="1">
       <c r="A69" s="4">
         <v>68</v>
       </c>
@@ -8322,7 +8330,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="70" spans="1:11">
+    <row r="70" spans="1:11" hidden="1">
       <c r="A70" s="4">
         <v>69</v>
       </c>
@@ -8352,7 +8360,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="71" spans="1:11">
+    <row r="71" spans="1:11" hidden="1">
       <c r="A71" s="4">
         <v>70</v>
       </c>
@@ -8385,7 +8393,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="72" spans="1:11">
+    <row r="72" spans="1:11" hidden="1">
       <c r="A72" s="4">
         <v>71</v>
       </c>
@@ -8418,7 +8426,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="73" spans="1:11">
+    <row r="73" spans="1:11" hidden="1">
       <c r="A73" s="4">
         <v>72</v>
       </c>
@@ -8448,7 +8456,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="74" spans="1:11">
+    <row r="74" spans="1:11" hidden="1">
       <c r="A74" s="4">
         <v>73</v>
       </c>
@@ -8481,7 +8489,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="75" spans="1:11">
+    <row r="75" spans="1:11" hidden="1">
       <c r="A75" s="4">
         <v>74</v>
       </c>
@@ -8511,7 +8519,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="76" spans="1:11">
+    <row r="76" spans="1:11" hidden="1">
       <c r="A76" s="4">
         <v>75</v>
       </c>
@@ -8541,7 +8549,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="77" spans="1:11">
+    <row r="77" spans="1:11" hidden="1">
       <c r="A77" s="4">
         <v>76</v>
       </c>
@@ -8571,7 +8579,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="78" spans="1:11">
+    <row r="78" spans="1:11" hidden="1">
       <c r="A78" s="4">
         <v>77</v>
       </c>
@@ -8601,7 +8609,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="79" spans="1:11">
+    <row r="79" spans="1:11" hidden="1">
       <c r="A79" s="4">
         <v>78</v>
       </c>
@@ -8634,7 +8642,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80" spans="1:11" hidden="1">
       <c r="A80" s="4">
         <v>79</v>
       </c>
@@ -8667,7 +8675,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="81" spans="1:11">
+    <row r="81" spans="1:11" hidden="1">
       <c r="A81" s="4">
         <v>80</v>
       </c>
@@ -8697,7 +8705,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="82" spans="1:11">
+    <row r="82" spans="1:11" hidden="1">
       <c r="A82" s="4">
         <v>81</v>
       </c>
@@ -8732,7 +8740,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="83" spans="1:11">
+    <row r="83" spans="1:11" hidden="1">
       <c r="A83" s="4">
         <v>82</v>
       </c>
@@ -8765,7 +8773,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="84" spans="1:11">
+    <row r="84" spans="1:11" hidden="1">
       <c r="A84" s="4">
         <v>83</v>
       </c>
@@ -8798,7 +8806,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="85" spans="1:11">
+    <row r="85" spans="1:11" hidden="1">
       <c r="A85" s="4">
         <v>84</v>
       </c>
@@ -8828,7 +8836,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="86" spans="1:11">
+    <row r="86" spans="1:11" hidden="1">
       <c r="A86" s="4">
         <v>85</v>
       </c>
@@ -8861,7 +8869,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="87" spans="1:11">
+    <row r="87" spans="1:11" hidden="1">
       <c r="A87" s="4">
         <v>86</v>
       </c>
@@ -8894,7 +8902,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="88" spans="1:11">
+    <row r="88" spans="1:11" hidden="1">
       <c r="A88" s="4">
         <v>87</v>
       </c>
@@ -8927,7 +8935,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="89" spans="1:11">
+    <row r="89" spans="1:11" hidden="1">
       <c r="A89" s="4">
         <v>88</v>
       </c>
@@ -8960,7 +8968,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="90" spans="1:11">
+    <row r="90" spans="1:11" hidden="1">
       <c r="A90" s="4">
         <v>89</v>
       </c>
@@ -8993,7 +9001,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="91" spans="1:11">
+    <row r="91" spans="1:11" hidden="1">
       <c r="A91" s="4">
         <v>90</v>
       </c>
@@ -9026,7 +9034,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="92" spans="1:11">
+    <row r="92" spans="1:11" hidden="1">
       <c r="A92" s="4">
         <v>91</v>
       </c>
@@ -9053,7 +9061,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="93" spans="1:11">
+    <row r="93" spans="1:11" hidden="1">
       <c r="A93" s="4">
         <v>92</v>
       </c>
@@ -9080,7 +9088,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="94" spans="1:11">
+    <row r="94" spans="1:11" hidden="1">
       <c r="A94" s="4">
         <v>93</v>
       </c>
@@ -9107,7 +9115,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="95" spans="1:11">
+    <row r="95" spans="1:11" hidden="1">
       <c r="A95" s="4">
         <v>94</v>
       </c>
@@ -9140,7 +9148,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="96" spans="1:11">
+    <row r="96" spans="1:11" hidden="1">
       <c r="A96" s="4">
         <v>95</v>
       </c>
@@ -9208,7 +9216,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="98" spans="1:11">
+    <row r="98" spans="1:11" hidden="1">
       <c r="A98" s="4">
         <v>97</v>
       </c>
@@ -9241,7 +9249,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="99" spans="1:11">
+    <row r="99" spans="1:11" hidden="1">
       <c r="A99" s="4">
         <v>98</v>
       </c>
@@ -9271,7 +9279,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="100" spans="1:11">
+    <row r="100" spans="1:11" hidden="1">
       <c r="A100" s="4">
         <v>99</v>
       </c>
@@ -9304,7 +9312,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="101" spans="1:11">
+    <row r="101" spans="1:11" hidden="1">
       <c r="A101" s="4">
         <v>100</v>
       </c>
@@ -9337,7 +9345,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="102" spans="1:11">
+    <row r="102" spans="1:11" hidden="1">
       <c r="A102" s="4">
         <v>101</v>
       </c>
@@ -9364,7 +9372,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="103" spans="1:11">
+    <row r="103" spans="1:11" hidden="1">
       <c r="A103" s="4">
         <v>102</v>
       </c>
@@ -9391,7 +9399,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="104" spans="1:11">
+    <row r="104" spans="1:11" hidden="1">
       <c r="A104" s="4">
         <v>103</v>
       </c>
@@ -9424,7 +9432,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="105" spans="1:11">
+    <row r="105" spans="1:11" hidden="1">
       <c r="A105" s="4">
         <v>104</v>
       </c>
@@ -9454,7 +9462,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="106" spans="1:11">
+    <row r="106" spans="1:11" hidden="1">
       <c r="A106" s="4">
         <v>105</v>
       </c>
@@ -9486,7 +9494,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="107" spans="1:11">
+    <row r="107" spans="1:11" hidden="1">
       <c r="A107" s="4">
         <v>106</v>
       </c>
@@ -9516,7 +9524,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="108" spans="1:11">
+    <row r="108" spans="1:11" hidden="1">
       <c r="A108" s="4">
         <v>107</v>
       </c>
@@ -9546,7 +9554,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="109" spans="1:11">
+    <row r="109" spans="1:11" hidden="1">
       <c r="A109" s="4">
         <v>108</v>
       </c>
@@ -9581,7 +9589,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="110" spans="1:11">
+    <row r="110" spans="1:11" hidden="1">
       <c r="A110" s="4">
         <v>109</v>
       </c>
@@ -9614,7 +9622,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="111" spans="1:11">
+    <row r="111" spans="1:11" hidden="1">
       <c r="A111" s="4">
         <v>110</v>
       </c>
@@ -9647,7 +9655,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="112" spans="1:11">
+    <row r="112" spans="1:11" hidden="1">
       <c r="A112" s="4">
         <v>111</v>
       </c>
@@ -9682,7 +9690,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="113" spans="1:11">
+    <row r="113" spans="1:11" hidden="1">
       <c r="A113" s="4">
         <v>112</v>
       </c>
@@ -9715,7 +9723,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="114" spans="1:11">
+    <row r="114" spans="1:11" hidden="1">
       <c r="A114" s="4">
         <v>113</v>
       </c>
@@ -9748,7 +9756,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="115" spans="1:11">
+    <row r="115" spans="1:11" hidden="1">
       <c r="A115" s="4">
         <v>114</v>
       </c>
@@ -9781,7 +9789,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="116" spans="1:11">
+    <row r="116" spans="1:11" hidden="1">
       <c r="A116" s="4">
         <v>115</v>
       </c>
@@ -9814,7 +9822,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="117" spans="1:11">
+    <row r="117" spans="1:11" hidden="1">
       <c r="A117" s="4">
         <v>116</v>
       </c>
@@ -9847,7 +9855,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="118" spans="1:11">
+    <row r="118" spans="1:11" hidden="1">
       <c r="A118" s="4">
         <v>117</v>
       </c>
@@ -9876,7 +9884,7 @@
       </c>
       <c r="K118" s="24"/>
     </row>
-    <row r="119" spans="1:11">
+    <row r="119" spans="1:11" hidden="1">
       <c r="A119" s="4">
         <v>118</v>
       </c>
@@ -9909,7 +9917,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="120" spans="1:11">
+    <row r="120" spans="1:11" hidden="1">
       <c r="A120" s="4">
         <v>119</v>
       </c>
@@ -9942,7 +9950,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="121" spans="1:11">
+    <row r="121" spans="1:11" hidden="1">
       <c r="A121" s="4">
         <v>120</v>
       </c>
@@ -9975,7 +9983,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="122" spans="1:11">
+    <row r="122" spans="1:11" hidden="1">
       <c r="A122" s="4">
         <v>121</v>
       </c>
@@ -10008,7 +10016,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="123" spans="1:11">
+    <row r="123" spans="1:11" hidden="1">
       <c r="A123" s="4">
         <v>122</v>
       </c>
@@ -10041,7 +10049,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="124" spans="1:11">
+    <row r="124" spans="1:11" hidden="1">
       <c r="A124" s="4">
         <v>123</v>
       </c>
@@ -10074,7 +10082,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="125" spans="1:11">
+    <row r="125" spans="1:11" hidden="1">
       <c r="A125" s="4">
         <v>124</v>
       </c>
@@ -10107,7 +10115,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="126" spans="1:11">
+    <row r="126" spans="1:11" hidden="1">
       <c r="A126" s="4">
         <v>125</v>
       </c>
@@ -10140,7 +10148,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="127" spans="1:11">
+    <row r="127" spans="1:11" hidden="1">
       <c r="A127" s="4">
         <v>126</v>
       </c>
@@ -10173,7 +10181,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="128" spans="1:11">
+    <row r="128" spans="1:11" hidden="1">
       <c r="A128" s="4">
         <v>127</v>
       </c>
@@ -10206,7 +10214,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="129" spans="1:11">
+    <row r="129" spans="1:11" hidden="1">
       <c r="A129" s="4">
         <v>128</v>
       </c>
@@ -10239,7 +10247,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="130" spans="1:11">
+    <row r="130" spans="1:11" hidden="1">
       <c r="A130" s="4">
         <v>129</v>
       </c>
@@ -10272,7 +10280,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="131" spans="1:11">
+    <row r="131" spans="1:11" hidden="1">
       <c r="A131" s="4">
         <v>130</v>
       </c>
@@ -10305,7 +10313,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="132" spans="1:11">
+    <row r="132" spans="1:11" hidden="1">
       <c r="A132" s="4">
         <v>131</v>
       </c>
@@ -10338,7 +10346,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="133" spans="1:11">
+    <row r="133" spans="1:11" hidden="1">
       <c r="A133" s="4">
         <v>132</v>
       </c>
@@ -10371,7 +10379,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="134" spans="1:11">
+    <row r="134" spans="1:11" hidden="1">
       <c r="A134" s="4">
         <v>133</v>
       </c>
@@ -10406,7 +10414,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="135" spans="1:11">
+    <row r="135" spans="1:11" hidden="1">
       <c r="A135" s="4">
         <v>134</v>
       </c>
@@ -10476,7 +10484,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="137" spans="1:11">
+    <row r="137" spans="1:11" hidden="1">
       <c r="A137" s="4">
         <v>136</v>
       </c>
@@ -10509,7 +10517,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="138" spans="1:11">
+    <row r="138" spans="1:11" hidden="1">
       <c r="A138" s="4">
         <v>137</v>
       </c>
@@ -10542,7 +10550,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="139" spans="1:11">
+    <row r="139" spans="1:11" hidden="1">
       <c r="A139" s="4">
         <v>138</v>
       </c>
@@ -10575,7 +10583,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="140" spans="1:11">
+    <row r="140" spans="1:11" hidden="1">
       <c r="A140" s="4">
         <v>139</v>
       </c>
@@ -10608,7 +10616,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="141" spans="1:11">
+    <row r="141" spans="1:11" hidden="1">
       <c r="A141" s="4">
         <v>140</v>
       </c>
@@ -10641,7 +10649,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="142" spans="1:11">
+    <row r="142" spans="1:11" hidden="1">
       <c r="A142" s="4">
         <v>141</v>
       </c>
@@ -10676,7 +10684,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="143" spans="1:11">
+    <row r="143" spans="1:11" hidden="1">
       <c r="A143" s="4">
         <v>142</v>
       </c>
@@ -10711,7 +10719,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="144" spans="1:11">
+    <row r="144" spans="1:11" hidden="1">
       <c r="A144" s="4">
         <v>143</v>
       </c>
@@ -10746,7 +10754,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="145" spans="1:11">
+    <row r="145" spans="1:11" hidden="1">
       <c r="A145" s="4">
         <v>144</v>
       </c>
@@ -10779,7 +10787,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="146" spans="1:11">
+    <row r="146" spans="1:11" hidden="1">
       <c r="A146" s="4">
         <v>145</v>
       </c>
@@ -10814,7 +10822,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="147" spans="1:11">
+    <row r="147" spans="1:11" hidden="1">
       <c r="A147" s="4">
         <v>146</v>
       </c>
@@ -10847,7 +10855,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="148" spans="1:11">
+    <row r="148" spans="1:11" hidden="1">
       <c r="A148" s="4">
         <v>147</v>
       </c>
@@ -10880,7 +10888,7 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="149" spans="1:11">
+    <row r="149" spans="1:11" hidden="1">
       <c r="A149" s="4">
         <v>148</v>
       </c>
@@ -10913,7 +10921,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="150" spans="1:11">
+    <row r="150" spans="1:11" hidden="1">
       <c r="A150" s="4">
         <v>149</v>
       </c>
@@ -10946,7 +10954,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="151" spans="1:11">
+    <row r="151" spans="1:11" hidden="1">
       <c r="A151" s="4">
         <v>150</v>
       </c>
@@ -10979,7 +10987,7 @@
         <v>1299</v>
       </c>
     </row>
-    <row r="152" spans="1:11">
+    <row r="152" spans="1:11" hidden="1">
       <c r="A152" s="4">
         <v>151</v>
       </c>
@@ -11012,7 +11020,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="153" spans="1:11">
+    <row r="153" spans="1:11" hidden="1">
       <c r="A153" s="4">
         <v>152</v>
       </c>
@@ -11045,7 +11053,7 @@
       </c>
       <c r="K153" s="24"/>
     </row>
-    <row r="154" spans="1:11">
+    <row r="154" spans="1:11" hidden="1">
       <c r="A154" s="4">
         <v>153</v>
       </c>
@@ -11080,7 +11088,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="155" spans="1:11">
+    <row r="155" spans="1:11" hidden="1">
       <c r="A155" s="4">
         <v>154</v>
       </c>
@@ -11115,7 +11123,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="156" spans="1:11">
+    <row r="156" spans="1:11" hidden="1">
       <c r="A156" s="4">
         <v>155</v>
       </c>
@@ -11185,7 +11193,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="158" spans="1:11">
+    <row r="158" spans="1:11" hidden="1">
       <c r="A158" s="4">
         <v>157</v>
       </c>
@@ -11220,7 +11228,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="159" spans="1:11">
+    <row r="159" spans="1:11" hidden="1">
       <c r="A159" s="4">
         <v>158</v>
       </c>
@@ -11426,7 +11434,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="165" spans="1:11">
+    <row r="165" spans="1:11" hidden="1">
       <c r="A165" s="4">
         <v>164</v>
       </c>
@@ -11461,7 +11469,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="166" spans="1:11">
+    <row r="166" spans="1:11" hidden="1">
       <c r="A166" s="4">
         <v>165</v>
       </c>
@@ -11496,7 +11504,7 @@
         <v>1290</v>
       </c>
     </row>
-    <row r="167" spans="1:11">
+    <row r="167" spans="1:11" hidden="1">
       <c r="A167" s="4">
         <v>166</v>
       </c>
@@ -11531,7 +11539,7 @@
         <v>1296</v>
       </c>
     </row>
-    <row r="168" spans="1:11">
+    <row r="168" spans="1:11" hidden="1">
       <c r="A168" s="4">
         <v>167</v>
       </c>
@@ -11564,7 +11572,7 @@
       </c>
       <c r="K168" s="55"/>
     </row>
-    <row r="169" spans="1:11">
+    <row r="169" spans="1:11" hidden="1">
       <c r="A169" s="4">
         <v>168</v>
       </c>
@@ -11597,7 +11605,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="170" spans="1:11">
+    <row r="170" spans="1:11" hidden="1">
       <c r="A170" s="4">
         <v>169</v>
       </c>
@@ -11630,7 +11638,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="171" spans="1:11">
+    <row r="171" spans="1:11" hidden="1">
       <c r="A171" s="4">
         <v>170</v>
       </c>
@@ -11663,7 +11671,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="172" spans="1:11">
+    <row r="172" spans="1:11" hidden="1">
       <c r="A172" s="4">
         <v>171</v>
       </c>
@@ -11698,7 +11706,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="173" spans="1:11">
+    <row r="173" spans="1:11" hidden="1">
       <c r="A173" s="4">
         <v>172</v>
       </c>
@@ -11731,7 +11739,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="174" spans="1:11">
+    <row r="174" spans="1:11" hidden="1">
       <c r="A174" s="4">
         <v>173</v>
       </c>
@@ -11764,7 +11772,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="175" spans="1:11">
+    <row r="175" spans="1:11" hidden="1">
       <c r="A175" s="4">
         <v>174</v>
       </c>
@@ -11799,7 +11807,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="176" spans="1:11">
+    <row r="176" spans="1:11" hidden="1">
       <c r="A176" s="4">
         <v>175</v>
       </c>
@@ -11829,7 +11837,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="177" spans="1:11">
+    <row r="177" spans="1:11" hidden="1">
       <c r="A177" s="4">
         <v>176</v>
       </c>
@@ -11859,7 +11867,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="178" spans="1:11">
+    <row r="178" spans="1:11" hidden="1">
       <c r="A178" s="4">
         <v>177</v>
       </c>
@@ -11887,7 +11895,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="179" spans="1:11">
+    <row r="179" spans="1:11" hidden="1">
       <c r="A179" s="4">
         <v>178</v>
       </c>
@@ -11922,7 +11930,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="180" spans="1:11">
+    <row r="180" spans="1:11" hidden="1">
       <c r="A180" s="4">
         <v>179</v>
       </c>
@@ -11952,7 +11960,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="181" spans="1:11">
+    <row r="181" spans="1:11" hidden="1">
       <c r="A181" s="4">
         <v>180</v>
       </c>
@@ -11985,7 +11993,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="182" spans="1:11">
+    <row r="182" spans="1:11" hidden="1">
       <c r="A182" s="4">
         <v>181</v>
       </c>
@@ -12018,7 +12026,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="183" spans="1:11">
+    <row r="183" spans="1:11" hidden="1">
       <c r="A183" s="4">
         <v>182</v>
       </c>
@@ -12051,7 +12059,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="184" spans="1:11">
+    <row r="184" spans="1:11" hidden="1">
       <c r="A184" s="4">
         <v>183</v>
       </c>
@@ -12084,7 +12092,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="185" spans="1:11">
+    <row r="185" spans="1:11" hidden="1">
       <c r="A185" s="4">
         <v>184</v>
       </c>
@@ -12114,7 +12122,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="186" spans="1:11">
+    <row r="186" spans="1:11" hidden="1">
       <c r="A186" s="4">
         <v>185</v>
       </c>
@@ -12144,7 +12152,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="187" spans="1:11">
+    <row r="187" spans="1:11" hidden="1">
       <c r="A187" s="4">
         <v>186</v>
       </c>
@@ -12177,7 +12185,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="188" spans="1:11">
+    <row r="188" spans="1:11" hidden="1">
       <c r="A188" s="4">
         <v>187</v>
       </c>
@@ -12204,7 +12212,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="189" spans="1:11">
+    <row r="189" spans="1:11" hidden="1">
       <c r="A189" s="4">
         <v>188</v>
       </c>
@@ -12235,7 +12243,7 @@
       </c>
       <c r="K189" s="24"/>
     </row>
-    <row r="190" spans="1:11">
+    <row r="190" spans="1:11" hidden="1">
       <c r="A190" s="4">
         <v>189</v>
       </c>
@@ -12270,7 +12278,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="191" spans="1:11">
+    <row r="191" spans="1:11" hidden="1">
       <c r="A191" s="4">
         <v>190</v>
       </c>
@@ -12300,7 +12308,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="192" spans="1:11">
+    <row r="192" spans="1:11" hidden="1">
       <c r="A192" s="4">
         <v>191</v>
       </c>
@@ -12333,7 +12341,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="193" spans="1:10">
+    <row r="193" spans="1:10" hidden="1">
       <c r="A193" s="4">
         <v>192</v>
       </c>
@@ -12363,7 +12371,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="194" spans="1:10">
+    <row r="194" spans="1:10" hidden="1">
       <c r="A194" s="4">
         <v>193</v>
       </c>
@@ -12395,7 +12403,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="195" spans="1:10">
+    <row r="195" spans="1:10" hidden="1">
       <c r="A195" s="4">
         <v>194</v>
       </c>
@@ -12427,7 +12435,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="196" spans="1:10">
+    <row r="196" spans="1:10" hidden="1">
       <c r="A196" s="4">
         <v>195</v>
       </c>
@@ -12459,7 +12467,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="197" spans="1:10">
+    <row r="197" spans="1:10" hidden="1">
       <c r="A197" s="4">
         <v>196</v>
       </c>
@@ -12491,7 +12499,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="198" spans="1:10">
+    <row r="198" spans="1:10" hidden="1">
       <c r="A198" s="4">
         <v>197</v>
       </c>
@@ -12523,7 +12531,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="199" spans="1:10">
+    <row r="199" spans="1:10" hidden="1">
       <c r="A199" s="4">
         <v>198</v>
       </c>
@@ -12555,7 +12563,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="200" spans="1:10">
+    <row r="200" spans="1:10" hidden="1">
       <c r="A200" s="4">
         <v>199</v>
       </c>
@@ -12587,7 +12595,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="201" spans="1:10">
+    <row r="201" spans="1:10" hidden="1">
       <c r="A201" s="4">
         <v>200</v>
       </c>
@@ -12619,7 +12627,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="202" spans="1:10">
+    <row r="202" spans="1:10" hidden="1">
       <c r="A202" s="4">
         <v>201</v>
       </c>
@@ -12651,7 +12659,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="203" spans="1:10">
+    <row r="203" spans="1:10" hidden="1">
       <c r="A203" s="4">
         <v>202</v>
       </c>
@@ -12683,7 +12691,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="204" spans="1:10">
+    <row r="204" spans="1:10" hidden="1">
       <c r="A204" s="4">
         <v>203</v>
       </c>
@@ -12715,7 +12723,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="205" spans="1:10">
+    <row r="205" spans="1:10" hidden="1">
       <c r="A205" s="4">
         <v>204</v>
       </c>
@@ -12747,7 +12755,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="206" spans="1:10">
+    <row r="206" spans="1:10" hidden="1">
       <c r="A206" s="4">
         <v>205</v>
       </c>
@@ -12779,7 +12787,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="207" spans="1:10">
+    <row r="207" spans="1:10" hidden="1">
       <c r="A207" s="4">
         <v>206</v>
       </c>
@@ -12811,7 +12819,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="208" spans="1:10">
+    <row r="208" spans="1:10" hidden="1">
       <c r="A208" s="4">
         <v>207</v>
       </c>
@@ -12843,7 +12851,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="209" spans="1:11">
+    <row r="209" spans="1:11" hidden="1">
       <c r="A209" s="4">
         <v>208</v>
       </c>
@@ -12875,7 +12883,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="210" spans="1:11">
+    <row r="210" spans="1:11" hidden="1">
       <c r="A210" s="4">
         <v>209</v>
       </c>
@@ -12907,7 +12915,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="211" spans="1:11">
+    <row r="211" spans="1:11" hidden="1">
       <c r="A211" s="4">
         <v>210</v>
       </c>
@@ -12939,7 +12947,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="212" spans="1:11">
+    <row r="212" spans="1:11" hidden="1">
       <c r="A212" s="4">
         <v>211</v>
       </c>
@@ -12971,7 +12979,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="213" spans="1:11">
+    <row r="213" spans="1:11" hidden="1">
       <c r="A213" s="4">
         <v>212</v>
       </c>
@@ -13003,7 +13011,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="214" spans="1:11">
+    <row r="214" spans="1:11" hidden="1">
       <c r="A214" s="4">
         <v>213</v>
       </c>
@@ -13035,7 +13043,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="215" spans="1:11">
+    <row r="215" spans="1:11" hidden="1">
       <c r="A215" s="4">
         <v>214</v>
       </c>
@@ -13070,7 +13078,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="216" spans="1:11">
+    <row r="216" spans="1:11" hidden="1">
       <c r="A216" s="4">
         <v>215</v>
       </c>
@@ -13105,7 +13113,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="217" spans="1:11">
+    <row r="217" spans="1:11" hidden="1">
       <c r="A217" s="4">
         <v>216</v>
       </c>
@@ -13138,7 +13146,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="218" spans="1:11">
+    <row r="218" spans="1:11" hidden="1">
       <c r="A218" s="4">
         <v>217</v>
       </c>
@@ -13171,7 +13179,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="219" spans="1:11">
+    <row r="219" spans="1:11" hidden="1">
       <c r="A219" s="4">
         <v>218</v>
       </c>
@@ -13202,7 +13210,7 @@
       </c>
       <c r="K219" s="24"/>
     </row>
-    <row r="220" spans="1:11">
+    <row r="220" spans="1:11" hidden="1">
       <c r="A220" s="4">
         <v>219</v>
       </c>
@@ -13235,7 +13243,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="221" spans="1:11">
+    <row r="221" spans="1:11" hidden="1">
       <c r="A221" s="4">
         <v>220</v>
       </c>
@@ -13268,7 +13276,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="222" spans="1:11">
+    <row r="222" spans="1:11" hidden="1">
       <c r="A222" s="4">
         <v>221</v>
       </c>
@@ -13301,7 +13309,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="223" spans="1:11">
+    <row r="223" spans="1:11" hidden="1">
       <c r="A223" s="4">
         <v>222</v>
       </c>
@@ -13336,7 +13344,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="224" spans="1:11">
+    <row r="224" spans="1:11" hidden="1">
       <c r="A224" s="4">
         <v>223</v>
       </c>
@@ -13369,7 +13377,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="225" spans="1:11">
+    <row r="225" spans="1:11" hidden="1">
       <c r="A225" s="4">
         <v>224</v>
       </c>
@@ -13404,7 +13412,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="226" spans="1:11">
+    <row r="226" spans="1:11" hidden="1">
       <c r="A226" s="4">
         <v>225</v>
       </c>
@@ -13439,7 +13447,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="227" spans="1:11">
+    <row r="227" spans="1:11" hidden="1">
       <c r="A227" s="4">
         <v>226</v>
       </c>
@@ -13472,7 +13480,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="228" spans="1:11">
+    <row r="228" spans="1:11" hidden="1">
       <c r="A228" s="4">
         <v>227</v>
       </c>
@@ -13505,7 +13513,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="229" spans="1:11">
+    <row r="229" spans="1:11" hidden="1">
       <c r="A229" s="4">
         <v>228</v>
       </c>
@@ -13540,7 +13548,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="230" spans="1:11">
+    <row r="230" spans="1:11" hidden="1">
       <c r="A230" s="4">
         <v>229</v>
       </c>
@@ -13575,7 +13583,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="231" spans="1:11">
+    <row r="231" spans="1:11" hidden="1">
       <c r="A231" s="4">
         <v>230</v>
       </c>
@@ -13610,7 +13618,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="232" spans="1:11">
+    <row r="232" spans="1:11" hidden="1">
       <c r="A232" s="4">
         <v>231</v>
       </c>
@@ -13643,7 +13651,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="233" spans="1:11">
+    <row r="233" spans="1:11" hidden="1">
       <c r="A233" s="4">
         <v>232</v>
       </c>
@@ -13676,7 +13684,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="234" spans="1:11">
+    <row r="234" spans="1:11" hidden="1">
       <c r="A234" s="4">
         <v>233</v>
       </c>
@@ -13709,7 +13717,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="235" spans="1:11">
+    <row r="235" spans="1:11" hidden="1">
       <c r="A235" s="4">
         <v>234</v>
       </c>
@@ -13742,7 +13750,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="236" spans="1:11">
+    <row r="236" spans="1:11" hidden="1">
       <c r="A236" s="4">
         <v>235</v>
       </c>
@@ -13775,7 +13783,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="237" spans="1:11">
+    <row r="237" spans="1:11" hidden="1">
       <c r="A237" s="4">
         <v>236</v>
       </c>
@@ -13808,7 +13816,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="238" spans="1:11">
+    <row r="238" spans="1:11" hidden="1">
       <c r="A238" s="4">
         <v>237</v>
       </c>
@@ -13843,7 +13851,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="239" spans="1:11">
+    <row r="239" spans="1:11" hidden="1">
       <c r="A239" s="4">
         <v>238</v>
       </c>
@@ -13876,7 +13884,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="240" spans="1:11">
+    <row r="240" spans="1:11" hidden="1">
       <c r="A240" s="4">
         <v>239</v>
       </c>
@@ -13911,7 +13919,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="241" spans="1:11">
+    <row r="241" spans="1:11" hidden="1">
       <c r="A241" s="4">
         <v>240</v>
       </c>
@@ -13944,7 +13952,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="242" spans="1:11">
+    <row r="242" spans="1:11" hidden="1">
       <c r="A242" s="4">
         <v>241</v>
       </c>
@@ -13979,7 +13987,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="243" spans="1:11">
+    <row r="243" spans="1:11" hidden="1">
       <c r="A243" s="4">
         <v>242</v>
       </c>
@@ -14012,7 +14020,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="244" spans="1:11">
+    <row r="244" spans="1:11" hidden="1">
       <c r="A244" s="4">
         <v>243</v>
       </c>
@@ -14080,7 +14088,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="246" spans="1:11">
+    <row r="246" spans="1:11" hidden="1">
       <c r="A246" s="4">
         <v>245</v>
       </c>
@@ -14113,7 +14121,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="247" spans="1:11">
+    <row r="247" spans="1:11" hidden="1">
       <c r="A247" s="4">
         <v>246</v>
       </c>
@@ -14148,7 +14156,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="248" spans="1:11">
+    <row r="248" spans="1:11" hidden="1">
       <c r="A248" s="4">
         <v>247</v>
       </c>
@@ -14181,7 +14189,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="249" spans="1:11">
+    <row r="249" spans="1:11" hidden="1">
       <c r="A249" s="4">
         <v>248</v>
       </c>
@@ -14214,7 +14222,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="250" spans="1:11">
+    <row r="250" spans="1:11" hidden="1">
       <c r="A250" s="4">
         <v>249</v>
       </c>
@@ -14247,7 +14255,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="251" spans="1:11">
+    <row r="251" spans="1:11" hidden="1">
       <c r="A251" s="4">
         <v>250</v>
       </c>
@@ -14282,7 +14290,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="252" spans="1:11">
+    <row r="252" spans="1:11" hidden="1">
       <c r="A252" s="4">
         <v>251</v>
       </c>
@@ -14317,7 +14325,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="253" spans="1:11" ht="15.6">
+    <row r="253" spans="1:11" ht="15.6" hidden="1">
       <c r="A253" s="4">
         <v>252</v>
       </c>
@@ -14352,7 +14360,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="254" spans="1:11">
+    <row r="254" spans="1:11" hidden="1">
       <c r="A254" s="4">
         <v>253</v>
       </c>
@@ -14422,7 +14430,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="256" spans="1:11">
+    <row r="256" spans="1:11" hidden="1">
       <c r="A256" s="4">
         <v>255</v>
       </c>
@@ -14457,7 +14465,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="257" spans="1:11">
+    <row r="257" spans="1:11" hidden="1">
       <c r="A257" s="4">
         <v>256</v>
       </c>
@@ -14492,7 +14500,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="258" spans="1:11">
+    <row r="258" spans="1:11" hidden="1">
       <c r="A258" s="4">
         <v>257</v>
       </c>
@@ -14523,7 +14531,7 @@
       </c>
       <c r="K258" s="20"/>
     </row>
-    <row r="259" spans="1:11">
+    <row r="259" spans="1:11" hidden="1">
       <c r="A259" s="4">
         <v>258</v>
       </c>
@@ -14556,7 +14564,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="260" spans="1:11">
+    <row r="260" spans="1:11" hidden="1">
       <c r="A260" s="4">
         <v>259</v>
       </c>
@@ -14591,7 +14599,7 @@
         <v>1309</v>
       </c>
     </row>
-    <row r="261" spans="1:11">
+    <row r="261" spans="1:11" hidden="1">
       <c r="A261" s="4">
         <v>260</v>
       </c>
@@ -14626,7 +14634,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="262" spans="1:11">
+    <row r="262" spans="1:11" hidden="1">
       <c r="A262" s="4">
         <v>261</v>
       </c>
@@ -14661,7 +14669,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="263" spans="1:11">
+    <row r="263" spans="1:11" hidden="1">
       <c r="A263" s="4">
         <v>262</v>
       </c>
@@ -14694,7 +14702,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="264" spans="1:11">
+    <row r="264" spans="1:11" hidden="1">
       <c r="A264" s="4">
         <v>263</v>
       </c>
@@ -14724,7 +14732,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="265" spans="1:11">
+    <row r="265" spans="1:11" hidden="1">
       <c r="A265" s="4">
         <v>264</v>
       </c>
@@ -14757,7 +14765,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="266" spans="1:11">
+    <row r="266" spans="1:11" hidden="1">
       <c r="A266" s="4">
         <v>265</v>
       </c>
@@ -14790,7 +14798,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="267" spans="1:11">
+    <row r="267" spans="1:11" hidden="1">
       <c r="A267" s="4">
         <v>266</v>
       </c>
@@ -14823,7 +14831,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="268" spans="1:11">
+    <row r="268" spans="1:11" hidden="1">
       <c r="A268" s="4">
         <v>267</v>
       </c>
@@ -14853,7 +14861,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="269" spans="1:11">
+    <row r="269" spans="1:11" hidden="1">
       <c r="A269" s="4">
         <v>268</v>
       </c>
@@ -14886,7 +14894,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="270" spans="1:11">
+    <row r="270" spans="1:11" hidden="1">
       <c r="A270" s="4">
         <v>269</v>
       </c>
@@ -14916,7 +14924,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="271" spans="1:11">
+    <row r="271" spans="1:11" hidden="1">
       <c r="A271" s="4">
         <v>270</v>
       </c>
@@ -14946,7 +14954,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="272" spans="1:11">
+    <row r="272" spans="1:11" hidden="1">
       <c r="A272" s="4">
         <v>271</v>
       </c>
@@ -14979,7 +14987,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="273" spans="1:11">
+    <row r="273" spans="1:11" hidden="1">
       <c r="A273" s="4">
         <v>272</v>
       </c>
@@ -15082,7 +15090,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="276" spans="1:11">
+    <row r="276" spans="1:11" hidden="1">
       <c r="A276" s="4">
         <v>275</v>
       </c>
@@ -15115,7 +15123,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="277" spans="1:11">
+    <row r="277" spans="1:11" hidden="1">
       <c r="A277" s="4">
         <v>276</v>
       </c>
@@ -15148,7 +15156,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="278" spans="1:11">
+    <row r="278" spans="1:11" hidden="1">
       <c r="A278" s="4">
         <v>277</v>
       </c>
@@ -15181,7 +15189,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="279" spans="1:11">
+    <row r="279" spans="1:11" hidden="1">
       <c r="A279" s="4">
         <v>278</v>
       </c>
@@ -15214,7 +15222,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="280" spans="1:11">
+    <row r="280" spans="1:11" hidden="1">
       <c r="A280" s="4">
         <v>279</v>
       </c>
@@ -15247,7 +15255,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="281" spans="1:11">
+    <row r="281" spans="1:11" hidden="1">
       <c r="A281" s="4">
         <v>280</v>
       </c>
@@ -15280,7 +15288,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="282" spans="1:11">
+    <row r="282" spans="1:11" hidden="1">
       <c r="A282" s="4">
         <v>281</v>
       </c>
@@ -15313,7 +15321,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="283" spans="1:11">
+    <row r="283" spans="1:11" hidden="1">
       <c r="A283" s="4">
         <v>282</v>
       </c>
@@ -15346,7 +15354,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="284" spans="1:11">
+    <row r="284" spans="1:11" hidden="1">
       <c r="A284" s="4">
         <v>283</v>
       </c>
@@ -15379,7 +15387,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="285" spans="1:11">
+    <row r="285" spans="1:11" hidden="1">
       <c r="A285" s="4">
         <v>284</v>
       </c>
@@ -15412,7 +15420,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="286" spans="1:11">
+    <row r="286" spans="1:11" hidden="1">
       <c r="A286" s="4">
         <v>285</v>
       </c>
@@ -15447,7 +15455,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="287" spans="1:11">
+    <row r="287" spans="1:11" hidden="1">
       <c r="A287" s="4">
         <v>286</v>
       </c>
@@ -15480,7 +15488,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="288" spans="1:11">
+    <row r="288" spans="1:11" hidden="1">
       <c r="A288" s="4">
         <v>287</v>
       </c>
@@ -15513,7 +15521,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="289" spans="1:11">
+    <row r="289" spans="1:11" hidden="1">
       <c r="A289" s="4">
         <v>288</v>
       </c>
@@ -15546,7 +15554,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="290" spans="1:11">
+    <row r="290" spans="1:11" hidden="1">
       <c r="A290" s="4">
         <v>289</v>
       </c>
@@ -15581,7 +15589,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="291" spans="1:11">
+    <row r="291" spans="1:11" hidden="1">
       <c r="A291" s="4">
         <v>290</v>
       </c>
@@ -15616,7 +15624,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="292" spans="1:11">
+    <row r="292" spans="1:11" hidden="1">
       <c r="A292" s="4">
         <v>291</v>
       </c>
@@ -15651,7 +15659,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="293" spans="1:11">
+    <row r="293" spans="1:11" hidden="1">
       <c r="A293" s="4">
         <v>292</v>
       </c>
@@ -15686,7 +15694,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="294" spans="1:11">
+    <row r="294" spans="1:11" hidden="1">
       <c r="A294" s="4">
         <v>293</v>
       </c>
@@ -15721,7 +15729,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="295" spans="1:11">
+    <row r="295" spans="1:11" hidden="1">
       <c r="A295" s="4">
         <v>294</v>
       </c>
@@ -15756,7 +15764,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="296" spans="1:11">
+    <row r="296" spans="1:11" hidden="1">
       <c r="A296" s="4">
         <v>295</v>
       </c>
@@ -15791,7 +15799,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="297" spans="1:11">
+    <row r="297" spans="1:11" hidden="1">
       <c r="A297" s="4">
         <v>296</v>
       </c>
@@ -15826,7 +15834,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="298" spans="1:11">
+    <row r="298" spans="1:11" hidden="1">
       <c r="A298" s="4">
         <v>297</v>
       </c>
@@ -15861,7 +15869,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="299" spans="1:11">
+    <row r="299" spans="1:11" hidden="1">
       <c r="A299" s="4">
         <v>298</v>
       </c>
@@ -15896,7 +15904,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="300" spans="1:11">
+    <row r="300" spans="1:11" hidden="1">
       <c r="A300" s="4">
         <v>299</v>
       </c>
@@ -15931,7 +15939,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="301" spans="1:11">
+    <row r="301" spans="1:11" hidden="1">
       <c r="A301" s="4">
         <v>300</v>
       </c>
@@ -15966,7 +15974,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="302" spans="1:11">
+    <row r="302" spans="1:11" hidden="1">
       <c r="A302" s="4">
         <v>301</v>
       </c>
@@ -16001,7 +16009,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="303" spans="1:11">
+    <row r="303" spans="1:11" hidden="1">
       <c r="A303" s="4">
         <v>302</v>
       </c>
@@ -16036,7 +16044,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="304" spans="1:11">
+    <row r="304" spans="1:11" hidden="1">
       <c r="A304" s="4">
         <v>303</v>
       </c>
@@ -16071,7 +16079,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="305" spans="1:11">
+    <row r="305" spans="1:11" hidden="1">
       <c r="A305" s="4">
         <v>304</v>
       </c>
@@ -16106,7 +16114,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="306" spans="1:11">
+    <row r="306" spans="1:11" hidden="1">
       <c r="A306" s="4">
         <v>305</v>
       </c>
@@ -16141,7 +16149,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="307" spans="1:11">
+    <row r="307" spans="1:11" hidden="1">
       <c r="A307" s="4">
         <v>306</v>
       </c>
@@ -16176,7 +16184,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="308" spans="1:11">
+    <row r="308" spans="1:11" hidden="1">
       <c r="A308" s="4">
         <v>307</v>
       </c>
@@ -16211,7 +16219,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="309" spans="1:11">
+    <row r="309" spans="1:11" hidden="1">
       <c r="A309" s="4">
         <v>308</v>
       </c>
@@ -16246,7 +16254,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="310" spans="1:11">
+    <row r="310" spans="1:11" hidden="1">
       <c r="A310" s="4">
         <v>309</v>
       </c>
@@ -16281,7 +16289,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="311" spans="1:11">
+    <row r="311" spans="1:11" hidden="1">
       <c r="A311" s="4">
         <v>310</v>
       </c>
@@ -16316,7 +16324,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="312" spans="1:11">
+    <row r="312" spans="1:11" hidden="1">
       <c r="A312" s="4">
         <v>311</v>
       </c>
@@ -16351,7 +16359,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="313" spans="1:11">
+    <row r="313" spans="1:11" hidden="1">
       <c r="A313" s="4">
         <v>312</v>
       </c>
@@ -16386,7 +16394,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="314" spans="1:11">
+    <row r="314" spans="1:11" hidden="1">
       <c r="A314" s="4">
         <v>313</v>
       </c>
@@ -16421,7 +16429,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="315" spans="1:11">
+    <row r="315" spans="1:11" hidden="1">
       <c r="A315" s="4">
         <v>314</v>
       </c>
@@ -16456,7 +16464,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="316" spans="1:11">
+    <row r="316" spans="1:11" hidden="1">
       <c r="A316" s="4">
         <v>315</v>
       </c>
@@ -16491,7 +16499,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="317" spans="1:11">
+    <row r="317" spans="1:11" hidden="1">
       <c r="A317" s="4">
         <v>316</v>
       </c>
@@ -16526,7 +16534,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="318" spans="1:11">
+    <row r="318" spans="1:11" hidden="1">
       <c r="A318" s="4">
         <v>317</v>
       </c>
@@ -16561,7 +16569,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="319" spans="1:11">
+    <row r="319" spans="1:11" hidden="1">
       <c r="A319" s="4">
         <v>318</v>
       </c>
@@ -16596,7 +16604,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="320" spans="1:11">
+    <row r="320" spans="1:11" hidden="1">
       <c r="A320" s="4">
         <v>319</v>
       </c>
@@ -16631,7 +16639,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="321" spans="1:11">
+    <row r="321" spans="1:11" hidden="1">
       <c r="A321" s="4">
         <v>320</v>
       </c>
@@ -16666,7 +16674,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="322" spans="1:11">
+    <row r="322" spans="1:11" hidden="1">
       <c r="A322" s="4">
         <v>321</v>
       </c>
@@ -16701,7 +16709,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="323" spans="1:11">
+    <row r="323" spans="1:11" hidden="1">
       <c r="A323" s="4">
         <v>322</v>
       </c>
@@ -16736,7 +16744,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="324" spans="1:11">
+    <row r="324" spans="1:11" hidden="1">
       <c r="A324" s="4">
         <v>323</v>
       </c>
@@ -16771,7 +16779,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="325" spans="1:11">
+    <row r="325" spans="1:11" hidden="1">
       <c r="A325" s="4">
         <v>324</v>
       </c>
@@ -16806,7 +16814,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="326" spans="1:11">
+    <row r="326" spans="1:11" hidden="1">
       <c r="A326" s="4">
         <v>325</v>
       </c>
@@ -16841,7 +16849,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="327" spans="1:11">
+    <row r="327" spans="1:11" hidden="1">
       <c r="A327" s="4">
         <v>326</v>
       </c>
@@ -16876,7 +16884,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="328" spans="1:11">
+    <row r="328" spans="1:11" hidden="1">
       <c r="A328" s="4">
         <v>327</v>
       </c>
@@ -16909,7 +16917,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="329" spans="1:11">
+    <row r="329" spans="1:11" hidden="1">
       <c r="A329" s="4">
         <v>328</v>
       </c>
@@ -16942,7 +16950,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="330" spans="1:11">
+    <row r="330" spans="1:11" hidden="1">
       <c r="A330" s="4">
         <v>329</v>
       </c>
@@ -16975,7 +16983,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="331" spans="1:11">
+    <row r="331" spans="1:11" hidden="1">
       <c r="A331" s="4">
         <v>330</v>
       </c>
@@ -17008,7 +17016,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="332" spans="1:11">
+    <row r="332" spans="1:11" hidden="1">
       <c r="A332" s="4">
         <v>331</v>
       </c>
@@ -17041,7 +17049,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="333" spans="1:11">
+    <row r="333" spans="1:11" hidden="1">
       <c r="A333" s="4">
         <v>332</v>
       </c>
@@ -17076,7 +17084,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="334" spans="1:11">
+    <row r="334" spans="1:11" hidden="1">
       <c r="A334" s="4">
         <v>333</v>
       </c>
@@ -17109,7 +17117,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="335" spans="1:11">
+    <row r="335" spans="1:11" hidden="1">
       <c r="A335" s="4">
         <v>334</v>
       </c>
@@ -17142,7 +17150,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="336" spans="1:11">
+    <row r="336" spans="1:11" hidden="1">
       <c r="A336" s="4">
         <v>335</v>
       </c>
@@ -17175,7 +17183,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="337" spans="1:11">
+    <row r="337" spans="1:11" hidden="1">
       <c r="A337" s="4">
         <v>336</v>
       </c>
@@ -17210,7 +17218,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="338" spans="1:11">
+    <row r="338" spans="1:11" hidden="1">
       <c r="A338" s="4">
         <v>337</v>
       </c>
@@ -17245,7 +17253,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="339" spans="1:11">
+    <row r="339" spans="1:11" hidden="1">
       <c r="A339" s="4">
         <v>338</v>
       </c>
@@ -17280,7 +17288,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="340" spans="1:11">
+    <row r="340" spans="1:11" hidden="1">
       <c r="A340" s="4">
         <v>339</v>
       </c>
@@ -17315,7 +17323,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="341" spans="1:11">
+    <row r="341" spans="1:11" hidden="1">
       <c r="A341" s="4">
         <v>340</v>
       </c>
@@ -17350,7 +17358,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="342" spans="1:11">
+    <row r="342" spans="1:11" hidden="1">
       <c r="A342" s="4">
         <v>341</v>
       </c>
@@ -17385,7 +17393,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="343" spans="1:11">
+    <row r="343" spans="1:11" hidden="1">
       <c r="A343" s="4">
         <v>342</v>
       </c>
@@ -17420,7 +17428,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="344" spans="1:11">
+    <row r="344" spans="1:11" hidden="1">
       <c r="A344" s="4">
         <v>343</v>
       </c>
@@ -17455,7 +17463,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="345" spans="1:11">
+    <row r="345" spans="1:11" hidden="1">
       <c r="A345" s="4">
         <v>344</v>
       </c>
@@ -17490,7 +17498,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="346" spans="1:11">
+    <row r="346" spans="1:11" hidden="1">
       <c r="A346" s="4">
         <v>345</v>
       </c>
@@ -17525,7 +17533,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="347" spans="1:11">
+    <row r="347" spans="1:11" hidden="1">
       <c r="A347" s="4">
         <v>346</v>
       </c>
@@ -17560,7 +17568,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="348" spans="1:11">
+    <row r="348" spans="1:11" hidden="1">
       <c r="A348" s="4">
         <v>347</v>
       </c>
@@ -17595,7 +17603,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="349" spans="1:11">
+    <row r="349" spans="1:11" hidden="1">
       <c r="A349" s="4">
         <v>348</v>
       </c>
@@ -17630,7 +17638,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="350" spans="1:11">
+    <row r="350" spans="1:11" hidden="1">
       <c r="A350" s="4">
         <v>349</v>
       </c>
@@ -17665,7 +17673,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="351" spans="1:11">
+    <row r="351" spans="1:11" hidden="1">
       <c r="A351" s="4">
         <v>350</v>
       </c>
@@ -17700,7 +17708,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="352" spans="1:11">
+    <row r="352" spans="1:11" hidden="1">
       <c r="A352" s="4">
         <v>351</v>
       </c>
@@ -17735,7 +17743,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="353" spans="1:11">
+    <row r="353" spans="1:11" hidden="1">
       <c r="A353" s="4">
         <v>352</v>
       </c>
@@ -17770,7 +17778,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="354" spans="1:11">
+    <row r="354" spans="1:11" hidden="1">
       <c r="A354" s="4">
         <v>353</v>
       </c>
@@ -17805,7 +17813,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="355" spans="1:11">
+    <row r="355" spans="1:11" hidden="1">
       <c r="A355" s="4">
         <v>354</v>
       </c>
@@ -17840,7 +17848,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="356" spans="1:11">
+    <row r="356" spans="1:11" hidden="1">
       <c r="A356" s="4">
         <v>355</v>
       </c>
@@ -17875,7 +17883,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="357" spans="1:11">
+    <row r="357" spans="1:11" hidden="1">
       <c r="A357" s="4">
         <v>356</v>
       </c>
@@ -17910,7 +17918,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="358" spans="1:11">
+    <row r="358" spans="1:11" hidden="1">
       <c r="A358" s="4">
         <v>357</v>
       </c>
@@ -17945,7 +17953,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="359" spans="1:11">
+    <row r="359" spans="1:11" hidden="1">
       <c r="A359" s="4">
         <v>358</v>
       </c>
@@ -17980,7 +17988,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="360" spans="1:11">
+    <row r="360" spans="1:11" hidden="1">
       <c r="A360" s="4">
         <v>359</v>
       </c>
@@ -18015,7 +18023,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="361" spans="1:11">
+    <row r="361" spans="1:11" hidden="1">
       <c r="A361" s="4">
         <v>360</v>
       </c>
@@ -18050,7 +18058,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="362" spans="1:11">
+    <row r="362" spans="1:11" hidden="1">
       <c r="A362" s="4">
         <v>361</v>
       </c>
@@ -18085,7 +18093,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="363" spans="1:11">
+    <row r="363" spans="1:11" hidden="1">
       <c r="A363" s="4">
         <v>362</v>
       </c>
@@ -18120,7 +18128,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="364" spans="1:11">
+    <row r="364" spans="1:11" hidden="1">
       <c r="A364" s="4">
         <v>363</v>
       </c>
@@ -18155,7 +18163,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="365" spans="1:11">
+    <row r="365" spans="1:11" hidden="1">
       <c r="A365" s="4">
         <v>364</v>
       </c>
@@ -18188,7 +18196,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="366" spans="1:11">
+    <row r="366" spans="1:11" hidden="1">
       <c r="A366" s="4">
         <v>365</v>
       </c>
@@ -18223,7 +18231,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="367" spans="1:11">
+    <row r="367" spans="1:11" hidden="1">
       <c r="A367" s="4">
         <v>366</v>
       </c>
@@ -18258,7 +18266,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="368" spans="1:11">
+    <row r="368" spans="1:11" hidden="1">
       <c r="A368" s="4">
         <v>367</v>
       </c>
@@ -18293,7 +18301,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="369" spans="1:11">
+    <row r="369" spans="1:11" hidden="1">
       <c r="A369" s="4">
         <v>368</v>
       </c>
@@ -18328,7 +18336,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="370" spans="1:11">
+    <row r="370" spans="1:11" hidden="1">
       <c r="A370" s="4">
         <v>369</v>
       </c>
@@ -18363,7 +18371,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="371" spans="1:11">
+    <row r="371" spans="1:11" hidden="1">
       <c r="A371" s="4">
         <v>370</v>
       </c>
@@ -18398,7 +18406,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="372" spans="1:11">
+    <row r="372" spans="1:11" hidden="1">
       <c r="A372" s="4">
         <v>371</v>
       </c>
@@ -18433,7 +18441,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="373" spans="1:11">
+    <row r="373" spans="1:11" hidden="1">
       <c r="A373" s="4">
         <v>372</v>
       </c>
@@ -18468,7 +18476,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="374" spans="1:11">
+    <row r="374" spans="1:11" hidden="1">
       <c r="A374" s="4">
         <v>373</v>
       </c>
@@ -18503,7 +18511,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="375" spans="1:11">
+    <row r="375" spans="1:11" hidden="1">
       <c r="A375" s="4">
         <v>374</v>
       </c>
@@ -18538,7 +18546,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="376" spans="1:11">
+    <row r="376" spans="1:11" hidden="1">
       <c r="A376" s="4">
         <v>375</v>
       </c>
@@ -18573,7 +18581,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="377" spans="1:11">
+    <row r="377" spans="1:11" hidden="1">
       <c r="A377" s="4">
         <v>376</v>
       </c>
@@ -18608,7 +18616,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="378" spans="1:11">
+    <row r="378" spans="1:11" hidden="1">
       <c r="A378" s="4">
         <v>377</v>
       </c>
@@ -18643,7 +18651,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="379" spans="1:11">
+    <row r="379" spans="1:11" hidden="1">
       <c r="A379" s="4">
         <v>378</v>
       </c>
@@ -18678,7 +18686,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="380" spans="1:11">
+    <row r="380" spans="1:11" hidden="1">
       <c r="A380" s="4">
         <v>379</v>
       </c>
@@ -18713,7 +18721,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="381" spans="1:11">
+    <row r="381" spans="1:11" hidden="1">
       <c r="A381" s="4">
         <v>380</v>
       </c>
@@ -18748,7 +18756,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="382" spans="1:11">
+    <row r="382" spans="1:11" hidden="1">
       <c r="A382" s="4">
         <v>381</v>
       </c>
@@ -18783,7 +18791,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="383" spans="1:11">
+    <row r="383" spans="1:11" hidden="1">
       <c r="A383" s="4">
         <v>382</v>
       </c>
@@ -18818,7 +18826,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="384" spans="1:11">
+    <row r="384" spans="1:11" hidden="1">
       <c r="A384" s="4">
         <v>383</v>
       </c>
@@ -18853,7 +18861,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="385" spans="1:11">
+    <row r="385" spans="1:11" hidden="1">
       <c r="A385" s="4">
         <v>384</v>
       </c>
@@ -18888,7 +18896,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="386" spans="1:11">
+    <row r="386" spans="1:11" hidden="1">
       <c r="A386" s="4">
         <v>385</v>
       </c>
@@ -18923,7 +18931,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="387" spans="1:11">
+    <row r="387" spans="1:11" hidden="1">
       <c r="A387" s="4">
         <v>386</v>
       </c>
@@ -18958,7 +18966,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="388" spans="1:11">
+    <row r="388" spans="1:11" hidden="1">
       <c r="A388" s="4">
         <v>387</v>
       </c>
@@ -18993,7 +19001,7 @@
         <v>1457</v>
       </c>
     </row>
-    <row r="389" spans="1:11">
+    <row r="389" spans="1:11" hidden="1">
       <c r="A389" s="4">
         <v>388</v>
       </c>
@@ -19028,7 +19036,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="390" spans="1:11">
+    <row r="390" spans="1:11" hidden="1">
       <c r="A390" s="4">
         <v>389</v>
       </c>
@@ -19063,7 +19071,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="391" spans="1:11">
+    <row r="391" spans="1:11" hidden="1">
       <c r="A391" s="4">
         <v>390</v>
       </c>
@@ -19098,7 +19106,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="392" spans="1:11">
+    <row r="392" spans="1:11" hidden="1">
       <c r="A392" s="4">
         <v>391</v>
       </c>
@@ -19133,7 +19141,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="393" spans="1:11">
+    <row r="393" spans="1:11" hidden="1">
       <c r="A393" s="4">
         <v>392</v>
       </c>
@@ -19147,16 +19155,16 @@
         <v>1377</v>
       </c>
       <c r="E393" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F393" s="1" t="s">
-        <v>1453</v>
+        <v>605</v>
       </c>
       <c r="G393" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H393" s="1" t="s">
-        <v>1339</v>
+        <v>605</v>
       </c>
       <c r="I393" s="54">
         <v>46279</v>
@@ -19168,7 +19176,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="394" spans="1:11">
+    <row r="394" spans="1:11" hidden="1">
       <c r="A394" s="4">
         <v>393</v>
       </c>
@@ -19201,7 +19209,7 @@
       </c>
       <c r="K394" s="55"/>
     </row>
-    <row r="395" spans="1:11">
+    <row r="395" spans="1:11" hidden="1">
       <c r="A395" s="4">
         <v>394</v>
       </c>
@@ -19234,7 +19242,7 @@
       </c>
       <c r="K395" s="55"/>
     </row>
-    <row r="396" spans="1:11">
+    <row r="396" spans="1:11" hidden="1">
       <c r="A396" s="4">
         <v>395</v>
       </c>
@@ -19267,7 +19275,7 @@
       </c>
       <c r="K396" s="55"/>
     </row>
-    <row r="397" spans="1:11">
+    <row r="397" spans="1:11" hidden="1">
       <c r="A397" s="4">
         <v>396</v>
       </c>
@@ -19302,7 +19310,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="398" spans="1:11">
+    <row r="398" spans="1:11" hidden="1">
       <c r="A398" s="4">
         <v>397</v>
       </c>
@@ -19337,7 +19345,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="399" spans="1:11">
+    <row r="399" spans="1:11" hidden="1">
       <c r="A399" s="4">
         <v>398</v>
       </c>
@@ -19372,7 +19380,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="400" spans="1:11">
+    <row r="400" spans="1:11" hidden="1">
       <c r="A400" s="4">
         <v>399</v>
       </c>
@@ -19442,7 +19450,7 @@
         <v>1316</v>
       </c>
     </row>
-    <row r="402" spans="1:11">
+    <row r="402" spans="1:11" hidden="1">
       <c r="A402" s="4">
         <v>401</v>
       </c>
@@ -19477,7 +19485,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="403" spans="1:11">
+    <row r="403" spans="1:11" hidden="1">
       <c r="A403" s="4">
         <v>402</v>
       </c>
@@ -19512,7 +19520,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="404" spans="1:11">
+    <row r="404" spans="1:11" hidden="1">
       <c r="A404" s="4">
         <v>403</v>
       </c>
@@ -19547,7 +19555,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="405" spans="1:11">
+    <row r="405" spans="1:11" hidden="1">
       <c r="A405" s="4">
         <v>404</v>
       </c>
@@ -19582,7 +19590,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="406" spans="1:11">
+    <row r="406" spans="1:11" hidden="1">
       <c r="A406" s="4">
         <v>405</v>
       </c>
@@ -19617,7 +19625,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="407" spans="1:11">
+    <row r="407" spans="1:11" hidden="1">
       <c r="A407" s="4">
         <v>406</v>
       </c>
@@ -19652,7 +19660,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="408" spans="1:11">
+    <row r="408" spans="1:11" hidden="1">
       <c r="A408" s="4">
         <v>407</v>
       </c>
@@ -19687,7 +19695,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="409" spans="1:11">
+    <row r="409" spans="1:11" hidden="1">
       <c r="A409" s="4">
         <v>408</v>
       </c>
@@ -19722,7 +19730,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="410" spans="1:11">
+    <row r="410" spans="1:11" hidden="1">
       <c r="A410" s="4">
         <v>409</v>
       </c>
@@ -19757,7 +19765,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="411" spans="1:11">
+    <row r="411" spans="1:11" hidden="1">
       <c r="A411" s="4">
         <v>410</v>
       </c>
@@ -19790,7 +19798,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="412" spans="1:11">
+    <row r="412" spans="1:11" hidden="1">
       <c r="A412" s="4">
         <v>411</v>
       </c>
@@ -19825,7 +19833,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="413" spans="1:11">
+    <row r="413" spans="1:11" hidden="1">
       <c r="A413" s="4">
         <v>412</v>
       </c>
@@ -19860,7 +19868,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="414" spans="1:11">
+    <row r="414" spans="1:11" hidden="1">
       <c r="A414" s="4">
         <v>413</v>
       </c>
@@ -19895,7 +19903,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="415" spans="1:11">
+    <row r="415" spans="1:11" hidden="1">
       <c r="A415" s="4">
         <v>414</v>
       </c>
@@ -19930,7 +19938,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="416" spans="1:11">
+    <row r="416" spans="1:11" hidden="1">
       <c r="A416" s="4">
         <v>415</v>
       </c>
@@ -19963,7 +19971,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="417" spans="1:11">
+    <row r="417" spans="1:11" hidden="1">
       <c r="A417" s="4">
         <v>416</v>
       </c>
@@ -19998,7 +20006,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="418" spans="1:11">
+    <row r="418" spans="1:11" hidden="1">
       <c r="A418" s="4">
         <v>417</v>
       </c>
@@ -20033,7 +20041,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="419" spans="1:11">
+    <row r="419" spans="1:11" hidden="1">
       <c r="A419" s="4">
         <v>418</v>
       </c>
@@ -20068,7 +20076,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="420" spans="1:11">
+    <row r="420" spans="1:11" hidden="1">
       <c r="A420" s="4">
         <v>419</v>
       </c>
@@ -20103,7 +20111,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="421" spans="1:11">
+    <row r="421" spans="1:11" hidden="1">
       <c r="A421" s="4">
         <v>420</v>
       </c>
@@ -20138,7 +20146,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="422" spans="1:11">
+    <row r="422" spans="1:11" hidden="1">
       <c r="A422" s="4">
         <v>421</v>
       </c>
@@ -20173,7 +20181,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="423" spans="1:11">
+    <row r="423" spans="1:11" hidden="1">
       <c r="A423" s="4">
         <v>422</v>
       </c>
@@ -20208,7 +20216,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="424" spans="1:11">
+    <row r="424" spans="1:11" hidden="1">
       <c r="A424" s="4">
         <v>423</v>
       </c>
@@ -20243,7 +20251,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="425" spans="1:11">
+    <row r="425" spans="1:11" hidden="1">
       <c r="A425" s="4">
         <v>424</v>
       </c>
@@ -20278,7 +20286,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="426" spans="1:11">
+    <row r="426" spans="1:11" hidden="1">
       <c r="A426" s="4">
         <v>425</v>
       </c>
@@ -20313,7 +20321,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="427" spans="1:11">
+    <row r="427" spans="1:11" hidden="1">
       <c r="A427" s="4">
         <v>426</v>
       </c>
@@ -20348,7 +20356,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="428" spans="1:11">
+    <row r="428" spans="1:11" hidden="1">
       <c r="A428" s="4">
         <v>427</v>
       </c>
@@ -20383,7 +20391,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="429" spans="1:11">
+    <row r="429" spans="1:11" hidden="1">
       <c r="A429" s="4">
         <v>428</v>
       </c>
@@ -20418,7 +20426,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="430" spans="1:11">
+    <row r="430" spans="1:11" hidden="1">
       <c r="A430" s="4">
         <v>429</v>
       </c>
@@ -20453,7 +20461,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="431" spans="1:11">
+    <row r="431" spans="1:11" hidden="1">
       <c r="A431" s="4">
         <v>430</v>
       </c>
@@ -20488,7 +20496,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="432" spans="1:11">
+    <row r="432" spans="1:11" hidden="1">
       <c r="A432" s="4">
         <v>431</v>
       </c>
@@ -20523,7 +20531,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="433" spans="1:11">
+    <row r="433" spans="1:11" hidden="1">
       <c r="A433" s="4">
         <v>432</v>
       </c>
@@ -20558,7 +20566,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="434" spans="1:11">
+    <row r="434" spans="1:11" hidden="1">
       <c r="A434" s="4">
         <v>433</v>
       </c>
@@ -20591,7 +20599,7 @@
       </c>
       <c r="K434" s="55"/>
     </row>
-    <row r="435" spans="1:11">
+    <row r="435" spans="1:11" hidden="1">
       <c r="A435" s="4">
         <v>434</v>
       </c>
@@ -20624,7 +20632,7 @@
       </c>
       <c r="K435" s="55"/>
     </row>
-    <row r="436" spans="1:11">
+    <row r="436" spans="1:11" hidden="1">
       <c r="A436" s="4">
         <v>435</v>
       </c>
@@ -20657,7 +20665,7 @@
       </c>
       <c r="K436" s="55"/>
     </row>
-    <row r="437" spans="1:11">
+    <row r="437" spans="1:11" hidden="1">
       <c r="A437" s="4">
         <v>436</v>
       </c>
@@ -20690,7 +20698,7 @@
       </c>
       <c r="K437" s="55"/>
     </row>
-    <row r="438" spans="1:11">
+    <row r="438" spans="1:11" hidden="1">
       <c r="A438" s="4">
         <v>437</v>
       </c>
@@ -20723,7 +20731,7 @@
       </c>
       <c r="K438" s="55"/>
     </row>
-    <row r="439" spans="1:11">
+    <row r="439" spans="1:11" hidden="1">
       <c r="A439" s="4">
         <v>438</v>
       </c>
@@ -20756,7 +20764,7 @@
       </c>
       <c r="K439" s="55"/>
     </row>
-    <row r="440" spans="1:11">
+    <row r="440" spans="1:11" hidden="1">
       <c r="A440" s="4">
         <v>439</v>
       </c>
@@ -20789,7 +20797,7 @@
       </c>
       <c r="K440" s="55"/>
     </row>
-    <row r="441" spans="1:11">
+    <row r="441" spans="1:11" hidden="1">
       <c r="A441" s="4">
         <v>440</v>
       </c>
@@ -20822,7 +20830,7 @@
       </c>
       <c r="K441" s="55"/>
     </row>
-    <row r="442" spans="1:11">
+    <row r="442" spans="1:11" hidden="1">
       <c r="A442" s="4">
         <v>441</v>
       </c>
@@ -20855,7 +20863,7 @@
       </c>
       <c r="K442" s="55"/>
     </row>
-    <row r="443" spans="1:11">
+    <row r="443" spans="1:11" hidden="1">
       <c r="A443" s="4">
         <v>442</v>
       </c>
@@ -20888,7 +20896,7 @@
       </c>
       <c r="K443" s="55"/>
     </row>
-    <row r="444" spans="1:11">
+    <row r="444" spans="1:11" hidden="1">
       <c r="A444" s="4">
         <v>443</v>
       </c>
@@ -20921,7 +20929,7 @@
       </c>
       <c r="K444" s="55"/>
     </row>
-    <row r="445" spans="1:11">
+    <row r="445" spans="1:11" hidden="1">
       <c r="A445" s="4">
         <v>444</v>
       </c>
@@ -20954,7 +20962,7 @@
       </c>
       <c r="K445" s="55"/>
     </row>
-    <row r="446" spans="1:11">
+    <row r="446" spans="1:11" hidden="1">
       <c r="A446" s="4">
         <v>445</v>
       </c>
@@ -20987,7 +20995,7 @@
       </c>
       <c r="K446" s="55"/>
     </row>
-    <row r="447" spans="1:11">
+    <row r="447" spans="1:11" hidden="1">
       <c r="A447" s="4">
         <v>446</v>
       </c>
@@ -21020,7 +21028,7 @@
       </c>
       <c r="K447" s="55"/>
     </row>
-    <row r="448" spans="1:11">
+    <row r="448" spans="1:11" hidden="1">
       <c r="A448" s="4">
         <v>447</v>
       </c>
@@ -21053,7 +21061,7 @@
       </c>
       <c r="K448" s="55"/>
     </row>
-    <row r="449" spans="1:11">
+    <row r="449" spans="1:11" hidden="1">
       <c r="A449" s="4">
         <v>448</v>
       </c>
@@ -21086,7 +21094,7 @@
       </c>
       <c r="K449" s="55"/>
     </row>
-    <row r="450" spans="1:11">
+    <row r="450" spans="1:11" hidden="1">
       <c r="A450" s="4">
         <v>449</v>
       </c>
@@ -21119,7 +21127,7 @@
       </c>
       <c r="K450" s="55"/>
     </row>
-    <row r="451" spans="1:11">
+    <row r="451" spans="1:11" hidden="1">
       <c r="A451" s="4">
         <v>450</v>
       </c>
@@ -21152,7 +21160,7 @@
       </c>
       <c r="K451" s="55"/>
     </row>
-    <row r="452" spans="1:11">
+    <row r="452" spans="1:11" hidden="1">
       <c r="A452" s="4">
         <v>451</v>
       </c>
@@ -21185,7 +21193,7 @@
       </c>
       <c r="K452" s="55"/>
     </row>
-    <row r="453" spans="1:11">
+    <row r="453" spans="1:11" hidden="1">
       <c r="A453" s="4">
         <v>452</v>
       </c>
@@ -21218,7 +21226,7 @@
       </c>
       <c r="K453" s="55"/>
     </row>
-    <row r="454" spans="1:11">
+    <row r="454" spans="1:11" hidden="1">
       <c r="A454" s="4">
         <v>453</v>
       </c>
@@ -21251,7 +21259,7 @@
       </c>
       <c r="K454" s="55"/>
     </row>
-    <row r="455" spans="1:11">
+    <row r="455" spans="1:11" hidden="1">
       <c r="A455" s="4">
         <v>454</v>
       </c>
@@ -21284,7 +21292,7 @@
       </c>
       <c r="K455" s="55"/>
     </row>
-    <row r="456" spans="1:11">
+    <row r="456" spans="1:11" hidden="1">
       <c r="A456" s="4">
         <v>455</v>
       </c>
@@ -21317,7 +21325,7 @@
       </c>
       <c r="K456" s="55"/>
     </row>
-    <row r="457" spans="1:11">
+    <row r="457" spans="1:11" hidden="1">
       <c r="A457" s="4">
         <v>456</v>
       </c>
@@ -21350,7 +21358,7 @@
       </c>
       <c r="K457" s="55"/>
     </row>
-    <row r="458" spans="1:11">
+    <row r="458" spans="1:11" hidden="1">
       <c r="A458" s="4">
         <v>457</v>
       </c>
@@ -21383,7 +21391,7 @@
       </c>
       <c r="K458" s="55"/>
     </row>
-    <row r="459" spans="1:11">
+    <row r="459" spans="1:11" hidden="1">
       <c r="A459" s="4">
         <v>458</v>
       </c>
@@ -21416,7 +21424,7 @@
       </c>
       <c r="K459" s="55"/>
     </row>
-    <row r="460" spans="1:11">
+    <row r="460" spans="1:11" hidden="1">
       <c r="A460" s="4">
         <v>459</v>
       </c>
@@ -21449,7 +21457,7 @@
       </c>
       <c r="K460" s="55"/>
     </row>
-    <row r="461" spans="1:11">
+    <row r="461" spans="1:11" hidden="1">
       <c r="A461" s="4">
         <v>460</v>
       </c>
@@ -21482,7 +21490,7 @@
       </c>
       <c r="K461" s="55"/>
     </row>
-    <row r="462" spans="1:11">
+    <row r="462" spans="1:11" hidden="1">
       <c r="A462" s="4">
         <v>461</v>
       </c>
@@ -21515,7 +21523,7 @@
       </c>
       <c r="K462" s="55"/>
     </row>
-    <row r="463" spans="1:11">
+    <row r="463" spans="1:11" hidden="1">
       <c r="A463" s="4">
         <v>462</v>
       </c>
@@ -21548,7 +21556,7 @@
       </c>
       <c r="K463" s="55"/>
     </row>
-    <row r="464" spans="1:11">
+    <row r="464" spans="1:11" hidden="1">
       <c r="A464" s="4">
         <v>463</v>
       </c>
@@ -21581,7 +21589,7 @@
       </c>
       <c r="K464" s="55"/>
     </row>
-    <row r="465" spans="1:11">
+    <row r="465" spans="1:11" hidden="1">
       <c r="A465" s="4">
         <v>464</v>
       </c>
@@ -21614,7 +21622,7 @@
       </c>
       <c r="K465" s="55"/>
     </row>
-    <row r="466" spans="1:11">
+    <row r="466" spans="1:11" hidden="1">
       <c r="A466" s="4">
         <v>465</v>
       </c>
@@ -21647,7 +21655,7 @@
       </c>
       <c r="K466" s="55"/>
     </row>
-    <row r="467" spans="1:11">
+    <row r="467" spans="1:11" hidden="1">
       <c r="A467" s="4">
         <v>466</v>
       </c>
@@ -21680,7 +21688,7 @@
       </c>
       <c r="K467" s="55"/>
     </row>
-    <row r="468" spans="1:11">
+    <row r="468" spans="1:11" hidden="1">
       <c r="A468" s="4">
         <v>467</v>
       </c>
@@ -21713,7 +21721,7 @@
       </c>
       <c r="K468" s="55"/>
     </row>
-    <row r="469" spans="1:11">
+    <row r="469" spans="1:11" hidden="1">
       <c r="A469" s="4">
         <v>468</v>
       </c>
@@ -21746,7 +21754,7 @@
       </c>
       <c r="K469" s="55"/>
     </row>
-    <row r="470" spans="1:11">
+    <row r="470" spans="1:11" hidden="1">
       <c r="A470" s="4">
         <v>469</v>
       </c>
@@ -21779,7 +21787,7 @@
       </c>
       <c r="K470" s="55"/>
     </row>
-    <row r="471" spans="1:11">
+    <row r="471" spans="1:11" hidden="1">
       <c r="A471" s="4">
         <v>470</v>
       </c>
@@ -21812,7 +21820,7 @@
       </c>
       <c r="K471" s="55"/>
     </row>
-    <row r="472" spans="1:11">
+    <row r="472" spans="1:11" hidden="1">
       <c r="A472" s="4">
         <v>471</v>
       </c>
@@ -21845,7 +21853,7 @@
       </c>
       <c r="K472" s="55"/>
     </row>
-    <row r="473" spans="1:11">
+    <row r="473" spans="1:11" hidden="1">
       <c r="A473" s="4">
         <v>472</v>
       </c>
@@ -21880,7 +21888,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="474" spans="1:11">
+    <row r="474" spans="1:11" hidden="1">
       <c r="A474" s="4">
         <v>473</v>
       </c>
@@ -21915,7 +21923,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="475" spans="1:11">
+    <row r="475" spans="1:11" hidden="1">
       <c r="A475" s="4">
         <v>474</v>
       </c>
@@ -21950,7 +21958,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="476" spans="1:11">
+    <row r="476" spans="1:11" hidden="1">
       <c r="A476" s="4">
         <v>475</v>
       </c>
@@ -21985,7 +21993,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="477" spans="1:11">
+    <row r="477" spans="1:11" hidden="1">
       <c r="A477" s="4">
         <v>476</v>
       </c>
@@ -22020,7 +22028,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="478" spans="1:11">
+    <row r="478" spans="1:11" hidden="1">
       <c r="A478" s="4">
         <v>477</v>
       </c>
@@ -22055,7 +22063,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="479" spans="1:11">
+    <row r="479" spans="1:11" hidden="1">
       <c r="A479" s="4">
         <v>478</v>
       </c>
@@ -22090,7 +22098,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="480" spans="1:11">
+    <row r="480" spans="1:11" hidden="1">
       <c r="A480" s="4">
         <v>479</v>
       </c>
@@ -22125,7 +22133,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="481" spans="1:11">
+    <row r="481" spans="1:11" hidden="1">
       <c r="A481" s="4">
         <v>480</v>
       </c>
@@ -22160,7 +22168,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="482" spans="1:11">
+    <row r="482" spans="1:11" hidden="1">
       <c r="A482" s="4">
         <v>481</v>
       </c>
@@ -22195,7 +22203,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="483" spans="1:11">
+    <row r="483" spans="1:11" hidden="1">
       <c r="A483" s="4">
         <v>482</v>
       </c>
@@ -22230,7 +22238,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="484" spans="1:11">
+    <row r="484" spans="1:11" hidden="1">
       <c r="A484" s="4">
         <v>483</v>
       </c>
@@ -22265,7 +22273,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="485" spans="1:11">
+    <row r="485" spans="1:11" hidden="1">
       <c r="A485" s="4">
         <v>484</v>
       </c>
@@ -22300,7 +22308,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="486" spans="1:11">
+    <row r="486" spans="1:11" hidden="1">
       <c r="A486" s="4">
         <v>485</v>
       </c>
@@ -22335,7 +22343,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="487" spans="1:11">
+    <row r="487" spans="1:11" hidden="1">
       <c r="A487" s="4">
         <v>486</v>
       </c>
@@ -22370,7 +22378,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="488" spans="1:11">
+    <row r="488" spans="1:11" hidden="1">
       <c r="A488" s="4">
         <v>487</v>
       </c>
@@ -22405,7 +22413,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="489" spans="1:11">
+    <row r="489" spans="1:11" hidden="1">
       <c r="A489" s="4">
         <v>488</v>
       </c>
@@ -22440,7 +22448,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="490" spans="1:11">
+    <row r="490" spans="1:11" hidden="1">
       <c r="A490" s="4">
         <v>489</v>
       </c>
@@ -22473,7 +22481,7 @@
       </c>
       <c r="K490" s="24"/>
     </row>
-    <row r="491" spans="1:11">
+    <row r="491" spans="1:11" hidden="1">
       <c r="A491" s="4">
         <v>490</v>
       </c>
@@ -22508,7 +22516,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="492" spans="1:11">
+    <row r="492" spans="1:11" hidden="1">
       <c r="A492" s="4">
         <v>491</v>
       </c>
@@ -22543,7 +22551,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="493" spans="1:11">
+    <row r="493" spans="1:11" hidden="1">
       <c r="A493" s="4">
         <v>492</v>
       </c>
@@ -22578,7 +22586,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="494" spans="1:11">
+    <row r="494" spans="1:11" hidden="1">
       <c r="A494" s="4">
         <v>493</v>
       </c>
@@ -22613,7 +22621,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="495" spans="1:11">
+    <row r="495" spans="1:11" hidden="1">
       <c r="A495" s="4">
         <v>494</v>
       </c>
@@ -22648,7 +22656,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="496" spans="1:11">
+    <row r="496" spans="1:11" hidden="1">
       <c r="A496" s="4">
         <v>495</v>
       </c>
@@ -22683,7 +22691,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="497" spans="1:11">
+    <row r="497" spans="1:11" hidden="1">
       <c r="A497" s="4">
         <v>496</v>
       </c>
@@ -22718,7 +22726,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="498" spans="1:11">
+    <row r="498" spans="1:11" hidden="1">
       <c r="A498" s="4">
         <v>497</v>
       </c>
@@ -22753,7 +22761,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="499" spans="1:11">
+    <row r="499" spans="1:11" hidden="1">
       <c r="A499" s="4">
         <v>498</v>
       </c>
@@ -22788,7 +22796,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="500" spans="1:11">
+    <row r="500" spans="1:11" hidden="1">
       <c r="A500" s="4">
         <v>499</v>
       </c>
@@ -22823,7 +22831,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="501" spans="1:11">
+    <row r="501" spans="1:11" hidden="1">
       <c r="A501" s="4">
         <v>500</v>
       </c>
@@ -22858,7 +22866,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="502" spans="1:11">
+    <row r="502" spans="1:11" hidden="1">
       <c r="A502" s="4">
         <v>501</v>
       </c>
@@ -22926,7 +22934,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="504" spans="1:11">
+    <row r="504" spans="1:11" hidden="1">
       <c r="A504" s="4">
         <v>503</v>
       </c>
@@ -22959,7 +22967,7 @@
       </c>
       <c r="K504" s="24"/>
     </row>
-    <row r="505" spans="1:11">
+    <row r="505" spans="1:11" hidden="1">
       <c r="A505" s="4">
         <v>504</v>
       </c>
@@ -22992,7 +23000,7 @@
       </c>
       <c r="K505" s="24"/>
     </row>
-    <row r="506" spans="1:11">
+    <row r="506" spans="1:11" hidden="1">
       <c r="A506" s="4">
         <v>505</v>
       </c>
@@ -23014,7 +23022,9 @@
       <c r="G506" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H506" s="1"/>
+      <c r="H506" s="1" t="s">
+        <v>1471</v>
+      </c>
       <c r="I506" s="23">
         <v>46197</v>
       </c>
@@ -23025,7 +23035,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="507" spans="1:11">
+    <row r="507" spans="1:11" hidden="1">
       <c r="A507" s="4">
         <v>506</v>
       </c>
@@ -23157,7 +23167,7 @@
       </c>
       <c r="K510" s="24"/>
     </row>
-    <row r="511" spans="1:11">
+    <row r="511" spans="1:11" hidden="1">
       <c r="A511" s="4">
         <v>510</v>
       </c>
@@ -23190,7 +23200,7 @@
       </c>
       <c r="K511" s="24"/>
     </row>
-    <row r="512" spans="1:11">
+    <row r="512" spans="1:11" hidden="1">
       <c r="A512" s="4">
         <v>511</v>
       </c>
@@ -23234,22 +23244,22 @@
         <v>83</v>
       </c>
       <c r="D513" s="2" t="s">
-        <v>1356</v>
+        <v>1468</v>
       </c>
       <c r="E513" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F513" s="1" t="s">
-        <v>521</v>
+        <v>1453</v>
       </c>
       <c r="G513" s="1" t="s">
         <v>30</v>
       </c>
       <c r="H513" s="1" t="s">
-        <v>1357</v>
+        <v>1339</v>
       </c>
       <c r="I513" s="54">
-        <v>46279</v>
+        <v>46322</v>
       </c>
       <c r="J513" s="4" t="s">
         <v>574</v>
@@ -23267,29 +23277,29 @@
         <v>83</v>
       </c>
       <c r="D514" s="2" t="s">
-        <v>1356</v>
+        <v>1469</v>
       </c>
       <c r="E514" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F514" s="1" t="s">
-        <v>521</v>
+        <v>1470</v>
       </c>
       <c r="G514" s="1" t="s">
         <v>30</v>
       </c>
       <c r="H514" s="1" t="s">
-        <v>1357</v>
+        <v>1339</v>
       </c>
       <c r="I514" s="54">
-        <v>46279</v>
+        <v>46322</v>
       </c>
       <c r="J514" s="4" t="s">
         <v>574</v>
       </c>
       <c r="K514" s="55"/>
     </row>
-    <row r="515" spans="1:11">
+    <row r="515" spans="1:11" hidden="1">
       <c r="A515" s="4">
         <v>514</v>
       </c>
@@ -23322,7 +23332,7 @@
       </c>
       <c r="K515" s="55"/>
     </row>
-    <row r="516" spans="1:11">
+    <row r="516" spans="1:11" hidden="1">
       <c r="A516" s="4">
         <v>515</v>
       </c>
@@ -23355,7 +23365,7 @@
       </c>
       <c r="K516" s="55"/>
     </row>
-    <row r="517" spans="1:11">
+    <row r="517" spans="1:11" hidden="1">
       <c r="A517" s="4">
         <v>516</v>
       </c>
@@ -23388,7 +23398,7 @@
       </c>
       <c r="K517" s="55"/>
     </row>
-    <row r="518" spans="1:11">
+    <row r="518" spans="1:11" hidden="1">
       <c r="A518" s="4">
         <v>517</v>
       </c>
@@ -25151,7 +25161,7 @@
       </c>
       <c r="K570" s="55"/>
     </row>
-    <row r="571" spans="1:11">
+    <row r="571" spans="1:11" hidden="1">
       <c r="A571" s="4">
         <v>570</v>
       </c>
@@ -25252,7 +25262,7 @@
       </c>
       <c r="K573" s="55"/>
     </row>
-    <row r="574" spans="1:11">
+    <row r="574" spans="1:11" hidden="1">
       <c r="A574" s="4">
         <v>573</v>
       </c>
@@ -25285,7 +25295,7 @@
       </c>
       <c r="K574" s="55"/>
     </row>
-    <row r="575" spans="1:11">
+    <row r="575" spans="1:11" hidden="1">
       <c r="A575" s="4">
         <v>574</v>
       </c>
@@ -25318,7 +25328,7 @@
       </c>
       <c r="K575" s="55"/>
     </row>
-    <row r="576" spans="1:11">
+    <row r="576" spans="1:11" hidden="1">
       <c r="A576" s="4">
         <v>575</v>
       </c>
@@ -25351,7 +25361,7 @@
       </c>
       <c r="K576" s="55"/>
     </row>
-    <row r="577" spans="1:11">
+    <row r="577" spans="1:11" hidden="1">
       <c r="A577" s="4">
         <v>576</v>
       </c>
@@ -25384,7 +25394,7 @@
       </c>
       <c r="K577" s="55"/>
     </row>
-    <row r="578" spans="1:11">
+    <row r="578" spans="1:11" hidden="1">
       <c r="A578" s="4">
         <v>577</v>
       </c>
@@ -25417,7 +25427,7 @@
       </c>
       <c r="K578" s="55"/>
     </row>
-    <row r="579" spans="1:11">
+    <row r="579" spans="1:11" hidden="1">
       <c r="A579" s="4">
         <v>578</v>
       </c>
@@ -25450,7 +25460,7 @@
       </c>
       <c r="K579" s="55"/>
     </row>
-    <row r="580" spans="1:11">
+    <row r="580" spans="1:11" hidden="1">
       <c r="A580" s="4">
         <v>579</v>
       </c>
@@ -25483,7 +25493,7 @@
       </c>
       <c r="K580" s="55"/>
     </row>
-    <row r="581" spans="1:11">
+    <row r="581" spans="1:11" hidden="1">
       <c r="A581" s="4">
         <v>580</v>
       </c>
@@ -25516,7 +25526,7 @@
       </c>
       <c r="K581" s="55"/>
     </row>
-    <row r="582" spans="1:11">
+    <row r="582" spans="1:11" hidden="1">
       <c r="A582" s="4">
         <v>581</v>
       </c>
@@ -25549,7 +25559,7 @@
       </c>
       <c r="K582" s="55"/>
     </row>
-    <row r="583" spans="1:11">
+    <row r="583" spans="1:11" hidden="1">
       <c r="A583" s="4">
         <v>582</v>
       </c>
@@ -25582,7 +25592,7 @@
       </c>
       <c r="K583" s="24"/>
     </row>
-    <row r="584" spans="1:11">
+    <row r="584" spans="1:11" hidden="1">
       <c r="A584" s="4">
         <v>583</v>
       </c>
@@ -25617,127 +25627,122 @@
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="D1:D517 D519:D1048576">
-    <cfRule type="duplicateValues" dxfId="49" priority="24"/>
+  <conditionalFormatting sqref="D519:D1048576 D1:D517">
+    <cfRule type="duplicateValues" dxfId="48" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D268">
-    <cfRule type="duplicateValues" dxfId="48" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D366">
-    <cfRule type="duplicateValues" dxfId="45" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D367">
-    <cfRule type="duplicateValues" dxfId="44" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="112"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D502 D2:D367">
-    <cfRule type="duplicateValues" dxfId="43" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="103"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D518">
+    <cfRule type="duplicateValues" dxfId="41" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:E258 G215 E525:E1048576">
-    <cfRule type="cellIs" dxfId="42" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="33" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E260:E524">
-    <cfRule type="cellIs" dxfId="41" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="29" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F252 F254:F255 F257:F387 F389:F559 F561:F562 F564:F1048576">
-    <cfRule type="cellIs" dxfId="40" priority="26" operator="equal">
+  <conditionalFormatting sqref="F1:F252 F254:F255 F257:F387 F561:F562 F564:F1048576 F389:F559">
+    <cfRule type="cellIs" dxfId="38" priority="26" operator="equal">
       <formula>"DOADORA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F252 F254:F255 F561:F562 F564:F1048576">
-    <cfRule type="cellIs" dxfId="39" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="34" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F252 F389:F559 F254:F255 F257:F387 F561:F562 F564:F1048576">
-    <cfRule type="cellIs" dxfId="38" priority="25" operator="equal">
+  <conditionalFormatting sqref="F1:F252 F254:F255 F257:F387 F561:F562 F564:F1048576 F389:F559">
+    <cfRule type="cellIs" dxfId="36" priority="25" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F252">
-    <cfRule type="cellIs" dxfId="37" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="5" operator="equal">
       <formula>"DEPOSITO SOLAGOS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F18">
-    <cfRule type="cellIs" dxfId="36" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="9" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F25">
-    <cfRule type="cellIs" dxfId="35" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="4" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F254:F255 F561:F562 F564:F1048576">
-    <cfRule type="cellIs" dxfId="34" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="35" operator="equal">
       <formula>"DEPOSITO SOLAGOS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F257:F387 F389:F559">
-    <cfRule type="cellIs" dxfId="33" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="30" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F257:F387">
-    <cfRule type="cellIs" dxfId="32" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="31" operator="equal">
       <formula>"DEPOSITO SOLAGOS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F389:F559">
-    <cfRule type="cellIs" dxfId="31" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="7" operator="equal">
       <formula>"DEPOSITO SOLAGOS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F555">
-    <cfRule type="cellIs" dxfId="30" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="6" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:H258">
-    <cfRule type="cellIs" dxfId="29" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="8" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H260:H517 H519:H524">
-    <cfRule type="cellIs" dxfId="28" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="12" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H526:H547 H549:H584">
-    <cfRule type="cellIs" dxfId="27" priority="16" operator="equal">
+  <conditionalFormatting sqref="H518">
+    <cfRule type="duplicateValues" dxfId="25" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H526:H584">
+    <cfRule type="cellIs" dxfId="24" priority="3" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K215">
-    <cfRule type="cellIs" dxfId="26" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="20" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="21" operator="equal">
       <formula>"DOADORA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="22" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="23" operator="equal">
       <formula>"DEPOSITO SOLAGOS"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H548">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
-      <formula>"SOLAGOS DEPOSITO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H518">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D518">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -28134,51 +28139,51 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="D2:D51">
-    <cfRule type="duplicateValues" dxfId="22" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D52">
-    <cfRule type="duplicateValues" dxfId="21" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D53">
-    <cfRule type="duplicateValues" dxfId="20" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E51">
-    <cfRule type="cellIs" dxfId="17" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="16" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E52:E53">
-    <cfRule type="cellIs" dxfId="16" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="5" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F51">
-    <cfRule type="cellIs" dxfId="15" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="17" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="18" operator="equal">
       <formula>"DOADORA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="20" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="21" operator="equal">
       <formula>"DEPOSITO SOLAGOS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F52:F53">
-    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
       <formula>"DOADORA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="8" operator="equal">
       <formula>"DEPOSITO SOLAGOS"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28339,21 +28344,21 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
-    <cfRule type="cellIs" dxfId="7" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="23" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B8">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"DOADORA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"DEPOSITO SOLAGOS"</formula>
     </cfRule>
   </conditionalFormatting>
